--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -762,7 +762,7 @@
     <t>护体神戒</t>
   </si>
   <si>
-    <t>附加一个生命*{1}%盾，CD60S</t>
+    <t>附加一个面板生命*{1}%盾，CD60S</t>
   </si>
   <si>
     <t>复活神戒</t>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -582,7 +582,7 @@
     <t>免疫{2}秒控制</t>
   </si>
   <si>
-    <t>"401,5,0,0","6,360,3,1","9,360,3,0"</t>
+    <t>"401,20,0,0","6,360,3,1","9,360,3,0"</t>
   </si>
   <si>
     <t>开天斩</t>
@@ -1813,7 +1813,7 @@
     <col min="28" max="29" width="7.875" style="2" customWidth="1"/>
     <col min="30" max="30" width="12.625" style="2" customWidth="1"/>
     <col min="31" max="31" width="9.625" style="2" customWidth="1"/>
-    <col min="32" max="32" width="23.25" style="2" customWidth="1"/>
+    <col min="32" max="32" width="27.625" style="2" customWidth="1"/>
     <col min="33" max="33" width="17.875" style="2" customWidth="1"/>
     <col min="34" max="34" width="19.75" style="2" customWidth="1"/>
     <col min="35" max="35" width="9" style="2"/>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2854,7 +2854,7 @@
         <v>87</v>
       </c>
       <c r="U13" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="V13" s="1">
         <v>0</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3157,7 +3157,7 @@
         <v>4</v>
       </c>
       <c r="Y16" s="1">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="Z16" s="1">
         <v>100</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -176,7 +176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R3" authorId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -199,7 +199,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0">
+    <comment ref="T3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -223,7 +223,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0">
+    <comment ref="U3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -249,7 +249,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y3" authorId="0">
+    <comment ref="Z3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -271,7 +271,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF3" authorId="0">
+    <comment ref="AG3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -298,7 +298,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="171">
   <si>
     <t>_ID</t>
   </si>
@@ -337,6 +337,9 @@
   </si>
   <si>
     <t>RiseMaxLevel</t>
+  </si>
+  <si>
+    <t>MythRate</t>
   </si>
   <si>
     <t>等级成长</t>
@@ -1785,7 +1788,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:AJ77"/>
+  <dimension ref="C3:AK77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="5.625" style="2" customWidth="1"/>
@@ -1801,27 +1804,27 @@
     <col min="12" max="12" width="8.375" style="2" customWidth="1"/>
     <col min="13" max="13" width="5.875" style="2" customWidth="1"/>
     <col min="14" max="14" width="7.50833333333333" style="2" customWidth="1"/>
-    <col min="15" max="15" width="12.875" style="2" customWidth="1"/>
-    <col min="16" max="17" width="13.5" style="2" customWidth="1"/>
-    <col min="18" max="18" width="7.375" style="2" customWidth="1"/>
-    <col min="19" max="19" width="7.50833333333333" style="2" customWidth="1"/>
-    <col min="20" max="20" width="8.25" style="2" customWidth="1"/>
-    <col min="21" max="21" width="6.5" style="2" customWidth="1"/>
-    <col min="22" max="24" width="7.625" style="2" customWidth="1"/>
-    <col min="25" max="26" width="7.875" style="2" customWidth="1"/>
-    <col min="27" max="27" width="9.625" style="2" customWidth="1"/>
-    <col min="28" max="29" width="7.875" style="2" customWidth="1"/>
-    <col min="30" max="30" width="12.625" style="2" customWidth="1"/>
-    <col min="31" max="31" width="9.625" style="2" customWidth="1"/>
-    <col min="32" max="32" width="27.625" style="2" customWidth="1"/>
-    <col min="33" max="33" width="17.875" style="2" customWidth="1"/>
-    <col min="34" max="34" width="19.75" style="2" customWidth="1"/>
-    <col min="35" max="35" width="9" style="2"/>
-    <col min="36" max="36" width="19.25" style="2" customWidth="1"/>
-    <col min="37" max="16384" width="9" style="2"/>
+    <col min="15" max="16" width="12.875" style="2" customWidth="1"/>
+    <col min="17" max="18" width="13.5" style="2" customWidth="1"/>
+    <col min="19" max="19" width="7.375" style="2" customWidth="1"/>
+    <col min="20" max="20" width="7.50833333333333" style="2" customWidth="1"/>
+    <col min="21" max="21" width="8.25" style="2" customWidth="1"/>
+    <col min="22" max="22" width="6.5" style="2" customWidth="1"/>
+    <col min="23" max="25" width="7.625" style="2" customWidth="1"/>
+    <col min="26" max="27" width="7.875" style="2" customWidth="1"/>
+    <col min="28" max="28" width="9.625" style="2" customWidth="1"/>
+    <col min="29" max="30" width="7.875" style="2" customWidth="1"/>
+    <col min="31" max="31" width="12.625" style="2" customWidth="1"/>
+    <col min="32" max="32" width="9.625" style="2" customWidth="1"/>
+    <col min="33" max="33" width="27.625" style="2" customWidth="1"/>
+    <col min="34" max="34" width="17.875" style="2" customWidth="1"/>
+    <col min="35" max="35" width="19.75" style="2" customWidth="1"/>
+    <col min="36" max="36" width="9" style="2"/>
+    <col min="37" max="37" width="19.25" style="2" customWidth="1"/>
+    <col min="38" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:36">
+    <row r="3" spans="3:37">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1865,7 +1868,7 @@
         <v>13</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R3" s="3" t="s">
         <v>14</v>
@@ -1918,55 +1921,58 @@
       <c r="AH3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AI3" s="2" t="s">
+      <c r="AI3" s="3" t="s">
         <v>31</v>
       </c>
       <c r="AJ3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="AK3" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="4" spans="3:34">
+    <row r="4" spans="3:35">
       <c r="C4" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="Q4" s="3" t="s">
         <v>45</v>
@@ -2020,108 +2026,114 @@
         <v>61</v>
       </c>
       <c r="AH4" s="3" t="s">
-        <v>30</v>
+        <v>62</v>
+      </c>
+      <c r="AI4" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="5" spans="3:34">
+    <row r="5" spans="3:35">
       <c r="C5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="I5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="K5" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="L5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S5" s="3" t="s">
         <v>63</v>
       </c>
       <c r="T5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="U5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="V5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="U5" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="V5" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="W5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Y5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AB5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AC5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AD5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AE5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AF5" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AG5" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AH5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="AI5" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="3:34">
+    <row r="6" s="1" customFormat="1" spans="3:35">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
@@ -2129,10 +2141,10 @@
         <v>1001</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -2144,7 +2156,7 @@
         <v>10</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K6" s="1">
         <v>0</v>
@@ -2162,38 +2174,39 @@
         <v>60</v>
       </c>
       <c r="P6" s="1">
-        <v>1</v>
+        <f t="shared" ref="P6:P16" si="0">N6*5</f>
+        <v>3000</v>
       </c>
       <c r="Q6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="1">
-        <v>1</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>67</v>
+        <v>0</v>
+      </c>
+      <c r="S6" s="1">
+        <v>1</v>
       </c>
       <c r="T6" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="U6" s="1">
-        <v>0</v>
+      <c r="U6" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="V6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" s="1">
         <v>0</v>
       </c>
       <c r="Y6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="1">
         <v>120</v>
       </c>
-      <c r="Z6" s="1">
-        <v>0</v>
-      </c>
       <c r="AA6" s="1">
         <v>0</v>
       </c>
@@ -2209,14 +2222,17 @@
       <c r="AE6" s="1">
         <v>0</v>
       </c>
-      <c r="AG6" s="1">
-        <v>50</v>
+      <c r="AF6" s="1">
+        <v>0</v>
       </c>
       <c r="AH6" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI6" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" spans="3:34">
+    <row r="7" s="1" customFormat="1" spans="3:35">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
@@ -2224,10 +2240,10 @@
         <v>1002</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -2239,7 +2255,7 @@
         <v>10</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K7" s="1">
         <v>0</v>
@@ -2257,43 +2273,44 @@
         <v>60</v>
       </c>
       <c r="P7" s="1">
+        <f t="shared" si="0"/>
+        <v>3000</v>
+      </c>
+      <c r="Q7" s="1">
         <v>2</v>
       </c>
-      <c r="Q7" s="1">
-        <v>0</v>
-      </c>
       <c r="R7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1">
         <v>2</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="T7" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="U7" s="1">
-        <v>0</v>
+      <c r="U7" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="V7" s="1">
+        <v>0</v>
+      </c>
+      <c r="W7" s="1">
         <v>2</v>
       </c>
-      <c r="W7" s="1">
-        <v>0</v>
-      </c>
       <c r="X7" s="1">
         <v>0</v>
       </c>
       <c r="Y7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="1">
         <v>150</v>
       </c>
-      <c r="Z7" s="1">
-        <v>0</v>
-      </c>
       <c r="AA7" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AC7" s="1">
         <v>0</v>
@@ -2304,14 +2321,17 @@
       <c r="AE7" s="1">
         <v>0</v>
       </c>
-      <c r="AG7" s="1">
-        <v>50</v>
+      <c r="AF7" s="1">
+        <v>0</v>
       </c>
       <c r="AH7" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI7" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" spans="3:34">
+    <row r="8" s="1" customFormat="1" spans="3:35">
       <c r="C8" s="1">
         <v>1003</v>
       </c>
@@ -2319,10 +2339,10 @@
         <v>1003</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -2334,7 +2354,7 @@
         <v>10</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K8" s="1">
         <v>5</v>
@@ -2352,38 +2372,39 @@
         <v>60</v>
       </c>
       <c r="P8" s="1">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>3000</v>
       </c>
       <c r="Q8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" s="1">
-        <v>1</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>67</v>
+        <v>0</v>
+      </c>
+      <c r="S8" s="1">
+        <v>1</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="U8" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="V8" s="1">
+        <v>0</v>
+      </c>
+      <c r="W8" s="1">
         <v>5</v>
       </c>
-      <c r="W8" s="1">
-        <v>0</v>
-      </c>
       <c r="X8" s="1">
         <v>0</v>
       </c>
       <c r="Y8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="1">
         <v>100</v>
       </c>
-      <c r="Z8" s="1">
-        <v>0</v>
-      </c>
       <c r="AA8" s="1">
         <v>0</v>
       </c>
@@ -2399,17 +2420,20 @@
       <c r="AE8" s="1">
         <v>0</v>
       </c>
-      <c r="AF8" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AG8" s="1">
-        <v>50</v>
+      <c r="AF8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="AH8" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI8" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" spans="3:34">
+    <row r="9" s="1" customFormat="1" spans="3:35">
       <c r="C9" s="1">
         <v>1004</v>
       </c>
@@ -2417,10 +2441,10 @@
         <v>1004</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G9" s="1">
         <v>7</v>
@@ -2432,7 +2456,7 @@
         <v>10</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K9" s="1">
         <v>10</v>
@@ -2450,38 +2474,39 @@
         <v>60</v>
       </c>
       <c r="P9" s="1">
+        <f t="shared" si="0"/>
+        <v>3000</v>
+      </c>
+      <c r="Q9" s="1">
         <v>4</v>
       </c>
-      <c r="Q9" s="1">
-        <v>0</v>
-      </c>
       <c r="R9" s="1">
+        <v>0</v>
+      </c>
+      <c r="S9" s="1">
         <v>4</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="T9" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="U9" s="1">
+      <c r="U9" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="V9" s="1">
         <v>2</v>
       </c>
-      <c r="V9" s="1">
-        <v>1</v>
-      </c>
       <c r="W9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" s="1">
         <v>0</v>
       </c>
       <c r="Y9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="1">
         <v>200</v>
       </c>
-      <c r="Z9" s="1">
-        <v>0</v>
-      </c>
       <c r="AA9" s="1">
         <v>0</v>
       </c>
@@ -2497,17 +2522,20 @@
       <c r="AE9" s="1">
         <v>0</v>
       </c>
-      <c r="AF9" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG9" s="1">
-        <v>50</v>
+      <c r="AF9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="AH9" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI9" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" spans="3:34">
+    <row r="10" s="1" customFormat="1" spans="3:35">
       <c r="C10" s="1">
         <v>1005</v>
       </c>
@@ -2515,10 +2543,10 @@
         <v>1005</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G10" s="1">
         <v>5</v>
@@ -2530,7 +2558,7 @@
         <v>50</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K10" s="1">
         <v>55</v>
@@ -2548,26 +2576,27 @@
         <v>20</v>
       </c>
       <c r="P10" s="1">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>1000</v>
       </c>
       <c r="Q10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" s="1">
         <v>0</v>
       </c>
-      <c r="S10" s="1" t="s">
-        <v>67</v>
+      <c r="S10" s="1">
+        <v>0</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U10" s="1">
+        <v>68</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="V10" s="1">
         <v>30</v>
       </c>
-      <c r="V10" s="1">
-        <v>0</v>
-      </c>
       <c r="W10" s="1">
         <v>0</v>
       </c>
@@ -2575,11 +2604,11 @@
         <v>0</v>
       </c>
       <c r="Y10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="1">
         <v>100</v>
       </c>
-      <c r="Z10" s="1">
-        <v>0</v>
-      </c>
       <c r="AA10" s="1">
         <v>0</v>
       </c>
@@ -2595,17 +2624,20 @@
       <c r="AE10" s="1">
         <v>0</v>
       </c>
-      <c r="AF10" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG10" s="1">
-        <v>50</v>
+      <c r="AF10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="5" t="s">
+        <v>85</v>
       </c>
       <c r="AH10" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI10" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" spans="3:34">
+    <row r="11" s="1" customFormat="1" spans="3:35">
       <c r="C11" s="1">
         <v>1006</v>
       </c>
@@ -2613,10 +2645,10 @@
         <v>1006</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G11" s="1">
         <v>6</v>
@@ -2628,7 +2660,7 @@
         <v>10</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K11" s="1">
         <v>0</v>
@@ -2646,22 +2678,23 @@
         <v>20</v>
       </c>
       <c r="P11" s="1">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>1000</v>
       </c>
       <c r="Q11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" s="1">
         <v>0</v>
       </c>
-      <c r="S11" s="1" t="s">
-        <v>67</v>
+      <c r="S11" s="1">
+        <v>0</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="U11" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="V11" s="1">
         <v>0</v>
@@ -2673,10 +2706,10 @@
         <v>0</v>
       </c>
       <c r="Y11" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AA11" s="1">
         <v>0</v>
@@ -2693,14 +2726,17 @@
       <c r="AE11" s="1">
         <v>0</v>
       </c>
-      <c r="AG11" s="1">
-        <v>50</v>
+      <c r="AF11" s="1">
+        <v>0</v>
       </c>
       <c r="AH11" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI11" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" spans="3:34">
+    <row r="12" s="1" customFormat="1" spans="3:35">
       <c r="C12" s="1">
         <v>1007</v>
       </c>
@@ -2708,10 +2744,10 @@
         <v>1007</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
@@ -2723,7 +2759,7 @@
         <v>10</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K12" s="4">
         <v>5</v>
@@ -2740,44 +2776,45 @@
       <c r="O12" s="1">
         <v>60</v>
       </c>
-      <c r="P12" s="4">
+      <c r="P12" s="1">
+        <f t="shared" si="0"/>
+        <v>3000</v>
+      </c>
+      <c r="Q12" s="4">
         <v>10</v>
       </c>
-      <c r="Q12" s="1">
-        <v>0</v>
-      </c>
       <c r="R12" s="1">
-        <v>1</v>
-      </c>
-      <c r="S12" s="1" t="s">
-        <v>67</v>
+        <v>0</v>
+      </c>
+      <c r="S12" s="1">
+        <v>1</v>
       </c>
       <c r="T12" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="U12" s="1">
-        <v>0</v>
+      <c r="U12" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="V12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X12" s="1">
         <v>0</v>
       </c>
-      <c r="Y12" s="4">
+      <c r="Y12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="4">
         <v>500</v>
       </c>
-      <c r="Z12" s="1">
-        <v>0</v>
-      </c>
       <c r="AA12" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AB12" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AC12" s="1">
         <v>0</v>
@@ -2788,17 +2825,20 @@
       <c r="AE12" s="1">
         <v>0</v>
       </c>
-      <c r="AF12" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="AG12" s="1">
-        <v>50</v>
+      <c r="AF12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="4" t="s">
+        <v>92</v>
       </c>
       <c r="AH12" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI12" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" spans="3:34">
+    <row r="13" s="1" customFormat="1" spans="3:35">
       <c r="C13" s="1">
         <v>1008</v>
       </c>
@@ -2806,10 +2846,10 @@
         <v>1008</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G13" s="1">
         <v>1008</v>
@@ -2821,7 +2861,7 @@
         <v>200</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K13" s="1">
         <v>30</v>
@@ -2839,26 +2879,27 @@
         <v>3</v>
       </c>
       <c r="P13" s="1">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>150</v>
       </c>
       <c r="Q13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" s="1">
         <v>0</v>
       </c>
-      <c r="S13" s="1" t="s">
-        <v>67</v>
+      <c r="S13" s="1">
+        <v>0</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="U13" s="1">
+        <v>68</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="V13" s="1">
         <v>20</v>
       </c>
-      <c r="V13" s="1">
-        <v>0</v>
-      </c>
       <c r="W13" s="1">
         <v>0</v>
       </c>
@@ -2866,11 +2907,11 @@
         <v>0</v>
       </c>
       <c r="Y13" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="1">
         <v>30</v>
       </c>
-      <c r="Z13" s="1">
-        <v>0</v>
-      </c>
       <c r="AA13" s="1">
         <v>0</v>
       </c>
@@ -2886,17 +2927,20 @@
       <c r="AE13" s="1">
         <v>0</v>
       </c>
-      <c r="AF13" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AG13" s="1">
-        <v>50</v>
+      <c r="AF13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="AH13" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI13" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" spans="3:34">
+    <row r="14" s="1" customFormat="1" spans="3:35">
       <c r="C14" s="1">
         <v>1009</v>
       </c>
@@ -2904,10 +2948,10 @@
         <v>1009</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -2919,7 +2963,7 @@
         <v>10</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K14" s="1">
         <v>15</v>
@@ -2937,43 +2981,44 @@
         <v>30</v>
       </c>
       <c r="P14" s="1">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
+      <c r="Q14" s="1">
         <v>12</v>
       </c>
-      <c r="Q14" s="1">
-        <v>0</v>
-      </c>
       <c r="R14" s="1">
+        <v>0</v>
+      </c>
+      <c r="S14" s="1">
         <v>4</v>
-      </c>
-      <c r="S14" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="T14" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="U14" s="1">
-        <v>0</v>
+      <c r="U14" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="V14" s="1">
+        <v>0</v>
+      </c>
+      <c r="W14" s="1">
         <v>4</v>
       </c>
-      <c r="W14" s="1">
-        <v>0</v>
-      </c>
       <c r="X14" s="1">
         <v>0</v>
       </c>
       <c r="Y14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="1">
         <v>600</v>
       </c>
-      <c r="Z14" s="1">
-        <v>0</v>
-      </c>
       <c r="AA14" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AB14" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AC14" s="1">
         <v>0</v>
@@ -2984,17 +3029,20 @@
       <c r="AE14" s="1">
         <v>0</v>
       </c>
-      <c r="AF14" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="AG14" s="1">
-        <v>50</v>
+      <c r="AF14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="AH14" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI14" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" spans="3:34">
+    <row r="15" s="1" customFormat="1" spans="3:35">
       <c r="C15" s="1">
         <v>1010</v>
       </c>
@@ -3002,10 +3050,10 @@
         <v>1010</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G15" s="1">
         <v>1</v>
@@ -3017,7 +3065,7 @@
         <v>10</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K15" s="1">
         <v>0</v>
@@ -3035,22 +3083,23 @@
         <v>1</v>
       </c>
       <c r="P15" s="1">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="Q15" s="1">
         <v>10</v>
       </c>
-      <c r="Q15" s="1">
-        <v>0</v>
-      </c>
       <c r="R15" s="1">
+        <v>0</v>
+      </c>
+      <c r="S15" s="1">
         <v>2</v>
       </c>
-      <c r="S15" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="T15" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="U15" s="1">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="V15" s="1">
         <v>0</v>
@@ -3062,11 +3111,11 @@
         <v>0</v>
       </c>
       <c r="Y15" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="1">
         <v>200</v>
       </c>
-      <c r="Z15" s="1">
-        <v>0</v>
-      </c>
       <c r="AA15" s="1">
         <v>0</v>
       </c>
@@ -3082,14 +3131,17 @@
       <c r="AE15" s="1">
         <v>0</v>
       </c>
-      <c r="AG15" s="1">
-        <v>50</v>
+      <c r="AF15" s="1">
+        <v>0</v>
       </c>
       <c r="AH15" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI15" s="1">
         <v>4102</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" spans="3:34">
+    <row r="16" s="1" customFormat="1" spans="3:35">
       <c r="C16" s="1">
         <v>1011</v>
       </c>
@@ -3097,10 +3149,10 @@
         <v>1011</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G16" s="1">
         <v>8</v>
@@ -3112,7 +3164,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K16" s="1">
         <v>30</v>
@@ -3130,41 +3182,42 @@
         <v>1</v>
       </c>
       <c r="P16" s="1">
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="Q16" s="1">
+        <v>50</v>
+      </c>
+      <c r="R16" s="1">
         <v>10</v>
       </c>
-      <c r="R16" s="1">
+      <c r="S16" s="1">
         <v>3</v>
       </c>
-      <c r="S16" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="T16" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U16" s="1">
+        <v>79</v>
+      </c>
+      <c r="U16" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="V16" s="1">
         <v>15</v>
       </c>
-      <c r="V16" s="1">
+      <c r="W16" s="1">
         <v>5</v>
-      </c>
-      <c r="W16" s="1">
-        <v>4</v>
       </c>
       <c r="X16" s="1">
         <v>4</v>
       </c>
       <c r="Y16" s="1">
+        <v>4</v>
+      </c>
+      <c r="Z16" s="1">
         <v>500</v>
       </c>
-      <c r="Z16" s="1">
+      <c r="AA16" s="1">
         <v>100</v>
       </c>
-      <c r="AA16" s="1">
-        <v>0</v>
-      </c>
       <c r="AB16" s="1">
         <v>0</v>
       </c>
@@ -3177,10 +3230,13 @@
       <c r="AE16" s="1">
         <v>0</v>
       </c>
-      <c r="AG16" s="1">
-        <v>50</v>
+      <c r="AF16" s="1">
+        <v>0</v>
       </c>
       <c r="AH16" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI16" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3188,7 +3244,7 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
     </row>
-    <row r="18" s="1" customFormat="1" spans="3:34">
+    <row r="18" s="1" customFormat="1" spans="3:35">
       <c r="C18" s="1">
         <v>2001</v>
       </c>
@@ -3196,10 +3252,10 @@
         <v>2001</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G18" s="1">
         <v>1</v>
@@ -3211,7 +3267,7 @@
         <v>10</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K18" s="1">
         <v>0</v>
@@ -3229,38 +3285,39 @@
         <v>60</v>
       </c>
       <c r="P18" s="1">
+        <f t="shared" ref="P18:P28" si="1">N18*5</f>
+        <v>3000</v>
+      </c>
+      <c r="Q18" s="1">
         <v>2</v>
       </c>
-      <c r="Q18" s="1">
-        <v>0</v>
-      </c>
       <c r="R18" s="1">
+        <v>0</v>
+      </c>
+      <c r="S18" s="1">
         <v>2</v>
       </c>
-      <c r="S18" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="T18" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="U18" s="1">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="V18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" s="1">
         <v>0</v>
       </c>
       <c r="Y18" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="1">
         <v>120</v>
       </c>
-      <c r="Z18" s="1">
-        <v>0</v>
-      </c>
       <c r="AA18" s="1">
         <v>0</v>
       </c>
@@ -3276,14 +3333,17 @@
       <c r="AE18" s="1">
         <v>0</v>
       </c>
-      <c r="AG18" s="1">
-        <v>50</v>
+      <c r="AF18" s="1">
+        <v>0</v>
       </c>
       <c r="AH18" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI18" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" spans="3:34">
+    <row r="19" s="1" customFormat="1" spans="3:35">
       <c r="C19" s="1">
         <v>2002</v>
       </c>
@@ -3291,10 +3351,10 @@
         <v>2002</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G19" s="1">
         <v>1</v>
@@ -3306,7 +3366,7 @@
         <v>10</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K19" s="1">
         <v>0</v>
@@ -3324,43 +3384,44 @@
         <v>60</v>
       </c>
       <c r="P19" s="1">
+        <f t="shared" si="1"/>
+        <v>3000</v>
+      </c>
+      <c r="Q19" s="1">
         <v>3</v>
       </c>
-      <c r="Q19" s="1">
-        <v>0</v>
-      </c>
       <c r="R19" s="1">
+        <v>0</v>
+      </c>
+      <c r="S19" s="1">
         <v>3</v>
       </c>
-      <c r="S19" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="T19" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="U19" s="1">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="V19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" s="1">
         <v>0</v>
       </c>
       <c r="Y19" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="1">
         <v>150</v>
       </c>
-      <c r="Z19" s="1">
-        <v>0</v>
-      </c>
       <c r="AA19" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AB19" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AC19" s="1">
         <v>0</v>
@@ -3371,14 +3432,17 @@
       <c r="AE19" s="1">
         <v>0</v>
       </c>
-      <c r="AG19" s="1">
-        <v>50</v>
+      <c r="AF19" s="1">
+        <v>0</v>
       </c>
       <c r="AH19" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI19" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" spans="3:34">
+    <row r="20" s="1" customFormat="1" spans="3:35">
       <c r="C20" s="1">
         <v>2003</v>
       </c>
@@ -3386,10 +3450,10 @@
         <v>2003</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G20" s="1">
         <v>3</v>
@@ -3401,7 +3465,7 @@
         <v>10</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K20" s="1">
         <v>10</v>
@@ -3419,38 +3483,39 @@
         <v>60</v>
       </c>
       <c r="P20" s="1">
+        <f t="shared" si="1"/>
+        <v>3000</v>
+      </c>
+      <c r="Q20" s="1">
         <v>2</v>
       </c>
-      <c r="Q20" s="1">
-        <v>0</v>
-      </c>
       <c r="R20" s="1">
+        <v>0</v>
+      </c>
+      <c r="S20" s="1">
         <v>3</v>
       </c>
-      <c r="S20" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="T20" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U20" s="1">
+        <v>79</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="V20" s="1">
         <v>10</v>
       </c>
-      <c r="V20" s="1">
+      <c r="W20" s="1">
         <v>5</v>
-      </c>
-      <c r="W20" s="1">
-        <v>2</v>
       </c>
       <c r="X20" s="1">
         <v>2</v>
       </c>
       <c r="Y20" s="1">
+        <v>2</v>
+      </c>
+      <c r="Z20" s="1">
         <v>80</v>
       </c>
-      <c r="Z20" s="1">
-        <v>0</v>
-      </c>
       <c r="AA20" s="1">
         <v>0</v>
       </c>
@@ -3466,14 +3531,17 @@
       <c r="AE20" s="1">
         <v>0</v>
       </c>
-      <c r="AG20" s="1">
-        <v>50</v>
+      <c r="AF20" s="1">
+        <v>0</v>
       </c>
       <c r="AH20" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI20" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" spans="3:34">
+    <row r="21" s="1" customFormat="1" spans="3:35">
       <c r="C21" s="1">
         <v>2004</v>
       </c>
@@ -3481,10 +3549,10 @@
         <v>2004</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G21" s="1">
         <v>1</v>
@@ -3496,7 +3564,7 @@
         <v>10</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K21" s="1">
         <v>0</v>
@@ -3514,38 +3582,39 @@
         <v>60</v>
       </c>
       <c r="P21" s="1">
+        <f t="shared" si="1"/>
+        <v>3000</v>
+      </c>
+      <c r="Q21" s="1">
         <v>2</v>
       </c>
-      <c r="Q21" s="1">
-        <v>0</v>
-      </c>
       <c r="R21" s="1">
+        <v>0</v>
+      </c>
+      <c r="S21" s="1">
         <v>4</v>
       </c>
-      <c r="S21" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="T21" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U21" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="U21" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="V21" s="1">
+        <v>0</v>
+      </c>
+      <c r="W21" s="1">
         <v>4</v>
-      </c>
-      <c r="W21" s="1">
-        <v>2</v>
       </c>
       <c r="X21" s="1">
         <v>2</v>
       </c>
       <c r="Y21" s="1">
+        <v>2</v>
+      </c>
+      <c r="Z21" s="1">
         <v>100</v>
       </c>
-      <c r="Z21" s="1">
-        <v>0</v>
-      </c>
       <c r="AA21" s="1">
         <v>0</v>
       </c>
@@ -3561,17 +3630,20 @@
       <c r="AE21" s="1">
         <v>0</v>
       </c>
-      <c r="AF21" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="AG21" s="1">
-        <v>50</v>
+      <c r="AF21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="AH21" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI21" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" spans="3:34">
+    <row r="22" s="1" customFormat="1" spans="3:35">
       <c r="C22" s="1">
         <v>2005</v>
       </c>
@@ -3579,10 +3651,10 @@
         <v>2005</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G22" s="1">
         <v>5</v>
@@ -3594,7 +3666,7 @@
         <v>50</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K22" s="1">
         <v>55</v>
@@ -3612,26 +3684,27 @@
         <v>20</v>
       </c>
       <c r="P22" s="1">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>1000</v>
       </c>
       <c r="Q22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" s="1">
         <v>0</v>
       </c>
-      <c r="S22" s="1" t="s">
-        <v>67</v>
+      <c r="S22" s="1">
+        <v>0</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U22" s="1">
+        <v>68</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="V22" s="1">
         <v>30</v>
       </c>
-      <c r="V22" s="1">
-        <v>0</v>
-      </c>
       <c r="W22" s="1">
         <v>0</v>
       </c>
@@ -3639,11 +3712,11 @@
         <v>0</v>
       </c>
       <c r="Y22" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="1">
         <v>100</v>
       </c>
-      <c r="Z22" s="1">
-        <v>0</v>
-      </c>
       <c r="AA22" s="1">
         <v>0</v>
       </c>
@@ -3659,17 +3732,20 @@
       <c r="AE22" s="1">
         <v>0</v>
       </c>
-      <c r="AF22" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG22" s="1">
-        <v>50</v>
+      <c r="AF22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="5" t="s">
+        <v>85</v>
       </c>
       <c r="AH22" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI22" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" spans="3:34">
+    <row r="23" s="1" customFormat="1" spans="3:35">
       <c r="C23" s="1">
         <v>2006</v>
       </c>
@@ -3677,10 +3753,10 @@
         <v>2006</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G23" s="1">
         <v>6</v>
@@ -3692,7 +3768,7 @@
         <v>10</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K23" s="1">
         <v>0</v>
@@ -3710,22 +3786,23 @@
         <v>20</v>
       </c>
       <c r="P23" s="1">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>1000</v>
       </c>
       <c r="Q23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" s="1">
         <v>0</v>
       </c>
-      <c r="S23" s="1" t="s">
-        <v>67</v>
+      <c r="S23" s="1">
+        <v>0</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="U23" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="U23" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="V23" s="1">
         <v>0</v>
@@ -3737,10 +3814,10 @@
         <v>0</v>
       </c>
       <c r="Y23" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Z23" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AA23" s="1">
         <v>0</v>
@@ -3757,14 +3834,17 @@
       <c r="AE23" s="1">
         <v>0</v>
       </c>
-      <c r="AG23" s="1">
-        <v>50</v>
+      <c r="AF23" s="1">
+        <v>0</v>
       </c>
       <c r="AH23" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI23" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" spans="3:34">
+    <row r="24" s="1" customFormat="1" spans="3:35">
       <c r="C24" s="1">
         <v>2007</v>
       </c>
@@ -3772,10 +3852,10 @@
         <v>2007</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G24" s="1">
         <v>1</v>
@@ -3787,7 +3867,7 @@
         <v>10</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K24" s="4">
         <v>5</v>
@@ -3804,39 +3884,40 @@
       <c r="O24" s="1">
         <v>60</v>
       </c>
-      <c r="P24" s="4">
+      <c r="P24" s="1">
+        <f t="shared" si="1"/>
+        <v>3000</v>
+      </c>
+      <c r="Q24" s="4">
         <v>6</v>
       </c>
-      <c r="Q24" s="1">
-        <v>0</v>
-      </c>
       <c r="R24" s="1">
+        <v>0</v>
+      </c>
+      <c r="S24" s="1">
         <v>5</v>
       </c>
-      <c r="S24" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="T24" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U24" s="1">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="U24" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="V24" s="1">
+        <v>0</v>
+      </c>
+      <c r="W24" s="1">
         <v>5</v>
-      </c>
-      <c r="W24" s="1">
-        <v>3</v>
       </c>
       <c r="X24" s="1">
         <v>3</v>
       </c>
-      <c r="Y24" s="4">
+      <c r="Y24" s="1">
+        <v>3</v>
+      </c>
+      <c r="Z24" s="4">
         <v>300</v>
       </c>
-      <c r="Z24" s="1">
-        <v>0</v>
-      </c>
       <c r="AA24" s="1">
         <v>0</v>
       </c>
@@ -3852,17 +3933,20 @@
       <c r="AE24" s="1">
         <v>0</v>
       </c>
-      <c r="AF24" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="AG24" s="1">
-        <v>50</v>
+      <c r="AF24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="4" t="s">
+        <v>117</v>
       </c>
       <c r="AH24" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI24" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" spans="3:34">
+    <row r="25" s="1" customFormat="1" spans="3:35">
       <c r="C25" s="1">
         <v>2008</v>
       </c>
@@ -3870,10 +3954,10 @@
         <v>2008</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G25" s="1">
         <v>2008</v>
@@ -3885,7 +3969,7 @@
         <v>200</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K25" s="1">
         <v>30</v>
@@ -3903,22 +3987,23 @@
         <v>3</v>
       </c>
       <c r="P25" s="1">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>150</v>
       </c>
       <c r="Q25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" s="1">
         <v>0</v>
       </c>
-      <c r="S25" s="1" t="s">
-        <v>67</v>
+      <c r="S25" s="1">
+        <v>0</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="U25" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="V25" s="1">
         <v>0</v>
@@ -3930,10 +4015,10 @@
         <v>0</v>
       </c>
       <c r="Y25" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Z25" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AA25" s="1">
         <v>0</v>
@@ -3950,17 +4035,20 @@
       <c r="AE25" s="1">
         <v>0</v>
       </c>
-      <c r="AF25" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="AG25" s="1">
-        <v>50</v>
+      <c r="AF25" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="1" t="s">
+        <v>120</v>
       </c>
       <c r="AH25" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI25" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" spans="3:34">
+    <row r="26" s="1" customFormat="1" spans="3:35">
       <c r="C26" s="1">
         <v>2009</v>
       </c>
@@ -3968,10 +4056,10 @@
         <v>2009</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G26" s="1">
         <v>3</v>
@@ -3983,7 +4071,7 @@
         <v>10</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K26" s="1">
         <v>15</v>
@@ -4001,38 +4089,39 @@
         <v>30</v>
       </c>
       <c r="P26" s="1">
+        <f t="shared" si="1"/>
+        <v>1500</v>
+      </c>
+      <c r="Q26" s="1">
         <v>7</v>
       </c>
-      <c r="Q26" s="1">
-        <v>0</v>
-      </c>
       <c r="R26" s="1">
+        <v>0</v>
+      </c>
+      <c r="S26" s="1">
         <v>3</v>
       </c>
-      <c r="S26" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="T26" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U26" s="1">
+        <v>79</v>
+      </c>
+      <c r="U26" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="V26" s="1">
         <v>10</v>
       </c>
-      <c r="V26" s="1">
+      <c r="W26" s="1">
         <v>5</v>
-      </c>
-      <c r="W26" s="1">
-        <v>4</v>
       </c>
       <c r="X26" s="1">
         <v>4</v>
       </c>
       <c r="Y26" s="1">
+        <v>4</v>
+      </c>
+      <c r="Z26" s="1">
         <v>400</v>
       </c>
-      <c r="Z26" s="1">
-        <v>0</v>
-      </c>
       <c r="AA26" s="1">
         <v>0</v>
       </c>
@@ -4048,17 +4137,20 @@
       <c r="AE26" s="1">
         <v>0</v>
       </c>
-      <c r="AF26" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="AG26" s="1">
-        <v>50</v>
+      <c r="AF26" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="AH26" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI26" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" spans="3:34">
+    <row r="27" s="1" customFormat="1" spans="3:35">
       <c r="C27" s="1">
         <v>2010</v>
       </c>
@@ -4066,10 +4158,10 @@
         <v>2010</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G27" s="1">
         <v>2010</v>
@@ -4081,7 +4173,7 @@
         <v>100</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K27" s="1">
         <v>30</v>
@@ -4099,38 +4191,39 @@
         <v>1</v>
       </c>
       <c r="P27" s="1">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="Q27" s="1">
         <v>5</v>
       </c>
-      <c r="Q27" s="1">
-        <v>0</v>
-      </c>
       <c r="R27" s="1">
+        <v>0</v>
+      </c>
+      <c r="S27" s="1">
         <v>3</v>
       </c>
-      <c r="S27" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="T27" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U27" s="1">
+        <v>79</v>
+      </c>
+      <c r="U27" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="V27" s="1">
         <v>15</v>
       </c>
-      <c r="V27" s="1">
+      <c r="W27" s="1">
         <v>5</v>
-      </c>
-      <c r="W27" s="1">
-        <v>4</v>
       </c>
       <c r="X27" s="1">
         <v>4</v>
       </c>
       <c r="Y27" s="1">
+        <v>4</v>
+      </c>
+      <c r="Z27" s="1">
         <v>150</v>
       </c>
-      <c r="Z27" s="1">
-        <v>0</v>
-      </c>
       <c r="AA27" s="1">
         <v>0</v>
       </c>
@@ -4146,14 +4239,17 @@
       <c r="AE27" s="1">
         <v>0</v>
       </c>
-      <c r="AG27" s="1">
-        <v>50</v>
+      <c r="AF27" s="1">
+        <v>0</v>
       </c>
       <c r="AH27" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI27" s="1">
         <v>4102</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" spans="3:34">
+    <row r="28" s="1" customFormat="1" spans="3:35">
       <c r="C28" s="1">
         <v>2011</v>
       </c>
@@ -4161,10 +4257,10 @@
         <v>2011</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G28" s="1">
         <v>8</v>
@@ -4176,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K28" s="1">
         <v>30</v>
@@ -4194,41 +4290,42 @@
         <v>1</v>
       </c>
       <c r="P28" s="1">
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="Q28" s="1">
+        <v>50</v>
+      </c>
+      <c r="R28" s="1">
         <v>10</v>
       </c>
-      <c r="R28" s="1">
+      <c r="S28" s="1">
         <v>3</v>
       </c>
-      <c r="S28" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="T28" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U28" s="1">
+        <v>79</v>
+      </c>
+      <c r="U28" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="V28" s="1">
         <v>15</v>
       </c>
-      <c r="V28" s="1">
+      <c r="W28" s="1">
         <v>5</v>
-      </c>
-      <c r="W28" s="1">
-        <v>4</v>
       </c>
       <c r="X28" s="1">
         <v>4</v>
       </c>
       <c r="Y28" s="1">
+        <v>4</v>
+      </c>
+      <c r="Z28" s="1">
         <v>500</v>
       </c>
-      <c r="Z28" s="1">
+      <c r="AA28" s="1">
         <v>100</v>
       </c>
-      <c r="AA28" s="1">
-        <v>0</v>
-      </c>
       <c r="AB28" s="1">
         <v>0</v>
       </c>
@@ -4241,10 +4338,13 @@
       <c r="AE28" s="1">
         <v>0</v>
       </c>
-      <c r="AG28" s="1">
-        <v>50</v>
+      <c r="AF28" s="1">
+        <v>0</v>
       </c>
       <c r="AH28" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI28" s="1">
         <v>0</v>
       </c>
     </row>
@@ -4252,7 +4352,7 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
     </row>
-    <row r="30" s="1" customFormat="1" spans="3:34">
+    <row r="30" s="1" customFormat="1" spans="3:35">
       <c r="C30" s="1">
         <v>3001</v>
       </c>
@@ -4260,10 +4360,10 @@
         <v>3001</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G30" s="1">
         <v>4</v>
@@ -4275,7 +4375,7 @@
         <v>20</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K30" s="1">
         <v>4</v>
@@ -4293,22 +4393,23 @@
         <v>60</v>
       </c>
       <c r="P30" s="1">
+        <f>N30/20</f>
+        <v>30</v>
+      </c>
+      <c r="Q30" s="1">
         <v>3</v>
       </c>
-      <c r="Q30" s="1">
-        <v>0</v>
-      </c>
       <c r="R30" s="1">
         <v>0</v>
       </c>
-      <c r="S30" s="1" t="s">
-        <v>67</v>
+      <c r="S30" s="1">
+        <v>0</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U30" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="U30" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="V30" s="1">
         <v>0</v>
@@ -4320,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="Y30" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Z30" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AA30" s="1">
         <v>0</v>
@@ -4340,14 +4441,17 @@
       <c r="AE30" s="1">
         <v>0</v>
       </c>
-      <c r="AG30" s="1">
-        <v>50</v>
+      <c r="AF30" s="1">
+        <v>0</v>
       </c>
       <c r="AH30" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI30" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" spans="3:34">
+    <row r="31" s="1" customFormat="1" spans="3:35">
       <c r="C31" s="1">
         <v>3002</v>
       </c>
@@ -4355,10 +4459,10 @@
         <v>3002</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -4370,7 +4474,7 @@
         <v>10</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K31" s="1">
         <v>0</v>
@@ -4388,38 +4492,39 @@
         <v>60</v>
       </c>
       <c r="P31" s="1">
+        <f t="shared" ref="P30:P40" si="2">N31*5</f>
+        <v>2500</v>
+      </c>
+      <c r="Q31" s="1">
         <v>2</v>
       </c>
-      <c r="Q31" s="1">
-        <v>0</v>
-      </c>
       <c r="R31" s="1">
+        <v>0</v>
+      </c>
+      <c r="S31" s="1">
         <v>3</v>
       </c>
-      <c r="S31" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="T31" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="U31" s="1">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="U31" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="V31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W31" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X31" s="1">
         <v>0</v>
       </c>
       <c r="Y31" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="1">
         <v>120</v>
       </c>
-      <c r="Z31" s="1">
-        <v>0</v>
-      </c>
       <c r="AA31" s="1">
         <v>0</v>
       </c>
@@ -4435,14 +4540,17 @@
       <c r="AE31" s="1">
         <v>0</v>
       </c>
-      <c r="AG31" s="1">
-        <v>50</v>
+      <c r="AF31" s="1">
+        <v>0</v>
       </c>
       <c r="AH31" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI31" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" spans="3:34">
+    <row r="32" s="1" customFormat="1" spans="3:35">
       <c r="C32" s="1">
         <v>3003</v>
       </c>
@@ -4450,10 +4558,10 @@
         <v>3003</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G32" s="1">
         <v>1</v>
@@ -4465,7 +4573,7 @@
         <v>10</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K32" s="1">
         <v>10</v>
@@ -4483,44 +4591,45 @@
         <v>60</v>
       </c>
       <c r="P32" s="1">
+        <f t="shared" si="2"/>
+        <v>3000</v>
+      </c>
+      <c r="Q32" s="1">
         <v>2</v>
       </c>
-      <c r="Q32" s="1">
-        <v>0</v>
-      </c>
       <c r="R32" s="1">
+        <v>0</v>
+      </c>
+      <c r="S32" s="1">
         <v>2</v>
       </c>
-      <c r="S32" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="T32" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="U32" s="1">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="U32" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="V32" s="1">
+        <v>0</v>
+      </c>
+      <c r="W32" s="1">
         <v>5</v>
       </c>
-      <c r="W32" s="1">
-        <v>0</v>
-      </c>
       <c r="X32" s="1">
         <v>0</v>
       </c>
       <c r="Y32" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="1">
         <v>35</v>
       </c>
-      <c r="Z32" s="1">
-        <v>0</v>
-      </c>
       <c r="AA32" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="1">
         <v>60</v>
       </c>
-      <c r="AB32" s="1">
-        <v>0</v>
-      </c>
       <c r="AC32" s="1">
         <v>0</v>
       </c>
@@ -4530,17 +4639,20 @@
       <c r="AE32" s="1">
         <v>0</v>
       </c>
-      <c r="AF32" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="AG32" s="1">
-        <v>50</v>
+      <c r="AF32" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="1" t="s">
+        <v>134</v>
       </c>
       <c r="AH32" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI32" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" spans="3:34">
+    <row r="33" s="1" customFormat="1" spans="3:35">
       <c r="C33" s="1">
         <v>3004</v>
       </c>
@@ -4548,10 +4660,10 @@
         <v>3004</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G33" s="1">
         <v>2</v>
@@ -4563,7 +4675,7 @@
         <v>100</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K33" s="1">
         <v>15</v>
@@ -4581,38 +4693,39 @@
         <v>60</v>
       </c>
       <c r="P33" s="1">
+        <f t="shared" si="2"/>
+        <v>3000</v>
+      </c>
+      <c r="Q33" s="1">
         <v>2</v>
       </c>
-      <c r="Q33" s="1">
-        <v>0</v>
-      </c>
       <c r="R33" s="1">
         <v>0</v>
       </c>
-      <c r="S33" s="1" t="s">
-        <v>67</v>
+      <c r="S33" s="1">
+        <v>0</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="U33" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="U33" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="V33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W33" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X33" s="1">
         <v>0</v>
       </c>
       <c r="Y33" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="1">
         <v>100</v>
       </c>
-      <c r="Z33" s="1">
-        <v>0</v>
-      </c>
       <c r="AA33" s="1">
         <v>0</v>
       </c>
@@ -4628,14 +4741,17 @@
       <c r="AE33" s="1">
         <v>0</v>
       </c>
-      <c r="AG33" s="1">
-        <v>50</v>
+      <c r="AF33" s="1">
+        <v>0</v>
       </c>
       <c r="AH33" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI33" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" spans="3:34">
+    <row r="34" s="1" customFormat="1" spans="3:35">
       <c r="C34" s="1">
         <v>3005</v>
       </c>
@@ -4643,10 +4759,10 @@
         <v>3005</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G34" s="1">
         <v>5</v>
@@ -4658,7 +4774,7 @@
         <v>50</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K34" s="1">
         <v>55</v>
@@ -4676,26 +4792,27 @@
         <v>20</v>
       </c>
       <c r="P34" s="1">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>1000</v>
       </c>
       <c r="Q34" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" s="1">
         <v>0</v>
       </c>
-      <c r="S34" s="1" t="s">
-        <v>67</v>
+      <c r="S34" s="1">
+        <v>0</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U34" s="1">
+        <v>68</v>
+      </c>
+      <c r="U34" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="V34" s="1">
         <v>30</v>
       </c>
-      <c r="V34" s="1">
-        <v>0</v>
-      </c>
       <c r="W34" s="1">
         <v>0</v>
       </c>
@@ -4703,11 +4820,11 @@
         <v>0</v>
       </c>
       <c r="Y34" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="1">
         <v>100</v>
       </c>
-      <c r="Z34" s="1">
-        <v>0</v>
-      </c>
       <c r="AA34" s="1">
         <v>0</v>
       </c>
@@ -4723,17 +4840,20 @@
       <c r="AE34" s="1">
         <v>0</v>
       </c>
-      <c r="AF34" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG34" s="1">
-        <v>50</v>
+      <c r="AF34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="5" t="s">
+        <v>85</v>
       </c>
       <c r="AH34" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI34" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" spans="3:34">
+    <row r="35" s="1" customFormat="1" spans="3:35">
       <c r="C35" s="1">
         <v>3006</v>
       </c>
@@ -4741,10 +4861,10 @@
         <v>3006</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G35" s="1">
         <v>6</v>
@@ -4756,7 +4876,7 @@
         <v>10</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K35" s="1">
         <v>0</v>
@@ -4774,22 +4894,23 @@
         <v>20</v>
       </c>
       <c r="P35" s="1">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>1000</v>
       </c>
       <c r="Q35" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" s="1">
+        <v>0</v>
+      </c>
+      <c r="S35" s="1">
         <v>3</v>
       </c>
-      <c r="S35" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="T35" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="U35" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="U35" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="V35" s="1">
         <v>0</v>
@@ -4801,10 +4922,10 @@
         <v>0</v>
       </c>
       <c r="Y35" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Z35" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AA35" s="1">
         <v>0</v>
@@ -4821,14 +4942,17 @@
       <c r="AE35" s="1">
         <v>0</v>
       </c>
-      <c r="AG35" s="1">
-        <v>50</v>
+      <c r="AF35" s="1">
+        <v>0</v>
       </c>
       <c r="AH35" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI35" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" spans="3:34">
+    <row r="36" s="1" customFormat="1" spans="3:35">
       <c r="C36" s="1">
         <v>3007</v>
       </c>
@@ -4836,10 +4960,10 @@
         <v>3007</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G36" s="1">
         <v>2</v>
@@ -4851,7 +4975,7 @@
         <v>100</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K36" s="1">
         <v>30</v>
@@ -4869,38 +4993,39 @@
         <v>60</v>
       </c>
       <c r="P36" s="1">
+        <f t="shared" si="2"/>
+        <v>3000</v>
+      </c>
+      <c r="Q36" s="1">
         <v>3</v>
       </c>
-      <c r="Q36" s="1">
-        <v>0</v>
-      </c>
       <c r="R36" s="1">
+        <v>0</v>
+      </c>
+      <c r="S36" s="1">
         <v>2</v>
       </c>
-      <c r="S36" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="T36" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U36" s="1">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="U36" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="V36" s="1">
+        <v>0</v>
+      </c>
+      <c r="W36" s="1">
         <v>2</v>
       </c>
-      <c r="W36" s="1">
-        <v>0</v>
-      </c>
       <c r="X36" s="1">
         <v>0</v>
       </c>
       <c r="Y36" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="1">
         <v>120</v>
       </c>
-      <c r="Z36" s="1">
-        <v>0</v>
-      </c>
       <c r="AA36" s="1">
         <v>0</v>
       </c>
@@ -4916,14 +5041,17 @@
       <c r="AE36" s="1">
         <v>0</v>
       </c>
-      <c r="AG36" s="1">
-        <v>50</v>
+      <c r="AF36" s="1">
+        <v>0</v>
       </c>
       <c r="AH36" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI36" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" spans="3:34">
+    <row r="37" s="1" customFormat="1" spans="3:35">
       <c r="C37" s="1">
         <v>3008</v>
       </c>
@@ -4931,10 +5059,10 @@
         <v>3008</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G37" s="1">
         <v>3008</v>
@@ -4946,7 +5074,7 @@
         <v>200</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K37" s="1">
         <v>30</v>
@@ -4964,26 +5092,27 @@
         <v>3</v>
       </c>
       <c r="P37" s="1">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="Q37" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" s="1">
         <v>0</v>
       </c>
-      <c r="S37" s="1" t="s">
-        <v>67</v>
+      <c r="S37" s="1">
+        <v>0</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="U37" s="1">
+        <v>68</v>
+      </c>
+      <c r="U37" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="V37" s="1">
         <v>5</v>
       </c>
-      <c r="V37" s="1">
-        <v>0</v>
-      </c>
       <c r="W37" s="1">
         <v>0</v>
       </c>
@@ -4991,11 +5120,11 @@
         <v>0</v>
       </c>
       <c r="Y37" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="1">
         <v>30</v>
       </c>
-      <c r="Z37" s="1">
-        <v>0</v>
-      </c>
       <c r="AA37" s="1">
         <v>0</v>
       </c>
@@ -5011,17 +5140,20 @@
       <c r="AE37" s="1">
         <v>0</v>
       </c>
-      <c r="AF37" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="AG37" s="1">
-        <v>50</v>
+      <c r="AF37" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG37" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="AH37" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI37" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" spans="3:34">
+    <row r="38" s="1" customFormat="1" spans="3:35">
       <c r="C38" s="1">
         <v>3009</v>
       </c>
@@ -5029,10 +5161,10 @@
         <v>3009</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G38" s="1">
         <v>2</v>
@@ -5044,7 +5176,7 @@
         <v>100</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K38" s="1">
         <v>30</v>
@@ -5062,38 +5194,39 @@
         <v>30</v>
       </c>
       <c r="P38" s="1">
+        <f t="shared" si="2"/>
+        <v>1500</v>
+      </c>
+      <c r="Q38" s="1">
         <v>4</v>
       </c>
-      <c r="Q38" s="1">
-        <v>0</v>
-      </c>
       <c r="R38" s="1">
+        <v>0</v>
+      </c>
+      <c r="S38" s="1">
         <v>2</v>
       </c>
-      <c r="S38" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="T38" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U38" s="1">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="U38" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="V38" s="1">
+        <v>0</v>
+      </c>
+      <c r="W38" s="1">
         <v>3</v>
       </c>
-      <c r="W38" s="1">
-        <v>0</v>
-      </c>
       <c r="X38" s="1">
         <v>0</v>
       </c>
       <c r="Y38" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="1">
         <v>300</v>
       </c>
-      <c r="Z38" s="1">
-        <v>0</v>
-      </c>
       <c r="AA38" s="1">
         <v>0</v>
       </c>
@@ -5109,14 +5242,17 @@
       <c r="AE38" s="1">
         <v>0</v>
       </c>
-      <c r="AG38" s="1">
-        <v>50</v>
+      <c r="AF38" s="1">
+        <v>0</v>
       </c>
       <c r="AH38" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI38" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" spans="3:34">
+    <row r="39" s="1" customFormat="1" spans="3:35">
       <c r="C39" s="1">
         <v>3010</v>
       </c>
@@ -5124,10 +5260,10 @@
         <v>3010</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G39" s="1">
         <v>8</v>
@@ -5139,7 +5275,7 @@
         <v>100</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K39" s="1">
         <v>0</v>
@@ -5157,41 +5293,42 @@
         <v>1</v>
       </c>
       <c r="P39" s="1">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>50</v>
       </c>
       <c r="Q39" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" s="1">
         <v>0</v>
       </c>
-      <c r="S39" s="1" t="s">
-        <v>78</v>
+      <c r="S39" s="1">
+        <v>0</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U39" s="1">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="U39" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="V39" s="1">
+        <v>0</v>
+      </c>
+      <c r="W39" s="1">
         <v>3</v>
       </c>
-      <c r="W39" s="1">
-        <v>0</v>
-      </c>
       <c r="X39" s="1">
         <v>0</v>
       </c>
       <c r="Y39" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="1">
         <v>20</v>
       </c>
-      <c r="Z39" s="1">
+      <c r="AA39" s="1">
         <v>400</v>
       </c>
-      <c r="AA39" s="1">
-        <v>0</v>
-      </c>
       <c r="AB39" s="1">
         <v>0</v>
       </c>
@@ -5204,14 +5341,17 @@
       <c r="AE39" s="1">
         <v>0</v>
       </c>
-      <c r="AG39" s="1">
-        <v>50</v>
+      <c r="AF39" s="1">
+        <v>0</v>
       </c>
       <c r="AH39" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI39" s="1">
         <v>4102</v>
       </c>
     </row>
-    <row r="40" s="1" customFormat="1" spans="3:34">
+    <row r="40" s="1" customFormat="1" spans="3:35">
       <c r="C40" s="1">
         <v>3011</v>
       </c>
@@ -5219,10 +5359,10 @@
         <v>3011</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G40" s="1">
         <v>8</v>
@@ -5234,7 +5374,7 @@
         <v>0</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K40" s="1">
         <v>30</v>
@@ -5252,41 +5392,42 @@
         <v>1</v>
       </c>
       <c r="P40" s="1">
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
       <c r="Q40" s="1">
+        <v>50</v>
+      </c>
+      <c r="R40" s="1">
         <v>10</v>
       </c>
-      <c r="R40" s="1">
+      <c r="S40" s="1">
         <v>3</v>
       </c>
-      <c r="S40" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="T40" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U40" s="1">
+        <v>79</v>
+      </c>
+      <c r="U40" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="V40" s="1">
         <v>15</v>
       </c>
-      <c r="V40" s="1">
+      <c r="W40" s="1">
         <v>5</v>
-      </c>
-      <c r="W40" s="1">
-        <v>4</v>
       </c>
       <c r="X40" s="1">
         <v>4</v>
       </c>
       <c r="Y40" s="1">
+        <v>4</v>
+      </c>
+      <c r="Z40" s="1">
         <v>500</v>
       </c>
-      <c r="Z40" s="1">
+      <c r="AA40" s="1">
         <v>100</v>
       </c>
-      <c r="AA40" s="1">
-        <v>0</v>
-      </c>
       <c r="AB40" s="1">
         <v>0</v>
       </c>
@@ -5299,10 +5440,13 @@
       <c r="AE40" s="1">
         <v>0</v>
       </c>
-      <c r="AG40" s="1">
-        <v>50</v>
+      <c r="AF40" s="1">
+        <v>0</v>
       </c>
       <c r="AH40" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI40" s="1">
         <v>0</v>
       </c>
     </row>
@@ -5310,7 +5454,7 @@
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
     </row>
-    <row r="42" s="1" customFormat="1" spans="3:33">
+    <row r="42" s="1" customFormat="1" spans="3:34">
       <c r="C42" s="1">
         <v>4001</v>
       </c>
@@ -5318,10 +5462,10 @@
         <v>4001</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G42" s="1">
         <v>4001</v>
@@ -5333,7 +5477,7 @@
         <v>-100</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K42" s="1">
         <v>30</v>
@@ -5350,27 +5494,24 @@
       <c r="O42" s="1">
         <v>0</v>
       </c>
-      <c r="P42" s="1">
-        <v>0</v>
-      </c>
       <c r="Q42" s="1">
         <v>0</v>
       </c>
       <c r="R42" s="1">
         <v>0</v>
       </c>
-      <c r="S42" s="1" t="s">
-        <v>67</v>
+      <c r="S42" s="1">
+        <v>0</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U42" s="1">
+        <v>68</v>
+      </c>
+      <c r="U42" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="V42" s="1">
         <v>2</v>
       </c>
-      <c r="V42" s="1">
-        <v>0</v>
-      </c>
       <c r="W42" s="1">
         <v>0</v>
       </c>
@@ -5398,14 +5539,17 @@
       <c r="AE42" s="1">
         <v>0</v>
       </c>
-      <c r="AF42" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="AG42" s="1">
+      <c r="AF42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH42" s="1">
         <v>99999</v>
       </c>
     </row>
-    <row r="43" s="1" customFormat="1" spans="3:33">
+    <row r="43" s="1" customFormat="1" spans="3:34">
       <c r="C43" s="1">
         <v>4002</v>
       </c>
@@ -5413,10 +5557,10 @@
         <v>4002</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G43" s="1">
         <v>4002</v>
@@ -5428,7 +5572,7 @@
         <v>200</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K43" s="1">
         <v>60</v>
@@ -5445,23 +5589,20 @@
       <c r="O43" s="1">
         <v>0</v>
       </c>
-      <c r="P43" s="1">
+      <c r="Q43" s="1">
         <v>10</v>
       </c>
-      <c r="Q43" s="1">
-        <v>0</v>
-      </c>
       <c r="R43" s="1">
         <v>0</v>
       </c>
-      <c r="S43" s="1" t="s">
-        <v>67</v>
+      <c r="S43" s="1">
+        <v>0</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U43" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="U43" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="V43" s="1">
         <v>0</v>
@@ -5473,11 +5614,11 @@
         <v>0</v>
       </c>
       <c r="Y43" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="1">
         <v>100</v>
       </c>
-      <c r="Z43" s="1">
-        <v>0</v>
-      </c>
       <c r="AA43" s="1">
         <v>0</v>
       </c>
@@ -5493,12 +5634,15 @@
       <c r="AE43" s="1">
         <v>0</v>
       </c>
-      <c r="AF43" s="5"/>
-      <c r="AG43" s="1">
+      <c r="AF43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="5"/>
+      <c r="AH43" s="1">
         <v>99999</v>
       </c>
     </row>
-    <row r="44" s="1" customFormat="1" spans="3:33">
+    <row r="44" s="1" customFormat="1" spans="3:34">
       <c r="C44" s="1">
         <v>4003</v>
       </c>
@@ -5506,10 +5650,10 @@
         <v>4003</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G44" s="1">
         <v>4003</v>
@@ -5521,7 +5665,7 @@
         <v>-1</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K44" s="1">
         <v>60</v>
@@ -5538,23 +5682,20 @@
       <c r="O44" s="1">
         <v>0</v>
       </c>
-      <c r="P44" s="1">
-        <v>0</v>
-      </c>
       <c r="Q44" s="1">
         <v>0</v>
       </c>
       <c r="R44" s="1">
         <v>0</v>
       </c>
-      <c r="S44" s="1" t="s">
-        <v>67</v>
+      <c r="S44" s="1">
+        <v>0</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U44" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="U44" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="V44" s="1">
         <v>0</v>
@@ -5566,11 +5707,11 @@
         <v>0</v>
       </c>
       <c r="Y44" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="1">
         <v>100</v>
       </c>
-      <c r="Z44" s="1">
-        <v>0</v>
-      </c>
       <c r="AA44" s="1">
         <v>0</v>
       </c>
@@ -5586,10 +5727,13 @@
       <c r="AE44" s="1">
         <v>0</v>
       </c>
-      <c r="AF44" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="AG44" s="1">
+      <c r="AF44" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="AH44" s="1">
         <v>99999</v>
       </c>
     </row>
@@ -5597,7 +5741,7 @@
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
     </row>
-    <row r="46" s="1" customFormat="1" spans="3:34">
+    <row r="46" s="1" customFormat="1" spans="3:35">
       <c r="C46" s="1">
         <v>9001</v>
       </c>
@@ -5605,10 +5749,10 @@
         <v>9001</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G46" s="1">
         <v>9</v>
@@ -5634,36 +5778,33 @@
       <c r="O46" s="1">
         <v>0</v>
       </c>
-      <c r="P46" s="1">
-        <v>0</v>
-      </c>
-      <c r="R46" s="1">
-        <v>1</v>
-      </c>
-      <c r="S46" s="1" t="s">
-        <v>67</v>
+      <c r="Q46" s="1">
+        <v>0</v>
+      </c>
+      <c r="S46" s="1">
+        <v>1</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="U46" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="U46" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="V46" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W46" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X46" s="1">
         <v>0</v>
       </c>
       <c r="Y46" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="1">
         <v>100</v>
       </c>
-      <c r="Z46" s="1">
-        <v>0</v>
-      </c>
       <c r="AA46" s="1">
         <v>0</v>
       </c>
@@ -5679,14 +5820,17 @@
       <c r="AE46" s="1">
         <v>0</v>
       </c>
-      <c r="AG46" s="1">
-        <v>50</v>
+      <c r="AF46" s="1">
+        <v>0</v>
       </c>
       <c r="AH46" s="1">
         <v>50</v>
       </c>
+      <c r="AI46" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="47" s="1" customFormat="1" spans="3:34">
+    <row r="47" s="1" customFormat="1" spans="3:35">
       <c r="C47" s="1">
         <v>9002</v>
       </c>
@@ -5694,10 +5838,10 @@
         <v>9002</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G47" s="1">
         <v>9</v>
@@ -5723,36 +5867,33 @@
       <c r="O47" s="1">
         <v>0</v>
       </c>
-      <c r="P47" s="1">
-        <v>0</v>
-      </c>
-      <c r="R47" s="1">
+      <c r="Q47" s="1">
+        <v>0</v>
+      </c>
+      <c r="S47" s="1">
         <v>2</v>
-      </c>
-      <c r="S47" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="T47" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="U47" s="1">
-        <v>0</v>
+      <c r="U47" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="V47" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W47" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X47" s="1">
         <v>0</v>
       </c>
       <c r="Y47" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="1">
         <v>100</v>
       </c>
-      <c r="Z47" s="1">
-        <v>0</v>
-      </c>
       <c r="AA47" s="1">
         <v>0</v>
       </c>
@@ -5768,15 +5909,18 @@
       <c r="AE47" s="1">
         <v>0</v>
       </c>
-      <c r="AG47" s="1">
-        <v>50</v>
+      <c r="AF47" s="1">
+        <v>0</v>
       </c>
       <c r="AH47" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI47" s="1">
         <v>50</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1"/>
-    <row r="49" s="1" customFormat="1" spans="3:34">
+    <row r="49" s="1" customFormat="1" spans="3:35">
       <c r="C49" s="1">
         <v>10001</v>
       </c>
@@ -5784,23 +5928,23 @@
         <v>10001</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F49" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="G49" s="1">
+        <v>1</v>
+      </c>
+      <c r="H49" s="1">
+        <v>0</v>
+      </c>
+      <c r="I49" s="1">
+        <v>1</v>
+      </c>
+      <c r="J49" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="G49" s="1">
-        <v>1</v>
-      </c>
-      <c r="H49" s="1">
-        <v>0</v>
-      </c>
-      <c r="I49" s="1">
-        <v>1</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>160</v>
-      </c>
       <c r="K49" s="1">
         <v>0</v>
       </c>
@@ -5816,36 +5960,33 @@
       <c r="O49" s="1">
         <v>0</v>
       </c>
-      <c r="P49" s="1">
-        <v>0</v>
-      </c>
-      <c r="R49" s="1">
+      <c r="Q49" s="1">
+        <v>0</v>
+      </c>
+      <c r="S49" s="1">
         <v>3</v>
       </c>
-      <c r="S49" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="T49" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="U49" s="1">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="U49" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="V49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X49" s="1">
         <v>0</v>
       </c>
       <c r="Y49" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="1">
         <v>150</v>
       </c>
-      <c r="Z49" s="1">
-        <v>0</v>
-      </c>
       <c r="AA49" s="1">
         <v>0</v>
       </c>
@@ -5861,14 +6002,17 @@
       <c r="AE49" s="1">
         <v>0</v>
       </c>
-      <c r="AG49" s="1">
-        <v>50</v>
+      <c r="AF49" s="1">
+        <v>0</v>
       </c>
       <c r="AH49" s="1">
         <v>50</v>
       </c>
+      <c r="AI49" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="50" spans="3:34">
+    <row r="50" spans="3:35">
       <c r="C50" s="2">
         <v>10002</v>
       </c>
@@ -5876,10 +6020,10 @@
         <v>10002</v>
       </c>
       <c r="E50" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F50" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="G50" s="2">
         <v>4</v>
@@ -5891,7 +6035,7 @@
         <v>10</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K50" s="2">
         <v>0</v>
@@ -5908,37 +6052,35 @@
       <c r="O50" s="1">
         <v>0</v>
       </c>
-      <c r="P50" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="1"/>
-      <c r="R50" s="2">
-        <v>0</v>
-      </c>
-      <c r="S50" s="1" t="s">
-        <v>67</v>
+      <c r="P50" s="1"/>
+      <c r="Q50" s="1">
+        <v>0</v>
+      </c>
+      <c r="R50" s="1"/>
+      <c r="S50" s="2">
+        <v>0</v>
       </c>
       <c r="T50" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="U50" s="2">
-        <v>0</v>
+      <c r="U50" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="V50" s="2">
-        <v>1</v>
-      </c>
-      <c r="W50" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="W50" s="2">
+        <v>1</v>
       </c>
       <c r="X50" s="1">
         <v>0</v>
       </c>
-      <c r="Y50" s="2">
+      <c r="Y50" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="2">
         <v>100</v>
       </c>
-      <c r="Z50" s="1">
-        <v>0</v>
-      </c>
       <c r="AA50" s="1">
         <v>0</v>
       </c>
@@ -5954,15 +6096,18 @@
       <c r="AE50" s="1">
         <v>0</v>
       </c>
-      <c r="AF50" s="1"/>
-      <c r="AG50" s="1">
-        <v>50</v>
-      </c>
+      <c r="AF50" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="1"/>
       <c r="AH50" s="1">
         <v>50</v>
       </c>
+      <c r="AI50" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="51" spans="3:34">
+    <row r="51" spans="3:35">
       <c r="C51" s="2">
         <v>10003</v>
       </c>
@@ -5970,10 +6115,10 @@
         <v>10003</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -5985,7 +6130,7 @@
         <v>1</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K51" s="2">
         <v>0</v>
@@ -6002,37 +6147,35 @@
       <c r="O51" s="1">
         <v>0</v>
       </c>
-      <c r="P51" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="1"/>
-      <c r="R51" s="1">
-        <v>0</v>
-      </c>
-      <c r="S51" s="1" t="s">
-        <v>78</v>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="1">
+        <v>0</v>
+      </c>
+      <c r="R51" s="1"/>
+      <c r="S51" s="1">
+        <v>0</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="U51" s="1">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="U51" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="V51" s="1">
+        <v>0</v>
+      </c>
+      <c r="W51" s="1">
         <v>10</v>
       </c>
-      <c r="W51" s="1">
-        <v>0</v>
-      </c>
       <c r="X51" s="1">
         <v>0</v>
       </c>
       <c r="Y51" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="1">
         <v>100</v>
       </c>
-      <c r="Z51" s="1">
-        <v>0</v>
-      </c>
       <c r="AA51" s="1">
         <v>0</v>
       </c>
@@ -6048,15 +6191,18 @@
       <c r="AE51" s="1">
         <v>0</v>
       </c>
-      <c r="AF51" s="1"/>
-      <c r="AG51" s="1">
-        <v>50</v>
-      </c>
+      <c r="AF51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="1"/>
       <c r="AH51" s="1">
         <v>50</v>
       </c>
+      <c r="AI51" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="52" spans="3:34">
+    <row r="52" spans="3:35">
       <c r="C52" s="2">
         <v>10004</v>
       </c>
@@ -6064,10 +6210,10 @@
         <v>10004</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G52" s="2">
         <v>4</v>
@@ -6079,7 +6225,7 @@
         <v>10</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K52" s="2">
         <v>0</v>
@@ -6096,41 +6242,39 @@
       <c r="O52" s="1">
         <v>0</v>
       </c>
-      <c r="P52" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="1"/>
-      <c r="R52" s="2">
+      <c r="P52" s="1"/>
+      <c r="Q52" s="1">
+        <v>0</v>
+      </c>
+      <c r="R52" s="1"/>
+      <c r="S52" s="2">
         <v>3</v>
       </c>
-      <c r="S52" s="2" t="s">
-        <v>166</v>
-      </c>
       <c r="T52" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="U52" s="2">
-        <v>0</v>
+        <v>167</v>
+      </c>
+      <c r="U52" s="2" t="s">
+        <v>84</v>
       </c>
       <c r="V52" s="2">
+        <v>0</v>
+      </c>
+      <c r="W52" s="2">
         <v>4</v>
       </c>
-      <c r="W52" s="1">
-        <v>0</v>
-      </c>
       <c r="X52" s="1">
         <v>0</v>
       </c>
-      <c r="Y52" s="2">
-        <v>50</v>
+      <c r="Y52" s="1">
+        <v>0</v>
       </c>
       <c r="Z52" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA52" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB52" s="2">
+        <v>50</v>
+      </c>
+      <c r="AA52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="1">
         <v>0</v>
       </c>
       <c r="AC52" s="2">
@@ -6139,17 +6283,20 @@
       <c r="AD52" s="2">
         <v>0</v>
       </c>
-      <c r="AE52" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG52" s="1">
-        <v>50</v>
+      <c r="AE52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="1">
+        <v>0</v>
       </c>
       <c r="AH52" s="1">
         <v>50</v>
       </c>
+      <c r="AI52" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="53" s="1" customFormat="1" spans="3:34">
+    <row r="53" s="1" customFormat="1" spans="3:35">
       <c r="C53" s="1">
         <v>10005</v>
       </c>
@@ -6157,10 +6304,10 @@
         <v>10005</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G53" s="1">
         <v>1</v>
@@ -6172,7 +6319,7 @@
         <v>10</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K53" s="1">
         <v>0</v>
@@ -6189,42 +6336,39 @@
       <c r="O53" s="1">
         <v>0</v>
       </c>
-      <c r="P53" s="1">
-        <v>0</v>
-      </c>
-      <c r="R53" s="1">
+      <c r="Q53" s="1">
+        <v>0</v>
+      </c>
+      <c r="S53" s="1">
         <v>2</v>
-      </c>
-      <c r="S53" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="T53" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="U53" s="1">
-        <v>0</v>
+      <c r="U53" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="V53" s="1">
+        <v>0</v>
+      </c>
+      <c r="W53" s="1">
         <v>2</v>
       </c>
-      <c r="W53" s="1">
-        <v>0</v>
-      </c>
       <c r="X53" s="1">
         <v>0</v>
       </c>
       <c r="Y53" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="1">
         <v>150</v>
       </c>
-      <c r="Z53" s="1">
-        <v>0</v>
-      </c>
       <c r="AA53" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="1">
         <v>20</v>
       </c>
-      <c r="AB53" s="1">
-        <v>0</v>
-      </c>
       <c r="AC53" s="1">
         <v>0</v>
       </c>
@@ -6234,14 +6378,17 @@
       <c r="AE53" s="1">
         <v>0</v>
       </c>
-      <c r="AG53" s="1">
-        <v>50</v>
+      <c r="AF53" s="1">
+        <v>0</v>
       </c>
       <c r="AH53" s="1">
         <v>50</v>
       </c>
+      <c r="AI53" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="55" s="1" customFormat="1" spans="3:34">
+    <row r="55" s="1" customFormat="1" spans="3:35">
       <c r="C55" s="1">
         <v>11001</v>
       </c>
@@ -6249,10 +6396,10 @@
         <v>1001</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G55" s="1">
         <v>1</v>
@@ -6278,36 +6425,33 @@
       <c r="O55" s="1">
         <v>0</v>
       </c>
-      <c r="P55" s="1">
-        <v>0</v>
-      </c>
-      <c r="R55" s="1">
-        <v>1</v>
-      </c>
-      <c r="S55" s="1" t="s">
-        <v>67</v>
+      <c r="Q55" s="1">
+        <v>0</v>
+      </c>
+      <c r="S55" s="1">
+        <v>1</v>
       </c>
       <c r="T55" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="U55" s="1">
-        <v>0</v>
+      <c r="U55" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="V55" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W55" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X55" s="1">
         <v>0</v>
       </c>
       <c r="Y55" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="1">
         <v>120</v>
       </c>
-      <c r="Z55" s="1">
-        <v>0</v>
-      </c>
       <c r="AA55" s="1">
         <v>0</v>
       </c>
@@ -6323,14 +6467,17 @@
       <c r="AE55" s="1">
         <v>0</v>
       </c>
-      <c r="AG55" s="1">
-        <v>50</v>
+      <c r="AF55" s="1">
+        <v>0</v>
       </c>
       <c r="AH55" s="1">
         <v>50</v>
       </c>
+      <c r="AI55" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="56" s="1" customFormat="1" spans="3:34">
+    <row r="56" s="1" customFormat="1" spans="3:35">
       <c r="C56" s="1">
         <v>11002</v>
       </c>
@@ -6338,10 +6485,10 @@
         <v>1002</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
@@ -6367,42 +6514,39 @@
       <c r="O56" s="1">
         <v>0</v>
       </c>
-      <c r="P56" s="1">
-        <v>0</v>
-      </c>
-      <c r="R56" s="1">
+      <c r="Q56" s="1">
+        <v>0</v>
+      </c>
+      <c r="S56" s="1">
         <v>2</v>
-      </c>
-      <c r="S56" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="T56" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="U56" s="1">
-        <v>0</v>
+      <c r="U56" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="V56" s="1">
+        <v>0</v>
+      </c>
+      <c r="W56" s="1">
         <v>2</v>
       </c>
-      <c r="W56" s="1">
-        <v>0</v>
-      </c>
       <c r="X56" s="1">
         <v>0</v>
       </c>
       <c r="Y56" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z56" s="1">
         <v>150</v>
       </c>
-      <c r="Z56" s="1">
-        <v>0</v>
-      </c>
       <c r="AA56" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB56" s="1">
         <v>20</v>
       </c>
-      <c r="AB56" s="1">
-        <v>0</v>
-      </c>
       <c r="AC56" s="1">
         <v>0</v>
       </c>
@@ -6412,14 +6556,17 @@
       <c r="AE56" s="1">
         <v>0</v>
       </c>
-      <c r="AG56" s="1">
-        <v>50</v>
+      <c r="AF56" s="1">
+        <v>0</v>
       </c>
       <c r="AH56" s="1">
         <v>50</v>
       </c>
+      <c r="AI56" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="57" s="1" customFormat="1" spans="3:34">
+    <row r="57" s="1" customFormat="1" spans="3:35">
       <c r="C57" s="1">
         <v>11003</v>
       </c>
@@ -6427,10 +6574,10 @@
         <v>1003</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G57" s="1">
         <v>1</v>
@@ -6456,36 +6603,33 @@
       <c r="O57" s="1">
         <v>0</v>
       </c>
-      <c r="P57" s="1">
-        <v>0</v>
-      </c>
-      <c r="R57" s="1">
-        <v>1</v>
-      </c>
-      <c r="S57" s="1" t="s">
-        <v>67</v>
+      <c r="Q57" s="1">
+        <v>0</v>
+      </c>
+      <c r="S57" s="1">
+        <v>1</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="U57" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="U57" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="V57" s="1">
+        <v>0</v>
+      </c>
+      <c r="W57" s="1">
         <v>5</v>
       </c>
-      <c r="W57" s="1">
-        <v>0</v>
-      </c>
       <c r="X57" s="1">
         <v>0</v>
       </c>
       <c r="Y57" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="1">
         <v>100</v>
       </c>
-      <c r="Z57" s="1">
-        <v>0</v>
-      </c>
       <c r="AA57" s="1">
         <v>0</v>
       </c>
@@ -6501,14 +6645,17 @@
       <c r="AE57" s="1">
         <v>0</v>
       </c>
-      <c r="AG57" s="1">
-        <v>50</v>
+      <c r="AF57" s="1">
+        <v>0</v>
       </c>
       <c r="AH57" s="1">
         <v>50</v>
       </c>
+      <c r="AI57" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="58" s="1" customFormat="1" spans="3:34">
+    <row r="58" s="1" customFormat="1" spans="3:35">
       <c r="C58" s="1">
         <v>11004</v>
       </c>
@@ -6516,10 +6663,10 @@
         <v>1004</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G58" s="1">
         <v>7</v>
@@ -6545,36 +6692,33 @@
       <c r="O58" s="1">
         <v>0</v>
       </c>
-      <c r="P58" s="1">
-        <v>0</v>
-      </c>
-      <c r="R58" s="1">
+      <c r="Q58" s="1">
+        <v>0</v>
+      </c>
+      <c r="S58" s="1">
         <v>4</v>
-      </c>
-      <c r="S58" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="T58" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="U58" s="1">
+      <c r="U58" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="V58" s="1">
         <v>2</v>
       </c>
-      <c r="V58" s="1">
-        <v>1</v>
-      </c>
       <c r="W58" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X58" s="1">
         <v>0</v>
       </c>
       <c r="Y58" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="1">
         <v>200</v>
       </c>
-      <c r="Z58" s="1">
-        <v>0</v>
-      </c>
       <c r="AA58" s="1">
         <v>0</v>
       </c>
@@ -6590,17 +6734,20 @@
       <c r="AE58" s="1">
         <v>0</v>
       </c>
-      <c r="AF58" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="AG58" s="1">
-        <v>50</v>
+      <c r="AF58" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="AH58" s="1">
         <v>50</v>
       </c>
+      <c r="AI58" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="59" s="1" customFormat="1" spans="3:34">
+    <row r="59" s="1" customFormat="1" spans="3:35">
       <c r="C59" s="1">
         <v>11005</v>
       </c>
@@ -6608,10 +6755,10 @@
         <v>1005</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G59" s="1">
         <v>5</v>
@@ -6637,24 +6784,21 @@
       <c r="O59" s="1">
         <v>0</v>
       </c>
-      <c r="P59" s="1">
-        <v>0</v>
-      </c>
-      <c r="R59" s="1">
-        <v>0</v>
-      </c>
-      <c r="S59" s="1" t="s">
-        <v>67</v>
+      <c r="Q59" s="1">
+        <v>0</v>
+      </c>
+      <c r="S59" s="1">
+        <v>0</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U59" s="1">
+        <v>68</v>
+      </c>
+      <c r="U59" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="V59" s="1">
         <v>30</v>
       </c>
-      <c r="V59" s="1">
-        <v>0</v>
-      </c>
       <c r="W59" s="1">
         <v>0</v>
       </c>
@@ -6662,11 +6806,11 @@
         <v>0</v>
       </c>
       <c r="Y59" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="1">
         <v>20</v>
       </c>
-      <c r="Z59" s="1">
-        <v>0</v>
-      </c>
       <c r="AA59" s="1">
         <v>0</v>
       </c>
@@ -6682,15 +6826,18 @@
       <c r="AE59" s="1">
         <v>0</v>
       </c>
-      <c r="AF59" s="5"/>
-      <c r="AG59" s="1">
-        <v>50</v>
-      </c>
+      <c r="AF59" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG59" s="5"/>
       <c r="AH59" s="1">
         <v>50</v>
       </c>
+      <c r="AI59" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="60" s="1" customFormat="1" spans="3:34">
+    <row r="60" s="1" customFormat="1" spans="3:35">
       <c r="C60" s="1">
         <v>11006</v>
       </c>
@@ -6698,10 +6845,10 @@
         <v>1006</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G60" s="1">
         <v>6</v>
@@ -6727,20 +6874,17 @@
       <c r="O60" s="1">
         <v>0</v>
       </c>
-      <c r="P60" s="1">
-        <v>0</v>
-      </c>
-      <c r="R60" s="1">
-        <v>0</v>
-      </c>
-      <c r="S60" s="1" t="s">
-        <v>67</v>
+      <c r="Q60" s="1">
+        <v>0</v>
+      </c>
+      <c r="S60" s="1">
+        <v>0</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="U60" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="U60" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="V60" s="1">
         <v>0</v>
@@ -6752,10 +6896,10 @@
         <v>0</v>
       </c>
       <c r="Y60" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Z60" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AA60" s="1">
         <v>0</v>
@@ -6772,14 +6916,17 @@
       <c r="AE60" s="1">
         <v>0</v>
       </c>
-      <c r="AG60" s="1">
-        <v>50</v>
+      <c r="AF60" s="1">
+        <v>0</v>
       </c>
       <c r="AH60" s="1">
         <v>50</v>
       </c>
+      <c r="AI60" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="61" s="1" customFormat="1" spans="3:34">
+    <row r="61" s="1" customFormat="1" spans="3:35">
       <c r="C61" s="1">
         <v>11007</v>
       </c>
@@ -6787,10 +6934,10 @@
         <v>1007</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G61" s="1">
         <v>1</v>
@@ -6816,36 +6963,33 @@
       <c r="O61" s="1">
         <v>0</v>
       </c>
-      <c r="P61" s="1">
-        <v>0</v>
-      </c>
-      <c r="R61" s="1">
-        <v>1</v>
-      </c>
-      <c r="S61" s="1" t="s">
-        <v>67</v>
+      <c r="Q61" s="1">
+        <v>0</v>
+      </c>
+      <c r="S61" s="1">
+        <v>1</v>
       </c>
       <c r="T61" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="U61" s="1">
-        <v>0</v>
+      <c r="U61" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="V61" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W61" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X61" s="1">
         <v>0</v>
       </c>
       <c r="Y61" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="1">
         <v>300</v>
       </c>
-      <c r="Z61" s="1">
-        <v>0</v>
-      </c>
       <c r="AA61" s="1">
         <v>0</v>
       </c>
@@ -6861,14 +7005,17 @@
       <c r="AE61" s="1">
         <v>0</v>
       </c>
-      <c r="AG61" s="1">
-        <v>50</v>
+      <c r="AF61" s="1">
+        <v>0</v>
       </c>
       <c r="AH61" s="1">
         <v>50</v>
       </c>
+      <c r="AI61" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="62" s="1" customFormat="1" spans="3:34">
+    <row r="62" s="1" customFormat="1" spans="3:35">
       <c r="C62" s="1">
         <v>12001</v>
       </c>
@@ -6876,10 +7023,10 @@
         <v>2001</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G62" s="1">
         <v>1</v>
@@ -6905,36 +7052,33 @@
       <c r="O62" s="1">
         <v>0</v>
       </c>
-      <c r="P62" s="1">
-        <v>0</v>
-      </c>
-      <c r="R62" s="1">
+      <c r="Q62" s="1">
+        <v>0</v>
+      </c>
+      <c r="S62" s="1">
         <v>2</v>
       </c>
-      <c r="S62" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="T62" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="U62" s="1">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="U62" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="V62" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W62" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X62" s="1">
         <v>0</v>
       </c>
       <c r="Y62" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="1">
         <v>120</v>
       </c>
-      <c r="Z62" s="1">
-        <v>0</v>
-      </c>
       <c r="AA62" s="1">
         <v>0</v>
       </c>
@@ -6950,14 +7094,17 @@
       <c r="AE62" s="1">
         <v>0</v>
       </c>
-      <c r="AG62" s="1">
-        <v>50</v>
+      <c r="AF62" s="1">
+        <v>0</v>
       </c>
       <c r="AH62" s="1">
         <v>50</v>
       </c>
+      <c r="AI62" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="63" s="1" customFormat="1" spans="3:34">
+    <row r="63" s="1" customFormat="1" spans="3:35">
       <c r="C63" s="1">
         <v>12002</v>
       </c>
@@ -6965,10 +7112,10 @@
         <v>2002</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G63" s="1">
         <v>1</v>
@@ -6994,36 +7141,33 @@
       <c r="O63" s="1">
         <v>0</v>
       </c>
-      <c r="P63" s="1">
-        <v>0</v>
-      </c>
-      <c r="R63" s="1">
+      <c r="Q63" s="1">
+        <v>0</v>
+      </c>
+      <c r="S63" s="1">
         <v>3</v>
       </c>
-      <c r="S63" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="T63" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="U63" s="1">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="U63" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="V63" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W63" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X63" s="1">
         <v>0</v>
       </c>
       <c r="Y63" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="1">
         <v>150</v>
       </c>
-      <c r="Z63" s="1">
-        <v>0</v>
-      </c>
       <c r="AA63" s="1">
         <v>0</v>
       </c>
@@ -7039,14 +7183,17 @@
       <c r="AE63" s="1">
         <v>0</v>
       </c>
-      <c r="AG63" s="1">
-        <v>50</v>
+      <c r="AF63" s="1">
+        <v>0</v>
       </c>
       <c r="AH63" s="1">
         <v>50</v>
       </c>
+      <c r="AI63" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="64" s="1" customFormat="1" spans="3:34">
+    <row r="64" s="1" customFormat="1" spans="3:35">
       <c r="C64" s="1">
         <v>12003</v>
       </c>
@@ -7054,10 +7201,10 @@
         <v>2003</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G64" s="1">
         <v>3</v>
@@ -7083,36 +7230,33 @@
       <c r="O64" s="1">
         <v>0</v>
       </c>
-      <c r="P64" s="1">
-        <v>0</v>
-      </c>
-      <c r="R64" s="1">
+      <c r="Q64" s="1">
+        <v>0</v>
+      </c>
+      <c r="S64" s="1">
         <v>3</v>
       </c>
-      <c r="S64" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="T64" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U64" s="1">
-        <v>5</v>
+        <v>79</v>
+      </c>
+      <c r="U64" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="V64" s="1">
         <v>5</v>
       </c>
       <c r="W64" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="X64" s="1">
         <v>2</v>
       </c>
       <c r="Y64" s="1">
+        <v>2</v>
+      </c>
+      <c r="Z64" s="1">
         <v>80</v>
       </c>
-      <c r="Z64" s="1">
-        <v>0</v>
-      </c>
       <c r="AA64" s="1">
         <v>0</v>
       </c>
@@ -7128,14 +7272,17 @@
       <c r="AE64" s="1">
         <v>0</v>
       </c>
-      <c r="AG64" s="1">
-        <v>50</v>
+      <c r="AF64" s="1">
+        <v>0</v>
       </c>
       <c r="AH64" s="1">
         <v>50</v>
       </c>
+      <c r="AI64" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="65" s="1" customFormat="1" spans="3:34">
+    <row r="65" s="1" customFormat="1" spans="3:35">
       <c r="C65" s="1">
         <v>12004</v>
       </c>
@@ -7143,10 +7290,10 @@
         <v>2004</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G65" s="1">
         <v>1</v>
@@ -7172,36 +7319,33 @@
       <c r="O65" s="1">
         <v>0</v>
       </c>
-      <c r="P65" s="1">
-        <v>0</v>
-      </c>
-      <c r="R65" s="1">
+      <c r="Q65" s="1">
+        <v>0</v>
+      </c>
+      <c r="S65" s="1">
         <v>4</v>
       </c>
-      <c r="S65" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="T65" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U65" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="U65" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="V65" s="1">
+        <v>0</v>
+      </c>
+      <c r="W65" s="1">
         <v>4</v>
-      </c>
-      <c r="W65" s="1">
-        <v>2</v>
       </c>
       <c r="X65" s="1">
         <v>2</v>
       </c>
       <c r="Y65" s="1">
+        <v>2</v>
+      </c>
+      <c r="Z65" s="1">
         <v>100</v>
       </c>
-      <c r="Z65" s="1">
-        <v>0</v>
-      </c>
       <c r="AA65" s="1">
         <v>0</v>
       </c>
@@ -7217,14 +7361,17 @@
       <c r="AE65" s="1">
         <v>0</v>
       </c>
-      <c r="AG65" s="1">
-        <v>50</v>
+      <c r="AF65" s="1">
+        <v>0</v>
       </c>
       <c r="AH65" s="1">
         <v>50</v>
       </c>
+      <c r="AI65" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="66" s="1" customFormat="1" spans="3:34">
+    <row r="66" s="1" customFormat="1" spans="3:35">
       <c r="C66" s="1">
         <v>12005</v>
       </c>
@@ -7232,10 +7379,10 @@
         <v>2005</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G66" s="1">
         <v>5</v>
@@ -7261,24 +7408,21 @@
       <c r="O66" s="1">
         <v>0</v>
       </c>
-      <c r="P66" s="1">
-        <v>0</v>
-      </c>
-      <c r="R66" s="1">
-        <v>0</v>
-      </c>
-      <c r="S66" s="1" t="s">
-        <v>67</v>
+      <c r="Q66" s="1">
+        <v>0</v>
+      </c>
+      <c r="S66" s="1">
+        <v>0</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U66" s="1">
+        <v>68</v>
+      </c>
+      <c r="U66" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="V66" s="1">
         <v>30</v>
       </c>
-      <c r="V66" s="1">
-        <v>0</v>
-      </c>
       <c r="W66" s="1">
         <v>0</v>
       </c>
@@ -7286,11 +7430,11 @@
         <v>0</v>
       </c>
       <c r="Y66" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z66" s="1">
         <v>20</v>
       </c>
-      <c r="Z66" s="1">
-        <v>0</v>
-      </c>
       <c r="AA66" s="1">
         <v>0</v>
       </c>
@@ -7306,15 +7450,18 @@
       <c r="AE66" s="1">
         <v>0</v>
       </c>
-      <c r="AF66" s="5"/>
-      <c r="AG66" s="1">
-        <v>50</v>
-      </c>
+      <c r="AF66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG66" s="5"/>
       <c r="AH66" s="1">
         <v>50</v>
       </c>
+      <c r="AI66" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="67" s="1" customFormat="1" spans="3:34">
+    <row r="67" s="1" customFormat="1" spans="3:35">
       <c r="C67" s="1">
         <v>12006</v>
       </c>
@@ -7322,10 +7469,10 @@
         <v>2006</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G67" s="1">
         <v>6</v>
@@ -7351,20 +7498,17 @@
       <c r="O67" s="1">
         <v>0</v>
       </c>
-      <c r="P67" s="1">
-        <v>0</v>
-      </c>
-      <c r="R67" s="1">
-        <v>0</v>
-      </c>
-      <c r="S67" s="1" t="s">
-        <v>67</v>
+      <c r="Q67" s="1">
+        <v>0</v>
+      </c>
+      <c r="S67" s="1">
+        <v>0</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="U67" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="U67" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="V67" s="1">
         <v>0</v>
@@ -7376,10 +7520,10 @@
         <v>0</v>
       </c>
       <c r="Y67" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Z67" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AA67" s="1">
         <v>0</v>
@@ -7396,14 +7540,17 @@
       <c r="AE67" s="1">
         <v>0</v>
       </c>
-      <c r="AG67" s="1">
-        <v>50</v>
+      <c r="AF67" s="1">
+        <v>0</v>
       </c>
       <c r="AH67" s="1">
         <v>50</v>
       </c>
+      <c r="AI67" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="68" s="1" customFormat="1" spans="3:34">
+    <row r="68" s="1" customFormat="1" spans="3:35">
       <c r="C68" s="1">
         <v>12007</v>
       </c>
@@ -7411,10 +7558,10 @@
         <v>2007</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G68" s="1">
         <v>1</v>
@@ -7440,36 +7587,33 @@
       <c r="O68" s="1">
         <v>0</v>
       </c>
-      <c r="P68" s="1">
-        <v>0</v>
-      </c>
-      <c r="R68" s="1">
+      <c r="Q68" s="1">
+        <v>0</v>
+      </c>
+      <c r="S68" s="1">
         <v>5</v>
       </c>
-      <c r="S68" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="T68" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U68" s="1">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="U68" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="V68" s="1">
+        <v>0</v>
+      </c>
+      <c r="W68" s="1">
         <v>5</v>
-      </c>
-      <c r="W68" s="1">
-        <v>3</v>
       </c>
       <c r="X68" s="1">
         <v>3</v>
       </c>
       <c r="Y68" s="1">
+        <v>3</v>
+      </c>
+      <c r="Z68" s="1">
         <v>150</v>
       </c>
-      <c r="Z68" s="1">
-        <v>0</v>
-      </c>
       <c r="AA68" s="1">
         <v>0</v>
       </c>
@@ -7485,14 +7629,17 @@
       <c r="AE68" s="1">
         <v>0</v>
       </c>
-      <c r="AG68" s="1">
-        <v>50</v>
+      <c r="AF68" s="1">
+        <v>0</v>
       </c>
       <c r="AH68" s="1">
         <v>50</v>
       </c>
+      <c r="AI68" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="69" s="1" customFormat="1" spans="3:34">
+    <row r="69" s="1" customFormat="1" spans="3:35">
       <c r="C69" s="1">
         <v>13001</v>
       </c>
@@ -7500,10 +7647,10 @@
         <v>3001</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G69" s="1">
         <v>4</v>
@@ -7529,20 +7676,17 @@
       <c r="O69" s="1">
         <v>0</v>
       </c>
-      <c r="P69" s="1">
-        <v>0</v>
-      </c>
-      <c r="R69" s="1">
-        <v>0</v>
-      </c>
-      <c r="S69" s="1" t="s">
-        <v>67</v>
+      <c r="Q69" s="1">
+        <v>0</v>
+      </c>
+      <c r="S69" s="1">
+        <v>0</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U69" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="U69" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="V69" s="1">
         <v>0</v>
@@ -7554,10 +7698,10 @@
         <v>0</v>
       </c>
       <c r="Y69" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Z69" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AA69" s="1">
         <v>0</v>
@@ -7574,14 +7718,17 @@
       <c r="AE69" s="1">
         <v>0</v>
       </c>
-      <c r="AG69" s="1">
-        <v>50</v>
+      <c r="AF69" s="1">
+        <v>0</v>
       </c>
       <c r="AH69" s="1">
         <v>50</v>
       </c>
+      <c r="AI69" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="70" s="1" customFormat="1" spans="3:34">
+    <row r="70" s="1" customFormat="1" spans="3:35">
       <c r="C70" s="1">
         <v>13002</v>
       </c>
@@ -7589,10 +7736,10 @@
         <v>3002</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G70" s="1">
         <v>1</v>
@@ -7618,36 +7765,33 @@
       <c r="O70" s="1">
         <v>0</v>
       </c>
-      <c r="P70" s="1">
-        <v>0</v>
-      </c>
-      <c r="R70" s="1">
+      <c r="Q70" s="1">
+        <v>0</v>
+      </c>
+      <c r="S70" s="1">
         <v>3</v>
       </c>
-      <c r="S70" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="T70" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="U70" s="1">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="U70" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="V70" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W70" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X70" s="1">
         <v>0</v>
       </c>
       <c r="Y70" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="1">
         <v>120</v>
       </c>
-      <c r="Z70" s="1">
-        <v>0</v>
-      </c>
       <c r="AA70" s="1">
         <v>0</v>
       </c>
@@ -7663,14 +7807,17 @@
       <c r="AE70" s="1">
         <v>0</v>
       </c>
-      <c r="AG70" s="1">
-        <v>50</v>
+      <c r="AF70" s="1">
+        <v>0</v>
       </c>
       <c r="AH70" s="1">
         <v>50</v>
       </c>
+      <c r="AI70" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="71" s="1" customFormat="1" spans="3:34">
+    <row r="71" s="1" customFormat="1" spans="3:35">
       <c r="C71" s="1">
         <v>13003</v>
       </c>
@@ -7678,10 +7825,10 @@
         <v>3003</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G71" s="1">
         <v>1</v>
@@ -7707,42 +7854,39 @@
       <c r="O71" s="1">
         <v>0</v>
       </c>
-      <c r="P71" s="1">
-        <v>0</v>
-      </c>
-      <c r="R71" s="1">
+      <c r="Q71" s="1">
+        <v>0</v>
+      </c>
+      <c r="S71" s="1">
         <v>2</v>
       </c>
-      <c r="S71" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="T71" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="U71" s="1">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="U71" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="V71" s="1">
+        <v>0</v>
+      </c>
+      <c r="W71" s="1">
         <v>5</v>
       </c>
-      <c r="W71" s="1">
-        <v>0</v>
-      </c>
       <c r="X71" s="1">
         <v>0</v>
       </c>
       <c r="Y71" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="1">
         <v>35</v>
       </c>
-      <c r="Z71" s="1">
-        <v>0</v>
-      </c>
       <c r="AA71" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB71" s="1">
         <v>65</v>
       </c>
-      <c r="AB71" s="1">
-        <v>0</v>
-      </c>
       <c r="AC71" s="1">
         <v>0</v>
       </c>
@@ -7752,14 +7896,17 @@
       <c r="AE71" s="1">
         <v>0</v>
       </c>
-      <c r="AG71" s="1">
-        <v>50</v>
+      <c r="AF71" s="1">
+        <v>0</v>
       </c>
       <c r="AH71" s="1">
         <v>50</v>
       </c>
+      <c r="AI71" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="72" s="1" customFormat="1" spans="3:34">
+    <row r="72" s="1" customFormat="1" spans="3:35">
       <c r="C72" s="1">
         <v>13004</v>
       </c>
@@ -7767,10 +7914,10 @@
         <v>3004</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G72" s="1">
         <v>2</v>
@@ -7796,36 +7943,33 @@
       <c r="O72" s="1">
         <v>0</v>
       </c>
-      <c r="P72" s="1">
-        <v>0</v>
-      </c>
-      <c r="R72" s="1">
-        <v>0</v>
-      </c>
-      <c r="S72" s="1" t="s">
-        <v>67</v>
+      <c r="Q72" s="1">
+        <v>0</v>
+      </c>
+      <c r="S72" s="1">
+        <v>0</v>
       </c>
       <c r="T72" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="U72" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="U72" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="V72" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W72" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X72" s="1">
         <v>0</v>
       </c>
       <c r="Y72" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z72" s="1">
         <v>100</v>
       </c>
-      <c r="Z72" s="1">
-        <v>0</v>
-      </c>
       <c r="AA72" s="1">
         <v>0</v>
       </c>
@@ -7841,14 +7985,17 @@
       <c r="AE72" s="1">
         <v>0</v>
       </c>
-      <c r="AG72" s="1">
-        <v>50</v>
+      <c r="AF72" s="1">
+        <v>0</v>
       </c>
       <c r="AH72" s="1">
         <v>50</v>
       </c>
+      <c r="AI72" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="73" s="1" customFormat="1" spans="3:34">
+    <row r="73" s="1" customFormat="1" spans="3:35">
       <c r="C73" s="1">
         <v>13005</v>
       </c>
@@ -7856,10 +8003,10 @@
         <v>3005</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G73" s="1">
         <v>5</v>
@@ -7885,24 +8032,21 @@
       <c r="O73" s="1">
         <v>0</v>
       </c>
-      <c r="P73" s="1">
-        <v>0</v>
-      </c>
-      <c r="R73" s="1">
-        <v>0</v>
-      </c>
-      <c r="S73" s="1" t="s">
-        <v>67</v>
+      <c r="Q73" s="1">
+        <v>0</v>
+      </c>
+      <c r="S73" s="1">
+        <v>0</v>
       </c>
       <c r="T73" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U73" s="1">
+        <v>68</v>
+      </c>
+      <c r="U73" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="V73" s="1">
         <v>30</v>
       </c>
-      <c r="V73" s="1">
-        <v>0</v>
-      </c>
       <c r="W73" s="1">
         <v>0</v>
       </c>
@@ -7910,11 +8054,11 @@
         <v>0</v>
       </c>
       <c r="Y73" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="1">
         <v>20</v>
       </c>
-      <c r="Z73" s="1">
-        <v>0</v>
-      </c>
       <c r="AA73" s="1">
         <v>0</v>
       </c>
@@ -7930,15 +8074,18 @@
       <c r="AE73" s="1">
         <v>0</v>
       </c>
-      <c r="AF73" s="5"/>
-      <c r="AG73" s="1">
-        <v>50</v>
-      </c>
+      <c r="AF73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="5"/>
       <c r="AH73" s="1">
         <v>50</v>
       </c>
+      <c r="AI73" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="74" s="1" customFormat="1" spans="3:34">
+    <row r="74" s="1" customFormat="1" spans="3:35">
       <c r="C74" s="1">
         <v>13006</v>
       </c>
@@ -7946,10 +8093,10 @@
         <v>3006</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G74" s="1">
         <v>6</v>
@@ -7975,20 +8122,17 @@
       <c r="O74" s="1">
         <v>0</v>
       </c>
-      <c r="P74" s="1">
-        <v>0</v>
-      </c>
-      <c r="R74" s="1">
+      <c r="Q74" s="1">
+        <v>0</v>
+      </c>
+      <c r="S74" s="1">
         <v>3</v>
       </c>
-      <c r="S74" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="T74" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="U74" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="U74" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="V74" s="1">
         <v>0</v>
@@ -8000,10 +8144,10 @@
         <v>0</v>
       </c>
       <c r="Y74" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Z74" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AA74" s="1">
         <v>0</v>
@@ -8020,14 +8164,17 @@
       <c r="AE74" s="1">
         <v>0</v>
       </c>
-      <c r="AG74" s="1">
-        <v>50</v>
+      <c r="AF74" s="1">
+        <v>0</v>
       </c>
       <c r="AH74" s="1">
         <v>50</v>
       </c>
+      <c r="AI74" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="75" s="1" customFormat="1" spans="3:34">
+    <row r="75" s="1" customFormat="1" spans="3:35">
       <c r="C75" s="1">
         <v>13007</v>
       </c>
@@ -8035,10 +8182,10 @@
         <v>3007</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G75" s="1">
         <v>2</v>
@@ -8064,36 +8211,33 @@
       <c r="O75" s="1">
         <v>0</v>
       </c>
-      <c r="P75" s="1">
-        <v>0</v>
-      </c>
-      <c r="R75" s="1">
+      <c r="Q75" s="1">
+        <v>0</v>
+      </c>
+      <c r="S75" s="1">
         <v>2</v>
       </c>
-      <c r="S75" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="T75" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U75" s="1">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="U75" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="V75" s="1">
+        <v>0</v>
+      </c>
+      <c r="W75" s="1">
         <v>2</v>
       </c>
-      <c r="W75" s="1">
-        <v>0</v>
-      </c>
       <c r="X75" s="1">
         <v>0</v>
       </c>
       <c r="Y75" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="1">
         <v>120</v>
       </c>
-      <c r="Z75" s="1">
-        <v>0</v>
-      </c>
       <c r="AA75" s="1">
         <v>0</v>
       </c>
@@ -8109,14 +8253,17 @@
       <c r="AE75" s="1">
         <v>0</v>
       </c>
-      <c r="AG75" s="1">
-        <v>50</v>
+      <c r="AF75" s="1">
+        <v>0</v>
       </c>
       <c r="AH75" s="1">
         <v>50</v>
       </c>
+      <c r="AI75" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="76" s="1" customFormat="1" spans="5:17">
+    <row r="76" s="1" customFormat="1" spans="5:18">
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
       <c r="J76" s="2"/>
@@ -8124,8 +8271,9 @@
       <c r="O76" s="2"/>
       <c r="P76" s="2"/>
       <c r="Q76" s="2"/>
+      <c r="R76" s="2"/>
     </row>
-    <row r="77" s="1" customFormat="1" spans="3:34">
+    <row r="77" s="1" customFormat="1" spans="3:35">
       <c r="C77" s="1">
         <v>21002</v>
       </c>
@@ -8133,10 +8281,10 @@
         <v>1002</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G77" s="1">
         <v>1</v>
@@ -8162,42 +8310,39 @@
       <c r="O77" s="1">
         <v>0</v>
       </c>
-      <c r="P77" s="1">
-        <v>0</v>
-      </c>
-      <c r="R77" s="1">
+      <c r="Q77" s="1">
+        <v>0</v>
+      </c>
+      <c r="S77" s="1">
         <v>2</v>
-      </c>
-      <c r="S77" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="T77" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="U77" s="1">
-        <v>0</v>
+      <c r="U77" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="V77" s="1">
+        <v>0</v>
+      </c>
+      <c r="W77" s="1">
         <v>2</v>
       </c>
-      <c r="W77" s="1">
-        <v>0</v>
-      </c>
       <c r="X77" s="1">
         <v>0</v>
       </c>
       <c r="Y77" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="1">
         <v>150</v>
       </c>
-      <c r="Z77" s="1">
-        <v>0</v>
-      </c>
       <c r="AA77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="1">
         <v>20</v>
       </c>
-      <c r="AB77" s="1">
-        <v>0</v>
-      </c>
       <c r="AC77" s="1">
         <v>0</v>
       </c>
@@ -8207,13 +8352,16 @@
       <c r="AE77" s="1">
         <v>0</v>
       </c>
-      <c r="AF77" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="AG77" s="1">
-        <v>50</v>
+      <c r="AF77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="AH77" s="1">
+        <v>50</v>
+      </c>
+      <c r="AI77" s="1">
         <v>50</v>
       </c>
     </row>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -3083,8 +3083,7 @@
         <v>1</v>
       </c>
       <c r="P15" s="1">
-        <f t="shared" si="0"/>
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="Q15" s="1">
         <v>10</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3383,8 +3383,8 @@
         <v>60</v>
       </c>
       <c r="P19" s="1">
-        <f t="shared" si="1"/>
-        <v>3000</v>
+        <f>N19*2.5</f>
+        <v>1500</v>
       </c>
       <c r="Q19" s="1">
         <v>3</v>
@@ -5193,8 +5193,7 @@
         <v>30</v>
       </c>
       <c r="P38" s="1">
-        <f t="shared" si="2"/>
-        <v>1500</v>
+        <v>200</v>
       </c>
       <c r="Q38" s="1">
         <v>4</v>
@@ -5292,8 +5291,7 @@
         <v>1</v>
       </c>
       <c r="P39" s="1">
-        <f t="shared" si="2"/>
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="Q39" s="1">
         <v>1</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -687,7 +687,7 @@
     <t>治疗术</t>
   </si>
   <si>
-    <t>回复自己{1}%道术的生命</t>
+    <t>回复自己或者队友{1}%道术的生命</t>
   </si>
   <si>
     <t>火符术</t>
@@ -4392,8 +4392,7 @@
         <v>60</v>
       </c>
       <c r="P30" s="1">
-        <f>N30/20</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="Q30" s="1">
         <v>3</v>
@@ -4402,13 +4401,13 @@
         <v>0</v>
       </c>
       <c r="S30" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T30" s="1" t="s">
         <v>68</v>
       </c>
       <c r="U30" s="1" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="V30" s="1">
         <v>0</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -298,7 +298,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="191">
   <si>
     <t>_ID</t>
   </si>
@@ -510,304 +510,364 @@
     <t>FrontRow</t>
   </si>
   <si>
+    <t>穿刺剑术</t>
+  </si>
+  <si>
+    <t>刺杀</t>
+  </si>
+  <si>
+    <t>对直线内的敌人造成{1}%物攻伤害,忽视敌方50%防御</t>
+  </si>
+  <si>
+    <t>圆月弯刀</t>
+  </si>
+  <si>
+    <t>半月弯刀</t>
+  </si>
+  <si>
+    <t>对周围的{0}个敌人造成{1}%物攻伤害</t>
+  </si>
+  <si>
+    <t>Arc</t>
+  </si>
+  <si>
+    <t>"14,60,3,10"</t>
+  </si>
+  <si>
+    <t>蛮力撞击</t>
+  </si>
+  <si>
+    <t>野蛮撞击</t>
+  </si>
+  <si>
+    <t>对{0}个敌人造成{1}%物攻伤害，并且晕眩2秒</t>
+  </si>
+  <si>
+    <t>Enemy</t>
+  </si>
+  <si>
+    <t>Chase</t>
+  </si>
+  <si>
+    <t>"306,2,0,0"</t>
+  </si>
+  <si>
+    <t>武力盾</t>
+  </si>
+  <si>
+    <t>持续{2}秒</t>
+  </si>
+  <si>
+    <t>Square</t>
+  </si>
+  <si>
+    <t>"14,0,0,10","4,0,0,0","5,0,0,0"</t>
+  </si>
+  <si>
+    <t>武力精通</t>
+  </si>
+  <si>
+    <t>战士技能增加{1}%技能系数</t>
+  </si>
+  <si>
+    <t>FullBox</t>
+  </si>
+  <si>
+    <t>火焰剑法</t>
+  </si>
+  <si>
+    <t>烈火</t>
+  </si>
+  <si>
+    <t>对{0}个敌人造成{1}%物攻伤害,忽视敌方50%防御</t>
+  </si>
+  <si>
+    <t>"103,4,0,25","101,0,0,10"</t>
+  </si>
+  <si>
+    <t>护体神盾</t>
+  </si>
+  <si>
+    <t>免疫{2}秒控制</t>
+  </si>
+  <si>
+    <t>"401,20,0,0","6,360,3,1","9,360,3,0"</t>
+  </si>
+  <si>
+    <t>开天辟地</t>
+  </si>
+  <si>
+    <t>开天斩</t>
+  </si>
+  <si>
+    <t>"109,0,0,5"</t>
+  </si>
+  <si>
+    <t>地刺术</t>
+  </si>
+  <si>
+    <t>彻地钉</t>
+  </si>
+  <si>
+    <t>释放战士攻击技能后，有20%概率触发，对周围2格范围内，造原技能伤害*20%*{1}%的真实伤害</t>
+  </si>
+  <si>
+    <t>Circle</t>
+  </si>
+  <si>
+    <t>战士之魂</t>
+  </si>
+  <si>
+    <t>上阵后，提高人物{1}%的生命倍率和{5}%的物攻倍率（分身和宠物不享受）</t>
+  </si>
+  <si>
+    <t>火球术</t>
+  </si>
+  <si>
+    <t>小火球</t>
+  </si>
+  <si>
+    <t>对{0}个敌人敌人造成{1}%魔法伤害</t>
+  </si>
+  <si>
+    <t>神雷术</t>
+  </si>
+  <si>
+    <t>雷电术</t>
+  </si>
+  <si>
+    <t>对{0}个敌人敌人造成{1}%魔法伤害,忽视敌方50%防御</t>
+  </si>
+  <si>
+    <t>火墙术</t>
+  </si>
+  <si>
+    <t>火墙</t>
+  </si>
+  <si>
+    <t>施展{3}*{4}范围的火墙，持续{2}s，对其内的敌人每秒造成{1}%魔法伤害</t>
+  </si>
+  <si>
+    <t>火焰术</t>
+  </si>
+  <si>
+    <t>抗拒火环</t>
+  </si>
+  <si>
+    <t>对{3}*{4}范围内的敌人造成{1}%魔法伤害</t>
+  </si>
+  <si>
+    <t>"12,60,3,10"</t>
+  </si>
+  <si>
+    <t>魔法盾</t>
+  </si>
+  <si>
+    <t>法术精通</t>
+  </si>
+  <si>
+    <t>法师技能增加{1}%技能系数</t>
+  </si>
+  <si>
+    <t>冰冻术</t>
+  </si>
+  <si>
+    <t>冰咆哮</t>
+  </si>
+  <si>
+    <t>"305,1,1,0"</t>
+  </si>
+  <si>
+    <t>闪烁术</t>
+  </si>
+  <si>
+    <t>瞬息移动</t>
+  </si>
+  <si>
+    <t>随机到一个空位</t>
+  </si>
+  <si>
+    <t>"10,360,3,0"</t>
+  </si>
+  <si>
+    <t>火雨术</t>
+  </si>
+  <si>
+    <t>流星火雨</t>
+  </si>
+  <si>
+    <t>施展{3}*{4}范围的火雨，持续{2}s，对其内的敌人每秒造成{1}%魔法伤害</t>
+  </si>
+  <si>
+    <t>"103,5,1,100"</t>
+  </si>
+  <si>
+    <t>分身术</t>
+  </si>
+  <si>
+    <t>创造一个{2}秒的分身，继承其他技能(除此技能和召唤技能)，魔攻为*{1}%，物攻道攻为继承一半，其他属性完全继承。</t>
+  </si>
+  <si>
+    <t>法师之魂</t>
+  </si>
+  <si>
+    <t>上阵后，提高人物{1}%的生命倍率和{5}%的魔攻倍率（分身和宠物不享受）</t>
+  </si>
+  <si>
+    <t>治疗道法</t>
+  </si>
+  <si>
+    <t>治疗术</t>
+  </si>
+  <si>
+    <t>回复自己或者队友{1}%道术的生命</t>
+  </si>
+  <si>
+    <t>火符道法</t>
+  </si>
+  <si>
+    <t>火符术</t>
+  </si>
+  <si>
+    <t>对{0}个敌人造成{1}%道术伤害</t>
+  </si>
+  <si>
+    <t>毒咒道法</t>
+  </si>
+  <si>
+    <t>施毒术</t>
+  </si>
+  <si>
+    <t>对{0}个敌人造成每秒{1}%道术持续伤害，无视60%防御</t>
+  </si>
+  <si>
+    <t>"104,5,0,35"</t>
+  </si>
+  <si>
+    <t>召唤金刚</t>
+  </si>
+  <si>
+    <t>召唤骷髅</t>
+  </si>
+  <si>
+    <t>召唤{0}只骷髅战斗，额外继承{1}%人物属性</t>
+  </si>
+  <si>
+    <t>道力盾</t>
+  </si>
+  <si>
+    <t>道力精通</t>
+  </si>
+  <si>
+    <t>道士技能增加{1}%技能系数</t>
+  </si>
+  <si>
+    <t>召唤魔兽</t>
+  </si>
+  <si>
+    <t>召唤神兽</t>
+  </si>
+  <si>
+    <t>召唤{0}只神兽战斗，额外继承{1}%人物属性</t>
+  </si>
+  <si>
+    <t>隐身道法</t>
+  </si>
+  <si>
+    <t>隐身术</t>
+  </si>
+  <si>
+    <t>隐身持续{2}s</t>
+  </si>
+  <si>
+    <t>"8,360,3,0"</t>
+  </si>
+  <si>
+    <t>召唤护法</t>
+  </si>
+  <si>
+    <t>召唤月灵</t>
+  </si>
+  <si>
+    <t>召唤{0}只月灵战斗，额外继承{1}%人物属性</t>
+  </si>
+  <si>
+    <t>无极道体</t>
+  </si>
+  <si>
+    <t>提高召唤物的{1}%特殊继承,并且额外增加{5}%的生命</t>
+  </si>
+  <si>
+    <t>道士之魂</t>
+  </si>
+  <si>
+    <t>上阵后，提高人物{1}%的生命倍率和{5}%的道攻倍率（分身和宠物不享受）</t>
+  </si>
+  <si>
+    <t>定身神戒</t>
+  </si>
+  <si>
+    <t>麻痹敌人{2}S，CD30S</t>
+  </si>
+  <si>
+    <t>"307,2,0,0"</t>
+  </si>
+  <si>
+    <t>护体神戒</t>
+  </si>
+  <si>
+    <t>附加一个面板生命*{1}%盾，CD60S</t>
+  </si>
+  <si>
+    <t>重生神戒</t>
+  </si>
+  <si>
+    <t>复活自己并且免疫2S所有伤害，CD60S</t>
+  </si>
+  <si>
+    <t>"18,3,0,100"</t>
+  </si>
+  <si>
+    <t>普攻</t>
+  </si>
+  <si>
+    <t>远程普通</t>
+  </si>
+  <si>
+    <t>怪物雷电</t>
+  </si>
+  <si>
+    <t>默认</t>
+  </si>
+  <si>
+    <t>怪物治疗术</t>
+  </si>
+  <si>
+    <t>怪物治疗</t>
+  </si>
+  <si>
+    <t>群体地刺</t>
+  </si>
+  <si>
+    <t>怪物群疗</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>怪物刺杀</t>
+  </si>
+  <si>
     <t>刺杀剑术</t>
   </si>
   <si>
-    <t>刺杀</t>
-  </si>
-  <si>
-    <t>对直线内的敌人造成{1}%物攻伤害,忽视敌方50%防御</t>
-  </si>
-  <si>
-    <t>半月弯刀</t>
-  </si>
-  <si>
-    <t>对周围的{0}个敌人造成{1}%物攻伤害</t>
-  </si>
-  <si>
-    <t>Arc</t>
-  </si>
-  <si>
-    <t>"14,60,3,10"</t>
-  </si>
-  <si>
-    <t>野蛮撞击</t>
-  </si>
-  <si>
-    <t>对{0}个敌人造成{1}%物攻伤害，并且晕眩2秒</t>
-  </si>
-  <si>
-    <t>Enemy</t>
-  </si>
-  <si>
-    <t>Chase</t>
-  </si>
-  <si>
-    <t>"306,2,0,0"</t>
-  </si>
-  <si>
-    <t>武力盾</t>
-  </si>
-  <si>
-    <t>持续{2}秒</t>
-  </si>
-  <si>
-    <t>Square</t>
-  </si>
-  <si>
-    <t>"14,0,0,10","4,0,0,0","5,0,0,0"</t>
-  </si>
-  <si>
-    <t>武力精通</t>
-  </si>
-  <si>
-    <t>战士技能增加{1}%技能系数</t>
-  </si>
-  <si>
-    <t>FullBox</t>
+    <t>"306,1,0,0"</t>
   </si>
   <si>
     <t>烈火剑法</t>
   </si>
   <si>
-    <t>烈火</t>
-  </si>
-  <si>
-    <t>对{0}个敌人造成{1}%物攻伤害,忽视敌方50%防御</t>
-  </si>
-  <si>
-    <t>"103,4,0,25","101,0,0,10"</t>
-  </si>
-  <si>
-    <t>护体神盾</t>
-  </si>
-  <si>
-    <t>免疫{2}秒控制</t>
-  </si>
-  <si>
-    <t>"401,20,0,0","6,360,3,1","9,360,3,0"</t>
-  </si>
-  <si>
-    <t>开天斩</t>
-  </si>
-  <si>
-    <t>"109,0,0,5"</t>
-  </si>
-  <si>
-    <t>彻地钉</t>
-  </si>
-  <si>
-    <t>释放战士攻击技能后，有20%概率触发，对周围2格范围内，造原技能伤害*20%*{1}%的真实伤害</t>
-  </si>
-  <si>
-    <t>Circle</t>
-  </si>
-  <si>
-    <t>战士之魂</t>
-  </si>
-  <si>
-    <t>上阵后，提高人物{1}%的生命倍率和{5}%的物攻倍率（分身和宠物不享受）</t>
-  </si>
-  <si>
-    <t>小火球</t>
-  </si>
-  <si>
-    <t>对{0}个敌人敌人造成{1}%魔法伤害</t>
-  </si>
-  <si>
-    <t>雷电术</t>
-  </si>
-  <si>
-    <t>对{0}个敌人敌人造成{1}%魔法伤害,忽视敌方50%防御</t>
-  </si>
-  <si>
-    <t>火墙</t>
-  </si>
-  <si>
-    <t>施展{3}*{4}范围的火墙，持续{2}s，对其内的敌人每秒造成{1}%魔法伤害</t>
-  </si>
-  <si>
     <t>爆裂火焰</t>
-  </si>
-  <si>
-    <t>抗拒火环</t>
-  </si>
-  <si>
-    <t>对{3}*{4}范围内的敌人造成{1}%魔法伤害</t>
-  </si>
-  <si>
-    <t>"12,60,3,10"</t>
-  </si>
-  <si>
-    <t>魔法盾</t>
-  </si>
-  <si>
-    <t>法术精通</t>
-  </si>
-  <si>
-    <t>法师技能增加{1}%技能系数</t>
-  </si>
-  <si>
-    <t>冰咆哮</t>
-  </si>
-  <si>
-    <t>"305,1,1,0"</t>
-  </si>
-  <si>
-    <t>瞬息移动</t>
-  </si>
-  <si>
-    <t>随机到一个空位</t>
-  </si>
-  <si>
-    <t>"10,360,3,0"</t>
-  </si>
-  <si>
-    <t>流星火雨</t>
-  </si>
-  <si>
-    <t>施展{3}*{4}范围的火雨，持续{2}s，对其内的敌人每秒造成{1}%魔法伤害</t>
-  </si>
-  <si>
-    <t>"103,5,1,100"</t>
-  </si>
-  <si>
-    <t>分身术</t>
-  </si>
-  <si>
-    <t>创造一个{2}秒的分身，继承其他技能(除此技能和召唤技能)，魔攻为*{1}%，物攻道攻为继承一半，其他属性完全继承。</t>
-  </si>
-  <si>
-    <t>法师之魂</t>
-  </si>
-  <si>
-    <t>上阵后，提高人物{1}%的生命倍率和{5}%的魔攻倍率（分身和宠物不享受）</t>
-  </si>
-  <si>
-    <t>治疗术</t>
-  </si>
-  <si>
-    <t>回复自己或者队友{1}%道术的生命</t>
-  </si>
-  <si>
-    <t>火符术</t>
-  </si>
-  <si>
-    <t>对{0}个敌人造成{1}%道术伤害</t>
-  </si>
-  <si>
-    <t>施毒术</t>
-  </si>
-  <si>
-    <t>对{0}个敌人造成每秒{1}%道术持续伤害，无视60%防御</t>
-  </si>
-  <si>
-    <t>"104,5,0,35"</t>
-  </si>
-  <si>
-    <t>召唤骷髅</t>
-  </si>
-  <si>
-    <t>召唤{0}只骷髅战斗，额外继承{1}%人物属性</t>
-  </si>
-  <si>
-    <t>道力盾</t>
-  </si>
-  <si>
-    <t>道力精通</t>
-  </si>
-  <si>
-    <t>道士技能增加{1}%技能系数</t>
-  </si>
-  <si>
-    <t>召唤神兽</t>
-  </si>
-  <si>
-    <t>召唤{0}只神兽战斗，额外继承{1}%人物属性</t>
-  </si>
-  <si>
-    <t>隐身术</t>
-  </si>
-  <si>
-    <t>隐身持续{2}s</t>
-  </si>
-  <si>
-    <t>"8,360,3,0"</t>
-  </si>
-  <si>
-    <t>召唤月灵</t>
-  </si>
-  <si>
-    <t>召唤{0}只月灵战斗，额外继承{1}%人物属性</t>
-  </si>
-  <si>
-    <t>无极道体</t>
-  </si>
-  <si>
-    <t>提高召唤物的{1}%特殊继承,并且额外增加{5}%的生命</t>
-  </si>
-  <si>
-    <t>道士之魂</t>
-  </si>
-  <si>
-    <t>上阵后，提高人物{1}%的生命倍率和{5}%的道攻倍率（分身和宠物不享受）</t>
-  </si>
-  <si>
-    <t>麻痹神戒</t>
-  </si>
-  <si>
-    <t>麻痹敌人{2}S，CD30S</t>
-  </si>
-  <si>
-    <t>"307,2,0,0"</t>
-  </si>
-  <si>
-    <t>护体神戒</t>
-  </si>
-  <si>
-    <t>附加一个面板生命*{1}%盾，CD60S</t>
-  </si>
-  <si>
-    <t>复活神戒</t>
-  </si>
-  <si>
-    <t>复活自己并且免疫2S所有伤害，CD60S</t>
-  </si>
-  <si>
-    <t>"18,3,0,100"</t>
-  </si>
-  <si>
-    <t>普攻</t>
-  </si>
-  <si>
-    <t>远程普通</t>
-  </si>
-  <si>
-    <t>怪物雷电</t>
-  </si>
-  <si>
-    <t>默认</t>
-  </si>
-  <si>
-    <t>怪物治疗术</t>
-  </si>
-  <si>
-    <t>怪物治疗</t>
-  </si>
-  <si>
-    <t>群体地刺</t>
-  </si>
-  <si>
-    <t>怪物群疗</t>
-  </si>
-  <si>
-    <t>Team</t>
-  </si>
-  <si>
-    <t>怪物刺杀</t>
-  </si>
-  <si>
-    <t>"306,1,0,0"</t>
   </si>
   <si>
     <t>"101,0,0,20"</t>
@@ -823,7 +883,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -842,6 +902,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1330,16 +1396,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1348,125 +1411,129 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
@@ -2342,7 +2409,7 @@
         <v>73</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -2354,7 +2421,7 @@
         <v>10</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K8" s="1">
         <v>5</v>
@@ -2388,7 +2455,7 @@
         <v>68</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="V8" s="1">
         <v>0</v>
@@ -2424,7 +2491,7 @@
         <v>0</v>
       </c>
       <c r="AG8" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH8" s="1">
         <v>50</v>
@@ -2441,10 +2508,10 @@
         <v>1004</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G9" s="1">
         <v>7</v>
@@ -2456,7 +2523,7 @@
         <v>10</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K9" s="1">
         <v>10</v>
@@ -2487,10 +2554,10 @@
         <v>4</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="V9" s="1">
         <v>2</v>
@@ -2526,7 +2593,7 @@
         <v>0</v>
       </c>
       <c r="AG9" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AH9" s="1">
         <v>50</v>
@@ -2543,10 +2610,10 @@
         <v>1005</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G10" s="1">
         <v>5</v>
@@ -2558,7 +2625,7 @@
         <v>50</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K10" s="1">
         <v>55</v>
@@ -2592,7 +2659,7 @@
         <v>68</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V10" s="1">
         <v>30</v>
@@ -2627,8 +2694,8 @@
       <c r="AF10" s="1">
         <v>0</v>
       </c>
-      <c r="AG10" s="5" t="s">
-        <v>85</v>
+      <c r="AG10" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="AH10" s="1">
         <v>50</v>
@@ -2645,10 +2712,10 @@
         <v>1006</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G11" s="1">
         <v>6</v>
@@ -2660,7 +2727,7 @@
         <v>10</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K11" s="1">
         <v>0</v>
@@ -2694,7 +2761,7 @@
         <v>68</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="V11" s="1">
         <v>0</v>
@@ -2744,10 +2811,10 @@
         <v>1007</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
@@ -2759,9 +2826,9 @@
         <v>10</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="K12" s="4">
+        <v>93</v>
+      </c>
+      <c r="K12" s="5">
         <v>5</v>
       </c>
       <c r="L12" s="1">
@@ -2780,7 +2847,7 @@
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="Q12" s="4">
+      <c r="Q12" s="5">
         <v>10</v>
       </c>
       <c r="R12" s="1">
@@ -2807,7 +2874,7 @@
       <c r="Y12" s="1">
         <v>0</v>
       </c>
-      <c r="Z12" s="4">
+      <c r="Z12" s="5">
         <v>500</v>
       </c>
       <c r="AA12" s="1">
@@ -2828,8 +2895,8 @@
       <c r="AF12" s="1">
         <v>0</v>
       </c>
-      <c r="AG12" s="4" t="s">
-        <v>92</v>
+      <c r="AG12" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="AH12" s="1">
         <v>50</v>
@@ -2846,10 +2913,10 @@
         <v>1008</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G13" s="1">
         <v>1008</v>
@@ -2861,7 +2928,7 @@
         <v>200</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K13" s="1">
         <v>30</v>
@@ -2895,7 +2962,7 @@
         <v>68</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="V13" s="1">
         <v>20</v>
@@ -2931,7 +2998,7 @@
         <v>0</v>
       </c>
       <c r="AG13" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AH13" s="1">
         <v>50</v>
@@ -2948,10 +3015,10 @@
         <v>1009</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -3033,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="AG14" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AH14" s="1">
         <v>50</v>
@@ -3050,10 +3117,10 @@
         <v>1010</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G15" s="1">
         <v>1</v>
@@ -3065,7 +3132,7 @@
         <v>10</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K15" s="1">
         <v>0</v>
@@ -3095,10 +3162,10 @@
         <v>2</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="V15" s="1">
         <v>0</v>
@@ -3148,10 +3215,10 @@
         <v>1011</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G16" s="1">
         <v>8</v>
@@ -3163,7 +3230,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K16" s="1">
         <v>30</v>
@@ -3194,10 +3261,10 @@
         <v>3</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V16" s="1">
         <v>15</v>
@@ -3251,10 +3318,10 @@
         <v>2001</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G18" s="1">
         <v>1</v>
@@ -3266,7 +3333,7 @@
         <v>10</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="K18" s="1">
         <v>0</v>
@@ -3297,10 +3364,10 @@
         <v>2</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="V18" s="1">
         <v>0</v>
@@ -3350,10 +3417,10 @@
         <v>2002</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G19" s="1">
         <v>1</v>
@@ -3365,7 +3432,7 @@
         <v>10</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="K19" s="1">
         <v>0</v>
@@ -3396,10 +3463,10 @@
         <v>3</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="V19" s="1">
         <v>0</v>
@@ -3449,10 +3516,10 @@
         <v>2003</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="G20" s="1">
         <v>3</v>
@@ -3464,7 +3531,7 @@
         <v>10</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="K20" s="1">
         <v>10</v>
@@ -3495,10 +3562,10 @@
         <v>3</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V20" s="1">
         <v>10</v>
@@ -3548,10 +3615,10 @@
         <v>2004</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G21" s="1">
         <v>1</v>
@@ -3563,7 +3630,7 @@
         <v>10</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="K21" s="1">
         <v>0</v>
@@ -3597,7 +3664,7 @@
         <v>68</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V21" s="1">
         <v>0</v>
@@ -3633,7 +3700,7 @@
         <v>0</v>
       </c>
       <c r="AG21" s="1" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="AH21" s="1">
         <v>50</v>
@@ -3650,10 +3717,10 @@
         <v>2005</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="G22" s="1">
         <v>5</v>
@@ -3665,7 +3732,7 @@
         <v>50</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K22" s="1">
         <v>55</v>
@@ -3699,7 +3766,7 @@
         <v>68</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V22" s="1">
         <v>30</v>
@@ -3734,8 +3801,8 @@
       <c r="AF22" s="1">
         <v>0</v>
       </c>
-      <c r="AG22" s="5" t="s">
-        <v>85</v>
+      <c r="AG22" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="AH22" s="1">
         <v>50</v>
@@ -3752,10 +3819,10 @@
         <v>2006</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="G23" s="1">
         <v>6</v>
@@ -3767,7 +3834,7 @@
         <v>10</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="K23" s="1">
         <v>0</v>
@@ -3801,7 +3868,7 @@
         <v>68</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="V23" s="1">
         <v>0</v>
@@ -3851,10 +3918,10 @@
         <v>2007</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="G24" s="1">
         <v>1</v>
@@ -3866,9 +3933,9 @@
         <v>10</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="K24" s="4">
+        <v>118</v>
+      </c>
+      <c r="K24" s="5">
         <v>5</v>
       </c>
       <c r="L24" s="1">
@@ -3887,7 +3954,7 @@
         <f t="shared" si="1"/>
         <v>3000</v>
       </c>
-      <c r="Q24" s="4">
+      <c r="Q24" s="5">
         <v>6</v>
       </c>
       <c r="R24" s="1">
@@ -3897,10 +3964,10 @@
         <v>5</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U24" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V24" s="1">
         <v>0</v>
@@ -3914,7 +3981,7 @@
       <c r="Y24" s="1">
         <v>3</v>
       </c>
-      <c r="Z24" s="4">
+      <c r="Z24" s="5">
         <v>300</v>
       </c>
       <c r="AA24" s="1">
@@ -3935,8 +4002,8 @@
       <c r="AF24" s="1">
         <v>0</v>
       </c>
-      <c r="AG24" s="4" t="s">
-        <v>117</v>
+      <c r="AG24" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="AH24" s="1">
         <v>50</v>
@@ -3953,10 +4020,10 @@
         <v>2008</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="G25" s="1">
         <v>2008</v>
@@ -3968,7 +4035,7 @@
         <v>200</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="K25" s="1">
         <v>30</v>
@@ -4002,7 +4069,7 @@
         <v>68</v>
       </c>
       <c r="U25" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="V25" s="1">
         <v>0</v>
@@ -4038,7 +4105,7 @@
         <v>0</v>
       </c>
       <c r="AG25" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="AH25" s="1">
         <v>50</v>
@@ -4055,10 +4122,10 @@
         <v>2009</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="G26" s="1">
         <v>3</v>
@@ -4070,7 +4137,7 @@
         <v>10</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="K26" s="1">
         <v>15</v>
@@ -4101,10 +4168,10 @@
         <v>3</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U26" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V26" s="1">
         <v>10</v>
@@ -4140,7 +4207,7 @@
         <v>0</v>
       </c>
       <c r="AG26" s="1" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="AH26" s="1">
         <v>50</v>
@@ -4157,10 +4224,10 @@
         <v>2010</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="G27" s="1">
         <v>2010</v>
@@ -4172,7 +4239,7 @@
         <v>100</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="K27" s="1">
         <v>30</v>
@@ -4203,10 +4270,10 @@
         <v>3</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U27" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V27" s="1">
         <v>15</v>
@@ -4256,10 +4323,10 @@
         <v>2011</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="G28" s="1">
         <v>8</v>
@@ -4271,7 +4338,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="K28" s="1">
         <v>30</v>
@@ -4302,10 +4369,10 @@
         <v>3</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U28" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V28" s="1">
         <v>15</v>
@@ -4359,10 +4426,10 @@
         <v>3001</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="G30" s="1">
         <v>4</v>
@@ -4374,7 +4441,7 @@
         <v>20</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="K30" s="1">
         <v>4</v>
@@ -4407,7 +4474,7 @@
         <v>68</v>
       </c>
       <c r="U30" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="V30" s="1">
         <v>0</v>
@@ -4457,10 +4524,10 @@
         <v>3002</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -4472,7 +4539,7 @@
         <v>10</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="K31" s="1">
         <v>0</v>
@@ -4503,10 +4570,10 @@
         <v>3</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U31" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="V31" s="1">
         <v>0</v>
@@ -4556,10 +4623,10 @@
         <v>3003</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="G32" s="1">
         <v>1</v>
@@ -4571,7 +4638,7 @@
         <v>10</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="K32" s="1">
         <v>10</v>
@@ -4602,10 +4669,10 @@
         <v>2</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U32" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="V32" s="1">
         <v>0</v>
@@ -4641,7 +4708,7 @@
         <v>0</v>
       </c>
       <c r="AG32" s="1" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="AH32" s="1">
         <v>50</v>
@@ -4658,10 +4725,10 @@
         <v>3004</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="G33" s="1">
         <v>2</v>
@@ -4673,7 +4740,7 @@
         <v>100</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="K33" s="1">
         <v>15</v>
@@ -4707,7 +4774,7 @@
         <v>68</v>
       </c>
       <c r="U33" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="V33" s="1">
         <v>0</v>
@@ -4757,10 +4824,10 @@
         <v>3005</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="G34" s="1">
         <v>5</v>
@@ -4772,7 +4839,7 @@
         <v>50</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K34" s="1">
         <v>55</v>
@@ -4806,7 +4873,7 @@
         <v>68</v>
       </c>
       <c r="U34" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V34" s="1">
         <v>30</v>
@@ -4841,8 +4908,8 @@
       <c r="AF34" s="1">
         <v>0</v>
       </c>
-      <c r="AG34" s="5" t="s">
-        <v>85</v>
+      <c r="AG34" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="AH34" s="1">
         <v>50</v>
@@ -4859,10 +4926,10 @@
         <v>3006</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="G35" s="1">
         <v>6</v>
@@ -4874,7 +4941,7 @@
         <v>10</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="K35" s="1">
         <v>0</v>
@@ -4908,7 +4975,7 @@
         <v>68</v>
       </c>
       <c r="U35" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="V35" s="1">
         <v>0</v>
@@ -4958,10 +5025,10 @@
         <v>3007</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="G36" s="1">
         <v>2</v>
@@ -4973,7 +5040,7 @@
         <v>100</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="K36" s="1">
         <v>30</v>
@@ -5004,10 +5071,10 @@
         <v>2</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U36" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V36" s="1">
         <v>0</v>
@@ -5057,10 +5124,10 @@
         <v>3008</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="G37" s="1">
         <v>3008</v>
@@ -5072,7 +5139,7 @@
         <v>200</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="K37" s="1">
         <v>30</v>
@@ -5106,7 +5173,7 @@
         <v>68</v>
       </c>
       <c r="U37" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="V37" s="1">
         <v>5</v>
@@ -5142,7 +5209,7 @@
         <v>0</v>
       </c>
       <c r="AG37" s="1" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="AH37" s="1">
         <v>50</v>
@@ -5159,10 +5226,10 @@
         <v>3009</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="G38" s="1">
         <v>2</v>
@@ -5174,7 +5241,7 @@
         <v>100</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="K38" s="1">
         <v>30</v>
@@ -5204,10 +5271,10 @@
         <v>2</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U38" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V38" s="1">
         <v>0</v>
@@ -5257,10 +5324,10 @@
         <v>3010</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="G39" s="1">
         <v>8</v>
@@ -5272,7 +5339,7 @@
         <v>100</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="K39" s="1">
         <v>0</v>
@@ -5302,10 +5369,10 @@
         <v>0</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U39" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V39" s="1">
         <v>0</v>
@@ -5355,10 +5422,10 @@
         <v>3011</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="G40" s="1">
         <v>8</v>
@@ -5370,7 +5437,7 @@
         <v>0</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="K40" s="1">
         <v>30</v>
@@ -5401,10 +5468,10 @@
         <v>3</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U40" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V40" s="1">
         <v>15</v>
@@ -5457,11 +5524,11 @@
       <c r="D42" s="1">
         <v>4001</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>151</v>
+      <c r="E42" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>168</v>
       </c>
       <c r="G42" s="1">
         <v>4001</v>
@@ -5473,7 +5540,7 @@
         <v>-100</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="K42" s="1">
         <v>30</v>
@@ -5503,7 +5570,7 @@
         <v>68</v>
       </c>
       <c r="U42" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V42" s="1">
         <v>2</v>
@@ -5539,7 +5606,7 @@
         <v>0</v>
       </c>
       <c r="AG42" s="1" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="AH42" s="1">
         <v>99999</v>
@@ -5552,11 +5619,11 @@
       <c r="D43" s="1">
         <v>4002</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>154</v>
+      <c r="E43" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>171</v>
       </c>
       <c r="G43" s="1">
         <v>4002</v>
@@ -5568,7 +5635,7 @@
         <v>200</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="K43" s="1">
         <v>60</v>
@@ -5598,7 +5665,7 @@
         <v>68</v>
       </c>
       <c r="U43" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V43" s="1">
         <v>0</v>
@@ -5633,7 +5700,7 @@
       <c r="AF43" s="1">
         <v>0</v>
       </c>
-      <c r="AG43" s="5"/>
+      <c r="AG43" s="6"/>
       <c r="AH43" s="1">
         <v>99999</v>
       </c>
@@ -5645,11 +5712,11 @@
       <c r="D44" s="1">
         <v>4003</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>156</v>
+      <c r="E44" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>173</v>
       </c>
       <c r="G44" s="1">
         <v>4003</v>
@@ -5661,7 +5728,7 @@
         <v>-1</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="K44" s="1">
         <v>60</v>
@@ -5691,7 +5758,7 @@
         <v>68</v>
       </c>
       <c r="U44" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V44" s="1">
         <v>0</v>
@@ -5727,7 +5794,7 @@
         <v>0</v>
       </c>
       <c r="AG44" s="1" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="AH44" s="1">
         <v>99999</v>
@@ -5745,10 +5812,10 @@
         <v>9001</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="G46" s="1">
         <v>9</v>
@@ -5784,7 +5851,7 @@
         <v>68</v>
       </c>
       <c r="U46" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="V46" s="1">
         <v>0</v>
@@ -5834,10 +5901,10 @@
         <v>9002</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="G47" s="1">
         <v>9</v>
@@ -5924,10 +5991,10 @@
         <v>10001</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="G49" s="1">
         <v>1</v>
@@ -5939,7 +6006,7 @@
         <v>1</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="K49" s="1">
         <v>0</v>
@@ -5963,10 +6030,10 @@
         <v>3</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U49" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="V49" s="1">
         <v>0</v>
@@ -6016,10 +6083,10 @@
         <v>10002</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="G50" s="2">
         <v>4</v>
@@ -6031,7 +6098,7 @@
         <v>10</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="K50" s="2">
         <v>0</v>
@@ -6111,10 +6178,10 @@
         <v>10003</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -6126,7 +6193,7 @@
         <v>1</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="K51" s="2">
         <v>0</v>
@@ -6152,10 +6219,10 @@
         <v>0</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U51" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="V51" s="1">
         <v>0</v>
@@ -6206,10 +6273,10 @@
         <v>10004</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="G52" s="2">
         <v>4</v>
@@ -6221,7 +6288,7 @@
         <v>10</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="K52" s="2">
         <v>0</v>
@@ -6247,10 +6314,10 @@
         <v>3</v>
       </c>
       <c r="T52" s="2" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="U52" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V52" s="2">
         <v>0</v>
@@ -6300,7 +6367,7 @@
         <v>10005</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>71</v>
@@ -6315,7 +6382,7 @@
         <v>10</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="K53" s="1">
         <v>0</v>
@@ -6481,7 +6548,7 @@
         <v>1002</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>70</v>
+        <v>186</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>71</v>
@@ -6570,10 +6637,10 @@
         <v>1003</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G57" s="1">
         <v>1</v>
@@ -6609,7 +6676,7 @@
         <v>68</v>
       </c>
       <c r="U57" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="V57" s="1">
         <v>0</v>
@@ -6659,10 +6726,10 @@
         <v>1004</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G58" s="1">
         <v>7</v>
@@ -6695,10 +6762,10 @@
         <v>4</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U58" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="V58" s="1">
         <v>2</v>
@@ -6734,7 +6801,7 @@
         <v>0</v>
       </c>
       <c r="AG58" s="1" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="AH58" s="1">
         <v>50</v>
@@ -6751,10 +6818,10 @@
         <v>1005</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G59" s="1">
         <v>5</v>
@@ -6790,7 +6857,7 @@
         <v>68</v>
       </c>
       <c r="U59" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V59" s="1">
         <v>30</v>
@@ -6825,7 +6892,7 @@
       <c r="AF59" s="1">
         <v>0</v>
       </c>
-      <c r="AG59" s="5"/>
+      <c r="AG59" s="6"/>
       <c r="AH59" s="1">
         <v>50</v>
       </c>
@@ -6841,10 +6908,10 @@
         <v>1006</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G60" s="1">
         <v>6</v>
@@ -6880,7 +6947,7 @@
         <v>68</v>
       </c>
       <c r="U60" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="V60" s="1">
         <v>0</v>
@@ -6930,10 +6997,10 @@
         <v>1007</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>89</v>
+        <v>188</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G61" s="1">
         <v>1</v>
@@ -7019,10 +7086,10 @@
         <v>2001</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G62" s="1">
         <v>1</v>
@@ -7055,10 +7122,10 @@
         <v>2</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U62" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="V62" s="1">
         <v>0</v>
@@ -7108,10 +7175,10 @@
         <v>2002</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G63" s="1">
         <v>1</v>
@@ -7144,10 +7211,10 @@
         <v>3</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U63" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="V63" s="1">
         <v>0</v>
@@ -7197,10 +7264,10 @@
         <v>2003</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="G64" s="1">
         <v>3</v>
@@ -7233,10 +7300,10 @@
         <v>3</v>
       </c>
       <c r="T64" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U64" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V64" s="1">
         <v>5</v>
@@ -7286,10 +7353,10 @@
         <v>2004</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>109</v>
+        <v>189</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G65" s="1">
         <v>1</v>
@@ -7325,7 +7392,7 @@
         <v>68</v>
       </c>
       <c r="U65" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V65" s="1">
         <v>0</v>
@@ -7375,10 +7442,10 @@
         <v>2005</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="G66" s="1">
         <v>5</v>
@@ -7414,7 +7481,7 @@
         <v>68</v>
       </c>
       <c r="U66" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V66" s="1">
         <v>30</v>
@@ -7449,7 +7516,7 @@
       <c r="AF66" s="1">
         <v>0</v>
       </c>
-      <c r="AG66" s="5"/>
+      <c r="AG66" s="6"/>
       <c r="AH66" s="1">
         <v>50</v>
       </c>
@@ -7465,10 +7532,10 @@
         <v>2006</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="G67" s="1">
         <v>6</v>
@@ -7504,7 +7571,7 @@
         <v>68</v>
       </c>
       <c r="U67" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="V67" s="1">
         <v>0</v>
@@ -7554,10 +7621,10 @@
         <v>2007</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="G68" s="1">
         <v>1</v>
@@ -7590,10 +7657,10 @@
         <v>5</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U68" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V68" s="1">
         <v>0</v>
@@ -7643,10 +7710,10 @@
         <v>3001</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="G69" s="1">
         <v>4</v>
@@ -7682,7 +7749,7 @@
         <v>68</v>
       </c>
       <c r="U69" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V69" s="1">
         <v>0</v>
@@ -7732,10 +7799,10 @@
         <v>3002</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="G70" s="1">
         <v>1</v>
@@ -7768,10 +7835,10 @@
         <v>3</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U70" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="V70" s="1">
         <v>0</v>
@@ -7821,10 +7888,10 @@
         <v>3003</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="G71" s="1">
         <v>1</v>
@@ -7857,10 +7924,10 @@
         <v>2</v>
       </c>
       <c r="T71" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U71" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="V71" s="1">
         <v>0</v>
@@ -7910,10 +7977,10 @@
         <v>3004</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="G72" s="1">
         <v>2</v>
@@ -7949,7 +8016,7 @@
         <v>68</v>
       </c>
       <c r="U72" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="V72" s="1">
         <v>0</v>
@@ -7999,10 +8066,10 @@
         <v>3005</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="G73" s="1">
         <v>5</v>
@@ -8038,7 +8105,7 @@
         <v>68</v>
       </c>
       <c r="U73" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V73" s="1">
         <v>30</v>
@@ -8073,7 +8140,7 @@
       <c r="AF73" s="1">
         <v>0</v>
       </c>
-      <c r="AG73" s="5"/>
+      <c r="AG73" s="6"/>
       <c r="AH73" s="1">
         <v>50</v>
       </c>
@@ -8089,10 +8156,10 @@
         <v>3006</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="G74" s="1">
         <v>6</v>
@@ -8128,7 +8195,7 @@
         <v>68</v>
       </c>
       <c r="U74" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="V74" s="1">
         <v>0</v>
@@ -8178,10 +8245,10 @@
         <v>3007</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="G75" s="1">
         <v>2</v>
@@ -8214,10 +8281,10 @@
         <v>2</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U75" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V75" s="1">
         <v>0</v>
@@ -8277,7 +8344,7 @@
         <v>1002</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>70</v>
+        <v>186</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>71</v>
@@ -8352,7 +8419,7 @@
         <v>0</v>
       </c>
       <c r="AG77" s="1" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AH77" s="1">
         <v>50</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -298,7 +298,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="188">
   <si>
     <t>_ID</t>
   </si>
@@ -858,16 +858,7 @@
     <t>怪物刺杀</t>
   </si>
   <si>
-    <t>刺杀剑术</t>
-  </si>
-  <si>
     <t>"306,1,0,0"</t>
-  </si>
-  <si>
-    <t>烈火剑法</t>
-  </si>
-  <si>
-    <t>爆裂火焰</t>
   </si>
   <si>
     <t>"101,0,0,20"</t>
@@ -6548,7 +6539,7 @@
         <v>1002</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>186</v>
+        <v>70</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>71</v>
@@ -6637,7 +6628,7 @@
         <v>1003</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>74</v>
@@ -6726,7 +6717,7 @@
         <v>1004</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>79</v>
@@ -6801,7 +6792,7 @@
         <v>0</v>
       </c>
       <c r="AG58" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AH58" s="1">
         <v>50</v>
@@ -6997,7 +6988,7 @@
         <v>1007</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>188</v>
+        <v>91</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>92</v>
@@ -7086,7 +7077,7 @@
         <v>2001</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>108</v>
@@ -7175,7 +7166,7 @@
         <v>2002</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>111</v>
@@ -7264,7 +7255,7 @@
         <v>2003</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>114</v>
@@ -7353,7 +7344,7 @@
         <v>2004</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>117</v>
@@ -7621,7 +7612,7 @@
         <v>2007</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>124</v>
@@ -7710,7 +7701,7 @@
         <v>3001</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>139</v>
@@ -7799,7 +7790,7 @@
         <v>3002</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>142</v>
@@ -7888,7 +7879,7 @@
         <v>3003</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>145</v>
@@ -7977,7 +7968,7 @@
         <v>3004</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>149</v>
@@ -8245,7 +8236,7 @@
         <v>3007</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>155</v>
@@ -8344,7 +8335,7 @@
         <v>1002</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>186</v>
+        <v>70</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>71</v>
@@ -8419,7 +8410,7 @@
         <v>0</v>
       </c>
       <c r="AG77" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AH77" s="1">
         <v>50</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -744,7 +744,7 @@
     <t>"104,5,0,35"</t>
   </si>
   <si>
-    <t>召唤金刚</t>
+    <t>召唤小兵</t>
   </si>
   <si>
     <t>召唤骷髅</t>
@@ -783,7 +783,7 @@
     <t>"8,360,3,0"</t>
   </si>
   <si>
-    <t>召唤护法</t>
+    <t>召唤月神</t>
   </si>
   <si>
     <t>召唤月灵</t>
@@ -7968,7 +7968,7 @@
         <v>3004</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>149</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -618,7 +618,7 @@
     <t>战士之魂</t>
   </si>
   <si>
-    <t>上阵后，提高人物{1}%的生命倍率和{5}%的物攻倍率（分身和宠物不享受）</t>
+    <t>上阵后，提高人物{1}%的生命倍率和{5}%的物攻倍率（分身和宠物享受）</t>
   </si>
   <si>
     <t>火球术</t>
@@ -711,7 +711,7 @@
     <t>法师之魂</t>
   </si>
   <si>
-    <t>上阵后，提高人物{1}%的生命倍率和{5}%的魔攻倍率（分身和宠物不享受）</t>
+    <t>上阵后，提高人物{1}%的生命倍率和{5}%的魔攻倍率（分身和宠物享受）</t>
   </si>
   <si>
     <t>治疗道法</t>
@@ -801,7 +801,7 @@
     <t>道士之魂</t>
   </si>
   <si>
-    <t>上阵后，提高人物{1}%的生命倍率和{5}%的道攻倍率（分身和宠物不享受）</t>
+    <t>上阵后，提高人物{1}%的生命倍率和{5}%的道攻倍率（分身和宠物享受）</t>
   </si>
   <si>
     <t>定身神戒</t>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -678,7 +678,7 @@
     <t>"305,1,1,0"</t>
   </si>
   <si>
-    <t>闪烁术</t>
+    <t>瞬移术</t>
   </si>
   <si>
     <t>瞬息移动</t>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -298,7 +298,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="193">
   <si>
     <t>_ID</t>
   </si>
@@ -510,7 +510,7 @@
     <t>FrontRow</t>
   </si>
   <si>
-    <t>穿刺剑术</t>
+    <t>流光剑法</t>
   </si>
   <si>
     <t>刺杀</t>
@@ -519,7 +519,7 @@
     <t>对直线内的敌人造成{1}%物攻伤害,忽视敌方50%防御</t>
   </si>
   <si>
-    <t>圆月弯刀</t>
+    <t>旋风斩</t>
   </si>
   <si>
     <t>半月弯刀</t>
@@ -534,7 +534,7 @@
     <t>"14,60,3,10"</t>
   </si>
   <si>
-    <t>蛮力撞击</t>
+    <t>腾空斩</t>
   </si>
   <si>
     <t>野蛮撞击</t>
@@ -552,6 +552,9 @@
     <t>"306,2,0,0"</t>
   </si>
   <si>
+    <t>武神盾</t>
+  </si>
+  <si>
     <t>武力盾</t>
   </si>
   <si>
@@ -573,7 +576,7 @@
     <t>FullBox</t>
   </si>
   <si>
-    <t>火焰剑法</t>
+    <t>烈焰斩</t>
   </si>
   <si>
     <t>烈火</t>
@@ -585,7 +588,7 @@
     <t>"103,4,0,25","101,0,0,10"</t>
   </si>
   <si>
-    <t>护体神盾</t>
+    <t>战吼</t>
   </si>
   <si>
     <t>免疫{2}秒控制</t>
@@ -594,7 +597,7 @@
     <t>"401,20,0,0","6,360,3,1","9,360,3,0"</t>
   </si>
   <si>
-    <t>开天辟地</t>
+    <t>裂天斩</t>
   </si>
   <si>
     <t>开天斩</t>
@@ -630,7 +633,7 @@
     <t>对{0}个敌人敌人造成{1}%魔法伤害</t>
   </si>
   <si>
-    <t>神雷术</t>
+    <t>落雷术</t>
   </si>
   <si>
     <t>雷电术</t>
@@ -639,7 +642,7 @@
     <t>对{0}个敌人敌人造成{1}%魔法伤害,忽视敌方50%防御</t>
   </si>
   <si>
-    <t>火墙术</t>
+    <t>火焰墙</t>
   </si>
   <si>
     <t>火墙</t>
@@ -648,7 +651,7 @@
     <t>施展{3}*{4}范围的火墙，持续{2}s，对其内的敌人每秒造成{1}%魔法伤害</t>
   </si>
   <si>
-    <t>火焰术</t>
+    <t>烈焰环</t>
   </si>
   <si>
     <t>抗拒火环</t>
@@ -660,6 +663,9 @@
     <t>"12,60,3,10"</t>
   </si>
   <si>
+    <t>法力盾</t>
+  </si>
+  <si>
     <t>魔法盾</t>
   </si>
   <si>
@@ -669,7 +675,7 @@
     <t>法师技能增加{1}%技能系数</t>
   </si>
   <si>
-    <t>冰冻术</t>
+    <t>冰爆术</t>
   </si>
   <si>
     <t>冰咆哮</t>
@@ -678,7 +684,7 @@
     <t>"305,1,1,0"</t>
   </si>
   <si>
-    <t>瞬移术</t>
+    <t>心灵传送</t>
   </si>
   <si>
     <t>瞬息移动</t>
@@ -690,7 +696,7 @@
     <t>"10,360,3,0"</t>
   </si>
   <si>
-    <t>火雨术</t>
+    <t>毁灭流星</t>
   </si>
   <si>
     <t>流星火雨</t>
@@ -714,7 +720,7 @@
     <t>上阵后，提高人物{1}%的生命倍率和{5}%的魔攻倍率（分身和宠物享受）</t>
   </si>
   <si>
-    <t>治疗道法</t>
+    <t>疗伤术</t>
   </si>
   <si>
     <t>治疗术</t>
@@ -723,7 +729,7 @@
     <t>回复自己或者队友{1}%道术的生命</t>
   </si>
   <si>
-    <t>火符道法</t>
+    <t>驱魔符</t>
   </si>
   <si>
     <t>火符术</t>
@@ -732,7 +738,7 @@
     <t>对{0}个敌人造成{1}%道术伤害</t>
   </si>
   <si>
-    <t>毒咒道法</t>
+    <t>毒咒术</t>
   </si>
   <si>
     <t>施毒术</t>
@@ -804,6 +810,9 @@
     <t>上阵后，提高人物{1}%的生命倍率和{5}%的道攻倍率（分身和宠物享受）</t>
   </si>
   <si>
+    <t>定身指环</t>
+  </si>
+  <si>
     <t>定身神戒</t>
   </si>
   <si>
@@ -813,10 +822,16 @@
     <t>"307,2,0,0"</t>
   </si>
   <si>
+    <t>神盾指环</t>
+  </si>
+  <si>
     <t>护体神戒</t>
   </si>
   <si>
     <t>附加一个面板生命*{1}%盾，CD60S</t>
+  </si>
+  <si>
+    <t>复生指环</t>
   </si>
   <si>
     <t>重生神戒</t>
@@ -874,7 +889,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -894,6 +909,13 @@
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1387,16 +1409,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1405,119 +1424,122 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1525,6 +1547,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
@@ -2297,7 +2320,7 @@
       <c r="D7" s="1">
         <v>1002</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="1" t="s">
         <v>70</v>
       </c>
       <c r="F7" s="2" t="s">
@@ -2396,7 +2419,7 @@
       <c r="D8" s="1">
         <v>1003</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="1" t="s">
         <v>73</v>
       </c>
       <c r="F8" s="2" t="s">
@@ -2600,11 +2623,11 @@
       <c r="D10" s="1">
         <v>1005</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="1" t="s">
         <v>84</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G10" s="1">
         <v>5</v>
@@ -2616,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K10" s="1">
         <v>55</v>
@@ -2650,7 +2673,7 @@
         <v>68</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V10" s="1">
         <v>30</v>
@@ -2685,8 +2708,8 @@
       <c r="AF10" s="1">
         <v>0</v>
       </c>
-      <c r="AG10" s="6" t="s">
-        <v>87</v>
+      <c r="AG10" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="AH10" s="1">
         <v>50</v>
@@ -2702,11 +2725,11 @@
       <c r="D11" s="1">
         <v>1006</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>88</v>
+      <c r="E11" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G11" s="1">
         <v>6</v>
@@ -2718,7 +2741,7 @@
         <v>10</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K11" s="1">
         <v>0</v>
@@ -2752,7 +2775,7 @@
         <v>68</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="V11" s="1">
         <v>0</v>
@@ -2801,11 +2824,11 @@
       <c r="D12" s="1">
         <v>1007</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>91</v>
+      <c r="E12" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
@@ -2817,9 +2840,9 @@
         <v>10</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="K12" s="5">
+        <v>94</v>
+      </c>
+      <c r="K12" s="6">
         <v>5</v>
       </c>
       <c r="L12" s="1">
@@ -2838,7 +2861,7 @@
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="Q12" s="5">
+      <c r="Q12" s="6">
         <v>10</v>
       </c>
       <c r="R12" s="1">
@@ -2865,7 +2888,7 @@
       <c r="Y12" s="1">
         <v>0</v>
       </c>
-      <c r="Z12" s="5">
+      <c r="Z12" s="6">
         <v>500</v>
       </c>
       <c r="AA12" s="1">
@@ -2886,8 +2909,8 @@
       <c r="AF12" s="1">
         <v>0</v>
       </c>
-      <c r="AG12" s="5" t="s">
-        <v>94</v>
+      <c r="AG12" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="AH12" s="1">
         <v>50</v>
@@ -2903,11 +2926,11 @@
       <c r="D13" s="1">
         <v>1008</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>95</v>
+      <c r="E13" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G13" s="1">
         <v>1008</v>
@@ -2919,7 +2942,7 @@
         <v>200</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K13" s="1">
         <v>30</v>
@@ -2953,7 +2976,7 @@
         <v>68</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="V13" s="1">
         <v>20</v>
@@ -2989,7 +3012,7 @@
         <v>0</v>
       </c>
       <c r="AG13" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AH13" s="1">
         <v>50</v>
@@ -3005,11 +3028,11 @@
       <c r="D14" s="1">
         <v>1009</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>98</v>
+      <c r="E14" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -3091,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="AG14" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AH14" s="1">
         <v>50</v>
@@ -3107,11 +3130,11 @@
       <c r="D15" s="1">
         <v>1010</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>101</v>
+      <c r="E15" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G15" s="1">
         <v>1</v>
@@ -3123,7 +3146,7 @@
         <v>10</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K15" s="1">
         <v>0</v>
@@ -3156,7 +3179,7 @@
         <v>81</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="V15" s="1">
         <v>0</v>
@@ -3205,11 +3228,11 @@
       <c r="D16" s="1">
         <v>1011</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>105</v>
+      <c r="E16" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G16" s="1">
         <v>8</v>
@@ -3221,7 +3244,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K16" s="1">
         <v>30</v>
@@ -3255,7 +3278,7 @@
         <v>81</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V16" s="1">
         <v>15</v>
@@ -3297,8 +3320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" spans="5:6">
-      <c r="E17" s="2"/>
+    <row r="17" s="1" customFormat="1" spans="6:6">
       <c r="F17" s="2"/>
     </row>
     <row r="18" s="1" customFormat="1" spans="3:35">
@@ -3309,10 +3331,10 @@
         <v>2001</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G18" s="1">
         <v>1</v>
@@ -3324,7 +3346,7 @@
         <v>10</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K18" s="1">
         <v>0</v>
@@ -3358,7 +3380,7 @@
         <v>81</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="V18" s="1">
         <v>0</v>
@@ -3407,11 +3429,11 @@
       <c r="D19" s="1">
         <v>2002</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>110</v>
+      <c r="E19" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G19" s="1">
         <v>1</v>
@@ -3423,7 +3445,7 @@
         <v>10</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K19" s="1">
         <v>0</v>
@@ -3457,7 +3479,7 @@
         <v>81</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="V19" s="1">
         <v>0</v>
@@ -3506,11 +3528,11 @@
       <c r="D20" s="1">
         <v>2003</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>113</v>
+      <c r="E20" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G20" s="1">
         <v>3</v>
@@ -3522,7 +3544,7 @@
         <v>10</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K20" s="1">
         <v>10</v>
@@ -3556,7 +3578,7 @@
         <v>81</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V20" s="1">
         <v>10</v>
@@ -3605,11 +3627,11 @@
       <c r="D21" s="1">
         <v>2004</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>116</v>
+      <c r="E21" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G21" s="1">
         <v>1</v>
@@ -3621,7 +3643,7 @@
         <v>10</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K21" s="1">
         <v>0</v>
@@ -3655,7 +3677,7 @@
         <v>68</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V21" s="1">
         <v>0</v>
@@ -3691,7 +3713,7 @@
         <v>0</v>
       </c>
       <c r="AG21" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AH21" s="1">
         <v>50</v>
@@ -3707,11 +3729,11 @@
       <c r="D22" s="1">
         <v>2005</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>120</v>
+      <c r="E22" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G22" s="1">
         <v>5</v>
@@ -3723,7 +3745,7 @@
         <v>50</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K22" s="1">
         <v>55</v>
@@ -3757,7 +3779,7 @@
         <v>68</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V22" s="1">
         <v>30</v>
@@ -3792,8 +3814,8 @@
       <c r="AF22" s="1">
         <v>0</v>
       </c>
-      <c r="AG22" s="6" t="s">
-        <v>87</v>
+      <c r="AG22" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="AH22" s="1">
         <v>50</v>
@@ -3810,10 +3832,10 @@
         <v>2006</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G23" s="1">
         <v>6</v>
@@ -3825,7 +3847,7 @@
         <v>10</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K23" s="1">
         <v>0</v>
@@ -3859,7 +3881,7 @@
         <v>68</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="V23" s="1">
         <v>0</v>
@@ -3908,11 +3930,11 @@
       <c r="D24" s="1">
         <v>2007</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>123</v>
+      <c r="E24" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G24" s="1">
         <v>1</v>
@@ -3924,9 +3946,9 @@
         <v>10</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="K24" s="5">
+        <v>119</v>
+      </c>
+      <c r="K24" s="6">
         <v>5</v>
       </c>
       <c r="L24" s="1">
@@ -3945,7 +3967,7 @@
         <f t="shared" si="1"/>
         <v>3000</v>
       </c>
-      <c r="Q24" s="5">
+      <c r="Q24" s="6">
         <v>6</v>
       </c>
       <c r="R24" s="1">
@@ -3958,7 +3980,7 @@
         <v>81</v>
       </c>
       <c r="U24" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V24" s="1">
         <v>0</v>
@@ -3972,7 +3994,7 @@
       <c r="Y24" s="1">
         <v>3</v>
       </c>
-      <c r="Z24" s="5">
+      <c r="Z24" s="6">
         <v>300</v>
       </c>
       <c r="AA24" s="1">
@@ -3993,8 +4015,8 @@
       <c r="AF24" s="1">
         <v>0</v>
       </c>
-      <c r="AG24" s="5" t="s">
-        <v>125</v>
+      <c r="AG24" s="6" t="s">
+        <v>127</v>
       </c>
       <c r="AH24" s="1">
         <v>50</v>
@@ -4010,11 +4032,11 @@
       <c r="D25" s="1">
         <v>2008</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>126</v>
+      <c r="E25" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G25" s="1">
         <v>2008</v>
@@ -4026,7 +4048,7 @@
         <v>200</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K25" s="1">
         <v>30</v>
@@ -4060,7 +4082,7 @@
         <v>68</v>
       </c>
       <c r="U25" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="V25" s="1">
         <v>0</v>
@@ -4096,7 +4118,7 @@
         <v>0</v>
       </c>
       <c r="AG25" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AH25" s="1">
         <v>50</v>
@@ -4112,11 +4134,11 @@
       <c r="D26" s="1">
         <v>2009</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>130</v>
+      <c r="E26" s="1" t="s">
+        <v>132</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G26" s="1">
         <v>3</v>
@@ -4128,7 +4150,7 @@
         <v>10</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K26" s="1">
         <v>15</v>
@@ -4162,7 +4184,7 @@
         <v>81</v>
       </c>
       <c r="U26" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V26" s="1">
         <v>10</v>
@@ -4198,7 +4220,7 @@
         <v>0</v>
       </c>
       <c r="AG26" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AH26" s="1">
         <v>50</v>
@@ -4214,11 +4236,11 @@
       <c r="D27" s="1">
         <v>2010</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>134</v>
+      <c r="E27" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G27" s="1">
         <v>2010</v>
@@ -4230,7 +4252,7 @@
         <v>100</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="K27" s="1">
         <v>30</v>
@@ -4264,7 +4286,7 @@
         <v>81</v>
       </c>
       <c r="U27" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V27" s="1">
         <v>15</v>
@@ -4313,11 +4335,11 @@
       <c r="D28" s="1">
         <v>2011</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>136</v>
+      <c r="E28" s="1" t="s">
+        <v>138</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G28" s="1">
         <v>8</v>
@@ -4329,7 +4351,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K28" s="1">
         <v>30</v>
@@ -4363,7 +4385,7 @@
         <v>81</v>
       </c>
       <c r="U28" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V28" s="1">
         <v>15</v>
@@ -4405,8 +4427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" spans="5:6">
-      <c r="E29" s="2"/>
+    <row r="29" s="1" customFormat="1" spans="6:6">
       <c r="F29" s="2"/>
     </row>
     <row r="30" s="1" customFormat="1" spans="3:35">
@@ -4416,11 +4437,11 @@
       <c r="D30" s="1">
         <v>3001</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>138</v>
+      <c r="E30" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G30" s="1">
         <v>4</v>
@@ -4432,7 +4453,7 @@
         <v>20</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K30" s="1">
         <v>4</v>
@@ -4465,7 +4486,7 @@
         <v>68</v>
       </c>
       <c r="U30" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="V30" s="1">
         <v>0</v>
@@ -4515,10 +4536,10 @@
         <v>3002</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -4530,7 +4551,7 @@
         <v>10</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K31" s="1">
         <v>0</v>
@@ -4564,7 +4585,7 @@
         <v>81</v>
       </c>
       <c r="U31" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="V31" s="1">
         <v>0</v>
@@ -4613,11 +4634,11 @@
       <c r="D32" s="1">
         <v>3003</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>144</v>
+      <c r="E32" s="1" t="s">
+        <v>146</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G32" s="1">
         <v>1</v>
@@ -4629,7 +4650,7 @@
         <v>10</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K32" s="1">
         <v>10</v>
@@ -4663,7 +4684,7 @@
         <v>81</v>
       </c>
       <c r="U32" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="V32" s="1">
         <v>0</v>
@@ -4699,7 +4720,7 @@
         <v>0</v>
       </c>
       <c r="AG32" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AH32" s="1">
         <v>50</v>
@@ -4715,11 +4736,11 @@
       <c r="D33" s="1">
         <v>3004</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>148</v>
+      <c r="E33" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G33" s="1">
         <v>2</v>
@@ -4731,7 +4752,7 @@
         <v>100</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K33" s="1">
         <v>15</v>
@@ -4765,7 +4786,7 @@
         <v>68</v>
       </c>
       <c r="U33" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="V33" s="1">
         <v>0</v>
@@ -4814,11 +4835,11 @@
       <c r="D34" s="1">
         <v>3005</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>151</v>
+      <c r="E34" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G34" s="1">
         <v>5</v>
@@ -4830,7 +4851,7 @@
         <v>50</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K34" s="1">
         <v>55</v>
@@ -4864,7 +4885,7 @@
         <v>68</v>
       </c>
       <c r="U34" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V34" s="1">
         <v>30</v>
@@ -4899,8 +4920,8 @@
       <c r="AF34" s="1">
         <v>0</v>
       </c>
-      <c r="AG34" s="6" t="s">
-        <v>87</v>
+      <c r="AG34" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="AH34" s="1">
         <v>50</v>
@@ -4917,10 +4938,10 @@
         <v>3006</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G35" s="1">
         <v>6</v>
@@ -4932,7 +4953,7 @@
         <v>10</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K35" s="1">
         <v>0</v>
@@ -4966,7 +4987,7 @@
         <v>68</v>
       </c>
       <c r="U35" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="V35" s="1">
         <v>0</v>
@@ -5015,11 +5036,11 @@
       <c r="D36" s="1">
         <v>3007</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>154</v>
+      <c r="E36" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G36" s="1">
         <v>2</v>
@@ -5031,7 +5052,7 @@
         <v>100</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K36" s="1">
         <v>30</v>
@@ -5065,7 +5086,7 @@
         <v>81</v>
       </c>
       <c r="U36" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V36" s="1">
         <v>0</v>
@@ -5114,11 +5135,11 @@
       <c r="D37" s="1">
         <v>3008</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>157</v>
+      <c r="E37" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G37" s="1">
         <v>3008</v>
@@ -5130,7 +5151,7 @@
         <v>200</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="K37" s="1">
         <v>30</v>
@@ -5164,7 +5185,7 @@
         <v>68</v>
       </c>
       <c r="U37" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="V37" s="1">
         <v>5</v>
@@ -5200,7 +5221,7 @@
         <v>0</v>
       </c>
       <c r="AG37" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AH37" s="1">
         <v>50</v>
@@ -5216,11 +5237,11 @@
       <c r="D38" s="1">
         <v>3009</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>161</v>
+      <c r="E38" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G38" s="1">
         <v>2</v>
@@ -5232,7 +5253,7 @@
         <v>100</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K38" s="1">
         <v>30</v>
@@ -5265,7 +5286,7 @@
         <v>81</v>
       </c>
       <c r="U38" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V38" s="1">
         <v>0</v>
@@ -5314,11 +5335,11 @@
       <c r="D39" s="1">
         <v>3010</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>164</v>
+      <c r="E39" s="1" t="s">
+        <v>166</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G39" s="1">
         <v>8</v>
@@ -5330,7 +5351,7 @@
         <v>100</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="K39" s="1">
         <v>0</v>
@@ -5363,7 +5384,7 @@
         <v>81</v>
       </c>
       <c r="U39" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V39" s="1">
         <v>0</v>
@@ -5412,11 +5433,11 @@
       <c r="D40" s="1">
         <v>3011</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>166</v>
+      <c r="E40" s="1" t="s">
+        <v>168</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G40" s="1">
         <v>8</v>
@@ -5428,7 +5449,7 @@
         <v>0</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K40" s="1">
         <v>30</v>
@@ -5462,7 +5483,7 @@
         <v>81</v>
       </c>
       <c r="U40" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V40" s="1">
         <v>15</v>
@@ -5516,10 +5537,10 @@
         <v>4001</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>171</v>
       </c>
       <c r="G42" s="1">
         <v>4001</v>
@@ -5531,7 +5552,7 @@
         <v>-100</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="K42" s="1">
         <v>30</v>
@@ -5561,7 +5582,7 @@
         <v>68</v>
       </c>
       <c r="U42" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V42" s="1">
         <v>2</v>
@@ -5597,7 +5618,7 @@
         <v>0</v>
       </c>
       <c r="AG42" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="AH42" s="1">
         <v>99999</v>
@@ -5611,10 +5632,10 @@
         <v>4002</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>175</v>
       </c>
       <c r="G43" s="1">
         <v>4002</v>
@@ -5626,7 +5647,7 @@
         <v>200</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="K43" s="1">
         <v>60</v>
@@ -5656,7 +5677,7 @@
         <v>68</v>
       </c>
       <c r="U43" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V43" s="1">
         <v>0</v>
@@ -5691,7 +5712,7 @@
       <c r="AF43" s="1">
         <v>0</v>
       </c>
-      <c r="AG43" s="6"/>
+      <c r="AG43" s="7"/>
       <c r="AH43" s="1">
         <v>99999</v>
       </c>
@@ -5704,10 +5725,10 @@
         <v>4003</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>178</v>
       </c>
       <c r="G44" s="1">
         <v>4003</v>
@@ -5719,7 +5740,7 @@
         <v>-1</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="K44" s="1">
         <v>60</v>
@@ -5749,7 +5770,7 @@
         <v>68</v>
       </c>
       <c r="U44" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V44" s="1">
         <v>0</v>
@@ -5785,7 +5806,7 @@
         <v>0</v>
       </c>
       <c r="AG44" s="1" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="AH44" s="1">
         <v>99999</v>
@@ -5803,10 +5824,10 @@
         <v>9001</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="G46" s="1">
         <v>9</v>
@@ -5842,7 +5863,7 @@
         <v>68</v>
       </c>
       <c r="U46" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="V46" s="1">
         <v>0</v>
@@ -5892,10 +5913,10 @@
         <v>9002</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="G47" s="1">
         <v>9</v>
@@ -5982,10 +6003,10 @@
         <v>10001</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="G49" s="1">
         <v>1</v>
@@ -5997,7 +6018,7 @@
         <v>1</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="K49" s="1">
         <v>0</v>
@@ -6024,7 +6045,7 @@
         <v>81</v>
       </c>
       <c r="U49" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="V49" s="1">
         <v>0</v>
@@ -6074,10 +6095,10 @@
         <v>10002</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="G50" s="2">
         <v>4</v>
@@ -6089,7 +6110,7 @@
         <v>10</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="K50" s="2">
         <v>0</v>
@@ -6169,10 +6190,10 @@
         <v>10003</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -6184,7 +6205,7 @@
         <v>1</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="K51" s="2">
         <v>0</v>
@@ -6213,7 +6234,7 @@
         <v>81</v>
       </c>
       <c r="U51" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="V51" s="1">
         <v>0</v>
@@ -6264,10 +6285,10 @@
         <v>10004</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="G52" s="2">
         <v>4</v>
@@ -6279,7 +6300,7 @@
         <v>10</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="K52" s="2">
         <v>0</v>
@@ -6305,10 +6326,10 @@
         <v>3</v>
       </c>
       <c r="T52" s="2" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="U52" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V52" s="2">
         <v>0</v>
@@ -6358,7 +6379,7 @@
         <v>10005</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>71</v>
@@ -6373,7 +6394,7 @@
         <v>10</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="K53" s="1">
         <v>0</v>
@@ -6538,7 +6559,7 @@
       <c r="D56" s="1">
         <v>1002</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="E56" s="1" t="s">
         <v>70</v>
       </c>
       <c r="F56" s="2" t="s">
@@ -6627,7 +6648,7 @@
       <c r="D57" s="1">
         <v>1003</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="E57" s="1" t="s">
         <v>73</v>
       </c>
       <c r="F57" s="2" t="s">
@@ -6792,7 +6813,7 @@
         <v>0</v>
       </c>
       <c r="AG58" s="1" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="AH58" s="1">
         <v>50</v>
@@ -6808,11 +6829,11 @@
       <c r="D59" s="1">
         <v>1005</v>
       </c>
-      <c r="E59" s="2" t="s">
+      <c r="E59" s="1" t="s">
         <v>84</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G59" s="1">
         <v>5</v>
@@ -6848,7 +6869,7 @@
         <v>68</v>
       </c>
       <c r="U59" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V59" s="1">
         <v>30</v>
@@ -6883,7 +6904,7 @@
       <c r="AF59" s="1">
         <v>0</v>
       </c>
-      <c r="AG59" s="6"/>
+      <c r="AG59" s="7"/>
       <c r="AH59" s="1">
         <v>50</v>
       </c>
@@ -6898,11 +6919,11 @@
       <c r="D60" s="1">
         <v>1006</v>
       </c>
-      <c r="E60" s="2" t="s">
-        <v>88</v>
+      <c r="E60" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G60" s="1">
         <v>6</v>
@@ -6938,7 +6959,7 @@
         <v>68</v>
       </c>
       <c r="U60" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="V60" s="1">
         <v>0</v>
@@ -6987,11 +7008,11 @@
       <c r="D61" s="1">
         <v>1007</v>
       </c>
-      <c r="E61" s="2" t="s">
-        <v>91</v>
+      <c r="E61" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G61" s="1">
         <v>1</v>
@@ -7077,10 +7098,10 @@
         <v>2001</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G62" s="1">
         <v>1</v>
@@ -7116,7 +7137,7 @@
         <v>81</v>
       </c>
       <c r="U62" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="V62" s="1">
         <v>0</v>
@@ -7165,11 +7186,11 @@
       <c r="D63" s="1">
         <v>2002</v>
       </c>
-      <c r="E63" s="2" t="s">
-        <v>110</v>
+      <c r="E63" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G63" s="1">
         <v>1</v>
@@ -7205,7 +7226,7 @@
         <v>81</v>
       </c>
       <c r="U63" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="V63" s="1">
         <v>0</v>
@@ -7254,11 +7275,11 @@
       <c r="D64" s="1">
         <v>2003</v>
       </c>
-      <c r="E64" s="2" t="s">
-        <v>113</v>
+      <c r="E64" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G64" s="1">
         <v>3</v>
@@ -7294,7 +7315,7 @@
         <v>81</v>
       </c>
       <c r="U64" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V64" s="1">
         <v>5</v>
@@ -7343,11 +7364,11 @@
       <c r="D65" s="1">
         <v>2004</v>
       </c>
-      <c r="E65" s="2" t="s">
-        <v>116</v>
+      <c r="E65" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G65" s="1">
         <v>1</v>
@@ -7383,7 +7404,7 @@
         <v>68</v>
       </c>
       <c r="U65" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V65" s="1">
         <v>0</v>
@@ -7432,11 +7453,11 @@
       <c r="D66" s="1">
         <v>2005</v>
       </c>
-      <c r="E66" s="2" t="s">
-        <v>120</v>
+      <c r="E66" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G66" s="1">
         <v>5</v>
@@ -7472,7 +7493,7 @@
         <v>68</v>
       </c>
       <c r="U66" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V66" s="1">
         <v>30</v>
@@ -7507,7 +7528,7 @@
       <c r="AF66" s="1">
         <v>0</v>
       </c>
-      <c r="AG66" s="6"/>
+      <c r="AG66" s="7"/>
       <c r="AH66" s="1">
         <v>50</v>
       </c>
@@ -7523,10 +7544,10 @@
         <v>2006</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G67" s="1">
         <v>6</v>
@@ -7562,7 +7583,7 @@
         <v>68</v>
       </c>
       <c r="U67" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="V67" s="1">
         <v>0</v>
@@ -7611,11 +7632,11 @@
       <c r="D68" s="1">
         <v>2007</v>
       </c>
-      <c r="E68" s="2" t="s">
-        <v>123</v>
+      <c r="E68" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G68" s="1">
         <v>1</v>
@@ -7651,7 +7672,7 @@
         <v>81</v>
       </c>
       <c r="U68" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V68" s="1">
         <v>0</v>
@@ -7700,11 +7721,11 @@
       <c r="D69" s="1">
         <v>3001</v>
       </c>
-      <c r="E69" s="2" t="s">
-        <v>138</v>
+      <c r="E69" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G69" s="1">
         <v>4</v>
@@ -7740,7 +7761,7 @@
         <v>68</v>
       </c>
       <c r="U69" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V69" s="1">
         <v>0</v>
@@ -7790,10 +7811,10 @@
         <v>3002</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G70" s="1">
         <v>1</v>
@@ -7829,7 +7850,7 @@
         <v>81</v>
       </c>
       <c r="U70" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="V70" s="1">
         <v>0</v>
@@ -7878,11 +7899,11 @@
       <c r="D71" s="1">
         <v>3003</v>
       </c>
-      <c r="E71" s="2" t="s">
-        <v>144</v>
+      <c r="E71" s="1" t="s">
+        <v>146</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G71" s="1">
         <v>1</v>
@@ -7918,7 +7939,7 @@
         <v>81</v>
       </c>
       <c r="U71" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="V71" s="1">
         <v>0</v>
@@ -7967,11 +7988,11 @@
       <c r="D72" s="1">
         <v>3004</v>
       </c>
-      <c r="E72" s="2" t="s">
-        <v>161</v>
+      <c r="E72" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G72" s="1">
         <v>2</v>
@@ -8007,7 +8028,7 @@
         <v>68</v>
       </c>
       <c r="U72" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="V72" s="1">
         <v>0</v>
@@ -8056,11 +8077,11 @@
       <c r="D73" s="1">
         <v>3005</v>
       </c>
-      <c r="E73" s="2" t="s">
-        <v>151</v>
+      <c r="E73" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G73" s="1">
         <v>5</v>
@@ -8096,7 +8117,7 @@
         <v>68</v>
       </c>
       <c r="U73" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V73" s="1">
         <v>30</v>
@@ -8131,7 +8152,7 @@
       <c r="AF73" s="1">
         <v>0</v>
       </c>
-      <c r="AG73" s="6"/>
+      <c r="AG73" s="7"/>
       <c r="AH73" s="1">
         <v>50</v>
       </c>
@@ -8147,10 +8168,10 @@
         <v>3006</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G74" s="1">
         <v>6</v>
@@ -8186,7 +8207,7 @@
         <v>68</v>
       </c>
       <c r="U74" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="V74" s="1">
         <v>0</v>
@@ -8235,11 +8256,11 @@
       <c r="D75" s="1">
         <v>3007</v>
       </c>
-      <c r="E75" s="2" t="s">
-        <v>154</v>
+      <c r="E75" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G75" s="1">
         <v>2</v>
@@ -8275,7 +8296,7 @@
         <v>81</v>
       </c>
       <c r="U75" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V75" s="1">
         <v>0</v>
@@ -8334,7 +8355,7 @@
       <c r="D77" s="1">
         <v>1002</v>
       </c>
-      <c r="E77" s="2" t="s">
+      <c r="E77" s="1" t="s">
         <v>70</v>
       </c>
       <c r="F77" s="2" t="s">
@@ -8410,7 +8431,7 @@
         <v>0</v>
       </c>
       <c r="AG77" s="1" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="AH77" s="1">
         <v>50</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -606,7 +606,7 @@
     <t>"109,0,0,5"</t>
   </si>
   <si>
-    <t>地刺术</t>
+    <t>裂地斩</t>
   </si>
   <si>
     <t>彻地钉</t>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1068,12 +1068,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1870,7 +1870,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C3:AK77"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.625" style="2" customWidth="1"/>
     <col min="2" max="2" width="3.5" style="2" customWidth="1"/>
@@ -1905,7 +1905,7 @@
     <col min="38" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:37">
+    <row r="3" ht="13.5" spans="3:37">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -2012,7 +2012,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="3:35">
+    <row r="4" ht="13.5" spans="3:35">
       <c r="C4" s="3" t="s">
         <v>33</v>
       </c>
@@ -2113,7 +2113,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="3:35">
+    <row r="5" ht="13.5" spans="3:35">
       <c r="C5" s="3" t="s">
         <v>63</v>
       </c>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -1068,12 +1068,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1870,7 +1870,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C3:AK77"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="5.625" style="2" customWidth="1"/>
     <col min="2" max="2" width="3.5" style="2" customWidth="1"/>
@@ -1905,7 +1905,7 @@
     <col min="38" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" ht="13.5" spans="3:37">
+    <row r="3" spans="3:37">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -2012,7 +2012,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" ht="13.5" spans="3:35">
+    <row r="4" spans="3:35">
       <c r="C4" s="3" t="s">
         <v>33</v>
       </c>
@@ -2113,7 +2113,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" ht="13.5" spans="3:35">
+    <row r="5" spans="3:35">
       <c r="C5" s="3" t="s">
         <v>63</v>
       </c>
@@ -2565,7 +2565,7 @@
         <v>0</v>
       </c>
       <c r="S9" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T9" s="1" t="s">
         <v>81</v>
@@ -3072,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T14" s="1" t="s">
         <v>68</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -130,7 +130,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L3" authorId="0">
+    <comment ref="M3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -154,7 +154,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M3" authorId="0">
+    <comment ref="N3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -176,7 +176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0">
+    <comment ref="T3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -199,7 +199,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0">
+    <comment ref="U3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -223,7 +223,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U3" authorId="0">
+    <comment ref="V3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -249,7 +249,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z3" authorId="0">
+    <comment ref="AA3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -271,7 +271,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG3" authorId="0">
+    <comment ref="AH3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -298,7 +298,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="194">
   <si>
     <t>_ID</t>
   </si>
@@ -322,6 +322,9 @@
   </si>
   <si>
     <t>技能描述</t>
+  </si>
+  <si>
+    <t>Rate</t>
   </si>
   <si>
     <t>冷却时间</t>
@@ -1869,7 +1872,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:AK77"/>
+  <dimension ref="C3:AL77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="5.625" style="2" customWidth="1"/>
@@ -1881,31 +1884,32 @@
     <col min="8" max="8" width="9.375" style="2" customWidth="1"/>
     <col min="9" max="9" width="5.25" style="2" customWidth="1"/>
     <col min="10" max="10" width="74.875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="5.875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="8.375" style="2" customWidth="1"/>
-    <col min="13" max="13" width="5.875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="7.50833333333333" style="2" customWidth="1"/>
-    <col min="15" max="16" width="12.875" style="2" customWidth="1"/>
-    <col min="17" max="18" width="13.5" style="2" customWidth="1"/>
-    <col min="19" max="19" width="7.375" style="2" customWidth="1"/>
-    <col min="20" max="20" width="7.50833333333333" style="2" customWidth="1"/>
-    <col min="21" max="21" width="8.25" style="2" customWidth="1"/>
-    <col min="22" max="22" width="6.5" style="2" customWidth="1"/>
-    <col min="23" max="25" width="7.625" style="2" customWidth="1"/>
-    <col min="26" max="27" width="7.875" style="2" customWidth="1"/>
-    <col min="28" max="28" width="9.625" style="2" customWidth="1"/>
-    <col min="29" max="30" width="7.875" style="2" customWidth="1"/>
-    <col min="31" max="31" width="12.625" style="2" customWidth="1"/>
-    <col min="32" max="32" width="9.625" style="2" customWidth="1"/>
-    <col min="33" max="33" width="27.625" style="2" customWidth="1"/>
-    <col min="34" max="34" width="17.875" style="2" customWidth="1"/>
-    <col min="35" max="35" width="19.75" style="2" customWidth="1"/>
-    <col min="36" max="36" width="9" style="2"/>
-    <col min="37" max="37" width="19.25" style="2" customWidth="1"/>
-    <col min="38" max="16384" width="9" style="2"/>
+    <col min="11" max="11" width="10.5" style="2" customWidth="1"/>
+    <col min="12" max="12" width="5.875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="8.375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="5.875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.50833333333333" style="2" customWidth="1"/>
+    <col min="16" max="17" width="12.875" style="2" customWidth="1"/>
+    <col min="18" max="19" width="13.5" style="2" customWidth="1"/>
+    <col min="20" max="20" width="7.375" style="2" customWidth="1"/>
+    <col min="21" max="21" width="7.50833333333333" style="2" customWidth="1"/>
+    <col min="22" max="22" width="8.25" style="2" customWidth="1"/>
+    <col min="23" max="23" width="6.5" style="2" customWidth="1"/>
+    <col min="24" max="26" width="7.625" style="2" customWidth="1"/>
+    <col min="27" max="28" width="7.875" style="2" customWidth="1"/>
+    <col min="29" max="29" width="9.625" style="2" customWidth="1"/>
+    <col min="30" max="31" width="7.875" style="2" customWidth="1"/>
+    <col min="32" max="32" width="12.625" style="2" customWidth="1"/>
+    <col min="33" max="33" width="9.625" style="2" customWidth="1"/>
+    <col min="34" max="34" width="27.625" style="2" customWidth="1"/>
+    <col min="35" max="35" width="17.875" style="2" customWidth="1"/>
+    <col min="36" max="36" width="19.75" style="2" customWidth="1"/>
+    <col min="37" max="37" width="9" style="2"/>
+    <col min="38" max="38" width="19.25" style="2" customWidth="1"/>
+    <col min="39" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:37">
+    <row r="3" spans="3:38">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1952,7 +1956,7 @@
         <v>14</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>15</v>
@@ -2005,40 +2009,43 @@
       <c r="AI3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AJ3" s="2" t="s">
+      <c r="AJ3" s="3" t="s">
         <v>32</v>
       </c>
       <c r="AK3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="AL3" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="4" spans="3:35">
+    <row r="4" spans="3:36">
       <c r="C4" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>42</v>
@@ -2050,13 +2057,13 @@
         <v>44</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="P4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="R4" s="3" t="s">
         <v>46</v>
@@ -2110,111 +2117,117 @@
         <v>62</v>
       </c>
       <c r="AI4" s="3" t="s">
-        <v>31</v>
+        <v>63</v>
+      </c>
+      <c r="AJ4" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="5" spans="3:35">
+    <row r="5" spans="3:36">
       <c r="C5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="I5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="K5" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="L5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T5" s="3" t="s">
         <v>64</v>
       </c>
       <c r="U5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="V5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="W5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="V5" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="W5" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="X5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Y5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Z5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AA5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AC5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AD5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AE5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AF5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AG5" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AH5" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="AI5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="AJ5" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="3:35">
+    <row r="6" s="1" customFormat="1" spans="3:36">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
@@ -2222,10 +2235,10 @@
         <v>1001</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -2237,60 +2250,60 @@
         <v>10</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K6" s="1">
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="1">
         <v>1</v>
       </c>
       <c r="N6" s="1">
+        <v>1</v>
+      </c>
+      <c r="O6" s="1">
         <v>600</v>
       </c>
-      <c r="O6" s="1">
+      <c r="P6" s="1">
         <v>60</v>
       </c>
-      <c r="P6" s="1">
-        <f t="shared" ref="P6:P16" si="0">N6*5</f>
+      <c r="Q6" s="1">
+        <f t="shared" ref="Q6:Q16" si="0">O6*5</f>
         <v>3000</v>
       </c>
-      <c r="Q6" s="1">
-        <v>1</v>
-      </c>
       <c r="R6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" s="1">
-        <v>1</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>68</v>
+        <v>0</v>
+      </c>
+      <c r="T6" s="1">
+        <v>1</v>
       </c>
       <c r="U6" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="V6" s="1">
-        <v>0</v>
+      <c r="V6" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="W6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6" s="1">
         <v>0</v>
       </c>
       <c r="Z6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="1">
         <v>120</v>
       </c>
-      <c r="AA6" s="1">
-        <v>0</v>
-      </c>
       <c r="AB6" s="1">
         <v>0</v>
       </c>
@@ -2306,14 +2319,17 @@
       <c r="AF6" s="1">
         <v>0</v>
       </c>
-      <c r="AH6" s="1">
-        <v>50</v>
+      <c r="AG6" s="1">
+        <v>0</v>
       </c>
       <c r="AI6" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ6" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" spans="3:35">
+    <row r="7" s="1" customFormat="1" spans="3:36">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
@@ -2321,10 +2337,10 @@
         <v>1002</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -2336,65 +2352,65 @@
         <v>10</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K7" s="1">
         <v>0</v>
       </c>
       <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
         <v>2</v>
       </c>
-      <c r="M7" s="1">
-        <v>1</v>
-      </c>
       <c r="N7" s="1">
+        <v>1</v>
+      </c>
+      <c r="O7" s="1">
         <v>600</v>
       </c>
-      <c r="O7" s="1">
+      <c r="P7" s="1">
         <v>60</v>
       </c>
-      <c r="P7" s="1">
+      <c r="Q7" s="1">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="R7" s="1">
         <v>2</v>
       </c>
-      <c r="R7" s="1">
-        <v>0</v>
-      </c>
       <c r="S7" s="1">
+        <v>0</v>
+      </c>
+      <c r="T7" s="1">
         <v>2</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="U7" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="V7" s="1">
-        <v>0</v>
+      <c r="V7" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="W7" s="1">
+        <v>0</v>
+      </c>
+      <c r="X7" s="1">
         <v>2</v>
       </c>
-      <c r="X7" s="1">
-        <v>0</v>
-      </c>
       <c r="Y7" s="1">
         <v>0</v>
       </c>
       <c r="Z7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="1">
         <v>150</v>
       </c>
-      <c r="AA7" s="1">
-        <v>0</v>
-      </c>
       <c r="AB7" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AC7" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AD7" s="1">
         <v>0</v>
@@ -2405,14 +2421,17 @@
       <c r="AF7" s="1">
         <v>0</v>
       </c>
-      <c r="AH7" s="1">
-        <v>50</v>
+      <c r="AG7" s="1">
+        <v>0</v>
       </c>
       <c r="AI7" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ7" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" spans="3:35">
+    <row r="8" s="1" customFormat="1" spans="3:36">
       <c r="C8" s="1">
         <v>1003</v>
       </c>
@@ -2420,10 +2439,10 @@
         <v>1003</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -2435,60 +2454,60 @@
         <v>10</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K8" s="1">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1">
         <v>5</v>
       </c>
-      <c r="L8" s="1">
+      <c r="M8" s="1">
         <v>2</v>
       </c>
-      <c r="M8" s="1">
-        <v>1</v>
-      </c>
       <c r="N8" s="1">
+        <v>1</v>
+      </c>
+      <c r="O8" s="1">
         <v>600</v>
       </c>
-      <c r="O8" s="1">
+      <c r="P8" s="1">
         <v>60</v>
       </c>
-      <c r="P8" s="1">
+      <c r="Q8" s="1">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="Q8" s="1">
-        <v>1</v>
-      </c>
       <c r="R8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" s="1">
-        <v>1</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>68</v>
+        <v>0</v>
+      </c>
+      <c r="T8" s="1">
+        <v>1</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="V8" s="1">
-        <v>0</v>
+        <v>69</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="W8" s="1">
+        <v>0</v>
+      </c>
+      <c r="X8" s="1">
         <v>5</v>
       </c>
-      <c r="X8" s="1">
-        <v>0</v>
-      </c>
       <c r="Y8" s="1">
         <v>0</v>
       </c>
       <c r="Z8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="1">
         <v>100</v>
       </c>
-      <c r="AA8" s="1">
-        <v>0</v>
-      </c>
       <c r="AB8" s="1">
         <v>0</v>
       </c>
@@ -2504,17 +2523,20 @@
       <c r="AF8" s="1">
         <v>0</v>
       </c>
-      <c r="AG8" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="AH8" s="1">
-        <v>50</v>
+      <c r="AG8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="AI8" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ8" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" spans="3:35">
+    <row r="9" s="1" customFormat="1" spans="3:36">
       <c r="C9" s="1">
         <v>1004</v>
       </c>
@@ -2522,10 +2544,10 @@
         <v>1004</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G9" s="1">
         <v>7</v>
@@ -2537,60 +2559,60 @@
         <v>10</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
         <v>10</v>
       </c>
-      <c r="L9" s="1">
-        <v>1</v>
-      </c>
       <c r="M9" s="1">
         <v>1</v>
       </c>
       <c r="N9" s="1">
+        <v>1</v>
+      </c>
+      <c r="O9" s="1">
         <v>600</v>
       </c>
-      <c r="O9" s="1">
+      <c r="P9" s="1">
         <v>60</v>
       </c>
-      <c r="P9" s="1">
+      <c r="Q9" s="1">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="R9" s="1">
         <v>4</v>
       </c>
-      <c r="R9" s="1">
-        <v>0</v>
-      </c>
       <c r="S9" s="1">
+        <v>0</v>
+      </c>
+      <c r="T9" s="1">
         <v>5</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="U9" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="V9" s="1">
+      <c r="V9" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="W9" s="1">
         <v>2</v>
       </c>
-      <c r="W9" s="1">
-        <v>1</v>
-      </c>
       <c r="X9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" s="1">
         <v>0</v>
       </c>
       <c r="Z9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="1">
         <v>200</v>
       </c>
-      <c r="AA9" s="1">
-        <v>0</v>
-      </c>
       <c r="AB9" s="1">
         <v>0</v>
       </c>
@@ -2606,17 +2628,20 @@
       <c r="AF9" s="1">
         <v>0</v>
       </c>
-      <c r="AG9" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AH9" s="1">
-        <v>50</v>
+      <c r="AG9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="AI9" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ9" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" spans="3:35">
+    <row r="10" s="1" customFormat="1" spans="3:36">
       <c r="C10" s="1">
         <v>1005</v>
       </c>
@@ -2624,10 +2649,10 @@
         <v>1005</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G10" s="1">
         <v>5</v>
@@ -2639,48 +2664,48 @@
         <v>50</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K10" s="1">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1">
         <v>55</v>
       </c>
-      <c r="L10" s="1">
-        <v>1</v>
-      </c>
       <c r="M10" s="1">
         <v>1</v>
       </c>
       <c r="N10" s="1">
+        <v>1</v>
+      </c>
+      <c r="O10" s="1">
         <v>200</v>
       </c>
-      <c r="O10" s="1">
+      <c r="P10" s="1">
         <v>20</v>
       </c>
-      <c r="P10" s="1">
+      <c r="Q10" s="1">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="Q10" s="1">
-        <v>1</v>
-      </c>
       <c r="R10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" s="1">
         <v>0</v>
       </c>
-      <c r="T10" s="1" t="s">
-        <v>68</v>
+      <c r="T10" s="1">
+        <v>0</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V10" s="1">
+        <v>69</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="W10" s="1">
         <v>30</v>
       </c>
-      <c r="W10" s="1">
-        <v>0</v>
-      </c>
       <c r="X10" s="1">
         <v>0</v>
       </c>
@@ -2688,11 +2713,11 @@
         <v>0</v>
       </c>
       <c r="Z10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="1">
         <v>100</v>
       </c>
-      <c r="AA10" s="1">
-        <v>0</v>
-      </c>
       <c r="AB10" s="1">
         <v>0</v>
       </c>
@@ -2708,17 +2733,20 @@
       <c r="AF10" s="1">
         <v>0</v>
       </c>
-      <c r="AG10" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="AH10" s="1">
-        <v>50</v>
+      <c r="AG10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="AI10" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ10" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" spans="3:35">
+    <row r="11" s="1" customFormat="1" spans="3:36">
       <c r="C11" s="1">
         <v>1006</v>
       </c>
@@ -2726,10 +2754,10 @@
         <v>1006</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G11" s="1">
         <v>6</v>
@@ -2741,44 +2769,44 @@
         <v>10</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K11" s="1">
         <v>0</v>
       </c>
       <c r="L11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="1">
         <v>1</v>
       </c>
       <c r="N11" s="1">
+        <v>1</v>
+      </c>
+      <c r="O11" s="1">
         <v>200</v>
       </c>
-      <c r="O11" s="1">
+      <c r="P11" s="1">
         <v>20</v>
       </c>
-      <c r="P11" s="1">
+      <c r="Q11" s="1">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="Q11" s="1">
-        <v>1</v>
-      </c>
       <c r="R11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" s="1">
         <v>0</v>
       </c>
-      <c r="T11" s="1" t="s">
-        <v>68</v>
+      <c r="T11" s="1">
+        <v>0</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="V11" s="1">
-        <v>0</v>
+        <v>69</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="W11" s="1">
         <v>0</v>
@@ -2790,10 +2818,10 @@
         <v>0</v>
       </c>
       <c r="Z11" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AA11" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AB11" s="1">
         <v>0</v>
@@ -2810,14 +2838,17 @@
       <c r="AF11" s="1">
         <v>0</v>
       </c>
-      <c r="AH11" s="1">
-        <v>50</v>
+      <c r="AG11" s="1">
+        <v>0</v>
       </c>
       <c r="AI11" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ11" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" spans="3:35">
+    <row r="12" s="1" customFormat="1" spans="3:36">
       <c r="C12" s="1">
         <v>1007</v>
       </c>
@@ -2825,10 +2856,10 @@
         <v>1007</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
@@ -2840,65 +2871,65 @@
         <v>10</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="K12" s="6">
+        <v>95</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="L12" s="6">
         <v>5</v>
       </c>
-      <c r="L12" s="1">
-        <v>1</v>
-      </c>
       <c r="M12" s="1">
         <v>1</v>
       </c>
       <c r="N12" s="1">
+        <v>1</v>
+      </c>
+      <c r="O12" s="1">
         <v>600</v>
       </c>
-      <c r="O12" s="1">
+      <c r="P12" s="1">
         <v>60</v>
       </c>
-      <c r="P12" s="1">
+      <c r="Q12" s="1">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="Q12" s="6">
+      <c r="R12" s="6">
         <v>10</v>
       </c>
-      <c r="R12" s="1">
-        <v>0</v>
-      </c>
       <c r="S12" s="1">
-        <v>1</v>
-      </c>
-      <c r="T12" s="1" t="s">
-        <v>68</v>
+        <v>0</v>
+      </c>
+      <c r="T12" s="1">
+        <v>1</v>
       </c>
       <c r="U12" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="V12" s="1">
-        <v>0</v>
+      <c r="V12" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="W12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12" s="1">
         <v>0</v>
       </c>
-      <c r="Z12" s="6">
+      <c r="Z12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="6">
         <v>500</v>
       </c>
-      <c r="AA12" s="1">
-        <v>0</v>
-      </c>
       <c r="AB12" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AC12" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AD12" s="1">
         <v>0</v>
@@ -2909,17 +2940,20 @@
       <c r="AF12" s="1">
         <v>0</v>
       </c>
-      <c r="AG12" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="AH12" s="1">
-        <v>50</v>
+      <c r="AG12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="6" t="s">
+        <v>96</v>
       </c>
       <c r="AI12" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ12" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" spans="3:35">
+    <row r="13" s="1" customFormat="1" spans="3:36">
       <c r="C13" s="1">
         <v>1008</v>
       </c>
@@ -2927,10 +2961,10 @@
         <v>1008</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G13" s="1">
         <v>1008</v>
@@ -2942,48 +2976,48 @@
         <v>200</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K13" s="1">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1">
         <v>30</v>
       </c>
-      <c r="L13" s="1">
-        <v>1</v>
-      </c>
       <c r="M13" s="1">
         <v>1</v>
       </c>
       <c r="N13" s="1">
+        <v>1</v>
+      </c>
+      <c r="O13" s="1">
         <v>30</v>
       </c>
-      <c r="O13" s="1">
+      <c r="P13" s="1">
         <v>3</v>
       </c>
-      <c r="P13" s="1">
+      <c r="Q13" s="1">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-      <c r="Q13" s="1">
-        <v>1</v>
-      </c>
       <c r="R13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" s="1">
         <v>0</v>
       </c>
-      <c r="T13" s="1" t="s">
-        <v>68</v>
+      <c r="T13" s="1">
+        <v>0</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="V13" s="1">
+        <v>69</v>
+      </c>
+      <c r="V13" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="W13" s="1">
         <v>20</v>
       </c>
-      <c r="W13" s="1">
-        <v>0</v>
-      </c>
       <c r="X13" s="1">
         <v>0</v>
       </c>
@@ -2991,11 +3025,11 @@
         <v>0</v>
       </c>
       <c r="Z13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="1">
         <v>30</v>
       </c>
-      <c r="AA13" s="1">
-        <v>0</v>
-      </c>
       <c r="AB13" s="1">
         <v>0</v>
       </c>
@@ -3011,17 +3045,20 @@
       <c r="AF13" s="1">
         <v>0</v>
       </c>
-      <c r="AG13" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="AH13" s="1">
-        <v>50</v>
+      <c r="AG13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="AI13" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ13" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" spans="3:35">
+    <row r="14" s="1" customFormat="1" spans="3:36">
       <c r="C14" s="1">
         <v>1009</v>
       </c>
@@ -3029,10 +3066,10 @@
         <v>1009</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -3044,65 +3081,65 @@
         <v>10</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
         <v>15</v>
       </c>
-      <c r="L14" s="1">
+      <c r="M14" s="1">
         <v>2</v>
       </c>
-      <c r="M14" s="1">
-        <v>1</v>
-      </c>
       <c r="N14" s="1">
+        <v>1</v>
+      </c>
+      <c r="O14" s="1">
         <v>300</v>
       </c>
-      <c r="O14" s="1">
+      <c r="P14" s="1">
         <v>30</v>
       </c>
-      <c r="P14" s="1">
+      <c r="Q14" s="1">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
-      <c r="Q14" s="1">
+      <c r="R14" s="1">
         <v>12</v>
       </c>
-      <c r="R14" s="1">
-        <v>0</v>
-      </c>
       <c r="S14" s="1">
+        <v>0</v>
+      </c>
+      <c r="T14" s="1">
         <v>5</v>
-      </c>
-      <c r="T14" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="U14" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="V14" s="1">
-        <v>0</v>
+      <c r="V14" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="W14" s="1">
+        <v>0</v>
+      </c>
+      <c r="X14" s="1">
         <v>4</v>
       </c>
-      <c r="X14" s="1">
-        <v>0</v>
-      </c>
       <c r="Y14" s="1">
         <v>0</v>
       </c>
       <c r="Z14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="1">
         <v>600</v>
       </c>
-      <c r="AA14" s="1">
-        <v>0</v>
-      </c>
       <c r="AB14" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AC14" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AD14" s="1">
         <v>0</v>
@@ -3113,17 +3150,20 @@
       <c r="AF14" s="1">
         <v>0</v>
       </c>
-      <c r="AG14" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="AH14" s="1">
-        <v>50</v>
+      <c r="AG14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="AI14" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ14" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" spans="3:35">
+    <row r="15" s="1" customFormat="1" spans="3:36">
       <c r="C15" s="1">
         <v>1010</v>
       </c>
@@ -3131,10 +3171,10 @@
         <v>1010</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G15" s="1">
         <v>1</v>
@@ -3146,43 +3186,43 @@
         <v>10</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K15" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
         <v>2</v>
       </c>
-      <c r="M15" s="1">
-        <v>1</v>
-      </c>
       <c r="N15" s="1">
+        <v>1</v>
+      </c>
+      <c r="O15" s="1">
         <v>10</v>
       </c>
-      <c r="O15" s="1">
-        <v>1</v>
-      </c>
       <c r="P15" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="1">
         <v>250</v>
       </c>
-      <c r="Q15" s="1">
+      <c r="R15" s="1">
         <v>10</v>
       </c>
-      <c r="R15" s="1">
-        <v>0</v>
-      </c>
       <c r="S15" s="1">
+        <v>0</v>
+      </c>
+      <c r="T15" s="1">
         <v>2</v>
       </c>
-      <c r="T15" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="U15" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="V15" s="1">
-        <v>0</v>
+        <v>82</v>
+      </c>
+      <c r="V15" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="W15" s="1">
         <v>0</v>
@@ -3194,11 +3234,11 @@
         <v>0</v>
       </c>
       <c r="Z15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="1">
         <v>200</v>
       </c>
-      <c r="AA15" s="1">
-        <v>0</v>
-      </c>
       <c r="AB15" s="1">
         <v>0</v>
       </c>
@@ -3214,14 +3254,17 @@
       <c r="AF15" s="1">
         <v>0</v>
       </c>
-      <c r="AH15" s="1">
-        <v>50</v>
+      <c r="AG15" s="1">
+        <v>0</v>
       </c>
       <c r="AI15" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ15" s="1">
         <v>4102</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" spans="3:35">
+    <row r="16" s="1" customFormat="1" spans="3:36">
       <c r="C16" s="1">
         <v>1011</v>
       </c>
@@ -3229,10 +3272,10 @@
         <v>1011</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G16" s="1">
         <v>8</v>
@@ -3244,63 +3287,63 @@
         <v>0</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K16" s="1">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1">
         <v>30</v>
       </c>
-      <c r="L16" s="1">
+      <c r="M16" s="1">
         <v>2</v>
       </c>
-      <c r="M16" s="1">
-        <v>1</v>
-      </c>
       <c r="N16" s="1">
+        <v>1</v>
+      </c>
+      <c r="O16" s="1">
         <v>10</v>
       </c>
-      <c r="O16" s="1">
-        <v>1</v>
-      </c>
       <c r="P16" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="1">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="Q16" s="1">
-        <v>50</v>
-      </c>
       <c r="R16" s="1">
+        <v>50</v>
+      </c>
+      <c r="S16" s="1">
         <v>10</v>
       </c>
-      <c r="S16" s="1">
+      <c r="T16" s="1">
         <v>3</v>
       </c>
-      <c r="T16" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="U16" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V16" s="1">
+        <v>82</v>
+      </c>
+      <c r="V16" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="W16" s="1">
         <v>15</v>
       </c>
-      <c r="W16" s="1">
+      <c r="X16" s="1">
         <v>5</v>
-      </c>
-      <c r="X16" s="1">
-        <v>4</v>
       </c>
       <c r="Y16" s="1">
         <v>4</v>
       </c>
       <c r="Z16" s="1">
+        <v>4</v>
+      </c>
+      <c r="AA16" s="1">
         <v>500</v>
       </c>
-      <c r="AA16" s="1">
+      <c r="AB16" s="1">
         <v>100</v>
       </c>
-      <c r="AB16" s="1">
-        <v>0</v>
-      </c>
       <c r="AC16" s="1">
         <v>0</v>
       </c>
@@ -3313,17 +3356,20 @@
       <c r="AF16" s="1">
         <v>0</v>
       </c>
-      <c r="AH16" s="1">
-        <v>50</v>
+      <c r="AG16" s="1">
+        <v>0</v>
       </c>
       <c r="AI16" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ16" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="6:6">
       <c r="F17" s="2"/>
     </row>
-    <row r="18" s="1" customFormat="1" spans="3:35">
+    <row r="18" s="1" customFormat="1" spans="3:36">
       <c r="C18" s="1">
         <v>2001</v>
       </c>
@@ -3331,10 +3377,10 @@
         <v>2001</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G18" s="1">
         <v>1</v>
@@ -3346,60 +3392,60 @@
         <v>10</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K18" s="1">
         <v>0</v>
       </c>
       <c r="L18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="1">
+        <v>1</v>
+      </c>
+      <c r="N18" s="1">
         <v>2</v>
       </c>
-      <c r="N18" s="1">
+      <c r="O18" s="1">
         <v>600</v>
       </c>
-      <c r="O18" s="1">
+      <c r="P18" s="1">
         <v>60</v>
       </c>
-      <c r="P18" s="1">
-        <f t="shared" ref="P18:P28" si="1">N18*5</f>
+      <c r="Q18" s="1">
+        <f t="shared" ref="Q18:Q28" si="1">O18*5</f>
         <v>3000</v>
       </c>
-      <c r="Q18" s="1">
+      <c r="R18" s="1">
         <v>2</v>
       </c>
-      <c r="R18" s="1">
-        <v>0</v>
-      </c>
       <c r="S18" s="1">
+        <v>0</v>
+      </c>
+      <c r="T18" s="1">
         <v>2</v>
       </c>
-      <c r="T18" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="U18" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="V18" s="1">
-        <v>0</v>
+        <v>82</v>
+      </c>
+      <c r="V18" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="W18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18" s="1">
         <v>0</v>
       </c>
       <c r="Z18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="1">
         <v>120</v>
       </c>
-      <c r="AA18" s="1">
-        <v>0</v>
-      </c>
       <c r="AB18" s="1">
         <v>0</v>
       </c>
@@ -3415,14 +3461,17 @@
       <c r="AF18" s="1">
         <v>0</v>
       </c>
-      <c r="AH18" s="1">
-        <v>50</v>
+      <c r="AG18" s="1">
+        <v>0</v>
       </c>
       <c r="AI18" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ18" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" spans="3:35">
+    <row r="19" s="1" customFormat="1" spans="3:36">
       <c r="C19" s="1">
         <v>2002</v>
       </c>
@@ -3430,10 +3479,10 @@
         <v>2002</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G19" s="1">
         <v>1</v>
@@ -3445,65 +3494,65 @@
         <v>10</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K19" s="1">
         <v>0</v>
       </c>
       <c r="L19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" s="1">
+        <v>1</v>
+      </c>
+      <c r="N19" s="1">
         <v>2</v>
       </c>
-      <c r="N19" s="1">
+      <c r="O19" s="1">
         <v>600</v>
       </c>
-      <c r="O19" s="1">
+      <c r="P19" s="1">
         <v>60</v>
       </c>
-      <c r="P19" s="1">
-        <f>N19*2.5</f>
+      <c r="Q19" s="1">
+        <f>O19*2.5</f>
         <v>1500</v>
       </c>
-      <c r="Q19" s="1">
+      <c r="R19" s="1">
         <v>3</v>
       </c>
-      <c r="R19" s="1">
-        <v>0</v>
-      </c>
       <c r="S19" s="1">
+        <v>0</v>
+      </c>
+      <c r="T19" s="1">
         <v>3</v>
       </c>
-      <c r="T19" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="U19" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="V19" s="1">
-        <v>0</v>
+        <v>82</v>
+      </c>
+      <c r="V19" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="W19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19" s="1">
         <v>0</v>
       </c>
       <c r="Z19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="1">
         <v>150</v>
       </c>
-      <c r="AA19" s="1">
-        <v>0</v>
-      </c>
       <c r="AB19" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AC19" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AD19" s="1">
         <v>0</v>
@@ -3514,14 +3563,17 @@
       <c r="AF19" s="1">
         <v>0</v>
       </c>
-      <c r="AH19" s="1">
-        <v>50</v>
+      <c r="AG19" s="1">
+        <v>0</v>
       </c>
       <c r="AI19" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ19" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" spans="3:35">
+    <row r="20" s="1" customFormat="1" spans="3:36">
       <c r="C20" s="1">
         <v>2003</v>
       </c>
@@ -3529,10 +3581,10 @@
         <v>2003</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G20" s="1">
         <v>3</v>
@@ -3544,60 +3596,60 @@
         <v>10</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K20" s="1">
+        <v>0</v>
+      </c>
+      <c r="L20" s="1">
         <v>10</v>
-      </c>
-      <c r="L20" s="1">
-        <v>2</v>
       </c>
       <c r="M20" s="1">
         <v>2</v>
       </c>
       <c r="N20" s="1">
+        <v>2</v>
+      </c>
+      <c r="O20" s="1">
         <v>600</v>
       </c>
-      <c r="O20" s="1">
+      <c r="P20" s="1">
         <v>60</v>
       </c>
-      <c r="P20" s="1">
+      <c r="Q20" s="1">
         <f t="shared" si="1"/>
         <v>3000</v>
       </c>
-      <c r="Q20" s="1">
+      <c r="R20" s="1">
         <v>2</v>
       </c>
-      <c r="R20" s="1">
-        <v>0</v>
-      </c>
       <c r="S20" s="1">
+        <v>0</v>
+      </c>
+      <c r="T20" s="1">
         <v>3</v>
       </c>
-      <c r="T20" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="U20" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V20" s="1">
+        <v>82</v>
+      </c>
+      <c r="V20" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="W20" s="1">
         <v>10</v>
       </c>
-      <c r="W20" s="1">
+      <c r="X20" s="1">
         <v>5</v>
-      </c>
-      <c r="X20" s="1">
-        <v>2</v>
       </c>
       <c r="Y20" s="1">
         <v>2</v>
       </c>
       <c r="Z20" s="1">
+        <v>2</v>
+      </c>
+      <c r="AA20" s="1">
         <v>80</v>
       </c>
-      <c r="AA20" s="1">
-        <v>0</v>
-      </c>
       <c r="AB20" s="1">
         <v>0</v>
       </c>
@@ -3613,14 +3665,17 @@
       <c r="AF20" s="1">
         <v>0</v>
       </c>
-      <c r="AH20" s="1">
-        <v>50</v>
+      <c r="AG20" s="1">
+        <v>0</v>
       </c>
       <c r="AI20" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ20" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" spans="3:35">
+    <row r="21" s="1" customFormat="1" spans="3:36">
       <c r="C21" s="1">
         <v>2004</v>
       </c>
@@ -3628,10 +3683,10 @@
         <v>2004</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G21" s="1">
         <v>1</v>
@@ -3643,60 +3698,60 @@
         <v>10</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K21" s="1">
         <v>0</v>
       </c>
       <c r="L21" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M21" s="1">
         <v>2</v>
       </c>
       <c r="N21" s="1">
+        <v>2</v>
+      </c>
+      <c r="O21" s="1">
         <v>600</v>
       </c>
-      <c r="O21" s="1">
+      <c r="P21" s="1">
         <v>60</v>
       </c>
-      <c r="P21" s="1">
+      <c r="Q21" s="1">
         <f t="shared" si="1"/>
         <v>3000</v>
       </c>
-      <c r="Q21" s="1">
+      <c r="R21" s="1">
         <v>2</v>
       </c>
-      <c r="R21" s="1">
-        <v>0</v>
-      </c>
       <c r="S21" s="1">
+        <v>0</v>
+      </c>
+      <c r="T21" s="1">
         <v>4</v>
       </c>
-      <c r="T21" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="U21" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V21" s="1">
-        <v>0</v>
+        <v>69</v>
+      </c>
+      <c r="V21" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="W21" s="1">
+        <v>0</v>
+      </c>
+      <c r="X21" s="1">
         <v>4</v>
-      </c>
-      <c r="X21" s="1">
-        <v>2</v>
       </c>
       <c r="Y21" s="1">
         <v>2</v>
       </c>
       <c r="Z21" s="1">
+        <v>2</v>
+      </c>
+      <c r="AA21" s="1">
         <v>100</v>
       </c>
-      <c r="AA21" s="1">
-        <v>0</v>
-      </c>
       <c r="AB21" s="1">
         <v>0</v>
       </c>
@@ -3712,17 +3767,20 @@
       <c r="AF21" s="1">
         <v>0</v>
       </c>
-      <c r="AG21" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AH21" s="1">
-        <v>50</v>
+      <c r="AG21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH21" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="AI21" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ21" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" spans="3:35">
+    <row r="22" s="1" customFormat="1" spans="3:36">
       <c r="C22" s="1">
         <v>2005</v>
       </c>
@@ -3730,10 +3788,10 @@
         <v>2005</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G22" s="1">
         <v>5</v>
@@ -3745,48 +3803,48 @@
         <v>50</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K22" s="1">
+        <v>0</v>
+      </c>
+      <c r="L22" s="1">
         <v>55</v>
       </c>
-      <c r="L22" s="1">
-        <v>1</v>
-      </c>
       <c r="M22" s="1">
+        <v>1</v>
+      </c>
+      <c r="N22" s="1">
         <v>2</v>
       </c>
-      <c r="N22" s="1">
+      <c r="O22" s="1">
         <v>200</v>
       </c>
-      <c r="O22" s="1">
+      <c r="P22" s="1">
         <v>20</v>
       </c>
-      <c r="P22" s="1">
+      <c r="Q22" s="1">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="Q22" s="1">
-        <v>1</v>
-      </c>
       <c r="R22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" s="1">
         <v>0</v>
       </c>
-      <c r="T22" s="1" t="s">
-        <v>68</v>
+      <c r="T22" s="1">
+        <v>0</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V22" s="1">
+        <v>69</v>
+      </c>
+      <c r="V22" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="W22" s="1">
         <v>30</v>
       </c>
-      <c r="W22" s="1">
-        <v>0</v>
-      </c>
       <c r="X22" s="1">
         <v>0</v>
       </c>
@@ -3794,11 +3852,11 @@
         <v>0</v>
       </c>
       <c r="Z22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="1">
         <v>100</v>
       </c>
-      <c r="AA22" s="1">
-        <v>0</v>
-      </c>
       <c r="AB22" s="1">
         <v>0</v>
       </c>
@@ -3814,17 +3872,20 @@
       <c r="AF22" s="1">
         <v>0</v>
       </c>
-      <c r="AG22" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="AH22" s="1">
-        <v>50</v>
+      <c r="AG22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="AI22" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ22" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" spans="3:35">
+    <row r="23" s="1" customFormat="1" spans="3:36">
       <c r="C23" s="1">
         <v>2006</v>
       </c>
@@ -3832,10 +3893,10 @@
         <v>2006</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G23" s="1">
         <v>6</v>
@@ -3847,44 +3908,44 @@
         <v>10</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K23" s="1">
         <v>0</v>
       </c>
       <c r="L23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" s="1">
+        <v>1</v>
+      </c>
+      <c r="N23" s="1">
         <v>2</v>
       </c>
-      <c r="N23" s="1">
+      <c r="O23" s="1">
         <v>200</v>
       </c>
-      <c r="O23" s="1">
+      <c r="P23" s="1">
         <v>20</v>
       </c>
-      <c r="P23" s="1">
+      <c r="Q23" s="1">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="Q23" s="1">
-        <v>1</v>
-      </c>
       <c r="R23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" s="1">
         <v>0</v>
       </c>
-      <c r="T23" s="1" t="s">
-        <v>68</v>
+      <c r="T23" s="1">
+        <v>0</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="V23" s="1">
-        <v>0</v>
+        <v>69</v>
+      </c>
+      <c r="V23" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="W23" s="1">
         <v>0</v>
@@ -3896,10 +3957,10 @@
         <v>0</v>
       </c>
       <c r="Z23" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AA23" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AB23" s="1">
         <v>0</v>
@@ -3916,14 +3977,17 @@
       <c r="AF23" s="1">
         <v>0</v>
       </c>
-      <c r="AH23" s="1">
-        <v>50</v>
+      <c r="AG23" s="1">
+        <v>0</v>
       </c>
       <c r="AI23" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ23" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" spans="3:35">
+    <row r="24" s="1" customFormat="1" spans="3:36">
       <c r="C24" s="1">
         <v>2007</v>
       </c>
@@ -3931,10 +3995,10 @@
         <v>2007</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G24" s="1">
         <v>1</v>
@@ -3946,60 +4010,60 @@
         <v>10</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="K24" s="6">
+        <v>120</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0</v>
+      </c>
+      <c r="L24" s="6">
         <v>5</v>
-      </c>
-      <c r="L24" s="1">
-        <v>2</v>
       </c>
       <c r="M24" s="1">
         <v>2</v>
       </c>
       <c r="N24" s="1">
+        <v>2</v>
+      </c>
+      <c r="O24" s="1">
         <v>600</v>
       </c>
-      <c r="O24" s="1">
+      <c r="P24" s="1">
         <v>60</v>
       </c>
-      <c r="P24" s="1">
+      <c r="Q24" s="1">
         <f t="shared" si="1"/>
         <v>3000</v>
       </c>
-      <c r="Q24" s="6">
+      <c r="R24" s="6">
         <v>6</v>
       </c>
-      <c r="R24" s="1">
-        <v>0</v>
-      </c>
       <c r="S24" s="1">
+        <v>0</v>
+      </c>
+      <c r="T24" s="1">
         <v>5</v>
       </c>
-      <c r="T24" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="U24" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V24" s="1">
-        <v>0</v>
+        <v>82</v>
+      </c>
+      <c r="V24" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="W24" s="1">
+        <v>0</v>
+      </c>
+      <c r="X24" s="1">
         <v>5</v>
-      </c>
-      <c r="X24" s="1">
-        <v>3</v>
       </c>
       <c r="Y24" s="1">
         <v>3</v>
       </c>
-      <c r="Z24" s="6">
+      <c r="Z24" s="1">
+        <v>3</v>
+      </c>
+      <c r="AA24" s="6">
         <v>300</v>
       </c>
-      <c r="AA24" s="1">
-        <v>0</v>
-      </c>
       <c r="AB24" s="1">
         <v>0</v>
       </c>
@@ -4015,17 +4079,20 @@
       <c r="AF24" s="1">
         <v>0</v>
       </c>
-      <c r="AG24" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="AH24" s="1">
-        <v>50</v>
+      <c r="AG24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="6" t="s">
+        <v>128</v>
       </c>
       <c r="AI24" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ24" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" spans="3:35">
+    <row r="25" s="1" customFormat="1" spans="3:36">
       <c r="C25" s="1">
         <v>2008</v>
       </c>
@@ -4033,10 +4100,10 @@
         <v>2008</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G25" s="1">
         <v>2008</v>
@@ -4048,44 +4115,44 @@
         <v>200</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K25" s="1">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1">
         <v>30</v>
       </c>
-      <c r="L25" s="1">
-        <v>1</v>
-      </c>
       <c r="M25" s="1">
+        <v>1</v>
+      </c>
+      <c r="N25" s="1">
         <v>2</v>
       </c>
-      <c r="N25" s="1">
+      <c r="O25" s="1">
         <v>30</v>
       </c>
-      <c r="O25" s="1">
+      <c r="P25" s="1">
         <v>3</v>
       </c>
-      <c r="P25" s="1">
+      <c r="Q25" s="1">
         <f t="shared" si="1"/>
         <v>150</v>
       </c>
-      <c r="Q25" s="1">
-        <v>1</v>
-      </c>
       <c r="R25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" s="1">
         <v>0</v>
       </c>
-      <c r="T25" s="1" t="s">
-        <v>68</v>
+      <c r="T25" s="1">
+        <v>0</v>
       </c>
       <c r="U25" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="V25" s="1">
-        <v>0</v>
+        <v>69</v>
+      </c>
+      <c r="V25" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="W25" s="1">
         <v>0</v>
@@ -4097,10 +4164,10 @@
         <v>0</v>
       </c>
       <c r="Z25" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AA25" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AB25" s="1">
         <v>0</v>
@@ -4117,17 +4184,20 @@
       <c r="AF25" s="1">
         <v>0</v>
       </c>
-      <c r="AG25" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="AH25" s="1">
-        <v>50</v>
+      <c r="AG25" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="1" t="s">
+        <v>132</v>
       </c>
       <c r="AI25" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ25" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" spans="3:35">
+    <row r="26" s="1" customFormat="1" spans="3:36">
       <c r="C26" s="1">
         <v>2009</v>
       </c>
@@ -4135,10 +4205,10 @@
         <v>2009</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G26" s="1">
         <v>3</v>
@@ -4150,60 +4220,60 @@
         <v>10</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K26" s="1">
+        <v>0</v>
+      </c>
+      <c r="L26" s="1">
         <v>15</v>
-      </c>
-      <c r="L26" s="1">
-        <v>2</v>
       </c>
       <c r="M26" s="1">
         <v>2</v>
       </c>
       <c r="N26" s="1">
+        <v>2</v>
+      </c>
+      <c r="O26" s="1">
         <v>300</v>
       </c>
-      <c r="O26" s="1">
+      <c r="P26" s="1">
         <v>30</v>
       </c>
-      <c r="P26" s="1">
+      <c r="Q26" s="1">
         <f t="shared" si="1"/>
         <v>1500</v>
       </c>
-      <c r="Q26" s="1">
+      <c r="R26" s="1">
         <v>7</v>
       </c>
-      <c r="R26" s="1">
-        <v>0</v>
-      </c>
       <c r="S26" s="1">
+        <v>0</v>
+      </c>
+      <c r="T26" s="1">
         <v>3</v>
       </c>
-      <c r="T26" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="U26" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V26" s="1">
+        <v>82</v>
+      </c>
+      <c r="V26" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="W26" s="1">
         <v>10</v>
       </c>
-      <c r="W26" s="1">
+      <c r="X26" s="1">
         <v>5</v>
-      </c>
-      <c r="X26" s="1">
-        <v>4</v>
       </c>
       <c r="Y26" s="1">
         <v>4</v>
       </c>
       <c r="Z26" s="1">
+        <v>4</v>
+      </c>
+      <c r="AA26" s="1">
         <v>400</v>
       </c>
-      <c r="AA26" s="1">
-        <v>0</v>
-      </c>
       <c r="AB26" s="1">
         <v>0</v>
       </c>
@@ -4219,17 +4289,20 @@
       <c r="AF26" s="1">
         <v>0</v>
       </c>
-      <c r="AG26" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="AH26" s="1">
-        <v>50</v>
+      <c r="AG26" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="AI26" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ26" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" spans="3:35">
+    <row r="27" s="1" customFormat="1" spans="3:36">
       <c r="C27" s="1">
         <v>2010</v>
       </c>
@@ -4237,10 +4310,10 @@
         <v>2010</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G27" s="1">
         <v>2010</v>
@@ -4252,60 +4325,60 @@
         <v>100</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K27" s="1">
+        <v>0</v>
+      </c>
+      <c r="L27" s="1">
         <v>30</v>
-      </c>
-      <c r="L27" s="1">
-        <v>2</v>
       </c>
       <c r="M27" s="1">
         <v>2</v>
       </c>
       <c r="N27" s="1">
+        <v>2</v>
+      </c>
+      <c r="O27" s="1">
         <v>10</v>
       </c>
-      <c r="O27" s="1">
-        <v>1</v>
-      </c>
       <c r="P27" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="1">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="Q27" s="1">
+      <c r="R27" s="1">
         <v>5</v>
       </c>
-      <c r="R27" s="1">
-        <v>0</v>
-      </c>
       <c r="S27" s="1">
+        <v>0</v>
+      </c>
+      <c r="T27" s="1">
         <v>3</v>
       </c>
-      <c r="T27" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="U27" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V27" s="1">
+        <v>82</v>
+      </c>
+      <c r="V27" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="W27" s="1">
         <v>15</v>
       </c>
-      <c r="W27" s="1">
+      <c r="X27" s="1">
         <v>5</v>
-      </c>
-      <c r="X27" s="1">
-        <v>4</v>
       </c>
       <c r="Y27" s="1">
         <v>4</v>
       </c>
       <c r="Z27" s="1">
+        <v>4</v>
+      </c>
+      <c r="AA27" s="1">
         <v>150</v>
       </c>
-      <c r="AA27" s="1">
-        <v>0</v>
-      </c>
       <c r="AB27" s="1">
         <v>0</v>
       </c>
@@ -4321,14 +4394,17 @@
       <c r="AF27" s="1">
         <v>0</v>
       </c>
-      <c r="AH27" s="1">
-        <v>50</v>
+      <c r="AG27" s="1">
+        <v>0</v>
       </c>
       <c r="AI27" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ27" s="1">
         <v>4102</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" spans="3:35">
+    <row r="28" s="1" customFormat="1" spans="3:36">
       <c r="C28" s="1">
         <v>2011</v>
       </c>
@@ -4336,10 +4412,10 @@
         <v>2011</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G28" s="1">
         <v>8</v>
@@ -4351,63 +4427,63 @@
         <v>0</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K28" s="1">
+        <v>0</v>
+      </c>
+      <c r="L28" s="1">
         <v>30</v>
-      </c>
-      <c r="L28" s="1">
-        <v>2</v>
       </c>
       <c r="M28" s="1">
         <v>2</v>
       </c>
       <c r="N28" s="1">
+        <v>2</v>
+      </c>
+      <c r="O28" s="1">
         <v>10</v>
       </c>
-      <c r="O28" s="1">
-        <v>1</v>
-      </c>
       <c r="P28" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="1">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="Q28" s="1">
-        <v>50</v>
-      </c>
       <c r="R28" s="1">
+        <v>50</v>
+      </c>
+      <c r="S28" s="1">
         <v>10</v>
       </c>
-      <c r="S28" s="1">
+      <c r="T28" s="1">
         <v>3</v>
       </c>
-      <c r="T28" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="U28" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V28" s="1">
+        <v>82</v>
+      </c>
+      <c r="V28" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="W28" s="1">
         <v>15</v>
       </c>
-      <c r="W28" s="1">
+      <c r="X28" s="1">
         <v>5</v>
-      </c>
-      <c r="X28" s="1">
-        <v>4</v>
       </c>
       <c r="Y28" s="1">
         <v>4</v>
       </c>
       <c r="Z28" s="1">
+        <v>4</v>
+      </c>
+      <c r="AA28" s="1">
         <v>500</v>
       </c>
-      <c r="AA28" s="1">
+      <c r="AB28" s="1">
         <v>100</v>
       </c>
-      <c r="AB28" s="1">
-        <v>0</v>
-      </c>
       <c r="AC28" s="1">
         <v>0</v>
       </c>
@@ -4420,17 +4496,20 @@
       <c r="AF28" s="1">
         <v>0</v>
       </c>
-      <c r="AH28" s="1">
-        <v>50</v>
+      <c r="AG28" s="1">
+        <v>0</v>
       </c>
       <c r="AI28" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ28" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="6:6">
       <c r="F29" s="2"/>
     </row>
-    <row r="30" s="1" customFormat="1" spans="3:35">
+    <row r="30" s="1" customFormat="1" spans="3:36">
       <c r="C30" s="1">
         <v>3001</v>
       </c>
@@ -4438,10 +4517,10 @@
         <v>3001</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G30" s="1">
         <v>4</v>
@@ -4453,43 +4532,43 @@
         <v>20</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K30" s="1">
+        <v>0</v>
+      </c>
+      <c r="L30" s="1">
         <v>4</v>
       </c>
-      <c r="L30" s="1">
-        <v>1</v>
-      </c>
       <c r="M30" s="1">
+        <v>1</v>
+      </c>
+      <c r="N30" s="1">
         <v>3</v>
       </c>
-      <c r="N30" s="1">
+      <c r="O30" s="1">
         <v>600</v>
       </c>
-      <c r="O30" s="1">
+      <c r="P30" s="1">
         <v>60</v>
       </c>
-      <c r="P30" s="1">
+      <c r="Q30" s="1">
         <v>20</v>
       </c>
-      <c r="Q30" s="1">
+      <c r="R30" s="1">
         <v>3</v>
       </c>
-      <c r="R30" s="1">
-        <v>0</v>
-      </c>
       <c r="S30" s="1">
+        <v>0</v>
+      </c>
+      <c r="T30" s="1">
         <v>5</v>
       </c>
-      <c r="T30" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="U30" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="V30" s="1">
-        <v>0</v>
+        <v>69</v>
+      </c>
+      <c r="V30" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="W30" s="1">
         <v>0</v>
@@ -4501,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="Z30" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AA30" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AB30" s="1">
         <v>0</v>
@@ -4521,14 +4600,17 @@
       <c r="AF30" s="1">
         <v>0</v>
       </c>
-      <c r="AH30" s="1">
-        <v>50</v>
+      <c r="AG30" s="1">
+        <v>0</v>
       </c>
       <c r="AI30" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ30" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" spans="3:35">
+    <row r="31" s="1" customFormat="1" spans="3:36">
       <c r="C31" s="1">
         <v>3002</v>
       </c>
@@ -4536,10 +4618,10 @@
         <v>3002</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -4551,60 +4633,60 @@
         <v>10</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K31" s="1">
         <v>0</v>
       </c>
       <c r="L31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" s="1">
+        <v>1</v>
+      </c>
+      <c r="N31" s="1">
         <v>3</v>
       </c>
-      <c r="N31" s="1">
+      <c r="O31" s="1">
         <v>500</v>
       </c>
-      <c r="O31" s="1">
+      <c r="P31" s="1">
         <v>60</v>
       </c>
-      <c r="P31" s="1">
-        <f t="shared" ref="P30:P40" si="2">N31*5</f>
+      <c r="Q31" s="1">
+        <f t="shared" ref="Q30:Q40" si="2">O31*5</f>
         <v>2500</v>
       </c>
-      <c r="Q31" s="1">
+      <c r="R31" s="1">
         <v>2</v>
       </c>
-      <c r="R31" s="1">
-        <v>0</v>
-      </c>
       <c r="S31" s="1">
+        <v>0</v>
+      </c>
+      <c r="T31" s="1">
         <v>3</v>
       </c>
-      <c r="T31" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="U31" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="V31" s="1">
-        <v>0</v>
+        <v>82</v>
+      </c>
+      <c r="V31" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="W31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X31" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y31" s="1">
         <v>0</v>
       </c>
       <c r="Z31" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="1">
         <v>120</v>
       </c>
-      <c r="AA31" s="1">
-        <v>0</v>
-      </c>
       <c r="AB31" s="1">
         <v>0</v>
       </c>
@@ -4620,14 +4702,17 @@
       <c r="AF31" s="1">
         <v>0</v>
       </c>
-      <c r="AH31" s="1">
-        <v>50</v>
+      <c r="AG31" s="1">
+        <v>0</v>
       </c>
       <c r="AI31" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ31" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" spans="3:35">
+    <row r="32" s="1" customFormat="1" spans="3:36">
       <c r="C32" s="1">
         <v>3003</v>
       </c>
@@ -4635,10 +4720,10 @@
         <v>3003</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G32" s="1">
         <v>1</v>
@@ -4650,66 +4735,66 @@
         <v>10</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K32" s="1">
+        <v>0</v>
+      </c>
+      <c r="L32" s="1">
         <v>10</v>
       </c>
-      <c r="L32" s="1">
-        <v>1</v>
-      </c>
       <c r="M32" s="1">
+        <v>1</v>
+      </c>
+      <c r="N32" s="1">
         <v>3</v>
       </c>
-      <c r="N32" s="1">
+      <c r="O32" s="1">
         <v>600</v>
       </c>
-      <c r="O32" s="1">
+      <c r="P32" s="1">
         <v>60</v>
       </c>
-      <c r="P32" s="1">
+      <c r="Q32" s="1">
         <f t="shared" si="2"/>
         <v>3000</v>
       </c>
-      <c r="Q32" s="1">
+      <c r="R32" s="1">
         <v>2</v>
       </c>
-      <c r="R32" s="1">
-        <v>0</v>
-      </c>
       <c r="S32" s="1">
+        <v>0</v>
+      </c>
+      <c r="T32" s="1">
         <v>2</v>
       </c>
-      <c r="T32" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="U32" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="V32" s="1">
-        <v>0</v>
+        <v>82</v>
+      </c>
+      <c r="V32" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="W32" s="1">
+        <v>0</v>
+      </c>
+      <c r="X32" s="1">
         <v>5</v>
       </c>
-      <c r="X32" s="1">
-        <v>0</v>
-      </c>
       <c r="Y32" s="1">
         <v>0</v>
       </c>
       <c r="Z32" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="1">
         <v>35</v>
       </c>
-      <c r="AA32" s="1">
-        <v>0</v>
-      </c>
       <c r="AB32" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="1">
         <v>60</v>
       </c>
-      <c r="AC32" s="1">
-        <v>0</v>
-      </c>
       <c r="AD32" s="1">
         <v>0</v>
       </c>
@@ -4719,17 +4804,20 @@
       <c r="AF32" s="1">
         <v>0</v>
       </c>
-      <c r="AG32" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="AH32" s="1">
-        <v>50</v>
+      <c r="AG32" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="AI32" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ32" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" spans="3:35">
+    <row r="33" s="1" customFormat="1" spans="3:36">
       <c r="C33" s="1">
         <v>3004</v>
       </c>
@@ -4737,10 +4825,10 @@
         <v>3004</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G33" s="1">
         <v>2</v>
@@ -4752,60 +4840,60 @@
         <v>100</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K33" s="1">
+        <v>0</v>
+      </c>
+      <c r="L33" s="1">
         <v>15</v>
       </c>
-      <c r="L33" s="1">
-        <v>1</v>
-      </c>
       <c r="M33" s="1">
+        <v>1</v>
+      </c>
+      <c r="N33" s="1">
         <v>3</v>
       </c>
-      <c r="N33" s="1">
+      <c r="O33" s="1">
         <v>600</v>
       </c>
-      <c r="O33" s="1">
+      <c r="P33" s="1">
         <v>60</v>
       </c>
-      <c r="P33" s="1">
+      <c r="Q33" s="1">
         <f t="shared" si="2"/>
         <v>3000</v>
       </c>
-      <c r="Q33" s="1">
+      <c r="R33" s="1">
         <v>2</v>
       </c>
-      <c r="R33" s="1">
-        <v>0</v>
-      </c>
       <c r="S33" s="1">
         <v>0</v>
       </c>
-      <c r="T33" s="1" t="s">
-        <v>68</v>
+      <c r="T33" s="1">
+        <v>0</v>
       </c>
       <c r="U33" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="V33" s="1">
-        <v>0</v>
+        <v>69</v>
+      </c>
+      <c r="V33" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="W33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X33" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y33" s="1">
         <v>0</v>
       </c>
       <c r="Z33" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="1">
         <v>100</v>
       </c>
-      <c r="AA33" s="1">
-        <v>0</v>
-      </c>
       <c r="AB33" s="1">
         <v>0</v>
       </c>
@@ -4821,14 +4909,17 @@
       <c r="AF33" s="1">
         <v>0</v>
       </c>
-      <c r="AH33" s="1">
-        <v>50</v>
+      <c r="AG33" s="1">
+        <v>0</v>
       </c>
       <c r="AI33" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ33" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" spans="3:35">
+    <row r="34" s="1" customFormat="1" spans="3:36">
       <c r="C34" s="1">
         <v>3005</v>
       </c>
@@ -4836,10 +4927,10 @@
         <v>3005</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G34" s="1">
         <v>5</v>
@@ -4851,48 +4942,48 @@
         <v>50</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K34" s="1">
+        <v>0</v>
+      </c>
+      <c r="L34" s="1">
         <v>55</v>
       </c>
-      <c r="L34" s="1">
-        <v>1</v>
-      </c>
       <c r="M34" s="1">
+        <v>1</v>
+      </c>
+      <c r="N34" s="1">
         <v>3</v>
       </c>
-      <c r="N34" s="1">
+      <c r="O34" s="1">
         <v>200</v>
       </c>
-      <c r="O34" s="1">
+      <c r="P34" s="1">
         <v>20</v>
       </c>
-      <c r="P34" s="1">
+      <c r="Q34" s="1">
         <f t="shared" si="2"/>
         <v>1000</v>
       </c>
-      <c r="Q34" s="1">
-        <v>1</v>
-      </c>
       <c r="R34" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" s="1">
         <v>0</v>
       </c>
-      <c r="T34" s="1" t="s">
-        <v>68</v>
+      <c r="T34" s="1">
+        <v>0</v>
       </c>
       <c r="U34" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V34" s="1">
+        <v>69</v>
+      </c>
+      <c r="V34" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="W34" s="1">
         <v>30</v>
       </c>
-      <c r="W34" s="1">
-        <v>0</v>
-      </c>
       <c r="X34" s="1">
         <v>0</v>
       </c>
@@ -4900,11 +4991,11 @@
         <v>0</v>
       </c>
       <c r="Z34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="1">
         <v>100</v>
       </c>
-      <c r="AA34" s="1">
-        <v>0</v>
-      </c>
       <c r="AB34" s="1">
         <v>0</v>
       </c>
@@ -4920,17 +5011,20 @@
       <c r="AF34" s="1">
         <v>0</v>
       </c>
-      <c r="AG34" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="AH34" s="1">
-        <v>50</v>
+      <c r="AG34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="AI34" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ34" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" spans="3:35">
+    <row r="35" s="1" customFormat="1" spans="3:36">
       <c r="C35" s="1">
         <v>3006</v>
       </c>
@@ -4938,10 +5032,10 @@
         <v>3006</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G35" s="1">
         <v>6</v>
@@ -4953,44 +5047,44 @@
         <v>10</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K35" s="1">
         <v>0</v>
       </c>
       <c r="L35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" s="1">
+        <v>1</v>
+      </c>
+      <c r="N35" s="1">
         <v>3</v>
       </c>
-      <c r="N35" s="1">
+      <c r="O35" s="1">
         <v>200</v>
       </c>
-      <c r="O35" s="1">
+      <c r="P35" s="1">
         <v>20</v>
       </c>
-      <c r="P35" s="1">
+      <c r="Q35" s="1">
         <f t="shared" si="2"/>
         <v>1000</v>
       </c>
-      <c r="Q35" s="1">
-        <v>1</v>
-      </c>
       <c r="R35" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" s="1">
+        <v>0</v>
+      </c>
+      <c r="T35" s="1">
         <v>3</v>
       </c>
-      <c r="T35" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="U35" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="V35" s="1">
-        <v>0</v>
+        <v>69</v>
+      </c>
+      <c r="V35" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="W35" s="1">
         <v>0</v>
@@ -5002,10 +5096,10 @@
         <v>0</v>
       </c>
       <c r="Z35" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AA35" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AB35" s="1">
         <v>0</v>
@@ -5022,14 +5116,17 @@
       <c r="AF35" s="1">
         <v>0</v>
       </c>
-      <c r="AH35" s="1">
-        <v>50</v>
+      <c r="AG35" s="1">
+        <v>0</v>
       </c>
       <c r="AI35" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ35" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" spans="3:35">
+    <row r="36" s="1" customFormat="1" spans="3:36">
       <c r="C36" s="1">
         <v>3007</v>
       </c>
@@ -5037,10 +5134,10 @@
         <v>3007</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G36" s="1">
         <v>2</v>
@@ -5052,60 +5149,60 @@
         <v>100</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K36" s="1">
+        <v>0</v>
+      </c>
+      <c r="L36" s="1">
         <v>30</v>
       </c>
-      <c r="L36" s="1">
-        <v>1</v>
-      </c>
       <c r="M36" s="1">
+        <v>1</v>
+      </c>
+      <c r="N36" s="1">
         <v>3</v>
       </c>
-      <c r="N36" s="1">
+      <c r="O36" s="1">
         <v>600</v>
       </c>
-      <c r="O36" s="1">
+      <c r="P36" s="1">
         <v>60</v>
       </c>
-      <c r="P36" s="1">
+      <c r="Q36" s="1">
         <f t="shared" si="2"/>
         <v>3000</v>
       </c>
-      <c r="Q36" s="1">
+      <c r="R36" s="1">
         <v>3</v>
       </c>
-      <c r="R36" s="1">
-        <v>0</v>
-      </c>
       <c r="S36" s="1">
+        <v>0</v>
+      </c>
+      <c r="T36" s="1">
         <v>2</v>
       </c>
-      <c r="T36" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="U36" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V36" s="1">
-        <v>0</v>
+        <v>82</v>
+      </c>
+      <c r="V36" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="W36" s="1">
+        <v>0</v>
+      </c>
+      <c r="X36" s="1">
         <v>2</v>
       </c>
-      <c r="X36" s="1">
-        <v>0</v>
-      </c>
       <c r="Y36" s="1">
         <v>0</v>
       </c>
       <c r="Z36" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="1">
         <v>120</v>
       </c>
-      <c r="AA36" s="1">
-        <v>0</v>
-      </c>
       <c r="AB36" s="1">
         <v>0</v>
       </c>
@@ -5121,14 +5218,17 @@
       <c r="AF36" s="1">
         <v>0</v>
       </c>
-      <c r="AH36" s="1">
-        <v>50</v>
+      <c r="AG36" s="1">
+        <v>0</v>
       </c>
       <c r="AI36" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ36" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" spans="3:35">
+    <row r="37" s="1" customFormat="1" spans="3:36">
       <c r="C37" s="1">
         <v>3008</v>
       </c>
@@ -5136,10 +5236,10 @@
         <v>3008</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G37" s="1">
         <v>3008</v>
@@ -5151,48 +5251,48 @@
         <v>200</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K37" s="1">
+        <v>0</v>
+      </c>
+      <c r="L37" s="1">
         <v>30</v>
       </c>
-      <c r="L37" s="1">
-        <v>1</v>
-      </c>
       <c r="M37" s="1">
+        <v>1</v>
+      </c>
+      <c r="N37" s="1">
         <v>3</v>
       </c>
-      <c r="N37" s="1">
+      <c r="O37" s="1">
         <v>30</v>
       </c>
-      <c r="O37" s="1">
+      <c r="P37" s="1">
         <v>3</v>
       </c>
-      <c r="P37" s="1">
+      <c r="Q37" s="1">
         <f t="shared" si="2"/>
         <v>150</v>
       </c>
-      <c r="Q37" s="1">
-        <v>1</v>
-      </c>
       <c r="R37" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S37" s="1">
         <v>0</v>
       </c>
-      <c r="T37" s="1" t="s">
-        <v>68</v>
+      <c r="T37" s="1">
+        <v>0</v>
       </c>
       <c r="U37" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="V37" s="1">
+        <v>69</v>
+      </c>
+      <c r="V37" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="W37" s="1">
         <v>5</v>
       </c>
-      <c r="W37" s="1">
-        <v>0</v>
-      </c>
       <c r="X37" s="1">
         <v>0</v>
       </c>
@@ -5200,11 +5300,11 @@
         <v>0</v>
       </c>
       <c r="Z37" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="1">
         <v>30</v>
       </c>
-      <c r="AA37" s="1">
-        <v>0</v>
-      </c>
       <c r="AB37" s="1">
         <v>0</v>
       </c>
@@ -5220,17 +5320,20 @@
       <c r="AF37" s="1">
         <v>0</v>
       </c>
-      <c r="AG37" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="AH37" s="1">
-        <v>50</v>
+      <c r="AG37" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH37" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="AI37" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ37" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" spans="3:35">
+    <row r="38" s="1" customFormat="1" spans="3:36">
       <c r="C38" s="1">
         <v>3009</v>
       </c>
@@ -5238,10 +5341,10 @@
         <v>3009</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G38" s="1">
         <v>2</v>
@@ -5253,59 +5356,59 @@
         <v>100</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K38" s="1">
+        <v>0</v>
+      </c>
+      <c r="L38" s="1">
         <v>30</v>
       </c>
-      <c r="L38" s="1">
-        <v>1</v>
-      </c>
       <c r="M38" s="1">
+        <v>1</v>
+      </c>
+      <c r="N38" s="1">
         <v>3</v>
       </c>
-      <c r="N38" s="1">
+      <c r="O38" s="1">
         <v>300</v>
       </c>
-      <c r="O38" s="1">
+      <c r="P38" s="1">
         <v>30</v>
       </c>
-      <c r="P38" s="1">
+      <c r="Q38" s="1">
         <v>200</v>
       </c>
-      <c r="Q38" s="1">
+      <c r="R38" s="1">
         <v>4</v>
       </c>
-      <c r="R38" s="1">
-        <v>0</v>
-      </c>
       <c r="S38" s="1">
+        <v>0</v>
+      </c>
+      <c r="T38" s="1">
         <v>2</v>
       </c>
-      <c r="T38" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="U38" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V38" s="1">
-        <v>0</v>
+        <v>82</v>
+      </c>
+      <c r="V38" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="W38" s="1">
+        <v>0</v>
+      </c>
+      <c r="X38" s="1">
         <v>3</v>
       </c>
-      <c r="X38" s="1">
-        <v>0</v>
-      </c>
       <c r="Y38" s="1">
         <v>0</v>
       </c>
       <c r="Z38" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="1">
         <v>300</v>
       </c>
-      <c r="AA38" s="1">
-        <v>0</v>
-      </c>
       <c r="AB38" s="1">
         <v>0</v>
       </c>
@@ -5321,14 +5424,17 @@
       <c r="AF38" s="1">
         <v>0</v>
       </c>
-      <c r="AH38" s="1">
-        <v>50</v>
+      <c r="AG38" s="1">
+        <v>0</v>
       </c>
       <c r="AI38" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ38" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" spans="3:35">
+    <row r="39" s="1" customFormat="1" spans="3:36">
       <c r="C39" s="1">
         <v>3010</v>
       </c>
@@ -5336,10 +5442,10 @@
         <v>3010</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G39" s="1">
         <v>8</v>
@@ -5351,23 +5457,23 @@
         <v>100</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K39" s="1">
         <v>0</v>
       </c>
       <c r="L39" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" s="1">
+        <v>1</v>
+      </c>
+      <c r="N39" s="1">
         <v>3</v>
       </c>
-      <c r="N39" s="1">
+      <c r="O39" s="1">
         <v>10</v>
       </c>
-      <c r="O39" s="1">
-        <v>1</v>
-      </c>
       <c r="P39" s="1">
         <v>1</v>
       </c>
@@ -5375,38 +5481,38 @@
         <v>1</v>
       </c>
       <c r="R39" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" s="1">
         <v>0</v>
       </c>
-      <c r="T39" s="1" t="s">
-        <v>81</v>
+      <c r="T39" s="1">
+        <v>0</v>
       </c>
       <c r="U39" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V39" s="1">
-        <v>0</v>
+        <v>82</v>
+      </c>
+      <c r="V39" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="W39" s="1">
+        <v>0</v>
+      </c>
+      <c r="X39" s="1">
         <v>3</v>
       </c>
-      <c r="X39" s="1">
-        <v>0</v>
-      </c>
       <c r="Y39" s="1">
         <v>0</v>
       </c>
       <c r="Z39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="1">
         <v>20</v>
       </c>
-      <c r="AA39" s="1">
+      <c r="AB39" s="1">
         <v>400</v>
       </c>
-      <c r="AB39" s="1">
-        <v>0</v>
-      </c>
       <c r="AC39" s="1">
         <v>0</v>
       </c>
@@ -5419,14 +5525,17 @@
       <c r="AF39" s="1">
         <v>0</v>
       </c>
-      <c r="AH39" s="1">
-        <v>50</v>
+      <c r="AG39" s="1">
+        <v>0</v>
       </c>
       <c r="AI39" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ39" s="1">
         <v>4102</v>
       </c>
     </row>
-    <row r="40" s="1" customFormat="1" spans="3:35">
+    <row r="40" s="1" customFormat="1" spans="3:36">
       <c r="C40" s="1">
         <v>3011</v>
       </c>
@@ -5434,10 +5543,10 @@
         <v>3011</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G40" s="1">
         <v>8</v>
@@ -5449,63 +5558,63 @@
         <v>0</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K40" s="1">
+        <v>0</v>
+      </c>
+      <c r="L40" s="1">
         <v>30</v>
       </c>
-      <c r="L40" s="1">
+      <c r="M40" s="1">
         <v>2</v>
       </c>
-      <c r="M40" s="1">
+      <c r="N40" s="1">
         <v>3</v>
       </c>
-      <c r="N40" s="1">
+      <c r="O40" s="1">
         <v>10</v>
       </c>
-      <c r="O40" s="1">
-        <v>1</v>
-      </c>
       <c r="P40" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q40" s="1">
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
-      <c r="Q40" s="1">
-        <v>50</v>
-      </c>
       <c r="R40" s="1">
+        <v>50</v>
+      </c>
+      <c r="S40" s="1">
         <v>10</v>
       </c>
-      <c r="S40" s="1">
+      <c r="T40" s="1">
         <v>3</v>
       </c>
-      <c r="T40" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="U40" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V40" s="1">
+        <v>82</v>
+      </c>
+      <c r="V40" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="W40" s="1">
         <v>15</v>
       </c>
-      <c r="W40" s="1">
+      <c r="X40" s="1">
         <v>5</v>
-      </c>
-      <c r="X40" s="1">
-        <v>4</v>
       </c>
       <c r="Y40" s="1">
         <v>4</v>
       </c>
       <c r="Z40" s="1">
+        <v>4</v>
+      </c>
+      <c r="AA40" s="1">
         <v>500</v>
       </c>
-      <c r="AA40" s="1">
+      <c r="AB40" s="1">
         <v>100</v>
       </c>
-      <c r="AB40" s="1">
-        <v>0</v>
-      </c>
       <c r="AC40" s="1">
         <v>0</v>
       </c>
@@ -5518,10 +5627,13 @@
       <c r="AF40" s="1">
         <v>0</v>
       </c>
-      <c r="AH40" s="1">
-        <v>50</v>
+      <c r="AG40" s="1">
+        <v>0</v>
       </c>
       <c r="AI40" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ40" s="1">
         <v>0</v>
       </c>
     </row>
@@ -5529,7 +5641,7 @@
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
     </row>
-    <row r="42" s="1" customFormat="1" spans="3:34">
+    <row r="42" s="1" customFormat="1" spans="3:35">
       <c r="C42" s="1">
         <v>4001</v>
       </c>
@@ -5537,10 +5649,10 @@
         <v>4001</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G42" s="1">
         <v>4001</v>
@@ -5552,14 +5664,14 @@
         <v>-100</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K42" s="1">
+        <v>0</v>
+      </c>
+      <c r="L42" s="1">
         <v>30</v>
       </c>
-      <c r="L42" s="1">
-        <v>0</v>
-      </c>
       <c r="M42" s="1">
         <v>0</v>
       </c>
@@ -5569,7 +5681,7 @@
       <c r="O42" s="1">
         <v>0</v>
       </c>
-      <c r="Q42" s="1">
+      <c r="P42" s="1">
         <v>0</v>
       </c>
       <c r="R42" s="1">
@@ -5578,18 +5690,18 @@
       <c r="S42" s="1">
         <v>0</v>
       </c>
-      <c r="T42" s="1" t="s">
-        <v>68</v>
+      <c r="T42" s="1">
+        <v>0</v>
       </c>
       <c r="U42" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V42" s="1">
+        <v>69</v>
+      </c>
+      <c r="V42" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="W42" s="1">
         <v>2</v>
       </c>
-      <c r="W42" s="1">
-        <v>0</v>
-      </c>
       <c r="X42" s="1">
         <v>0</v>
       </c>
@@ -5617,14 +5729,17 @@
       <c r="AF42" s="1">
         <v>0</v>
       </c>
-      <c r="AG42" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="AH42" s="1">
+      <c r="AG42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="AI42" s="1">
         <v>99999</v>
       </c>
     </row>
-    <row r="43" s="1" customFormat="1" spans="3:34">
+    <row r="43" s="1" customFormat="1" spans="3:35">
       <c r="C43" s="1">
         <v>4002</v>
       </c>
@@ -5632,10 +5747,10 @@
         <v>4002</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G43" s="1">
         <v>4002</v>
@@ -5647,14 +5762,14 @@
         <v>200</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K43" s="1">
+        <v>0</v>
+      </c>
+      <c r="L43" s="1">
         <v>60</v>
       </c>
-      <c r="L43" s="1">
-        <v>0</v>
-      </c>
       <c r="M43" s="1">
         <v>0</v>
       </c>
@@ -5664,23 +5779,23 @@
       <c r="O43" s="1">
         <v>0</v>
       </c>
-      <c r="Q43" s="1">
+      <c r="P43" s="1">
+        <v>0</v>
+      </c>
+      <c r="R43" s="1">
         <v>10</v>
       </c>
-      <c r="R43" s="1">
-        <v>0</v>
-      </c>
       <c r="S43" s="1">
         <v>0</v>
       </c>
-      <c r="T43" s="1" t="s">
-        <v>68</v>
+      <c r="T43" s="1">
+        <v>0</v>
       </c>
       <c r="U43" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V43" s="1">
-        <v>0</v>
+        <v>69</v>
+      </c>
+      <c r="V43" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="W43" s="1">
         <v>0</v>
@@ -5692,11 +5807,11 @@
         <v>0</v>
       </c>
       <c r="Z43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="1">
         <v>100</v>
       </c>
-      <c r="AA43" s="1">
-        <v>0</v>
-      </c>
       <c r="AB43" s="1">
         <v>0</v>
       </c>
@@ -5712,12 +5827,15 @@
       <c r="AF43" s="1">
         <v>0</v>
       </c>
-      <c r="AG43" s="7"/>
-      <c r="AH43" s="1">
+      <c r="AG43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="7"/>
+      <c r="AI43" s="1">
         <v>99999</v>
       </c>
     </row>
-    <row r="44" s="1" customFormat="1" spans="3:34">
+    <row r="44" s="1" customFormat="1" spans="3:35">
       <c r="C44" s="1">
         <v>4003</v>
       </c>
@@ -5725,10 +5843,10 @@
         <v>4003</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G44" s="1">
         <v>4003</v>
@@ -5740,14 +5858,14 @@
         <v>-1</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K44" s="1">
+        <v>0</v>
+      </c>
+      <c r="L44" s="1">
         <v>60</v>
       </c>
-      <c r="L44" s="1">
-        <v>0</v>
-      </c>
       <c r="M44" s="1">
         <v>0</v>
       </c>
@@ -5757,7 +5875,7 @@
       <c r="O44" s="1">
         <v>0</v>
       </c>
-      <c r="Q44" s="1">
+      <c r="P44" s="1">
         <v>0</v>
       </c>
       <c r="R44" s="1">
@@ -5766,14 +5884,14 @@
       <c r="S44" s="1">
         <v>0</v>
       </c>
-      <c r="T44" s="1" t="s">
-        <v>68</v>
+      <c r="T44" s="1">
+        <v>0</v>
       </c>
       <c r="U44" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V44" s="1">
-        <v>0</v>
+        <v>69</v>
+      </c>
+      <c r="V44" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="W44" s="1">
         <v>0</v>
@@ -5785,11 +5903,11 @@
         <v>0</v>
       </c>
       <c r="Z44" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="1">
         <v>100</v>
       </c>
-      <c r="AA44" s="1">
-        <v>0</v>
-      </c>
       <c r="AB44" s="1">
         <v>0</v>
       </c>
@@ -5805,10 +5923,13 @@
       <c r="AF44" s="1">
         <v>0</v>
       </c>
-      <c r="AG44" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="AH44" s="1">
+      <c r="AG44" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="AI44" s="1">
         <v>99999</v>
       </c>
     </row>
@@ -5816,7 +5937,7 @@
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
     </row>
-    <row r="46" s="1" customFormat="1" spans="3:35">
+    <row r="46" s="1" customFormat="1" spans="3:36">
       <c r="C46" s="1">
         <v>9001</v>
       </c>
@@ -5824,10 +5945,10 @@
         <v>9001</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G46" s="1">
         <v>9</v>
@@ -5842,47 +5963,47 @@
         <v>0</v>
       </c>
       <c r="L46" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" s="1">
         <v>1</v>
       </c>
       <c r="N46" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O46" s="1">
         <v>0</v>
       </c>
-      <c r="Q46" s="1">
-        <v>0</v>
-      </c>
-      <c r="S46" s="1">
-        <v>1</v>
-      </c>
-      <c r="T46" s="1" t="s">
-        <v>68</v>
+      <c r="P46" s="1">
+        <v>0</v>
+      </c>
+      <c r="R46" s="1">
+        <v>0</v>
+      </c>
+      <c r="T46" s="1">
+        <v>1</v>
       </c>
       <c r="U46" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="V46" s="1">
-        <v>0</v>
+        <v>69</v>
+      </c>
+      <c r="V46" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="W46" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X46" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y46" s="1">
         <v>0</v>
       </c>
       <c r="Z46" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="1">
         <v>100</v>
       </c>
-      <c r="AA46" s="1">
-        <v>0</v>
-      </c>
       <c r="AB46" s="1">
         <v>0</v>
       </c>
@@ -5898,14 +6019,17 @@
       <c r="AF46" s="1">
         <v>0</v>
       </c>
-      <c r="AH46" s="1">
-        <v>50</v>
+      <c r="AG46" s="1">
+        <v>0</v>
       </c>
       <c r="AI46" s="1">
         <v>50</v>
       </c>
+      <c r="AJ46" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="47" s="1" customFormat="1" spans="3:35">
+    <row r="47" s="1" customFormat="1" spans="3:36">
       <c r="C47" s="1">
         <v>9002</v>
       </c>
@@ -5913,10 +6037,10 @@
         <v>9002</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G47" s="1">
         <v>9</v>
@@ -5931,47 +6055,47 @@
         <v>0</v>
       </c>
       <c r="L47" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" s="1">
         <v>1</v>
       </c>
       <c r="N47" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O47" s="1">
         <v>0</v>
       </c>
-      <c r="Q47" s="1">
-        <v>0</v>
-      </c>
-      <c r="S47" s="1">
+      <c r="P47" s="1">
+        <v>0</v>
+      </c>
+      <c r="R47" s="1">
+        <v>0</v>
+      </c>
+      <c r="T47" s="1">
         <v>2</v>
-      </c>
-      <c r="T47" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="U47" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="V47" s="1">
-        <v>0</v>
+      <c r="V47" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="W47" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X47" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y47" s="1">
         <v>0</v>
       </c>
       <c r="Z47" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="1">
         <v>100</v>
       </c>
-      <c r="AA47" s="1">
-        <v>0</v>
-      </c>
       <c r="AB47" s="1">
         <v>0</v>
       </c>
@@ -5987,15 +6111,18 @@
       <c r="AF47" s="1">
         <v>0</v>
       </c>
-      <c r="AH47" s="1">
-        <v>50</v>
+      <c r="AG47" s="1">
+        <v>0</v>
       </c>
       <c r="AI47" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ47" s="1">
         <v>50</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1"/>
-    <row r="49" s="1" customFormat="1" spans="3:35">
+    <row r="49" s="1" customFormat="1" spans="3:36">
       <c r="C49" s="1">
         <v>10001</v>
       </c>
@@ -6003,68 +6130,68 @@
         <v>10001</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F49" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="G49" s="1">
+        <v>1</v>
+      </c>
+      <c r="H49" s="1">
+        <v>0</v>
+      </c>
+      <c r="I49" s="1">
+        <v>1</v>
+      </c>
+      <c r="J49" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="G49" s="1">
-        <v>1</v>
-      </c>
-      <c r="H49" s="1">
-        <v>0</v>
-      </c>
-      <c r="I49" s="1">
-        <v>1</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>183</v>
-      </c>
       <c r="K49" s="1">
         <v>0</v>
       </c>
       <c r="L49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" s="1">
         <v>1</v>
       </c>
       <c r="N49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O49" s="1">
         <v>0</v>
       </c>
-      <c r="Q49" s="1">
-        <v>0</v>
-      </c>
-      <c r="S49" s="1">
+      <c r="P49" s="1">
+        <v>0</v>
+      </c>
+      <c r="R49" s="1">
+        <v>0</v>
+      </c>
+      <c r="T49" s="1">
         <v>3</v>
       </c>
-      <c r="T49" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="U49" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="V49" s="1">
-        <v>0</v>
+        <v>82</v>
+      </c>
+      <c r="V49" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="W49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y49" s="1">
         <v>0</v>
       </c>
       <c r="Z49" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="1">
         <v>150</v>
       </c>
-      <c r="AA49" s="1">
-        <v>0</v>
-      </c>
       <c r="AB49" s="1">
         <v>0</v>
       </c>
@@ -6080,14 +6207,17 @@
       <c r="AF49" s="1">
         <v>0</v>
       </c>
-      <c r="AH49" s="1">
-        <v>50</v>
+      <c r="AG49" s="1">
+        <v>0</v>
       </c>
       <c r="AI49" s="1">
         <v>50</v>
       </c>
+      <c r="AJ49" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="50" spans="3:35">
+    <row r="50" spans="3:36">
       <c r="C50" s="2">
         <v>10002</v>
       </c>
@@ -6095,10 +6225,10 @@
         <v>10002</v>
       </c>
       <c r="E50" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F50" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="G50" s="2">
         <v>4</v>
@@ -6110,55 +6240,55 @@
         <v>10</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="K50" s="2">
-        <v>0</v>
-      </c>
-      <c r="L50" s="1">
-        <v>1</v>
+        <v>187</v>
+      </c>
+      <c r="K50" s="1">
+        <v>0</v>
+      </c>
+      <c r="L50" s="2">
+        <v>0</v>
       </c>
       <c r="M50" s="1">
         <v>1</v>
       </c>
       <c r="N50" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O50" s="1">
         <v>0</v>
       </c>
-      <c r="P50" s="1"/>
-      <c r="Q50" s="1">
-        <v>0</v>
-      </c>
-      <c r="R50" s="1"/>
-      <c r="S50" s="2">
-        <v>0</v>
-      </c>
-      <c r="T50" s="1" t="s">
-        <v>68</v>
+      <c r="P50" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="1"/>
+      <c r="R50" s="1">
+        <v>0</v>
+      </c>
+      <c r="S50" s="1"/>
+      <c r="T50" s="2">
+        <v>0</v>
       </c>
       <c r="U50" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="V50" s="2">
-        <v>0</v>
+      <c r="V50" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="W50" s="2">
-        <v>1</v>
-      </c>
-      <c r="X50" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="X50" s="2">
+        <v>1</v>
       </c>
       <c r="Y50" s="1">
         <v>0</v>
       </c>
-      <c r="Z50" s="2">
+      <c r="Z50" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="2">
         <v>100</v>
       </c>
-      <c r="AA50" s="1">
-        <v>0</v>
-      </c>
       <c r="AB50" s="1">
         <v>0</v>
       </c>
@@ -6174,15 +6304,18 @@
       <c r="AF50" s="1">
         <v>0</v>
       </c>
-      <c r="AG50" s="1"/>
-      <c r="AH50" s="1">
-        <v>50</v>
-      </c>
+      <c r="AG50" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="1"/>
       <c r="AI50" s="1">
         <v>50</v>
       </c>
+      <c r="AJ50" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="51" spans="3:35">
+    <row r="51" spans="3:36">
       <c r="C51" s="2">
         <v>10003</v>
       </c>
@@ -6190,10 +6323,10 @@
         <v>10003</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -6205,55 +6338,55 @@
         <v>1</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="K51" s="2">
-        <v>0</v>
-      </c>
-      <c r="L51" s="1">
-        <v>1</v>
+        <v>188</v>
+      </c>
+      <c r="K51" s="1">
+        <v>0</v>
+      </c>
+      <c r="L51" s="2">
+        <v>0</v>
       </c>
       <c r="M51" s="1">
         <v>1</v>
       </c>
       <c r="N51" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O51" s="1">
         <v>0</v>
       </c>
-      <c r="P51" s="1"/>
-      <c r="Q51" s="1">
-        <v>0</v>
-      </c>
-      <c r="R51" s="1"/>
-      <c r="S51" s="1">
-        <v>0</v>
-      </c>
-      <c r="T51" s="1" t="s">
-        <v>81</v>
+      <c r="P51" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="1"/>
+      <c r="R51" s="1">
+        <v>0</v>
+      </c>
+      <c r="S51" s="1"/>
+      <c r="T51" s="1">
+        <v>0</v>
       </c>
       <c r="U51" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="V51" s="1">
-        <v>0</v>
+        <v>82</v>
+      </c>
+      <c r="V51" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="W51" s="1">
+        <v>0</v>
+      </c>
+      <c r="X51" s="1">
         <v>10</v>
       </c>
-      <c r="X51" s="1">
-        <v>0</v>
-      </c>
       <c r="Y51" s="1">
         <v>0</v>
       </c>
       <c r="Z51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="1">
         <v>100</v>
       </c>
-      <c r="AA51" s="1">
-        <v>0</v>
-      </c>
       <c r="AB51" s="1">
         <v>0</v>
       </c>
@@ -6269,15 +6402,18 @@
       <c r="AF51" s="1">
         <v>0</v>
       </c>
-      <c r="AG51" s="1"/>
-      <c r="AH51" s="1">
-        <v>50</v>
-      </c>
+      <c r="AG51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="1"/>
       <c r="AI51" s="1">
         <v>50</v>
       </c>
+      <c r="AJ51" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="52" spans="3:35">
+    <row r="52" spans="3:36">
       <c r="C52" s="2">
         <v>10004</v>
       </c>
@@ -6285,10 +6421,10 @@
         <v>10004</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G52" s="2">
         <v>4</v>
@@ -6300,59 +6436,59 @@
         <v>10</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="K52" s="2">
-        <v>0</v>
-      </c>
-      <c r="L52" s="1">
-        <v>1</v>
-      </c>
-      <c r="M52" s="2">
+        <v>189</v>
+      </c>
+      <c r="K52" s="1">
+        <v>0</v>
+      </c>
+      <c r="L52" s="2">
+        <v>0</v>
+      </c>
+      <c r="M52" s="1">
         <v>1</v>
       </c>
       <c r="N52" s="2">
-        <v>0</v>
-      </c>
-      <c r="O52" s="1">
-        <v>0</v>
-      </c>
-      <c r="P52" s="1"/>
-      <c r="Q52" s="1">
-        <v>0</v>
-      </c>
-      <c r="R52" s="1"/>
-      <c r="S52" s="2">
+        <v>1</v>
+      </c>
+      <c r="O52" s="2">
+        <v>0</v>
+      </c>
+      <c r="P52" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="1"/>
+      <c r="R52" s="1">
+        <v>0</v>
+      </c>
+      <c r="S52" s="1"/>
+      <c r="T52" s="2">
         <v>3</v>
       </c>
-      <c r="T52" s="2" t="s">
-        <v>189</v>
-      </c>
       <c r="U52" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="V52" s="2">
-        <v>0</v>
+        <v>190</v>
+      </c>
+      <c r="V52" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="W52" s="2">
+        <v>0</v>
+      </c>
+      <c r="X52" s="2">
         <v>4</v>
       </c>
-      <c r="X52" s="1">
-        <v>0</v>
-      </c>
       <c r="Y52" s="1">
         <v>0</v>
       </c>
-      <c r="Z52" s="2">
-        <v>50</v>
+      <c r="Z52" s="1">
+        <v>0</v>
       </c>
       <c r="AA52" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB52" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC52" s="2">
+        <v>50</v>
+      </c>
+      <c r="AB52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="1">
         <v>0</v>
       </c>
       <c r="AD52" s="2">
@@ -6361,17 +6497,20 @@
       <c r="AE52" s="2">
         <v>0</v>
       </c>
-      <c r="AF52" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH52" s="1">
-        <v>50</v>
+      <c r="AF52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="1">
+        <v>0</v>
       </c>
       <c r="AI52" s="1">
         <v>50</v>
       </c>
+      <c r="AJ52" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="53" s="1" customFormat="1" spans="3:35">
+    <row r="53" s="1" customFormat="1" spans="3:36">
       <c r="C53" s="1">
         <v>10005</v>
       </c>
@@ -6379,10 +6518,10 @@
         <v>10005</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G53" s="1">
         <v>1</v>
@@ -6394,59 +6533,59 @@
         <v>10</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K53" s="1">
         <v>0</v>
       </c>
       <c r="L53" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" s="1">
         <v>1</v>
       </c>
-      <c r="N53" s="2">
-        <v>0</v>
-      </c>
-      <c r="O53" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="1">
-        <v>0</v>
-      </c>
-      <c r="S53" s="1">
+      <c r="N53" s="1">
+        <v>1</v>
+      </c>
+      <c r="O53" s="2">
+        <v>0</v>
+      </c>
+      <c r="P53" s="1">
+        <v>0</v>
+      </c>
+      <c r="R53" s="1">
+        <v>0</v>
+      </c>
+      <c r="T53" s="1">
         <v>2</v>
-      </c>
-      <c r="T53" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="U53" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="V53" s="1">
-        <v>0</v>
+      <c r="V53" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="W53" s="1">
+        <v>0</v>
+      </c>
+      <c r="X53" s="1">
         <v>2</v>
       </c>
-      <c r="X53" s="1">
-        <v>0</v>
-      </c>
       <c r="Y53" s="1">
         <v>0</v>
       </c>
       <c r="Z53" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="1">
         <v>150</v>
       </c>
-      <c r="AA53" s="1">
-        <v>0</v>
-      </c>
       <c r="AB53" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="1">
         <v>20</v>
       </c>
-      <c r="AC53" s="1">
-        <v>0</v>
-      </c>
       <c r="AD53" s="1">
         <v>0</v>
       </c>
@@ -6456,14 +6595,17 @@
       <c r="AF53" s="1">
         <v>0</v>
       </c>
-      <c r="AH53" s="1">
-        <v>50</v>
+      <c r="AG53" s="1">
+        <v>0</v>
       </c>
       <c r="AI53" s="1">
         <v>50</v>
       </c>
+      <c r="AJ53" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="55" s="1" customFormat="1" spans="3:35">
+    <row r="55" s="1" customFormat="1" spans="3:36">
       <c r="C55" s="1">
         <v>11001</v>
       </c>
@@ -6471,10 +6613,10 @@
         <v>1001</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G55" s="1">
         <v>1</v>
@@ -6489,47 +6631,47 @@
         <v>0</v>
       </c>
       <c r="L55" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" s="1">
         <v>1</v>
       </c>
       <c r="N55" s="1">
+        <v>1</v>
+      </c>
+      <c r="O55" s="1">
         <v>9999</v>
       </c>
-      <c r="O55" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="1">
-        <v>0</v>
-      </c>
-      <c r="S55" s="1">
-        <v>1</v>
-      </c>
-      <c r="T55" s="1" t="s">
-        <v>68</v>
+      <c r="P55" s="1">
+        <v>0</v>
+      </c>
+      <c r="R55" s="1">
+        <v>0</v>
+      </c>
+      <c r="T55" s="1">
+        <v>1</v>
       </c>
       <c r="U55" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="V55" s="1">
-        <v>0</v>
+      <c r="V55" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="W55" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X55" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y55" s="1">
         <v>0</v>
       </c>
       <c r="Z55" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="1">
         <v>120</v>
       </c>
-      <c r="AA55" s="1">
-        <v>0</v>
-      </c>
       <c r="AB55" s="1">
         <v>0</v>
       </c>
@@ -6545,14 +6687,17 @@
       <c r="AF55" s="1">
         <v>0</v>
       </c>
-      <c r="AH55" s="1">
-        <v>50</v>
+      <c r="AG55" s="1">
+        <v>0</v>
       </c>
       <c r="AI55" s="1">
         <v>50</v>
       </c>
+      <c r="AJ55" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="56" s="1" customFormat="1" spans="3:35">
+    <row r="56" s="1" customFormat="1" spans="3:36">
       <c r="C56" s="1">
         <v>11002</v>
       </c>
@@ -6560,10 +6705,10 @@
         <v>1002</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
@@ -6578,53 +6723,53 @@
         <v>0</v>
       </c>
       <c r="L56" s="1">
+        <v>0</v>
+      </c>
+      <c r="M56" s="1">
         <v>2</v>
       </c>
-      <c r="M56" s="1">
-        <v>1</v>
-      </c>
       <c r="N56" s="1">
+        <v>1</v>
+      </c>
+      <c r="O56" s="1">
         <v>9999</v>
       </c>
-      <c r="O56" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="1">
-        <v>0</v>
-      </c>
-      <c r="S56" s="1">
+      <c r="P56" s="1">
+        <v>0</v>
+      </c>
+      <c r="R56" s="1">
+        <v>0</v>
+      </c>
+      <c r="T56" s="1">
         <v>2</v>
-      </c>
-      <c r="T56" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="U56" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="V56" s="1">
-        <v>0</v>
+      <c r="V56" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="W56" s="1">
+        <v>0</v>
+      </c>
+      <c r="X56" s="1">
         <v>2</v>
       </c>
-      <c r="X56" s="1">
-        <v>0</v>
-      </c>
       <c r="Y56" s="1">
         <v>0</v>
       </c>
       <c r="Z56" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA56" s="1">
         <v>150</v>
       </c>
-      <c r="AA56" s="1">
-        <v>0</v>
-      </c>
       <c r="AB56" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC56" s="1">
         <v>20</v>
       </c>
-      <c r="AC56" s="1">
-        <v>0</v>
-      </c>
       <c r="AD56" s="1">
         <v>0</v>
       </c>
@@ -6634,14 +6779,17 @@
       <c r="AF56" s="1">
         <v>0</v>
       </c>
-      <c r="AH56" s="1">
-        <v>50</v>
+      <c r="AG56" s="1">
+        <v>0</v>
       </c>
       <c r="AI56" s="1">
         <v>50</v>
       </c>
+      <c r="AJ56" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="57" s="1" customFormat="1" spans="3:35">
+    <row r="57" s="1" customFormat="1" spans="3:36">
       <c r="C57" s="1">
         <v>11003</v>
       </c>
@@ -6649,10 +6797,10 @@
         <v>1003</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G57" s="1">
         <v>1</v>
@@ -6667,47 +6815,47 @@
         <v>0</v>
       </c>
       <c r="L57" s="1">
+        <v>0</v>
+      </c>
+      <c r="M57" s="1">
         <v>2</v>
       </c>
-      <c r="M57" s="1">
-        <v>1</v>
-      </c>
       <c r="N57" s="1">
+        <v>1</v>
+      </c>
+      <c r="O57" s="1">
         <v>9999</v>
       </c>
-      <c r="O57" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="1">
-        <v>0</v>
-      </c>
-      <c r="S57" s="1">
-        <v>1</v>
-      </c>
-      <c r="T57" s="1" t="s">
-        <v>68</v>
+      <c r="P57" s="1">
+        <v>0</v>
+      </c>
+      <c r="R57" s="1">
+        <v>0</v>
+      </c>
+      <c r="T57" s="1">
+        <v>1</v>
       </c>
       <c r="U57" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="V57" s="1">
-        <v>0</v>
+        <v>69</v>
+      </c>
+      <c r="V57" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="W57" s="1">
+        <v>0</v>
+      </c>
+      <c r="X57" s="1">
         <v>5</v>
       </c>
-      <c r="X57" s="1">
-        <v>0</v>
-      </c>
       <c r="Y57" s="1">
         <v>0</v>
       </c>
       <c r="Z57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="1">
         <v>100</v>
       </c>
-      <c r="AA57" s="1">
-        <v>0</v>
-      </c>
       <c r="AB57" s="1">
         <v>0</v>
       </c>
@@ -6723,14 +6871,17 @@
       <c r="AF57" s="1">
         <v>0</v>
       </c>
-      <c r="AH57" s="1">
-        <v>50</v>
+      <c r="AG57" s="1">
+        <v>0</v>
       </c>
       <c r="AI57" s="1">
         <v>50</v>
       </c>
+      <c r="AJ57" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="58" s="1" customFormat="1" spans="3:35">
+    <row r="58" s="1" customFormat="1" spans="3:36">
       <c r="C58" s="1">
         <v>11004</v>
       </c>
@@ -6738,10 +6889,10 @@
         <v>1004</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G58" s="1">
         <v>7</v>
@@ -6753,50 +6904,50 @@
         <v>10</v>
       </c>
       <c r="K58" s="1">
+        <v>0</v>
+      </c>
+      <c r="L58" s="1">
         <v>5</v>
       </c>
-      <c r="L58" s="1">
-        <v>1</v>
-      </c>
       <c r="M58" s="1">
         <v>1</v>
       </c>
       <c r="N58" s="1">
+        <v>1</v>
+      </c>
+      <c r="O58" s="1">
         <v>9999</v>
       </c>
-      <c r="O58" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="1">
-        <v>0</v>
-      </c>
-      <c r="S58" s="1">
+      <c r="P58" s="1">
+        <v>0</v>
+      </c>
+      <c r="R58" s="1">
+        <v>0</v>
+      </c>
+      <c r="T58" s="1">
         <v>4</v>
-      </c>
-      <c r="T58" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="U58" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="V58" s="1">
+      <c r="V58" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="W58" s="1">
         <v>2</v>
       </c>
-      <c r="W58" s="1">
-        <v>1</v>
-      </c>
       <c r="X58" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y58" s="1">
         <v>0</v>
       </c>
       <c r="Z58" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="1">
         <v>200</v>
       </c>
-      <c r="AA58" s="1">
-        <v>0</v>
-      </c>
       <c r="AB58" s="1">
         <v>0</v>
       </c>
@@ -6812,17 +6963,20 @@
       <c r="AF58" s="1">
         <v>0</v>
       </c>
-      <c r="AG58" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="AH58" s="1">
-        <v>50</v>
+      <c r="AG58" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="1" t="s">
+        <v>192</v>
       </c>
       <c r="AI58" s="1">
         <v>50</v>
       </c>
+      <c r="AJ58" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="59" s="1" customFormat="1" spans="3:35">
+    <row r="59" s="1" customFormat="1" spans="3:36">
       <c r="C59" s="1">
         <v>11005</v>
       </c>
@@ -6830,10 +6984,10 @@
         <v>1005</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G59" s="1">
         <v>5</v>
@@ -6845,38 +6999,38 @@
         <v>50</v>
       </c>
       <c r="K59" s="1">
+        <v>0</v>
+      </c>
+      <c r="L59" s="1">
         <v>30</v>
       </c>
-      <c r="L59" s="1">
-        <v>1</v>
-      </c>
       <c r="M59" s="1">
         <v>1</v>
       </c>
       <c r="N59" s="1">
+        <v>1</v>
+      </c>
+      <c r="O59" s="1">
         <v>9999</v>
       </c>
-      <c r="O59" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="1">
-        <v>0</v>
-      </c>
-      <c r="S59" s="1">
-        <v>0</v>
-      </c>
-      <c r="T59" s="1" t="s">
-        <v>68</v>
+      <c r="P59" s="1">
+        <v>0</v>
+      </c>
+      <c r="R59" s="1">
+        <v>0</v>
+      </c>
+      <c r="T59" s="1">
+        <v>0</v>
       </c>
       <c r="U59" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V59" s="1">
+        <v>69</v>
+      </c>
+      <c r="V59" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="W59" s="1">
         <v>30</v>
       </c>
-      <c r="W59" s="1">
-        <v>0</v>
-      </c>
       <c r="X59" s="1">
         <v>0</v>
       </c>
@@ -6884,11 +7038,11 @@
         <v>0</v>
       </c>
       <c r="Z59" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="1">
         <v>20</v>
       </c>
-      <c r="AA59" s="1">
-        <v>0</v>
-      </c>
       <c r="AB59" s="1">
         <v>0</v>
       </c>
@@ -6904,15 +7058,18 @@
       <c r="AF59" s="1">
         <v>0</v>
       </c>
-      <c r="AG59" s="7"/>
-      <c r="AH59" s="1">
-        <v>50</v>
-      </c>
+      <c r="AG59" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH59" s="7"/>
       <c r="AI59" s="1">
         <v>50</v>
       </c>
+      <c r="AJ59" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="60" s="1" customFormat="1" spans="3:35">
+    <row r="60" s="1" customFormat="1" spans="3:36">
       <c r="C60" s="1">
         <v>11006</v>
       </c>
@@ -6920,10 +7077,10 @@
         <v>1006</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G60" s="1">
         <v>6</v>
@@ -6938,31 +7095,31 @@
         <v>0</v>
       </c>
       <c r="L60" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" s="1">
         <v>1</v>
       </c>
       <c r="N60" s="1">
+        <v>1</v>
+      </c>
+      <c r="O60" s="1">
         <v>9999</v>
       </c>
-      <c r="O60" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="1">
-        <v>0</v>
-      </c>
-      <c r="S60" s="1">
-        <v>0</v>
-      </c>
-      <c r="T60" s="1" t="s">
-        <v>68</v>
+      <c r="P60" s="1">
+        <v>0</v>
+      </c>
+      <c r="R60" s="1">
+        <v>0</v>
+      </c>
+      <c r="T60" s="1">
+        <v>0</v>
       </c>
       <c r="U60" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="V60" s="1">
-        <v>0</v>
+        <v>69</v>
+      </c>
+      <c r="V60" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="W60" s="1">
         <v>0</v>
@@ -6974,10 +7131,10 @@
         <v>0</v>
       </c>
       <c r="Z60" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AA60" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AB60" s="1">
         <v>0</v>
@@ -6994,14 +7151,17 @@
       <c r="AF60" s="1">
         <v>0</v>
       </c>
-      <c r="AH60" s="1">
-        <v>50</v>
+      <c r="AG60" s="1">
+        <v>0</v>
       </c>
       <c r="AI60" s="1">
         <v>50</v>
       </c>
+      <c r="AJ60" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="61" s="1" customFormat="1" spans="3:35">
+    <row r="61" s="1" customFormat="1" spans="3:36">
       <c r="C61" s="1">
         <v>11007</v>
       </c>
@@ -7009,10 +7169,10 @@
         <v>1007</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G61" s="1">
         <v>1</v>
@@ -7027,47 +7187,47 @@
         <v>0</v>
       </c>
       <c r="L61" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" s="1">
         <v>1</v>
       </c>
       <c r="N61" s="1">
+        <v>1</v>
+      </c>
+      <c r="O61" s="1">
         <v>9999</v>
       </c>
-      <c r="O61" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="1">
-        <v>0</v>
-      </c>
-      <c r="S61" s="1">
-        <v>1</v>
-      </c>
-      <c r="T61" s="1" t="s">
-        <v>68</v>
+      <c r="P61" s="1">
+        <v>0</v>
+      </c>
+      <c r="R61" s="1">
+        <v>0</v>
+      </c>
+      <c r="T61" s="1">
+        <v>1</v>
       </c>
       <c r="U61" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="V61" s="1">
-        <v>0</v>
+      <c r="V61" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="W61" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X61" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y61" s="1">
         <v>0</v>
       </c>
       <c r="Z61" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="1">
         <v>300</v>
       </c>
-      <c r="AA61" s="1">
-        <v>0</v>
-      </c>
       <c r="AB61" s="1">
         <v>0</v>
       </c>
@@ -7083,14 +7243,17 @@
       <c r="AF61" s="1">
         <v>0</v>
       </c>
-      <c r="AH61" s="1">
-        <v>50</v>
+      <c r="AG61" s="1">
+        <v>0</v>
       </c>
       <c r="AI61" s="1">
         <v>50</v>
       </c>
+      <c r="AJ61" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="62" s="1" customFormat="1" spans="3:35">
+    <row r="62" s="1" customFormat="1" spans="3:36">
       <c r="C62" s="1">
         <v>12001</v>
       </c>
@@ -7098,10 +7261,10 @@
         <v>2001</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G62" s="1">
         <v>1</v>
@@ -7116,47 +7279,47 @@
         <v>0</v>
       </c>
       <c r="L62" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="1">
+        <v>1</v>
+      </c>
+      <c r="N62" s="1">
         <v>2</v>
       </c>
-      <c r="N62" s="1">
+      <c r="O62" s="1">
         <v>9999</v>
       </c>
-      <c r="O62" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="1">
-        <v>0</v>
-      </c>
-      <c r="S62" s="1">
+      <c r="P62" s="1">
+        <v>0</v>
+      </c>
+      <c r="R62" s="1">
+        <v>0</v>
+      </c>
+      <c r="T62" s="1">
         <v>2</v>
       </c>
-      <c r="T62" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="U62" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="V62" s="1">
-        <v>0</v>
+        <v>82</v>
+      </c>
+      <c r="V62" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="W62" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X62" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y62" s="1">
         <v>0</v>
       </c>
       <c r="Z62" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="1">
         <v>120</v>
       </c>
-      <c r="AA62" s="1">
-        <v>0</v>
-      </c>
       <c r="AB62" s="1">
         <v>0</v>
       </c>
@@ -7172,14 +7335,17 @@
       <c r="AF62" s="1">
         <v>0</v>
       </c>
-      <c r="AH62" s="1">
-        <v>50</v>
+      <c r="AG62" s="1">
+        <v>0</v>
       </c>
       <c r="AI62" s="1">
         <v>50</v>
       </c>
+      <c r="AJ62" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="63" s="1" customFormat="1" spans="3:35">
+    <row r="63" s="1" customFormat="1" spans="3:36">
       <c r="C63" s="1">
         <v>12002</v>
       </c>
@@ -7187,10 +7353,10 @@
         <v>2002</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G63" s="1">
         <v>1</v>
@@ -7205,47 +7371,47 @@
         <v>0</v>
       </c>
       <c r="L63" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" s="1">
+        <v>1</v>
+      </c>
+      <c r="N63" s="1">
         <v>2</v>
       </c>
-      <c r="N63" s="1">
+      <c r="O63" s="1">
         <v>9999</v>
       </c>
-      <c r="O63" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q63" s="1">
-        <v>0</v>
-      </c>
-      <c r="S63" s="1">
+      <c r="P63" s="1">
+        <v>0</v>
+      </c>
+      <c r="R63" s="1">
+        <v>0</v>
+      </c>
+      <c r="T63" s="1">
         <v>3</v>
       </c>
-      <c r="T63" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="U63" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="V63" s="1">
-        <v>0</v>
+        <v>82</v>
+      </c>
+      <c r="V63" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="W63" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X63" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y63" s="1">
         <v>0</v>
       </c>
       <c r="Z63" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="1">
         <v>150</v>
       </c>
-      <c r="AA63" s="1">
-        <v>0</v>
-      </c>
       <c r="AB63" s="1">
         <v>0</v>
       </c>
@@ -7261,14 +7427,17 @@
       <c r="AF63" s="1">
         <v>0</v>
       </c>
-      <c r="AH63" s="1">
-        <v>50</v>
+      <c r="AG63" s="1">
+        <v>0</v>
       </c>
       <c r="AI63" s="1">
         <v>50</v>
       </c>
+      <c r="AJ63" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="64" s="1" customFormat="1" spans="3:35">
+    <row r="64" s="1" customFormat="1" spans="3:36">
       <c r="C64" s="1">
         <v>12003</v>
       </c>
@@ -7276,10 +7445,10 @@
         <v>2003</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G64" s="1">
         <v>3</v>
@@ -7291,50 +7460,50 @@
         <v>10</v>
       </c>
       <c r="K64" s="1">
+        <v>0</v>
+      </c>
+      <c r="L64" s="1">
         <v>5</v>
-      </c>
-      <c r="L64" s="1">
-        <v>2</v>
       </c>
       <c r="M64" s="1">
         <v>2</v>
       </c>
       <c r="N64" s="1">
+        <v>2</v>
+      </c>
+      <c r="O64" s="1">
         <v>9999</v>
       </c>
-      <c r="O64" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q64" s="1">
-        <v>0</v>
-      </c>
-      <c r="S64" s="1">
+      <c r="P64" s="1">
+        <v>0</v>
+      </c>
+      <c r="R64" s="1">
+        <v>0</v>
+      </c>
+      <c r="T64" s="1">
         <v>3</v>
       </c>
-      <c r="T64" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="U64" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V64" s="1">
-        <v>5</v>
+        <v>82</v>
+      </c>
+      <c r="V64" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="W64" s="1">
         <v>5</v>
       </c>
       <c r="X64" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y64" s="1">
         <v>2</v>
       </c>
       <c r="Z64" s="1">
+        <v>2</v>
+      </c>
+      <c r="AA64" s="1">
         <v>80</v>
       </c>
-      <c r="AA64" s="1">
-        <v>0</v>
-      </c>
       <c r="AB64" s="1">
         <v>0</v>
       </c>
@@ -7350,14 +7519,17 @@
       <c r="AF64" s="1">
         <v>0</v>
       </c>
-      <c r="AH64" s="1">
-        <v>50</v>
+      <c r="AG64" s="1">
+        <v>0</v>
       </c>
       <c r="AI64" s="1">
         <v>50</v>
       </c>
+      <c r="AJ64" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="65" s="1" customFormat="1" spans="3:35">
+    <row r="65" s="1" customFormat="1" spans="3:36">
       <c r="C65" s="1">
         <v>12004</v>
       </c>
@@ -7365,10 +7537,10 @@
         <v>2004</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G65" s="1">
         <v>1</v>
@@ -7383,47 +7555,47 @@
         <v>0</v>
       </c>
       <c r="L65" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M65" s="1">
         <v>2</v>
       </c>
       <c r="N65" s="1">
+        <v>2</v>
+      </c>
+      <c r="O65" s="1">
         <v>9999</v>
       </c>
-      <c r="O65" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="1">
-        <v>0</v>
-      </c>
-      <c r="S65" s="1">
+      <c r="P65" s="1">
+        <v>0</v>
+      </c>
+      <c r="R65" s="1">
+        <v>0</v>
+      </c>
+      <c r="T65" s="1">
         <v>4</v>
       </c>
-      <c r="T65" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="U65" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V65" s="1">
-        <v>0</v>
+        <v>69</v>
+      </c>
+      <c r="V65" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="W65" s="1">
+        <v>0</v>
+      </c>
+      <c r="X65" s="1">
         <v>4</v>
-      </c>
-      <c r="X65" s="1">
-        <v>2</v>
       </c>
       <c r="Y65" s="1">
         <v>2</v>
       </c>
       <c r="Z65" s="1">
+        <v>2</v>
+      </c>
+      <c r="AA65" s="1">
         <v>100</v>
       </c>
-      <c r="AA65" s="1">
-        <v>0</v>
-      </c>
       <c r="AB65" s="1">
         <v>0</v>
       </c>
@@ -7439,14 +7611,17 @@
       <c r="AF65" s="1">
         <v>0</v>
       </c>
-      <c r="AH65" s="1">
-        <v>50</v>
+      <c r="AG65" s="1">
+        <v>0</v>
       </c>
       <c r="AI65" s="1">
         <v>50</v>
       </c>
+      <c r="AJ65" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="66" s="1" customFormat="1" spans="3:35">
+    <row r="66" s="1" customFormat="1" spans="3:36">
       <c r="C66" s="1">
         <v>12005</v>
       </c>
@@ -7454,10 +7629,10 @@
         <v>2005</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G66" s="1">
         <v>5</v>
@@ -7469,38 +7644,38 @@
         <v>50</v>
       </c>
       <c r="K66" s="1">
+        <v>0</v>
+      </c>
+      <c r="L66" s="1">
         <v>30</v>
       </c>
-      <c r="L66" s="1">
-        <v>1</v>
-      </c>
       <c r="M66" s="1">
+        <v>1</v>
+      </c>
+      <c r="N66" s="1">
         <v>2</v>
       </c>
-      <c r="N66" s="1">
+      <c r="O66" s="1">
         <v>9999</v>
       </c>
-      <c r="O66" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="1">
-        <v>0</v>
-      </c>
-      <c r="S66" s="1">
-        <v>0</v>
-      </c>
-      <c r="T66" s="1" t="s">
-        <v>68</v>
+      <c r="P66" s="1">
+        <v>0</v>
+      </c>
+      <c r="R66" s="1">
+        <v>0</v>
+      </c>
+      <c r="T66" s="1">
+        <v>0</v>
       </c>
       <c r="U66" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V66" s="1">
+        <v>69</v>
+      </c>
+      <c r="V66" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="W66" s="1">
         <v>30</v>
       </c>
-      <c r="W66" s="1">
-        <v>0</v>
-      </c>
       <c r="X66" s="1">
         <v>0</v>
       </c>
@@ -7508,11 +7683,11 @@
         <v>0</v>
       </c>
       <c r="Z66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA66" s="1">
         <v>20</v>
       </c>
-      <c r="AA66" s="1">
-        <v>0</v>
-      </c>
       <c r="AB66" s="1">
         <v>0</v>
       </c>
@@ -7528,15 +7703,18 @@
       <c r="AF66" s="1">
         <v>0</v>
       </c>
-      <c r="AG66" s="7"/>
-      <c r="AH66" s="1">
-        <v>50</v>
-      </c>
+      <c r="AG66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH66" s="7"/>
       <c r="AI66" s="1">
         <v>50</v>
       </c>
+      <c r="AJ66" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="67" s="1" customFormat="1" spans="3:35">
+    <row r="67" s="1" customFormat="1" spans="3:36">
       <c r="C67" s="1">
         <v>12006</v>
       </c>
@@ -7544,10 +7722,10 @@
         <v>2006</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G67" s="1">
         <v>6</v>
@@ -7562,31 +7740,31 @@
         <v>0</v>
       </c>
       <c r="L67" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M67" s="1">
+        <v>1</v>
+      </c>
+      <c r="N67" s="1">
         <v>2</v>
       </c>
-      <c r="N67" s="1">
+      <c r="O67" s="1">
         <v>9999</v>
       </c>
-      <c r="O67" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q67" s="1">
-        <v>0</v>
-      </c>
-      <c r="S67" s="1">
-        <v>0</v>
-      </c>
-      <c r="T67" s="1" t="s">
-        <v>68</v>
+      <c r="P67" s="1">
+        <v>0</v>
+      </c>
+      <c r="R67" s="1">
+        <v>0</v>
+      </c>
+      <c r="T67" s="1">
+        <v>0</v>
       </c>
       <c r="U67" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="V67" s="1">
-        <v>0</v>
+        <v>69</v>
+      </c>
+      <c r="V67" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="W67" s="1">
         <v>0</v>
@@ -7598,10 +7776,10 @@
         <v>0</v>
       </c>
       <c r="Z67" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AA67" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AB67" s="1">
         <v>0</v>
@@ -7618,14 +7796,17 @@
       <c r="AF67" s="1">
         <v>0</v>
       </c>
-      <c r="AH67" s="1">
-        <v>50</v>
+      <c r="AG67" s="1">
+        <v>0</v>
       </c>
       <c r="AI67" s="1">
         <v>50</v>
       </c>
+      <c r="AJ67" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="68" s="1" customFormat="1" spans="3:35">
+    <row r="68" s="1" customFormat="1" spans="3:36">
       <c r="C68" s="1">
         <v>12007</v>
       </c>
@@ -7633,10 +7814,10 @@
         <v>2007</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G68" s="1">
         <v>1</v>
@@ -7651,47 +7832,47 @@
         <v>0</v>
       </c>
       <c r="L68" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M68" s="1">
         <v>2</v>
       </c>
       <c r="N68" s="1">
+        <v>2</v>
+      </c>
+      <c r="O68" s="1">
         <v>9999</v>
       </c>
-      <c r="O68" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q68" s="1">
-        <v>0</v>
-      </c>
-      <c r="S68" s="1">
+      <c r="P68" s="1">
+        <v>0</v>
+      </c>
+      <c r="R68" s="1">
+        <v>0</v>
+      </c>
+      <c r="T68" s="1">
         <v>5</v>
       </c>
-      <c r="T68" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="U68" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V68" s="1">
-        <v>0</v>
+        <v>82</v>
+      </c>
+      <c r="V68" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="W68" s="1">
+        <v>0</v>
+      </c>
+      <c r="X68" s="1">
         <v>5</v>
-      </c>
-      <c r="X68" s="1">
-        <v>3</v>
       </c>
       <c r="Y68" s="1">
         <v>3</v>
       </c>
       <c r="Z68" s="1">
+        <v>3</v>
+      </c>
+      <c r="AA68" s="1">
         <v>150</v>
       </c>
-      <c r="AA68" s="1">
-        <v>0</v>
-      </c>
       <c r="AB68" s="1">
         <v>0</v>
       </c>
@@ -7707,14 +7888,17 @@
       <c r="AF68" s="1">
         <v>0</v>
       </c>
-      <c r="AH68" s="1">
-        <v>50</v>
+      <c r="AG68" s="1">
+        <v>0</v>
       </c>
       <c r="AI68" s="1">
         <v>50</v>
       </c>
+      <c r="AJ68" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="69" s="1" customFormat="1" spans="3:35">
+    <row r="69" s="1" customFormat="1" spans="3:36">
       <c r="C69" s="1">
         <v>13001</v>
       </c>
@@ -7722,10 +7906,10 @@
         <v>3001</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G69" s="1">
         <v>4</v>
@@ -7737,34 +7921,34 @@
         <v>20</v>
       </c>
       <c r="K69" s="1">
+        <v>0</v>
+      </c>
+      <c r="L69" s="1">
         <v>4</v>
       </c>
-      <c r="L69" s="1">
-        <v>1</v>
-      </c>
       <c r="M69" s="1">
+        <v>1</v>
+      </c>
+      <c r="N69" s="1">
         <v>3</v>
       </c>
-      <c r="N69" s="1">
+      <c r="O69" s="1">
         <v>9999</v>
       </c>
-      <c r="O69" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q69" s="1">
-        <v>0</v>
-      </c>
-      <c r="S69" s="1">
-        <v>0</v>
-      </c>
-      <c r="T69" s="1" t="s">
-        <v>68</v>
+      <c r="P69" s="1">
+        <v>0</v>
+      </c>
+      <c r="R69" s="1">
+        <v>0</v>
+      </c>
+      <c r="T69" s="1">
+        <v>0</v>
       </c>
       <c r="U69" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V69" s="1">
-        <v>0</v>
+        <v>69</v>
+      </c>
+      <c r="V69" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="W69" s="1">
         <v>0</v>
@@ -7776,10 +7960,10 @@
         <v>0</v>
       </c>
       <c r="Z69" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AA69" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AB69" s="1">
         <v>0</v>
@@ -7796,14 +7980,17 @@
       <c r="AF69" s="1">
         <v>0</v>
       </c>
-      <c r="AH69" s="1">
-        <v>50</v>
+      <c r="AG69" s="1">
+        <v>0</v>
       </c>
       <c r="AI69" s="1">
         <v>50</v>
       </c>
+      <c r="AJ69" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="70" s="1" customFormat="1" spans="3:35">
+    <row r="70" s="1" customFormat="1" spans="3:36">
       <c r="C70" s="1">
         <v>13002</v>
       </c>
@@ -7811,10 +7998,10 @@
         <v>3002</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G70" s="1">
         <v>1</v>
@@ -7829,47 +8016,47 @@
         <v>0</v>
       </c>
       <c r="L70" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" s="1">
+        <v>1</v>
+      </c>
+      <c r="N70" s="1">
         <v>3</v>
       </c>
-      <c r="N70" s="1">
+      <c r="O70" s="1">
         <v>9999</v>
       </c>
-      <c r="O70" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="1">
-        <v>0</v>
-      </c>
-      <c r="S70" s="1">
+      <c r="P70" s="1">
+        <v>0</v>
+      </c>
+      <c r="R70" s="1">
+        <v>0</v>
+      </c>
+      <c r="T70" s="1">
         <v>3</v>
       </c>
-      <c r="T70" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="U70" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="V70" s="1">
-        <v>0</v>
+        <v>82</v>
+      </c>
+      <c r="V70" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="W70" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X70" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y70" s="1">
         <v>0</v>
       </c>
       <c r="Z70" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="1">
         <v>120</v>
       </c>
-      <c r="AA70" s="1">
-        <v>0</v>
-      </c>
       <c r="AB70" s="1">
         <v>0</v>
       </c>
@@ -7885,14 +8072,17 @@
       <c r="AF70" s="1">
         <v>0</v>
       </c>
-      <c r="AH70" s="1">
-        <v>50</v>
+      <c r="AG70" s="1">
+        <v>0</v>
       </c>
       <c r="AI70" s="1">
         <v>50</v>
       </c>
+      <c r="AJ70" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="71" s="1" customFormat="1" spans="3:35">
+    <row r="71" s="1" customFormat="1" spans="3:36">
       <c r="C71" s="1">
         <v>13003</v>
       </c>
@@ -7900,10 +8090,10 @@
         <v>3003</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G71" s="1">
         <v>1</v>
@@ -7915,56 +8105,56 @@
         <v>10</v>
       </c>
       <c r="K71" s="1">
+        <v>0</v>
+      </c>
+      <c r="L71" s="1">
         <v>5</v>
       </c>
-      <c r="L71" s="1">
-        <v>1</v>
-      </c>
       <c r="M71" s="1">
+        <v>1</v>
+      </c>
+      <c r="N71" s="1">
         <v>3</v>
       </c>
-      <c r="N71" s="1">
+      <c r="O71" s="1">
         <v>9999</v>
       </c>
-      <c r="O71" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q71" s="1">
-        <v>0</v>
-      </c>
-      <c r="S71" s="1">
+      <c r="P71" s="1">
+        <v>0</v>
+      </c>
+      <c r="R71" s="1">
+        <v>0</v>
+      </c>
+      <c r="T71" s="1">
         <v>2</v>
       </c>
-      <c r="T71" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="U71" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="V71" s="1">
-        <v>0</v>
+        <v>82</v>
+      </c>
+      <c r="V71" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="W71" s="1">
+        <v>0</v>
+      </c>
+      <c r="X71" s="1">
         <v>5</v>
       </c>
-      <c r="X71" s="1">
-        <v>0</v>
-      </c>
       <c r="Y71" s="1">
         <v>0</v>
       </c>
       <c r="Z71" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="1">
         <v>35</v>
       </c>
-      <c r="AA71" s="1">
-        <v>0</v>
-      </c>
       <c r="AB71" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="1">
         <v>65</v>
       </c>
-      <c r="AC71" s="1">
-        <v>0</v>
-      </c>
       <c r="AD71" s="1">
         <v>0</v>
       </c>
@@ -7974,14 +8164,17 @@
       <c r="AF71" s="1">
         <v>0</v>
       </c>
-      <c r="AH71" s="1">
-        <v>50</v>
+      <c r="AG71" s="1">
+        <v>0</v>
       </c>
       <c r="AI71" s="1">
         <v>50</v>
       </c>
+      <c r="AJ71" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="72" s="1" customFormat="1" spans="3:35">
+    <row r="72" s="1" customFormat="1" spans="3:36">
       <c r="C72" s="1">
         <v>13004</v>
       </c>
@@ -7989,10 +8182,10 @@
         <v>3004</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G72" s="1">
         <v>2</v>
@@ -8004,50 +8197,50 @@
         <v>100</v>
       </c>
       <c r="K72" s="1">
+        <v>0</v>
+      </c>
+      <c r="L72" s="1">
         <v>15</v>
       </c>
-      <c r="L72" s="1">
-        <v>1</v>
-      </c>
       <c r="M72" s="1">
+        <v>1</v>
+      </c>
+      <c r="N72" s="1">
         <v>3</v>
       </c>
-      <c r="N72" s="1">
+      <c r="O72" s="1">
         <v>9999</v>
       </c>
-      <c r="O72" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="1">
-        <v>0</v>
-      </c>
-      <c r="S72" s="1">
-        <v>0</v>
-      </c>
-      <c r="T72" s="1" t="s">
-        <v>68</v>
+      <c r="P72" s="1">
+        <v>0</v>
+      </c>
+      <c r="R72" s="1">
+        <v>0</v>
+      </c>
+      <c r="T72" s="1">
+        <v>0</v>
       </c>
       <c r="U72" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="V72" s="1">
-        <v>0</v>
+        <v>69</v>
+      </c>
+      <c r="V72" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="W72" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X72" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y72" s="1">
         <v>0</v>
       </c>
       <c r="Z72" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA72" s="1">
         <v>100</v>
       </c>
-      <c r="AA72" s="1">
-        <v>0</v>
-      </c>
       <c r="AB72" s="1">
         <v>0</v>
       </c>
@@ -8063,14 +8256,17 @@
       <c r="AF72" s="1">
         <v>0</v>
       </c>
-      <c r="AH72" s="1">
-        <v>50</v>
+      <c r="AG72" s="1">
+        <v>0</v>
       </c>
       <c r="AI72" s="1">
         <v>50</v>
       </c>
+      <c r="AJ72" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="73" s="1" customFormat="1" spans="3:35">
+    <row r="73" s="1" customFormat="1" spans="3:36">
       <c r="C73" s="1">
         <v>13005</v>
       </c>
@@ -8078,10 +8274,10 @@
         <v>3005</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G73" s="1">
         <v>5</v>
@@ -8093,38 +8289,38 @@
         <v>50</v>
       </c>
       <c r="K73" s="1">
+        <v>0</v>
+      </c>
+      <c r="L73" s="1">
         <v>30</v>
       </c>
-      <c r="L73" s="1">
-        <v>1</v>
-      </c>
       <c r="M73" s="1">
+        <v>1</v>
+      </c>
+      <c r="N73" s="1">
         <v>3</v>
       </c>
-      <c r="N73" s="1">
+      <c r="O73" s="1">
         <v>9999</v>
       </c>
-      <c r="O73" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q73" s="1">
-        <v>0</v>
-      </c>
-      <c r="S73" s="1">
-        <v>0</v>
-      </c>
-      <c r="T73" s="1" t="s">
-        <v>68</v>
+      <c r="P73" s="1">
+        <v>0</v>
+      </c>
+      <c r="R73" s="1">
+        <v>0</v>
+      </c>
+      <c r="T73" s="1">
+        <v>0</v>
       </c>
       <c r="U73" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V73" s="1">
+        <v>69</v>
+      </c>
+      <c r="V73" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="W73" s="1">
         <v>30</v>
       </c>
-      <c r="W73" s="1">
-        <v>0</v>
-      </c>
       <c r="X73" s="1">
         <v>0</v>
       </c>
@@ -8132,11 +8328,11 @@
         <v>0</v>
       </c>
       <c r="Z73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="1">
         <v>20</v>
       </c>
-      <c r="AA73" s="1">
-        <v>0</v>
-      </c>
       <c r="AB73" s="1">
         <v>0</v>
       </c>
@@ -8152,15 +8348,18 @@
       <c r="AF73" s="1">
         <v>0</v>
       </c>
-      <c r="AG73" s="7"/>
-      <c r="AH73" s="1">
-        <v>50</v>
-      </c>
+      <c r="AG73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="7"/>
       <c r="AI73" s="1">
         <v>50</v>
       </c>
+      <c r="AJ73" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="74" s="1" customFormat="1" spans="3:35">
+    <row r="74" s="1" customFormat="1" spans="3:36">
       <c r="C74" s="1">
         <v>13006</v>
       </c>
@@ -8168,10 +8367,10 @@
         <v>3006</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G74" s="1">
         <v>6</v>
@@ -8186,31 +8385,31 @@
         <v>0</v>
       </c>
       <c r="L74" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" s="1">
+        <v>1</v>
+      </c>
+      <c r="N74" s="1">
         <v>3</v>
       </c>
-      <c r="N74" s="1">
+      <c r="O74" s="1">
         <v>9999</v>
       </c>
-      <c r="O74" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q74" s="1">
-        <v>0</v>
-      </c>
-      <c r="S74" s="1">
+      <c r="P74" s="1">
+        <v>0</v>
+      </c>
+      <c r="R74" s="1">
+        <v>0</v>
+      </c>
+      <c r="T74" s="1">
         <v>3</v>
       </c>
-      <c r="T74" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="U74" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="V74" s="1">
-        <v>0</v>
+        <v>69</v>
+      </c>
+      <c r="V74" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="W74" s="1">
         <v>0</v>
@@ -8222,10 +8421,10 @@
         <v>0</v>
       </c>
       <c r="Z74" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AA74" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AB74" s="1">
         <v>0</v>
@@ -8242,14 +8441,17 @@
       <c r="AF74" s="1">
         <v>0</v>
       </c>
-      <c r="AH74" s="1">
-        <v>50</v>
+      <c r="AG74" s="1">
+        <v>0</v>
       </c>
       <c r="AI74" s="1">
         <v>50</v>
       </c>
+      <c r="AJ74" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="75" s="1" customFormat="1" spans="3:35">
+    <row r="75" s="1" customFormat="1" spans="3:36">
       <c r="C75" s="1">
         <v>13007</v>
       </c>
@@ -8257,10 +8459,10 @@
         <v>3007</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G75" s="1">
         <v>2</v>
@@ -8272,50 +8474,50 @@
         <v>100</v>
       </c>
       <c r="K75" s="1">
+        <v>0</v>
+      </c>
+      <c r="L75" s="1">
         <v>15</v>
       </c>
-      <c r="L75" s="1">
-        <v>1</v>
-      </c>
       <c r="M75" s="1">
+        <v>1</v>
+      </c>
+      <c r="N75" s="1">
         <v>3</v>
       </c>
-      <c r="N75" s="1">
+      <c r="O75" s="1">
         <v>9999</v>
       </c>
-      <c r="O75" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q75" s="1">
-        <v>0</v>
-      </c>
-      <c r="S75" s="1">
+      <c r="P75" s="1">
+        <v>0</v>
+      </c>
+      <c r="R75" s="1">
+        <v>0</v>
+      </c>
+      <c r="T75" s="1">
         <v>2</v>
       </c>
-      <c r="T75" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="U75" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="V75" s="1">
-        <v>0</v>
+        <v>82</v>
+      </c>
+      <c r="V75" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="W75" s="1">
+        <v>0</v>
+      </c>
+      <c r="X75" s="1">
         <v>2</v>
       </c>
-      <c r="X75" s="1">
-        <v>0</v>
-      </c>
       <c r="Y75" s="1">
         <v>0</v>
       </c>
       <c r="Z75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="1">
         <v>120</v>
       </c>
-      <c r="AA75" s="1">
-        <v>0</v>
-      </c>
       <c r="AB75" s="1">
         <v>0</v>
       </c>
@@ -8331,24 +8533,28 @@
       <c r="AF75" s="1">
         <v>0</v>
       </c>
-      <c r="AH75" s="1">
-        <v>50</v>
+      <c r="AG75" s="1">
+        <v>0</v>
       </c>
       <c r="AI75" s="1">
         <v>50</v>
       </c>
+      <c r="AJ75" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="76" s="1" customFormat="1" spans="5:18">
+    <row r="76" s="1" customFormat="1" spans="5:19">
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
       <c r="J76" s="2"/>
-      <c r="N76" s="2"/>
+      <c r="K76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" s="2"/>
       <c r="Q76" s="2"/>
       <c r="R76" s="2"/>
+      <c r="S76" s="2"/>
     </row>
-    <row r="77" s="1" customFormat="1" spans="3:35">
+    <row r="77" s="1" customFormat="1" spans="3:36">
       <c r="C77" s="1">
         <v>21002</v>
       </c>
@@ -8356,10 +8562,10 @@
         <v>1002</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G77" s="1">
         <v>1</v>
@@ -8374,53 +8580,53 @@
         <v>0</v>
       </c>
       <c r="L77" s="1">
+        <v>0</v>
+      </c>
+      <c r="M77" s="1">
         <v>2</v>
       </c>
-      <c r="M77" s="1">
-        <v>1</v>
-      </c>
       <c r="N77" s="1">
+        <v>1</v>
+      </c>
+      <c r="O77" s="1">
         <v>9999</v>
       </c>
-      <c r="O77" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q77" s="1">
-        <v>0</v>
-      </c>
-      <c r="S77" s="1">
+      <c r="P77" s="1">
+        <v>0</v>
+      </c>
+      <c r="R77" s="1">
+        <v>0</v>
+      </c>
+      <c r="T77" s="1">
         <v>2</v>
-      </c>
-      <c r="T77" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="U77" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="V77" s="1">
-        <v>0</v>
+      <c r="V77" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="W77" s="1">
+        <v>0</v>
+      </c>
+      <c r="X77" s="1">
         <v>2</v>
       </c>
-      <c r="X77" s="1">
-        <v>0</v>
-      </c>
       <c r="Y77" s="1">
         <v>0</v>
       </c>
       <c r="Z77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="1">
         <v>150</v>
       </c>
-      <c r="AA77" s="1">
-        <v>0</v>
-      </c>
       <c r="AB77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="1">
         <v>20</v>
       </c>
-      <c r="AC77" s="1">
-        <v>0</v>
-      </c>
       <c r="AD77" s="1">
         <v>0</v>
       </c>
@@ -8430,19 +8636,22 @@
       <c r="AF77" s="1">
         <v>0</v>
       </c>
-      <c r="AG77" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="AH77" s="1">
-        <v>50</v>
+      <c r="AG77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="1" t="s">
+        <v>193</v>
       </c>
       <c r="AI77" s="1">
+        <v>50</v>
+      </c>
+      <c r="AJ77" s="1">
         <v>50</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:K5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="K3 K4 K5 L3:L5 C3:J5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -5684,6 +5684,9 @@
       <c r="P42" s="1">
         <v>0</v>
       </c>
+      <c r="Q42" s="1">
+        <v>1</v>
+      </c>
       <c r="R42" s="1">
         <v>0</v>
       </c>
@@ -5782,6 +5785,9 @@
       <c r="P43" s="1">
         <v>0</v>
       </c>
+      <c r="Q43" s="1">
+        <v>1</v>
+      </c>
       <c r="R43" s="1">
         <v>10</v>
       </c>
@@ -5877,6 +5883,9 @@
       </c>
       <c r="P44" s="1">
         <v>0</v>
+      </c>
+      <c r="Q44" s="1">
+        <v>1</v>
       </c>
       <c r="R44" s="1">
         <v>0</v>
@@ -5977,6 +5986,9 @@
       <c r="P46" s="1">
         <v>0</v>
       </c>
+      <c r="Q46" s="1">
+        <v>1</v>
+      </c>
       <c r="R46" s="1">
         <v>0</v>
       </c>
@@ -6068,6 +6080,9 @@
       </c>
       <c r="P47" s="1">
         <v>0</v>
+      </c>
+      <c r="Q47" s="1">
+        <v>1</v>
       </c>
       <c r="R47" s="1">
         <v>0</v>
@@ -6165,6 +6180,9 @@
       <c r="P49" s="1">
         <v>0</v>
       </c>
+      <c r="Q49" s="1">
+        <v>1</v>
+      </c>
       <c r="R49" s="1">
         <v>0</v>
       </c>
@@ -6260,7 +6278,9 @@
       <c r="P50" s="1">
         <v>0</v>
       </c>
-      <c r="Q50" s="1"/>
+      <c r="Q50" s="1">
+        <v>1</v>
+      </c>
       <c r="R50" s="1">
         <v>0</v>
       </c>
@@ -6358,7 +6378,9 @@
       <c r="P51" s="1">
         <v>0</v>
       </c>
-      <c r="Q51" s="1"/>
+      <c r="Q51" s="1">
+        <v>1</v>
+      </c>
       <c r="R51" s="1">
         <v>0</v>
       </c>
@@ -6456,7 +6478,9 @@
       <c r="P52" s="1">
         <v>0</v>
       </c>
-      <c r="Q52" s="1"/>
+      <c r="Q52" s="1">
+        <v>1</v>
+      </c>
       <c r="R52" s="1">
         <v>0</v>
       </c>
@@ -6553,6 +6577,9 @@
       <c r="P53" s="1">
         <v>0</v>
       </c>
+      <c r="Q53" s="1">
+        <v>1</v>
+      </c>
       <c r="R53" s="1">
         <v>0</v>
       </c>
@@ -6645,6 +6672,9 @@
       <c r="P55" s="1">
         <v>0</v>
       </c>
+      <c r="Q55" s="1">
+        <v>1</v>
+      </c>
       <c r="R55" s="1">
         <v>0</v>
       </c>
@@ -6737,6 +6767,9 @@
       <c r="P56" s="1">
         <v>0</v>
       </c>
+      <c r="Q56" s="1">
+        <v>1</v>
+      </c>
       <c r="R56" s="1">
         <v>0</v>
       </c>
@@ -6829,6 +6862,9 @@
       <c r="P57" s="1">
         <v>0</v>
       </c>
+      <c r="Q57" s="1">
+        <v>1</v>
+      </c>
       <c r="R57" s="1">
         <v>0</v>
       </c>
@@ -6921,6 +6957,9 @@
       <c r="P58" s="1">
         <v>0</v>
       </c>
+      <c r="Q58" s="1">
+        <v>1</v>
+      </c>
       <c r="R58" s="1">
         <v>0</v>
       </c>
@@ -7016,6 +7055,9 @@
       <c r="P59" s="1">
         <v>0</v>
       </c>
+      <c r="Q59" s="1">
+        <v>1</v>
+      </c>
       <c r="R59" s="1">
         <v>0</v>
       </c>
@@ -7109,6 +7151,9 @@
       <c r="P60" s="1">
         <v>0</v>
       </c>
+      <c r="Q60" s="1">
+        <v>1</v>
+      </c>
       <c r="R60" s="1">
         <v>0</v>
       </c>
@@ -7201,6 +7246,9 @@
       <c r="P61" s="1">
         <v>0</v>
       </c>
+      <c r="Q61" s="1">
+        <v>1</v>
+      </c>
       <c r="R61" s="1">
         <v>0</v>
       </c>
@@ -7293,6 +7341,9 @@
       <c r="P62" s="1">
         <v>0</v>
       </c>
+      <c r="Q62" s="1">
+        <v>1</v>
+      </c>
       <c r="R62" s="1">
         <v>0</v>
       </c>
@@ -7385,6 +7436,9 @@
       <c r="P63" s="1">
         <v>0</v>
       </c>
+      <c r="Q63" s="1">
+        <v>1</v>
+      </c>
       <c r="R63" s="1">
         <v>0</v>
       </c>
@@ -7477,6 +7531,9 @@
       <c r="P64" s="1">
         <v>0</v>
       </c>
+      <c r="Q64" s="1">
+        <v>1</v>
+      </c>
       <c r="R64" s="1">
         <v>0</v>
       </c>
@@ -7569,6 +7626,9 @@
       <c r="P65" s="1">
         <v>0</v>
       </c>
+      <c r="Q65" s="1">
+        <v>1</v>
+      </c>
       <c r="R65" s="1">
         <v>0</v>
       </c>
@@ -7661,6 +7721,9 @@
       <c r="P66" s="1">
         <v>0</v>
       </c>
+      <c r="Q66" s="1">
+        <v>1</v>
+      </c>
       <c r="R66" s="1">
         <v>0</v>
       </c>
@@ -7754,6 +7817,9 @@
       <c r="P67" s="1">
         <v>0</v>
       </c>
+      <c r="Q67" s="1">
+        <v>1</v>
+      </c>
       <c r="R67" s="1">
         <v>0</v>
       </c>
@@ -7846,6 +7912,9 @@
       <c r="P68" s="1">
         <v>0</v>
       </c>
+      <c r="Q68" s="1">
+        <v>1</v>
+      </c>
       <c r="R68" s="1">
         <v>0</v>
       </c>
@@ -7938,6 +8007,9 @@
       <c r="P69" s="1">
         <v>0</v>
       </c>
+      <c r="Q69" s="1">
+        <v>1</v>
+      </c>
       <c r="R69" s="1">
         <v>0</v>
       </c>
@@ -8030,6 +8102,9 @@
       <c r="P70" s="1">
         <v>0</v>
       </c>
+      <c r="Q70" s="1">
+        <v>1</v>
+      </c>
       <c r="R70" s="1">
         <v>0</v>
       </c>
@@ -8122,6 +8197,9 @@
       <c r="P71" s="1">
         <v>0</v>
       </c>
+      <c r="Q71" s="1">
+        <v>1</v>
+      </c>
       <c r="R71" s="1">
         <v>0</v>
       </c>
@@ -8214,6 +8292,9 @@
       <c r="P72" s="1">
         <v>0</v>
       </c>
+      <c r="Q72" s="1">
+        <v>1</v>
+      </c>
       <c r="R72" s="1">
         <v>0</v>
       </c>
@@ -8306,6 +8387,9 @@
       <c r="P73" s="1">
         <v>0</v>
       </c>
+      <c r="Q73" s="1">
+        <v>1</v>
+      </c>
       <c r="R73" s="1">
         <v>0</v>
       </c>
@@ -8399,6 +8483,9 @@
       <c r="P74" s="1">
         <v>0</v>
       </c>
+      <c r="Q74" s="1">
+        <v>1</v>
+      </c>
       <c r="R74" s="1">
         <v>0</v>
       </c>
@@ -8490,6 +8577,9 @@
       </c>
       <c r="P75" s="1">
         <v>0</v>
+      </c>
+      <c r="Q75" s="1">
+        <v>1</v>
       </c>
       <c r="R75" s="1">
         <v>0</v>
@@ -8594,6 +8684,9 @@
       <c r="P77" s="1">
         <v>0</v>
       </c>
+      <c r="Q77" s="1">
+        <v>1</v>
+      </c>
       <c r="R77" s="1">
         <v>0</v>
       </c>
@@ -8651,7 +8744,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="K3 K4 K5 L3:L5 C3:J5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:L5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1071,12 +1071,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4648,14 +4648,14 @@
         <v>3</v>
       </c>
       <c r="O31" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="P31" s="1">
         <v>60</v>
       </c>
       <c r="Q31" s="1">
-        <f t="shared" ref="Q30:Q40" si="2">O31*5</f>
-        <v>2500</v>
+        <f>O31*1.8</f>
+        <v>1080</v>
       </c>
       <c r="R31" s="1">
         <v>2</v>
@@ -4756,7 +4756,7 @@
         <v>60</v>
       </c>
       <c r="Q32" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="Q30:Q40" si="2">O32*5</f>
         <v>3000</v>
       </c>
       <c r="R32" s="1">

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -56,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0">
+    <comment ref="H3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -85,7 +85,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="1">
+    <comment ref="I3" authorId="1">
       <text>
         <r>
           <rPr>
@@ -108,7 +108,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0">
+    <comment ref="J3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -130,7 +130,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M3" authorId="0">
+    <comment ref="N3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -154,7 +154,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N3" authorId="0">
+    <comment ref="O3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -176,7 +176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0">
+    <comment ref="U3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -199,7 +199,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U3" authorId="0">
+    <comment ref="V3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -223,7 +223,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V3" authorId="0">
+    <comment ref="W3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -249,7 +249,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA3" authorId="0">
+    <comment ref="AB3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -271,7 +271,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH3" authorId="0">
+    <comment ref="AI3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -298,12 +298,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="195">
   <si>
     <t>_ID</t>
   </si>
   <si>
     <t>技能ID</t>
+  </si>
+  <si>
+    <t>SkillLayer</t>
   </si>
   <si>
     <t>技能名字</t>
@@ -1872,44 +1875,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:AL77"/>
+  <dimension ref="C3:AM77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="5.625" style="2" customWidth="1"/>
     <col min="2" max="2" width="3.5" style="2" customWidth="1"/>
-    <col min="3" max="4" width="9" style="2"/>
-    <col min="5" max="5" width="11.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9" style="2" customWidth="1"/>
-    <col min="7" max="7" width="6.375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="9.375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="5.25" style="2" customWidth="1"/>
-    <col min="10" max="10" width="74.875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="10.5" style="2" customWidth="1"/>
-    <col min="12" max="12" width="5.875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="8.375" style="2" customWidth="1"/>
-    <col min="14" max="14" width="5.875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="7.50833333333333" style="2" customWidth="1"/>
-    <col min="16" max="17" width="12.875" style="2" customWidth="1"/>
-    <col min="18" max="19" width="13.5" style="2" customWidth="1"/>
-    <col min="20" max="20" width="7.375" style="2" customWidth="1"/>
-    <col min="21" max="21" width="7.50833333333333" style="2" customWidth="1"/>
-    <col min="22" max="22" width="8.25" style="2" customWidth="1"/>
-    <col min="23" max="23" width="6.5" style="2" customWidth="1"/>
-    <col min="24" max="26" width="7.625" style="2" customWidth="1"/>
-    <col min="27" max="28" width="7.875" style="2" customWidth="1"/>
-    <col min="29" max="29" width="9.625" style="2" customWidth="1"/>
-    <col min="30" max="31" width="7.875" style="2" customWidth="1"/>
-    <col min="32" max="32" width="12.625" style="2" customWidth="1"/>
-    <col min="33" max="33" width="9.625" style="2" customWidth="1"/>
-    <col min="34" max="34" width="27.625" style="2" customWidth="1"/>
-    <col min="35" max="35" width="17.875" style="2" customWidth="1"/>
-    <col min="36" max="36" width="19.75" style="2" customWidth="1"/>
-    <col min="37" max="37" width="9" style="2"/>
-    <col min="38" max="38" width="19.25" style="2" customWidth="1"/>
-    <col min="39" max="16384" width="9" style="2"/>
+    <col min="3" max="5" width="9" style="2"/>
+    <col min="6" max="6" width="11.5" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9" style="2" customWidth="1"/>
+    <col min="8" max="8" width="6.375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="9.375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="5.25" style="2" customWidth="1"/>
+    <col min="11" max="11" width="74.875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="10.5" style="2" customWidth="1"/>
+    <col min="13" max="13" width="5.875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="8.375" style="2" customWidth="1"/>
+    <col min="15" max="15" width="5.875" style="2" customWidth="1"/>
+    <col min="16" max="16" width="7.50833333333333" style="2" customWidth="1"/>
+    <col min="17" max="18" width="12.875" style="2" customWidth="1"/>
+    <col min="19" max="20" width="13.5" style="2" customWidth="1"/>
+    <col min="21" max="21" width="7.375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="7.50833333333333" style="2" customWidth="1"/>
+    <col min="23" max="23" width="8.25" style="2" customWidth="1"/>
+    <col min="24" max="24" width="6.5" style="2" customWidth="1"/>
+    <col min="25" max="27" width="7.625" style="2" customWidth="1"/>
+    <col min="28" max="29" width="7.875" style="2" customWidth="1"/>
+    <col min="30" max="30" width="9.625" style="2" customWidth="1"/>
+    <col min="31" max="32" width="7.875" style="2" customWidth="1"/>
+    <col min="33" max="33" width="12.625" style="2" customWidth="1"/>
+    <col min="34" max="34" width="9.625" style="2" customWidth="1"/>
+    <col min="35" max="35" width="27.625" style="2" customWidth="1"/>
+    <col min="36" max="36" width="17.875" style="2" customWidth="1"/>
+    <col min="37" max="37" width="19.75" style="2" customWidth="1"/>
+    <col min="38" max="38" width="9" style="2"/>
+    <col min="39" max="39" width="19.25" style="2" customWidth="1"/>
+    <col min="40" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:38">
+    <row r="3" spans="3:39">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1959,7 +1962,7 @@
         <v>15</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T3" s="3" t="s">
         <v>16</v>
@@ -2012,22 +2015,25 @@
       <c r="AJ3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AK3" s="2" t="s">
+      <c r="AK3" s="3" t="s">
         <v>33</v>
       </c>
       <c r="AL3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="4" spans="3:36">
+    <row r="4" spans="3:37">
       <c r="C4" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>37</v>
@@ -2045,10 +2051,10 @@
         <v>41</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>43</v>
@@ -2060,13 +2066,13 @@
         <v>45</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="Q4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="S4" s="3" t="s">
         <v>47</v>
@@ -2120,193 +2126,199 @@
         <v>63</v>
       </c>
       <c r="AJ4" s="3" t="s">
-        <v>32</v>
+        <v>64</v>
+      </c>
+      <c r="AK4" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="5" spans="3:36">
+    <row r="5" spans="3:37">
       <c r="C5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>65</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="I5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>65</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U5" s="3" t="s">
         <v>65</v>
       </c>
       <c r="V5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="W5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="X5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="W5" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="X5" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="Y5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Z5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AA5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AB5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AC5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AD5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AE5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AF5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AG5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AH5" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AI5" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="AJ5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="AK5" s="3" t="s">
+        <v>65</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="3:36">
+    <row r="6" s="1" customFormat="1" spans="3:37">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
       <c r="D6" s="1">
         <v>1001</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>67</v>
+      <c r="E6" s="1">
+        <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1</v>
+        <v>68</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
         <v>10</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="K6" s="1">
-        <v>0</v>
+      <c r="K6" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="L6" s="1">
         <v>0</v>
       </c>
       <c r="M6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" s="1">
         <v>1</v>
       </c>
       <c r="O6" s="1">
+        <v>1</v>
+      </c>
+      <c r="P6" s="1">
         <v>600</v>
       </c>
-      <c r="P6" s="1">
+      <c r="Q6" s="1">
         <v>60</v>
       </c>
-      <c r="Q6" s="1">
-        <f t="shared" ref="Q6:Q16" si="0">O6*5</f>
+      <c r="R6" s="1">
+        <f t="shared" ref="R6:R16" si="0">P6*5</f>
         <v>3000</v>
       </c>
-      <c r="R6" s="1">
-        <v>1</v>
-      </c>
       <c r="S6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" s="1">
-        <v>1</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>69</v>
+        <v>0</v>
+      </c>
+      <c r="U6" s="1">
+        <v>1</v>
       </c>
       <c r="V6" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="W6" s="1">
-        <v>0</v>
+      <c r="W6" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="X6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" s="1">
         <v>0</v>
       </c>
       <c r="AA6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="1">
         <v>120</v>
       </c>
-      <c r="AB6" s="1">
-        <v>0</v>
-      </c>
       <c r="AC6" s="1">
         <v>0</v>
       </c>
@@ -2322,98 +2334,101 @@
       <c r="AG6" s="1">
         <v>0</v>
       </c>
-      <c r="AI6" s="1">
-        <v>50</v>
+      <c r="AH6" s="1">
+        <v>0</v>
       </c>
       <c r="AJ6" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK6" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" spans="3:36">
+    <row r="7" s="1" customFormat="1" spans="3:37">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
       <c r="D7" s="1">
         <v>1002</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="E7" s="1">
+        <v>2</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G7" s="1">
-        <v>1</v>
+      <c r="G7" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="H7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
         <v>10</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0</v>
+      <c r="K7" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="L7" s="1">
         <v>0</v>
       </c>
       <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
         <v>2</v>
       </c>
-      <c r="N7" s="1">
-        <v>1</v>
-      </c>
       <c r="O7" s="1">
+        <v>1</v>
+      </c>
+      <c r="P7" s="1">
         <v>600</v>
       </c>
-      <c r="P7" s="1">
+      <c r="Q7" s="1">
         <v>60</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="R7" s="1">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="R7" s="1">
+      <c r="S7" s="1">
         <v>2</v>
       </c>
-      <c r="S7" s="1">
-        <v>0</v>
-      </c>
       <c r="T7" s="1">
+        <v>0</v>
+      </c>
+      <c r="U7" s="1">
         <v>2</v>
-      </c>
-      <c r="U7" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="V7" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="W7" s="1">
-        <v>0</v>
+      <c r="W7" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="X7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="1">
         <v>2</v>
       </c>
-      <c r="Y7" s="1">
-        <v>0</v>
-      </c>
       <c r="Z7" s="1">
         <v>0</v>
       </c>
       <c r="AA7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="1">
         <v>150</v>
       </c>
-      <c r="AB7" s="1">
-        <v>0</v>
-      </c>
       <c r="AC7" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AD7" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AE7" s="1">
         <v>0</v>
@@ -2424,93 +2439,96 @@
       <c r="AG7" s="1">
         <v>0</v>
       </c>
-      <c r="AI7" s="1">
-        <v>50</v>
+      <c r="AH7" s="1">
+        <v>0</v>
       </c>
       <c r="AJ7" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK7" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" spans="3:36">
+    <row r="8" s="1" customFormat="1" spans="3:37">
       <c r="C8" s="1">
         <v>1003</v>
       </c>
       <c r="D8" s="1">
         <v>1003</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="E8" s="1">
+        <v>3</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="G8" s="1">
-        <v>1</v>
+      <c r="G8" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="H8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
         <v>10</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="K8" s="1">
-        <v>0</v>
+      <c r="K8" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
         <v>5</v>
       </c>
-      <c r="M8" s="1">
+      <c r="N8" s="1">
         <v>2</v>
       </c>
-      <c r="N8" s="1">
-        <v>1</v>
-      </c>
       <c r="O8" s="1">
+        <v>1</v>
+      </c>
+      <c r="P8" s="1">
         <v>600</v>
       </c>
-      <c r="P8" s="1">
+      <c r="Q8" s="1">
         <v>60</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="R8" s="1">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="R8" s="1">
-        <v>1</v>
-      </c>
       <c r="S8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" s="1">
-        <v>1</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>69</v>
+        <v>0</v>
+      </c>
+      <c r="U8" s="1">
+        <v>1</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="W8" s="1">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="X8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="1">
         <v>5</v>
       </c>
-      <c r="Y8" s="1">
-        <v>0</v>
-      </c>
       <c r="Z8" s="1">
         <v>0</v>
       </c>
       <c r="AA8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="1">
         <v>100</v>
       </c>
-      <c r="AB8" s="1">
-        <v>0</v>
-      </c>
       <c r="AC8" s="1">
         <v>0</v>
       </c>
@@ -2526,96 +2544,99 @@
       <c r="AG8" s="1">
         <v>0</v>
       </c>
-      <c r="AH8" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI8" s="1">
-        <v>50</v>
+      <c r="AH8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="AJ8" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK8" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" spans="3:36">
+    <row r="9" s="1" customFormat="1" spans="3:37">
       <c r="C9" s="1">
         <v>1004</v>
       </c>
       <c r="D9" s="1">
         <v>1004</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>79</v>
+      <c r="E9" s="1">
+        <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H9" s="1">
         <v>7</v>
       </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
       <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
         <v>10</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="K9" s="1">
-        <v>0</v>
+      <c r="K9" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
         <v>10</v>
       </c>
-      <c r="M9" s="1">
-        <v>1</v>
-      </c>
       <c r="N9" s="1">
         <v>1</v>
       </c>
       <c r="O9" s="1">
+        <v>1</v>
+      </c>
+      <c r="P9" s="1">
         <v>600</v>
       </c>
-      <c r="P9" s="1">
+      <c r="Q9" s="1">
         <v>60</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="R9" s="1">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="R9" s="1">
+      <c r="S9" s="1">
         <v>4</v>
       </c>
-      <c r="S9" s="1">
-        <v>0</v>
-      </c>
       <c r="T9" s="1">
+        <v>0</v>
+      </c>
+      <c r="U9" s="1">
         <v>5</v>
-      </c>
-      <c r="U9" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="V9" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="W9" s="1">
+      <c r="W9" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="X9" s="1">
         <v>2</v>
       </c>
-      <c r="X9" s="1">
-        <v>1</v>
-      </c>
       <c r="Y9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" s="1">
         <v>0</v>
       </c>
       <c r="AA9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="1">
         <v>200</v>
       </c>
-      <c r="AB9" s="1">
-        <v>0</v>
-      </c>
       <c r="AC9" s="1">
         <v>0</v>
       </c>
@@ -2631,84 +2652,87 @@
       <c r="AG9" s="1">
         <v>0</v>
       </c>
-      <c r="AH9" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AI9" s="1">
-        <v>50</v>
+      <c r="AH9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="AJ9" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK9" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" spans="3:36">
+    <row r="10" s="1" customFormat="1" spans="3:37">
       <c r="C10" s="1">
         <v>1005</v>
       </c>
       <c r="D10" s="1">
         <v>1005</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F10" s="2" t="s">
+      <c r="E10" s="1">
+        <v>5</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G10" s="1">
-        <v>5</v>
+      <c r="G10" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="H10" s="1">
         <v>5</v>
       </c>
       <c r="I10" s="1">
-        <v>50</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="K10" s="1">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="J10" s="1">
+        <v>50</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
         <v>55</v>
       </c>
-      <c r="M10" s="1">
-        <v>1</v>
-      </c>
       <c r="N10" s="1">
         <v>1</v>
       </c>
       <c r="O10" s="1">
+        <v>1</v>
+      </c>
+      <c r="P10" s="1">
         <v>200</v>
       </c>
-      <c r="P10" s="1">
+      <c r="Q10" s="1">
         <v>20</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="R10" s="1">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="R10" s="1">
-        <v>1</v>
-      </c>
       <c r="S10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" s="1">
         <v>0</v>
       </c>
-      <c r="U10" s="1" t="s">
-        <v>69</v>
+      <c r="U10" s="1">
+        <v>0</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="W10" s="1">
+        <v>70</v>
+      </c>
+      <c r="W10" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="X10" s="1">
         <v>30</v>
       </c>
-      <c r="X10" s="1">
-        <v>0</v>
-      </c>
       <c r="Y10" s="1">
         <v>0</v>
       </c>
@@ -2716,11 +2740,11 @@
         <v>0</v>
       </c>
       <c r="AA10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="1">
         <v>100</v>
       </c>
-      <c r="AB10" s="1">
-        <v>0</v>
-      </c>
       <c r="AC10" s="1">
         <v>0</v>
       </c>
@@ -2736,80 +2760,83 @@
       <c r="AG10" s="1">
         <v>0</v>
       </c>
-      <c r="AH10" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="AI10" s="1">
-        <v>50</v>
+      <c r="AH10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="AJ10" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK10" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" spans="3:36">
+    <row r="11" s="1" customFormat="1" spans="3:37">
       <c r="C11" s="1">
         <v>1006</v>
       </c>
       <c r="D11" s="1">
         <v>1006</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G11" s="1">
+      <c r="E11" s="1">
         <v>6</v>
       </c>
+      <c r="F11" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>91</v>
+      </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
         <v>10</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="K11" s="1">
-        <v>0</v>
+      <c r="K11" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="L11" s="1">
         <v>0</v>
       </c>
       <c r="M11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" s="1">
         <v>1</v>
       </c>
       <c r="O11" s="1">
+        <v>1</v>
+      </c>
+      <c r="P11" s="1">
         <v>200</v>
       </c>
-      <c r="P11" s="1">
+      <c r="Q11" s="1">
         <v>20</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="R11" s="1">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="R11" s="1">
-        <v>1</v>
-      </c>
       <c r="S11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" s="1">
         <v>0</v>
       </c>
-      <c r="U11" s="1" t="s">
-        <v>69</v>
+      <c r="U11" s="1">
+        <v>0</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="W11" s="1">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="W11" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="X11" s="1">
         <v>0</v>
@@ -2821,10 +2848,10 @@
         <v>0</v>
       </c>
       <c r="AA11" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AB11" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AC11" s="1">
         <v>0</v>
@@ -2841,98 +2868,101 @@
       <c r="AG11" s="1">
         <v>0</v>
       </c>
-      <c r="AI11" s="1">
-        <v>50</v>
+      <c r="AH11" s="1">
+        <v>0</v>
       </c>
       <c r="AJ11" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK11" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" spans="3:36">
+    <row r="12" s="1" customFormat="1" spans="3:37">
       <c r="C12" s="1">
         <v>1007</v>
       </c>
       <c r="D12" s="1">
         <v>1007</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="E12" s="1">
+        <v>7</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G12" s="1">
-        <v>1</v>
+      <c r="G12" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
         <v>10</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="K12" s="1">
-        <v>0</v>
-      </c>
-      <c r="L12" s="6">
+      <c r="K12" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="6">
         <v>5</v>
       </c>
-      <c r="M12" s="1">
-        <v>1</v>
-      </c>
       <c r="N12" s="1">
         <v>1</v>
       </c>
       <c r="O12" s="1">
+        <v>1</v>
+      </c>
+      <c r="P12" s="1">
         <v>600</v>
       </c>
-      <c r="P12" s="1">
+      <c r="Q12" s="1">
         <v>60</v>
       </c>
-      <c r="Q12" s="1">
+      <c r="R12" s="1">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="R12" s="6">
+      <c r="S12" s="6">
         <v>10</v>
       </c>
-      <c r="S12" s="1">
-        <v>0</v>
-      </c>
       <c r="T12" s="1">
-        <v>1</v>
-      </c>
-      <c r="U12" s="1" t="s">
-        <v>69</v>
+        <v>0</v>
+      </c>
+      <c r="U12" s="1">
+        <v>1</v>
       </c>
       <c r="V12" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="W12" s="1">
-        <v>0</v>
+      <c r="W12" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="X12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z12" s="1">
         <v>0</v>
       </c>
-      <c r="AA12" s="6">
+      <c r="AA12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="6">
         <v>500</v>
       </c>
-      <c r="AB12" s="1">
-        <v>0</v>
-      </c>
       <c r="AC12" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AD12" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AE12" s="1">
         <v>0</v>
@@ -2943,84 +2973,87 @@
       <c r="AG12" s="1">
         <v>0</v>
       </c>
-      <c r="AH12" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="AI12" s="1">
-        <v>50</v>
+      <c r="AH12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="6" t="s">
+        <v>97</v>
       </c>
       <c r="AJ12" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK12" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" spans="3:36">
+    <row r="13" s="1" customFormat="1" spans="3:37">
       <c r="C13" s="1">
         <v>1008</v>
       </c>
       <c r="D13" s="1">
         <v>1008</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G13" s="1">
+      <c r="E13" s="1">
+        <v>8</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H13" s="1">
         <v>1008</v>
       </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
       <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
         <v>200</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="K13" s="1">
-        <v>0</v>
+      <c r="K13" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="L13" s="1">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1">
         <v>30</v>
       </c>
-      <c r="M13" s="1">
-        <v>1</v>
-      </c>
       <c r="N13" s="1">
         <v>1</v>
       </c>
       <c r="O13" s="1">
+        <v>1</v>
+      </c>
+      <c r="P13" s="1">
         <v>30</v>
       </c>
-      <c r="P13" s="1">
+      <c r="Q13" s="1">
         <v>3</v>
       </c>
-      <c r="Q13" s="1">
+      <c r="R13" s="1">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-      <c r="R13" s="1">
-        <v>1</v>
-      </c>
       <c r="S13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" s="1">
         <v>0</v>
       </c>
-      <c r="U13" s="1" t="s">
-        <v>69</v>
+      <c r="U13" s="1">
+        <v>0</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="W13" s="1">
+        <v>70</v>
+      </c>
+      <c r="W13" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="X13" s="1">
         <v>20</v>
       </c>
-      <c r="X13" s="1">
-        <v>0</v>
-      </c>
       <c r="Y13" s="1">
         <v>0</v>
       </c>
@@ -3028,11 +3061,11 @@
         <v>0</v>
       </c>
       <c r="AA13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="1">
         <v>30</v>
       </c>
-      <c r="AB13" s="1">
-        <v>0</v>
-      </c>
       <c r="AC13" s="1">
         <v>0</v>
       </c>
@@ -3048,101 +3081,104 @@
       <c r="AG13" s="1">
         <v>0</v>
       </c>
-      <c r="AH13" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="AI13" s="1">
-        <v>50</v>
+      <c r="AH13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="AJ13" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK13" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" spans="3:36">
+    <row r="14" s="1" customFormat="1" spans="3:37">
       <c r="C14" s="1">
         <v>1009</v>
       </c>
       <c r="D14" s="1">
         <v>1009</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="E14" s="1">
+        <v>9</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="G14" s="1">
-        <v>1</v>
+      <c r="G14" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
         <v>10</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0</v>
+      <c r="K14" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1">
         <v>15</v>
       </c>
-      <c r="M14" s="1">
+      <c r="N14" s="1">
         <v>2</v>
       </c>
-      <c r="N14" s="1">
-        <v>1</v>
-      </c>
       <c r="O14" s="1">
+        <v>1</v>
+      </c>
+      <c r="P14" s="1">
         <v>300</v>
       </c>
-      <c r="P14" s="1">
+      <c r="Q14" s="1">
         <v>30</v>
       </c>
-      <c r="Q14" s="1">
+      <c r="R14" s="1">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
-      <c r="R14" s="1">
+      <c r="S14" s="1">
         <v>12</v>
       </c>
-      <c r="S14" s="1">
-        <v>0</v>
-      </c>
       <c r="T14" s="1">
+        <v>0</v>
+      </c>
+      <c r="U14" s="1">
         <v>5</v>
-      </c>
-      <c r="U14" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="V14" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="W14" s="1">
-        <v>0</v>
+      <c r="W14" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="X14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="1">
         <v>4</v>
       </c>
-      <c r="Y14" s="1">
-        <v>0</v>
-      </c>
       <c r="Z14" s="1">
         <v>0</v>
       </c>
       <c r="AA14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="1">
         <v>600</v>
       </c>
-      <c r="AB14" s="1">
-        <v>0</v>
-      </c>
       <c r="AC14" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AD14" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AE14" s="1">
         <v>0</v>
@@ -3153,79 +3189,82 @@
       <c r="AG14" s="1">
         <v>0</v>
       </c>
-      <c r="AH14" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="AI14" s="1">
-        <v>50</v>
+      <c r="AH14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="AJ14" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK14" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" spans="3:36">
+    <row r="15" s="1" customFormat="1" spans="3:37">
       <c r="C15" s="1">
         <v>1010</v>
       </c>
       <c r="D15" s="1">
         <v>1010</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="E15" s="1">
+        <v>10</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="G15" s="1">
-        <v>1</v>
+      <c r="G15" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
         <v>10</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="K15" s="1">
+      <c r="K15" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L15" s="1">
         <v>20</v>
       </c>
-      <c r="L15" s="1">
-        <v>0</v>
-      </c>
       <c r="M15" s="1">
+        <v>0</v>
+      </c>
+      <c r="N15" s="1">
         <v>2</v>
       </c>
-      <c r="N15" s="1">
-        <v>1</v>
-      </c>
       <c r="O15" s="1">
+        <v>1</v>
+      </c>
+      <c r="P15" s="1">
         <v>10</v>
       </c>
-      <c r="P15" s="1">
-        <v>1</v>
-      </c>
       <c r="Q15" s="1">
+        <v>1</v>
+      </c>
+      <c r="R15" s="1">
         <v>250</v>
       </c>
-      <c r="R15" s="1">
+      <c r="S15" s="1">
         <v>10</v>
       </c>
-      <c r="S15" s="1">
-        <v>0</v>
-      </c>
       <c r="T15" s="1">
+        <v>0</v>
+      </c>
+      <c r="U15" s="1">
         <v>2</v>
       </c>
-      <c r="U15" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="V15" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="W15" s="1">
-        <v>0</v>
+        <v>83</v>
+      </c>
+      <c r="W15" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="X15" s="1">
         <v>0</v>
@@ -3237,11 +3276,11 @@
         <v>0</v>
       </c>
       <c r="AA15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="1">
         <v>200</v>
       </c>
-      <c r="AB15" s="1">
-        <v>0</v>
-      </c>
       <c r="AC15" s="1">
         <v>0</v>
       </c>
@@ -3257,96 +3296,99 @@
       <c r="AG15" s="1">
         <v>0</v>
       </c>
-      <c r="AI15" s="1">
-        <v>50</v>
+      <c r="AH15" s="1">
+        <v>0</v>
       </c>
       <c r="AJ15" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK15" s="1">
         <v>4102</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" spans="3:36">
+    <row r="16" s="1" customFormat="1" spans="3:37">
       <c r="C16" s="1">
         <v>1011</v>
       </c>
       <c r="D16" s="1">
         <v>1011</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G16" s="1">
+      <c r="E16" s="1">
+        <v>11</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H16" s="1">
         <v>8</v>
       </c>
-      <c r="H16" s="1">
+      <c r="I16" s="1">
         <v>11</v>
       </c>
-      <c r="I16" s="1">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="K16" s="1">
-        <v>0</v>
+      <c r="J16" s="1">
+        <v>0</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
         <v>30</v>
       </c>
-      <c r="M16" s="1">
+      <c r="N16" s="1">
         <v>2</v>
       </c>
-      <c r="N16" s="1">
-        <v>1</v>
-      </c>
       <c r="O16" s="1">
+        <v>1</v>
+      </c>
+      <c r="P16" s="1">
         <v>10</v>
       </c>
-      <c r="P16" s="1">
-        <v>1</v>
-      </c>
       <c r="Q16" s="1">
+        <v>1</v>
+      </c>
+      <c r="R16" s="1">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="R16" s="1">
-        <v>50</v>
-      </c>
       <c r="S16" s="1">
+        <v>50</v>
+      </c>
+      <c r="T16" s="1">
         <v>10</v>
       </c>
-      <c r="T16" s="1">
+      <c r="U16" s="1">
         <v>3</v>
       </c>
-      <c r="U16" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="V16" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="W16" s="1">
+        <v>83</v>
+      </c>
+      <c r="W16" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="X16" s="1">
         <v>15</v>
       </c>
-      <c r="X16" s="1">
+      <c r="Y16" s="1">
         <v>5</v>
-      </c>
-      <c r="Y16" s="1">
-        <v>4</v>
       </c>
       <c r="Z16" s="1">
         <v>4</v>
       </c>
       <c r="AA16" s="1">
+        <v>4</v>
+      </c>
+      <c r="AB16" s="1">
         <v>500</v>
       </c>
-      <c r="AB16" s="1">
+      <c r="AC16" s="1">
         <v>100</v>
       </c>
-      <c r="AC16" s="1">
-        <v>0</v>
-      </c>
       <c r="AD16" s="1">
         <v>0</v>
       </c>
@@ -3359,96 +3401,99 @@
       <c r="AG16" s="1">
         <v>0</v>
       </c>
-      <c r="AI16" s="1">
-        <v>50</v>
+      <c r="AH16" s="1">
+        <v>0</v>
       </c>
       <c r="AJ16" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK16" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" spans="6:6">
-      <c r="F17" s="2"/>
+    <row r="17" s="1" customFormat="1" spans="7:7">
+      <c r="G17" s="2"/>
     </row>
-    <row r="18" s="1" customFormat="1" spans="3:36">
+    <row r="18" s="1" customFormat="1" spans="3:37">
       <c r="C18" s="1">
         <v>2001</v>
       </c>
       <c r="D18" s="1">
         <v>2001</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>109</v>
+      <c r="E18" s="1">
+        <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="G18" s="1">
-        <v>1</v>
+      <c r="G18" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="H18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" s="1">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1">
         <v>10</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="K18" s="1">
-        <v>0</v>
+      <c r="K18" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="L18" s="1">
         <v>0</v>
       </c>
       <c r="M18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" s="1">
+        <v>1</v>
+      </c>
+      <c r="O18" s="1">
         <v>2</v>
       </c>
-      <c r="O18" s="1">
+      <c r="P18" s="1">
         <v>600</v>
       </c>
-      <c r="P18" s="1">
+      <c r="Q18" s="1">
         <v>60</v>
       </c>
-      <c r="Q18" s="1">
-        <f t="shared" ref="Q18:Q28" si="1">O18*5</f>
+      <c r="R18" s="1">
+        <f t="shared" ref="R18:R28" si="1">P18*5</f>
         <v>3000</v>
       </c>
-      <c r="R18" s="1">
+      <c r="S18" s="1">
         <v>2</v>
       </c>
-      <c r="S18" s="1">
-        <v>0</v>
-      </c>
       <c r="T18" s="1">
+        <v>0</v>
+      </c>
+      <c r="U18" s="1">
         <v>2</v>
       </c>
-      <c r="U18" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="V18" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="W18" s="1">
-        <v>0</v>
+        <v>83</v>
+      </c>
+      <c r="W18" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="X18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z18" s="1">
         <v>0</v>
       </c>
       <c r="AA18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="1">
         <v>120</v>
       </c>
-      <c r="AB18" s="1">
-        <v>0</v>
-      </c>
       <c r="AC18" s="1">
         <v>0</v>
       </c>
@@ -3464,98 +3509,101 @@
       <c r="AG18" s="1">
         <v>0</v>
       </c>
-      <c r="AI18" s="1">
-        <v>50</v>
+      <c r="AH18" s="1">
+        <v>0</v>
       </c>
       <c r="AJ18" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK18" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" spans="3:36">
+    <row r="19" s="1" customFormat="1" spans="3:37">
       <c r="C19" s="1">
         <v>2002</v>
       </c>
       <c r="D19" s="1">
         <v>2002</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F19" s="2" t="s">
+      <c r="E19" s="1">
+        <v>2</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="G19" s="1">
-        <v>1</v>
+      <c r="G19" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="H19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
         <v>10</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="K19" s="1">
-        <v>0</v>
+      <c r="K19" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="L19" s="1">
         <v>0</v>
       </c>
       <c r="M19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" s="1">
+        <v>1</v>
+      </c>
+      <c r="O19" s="1">
         <v>2</v>
       </c>
-      <c r="O19" s="1">
+      <c r="P19" s="1">
         <v>600</v>
       </c>
-      <c r="P19" s="1">
+      <c r="Q19" s="1">
         <v>60</v>
       </c>
-      <c r="Q19" s="1">
-        <f>O19*2.5</f>
+      <c r="R19" s="1">
+        <f>P19*2.5</f>
         <v>1500</v>
       </c>
-      <c r="R19" s="1">
+      <c r="S19" s="1">
         <v>3</v>
       </c>
-      <c r="S19" s="1">
-        <v>0</v>
-      </c>
       <c r="T19" s="1">
+        <v>0</v>
+      </c>
+      <c r="U19" s="1">
         <v>3</v>
       </c>
-      <c r="U19" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="V19" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="W19" s="1">
-        <v>0</v>
+        <v>83</v>
+      </c>
+      <c r="W19" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="X19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19" s="1">
         <v>0</v>
       </c>
       <c r="AA19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="1">
         <v>150</v>
       </c>
-      <c r="AB19" s="1">
-        <v>0</v>
-      </c>
       <c r="AC19" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AD19" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AE19" s="1">
         <v>0</v>
@@ -3566,93 +3614,96 @@
       <c r="AG19" s="1">
         <v>0</v>
       </c>
-      <c r="AI19" s="1">
-        <v>50</v>
+      <c r="AH19" s="1">
+        <v>0</v>
       </c>
       <c r="AJ19" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK19" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" spans="3:36">
+    <row r="20" s="1" customFormat="1" spans="3:37">
       <c r="C20" s="1">
         <v>2003</v>
       </c>
       <c r="D20" s="1">
         <v>2003</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F20" s="2" t="s">
+      <c r="E20" s="1">
+        <v>3</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H20" s="1">
         <v>3</v>
       </c>
-      <c r="H20" s="1">
-        <v>0</v>
-      </c>
       <c r="I20" s="1">
+        <v>0</v>
+      </c>
+      <c r="J20" s="1">
         <v>10</v>
       </c>
-      <c r="J20" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="K20" s="1">
-        <v>0</v>
+      <c r="K20" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="L20" s="1">
+        <v>0</v>
+      </c>
+      <c r="M20" s="1">
         <v>10</v>
-      </c>
-      <c r="M20" s="1">
-        <v>2</v>
       </c>
       <c r="N20" s="1">
         <v>2</v>
       </c>
       <c r="O20" s="1">
+        <v>2</v>
+      </c>
+      <c r="P20" s="1">
         <v>600</v>
       </c>
-      <c r="P20" s="1">
+      <c r="Q20" s="1">
         <v>60</v>
       </c>
-      <c r="Q20" s="1">
+      <c r="R20" s="1">
         <f t="shared" si="1"/>
         <v>3000</v>
       </c>
-      <c r="R20" s="1">
+      <c r="S20" s="1">
         <v>2</v>
       </c>
-      <c r="S20" s="1">
-        <v>0</v>
-      </c>
       <c r="T20" s="1">
+        <v>0</v>
+      </c>
+      <c r="U20" s="1">
         <v>3</v>
       </c>
-      <c r="U20" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="V20" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="W20" s="1">
+        <v>83</v>
+      </c>
+      <c r="W20" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="X20" s="1">
         <v>10</v>
       </c>
-      <c r="X20" s="1">
+      <c r="Y20" s="1">
         <v>5</v>
-      </c>
-      <c r="Y20" s="1">
-        <v>2</v>
       </c>
       <c r="Z20" s="1">
         <v>2</v>
       </c>
       <c r="AA20" s="1">
+        <v>2</v>
+      </c>
+      <c r="AB20" s="1">
         <v>80</v>
       </c>
-      <c r="AB20" s="1">
-        <v>0</v>
-      </c>
       <c r="AC20" s="1">
         <v>0</v>
       </c>
@@ -3668,93 +3719,96 @@
       <c r="AG20" s="1">
         <v>0</v>
       </c>
-      <c r="AI20" s="1">
-        <v>50</v>
+      <c r="AH20" s="1">
+        <v>0</v>
       </c>
       <c r="AJ20" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK20" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" spans="3:36">
+    <row r="21" s="1" customFormat="1" spans="3:37">
       <c r="C21" s="1">
         <v>2004</v>
       </c>
       <c r="D21" s="1">
         <v>2004</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F21" s="2" t="s">
+      <c r="E21" s="1">
+        <v>4</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="G21" s="1">
-        <v>1</v>
+      <c r="G21" s="2" t="s">
+        <v>120</v>
       </c>
       <c r="H21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1">
         <v>10</v>
       </c>
-      <c r="J21" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="K21" s="1">
-        <v>0</v>
+      <c r="K21" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="L21" s="1">
         <v>0</v>
       </c>
       <c r="M21" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N21" s="1">
         <v>2</v>
       </c>
       <c r="O21" s="1">
+        <v>2</v>
+      </c>
+      <c r="P21" s="1">
         <v>600</v>
       </c>
-      <c r="P21" s="1">
+      <c r="Q21" s="1">
         <v>60</v>
       </c>
-      <c r="Q21" s="1">
+      <c r="R21" s="1">
         <f t="shared" si="1"/>
         <v>3000</v>
       </c>
-      <c r="R21" s="1">
+      <c r="S21" s="1">
         <v>2</v>
       </c>
-      <c r="S21" s="1">
-        <v>0</v>
-      </c>
       <c r="T21" s="1">
+        <v>0</v>
+      </c>
+      <c r="U21" s="1">
         <v>4</v>
       </c>
-      <c r="U21" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="V21" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="W21" s="1">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="W21" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="X21" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="1">
         <v>4</v>
-      </c>
-      <c r="Y21" s="1">
-        <v>2</v>
       </c>
       <c r="Z21" s="1">
         <v>2</v>
       </c>
       <c r="AA21" s="1">
+        <v>2</v>
+      </c>
+      <c r="AB21" s="1">
         <v>100</v>
       </c>
-      <c r="AB21" s="1">
-        <v>0</v>
-      </c>
       <c r="AC21" s="1">
         <v>0</v>
       </c>
@@ -3770,84 +3824,87 @@
       <c r="AG21" s="1">
         <v>0</v>
       </c>
-      <c r="AH21" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI21" s="1">
-        <v>50</v>
+      <c r="AH21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="AJ21" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK21" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" spans="3:36">
+    <row r="22" s="1" customFormat="1" spans="3:37">
       <c r="C22" s="1">
         <v>2005</v>
       </c>
       <c r="D22" s="1">
         <v>2005</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="F22" s="2" t="s">
+      <c r="E22" s="1">
+        <v>5</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G22" s="1">
-        <v>5</v>
+      <c r="G22" s="2" t="s">
+        <v>124</v>
       </c>
       <c r="H22" s="1">
         <v>5</v>
       </c>
       <c r="I22" s="1">
-        <v>50</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="K22" s="1">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="J22" s="1">
+        <v>50</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="L22" s="1">
+        <v>0</v>
+      </c>
+      <c r="M22" s="1">
         <v>55</v>
       </c>
-      <c r="M22" s="1">
-        <v>1</v>
-      </c>
       <c r="N22" s="1">
+        <v>1</v>
+      </c>
+      <c r="O22" s="1">
         <v>2</v>
       </c>
-      <c r="O22" s="1">
+      <c r="P22" s="1">
         <v>200</v>
       </c>
-      <c r="P22" s="1">
+      <c r="Q22" s="1">
         <v>20</v>
       </c>
-      <c r="Q22" s="1">
+      <c r="R22" s="1">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="R22" s="1">
-        <v>1</v>
-      </c>
       <c r="S22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22" s="1">
         <v>0</v>
       </c>
-      <c r="U22" s="1" t="s">
-        <v>69</v>
+      <c r="U22" s="1">
+        <v>0</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="W22" s="1">
+        <v>70</v>
+      </c>
+      <c r="W22" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="X22" s="1">
         <v>30</v>
       </c>
-      <c r="X22" s="1">
-        <v>0</v>
-      </c>
       <c r="Y22" s="1">
         <v>0</v>
       </c>
@@ -3855,11 +3912,11 @@
         <v>0</v>
       </c>
       <c r="AA22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="1">
         <v>100</v>
       </c>
-      <c r="AB22" s="1">
-        <v>0</v>
-      </c>
       <c r="AC22" s="1">
         <v>0</v>
       </c>
@@ -3875,80 +3932,83 @@
       <c r="AG22" s="1">
         <v>0</v>
       </c>
-      <c r="AH22" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="AI22" s="1">
-        <v>50</v>
+      <c r="AH22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="AJ22" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK22" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" spans="3:36">
+    <row r="23" s="1" customFormat="1" spans="3:37">
       <c r="C23" s="1">
         <v>2006</v>
       </c>
       <c r="D23" s="1">
         <v>2006</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>124</v>
+      <c r="E23" s="1">
+        <v>6</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="G23" s="1">
+        <v>125</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H23" s="1">
         <v>6</v>
       </c>
-      <c r="H23" s="1">
-        <v>0</v>
-      </c>
       <c r="I23" s="1">
+        <v>0</v>
+      </c>
+      <c r="J23" s="1">
         <v>10</v>
       </c>
-      <c r="J23" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="K23" s="1">
-        <v>0</v>
+      <c r="K23" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="L23" s="1">
         <v>0</v>
       </c>
       <c r="M23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" s="1">
+        <v>1</v>
+      </c>
+      <c r="O23" s="1">
         <v>2</v>
       </c>
-      <c r="O23" s="1">
+      <c r="P23" s="1">
         <v>200</v>
       </c>
-      <c r="P23" s="1">
+      <c r="Q23" s="1">
         <v>20</v>
       </c>
-      <c r="Q23" s="1">
+      <c r="R23" s="1">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="R23" s="1">
-        <v>1</v>
-      </c>
       <c r="S23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T23" s="1">
         <v>0</v>
       </c>
-      <c r="U23" s="1" t="s">
-        <v>69</v>
+      <c r="U23" s="1">
+        <v>0</v>
       </c>
       <c r="V23" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="W23" s="1">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="W23" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="X23" s="1">
         <v>0</v>
@@ -3960,10 +4020,10 @@
         <v>0</v>
       </c>
       <c r="AA23" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AB23" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AC23" s="1">
         <v>0</v>
@@ -3980,93 +4040,96 @@
       <c r="AG23" s="1">
         <v>0</v>
       </c>
-      <c r="AI23" s="1">
-        <v>50</v>
+      <c r="AH23" s="1">
+        <v>0</v>
       </c>
       <c r="AJ23" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK23" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" spans="3:36">
+    <row r="24" s="1" customFormat="1" spans="3:37">
       <c r="C24" s="1">
         <v>2007</v>
       </c>
       <c r="D24" s="1">
         <v>2007</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F24" s="2" t="s">
+      <c r="E24" s="1">
+        <v>7</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="G24" s="1">
-        <v>1</v>
+      <c r="G24" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="H24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" s="1">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1">
         <v>10</v>
       </c>
-      <c r="J24" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="K24" s="1">
-        <v>0</v>
-      </c>
-      <c r="L24" s="6">
+      <c r="K24" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="L24" s="1">
+        <v>0</v>
+      </c>
+      <c r="M24" s="6">
         <v>5</v>
-      </c>
-      <c r="M24" s="1">
-        <v>2</v>
       </c>
       <c r="N24" s="1">
         <v>2</v>
       </c>
       <c r="O24" s="1">
+        <v>2</v>
+      </c>
+      <c r="P24" s="1">
         <v>600</v>
       </c>
-      <c r="P24" s="1">
+      <c r="Q24" s="1">
         <v>60</v>
       </c>
-      <c r="Q24" s="1">
+      <c r="R24" s="1">
         <f t="shared" si="1"/>
         <v>3000</v>
       </c>
-      <c r="R24" s="6">
+      <c r="S24" s="6">
         <v>6</v>
       </c>
-      <c r="S24" s="1">
-        <v>0</v>
-      </c>
       <c r="T24" s="1">
+        <v>0</v>
+      </c>
+      <c r="U24" s="1">
         <v>5</v>
       </c>
-      <c r="U24" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="V24" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="W24" s="1">
-        <v>0</v>
+        <v>83</v>
+      </c>
+      <c r="W24" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="X24" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="1">
         <v>5</v>
-      </c>
-      <c r="Y24" s="1">
-        <v>3</v>
       </c>
       <c r="Z24" s="1">
         <v>3</v>
       </c>
-      <c r="AA24" s="6">
+      <c r="AA24" s="1">
+        <v>3</v>
+      </c>
+      <c r="AB24" s="6">
         <v>300</v>
       </c>
-      <c r="AB24" s="1">
-        <v>0</v>
-      </c>
       <c r="AC24" s="1">
         <v>0</v>
       </c>
@@ -4082,80 +4145,83 @@
       <c r="AG24" s="1">
         <v>0</v>
       </c>
-      <c r="AH24" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="AI24" s="1">
-        <v>50</v>
+      <c r="AH24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="6" t="s">
+        <v>129</v>
       </c>
       <c r="AJ24" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK24" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" spans="3:36">
+    <row r="25" s="1" customFormat="1" spans="3:37">
       <c r="C25" s="1">
         <v>2008</v>
       </c>
       <c r="D25" s="1">
         <v>2008</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="F25" s="2" t="s">
+      <c r="E25" s="1">
+        <v>8</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="G25" s="1">
+      <c r="G25" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H25" s="1">
         <v>2008</v>
       </c>
-      <c r="H25" s="1">
-        <v>0</v>
-      </c>
       <c r="I25" s="1">
+        <v>0</v>
+      </c>
+      <c r="J25" s="1">
         <v>200</v>
       </c>
-      <c r="J25" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="K25" s="1">
-        <v>0</v>
+      <c r="K25" s="1" t="s">
+        <v>132</v>
       </c>
       <c r="L25" s="1">
+        <v>0</v>
+      </c>
+      <c r="M25" s="1">
         <v>30</v>
       </c>
-      <c r="M25" s="1">
-        <v>1</v>
-      </c>
       <c r="N25" s="1">
+        <v>1</v>
+      </c>
+      <c r="O25" s="1">
         <v>2</v>
       </c>
-      <c r="O25" s="1">
+      <c r="P25" s="1">
         <v>30</v>
       </c>
-      <c r="P25" s="1">
+      <c r="Q25" s="1">
         <v>3</v>
       </c>
-      <c r="Q25" s="1">
+      <c r="R25" s="1">
         <f t="shared" si="1"/>
         <v>150</v>
       </c>
-      <c r="R25" s="1">
-        <v>1</v>
-      </c>
       <c r="S25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25" s="1">
         <v>0</v>
       </c>
-      <c r="U25" s="1" t="s">
-        <v>69</v>
+      <c r="U25" s="1">
+        <v>0</v>
       </c>
       <c r="V25" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="W25" s="1">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="W25" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="X25" s="1">
         <v>0</v>
@@ -4167,10 +4233,10 @@
         <v>0</v>
       </c>
       <c r="AA25" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AB25" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AC25" s="1">
         <v>0</v>
@@ -4187,96 +4253,99 @@
       <c r="AG25" s="1">
         <v>0</v>
       </c>
-      <c r="AH25" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="AI25" s="1">
-        <v>50</v>
+      <c r="AH25" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="AJ25" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK25" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" spans="3:36">
+    <row r="26" s="1" customFormat="1" spans="3:37">
       <c r="C26" s="1">
         <v>2009</v>
       </c>
       <c r="D26" s="1">
         <v>2009</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="F26" s="2" t="s">
+      <c r="E26" s="1">
+        <v>9</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="G26" s="1">
+      <c r="G26" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="H26" s="1">
         <v>3</v>
       </c>
-      <c r="H26" s="1">
-        <v>0</v>
-      </c>
       <c r="I26" s="1">
+        <v>0</v>
+      </c>
+      <c r="J26" s="1">
         <v>10</v>
       </c>
-      <c r="J26" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="K26" s="1">
-        <v>0</v>
+      <c r="K26" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="L26" s="1">
+        <v>0</v>
+      </c>
+      <c r="M26" s="1">
         <v>15</v>
-      </c>
-      <c r="M26" s="1">
-        <v>2</v>
       </c>
       <c r="N26" s="1">
         <v>2</v>
       </c>
       <c r="O26" s="1">
+        <v>2</v>
+      </c>
+      <c r="P26" s="1">
         <v>300</v>
       </c>
-      <c r="P26" s="1">
+      <c r="Q26" s="1">
         <v>30</v>
       </c>
-      <c r="Q26" s="1">
+      <c r="R26" s="1">
         <f t="shared" si="1"/>
         <v>1500</v>
       </c>
-      <c r="R26" s="1">
+      <c r="S26" s="1">
         <v>7</v>
       </c>
-      <c r="S26" s="1">
-        <v>0</v>
-      </c>
       <c r="T26" s="1">
+        <v>0</v>
+      </c>
+      <c r="U26" s="1">
         <v>3</v>
       </c>
-      <c r="U26" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="V26" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="W26" s="1">
+        <v>83</v>
+      </c>
+      <c r="W26" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="X26" s="1">
         <v>10</v>
       </c>
-      <c r="X26" s="1">
+      <c r="Y26" s="1">
         <v>5</v>
-      </c>
-      <c r="Y26" s="1">
-        <v>4</v>
       </c>
       <c r="Z26" s="1">
         <v>4</v>
       </c>
       <c r="AA26" s="1">
+        <v>4</v>
+      </c>
+      <c r="AB26" s="1">
         <v>400</v>
       </c>
-      <c r="AB26" s="1">
-        <v>0</v>
-      </c>
       <c r="AC26" s="1">
         <v>0</v>
       </c>
@@ -4292,96 +4361,99 @@
       <c r="AG26" s="1">
         <v>0</v>
       </c>
-      <c r="AH26" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AI26" s="1">
-        <v>50</v>
+      <c r="AH26" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="1" t="s">
+        <v>137</v>
       </c>
       <c r="AJ26" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK26" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" spans="3:36">
+    <row r="27" s="1" customFormat="1" spans="3:37">
       <c r="C27" s="1">
         <v>2010</v>
       </c>
       <c r="D27" s="1">
         <v>2010</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G27" s="1">
+      <c r="E27" s="1">
+        <v>10</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H27" s="1">
         <v>2010</v>
       </c>
-      <c r="H27" s="1">
-        <v>0</v>
-      </c>
       <c r="I27" s="1">
+        <v>0</v>
+      </c>
+      <c r="J27" s="1">
         <v>100</v>
       </c>
-      <c r="J27" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="K27" s="1">
-        <v>0</v>
+      <c r="K27" s="2" t="s">
+        <v>139</v>
       </c>
       <c r="L27" s="1">
+        <v>0</v>
+      </c>
+      <c r="M27" s="1">
         <v>30</v>
-      </c>
-      <c r="M27" s="1">
-        <v>2</v>
       </c>
       <c r="N27" s="1">
         <v>2</v>
       </c>
       <c r="O27" s="1">
+        <v>2</v>
+      </c>
+      <c r="P27" s="1">
         <v>10</v>
       </c>
-      <c r="P27" s="1">
-        <v>1</v>
-      </c>
       <c r="Q27" s="1">
+        <v>1</v>
+      </c>
+      <c r="R27" s="1">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="R27" s="1">
+      <c r="S27" s="1">
         <v>5</v>
       </c>
-      <c r="S27" s="1">
-        <v>0</v>
-      </c>
       <c r="T27" s="1">
+        <v>0</v>
+      </c>
+      <c r="U27" s="1">
         <v>3</v>
       </c>
-      <c r="U27" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="V27" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="W27" s="1">
+        <v>83</v>
+      </c>
+      <c r="W27" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="X27" s="1">
         <v>15</v>
       </c>
-      <c r="X27" s="1">
+      <c r="Y27" s="1">
         <v>5</v>
-      </c>
-      <c r="Y27" s="1">
-        <v>4</v>
       </c>
       <c r="Z27" s="1">
         <v>4</v>
       </c>
       <c r="AA27" s="1">
+        <v>4</v>
+      </c>
+      <c r="AB27" s="1">
         <v>150</v>
       </c>
-      <c r="AB27" s="1">
-        <v>0</v>
-      </c>
       <c r="AC27" s="1">
         <v>0</v>
       </c>
@@ -4397,96 +4469,99 @@
       <c r="AG27" s="1">
         <v>0</v>
       </c>
-      <c r="AI27" s="1">
-        <v>50</v>
+      <c r="AH27" s="1">
+        <v>0</v>
       </c>
       <c r="AJ27" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK27" s="1">
         <v>4102</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" spans="3:36">
+    <row r="28" s="1" customFormat="1" spans="3:37">
       <c r="C28" s="1">
         <v>2011</v>
       </c>
       <c r="D28" s="1">
         <v>2011</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="G28" s="1">
+      <c r="E28" s="1">
+        <v>11</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H28" s="1">
         <v>8</v>
       </c>
-      <c r="H28" s="1">
+      <c r="I28" s="1">
         <v>11</v>
       </c>
-      <c r="I28" s="1">
-        <v>0</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="K28" s="1">
-        <v>0</v>
+      <c r="J28" s="1">
+        <v>0</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="L28" s="1">
+        <v>0</v>
+      </c>
+      <c r="M28" s="1">
         <v>30</v>
-      </c>
-      <c r="M28" s="1">
-        <v>2</v>
       </c>
       <c r="N28" s="1">
         <v>2</v>
       </c>
       <c r="O28" s="1">
+        <v>2</v>
+      </c>
+      <c r="P28" s="1">
         <v>10</v>
       </c>
-      <c r="P28" s="1">
-        <v>1</v>
-      </c>
       <c r="Q28" s="1">
+        <v>1</v>
+      </c>
+      <c r="R28" s="1">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="R28" s="1">
-        <v>50</v>
-      </c>
       <c r="S28" s="1">
+        <v>50</v>
+      </c>
+      <c r="T28" s="1">
         <v>10</v>
       </c>
-      <c r="T28" s="1">
+      <c r="U28" s="1">
         <v>3</v>
       </c>
-      <c r="U28" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="V28" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="W28" s="1">
+        <v>83</v>
+      </c>
+      <c r="W28" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="X28" s="1">
         <v>15</v>
       </c>
-      <c r="X28" s="1">
+      <c r="Y28" s="1">
         <v>5</v>
-      </c>
-      <c r="Y28" s="1">
-        <v>4</v>
       </c>
       <c r="Z28" s="1">
         <v>4</v>
       </c>
       <c r="AA28" s="1">
+        <v>4</v>
+      </c>
+      <c r="AB28" s="1">
         <v>500</v>
       </c>
-      <c r="AB28" s="1">
+      <c r="AC28" s="1">
         <v>100</v>
       </c>
-      <c r="AC28" s="1">
-        <v>0</v>
-      </c>
       <c r="AD28" s="1">
         <v>0</v>
       </c>
@@ -4499,79 +4574,82 @@
       <c r="AG28" s="1">
         <v>0</v>
       </c>
-      <c r="AI28" s="1">
-        <v>50</v>
+      <c r="AH28" s="1">
+        <v>0</v>
       </c>
       <c r="AJ28" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK28" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" spans="6:6">
-      <c r="F29" s="2"/>
+    <row r="29" s="1" customFormat="1" spans="7:7">
+      <c r="G29" s="2"/>
     </row>
-    <row r="30" s="1" customFormat="1" spans="3:36">
+    <row r="30" s="1" customFormat="1" spans="3:37">
       <c r="C30" s="1">
         <v>3001</v>
       </c>
       <c r="D30" s="1">
         <v>3001</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="F30" s="2" t="s">
+      <c r="E30" s="1">
+        <v>1</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="G30" s="1">
+      <c r="G30" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H30" s="1">
         <v>4</v>
       </c>
-      <c r="H30" s="1">
-        <v>0</v>
-      </c>
       <c r="I30" s="1">
+        <v>0</v>
+      </c>
+      <c r="J30" s="1">
         <v>20</v>
       </c>
-      <c r="J30" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="K30" s="1">
-        <v>0</v>
+      <c r="K30" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="L30" s="1">
+        <v>0</v>
+      </c>
+      <c r="M30" s="1">
         <v>4</v>
       </c>
-      <c r="M30" s="1">
-        <v>1</v>
-      </c>
       <c r="N30" s="1">
+        <v>1</v>
+      </c>
+      <c r="O30" s="1">
         <v>3</v>
       </c>
-      <c r="O30" s="1">
+      <c r="P30" s="1">
         <v>600</v>
       </c>
-      <c r="P30" s="1">
+      <c r="Q30" s="1">
         <v>60</v>
       </c>
-      <c r="Q30" s="1">
+      <c r="R30" s="1">
         <v>20</v>
       </c>
-      <c r="R30" s="1">
+      <c r="S30" s="1">
         <v>3</v>
       </c>
-      <c r="S30" s="1">
-        <v>0</v>
-      </c>
       <c r="T30" s="1">
+        <v>0</v>
+      </c>
+      <c r="U30" s="1">
         <v>5</v>
       </c>
-      <c r="U30" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="V30" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="W30" s="1">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="W30" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="X30" s="1">
         <v>0</v>
@@ -4583,10 +4661,10 @@
         <v>0</v>
       </c>
       <c r="AA30" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AB30" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AC30" s="1">
         <v>0</v>
@@ -4603,93 +4681,96 @@
       <c r="AG30" s="1">
         <v>0</v>
       </c>
-      <c r="AI30" s="1">
-        <v>50</v>
+      <c r="AH30" s="1">
+        <v>0</v>
       </c>
       <c r="AJ30" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK30" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" spans="3:36">
+    <row r="31" s="1" customFormat="1" spans="3:37">
       <c r="C31" s="1">
         <v>3002</v>
       </c>
       <c r="D31" s="1">
         <v>3002</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>144</v>
+      <c r="E31" s="1">
+        <v>2</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="G31" s="1">
-        <v>1</v>
+      <c r="G31" s="1" t="s">
+        <v>146</v>
       </c>
       <c r="H31" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" s="1">
+        <v>0</v>
+      </c>
+      <c r="J31" s="1">
         <v>10</v>
       </c>
-      <c r="J31" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="K31" s="1">
-        <v>0</v>
+      <c r="K31" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="L31" s="1">
         <v>0</v>
       </c>
       <c r="M31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" s="1">
+        <v>1</v>
+      </c>
+      <c r="O31" s="1">
         <v>3</v>
       </c>
-      <c r="O31" s="1">
+      <c r="P31" s="1">
         <v>600</v>
       </c>
-      <c r="P31" s="1">
+      <c r="Q31" s="1">
         <v>60</v>
       </c>
-      <c r="Q31" s="1">
-        <f>O31*1.8</f>
+      <c r="R31" s="1">
+        <f>P31*1.8</f>
         <v>1080</v>
       </c>
-      <c r="R31" s="1">
+      <c r="S31" s="1">
         <v>2</v>
       </c>
-      <c r="S31" s="1">
-        <v>0</v>
-      </c>
       <c r="T31" s="1">
+        <v>0</v>
+      </c>
+      <c r="U31" s="1">
         <v>3</v>
       </c>
-      <c r="U31" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="V31" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="W31" s="1">
-        <v>0</v>
+        <v>83</v>
+      </c>
+      <c r="W31" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="X31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y31" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z31" s="1">
         <v>0</v>
       </c>
       <c r="AA31" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="1">
         <v>120</v>
       </c>
-      <c r="AB31" s="1">
-        <v>0</v>
-      </c>
       <c r="AC31" s="1">
         <v>0</v>
       </c>
@@ -4705,99 +4786,102 @@
       <c r="AG31" s="1">
         <v>0</v>
       </c>
-      <c r="AI31" s="1">
-        <v>50</v>
+      <c r="AH31" s="1">
+        <v>0</v>
       </c>
       <c r="AJ31" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK31" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" spans="3:36">
+    <row r="32" s="1" customFormat="1" spans="3:37">
       <c r="C32" s="1">
         <v>3003</v>
       </c>
       <c r="D32" s="1">
         <v>3003</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="F32" s="2" t="s">
+      <c r="E32" s="1">
+        <v>3</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="G32" s="1">
-        <v>1</v>
+      <c r="G32" s="2" t="s">
+        <v>149</v>
       </c>
       <c r="H32" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" s="1">
+        <v>0</v>
+      </c>
+      <c r="J32" s="1">
         <v>10</v>
       </c>
-      <c r="J32" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="K32" s="1">
-        <v>0</v>
+      <c r="K32" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="L32" s="1">
+        <v>0</v>
+      </c>
+      <c r="M32" s="1">
         <v>10</v>
       </c>
-      <c r="M32" s="1">
-        <v>1</v>
-      </c>
       <c r="N32" s="1">
+        <v>1</v>
+      </c>
+      <c r="O32" s="1">
         <v>3</v>
       </c>
-      <c r="O32" s="1">
+      <c r="P32" s="1">
         <v>600</v>
       </c>
-      <c r="P32" s="1">
+      <c r="Q32" s="1">
         <v>60</v>
       </c>
-      <c r="Q32" s="1">
-        <f t="shared" ref="Q30:Q40" si="2">O32*5</f>
+      <c r="R32" s="1">
+        <f t="shared" ref="R30:R40" si="2">P32*5</f>
         <v>3000</v>
       </c>
-      <c r="R32" s="1">
+      <c r="S32" s="1">
         <v>2</v>
       </c>
-      <c r="S32" s="1">
-        <v>0</v>
-      </c>
       <c r="T32" s="1">
+        <v>0</v>
+      </c>
+      <c r="U32" s="1">
         <v>2</v>
       </c>
-      <c r="U32" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="V32" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="W32" s="1">
-        <v>0</v>
+        <v>83</v>
+      </c>
+      <c r="W32" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="X32" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="1">
         <v>5</v>
       </c>
-      <c r="Y32" s="1">
-        <v>0</v>
-      </c>
       <c r="Z32" s="1">
         <v>0</v>
       </c>
       <c r="AA32" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="1">
         <v>35</v>
       </c>
-      <c r="AB32" s="1">
-        <v>0</v>
-      </c>
       <c r="AC32" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="1">
         <v>60</v>
       </c>
-      <c r="AD32" s="1">
-        <v>0</v>
-      </c>
       <c r="AE32" s="1">
         <v>0</v>
       </c>
@@ -4807,96 +4891,99 @@
       <c r="AG32" s="1">
         <v>0</v>
       </c>
-      <c r="AH32" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="AI32" s="1">
-        <v>50</v>
+      <c r="AH32" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="1" t="s">
+        <v>151</v>
       </c>
       <c r="AJ32" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK32" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" spans="3:36">
+    <row r="33" s="1" customFormat="1" spans="3:37">
       <c r="C33" s="1">
         <v>3004</v>
       </c>
       <c r="D33" s="1">
         <v>3004</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="F33" s="2" t="s">
+      <c r="E33" s="1">
+        <v>4</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="G33" s="1">
+      <c r="G33" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="H33" s="1">
         <v>2</v>
       </c>
-      <c r="H33" s="1">
+      <c r="I33" s="1">
         <v>6</v>
       </c>
-      <c r="I33" s="1">
+      <c r="J33" s="1">
         <v>100</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="K33" s="1">
-        <v>0</v>
+      <c r="K33" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="L33" s="1">
+        <v>0</v>
+      </c>
+      <c r="M33" s="1">
         <v>15</v>
       </c>
-      <c r="M33" s="1">
-        <v>1</v>
-      </c>
       <c r="N33" s="1">
+        <v>1</v>
+      </c>
+      <c r="O33" s="1">
         <v>3</v>
       </c>
-      <c r="O33" s="1">
+      <c r="P33" s="1">
         <v>600</v>
       </c>
-      <c r="P33" s="1">
+      <c r="Q33" s="1">
         <v>60</v>
       </c>
-      <c r="Q33" s="1">
+      <c r="R33" s="1">
         <f t="shared" si="2"/>
         <v>3000</v>
       </c>
-      <c r="R33" s="1">
+      <c r="S33" s="1">
         <v>2</v>
       </c>
-      <c r="S33" s="1">
-        <v>0</v>
-      </c>
       <c r="T33" s="1">
         <v>0</v>
       </c>
-      <c r="U33" s="1" t="s">
-        <v>69</v>
+      <c r="U33" s="1">
+        <v>0</v>
       </c>
       <c r="V33" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="W33" s="1">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="W33" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="X33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y33" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z33" s="1">
         <v>0</v>
       </c>
       <c r="AA33" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="1">
         <v>100</v>
       </c>
-      <c r="AB33" s="1">
-        <v>0</v>
-      </c>
       <c r="AC33" s="1">
         <v>0</v>
       </c>
@@ -4912,81 +4999,84 @@
       <c r="AG33" s="1">
         <v>0</v>
       </c>
-      <c r="AI33" s="1">
-        <v>50</v>
+      <c r="AH33" s="1">
+        <v>0</v>
       </c>
       <c r="AJ33" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK33" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" spans="3:36">
+    <row r="34" s="1" customFormat="1" spans="3:37">
       <c r="C34" s="1">
         <v>3005</v>
       </c>
       <c r="D34" s="1">
         <v>3005</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="G34" s="1">
+      <c r="E34" s="1">
         <v>5</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="H34" s="1">
         <v>5</v>
       </c>
       <c r="I34" s="1">
-        <v>50</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="K34" s="1">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="J34" s="1">
+        <v>50</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="L34" s="1">
+        <v>0</v>
+      </c>
+      <c r="M34" s="1">
         <v>55</v>
       </c>
-      <c r="M34" s="1">
-        <v>1</v>
-      </c>
       <c r="N34" s="1">
+        <v>1</v>
+      </c>
+      <c r="O34" s="1">
         <v>3</v>
       </c>
-      <c r="O34" s="1">
+      <c r="P34" s="1">
         <v>200</v>
       </c>
-      <c r="P34" s="1">
+      <c r="Q34" s="1">
         <v>20</v>
       </c>
-      <c r="Q34" s="1">
+      <c r="R34" s="1">
         <f t="shared" si="2"/>
         <v>1000</v>
       </c>
-      <c r="R34" s="1">
-        <v>1</v>
-      </c>
       <c r="S34" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T34" s="1">
         <v>0</v>
       </c>
-      <c r="U34" s="1" t="s">
-        <v>69</v>
+      <c r="U34" s="1">
+        <v>0</v>
       </c>
       <c r="V34" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="W34" s="1">
+        <v>70</v>
+      </c>
+      <c r="W34" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="X34" s="1">
         <v>30</v>
       </c>
-      <c r="X34" s="1">
-        <v>0</v>
-      </c>
       <c r="Y34" s="1">
         <v>0</v>
       </c>
@@ -4994,11 +5084,11 @@
         <v>0</v>
       </c>
       <c r="AA34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="1">
         <v>100</v>
       </c>
-      <c r="AB34" s="1">
-        <v>0</v>
-      </c>
       <c r="AC34" s="1">
         <v>0</v>
       </c>
@@ -5014,80 +5104,83 @@
       <c r="AG34" s="1">
         <v>0</v>
       </c>
-      <c r="AH34" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="AI34" s="1">
-        <v>50</v>
+      <c r="AH34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="AJ34" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK34" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" spans="3:36">
+    <row r="35" s="1" customFormat="1" spans="3:37">
       <c r="C35" s="1">
         <v>3006</v>
       </c>
       <c r="D35" s="1">
         <v>3006</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>155</v>
+      <c r="E35" s="1">
+        <v>6</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="G35" s="1">
+        <v>156</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H35" s="1">
         <v>6</v>
       </c>
-      <c r="H35" s="1">
-        <v>0</v>
-      </c>
       <c r="I35" s="1">
+        <v>0</v>
+      </c>
+      <c r="J35" s="1">
         <v>10</v>
       </c>
-      <c r="J35" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="K35" s="1">
-        <v>0</v>
+      <c r="K35" s="1" t="s">
+        <v>157</v>
       </c>
       <c r="L35" s="1">
         <v>0</v>
       </c>
       <c r="M35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" s="1">
+        <v>1</v>
+      </c>
+      <c r="O35" s="1">
         <v>3</v>
       </c>
-      <c r="O35" s="1">
+      <c r="P35" s="1">
         <v>200</v>
       </c>
-      <c r="P35" s="1">
+      <c r="Q35" s="1">
         <v>20</v>
       </c>
-      <c r="Q35" s="1">
+      <c r="R35" s="1">
         <f t="shared" si="2"/>
         <v>1000</v>
       </c>
-      <c r="R35" s="1">
-        <v>1</v>
-      </c>
       <c r="S35" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T35" s="1">
+        <v>0</v>
+      </c>
+      <c r="U35" s="1">
         <v>3</v>
       </c>
-      <c r="U35" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="V35" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="W35" s="1">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="W35" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="X35" s="1">
         <v>0</v>
@@ -5099,10 +5192,10 @@
         <v>0</v>
       </c>
       <c r="AA35" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AB35" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AC35" s="1">
         <v>0</v>
@@ -5119,93 +5212,96 @@
       <c r="AG35" s="1">
         <v>0</v>
       </c>
-      <c r="AI35" s="1">
-        <v>50</v>
+      <c r="AH35" s="1">
+        <v>0</v>
       </c>
       <c r="AJ35" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK35" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" spans="3:36">
+    <row r="36" s="1" customFormat="1" spans="3:37">
       <c r="C36" s="1">
         <v>3007</v>
       </c>
       <c r="D36" s="1">
         <v>3007</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="F36" s="2" t="s">
+      <c r="E36" s="1">
+        <v>7</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="G36" s="1">
+      <c r="G36" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H36" s="1">
         <v>2</v>
       </c>
-      <c r="H36" s="1">
+      <c r="I36" s="1">
         <v>6</v>
       </c>
-      <c r="I36" s="1">
+      <c r="J36" s="1">
         <v>100</v>
       </c>
-      <c r="J36" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="K36" s="1">
-        <v>0</v>
+      <c r="K36" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="L36" s="1">
+        <v>0</v>
+      </c>
+      <c r="M36" s="1">
         <v>30</v>
       </c>
-      <c r="M36" s="1">
-        <v>1</v>
-      </c>
       <c r="N36" s="1">
+        <v>1</v>
+      </c>
+      <c r="O36" s="1">
         <v>3</v>
       </c>
-      <c r="O36" s="1">
+      <c r="P36" s="1">
         <v>600</v>
       </c>
-      <c r="P36" s="1">
+      <c r="Q36" s="1">
         <v>60</v>
       </c>
-      <c r="Q36" s="1">
+      <c r="R36" s="1">
         <f t="shared" si="2"/>
         <v>3000</v>
       </c>
-      <c r="R36" s="1">
+      <c r="S36" s="1">
         <v>3</v>
       </c>
-      <c r="S36" s="1">
-        <v>0</v>
-      </c>
       <c r="T36" s="1">
+        <v>0</v>
+      </c>
+      <c r="U36" s="1">
         <v>2</v>
       </c>
-      <c r="U36" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="V36" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="W36" s="1">
-        <v>0</v>
+        <v>83</v>
+      </c>
+      <c r="W36" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="X36" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="1">
         <v>2</v>
       </c>
-      <c r="Y36" s="1">
-        <v>0</v>
-      </c>
       <c r="Z36" s="1">
         <v>0</v>
       </c>
       <c r="AA36" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="1">
         <v>120</v>
       </c>
-      <c r="AB36" s="1">
-        <v>0</v>
-      </c>
       <c r="AC36" s="1">
         <v>0</v>
       </c>
@@ -5221,81 +5317,84 @@
       <c r="AG36" s="1">
         <v>0</v>
       </c>
-      <c r="AI36" s="1">
-        <v>50</v>
+      <c r="AH36" s="1">
+        <v>0</v>
       </c>
       <c r="AJ36" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK36" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" spans="3:36">
+    <row r="37" s="1" customFormat="1" spans="3:37">
       <c r="C37" s="1">
         <v>3008</v>
       </c>
       <c r="D37" s="1">
         <v>3008</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="F37" s="2" t="s">
+      <c r="E37" s="1">
+        <v>8</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="G37" s="1">
+      <c r="G37" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="H37" s="1">
         <v>3008</v>
       </c>
-      <c r="H37" s="1">
-        <v>0</v>
-      </c>
       <c r="I37" s="1">
+        <v>0</v>
+      </c>
+      <c r="J37" s="1">
         <v>200</v>
       </c>
-      <c r="J37" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="K37" s="1">
-        <v>0</v>
+      <c r="K37" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="L37" s="1">
+        <v>0</v>
+      </c>
+      <c r="M37" s="1">
         <v>30</v>
       </c>
-      <c r="M37" s="1">
-        <v>1</v>
-      </c>
       <c r="N37" s="1">
+        <v>1</v>
+      </c>
+      <c r="O37" s="1">
         <v>3</v>
       </c>
-      <c r="O37" s="1">
+      <c r="P37" s="1">
         <v>30</v>
       </c>
-      <c r="P37" s="1">
+      <c r="Q37" s="1">
         <v>3</v>
       </c>
-      <c r="Q37" s="1">
+      <c r="R37" s="1">
         <f t="shared" si="2"/>
         <v>150</v>
       </c>
-      <c r="R37" s="1">
-        <v>1</v>
-      </c>
       <c r="S37" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T37" s="1">
         <v>0</v>
       </c>
-      <c r="U37" s="1" t="s">
-        <v>69</v>
+      <c r="U37" s="1">
+        <v>0</v>
       </c>
       <c r="V37" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="W37" s="1">
+        <v>70</v>
+      </c>
+      <c r="W37" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="X37" s="1">
         <v>5</v>
       </c>
-      <c r="X37" s="1">
-        <v>0</v>
-      </c>
       <c r="Y37" s="1">
         <v>0</v>
       </c>
@@ -5303,11 +5402,11 @@
         <v>0</v>
       </c>
       <c r="AA37" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="1">
         <v>30</v>
       </c>
-      <c r="AB37" s="1">
-        <v>0</v>
-      </c>
       <c r="AC37" s="1">
         <v>0</v>
       </c>
@@ -5323,95 +5422,98 @@
       <c r="AG37" s="1">
         <v>0</v>
       </c>
-      <c r="AH37" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="AI37" s="1">
-        <v>50</v>
+      <c r="AH37" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI37" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="AJ37" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK37" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" spans="3:36">
+    <row r="38" s="1" customFormat="1" spans="3:37">
       <c r="C38" s="1">
         <v>3009</v>
       </c>
       <c r="D38" s="1">
         <v>3009</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F38" s="2" t="s">
+      <c r="E38" s="1">
+        <v>9</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="G38" s="1">
+      <c r="G38" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="H38" s="1">
         <v>2</v>
       </c>
-      <c r="H38" s="1">
+      <c r="I38" s="1">
         <v>6</v>
       </c>
-      <c r="I38" s="1">
+      <c r="J38" s="1">
         <v>100</v>
       </c>
-      <c r="J38" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="K38" s="1">
-        <v>0</v>
+      <c r="K38" s="1" t="s">
+        <v>167</v>
       </c>
       <c r="L38" s="1">
+        <v>0</v>
+      </c>
+      <c r="M38" s="1">
         <v>30</v>
       </c>
-      <c r="M38" s="1">
-        <v>1</v>
-      </c>
       <c r="N38" s="1">
+        <v>1</v>
+      </c>
+      <c r="O38" s="1">
         <v>3</v>
       </c>
-      <c r="O38" s="1">
+      <c r="P38" s="1">
         <v>300</v>
       </c>
-      <c r="P38" s="1">
+      <c r="Q38" s="1">
         <v>30</v>
       </c>
-      <c r="Q38" s="1">
+      <c r="R38" s="1">
         <v>200</v>
       </c>
-      <c r="R38" s="1">
+      <c r="S38" s="1">
         <v>4</v>
       </c>
-      <c r="S38" s="1">
-        <v>0</v>
-      </c>
       <c r="T38" s="1">
+        <v>0</v>
+      </c>
+      <c r="U38" s="1">
         <v>2</v>
       </c>
-      <c r="U38" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="V38" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="W38" s="1">
-        <v>0</v>
+        <v>83</v>
+      </c>
+      <c r="W38" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="X38" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="1">
         <v>3</v>
       </c>
-      <c r="Y38" s="1">
-        <v>0</v>
-      </c>
       <c r="Z38" s="1">
         <v>0</v>
       </c>
       <c r="AA38" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="1">
         <v>300</v>
       </c>
-      <c r="AB38" s="1">
-        <v>0</v>
-      </c>
       <c r="AC38" s="1">
         <v>0</v>
       </c>
@@ -5427,56 +5529,59 @@
       <c r="AG38" s="1">
         <v>0</v>
       </c>
-      <c r="AI38" s="1">
-        <v>50</v>
+      <c r="AH38" s="1">
+        <v>0</v>
       </c>
       <c r="AJ38" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK38" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" spans="3:36">
+    <row r="39" s="1" customFormat="1" spans="3:37">
       <c r="C39" s="1">
         <v>3010</v>
       </c>
       <c r="D39" s="1">
         <v>3010</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="G39" s="1">
+      <c r="E39" s="1">
+        <v>10</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="H39" s="1">
         <v>8</v>
       </c>
-      <c r="H39" s="1">
-        <v>0</v>
-      </c>
       <c r="I39" s="1">
+        <v>0</v>
+      </c>
+      <c r="J39" s="1">
         <v>100</v>
       </c>
-      <c r="J39" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="K39" s="1">
-        <v>0</v>
+      <c r="K39" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="L39" s="1">
         <v>0</v>
       </c>
       <c r="M39" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N39" s="1">
+        <v>1</v>
+      </c>
+      <c r="O39" s="1">
         <v>3</v>
       </c>
-      <c r="O39" s="1">
+      <c r="P39" s="1">
         <v>10</v>
       </c>
-      <c r="P39" s="1">
-        <v>1</v>
-      </c>
       <c r="Q39" s="1">
         <v>1</v>
       </c>
@@ -5484,38 +5589,38 @@
         <v>1</v>
       </c>
       <c r="S39" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T39" s="1">
         <v>0</v>
       </c>
-      <c r="U39" s="1" t="s">
-        <v>82</v>
+      <c r="U39" s="1">
+        <v>0</v>
       </c>
       <c r="V39" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="W39" s="1">
-        <v>0</v>
+        <v>83</v>
+      </c>
+      <c r="W39" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="X39" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="1">
         <v>3</v>
       </c>
-      <c r="Y39" s="1">
-        <v>0</v>
-      </c>
       <c r="Z39" s="1">
         <v>0</v>
       </c>
       <c r="AA39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="1">
         <v>20</v>
       </c>
-      <c r="AB39" s="1">
+      <c r="AC39" s="1">
         <v>400</v>
       </c>
-      <c r="AC39" s="1">
-        <v>0</v>
-      </c>
       <c r="AD39" s="1">
         <v>0</v>
       </c>
@@ -5528,96 +5633,99 @@
       <c r="AG39" s="1">
         <v>0</v>
       </c>
-      <c r="AI39" s="1">
-        <v>50</v>
+      <c r="AH39" s="1">
+        <v>0</v>
       </c>
       <c r="AJ39" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK39" s="1">
         <v>4102</v>
       </c>
     </row>
-    <row r="40" s="1" customFormat="1" spans="3:36">
+    <row r="40" s="1" customFormat="1" spans="3:37">
       <c r="C40" s="1">
         <v>3011</v>
       </c>
       <c r="D40" s="1">
         <v>3011</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="G40" s="1">
+      <c r="E40" s="1">
+        <v>11</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H40" s="1">
         <v>8</v>
       </c>
-      <c r="H40" s="1">
+      <c r="I40" s="1">
         <v>11</v>
       </c>
-      <c r="I40" s="1">
-        <v>0</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="K40" s="1">
-        <v>0</v>
+      <c r="J40" s="1">
+        <v>0</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="L40" s="1">
+        <v>0</v>
+      </c>
+      <c r="M40" s="1">
         <v>30</v>
       </c>
-      <c r="M40" s="1">
+      <c r="N40" s="1">
         <v>2</v>
       </c>
-      <c r="N40" s="1">
+      <c r="O40" s="1">
         <v>3</v>
       </c>
-      <c r="O40" s="1">
+      <c r="P40" s="1">
         <v>10</v>
       </c>
-      <c r="P40" s="1">
-        <v>1</v>
-      </c>
       <c r="Q40" s="1">
+        <v>1</v>
+      </c>
+      <c r="R40" s="1">
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
-      <c r="R40" s="1">
-        <v>50</v>
-      </c>
       <c r="S40" s="1">
+        <v>50</v>
+      </c>
+      <c r="T40" s="1">
         <v>10</v>
       </c>
-      <c r="T40" s="1">
+      <c r="U40" s="1">
         <v>3</v>
       </c>
-      <c r="U40" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="V40" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="W40" s="1">
+        <v>83</v>
+      </c>
+      <c r="W40" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="X40" s="1">
         <v>15</v>
       </c>
-      <c r="X40" s="1">
+      <c r="Y40" s="1">
         <v>5</v>
-      </c>
-      <c r="Y40" s="1">
-        <v>4</v>
       </c>
       <c r="Z40" s="1">
         <v>4</v>
       </c>
       <c r="AA40" s="1">
+        <v>4</v>
+      </c>
+      <c r="AB40" s="1">
         <v>500</v>
       </c>
-      <c r="AB40" s="1">
+      <c r="AC40" s="1">
         <v>100</v>
       </c>
-      <c r="AC40" s="1">
-        <v>0</v>
-      </c>
       <c r="AD40" s="1">
         <v>0</v>
       </c>
@@ -5630,51 +5738,54 @@
       <c r="AG40" s="1">
         <v>0</v>
       </c>
-      <c r="AI40" s="1">
-        <v>50</v>
+      <c r="AH40" s="1">
+        <v>0</v>
       </c>
       <c r="AJ40" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK40" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="41" s="1" customFormat="1" spans="5:6">
-      <c r="E41" s="2"/>
+    <row r="41" s="1" customFormat="1" spans="6:7">
       <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
     </row>
-    <row r="42" s="1" customFormat="1" spans="3:35">
+    <row r="42" s="1" customFormat="1" spans="3:36">
       <c r="C42" s="1">
         <v>4001</v>
       </c>
       <c r="D42" s="1">
         <v>4001</v>
       </c>
-      <c r="E42" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="F42" s="5" t="s">
+      <c r="E42" s="1">
+        <v>0</v>
+      </c>
+      <c r="F42" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="G42" s="1">
+      <c r="G42" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="H42" s="1">
         <v>4001</v>
       </c>
-      <c r="H42" s="1">
-        <v>0</v>
-      </c>
       <c r="I42" s="1">
+        <v>0</v>
+      </c>
+      <c r="J42" s="1">
         <v>-100</v>
       </c>
-      <c r="J42" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="K42" s="1">
-        <v>0</v>
+      <c r="K42" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="L42" s="1">
+        <v>0</v>
+      </c>
+      <c r="M42" s="1">
         <v>30</v>
       </c>
-      <c r="M42" s="1">
-        <v>0</v>
-      </c>
       <c r="N42" s="1">
         <v>0</v>
       </c>
@@ -5685,10 +5796,10 @@
         <v>0</v>
       </c>
       <c r="Q42" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42" s="1">
         <v>0</v>
@@ -5696,18 +5807,18 @@
       <c r="T42" s="1">
         <v>0</v>
       </c>
-      <c r="U42" s="1" t="s">
-        <v>69</v>
+      <c r="U42" s="1">
+        <v>0</v>
       </c>
       <c r="V42" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="W42" s="1">
+        <v>70</v>
+      </c>
+      <c r="W42" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="X42" s="1">
         <v>2</v>
       </c>
-      <c r="X42" s="1">
-        <v>0</v>
-      </c>
       <c r="Y42" s="1">
         <v>0</v>
       </c>
@@ -5735,47 +5846,50 @@
       <c r="AG42" s="1">
         <v>0</v>
       </c>
-      <c r="AH42" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="AI42" s="1">
+      <c r="AH42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="AJ42" s="1">
         <v>99999</v>
       </c>
     </row>
-    <row r="43" s="1" customFormat="1" spans="3:35">
+    <row r="43" s="1" customFormat="1" spans="3:36">
       <c r="C43" s="1">
         <v>4002</v>
       </c>
       <c r="D43" s="1">
         <v>4002</v>
       </c>
-      <c r="E43" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="F43" s="5" t="s">
+      <c r="E43" s="1">
+        <v>0</v>
+      </c>
+      <c r="F43" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="G43" s="1">
+      <c r="G43" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="H43" s="1">
         <v>4002</v>
       </c>
-      <c r="H43" s="1">
-        <v>0</v>
-      </c>
       <c r="I43" s="1">
+        <v>0</v>
+      </c>
+      <c r="J43" s="1">
         <v>200</v>
       </c>
-      <c r="J43" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="K43" s="1">
-        <v>0</v>
+      <c r="K43" s="1" t="s">
+        <v>178</v>
       </c>
       <c r="L43" s="1">
+        <v>0</v>
+      </c>
+      <c r="M43" s="1">
         <v>60</v>
       </c>
-      <c r="M43" s="1">
-        <v>0</v>
-      </c>
       <c r="N43" s="1">
         <v>0</v>
       </c>
@@ -5786,25 +5900,25 @@
         <v>0</v>
       </c>
       <c r="Q43" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" s="1">
+        <v>1</v>
+      </c>
+      <c r="S43" s="1">
         <v>10</v>
       </c>
-      <c r="S43" s="1">
-        <v>0</v>
-      </c>
       <c r="T43" s="1">
         <v>0</v>
       </c>
-      <c r="U43" s="1" t="s">
-        <v>69</v>
+      <c r="U43" s="1">
+        <v>0</v>
       </c>
       <c r="V43" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="W43" s="1">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="W43" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="X43" s="1">
         <v>0</v>
@@ -5816,11 +5930,11 @@
         <v>0</v>
       </c>
       <c r="AA43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="1">
         <v>100</v>
       </c>
-      <c r="AB43" s="1">
-        <v>0</v>
-      </c>
       <c r="AC43" s="1">
         <v>0</v>
       </c>
@@ -5836,45 +5950,48 @@
       <c r="AG43" s="1">
         <v>0</v>
       </c>
-      <c r="AH43" s="7"/>
-      <c r="AI43" s="1">
+      <c r="AH43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI43" s="7"/>
+      <c r="AJ43" s="1">
         <v>99999</v>
       </c>
     </row>
-    <row r="44" s="1" customFormat="1" spans="3:35">
+    <row r="44" s="1" customFormat="1" spans="3:36">
       <c r="C44" s="1">
         <v>4003</v>
       </c>
       <c r="D44" s="1">
         <v>4003</v>
       </c>
-      <c r="E44" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="F44" s="5" t="s">
+      <c r="E44" s="1">
+        <v>0</v>
+      </c>
+      <c r="F44" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="G44" s="1">
+      <c r="G44" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="H44" s="1">
         <v>4003</v>
       </c>
-      <c r="H44" s="1">
-        <v>0</v>
-      </c>
       <c r="I44" s="1">
+        <v>0</v>
+      </c>
+      <c r="J44" s="1">
         <v>-1</v>
       </c>
-      <c r="J44" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="K44" s="1">
-        <v>0</v>
+      <c r="K44" s="1" t="s">
+        <v>181</v>
       </c>
       <c r="L44" s="1">
+        <v>0</v>
+      </c>
+      <c r="M44" s="1">
         <v>60</v>
       </c>
-      <c r="M44" s="1">
-        <v>0</v>
-      </c>
       <c r="N44" s="1">
         <v>0</v>
       </c>
@@ -5885,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="Q44" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S44" s="1">
         <v>0</v>
@@ -5896,14 +6013,14 @@
       <c r="T44" s="1">
         <v>0</v>
       </c>
-      <c r="U44" s="1" t="s">
-        <v>69</v>
+      <c r="U44" s="1">
+        <v>0</v>
       </c>
       <c r="V44" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="W44" s="1">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="W44" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="X44" s="1">
         <v>0</v>
@@ -5915,11 +6032,11 @@
         <v>0</v>
       </c>
       <c r="AA44" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="1">
         <v>100</v>
       </c>
-      <c r="AB44" s="1">
-        <v>0</v>
-      </c>
       <c r="AC44" s="1">
         <v>0</v>
       </c>
@@ -5935,90 +6052,93 @@
       <c r="AG44" s="1">
         <v>0</v>
       </c>
-      <c r="AH44" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="AI44" s="1">
+      <c r="AH44" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI44" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="AJ44" s="1">
         <v>99999</v>
       </c>
     </row>
-    <row r="45" s="1" customFormat="1" spans="5:6">
-      <c r="E45" s="2"/>
+    <row r="45" s="1" customFormat="1" spans="6:7">
       <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
     </row>
-    <row r="46" s="1" customFormat="1" spans="3:36">
+    <row r="46" s="1" customFormat="1" spans="3:37">
       <c r="C46" s="1">
         <v>9001</v>
       </c>
       <c r="D46" s="1">
         <v>9001</v>
       </c>
-      <c r="E46" s="1" t="s">
-        <v>182</v>
+      <c r="E46" s="1">
+        <v>0</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="G46" s="1">
+        <v>183</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="H46" s="1">
         <v>9</v>
       </c>
-      <c r="H46" s="1">
-        <v>0</v>
-      </c>
       <c r="I46" s="1">
         <v>0</v>
       </c>
-      <c r="K46" s="1">
+      <c r="J46" s="1">
         <v>0</v>
       </c>
       <c r="L46" s="1">
         <v>0</v>
       </c>
       <c r="M46" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" s="1">
         <v>1</v>
       </c>
       <c r="O46" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P46" s="1">
         <v>0</v>
       </c>
       <c r="Q46" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" s="1">
-        <v>0</v>
-      </c>
-      <c r="T46" s="1">
-        <v>1</v>
-      </c>
-      <c r="U46" s="1" t="s">
-        <v>69</v>
+        <v>1</v>
+      </c>
+      <c r="S46" s="1">
+        <v>0</v>
+      </c>
+      <c r="U46" s="1">
+        <v>1</v>
       </c>
       <c r="V46" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="W46" s="1">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="W46" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="X46" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y46" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z46" s="1">
         <v>0</v>
       </c>
       <c r="AA46" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB46" s="1">
         <v>100</v>
       </c>
-      <c r="AB46" s="1">
-        <v>0</v>
-      </c>
       <c r="AC46" s="1">
         <v>0</v>
       </c>
@@ -6034,86 +6154,89 @@
       <c r="AG46" s="1">
         <v>0</v>
       </c>
-      <c r="AI46" s="1">
-        <v>50</v>
+      <c r="AH46" s="1">
+        <v>0</v>
       </c>
       <c r="AJ46" s="1">
         <v>50</v>
       </c>
+      <c r="AK46" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="47" s="1" customFormat="1" spans="3:36">
+    <row r="47" s="1" customFormat="1" spans="3:37">
       <c r="C47" s="1">
         <v>9002</v>
       </c>
       <c r="D47" s="1">
         <v>9002</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>183</v>
+      <c r="E47" s="1">
+        <v>0</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="G47" s="1">
+        <v>184</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H47" s="1">
         <v>9</v>
       </c>
-      <c r="H47" s="1">
-        <v>0</v>
-      </c>
       <c r="I47" s="1">
         <v>0</v>
       </c>
-      <c r="K47" s="1">
+      <c r="J47" s="1">
         <v>0</v>
       </c>
       <c r="L47" s="1">
         <v>0</v>
       </c>
       <c r="M47" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N47" s="1">
         <v>1</v>
       </c>
       <c r="O47" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P47" s="1">
         <v>0</v>
       </c>
       <c r="Q47" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" s="1">
-        <v>0</v>
-      </c>
-      <c r="T47" s="1">
+        <v>1</v>
+      </c>
+      <c r="S47" s="1">
+        <v>0</v>
+      </c>
+      <c r="U47" s="1">
         <v>2</v>
-      </c>
-      <c r="U47" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="V47" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="W47" s="1">
-        <v>0</v>
+      <c r="W47" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="X47" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y47" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z47" s="1">
         <v>0</v>
       </c>
       <c r="AA47" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="1">
         <v>100</v>
       </c>
-      <c r="AB47" s="1">
-        <v>0</v>
-      </c>
       <c r="AC47" s="1">
         <v>0</v>
       </c>
@@ -6129,90 +6252,93 @@
       <c r="AG47" s="1">
         <v>0</v>
       </c>
-      <c r="AI47" s="1">
-        <v>50</v>
+      <c r="AH47" s="1">
+        <v>0</v>
       </c>
       <c r="AJ47" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK47" s="1">
         <v>50</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1"/>
-    <row r="49" s="1" customFormat="1" spans="3:36">
+    <row r="49" s="1" customFormat="1" spans="3:37">
       <c r="C49" s="1">
         <v>10001</v>
       </c>
       <c r="D49" s="1">
         <v>10001</v>
       </c>
-      <c r="E49" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="F49" s="2" t="s">
+      <c r="E49" s="1">
+        <v>0</v>
+      </c>
+      <c r="F49" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="G49" s="1">
-        <v>1</v>
+      <c r="G49" s="2" t="s">
+        <v>186</v>
       </c>
       <c r="H49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" s="1">
-        <v>1</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="K49" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="J49" s="1">
+        <v>1</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="L49" s="1">
         <v>0</v>
       </c>
       <c r="M49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N49" s="1">
         <v>1</v>
       </c>
       <c r="O49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P49" s="1">
         <v>0</v>
       </c>
       <c r="Q49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R49" s="1">
-        <v>0</v>
-      </c>
-      <c r="T49" s="1">
+        <v>1</v>
+      </c>
+      <c r="S49" s="1">
+        <v>0</v>
+      </c>
+      <c r="U49" s="1">
         <v>3</v>
       </c>
-      <c r="U49" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="V49" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="W49" s="1">
-        <v>0</v>
+        <v>83</v>
+      </c>
+      <c r="W49" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="X49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z49" s="1">
         <v>0</v>
       </c>
       <c r="AA49" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB49" s="1">
         <v>150</v>
       </c>
-      <c r="AB49" s="1">
-        <v>0</v>
-      </c>
       <c r="AC49" s="1">
         <v>0</v>
       </c>
@@ -6228,90 +6354,93 @@
       <c r="AG49" s="1">
         <v>0</v>
       </c>
-      <c r="AI49" s="1">
-        <v>50</v>
+      <c r="AH49" s="1">
+        <v>0</v>
       </c>
       <c r="AJ49" s="1">
         <v>50</v>
       </c>
+      <c r="AK49" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="50" spans="3:36">
+    <row r="50" spans="3:37">
       <c r="C50" s="2">
         <v>10002</v>
       </c>
       <c r="D50" s="2">
         <v>10002</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="E50" s="1">
+        <v>0</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="G50" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="F50" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="G50" s="2">
+      <c r="H50" s="2">
         <v>4</v>
       </c>
-      <c r="H50" s="1">
-        <v>0</v>
-      </c>
-      <c r="I50" s="2">
+      <c r="I50" s="1">
+        <v>0</v>
+      </c>
+      <c r="J50" s="2">
         <v>10</v>
       </c>
-      <c r="J50" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="K50" s="1">
-        <v>0</v>
-      </c>
-      <c r="L50" s="2">
-        <v>0</v>
-      </c>
-      <c r="M50" s="1">
-        <v>1</v>
+      <c r="K50" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="L50" s="1">
+        <v>0</v>
+      </c>
+      <c r="M50" s="2">
+        <v>0</v>
       </c>
       <c r="N50" s="1">
         <v>1</v>
       </c>
       <c r="O50" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P50" s="1">
         <v>0</v>
       </c>
       <c r="Q50" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R50" s="1">
-        <v>0</v>
-      </c>
-      <c r="S50" s="1"/>
-      <c r="T50" s="2">
-        <v>0</v>
-      </c>
-      <c r="U50" s="1" t="s">
-        <v>69</v>
+        <v>1</v>
+      </c>
+      <c r="S50" s="1">
+        <v>0</v>
+      </c>
+      <c r="T50" s="1"/>
+      <c r="U50" s="2">
+        <v>0</v>
       </c>
       <c r="V50" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="W50" s="2">
-        <v>0</v>
+      <c r="W50" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="X50" s="2">
-        <v>1</v>
-      </c>
-      <c r="Y50" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="2">
+        <v>1</v>
       </c>
       <c r="Z50" s="1">
         <v>0</v>
       </c>
-      <c r="AA50" s="2">
+      <c r="AA50" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB50" s="2">
         <v>100</v>
       </c>
-      <c r="AB50" s="1">
-        <v>0</v>
-      </c>
       <c r="AC50" s="1">
         <v>0</v>
       </c>
@@ -6327,91 +6456,94 @@
       <c r="AG50" s="1">
         <v>0</v>
       </c>
-      <c r="AH50" s="1"/>
-      <c r="AI50" s="1">
-        <v>50</v>
-      </c>
+      <c r="AH50" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="1"/>
       <c r="AJ50" s="1">
         <v>50</v>
       </c>
+      <c r="AK50" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="51" spans="3:36">
+    <row r="51" spans="3:37">
       <c r="C51" s="2">
         <v>10003</v>
       </c>
       <c r="D51" s="2">
         <v>10003</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>188</v>
+      <c r="E51" s="1">
+        <v>0</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="G51" s="2">
-        <v>1</v>
-      </c>
-      <c r="H51" s="1">
-        <v>0</v>
-      </c>
-      <c r="I51" s="2">
-        <v>1</v>
-      </c>
-      <c r="J51" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="K51" s="1">
-        <v>0</v>
-      </c>
-      <c r="L51" s="2">
-        <v>0</v>
-      </c>
-      <c r="M51" s="1">
-        <v>1</v>
+        <v>189</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="H51" s="2">
+        <v>1</v>
+      </c>
+      <c r="I51" s="1">
+        <v>0</v>
+      </c>
+      <c r="J51" s="2">
+        <v>1</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="L51" s="1">
+        <v>0</v>
+      </c>
+      <c r="M51" s="2">
+        <v>0</v>
       </c>
       <c r="N51" s="1">
         <v>1</v>
       </c>
       <c r="O51" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P51" s="1">
         <v>0</v>
       </c>
       <c r="Q51" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R51" s="1">
-        <v>0</v>
-      </c>
-      <c r="S51" s="1"/>
-      <c r="T51" s="1">
-        <v>0</v>
-      </c>
-      <c r="U51" s="1" t="s">
-        <v>82</v>
+        <v>1</v>
+      </c>
+      <c r="S51" s="1">
+        <v>0</v>
+      </c>
+      <c r="T51" s="1"/>
+      <c r="U51" s="1">
+        <v>0</v>
       </c>
       <c r="V51" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="W51" s="1">
-        <v>0</v>
+        <v>83</v>
+      </c>
+      <c r="W51" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="X51" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="1">
         <v>10</v>
       </c>
-      <c r="Y51" s="1">
-        <v>0</v>
-      </c>
       <c r="Z51" s="1">
         <v>0</v>
       </c>
       <c r="AA51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="1">
         <v>100</v>
       </c>
-      <c r="AB51" s="1">
-        <v>0</v>
-      </c>
       <c r="AC51" s="1">
         <v>0</v>
       </c>
@@ -6427,95 +6559,98 @@
       <c r="AG51" s="1">
         <v>0</v>
       </c>
-      <c r="AH51" s="1"/>
-      <c r="AI51" s="1">
-        <v>50</v>
-      </c>
+      <c r="AH51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="1"/>
       <c r="AJ51" s="1">
         <v>50</v>
       </c>
+      <c r="AK51" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="52" spans="3:36">
+    <row r="52" spans="3:37">
       <c r="C52" s="2">
         <v>10004</v>
       </c>
       <c r="D52" s="2">
         <v>10004</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>189</v>
+      <c r="E52" s="1">
+        <v>0</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="G52" s="2">
+        <v>190</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="H52" s="2">
         <v>4</v>
       </c>
-      <c r="H52" s="1">
-        <v>0</v>
-      </c>
-      <c r="I52" s="2">
+      <c r="I52" s="1">
+        <v>0</v>
+      </c>
+      <c r="J52" s="2">
         <v>10</v>
       </c>
-      <c r="J52" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="K52" s="1">
-        <v>0</v>
-      </c>
-      <c r="L52" s="2">
-        <v>0</v>
-      </c>
-      <c r="M52" s="1">
-        <v>1</v>
-      </c>
-      <c r="N52" s="2">
+      <c r="K52" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="L52" s="1">
+        <v>0</v>
+      </c>
+      <c r="M52" s="2">
+        <v>0</v>
+      </c>
+      <c r="N52" s="1">
         <v>1</v>
       </c>
       <c r="O52" s="2">
-        <v>0</v>
-      </c>
-      <c r="P52" s="1">
+        <v>1</v>
+      </c>
+      <c r="P52" s="2">
         <v>0</v>
       </c>
       <c r="Q52" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R52" s="1">
-        <v>0</v>
-      </c>
-      <c r="S52" s="1"/>
-      <c r="T52" s="2">
+        <v>1</v>
+      </c>
+      <c r="S52" s="1">
+        <v>0</v>
+      </c>
+      <c r="T52" s="1"/>
+      <c r="U52" s="2">
         <v>3</v>
       </c>
-      <c r="U52" s="2" t="s">
-        <v>190</v>
-      </c>
       <c r="V52" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="W52" s="2">
-        <v>0</v>
+        <v>191</v>
+      </c>
+      <c r="W52" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="X52" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="2">
         <v>4</v>
       </c>
-      <c r="Y52" s="1">
-        <v>0</v>
-      </c>
       <c r="Z52" s="1">
         <v>0</v>
       </c>
-      <c r="AA52" s="2">
-        <v>50</v>
+      <c r="AA52" s="1">
+        <v>0</v>
       </c>
       <c r="AB52" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC52" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD52" s="2">
+        <v>50</v>
+      </c>
+      <c r="AC52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="1">
         <v>0</v>
       </c>
       <c r="AE52" s="2">
@@ -6524,98 +6659,101 @@
       <c r="AF52" s="2">
         <v>0</v>
       </c>
-      <c r="AG52" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI52" s="1">
-        <v>50</v>
+      <c r="AG52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="1">
+        <v>0</v>
       </c>
       <c r="AJ52" s="1">
         <v>50</v>
       </c>
+      <c r="AK52" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="53" s="1" customFormat="1" spans="3:36">
+    <row r="53" s="1" customFormat="1" spans="3:37">
       <c r="C53" s="1">
         <v>10005</v>
       </c>
       <c r="D53" s="1">
         <v>10005</v>
       </c>
-      <c r="E53" s="2" t="s">
-        <v>191</v>
+      <c r="E53" s="1">
+        <v>0</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G53" s="1">
-        <v>1</v>
+        <v>192</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="H53" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" s="1">
+        <v>0</v>
+      </c>
+      <c r="J53" s="1">
         <v>10</v>
       </c>
-      <c r="J53" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="K53" s="1">
-        <v>0</v>
+      <c r="K53" s="2" t="s">
+        <v>192</v>
       </c>
       <c r="L53" s="1">
         <v>0</v>
       </c>
       <c r="M53" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N53" s="1">
         <v>1</v>
       </c>
-      <c r="O53" s="2">
-        <v>0</v>
-      </c>
-      <c r="P53" s="1">
+      <c r="O53" s="1">
+        <v>1</v>
+      </c>
+      <c r="P53" s="2">
         <v>0</v>
       </c>
       <c r="Q53" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R53" s="1">
-        <v>0</v>
-      </c>
-      <c r="T53" s="1">
+        <v>1</v>
+      </c>
+      <c r="S53" s="1">
+        <v>0</v>
+      </c>
+      <c r="U53" s="1">
         <v>2</v>
-      </c>
-      <c r="U53" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="V53" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="W53" s="1">
-        <v>0</v>
+      <c r="W53" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="X53" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="1">
         <v>2</v>
       </c>
-      <c r="Y53" s="1">
-        <v>0</v>
-      </c>
       <c r="Z53" s="1">
         <v>0</v>
       </c>
       <c r="AA53" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="1">
         <v>150</v>
       </c>
-      <c r="AB53" s="1">
-        <v>0</v>
-      </c>
       <c r="AC53" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="1">
         <v>20</v>
       </c>
-      <c r="AD53" s="1">
-        <v>0</v>
-      </c>
       <c r="AE53" s="1">
         <v>0</v>
       </c>
@@ -6625,86 +6763,89 @@
       <c r="AG53" s="1">
         <v>0</v>
       </c>
-      <c r="AI53" s="1">
-        <v>50</v>
+      <c r="AH53" s="1">
+        <v>0</v>
       </c>
       <c r="AJ53" s="1">
         <v>50</v>
       </c>
+      <c r="AK53" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="55" s="1" customFormat="1" spans="3:36">
+    <row r="55" s="1" customFormat="1" spans="3:37">
       <c r="C55" s="1">
         <v>11001</v>
       </c>
       <c r="D55" s="1">
         <v>1001</v>
       </c>
-      <c r="E55" s="1" t="s">
-        <v>67</v>
+      <c r="E55" s="1">
+        <v>0</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="G55" s="1">
-        <v>1</v>
+        <v>68</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="H55" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" s="1">
+        <v>0</v>
+      </c>
+      <c r="J55" s="1">
         <v>10</v>
       </c>
-      <c r="K55" s="1">
-        <v>0</v>
-      </c>
       <c r="L55" s="1">
         <v>0</v>
       </c>
       <c r="M55" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N55" s="1">
         <v>1</v>
       </c>
       <c r="O55" s="1">
+        <v>1</v>
+      </c>
+      <c r="P55" s="1">
         <v>9999</v>
       </c>
-      <c r="P55" s="1">
-        <v>0</v>
-      </c>
       <c r="Q55" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R55" s="1">
-        <v>0</v>
-      </c>
-      <c r="T55" s="1">
-        <v>1</v>
-      </c>
-      <c r="U55" s="1" t="s">
-        <v>69</v>
+        <v>1</v>
+      </c>
+      <c r="S55" s="1">
+        <v>0</v>
+      </c>
+      <c r="U55" s="1">
+        <v>1</v>
       </c>
       <c r="V55" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="W55" s="1">
-        <v>0</v>
+      <c r="W55" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="X55" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y55" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z55" s="1">
         <v>0</v>
       </c>
       <c r="AA55" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB55" s="1">
         <v>120</v>
       </c>
-      <c r="AB55" s="1">
-        <v>0</v>
-      </c>
       <c r="AC55" s="1">
         <v>0</v>
       </c>
@@ -6720,92 +6861,95 @@
       <c r="AG55" s="1">
         <v>0</v>
       </c>
-      <c r="AI55" s="1">
-        <v>50</v>
+      <c r="AH55" s="1">
+        <v>0</v>
       </c>
       <c r="AJ55" s="1">
         <v>50</v>
       </c>
+      <c r="AK55" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="56" s="1" customFormat="1" spans="3:36">
+    <row r="56" s="1" customFormat="1" spans="3:37">
       <c r="C56" s="1">
         <v>11002</v>
       </c>
       <c r="D56" s="1">
         <v>1002</v>
       </c>
-      <c r="E56" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F56" s="2" t="s">
+      <c r="E56" s="1">
+        <v>0</v>
+      </c>
+      <c r="F56" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G56" s="1">
-        <v>1</v>
+      <c r="G56" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="H56" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" s="1">
+        <v>0</v>
+      </c>
+      <c r="J56" s="1">
         <v>10</v>
       </c>
-      <c r="K56" s="1">
-        <v>0</v>
-      </c>
       <c r="L56" s="1">
         <v>0</v>
       </c>
       <c r="M56" s="1">
+        <v>0</v>
+      </c>
+      <c r="N56" s="1">
         <v>2</v>
       </c>
-      <c r="N56" s="1">
-        <v>1</v>
-      </c>
       <c r="O56" s="1">
+        <v>1</v>
+      </c>
+      <c r="P56" s="1">
         <v>9999</v>
       </c>
-      <c r="P56" s="1">
-        <v>0</v>
-      </c>
       <c r="Q56" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R56" s="1">
-        <v>0</v>
-      </c>
-      <c r="T56" s="1">
+        <v>1</v>
+      </c>
+      <c r="S56" s="1">
+        <v>0</v>
+      </c>
+      <c r="U56" s="1">
         <v>2</v>
-      </c>
-      <c r="U56" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="V56" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="W56" s="1">
-        <v>0</v>
+      <c r="W56" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="X56" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y56" s="1">
         <v>2</v>
       </c>
-      <c r="Y56" s="1">
-        <v>0</v>
-      </c>
       <c r="Z56" s="1">
         <v>0</v>
       </c>
       <c r="AA56" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB56" s="1">
         <v>150</v>
       </c>
-      <c r="AB56" s="1">
-        <v>0</v>
-      </c>
       <c r="AC56" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD56" s="1">
         <v>20</v>
       </c>
-      <c r="AD56" s="1">
-        <v>0</v>
-      </c>
       <c r="AE56" s="1">
         <v>0</v>
       </c>
@@ -6815,86 +6959,89 @@
       <c r="AG56" s="1">
         <v>0</v>
       </c>
-      <c r="AI56" s="1">
-        <v>50</v>
+      <c r="AH56" s="1">
+        <v>0</v>
       </c>
       <c r="AJ56" s="1">
         <v>50</v>
       </c>
+      <c r="AK56" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="57" s="1" customFormat="1" spans="3:36">
+    <row r="57" s="1" customFormat="1" spans="3:37">
       <c r="C57" s="1">
         <v>11003</v>
       </c>
       <c r="D57" s="1">
         <v>1003</v>
       </c>
-      <c r="E57" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F57" s="2" t="s">
+      <c r="E57" s="1">
+        <v>0</v>
+      </c>
+      <c r="F57" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="G57" s="1">
-        <v>1</v>
+      <c r="G57" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="H57" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" s="1">
+        <v>0</v>
+      </c>
+      <c r="J57" s="1">
         <v>10</v>
       </c>
-      <c r="K57" s="1">
-        <v>0</v>
-      </c>
       <c r="L57" s="1">
         <v>0</v>
       </c>
       <c r="M57" s="1">
+        <v>0</v>
+      </c>
+      <c r="N57" s="1">
         <v>2</v>
       </c>
-      <c r="N57" s="1">
-        <v>1</v>
-      </c>
       <c r="O57" s="1">
+        <v>1</v>
+      </c>
+      <c r="P57" s="1">
         <v>9999</v>
       </c>
-      <c r="P57" s="1">
-        <v>0</v>
-      </c>
       <c r="Q57" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R57" s="1">
-        <v>0</v>
-      </c>
-      <c r="T57" s="1">
-        <v>1</v>
-      </c>
-      <c r="U57" s="1" t="s">
-        <v>69</v>
+        <v>1</v>
+      </c>
+      <c r="S57" s="1">
+        <v>0</v>
+      </c>
+      <c r="U57" s="1">
+        <v>1</v>
       </c>
       <c r="V57" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="W57" s="1">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="W57" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="X57" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="1">
         <v>5</v>
       </c>
-      <c r="Y57" s="1">
-        <v>0</v>
-      </c>
       <c r="Z57" s="1">
         <v>0</v>
       </c>
       <c r="AA57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="1">
         <v>100</v>
       </c>
-      <c r="AB57" s="1">
-        <v>0</v>
-      </c>
       <c r="AC57" s="1">
         <v>0</v>
       </c>
@@ -6910,86 +7057,89 @@
       <c r="AG57" s="1">
         <v>0</v>
       </c>
-      <c r="AI57" s="1">
-        <v>50</v>
+      <c r="AH57" s="1">
+        <v>0</v>
       </c>
       <c r="AJ57" s="1">
         <v>50</v>
       </c>
+      <c r="AK57" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="58" s="1" customFormat="1" spans="3:36">
+    <row r="58" s="1" customFormat="1" spans="3:37">
       <c r="C58" s="1">
         <v>11004</v>
       </c>
       <c r="D58" s="1">
         <v>1004</v>
       </c>
-      <c r="E58" s="1" t="s">
-        <v>79</v>
+      <c r="E58" s="1">
+        <v>0</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G58" s="1">
+      <c r="G58" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H58" s="1">
         <v>7</v>
       </c>
-      <c r="H58" s="1">
-        <v>0</v>
-      </c>
       <c r="I58" s="1">
+        <v>0</v>
+      </c>
+      <c r="J58" s="1">
         <v>10</v>
       </c>
-      <c r="K58" s="1">
-        <v>0</v>
-      </c>
       <c r="L58" s="1">
+        <v>0</v>
+      </c>
+      <c r="M58" s="1">
         <v>5</v>
       </c>
-      <c r="M58" s="1">
-        <v>1</v>
-      </c>
       <c r="N58" s="1">
         <v>1</v>
       </c>
       <c r="O58" s="1">
+        <v>1</v>
+      </c>
+      <c r="P58" s="1">
         <v>9999</v>
       </c>
-      <c r="P58" s="1">
-        <v>0</v>
-      </c>
       <c r="Q58" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R58" s="1">
-        <v>0</v>
-      </c>
-      <c r="T58" s="1">
+        <v>1</v>
+      </c>
+      <c r="S58" s="1">
+        <v>0</v>
+      </c>
+      <c r="U58" s="1">
         <v>4</v>
-      </c>
-      <c r="U58" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="V58" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="W58" s="1">
+      <c r="W58" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="X58" s="1">
         <v>2</v>
       </c>
-      <c r="X58" s="1">
-        <v>1</v>
-      </c>
       <c r="Y58" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z58" s="1">
         <v>0</v>
       </c>
       <c r="AA58" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="1">
         <v>200</v>
       </c>
-      <c r="AB58" s="1">
-        <v>0</v>
-      </c>
       <c r="AC58" s="1">
         <v>0</v>
       </c>
@@ -7005,77 +7155,80 @@
       <c r="AG58" s="1">
         <v>0</v>
       </c>
-      <c r="AH58" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="AI58" s="1">
-        <v>50</v>
+      <c r="AH58" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="1" t="s">
+        <v>193</v>
       </c>
       <c r="AJ58" s="1">
         <v>50</v>
       </c>
+      <c r="AK58" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="59" s="1" customFormat="1" spans="3:36">
+    <row r="59" s="1" customFormat="1" spans="3:37">
       <c r="C59" s="1">
         <v>11005</v>
       </c>
       <c r="D59" s="1">
         <v>1005</v>
       </c>
-      <c r="E59" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F59" s="2" t="s">
+      <c r="E59" s="1">
+        <v>0</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G59" s="1">
+      <c r="G59" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H59" s="1">
         <v>5</v>
       </c>
-      <c r="H59" s="1">
-        <v>0</v>
-      </c>
       <c r="I59" s="1">
-        <v>50</v>
-      </c>
-      <c r="K59" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="J59" s="1">
+        <v>50</v>
       </c>
       <c r="L59" s="1">
+        <v>0</v>
+      </c>
+      <c r="M59" s="1">
         <v>30</v>
       </c>
-      <c r="M59" s="1">
-        <v>1</v>
-      </c>
       <c r="N59" s="1">
         <v>1</v>
       </c>
       <c r="O59" s="1">
+        <v>1</v>
+      </c>
+      <c r="P59" s="1">
         <v>9999</v>
       </c>
-      <c r="P59" s="1">
-        <v>0</v>
-      </c>
       <c r="Q59" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R59" s="1">
-        <v>0</v>
-      </c>
-      <c r="T59" s="1">
-        <v>0</v>
-      </c>
-      <c r="U59" s="1" t="s">
-        <v>69</v>
+        <v>1</v>
+      </c>
+      <c r="S59" s="1">
+        <v>0</v>
+      </c>
+      <c r="U59" s="1">
+        <v>0</v>
       </c>
       <c r="V59" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="W59" s="1">
+        <v>70</v>
+      </c>
+      <c r="W59" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="X59" s="1">
         <v>30</v>
       </c>
-      <c r="X59" s="1">
-        <v>0</v>
-      </c>
       <c r="Y59" s="1">
         <v>0</v>
       </c>
@@ -7083,11 +7236,11 @@
         <v>0</v>
       </c>
       <c r="AA59" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB59" s="1">
         <v>20</v>
       </c>
-      <c r="AB59" s="1">
-        <v>0</v>
-      </c>
       <c r="AC59" s="1">
         <v>0</v>
       </c>
@@ -7103,71 +7256,74 @@
       <c r="AG59" s="1">
         <v>0</v>
       </c>
-      <c r="AH59" s="7"/>
-      <c r="AI59" s="1">
-        <v>50</v>
-      </c>
+      <c r="AH59" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI59" s="7"/>
       <c r="AJ59" s="1">
         <v>50</v>
       </c>
+      <c r="AK59" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="60" s="1" customFormat="1" spans="3:36">
+    <row r="60" s="1" customFormat="1" spans="3:37">
       <c r="C60" s="1">
         <v>11006</v>
       </c>
       <c r="D60" s="1">
         <v>1006</v>
       </c>
-      <c r="E60" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G60" s="1">
+      <c r="E60" s="1">
+        <v>0</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H60" s="1">
         <v>6</v>
       </c>
-      <c r="H60" s="1">
-        <v>0</v>
-      </c>
       <c r="I60" s="1">
+        <v>0</v>
+      </c>
+      <c r="J60" s="1">
         <v>10</v>
       </c>
-      <c r="K60" s="1">
-        <v>0</v>
-      </c>
       <c r="L60" s="1">
         <v>0</v>
       </c>
       <c r="M60" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N60" s="1">
         <v>1</v>
       </c>
       <c r="O60" s="1">
+        <v>1</v>
+      </c>
+      <c r="P60" s="1">
         <v>9999</v>
       </c>
-      <c r="P60" s="1">
-        <v>0</v>
-      </c>
       <c r="Q60" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R60" s="1">
-        <v>0</v>
-      </c>
-      <c r="T60" s="1">
-        <v>0</v>
-      </c>
-      <c r="U60" s="1" t="s">
-        <v>69</v>
+        <v>1</v>
+      </c>
+      <c r="S60" s="1">
+        <v>0</v>
+      </c>
+      <c r="U60" s="1">
+        <v>0</v>
       </c>
       <c r="V60" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="W60" s="1">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="W60" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="X60" s="1">
         <v>0</v>
@@ -7179,10 +7335,10 @@
         <v>0</v>
       </c>
       <c r="AA60" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AB60" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AC60" s="1">
         <v>0</v>
@@ -7199,86 +7355,89 @@
       <c r="AG60" s="1">
         <v>0</v>
       </c>
-      <c r="AI60" s="1">
-        <v>50</v>
+      <c r="AH60" s="1">
+        <v>0</v>
       </c>
       <c r="AJ60" s="1">
         <v>50</v>
       </c>
+      <c r="AK60" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="61" s="1" customFormat="1" spans="3:36">
+    <row r="61" s="1" customFormat="1" spans="3:37">
       <c r="C61" s="1">
         <v>11007</v>
       </c>
       <c r="D61" s="1">
         <v>1007</v>
       </c>
-      <c r="E61" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F61" s="2" t="s">
+      <c r="E61" s="1">
+        <v>0</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G61" s="1">
-        <v>1</v>
+      <c r="G61" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="H61" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" s="1">
+        <v>0</v>
+      </c>
+      <c r="J61" s="1">
         <v>10</v>
       </c>
-      <c r="K61" s="1">
-        <v>0</v>
-      </c>
       <c r="L61" s="1">
         <v>0</v>
       </c>
       <c r="M61" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N61" s="1">
         <v>1</v>
       </c>
       <c r="O61" s="1">
+        <v>1</v>
+      </c>
+      <c r="P61" s="1">
         <v>9999</v>
       </c>
-      <c r="P61" s="1">
-        <v>0</v>
-      </c>
       <c r="Q61" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R61" s="1">
-        <v>0</v>
-      </c>
-      <c r="T61" s="1">
-        <v>1</v>
-      </c>
-      <c r="U61" s="1" t="s">
-        <v>69</v>
+        <v>1</v>
+      </c>
+      <c r="S61" s="1">
+        <v>0</v>
+      </c>
+      <c r="U61" s="1">
+        <v>1</v>
       </c>
       <c r="V61" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="W61" s="1">
-        <v>0</v>
+      <c r="W61" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="X61" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y61" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z61" s="1">
         <v>0</v>
       </c>
       <c r="AA61" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="1">
         <v>300</v>
       </c>
-      <c r="AB61" s="1">
-        <v>0</v>
-      </c>
       <c r="AC61" s="1">
         <v>0</v>
       </c>
@@ -7294,86 +7453,89 @@
       <c r="AG61" s="1">
         <v>0</v>
       </c>
-      <c r="AI61" s="1">
-        <v>50</v>
+      <c r="AH61" s="1">
+        <v>0</v>
       </c>
       <c r="AJ61" s="1">
         <v>50</v>
       </c>
+      <c r="AK61" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="62" s="1" customFormat="1" spans="3:36">
+    <row r="62" s="1" customFormat="1" spans="3:37">
       <c r="C62" s="1">
         <v>12001</v>
       </c>
       <c r="D62" s="1">
         <v>2001</v>
       </c>
-      <c r="E62" s="1" t="s">
-        <v>109</v>
+      <c r="E62" s="1">
+        <v>0</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="G62" s="1">
-        <v>1</v>
+      <c r="G62" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="H62" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" s="1">
+        <v>0</v>
+      </c>
+      <c r="J62" s="1">
         <v>10</v>
       </c>
-      <c r="K62" s="1">
-        <v>0</v>
-      </c>
       <c r="L62" s="1">
         <v>0</v>
       </c>
       <c r="M62" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N62" s="1">
+        <v>1</v>
+      </c>
+      <c r="O62" s="1">
         <v>2</v>
       </c>
-      <c r="O62" s="1">
+      <c r="P62" s="1">
         <v>9999</v>
       </c>
-      <c r="P62" s="1">
-        <v>0</v>
-      </c>
       <c r="Q62" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R62" s="1">
-        <v>0</v>
-      </c>
-      <c r="T62" s="1">
+        <v>1</v>
+      </c>
+      <c r="S62" s="1">
+        <v>0</v>
+      </c>
+      <c r="U62" s="1">
         <v>2</v>
       </c>
-      <c r="U62" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="V62" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="W62" s="1">
-        <v>0</v>
+        <v>83</v>
+      </c>
+      <c r="W62" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="X62" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y62" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z62" s="1">
         <v>0</v>
       </c>
       <c r="AA62" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB62" s="1">
         <v>120</v>
       </c>
-      <c r="AB62" s="1">
-        <v>0</v>
-      </c>
       <c r="AC62" s="1">
         <v>0</v>
       </c>
@@ -7389,86 +7551,89 @@
       <c r="AG62" s="1">
         <v>0</v>
       </c>
-      <c r="AI62" s="1">
-        <v>50</v>
+      <c r="AH62" s="1">
+        <v>0</v>
       </c>
       <c r="AJ62" s="1">
         <v>50</v>
       </c>
+      <c r="AK62" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="63" s="1" customFormat="1" spans="3:36">
+    <row r="63" s="1" customFormat="1" spans="3:37">
       <c r="C63" s="1">
         <v>12002</v>
       </c>
       <c r="D63" s="1">
         <v>2002</v>
       </c>
-      <c r="E63" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F63" s="2" t="s">
+      <c r="E63" s="1">
+        <v>0</v>
+      </c>
+      <c r="F63" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="G63" s="1">
-        <v>1</v>
+      <c r="G63" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="H63" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63" s="1">
+        <v>0</v>
+      </c>
+      <c r="J63" s="1">
         <v>10</v>
       </c>
-      <c r="K63" s="1">
-        <v>0</v>
-      </c>
       <c r="L63" s="1">
         <v>0</v>
       </c>
       <c r="M63" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N63" s="1">
+        <v>1</v>
+      </c>
+      <c r="O63" s="1">
         <v>2</v>
       </c>
-      <c r="O63" s="1">
+      <c r="P63" s="1">
         <v>9999</v>
       </c>
-      <c r="P63" s="1">
-        <v>0</v>
-      </c>
       <c r="Q63" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R63" s="1">
-        <v>0</v>
-      </c>
-      <c r="T63" s="1">
+        <v>1</v>
+      </c>
+      <c r="S63" s="1">
+        <v>0</v>
+      </c>
+      <c r="U63" s="1">
         <v>3</v>
       </c>
-      <c r="U63" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="V63" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="W63" s="1">
-        <v>0</v>
+        <v>83</v>
+      </c>
+      <c r="W63" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="X63" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y63" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z63" s="1">
         <v>0</v>
       </c>
       <c r="AA63" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB63" s="1">
         <v>150</v>
       </c>
-      <c r="AB63" s="1">
-        <v>0</v>
-      </c>
       <c r="AC63" s="1">
         <v>0</v>
       </c>
@@ -7484,86 +7649,89 @@
       <c r="AG63" s="1">
         <v>0</v>
       </c>
-      <c r="AI63" s="1">
-        <v>50</v>
+      <c r="AH63" s="1">
+        <v>0</v>
       </c>
       <c r="AJ63" s="1">
         <v>50</v>
       </c>
+      <c r="AK63" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="64" s="1" customFormat="1" spans="3:36">
+    <row r="64" s="1" customFormat="1" spans="3:37">
       <c r="C64" s="1">
         <v>12003</v>
       </c>
       <c r="D64" s="1">
         <v>2003</v>
       </c>
-      <c r="E64" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F64" s="2" t="s">
+      <c r="E64" s="1">
+        <v>0</v>
+      </c>
+      <c r="F64" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="G64" s="1">
+      <c r="G64" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H64" s="1">
         <v>3</v>
       </c>
-      <c r="H64" s="1">
-        <v>0</v>
-      </c>
       <c r="I64" s="1">
+        <v>0</v>
+      </c>
+      <c r="J64" s="1">
         <v>10</v>
       </c>
-      <c r="K64" s="1">
-        <v>0</v>
-      </c>
       <c r="L64" s="1">
+        <v>0</v>
+      </c>
+      <c r="M64" s="1">
         <v>5</v>
-      </c>
-      <c r="M64" s="1">
-        <v>2</v>
       </c>
       <c r="N64" s="1">
         <v>2</v>
       </c>
       <c r="O64" s="1">
+        <v>2</v>
+      </c>
+      <c r="P64" s="1">
         <v>9999</v>
       </c>
-      <c r="P64" s="1">
-        <v>0</v>
-      </c>
       <c r="Q64" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R64" s="1">
-        <v>0</v>
-      </c>
-      <c r="T64" s="1">
+        <v>1</v>
+      </c>
+      <c r="S64" s="1">
+        <v>0</v>
+      </c>
+      <c r="U64" s="1">
         <v>3</v>
       </c>
-      <c r="U64" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="V64" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="W64" s="1">
-        <v>5</v>
+        <v>83</v>
+      </c>
+      <c r="W64" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="X64" s="1">
         <v>5</v>
       </c>
       <c r="Y64" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z64" s="1">
         <v>2</v>
       </c>
       <c r="AA64" s="1">
+        <v>2</v>
+      </c>
+      <c r="AB64" s="1">
         <v>80</v>
       </c>
-      <c r="AB64" s="1">
-        <v>0</v>
-      </c>
       <c r="AC64" s="1">
         <v>0</v>
       </c>
@@ -7579,86 +7747,89 @@
       <c r="AG64" s="1">
         <v>0</v>
       </c>
-      <c r="AI64" s="1">
-        <v>50</v>
+      <c r="AH64" s="1">
+        <v>0</v>
       </c>
       <c r="AJ64" s="1">
         <v>50</v>
       </c>
+      <c r="AK64" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="65" s="1" customFormat="1" spans="3:36">
+    <row r="65" s="1" customFormat="1" spans="3:37">
       <c r="C65" s="1">
         <v>12004</v>
       </c>
       <c r="D65" s="1">
         <v>2004</v>
       </c>
-      <c r="E65" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F65" s="2" t="s">
+      <c r="E65" s="1">
+        <v>0</v>
+      </c>
+      <c r="F65" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="G65" s="1">
-        <v>1</v>
+      <c r="G65" s="2" t="s">
+        <v>120</v>
       </c>
       <c r="H65" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" s="1">
+        <v>0</v>
+      </c>
+      <c r="J65" s="1">
         <v>10</v>
       </c>
-      <c r="K65" s="1">
-        <v>0</v>
-      </c>
       <c r="L65" s="1">
         <v>0</v>
       </c>
       <c r="M65" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N65" s="1">
         <v>2</v>
       </c>
       <c r="O65" s="1">
+        <v>2</v>
+      </c>
+      <c r="P65" s="1">
         <v>9999</v>
       </c>
-      <c r="P65" s="1">
-        <v>0</v>
-      </c>
       <c r="Q65" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R65" s="1">
-        <v>0</v>
-      </c>
-      <c r="T65" s="1">
+        <v>1</v>
+      </c>
+      <c r="S65" s="1">
+        <v>0</v>
+      </c>
+      <c r="U65" s="1">
         <v>4</v>
       </c>
-      <c r="U65" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="V65" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="W65" s="1">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="W65" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="X65" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="1">
         <v>4</v>
-      </c>
-      <c r="Y65" s="1">
-        <v>2</v>
       </c>
       <c r="Z65" s="1">
         <v>2</v>
       </c>
       <c r="AA65" s="1">
+        <v>2</v>
+      </c>
+      <c r="AB65" s="1">
         <v>100</v>
       </c>
-      <c r="AB65" s="1">
-        <v>0</v>
-      </c>
       <c r="AC65" s="1">
         <v>0</v>
       </c>
@@ -7674,74 +7845,77 @@
       <c r="AG65" s="1">
         <v>0</v>
       </c>
-      <c r="AI65" s="1">
-        <v>50</v>
+      <c r="AH65" s="1">
+        <v>0</v>
       </c>
       <c r="AJ65" s="1">
         <v>50</v>
       </c>
+      <c r="AK65" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="66" s="1" customFormat="1" spans="3:36">
+    <row r="66" s="1" customFormat="1" spans="3:37">
       <c r="C66" s="1">
         <v>12005</v>
       </c>
       <c r="D66" s="1">
         <v>2005</v>
       </c>
-      <c r="E66" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G66" s="1">
+      <c r="E66" s="1">
+        <v>0</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H66" s="1">
         <v>5</v>
       </c>
-      <c r="H66" s="1">
-        <v>0</v>
-      </c>
       <c r="I66" s="1">
-        <v>50</v>
-      </c>
-      <c r="K66" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="J66" s="1">
+        <v>50</v>
       </c>
       <c r="L66" s="1">
+        <v>0</v>
+      </c>
+      <c r="M66" s="1">
         <v>30</v>
       </c>
-      <c r="M66" s="1">
-        <v>1</v>
-      </c>
       <c r="N66" s="1">
+        <v>1</v>
+      </c>
+      <c r="O66" s="1">
         <v>2</v>
       </c>
-      <c r="O66" s="1">
+      <c r="P66" s="1">
         <v>9999</v>
       </c>
-      <c r="P66" s="1">
-        <v>0</v>
-      </c>
       <c r="Q66" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R66" s="1">
-        <v>0</v>
-      </c>
-      <c r="T66" s="1">
-        <v>0</v>
-      </c>
-      <c r="U66" s="1" t="s">
-        <v>69</v>
+        <v>1</v>
+      </c>
+      <c r="S66" s="1">
+        <v>0</v>
+      </c>
+      <c r="U66" s="1">
+        <v>0</v>
       </c>
       <c r="V66" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="W66" s="1">
+        <v>70</v>
+      </c>
+      <c r="W66" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="X66" s="1">
         <v>30</v>
       </c>
-      <c r="X66" s="1">
-        <v>0</v>
-      </c>
       <c r="Y66" s="1">
         <v>0</v>
       </c>
@@ -7749,11 +7923,11 @@
         <v>0</v>
       </c>
       <c r="AA66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB66" s="1">
         <v>20</v>
       </c>
-      <c r="AB66" s="1">
-        <v>0</v>
-      </c>
       <c r="AC66" s="1">
         <v>0</v>
       </c>
@@ -7769,71 +7943,74 @@
       <c r="AG66" s="1">
         <v>0</v>
       </c>
-      <c r="AH66" s="7"/>
-      <c r="AI66" s="1">
-        <v>50</v>
-      </c>
+      <c r="AH66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI66" s="7"/>
       <c r="AJ66" s="1">
         <v>50</v>
       </c>
+      <c r="AK66" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="67" s="1" customFormat="1" spans="3:36">
+    <row r="67" s="1" customFormat="1" spans="3:37">
       <c r="C67" s="1">
         <v>12006</v>
       </c>
       <c r="D67" s="1">
         <v>2006</v>
       </c>
-      <c r="E67" s="1" t="s">
-        <v>124</v>
+      <c r="E67" s="1">
+        <v>0</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="G67" s="1">
+        <v>125</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H67" s="1">
         <v>6</v>
       </c>
-      <c r="H67" s="1">
-        <v>0</v>
-      </c>
       <c r="I67" s="1">
+        <v>0</v>
+      </c>
+      <c r="J67" s="1">
         <v>10</v>
       </c>
-      <c r="K67" s="1">
-        <v>0</v>
-      </c>
       <c r="L67" s="1">
         <v>0</v>
       </c>
       <c r="M67" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N67" s="1">
+        <v>1</v>
+      </c>
+      <c r="O67" s="1">
         <v>2</v>
       </c>
-      <c r="O67" s="1">
+      <c r="P67" s="1">
         <v>9999</v>
       </c>
-      <c r="P67" s="1">
-        <v>0</v>
-      </c>
       <c r="Q67" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R67" s="1">
-        <v>0</v>
-      </c>
-      <c r="T67" s="1">
-        <v>0</v>
-      </c>
-      <c r="U67" s="1" t="s">
-        <v>69</v>
+        <v>1</v>
+      </c>
+      <c r="S67" s="1">
+        <v>0</v>
+      </c>
+      <c r="U67" s="1">
+        <v>0</v>
       </c>
       <c r="V67" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="W67" s="1">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="W67" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="X67" s="1">
         <v>0</v>
@@ -7845,10 +8022,10 @@
         <v>0</v>
       </c>
       <c r="AA67" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AB67" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AC67" s="1">
         <v>0</v>
@@ -7865,86 +8042,89 @@
       <c r="AG67" s="1">
         <v>0</v>
       </c>
-      <c r="AI67" s="1">
-        <v>50</v>
+      <c r="AH67" s="1">
+        <v>0</v>
       </c>
       <c r="AJ67" s="1">
         <v>50</v>
       </c>
+      <c r="AK67" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="68" s="1" customFormat="1" spans="3:36">
+    <row r="68" s="1" customFormat="1" spans="3:37">
       <c r="C68" s="1">
         <v>12007</v>
       </c>
       <c r="D68" s="1">
         <v>2007</v>
       </c>
-      <c r="E68" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F68" s="2" t="s">
+      <c r="E68" s="1">
+        <v>0</v>
+      </c>
+      <c r="F68" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="G68" s="1">
-        <v>1</v>
+      <c r="G68" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="H68" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" s="1">
+        <v>0</v>
+      </c>
+      <c r="J68" s="1">
         <v>10</v>
       </c>
-      <c r="K68" s="1">
-        <v>0</v>
-      </c>
       <c r="L68" s="1">
         <v>0</v>
       </c>
       <c r="M68" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N68" s="1">
         <v>2</v>
       </c>
       <c r="O68" s="1">
+        <v>2</v>
+      </c>
+      <c r="P68" s="1">
         <v>9999</v>
       </c>
-      <c r="P68" s="1">
-        <v>0</v>
-      </c>
       <c r="Q68" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R68" s="1">
-        <v>0</v>
-      </c>
-      <c r="T68" s="1">
+        <v>1</v>
+      </c>
+      <c r="S68" s="1">
+        <v>0</v>
+      </c>
+      <c r="U68" s="1">
         <v>5</v>
       </c>
-      <c r="U68" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="V68" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="W68" s="1">
-        <v>0</v>
+        <v>83</v>
+      </c>
+      <c r="W68" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="X68" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="1">
         <v>5</v>
-      </c>
-      <c r="Y68" s="1">
-        <v>3</v>
       </c>
       <c r="Z68" s="1">
         <v>3</v>
       </c>
       <c r="AA68" s="1">
+        <v>3</v>
+      </c>
+      <c r="AB68" s="1">
         <v>150</v>
       </c>
-      <c r="AB68" s="1">
-        <v>0</v>
-      </c>
       <c r="AC68" s="1">
         <v>0</v>
       </c>
@@ -7960,70 +8140,73 @@
       <c r="AG68" s="1">
         <v>0</v>
       </c>
-      <c r="AI68" s="1">
-        <v>50</v>
+      <c r="AH68" s="1">
+        <v>0</v>
       </c>
       <c r="AJ68" s="1">
         <v>50</v>
       </c>
+      <c r="AK68" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="69" s="1" customFormat="1" spans="3:36">
+    <row r="69" s="1" customFormat="1" spans="3:37">
       <c r="C69" s="1">
         <v>13001</v>
       </c>
       <c r="D69" s="1">
         <v>3001</v>
       </c>
-      <c r="E69" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="F69" s="2" t="s">
+      <c r="E69" s="1">
+        <v>0</v>
+      </c>
+      <c r="F69" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="G69" s="1">
+      <c r="G69" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H69" s="1">
         <v>4</v>
       </c>
-      <c r="H69" s="1">
-        <v>0</v>
-      </c>
       <c r="I69" s="1">
+        <v>0</v>
+      </c>
+      <c r="J69" s="1">
         <v>20</v>
       </c>
-      <c r="K69" s="1">
-        <v>0</v>
-      </c>
       <c r="L69" s="1">
+        <v>0</v>
+      </c>
+      <c r="M69" s="1">
         <v>4</v>
       </c>
-      <c r="M69" s="1">
-        <v>1</v>
-      </c>
       <c r="N69" s="1">
+        <v>1</v>
+      </c>
+      <c r="O69" s="1">
         <v>3</v>
       </c>
-      <c r="O69" s="1">
+      <c r="P69" s="1">
         <v>9999</v>
       </c>
-      <c r="P69" s="1">
-        <v>0</v>
-      </c>
       <c r="Q69" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R69" s="1">
-        <v>0</v>
-      </c>
-      <c r="T69" s="1">
-        <v>0</v>
-      </c>
-      <c r="U69" s="1" t="s">
-        <v>69</v>
+        <v>1</v>
+      </c>
+      <c r="S69" s="1">
+        <v>0</v>
+      </c>
+      <c r="U69" s="1">
+        <v>0</v>
       </c>
       <c r="V69" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="W69" s="1">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="W69" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="X69" s="1">
         <v>0</v>
@@ -8035,10 +8218,10 @@
         <v>0</v>
       </c>
       <c r="AA69" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AB69" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AC69" s="1">
         <v>0</v>
@@ -8055,86 +8238,89 @@
       <c r="AG69" s="1">
         <v>0</v>
       </c>
-      <c r="AI69" s="1">
-        <v>50</v>
+      <c r="AH69" s="1">
+        <v>0</v>
       </c>
       <c r="AJ69" s="1">
         <v>50</v>
       </c>
+      <c r="AK69" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="70" s="1" customFormat="1" spans="3:36">
+    <row r="70" s="1" customFormat="1" spans="3:37">
       <c r="C70" s="1">
         <v>13002</v>
       </c>
       <c r="D70" s="1">
         <v>3002</v>
       </c>
-      <c r="E70" s="1" t="s">
-        <v>144</v>
+      <c r="E70" s="1">
+        <v>0</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="G70" s="1">
-        <v>1</v>
+      <c r="G70" s="1" t="s">
+        <v>146</v>
       </c>
       <c r="H70" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70" s="1">
+        <v>0</v>
+      </c>
+      <c r="J70" s="1">
         <v>10</v>
       </c>
-      <c r="K70" s="1">
-        <v>0</v>
-      </c>
       <c r="L70" s="1">
         <v>0</v>
       </c>
       <c r="M70" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N70" s="1">
+        <v>1</v>
+      </c>
+      <c r="O70" s="1">
         <v>3</v>
       </c>
-      <c r="O70" s="1">
+      <c r="P70" s="1">
         <v>9999</v>
       </c>
-      <c r="P70" s="1">
-        <v>0</v>
-      </c>
       <c r="Q70" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R70" s="1">
-        <v>0</v>
-      </c>
-      <c r="T70" s="1">
+        <v>1</v>
+      </c>
+      <c r="S70" s="1">
+        <v>0</v>
+      </c>
+      <c r="U70" s="1">
         <v>3</v>
       </c>
-      <c r="U70" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="V70" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="W70" s="1">
-        <v>0</v>
+        <v>83</v>
+      </c>
+      <c r="W70" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="X70" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y70" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z70" s="1">
         <v>0</v>
       </c>
       <c r="AA70" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="1">
         <v>120</v>
       </c>
-      <c r="AB70" s="1">
-        <v>0</v>
-      </c>
       <c r="AC70" s="1">
         <v>0</v>
       </c>
@@ -8150,92 +8336,95 @@
       <c r="AG70" s="1">
         <v>0</v>
       </c>
-      <c r="AI70" s="1">
-        <v>50</v>
+      <c r="AH70" s="1">
+        <v>0</v>
       </c>
       <c r="AJ70" s="1">
         <v>50</v>
       </c>
+      <c r="AK70" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="71" s="1" customFormat="1" spans="3:36">
+    <row r="71" s="1" customFormat="1" spans="3:37">
       <c r="C71" s="1">
         <v>13003</v>
       </c>
       <c r="D71" s="1">
         <v>3003</v>
       </c>
-      <c r="E71" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="F71" s="2" t="s">
+      <c r="E71" s="1">
+        <v>0</v>
+      </c>
+      <c r="F71" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="G71" s="1">
-        <v>1</v>
+      <c r="G71" s="2" t="s">
+        <v>149</v>
       </c>
       <c r="H71" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71" s="1">
+        <v>0</v>
+      </c>
+      <c r="J71" s="1">
         <v>10</v>
       </c>
-      <c r="K71" s="1">
-        <v>0</v>
-      </c>
       <c r="L71" s="1">
+        <v>0</v>
+      </c>
+      <c r="M71" s="1">
         <v>5</v>
       </c>
-      <c r="M71" s="1">
-        <v>1</v>
-      </c>
       <c r="N71" s="1">
+        <v>1</v>
+      </c>
+      <c r="O71" s="1">
         <v>3</v>
       </c>
-      <c r="O71" s="1">
+      <c r="P71" s="1">
         <v>9999</v>
       </c>
-      <c r="P71" s="1">
-        <v>0</v>
-      </c>
       <c r="Q71" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R71" s="1">
-        <v>0</v>
-      </c>
-      <c r="T71" s="1">
+        <v>1</v>
+      </c>
+      <c r="S71" s="1">
+        <v>0</v>
+      </c>
+      <c r="U71" s="1">
         <v>2</v>
       </c>
-      <c r="U71" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="V71" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="W71" s="1">
-        <v>0</v>
+        <v>83</v>
+      </c>
+      <c r="W71" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="X71" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="1">
         <v>5</v>
       </c>
-      <c r="Y71" s="1">
-        <v>0</v>
-      </c>
       <c r="Z71" s="1">
         <v>0</v>
       </c>
       <c r="AA71" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB71" s="1">
         <v>35</v>
       </c>
-      <c r="AB71" s="1">
-        <v>0</v>
-      </c>
       <c r="AC71" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD71" s="1">
         <v>65</v>
       </c>
-      <c r="AD71" s="1">
-        <v>0</v>
-      </c>
       <c r="AE71" s="1">
         <v>0</v>
       </c>
@@ -8245,86 +8434,89 @@
       <c r="AG71" s="1">
         <v>0</v>
       </c>
-      <c r="AI71" s="1">
-        <v>50</v>
+      <c r="AH71" s="1">
+        <v>0</v>
       </c>
       <c r="AJ71" s="1">
         <v>50</v>
       </c>
+      <c r="AK71" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="72" s="1" customFormat="1" spans="3:36">
+    <row r="72" s="1" customFormat="1" spans="3:37">
       <c r="C72" s="1">
         <v>13004</v>
       </c>
       <c r="D72" s="1">
         <v>3004</v>
       </c>
-      <c r="E72" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="F72" s="2" t="s">
+      <c r="E72" s="1">
+        <v>0</v>
+      </c>
+      <c r="F72" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="G72" s="1">
+      <c r="G72" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="H72" s="1">
         <v>2</v>
       </c>
-      <c r="H72" s="1">
-        <v>0</v>
-      </c>
       <c r="I72" s="1">
+        <v>0</v>
+      </c>
+      <c r="J72" s="1">
         <v>100</v>
       </c>
-      <c r="K72" s="1">
-        <v>0</v>
-      </c>
       <c r="L72" s="1">
+        <v>0</v>
+      </c>
+      <c r="M72" s="1">
         <v>15</v>
       </c>
-      <c r="M72" s="1">
-        <v>1</v>
-      </c>
       <c r="N72" s="1">
+        <v>1</v>
+      </c>
+      <c r="O72" s="1">
         <v>3</v>
       </c>
-      <c r="O72" s="1">
+      <c r="P72" s="1">
         <v>9999</v>
       </c>
-      <c r="P72" s="1">
-        <v>0</v>
-      </c>
       <c r="Q72" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R72" s="1">
-        <v>0</v>
-      </c>
-      <c r="T72" s="1">
-        <v>0</v>
-      </c>
-      <c r="U72" s="1" t="s">
-        <v>69</v>
+        <v>1</v>
+      </c>
+      <c r="S72" s="1">
+        <v>0</v>
+      </c>
+      <c r="U72" s="1">
+        <v>0</v>
       </c>
       <c r="V72" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="W72" s="1">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="W72" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="X72" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y72" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z72" s="1">
         <v>0</v>
       </c>
       <c r="AA72" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB72" s="1">
         <v>100</v>
       </c>
-      <c r="AB72" s="1">
-        <v>0</v>
-      </c>
       <c r="AC72" s="1">
         <v>0</v>
       </c>
@@ -8340,74 +8532,77 @@
       <c r="AG72" s="1">
         <v>0</v>
       </c>
-      <c r="AI72" s="1">
-        <v>50</v>
+      <c r="AH72" s="1">
+        <v>0</v>
       </c>
       <c r="AJ72" s="1">
         <v>50</v>
       </c>
+      <c r="AK72" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="73" s="1" customFormat="1" spans="3:36">
+    <row r="73" s="1" customFormat="1" spans="3:37">
       <c r="C73" s="1">
         <v>13005</v>
       </c>
       <c r="D73" s="1">
         <v>3005</v>
       </c>
-      <c r="E73" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="G73" s="1">
+      <c r="E73" s="1">
+        <v>0</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="H73" s="1">
         <v>5</v>
       </c>
-      <c r="H73" s="1">
-        <v>0</v>
-      </c>
       <c r="I73" s="1">
-        <v>50</v>
-      </c>
-      <c r="K73" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="J73" s="1">
+        <v>50</v>
       </c>
       <c r="L73" s="1">
+        <v>0</v>
+      </c>
+      <c r="M73" s="1">
         <v>30</v>
       </c>
-      <c r="M73" s="1">
-        <v>1</v>
-      </c>
       <c r="N73" s="1">
+        <v>1</v>
+      </c>
+      <c r="O73" s="1">
         <v>3</v>
       </c>
-      <c r="O73" s="1">
+      <c r="P73" s="1">
         <v>9999</v>
       </c>
-      <c r="P73" s="1">
-        <v>0</v>
-      </c>
       <c r="Q73" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R73" s="1">
-        <v>0</v>
-      </c>
-      <c r="T73" s="1">
-        <v>0</v>
-      </c>
-      <c r="U73" s="1" t="s">
-        <v>69</v>
+        <v>1</v>
+      </c>
+      <c r="S73" s="1">
+        <v>0</v>
+      </c>
+      <c r="U73" s="1">
+        <v>0</v>
       </c>
       <c r="V73" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="W73" s="1">
+        <v>70</v>
+      </c>
+      <c r="W73" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="X73" s="1">
         <v>30</v>
       </c>
-      <c r="X73" s="1">
-        <v>0</v>
-      </c>
       <c r="Y73" s="1">
         <v>0</v>
       </c>
@@ -8415,11 +8610,11 @@
         <v>0</v>
       </c>
       <c r="AA73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB73" s="1">
         <v>20</v>
       </c>
-      <c r="AB73" s="1">
-        <v>0</v>
-      </c>
       <c r="AC73" s="1">
         <v>0</v>
       </c>
@@ -8435,71 +8630,74 @@
       <c r="AG73" s="1">
         <v>0</v>
       </c>
-      <c r="AH73" s="7"/>
-      <c r="AI73" s="1">
-        <v>50</v>
-      </c>
+      <c r="AH73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="7"/>
       <c r="AJ73" s="1">
         <v>50</v>
       </c>
+      <c r="AK73" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="74" s="1" customFormat="1" spans="3:36">
+    <row r="74" s="1" customFormat="1" spans="3:37">
       <c r="C74" s="1">
         <v>13006</v>
       </c>
       <c r="D74" s="1">
         <v>3006</v>
       </c>
-      <c r="E74" s="1" t="s">
-        <v>155</v>
+      <c r="E74" s="1">
+        <v>0</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="G74" s="1">
+        <v>156</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H74" s="1">
         <v>6</v>
       </c>
-      <c r="H74" s="1">
-        <v>0</v>
-      </c>
       <c r="I74" s="1">
+        <v>0</v>
+      </c>
+      <c r="J74" s="1">
         <v>10</v>
       </c>
-      <c r="K74" s="1">
-        <v>0</v>
-      </c>
       <c r="L74" s="1">
         <v>0</v>
       </c>
       <c r="M74" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N74" s="1">
+        <v>1</v>
+      </c>
+      <c r="O74" s="1">
         <v>3</v>
       </c>
-      <c r="O74" s="1">
+      <c r="P74" s="1">
         <v>9999</v>
       </c>
-      <c r="P74" s="1">
-        <v>0</v>
-      </c>
       <c r="Q74" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R74" s="1">
-        <v>0</v>
-      </c>
-      <c r="T74" s="1">
+        <v>1</v>
+      </c>
+      <c r="S74" s="1">
+        <v>0</v>
+      </c>
+      <c r="U74" s="1">
         <v>3</v>
       </c>
-      <c r="U74" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="V74" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="W74" s="1">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="W74" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="X74" s="1">
         <v>0</v>
@@ -8511,10 +8709,10 @@
         <v>0</v>
       </c>
       <c r="AA74" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AB74" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AC74" s="1">
         <v>0</v>
@@ -8531,86 +8729,89 @@
       <c r="AG74" s="1">
         <v>0</v>
       </c>
-      <c r="AI74" s="1">
-        <v>50</v>
+      <c r="AH74" s="1">
+        <v>0</v>
       </c>
       <c r="AJ74" s="1">
         <v>50</v>
       </c>
+      <c r="AK74" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="75" s="1" customFormat="1" spans="3:36">
+    <row r="75" s="1" customFormat="1" spans="3:37">
       <c r="C75" s="1">
         <v>13007</v>
       </c>
       <c r="D75" s="1">
         <v>3007</v>
       </c>
-      <c r="E75" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="F75" s="2" t="s">
+      <c r="E75" s="1">
+        <v>0</v>
+      </c>
+      <c r="F75" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="G75" s="1">
+      <c r="G75" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H75" s="1">
         <v>2</v>
       </c>
-      <c r="H75" s="1">
-        <v>0</v>
-      </c>
       <c r="I75" s="1">
+        <v>0</v>
+      </c>
+      <c r="J75" s="1">
         <v>100</v>
       </c>
-      <c r="K75" s="1">
-        <v>0</v>
-      </c>
       <c r="L75" s="1">
+        <v>0</v>
+      </c>
+      <c r="M75" s="1">
         <v>15</v>
       </c>
-      <c r="M75" s="1">
-        <v>1</v>
-      </c>
       <c r="N75" s="1">
+        <v>1</v>
+      </c>
+      <c r="O75" s="1">
         <v>3</v>
       </c>
-      <c r="O75" s="1">
+      <c r="P75" s="1">
         <v>9999</v>
       </c>
-      <c r="P75" s="1">
-        <v>0</v>
-      </c>
       <c r="Q75" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R75" s="1">
-        <v>0</v>
-      </c>
-      <c r="T75" s="1">
+        <v>1</v>
+      </c>
+      <c r="S75" s="1">
+        <v>0</v>
+      </c>
+      <c r="U75" s="1">
         <v>2</v>
       </c>
-      <c r="U75" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="V75" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="W75" s="1">
-        <v>0</v>
+        <v>83</v>
+      </c>
+      <c r="W75" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="X75" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="1">
         <v>2</v>
       </c>
-      <c r="Y75" s="1">
-        <v>0</v>
-      </c>
       <c r="Z75" s="1">
         <v>0</v>
       </c>
       <c r="AA75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="1">
         <v>120</v>
       </c>
-      <c r="AB75" s="1">
-        <v>0</v>
-      </c>
       <c r="AC75" s="1">
         <v>0</v>
       </c>
@@ -8626,103 +8827,106 @@
       <c r="AG75" s="1">
         <v>0</v>
       </c>
-      <c r="AI75" s="1">
-        <v>50</v>
+      <c r="AH75" s="1">
+        <v>0</v>
       </c>
       <c r="AJ75" s="1">
         <v>50</v>
       </c>
+      <c r="AK75" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="76" s="1" customFormat="1" spans="5:19">
-      <c r="E76" s="2"/>
+    <row r="76" s="1" customFormat="1" spans="6:20">
       <c r="F76" s="2"/>
-      <c r="J76" s="2"/>
+      <c r="G76" s="2"/>
       <c r="K76" s="2"/>
-      <c r="O76" s="2"/>
+      <c r="L76" s="2"/>
       <c r="P76" s="2"/>
       <c r="Q76" s="2"/>
       <c r="R76" s="2"/>
       <c r="S76" s="2"/>
+      <c r="T76" s="2"/>
     </row>
-    <row r="77" s="1" customFormat="1" spans="3:36">
+    <row r="77" s="1" customFormat="1" spans="3:37">
       <c r="C77" s="1">
         <v>21002</v>
       </c>
       <c r="D77" s="1">
         <v>1002</v>
       </c>
-      <c r="E77" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F77" s="2" t="s">
+      <c r="E77" s="1">
+        <v>0</v>
+      </c>
+      <c r="F77" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G77" s="1">
-        <v>1</v>
+      <c r="G77" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="H77" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77" s="1">
+        <v>0</v>
+      </c>
+      <c r="J77" s="1">
         <v>10</v>
       </c>
-      <c r="K77" s="1">
-        <v>0</v>
-      </c>
       <c r="L77" s="1">
         <v>0</v>
       </c>
       <c r="M77" s="1">
+        <v>0</v>
+      </c>
+      <c r="N77" s="1">
         <v>2</v>
       </c>
-      <c r="N77" s="1">
-        <v>1</v>
-      </c>
       <c r="O77" s="1">
+        <v>1</v>
+      </c>
+      <c r="P77" s="1">
         <v>9999</v>
       </c>
-      <c r="P77" s="1">
-        <v>0</v>
-      </c>
       <c r="Q77" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R77" s="1">
-        <v>0</v>
-      </c>
-      <c r="T77" s="1">
+        <v>1</v>
+      </c>
+      <c r="S77" s="1">
+        <v>0</v>
+      </c>
+      <c r="U77" s="1">
         <v>2</v>
-      </c>
-      <c r="U77" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="V77" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="W77" s="1">
-        <v>0</v>
+      <c r="W77" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="X77" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="1">
         <v>2</v>
       </c>
-      <c r="Y77" s="1">
-        <v>0</v>
-      </c>
       <c r="Z77" s="1">
         <v>0</v>
       </c>
       <c r="AA77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="1">
         <v>150</v>
       </c>
-      <c r="AB77" s="1">
-        <v>0</v>
-      </c>
       <c r="AC77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD77" s="1">
         <v>20</v>
       </c>
-      <c r="AD77" s="1">
-        <v>0</v>
-      </c>
       <c r="AE77" s="1">
         <v>0</v>
       </c>
@@ -8732,19 +8936,22 @@
       <c r="AG77" s="1">
         <v>0</v>
       </c>
-      <c r="AH77" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="AI77" s="1">
-        <v>50</v>
+      <c r="AH77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="1" t="s">
+        <v>194</v>
       </c>
       <c r="AJ77" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK77" s="1">
         <v>50</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:L5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 C3:D5 F3:M5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27952" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -298,7 +298,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="201">
   <si>
     <t>_ID</t>
   </si>
@@ -630,6 +630,12 @@
     <t>上阵后，提高人物{1}%的生命倍率和{5}%的物攻倍率（分身和宠物享受）</t>
   </si>
   <si>
+    <t>剑二十三</t>
+  </si>
+  <si>
+    <t>对3*3范围释放从天而降的流光剑气，造成流光剑法*10倍的伤害，并且附带20%的无视防御</t>
+  </si>
+  <si>
     <t>火球术</t>
   </si>
   <si>
@@ -726,6 +732,12 @@
     <t>上阵后，提高人物{1}%的生命倍率和{5}%的魔攻倍率（分身和宠物享受）</t>
   </si>
   <si>
+    <t>魔法大炮</t>
+  </si>
+  <si>
+    <t>每释放一个技能，增加1%攻击倍率和2%生命倍率，最高叠加1000次</t>
+  </si>
+  <si>
     <t>疗伤术</t>
   </si>
   <si>
@@ -814,6 +826,12 @@
   </si>
   <si>
     <t>上阵后，提高人物{1}%的生命倍率和{5}%的道攻倍率（分身和宠物享受）</t>
+  </si>
+  <si>
+    <t>召唤白虎</t>
+  </si>
+  <si>
+    <t>召唤一个技能，继承人物所有属性，并且自身拥有100%无视防御，攻击，防御，血量为人物的1000%</t>
   </si>
   <si>
     <t>定身指环</t>
@@ -1074,12 +1092,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1875,40 +1893,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:AM77"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="C3:AM80"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.35"/>
   <cols>
-    <col min="1" max="1" width="5.625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="3.5" style="2" customWidth="1"/>
+    <col min="1" max="1" width="5.6283185840708" style="2" customWidth="1"/>
+    <col min="2" max="2" width="3.50442477876106" style="2" customWidth="1"/>
     <col min="3" max="5" width="9" style="2"/>
-    <col min="6" max="6" width="11.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.5044247787611" style="2" customWidth="1"/>
     <col min="7" max="7" width="9" style="2" customWidth="1"/>
-    <col min="8" max="8" width="6.375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="9.375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="5.25" style="2" customWidth="1"/>
-    <col min="11" max="11" width="74.875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="10.5" style="2" customWidth="1"/>
-    <col min="13" max="13" width="5.875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="8.375" style="2" customWidth="1"/>
-    <col min="15" max="15" width="5.875" style="2" customWidth="1"/>
-    <col min="16" max="16" width="7.50833333333333" style="2" customWidth="1"/>
-    <col min="17" max="18" width="12.875" style="2" customWidth="1"/>
-    <col min="19" max="20" width="13.5" style="2" customWidth="1"/>
-    <col min="21" max="21" width="7.375" style="2" customWidth="1"/>
-    <col min="22" max="22" width="7.50833333333333" style="2" customWidth="1"/>
-    <col min="23" max="23" width="8.25" style="2" customWidth="1"/>
-    <col min="24" max="24" width="6.5" style="2" customWidth="1"/>
-    <col min="25" max="27" width="7.625" style="2" customWidth="1"/>
-    <col min="28" max="29" width="7.875" style="2" customWidth="1"/>
-    <col min="30" max="30" width="9.625" style="2" customWidth="1"/>
-    <col min="31" max="32" width="7.875" style="2" customWidth="1"/>
-    <col min="33" max="33" width="12.625" style="2" customWidth="1"/>
-    <col min="34" max="34" width="9.625" style="2" customWidth="1"/>
-    <col min="35" max="35" width="27.625" style="2" customWidth="1"/>
-    <col min="36" max="36" width="17.875" style="2" customWidth="1"/>
-    <col min="37" max="37" width="19.75" style="2" customWidth="1"/>
+    <col min="8" max="8" width="6.3716814159292" style="2" customWidth="1"/>
+    <col min="9" max="9" width="9.3716814159292" style="2" customWidth="1"/>
+    <col min="10" max="10" width="5.24778761061947" style="2" customWidth="1"/>
+    <col min="11" max="11" width="74.8761061946903" style="2" customWidth="1"/>
+    <col min="12" max="12" width="10.5044247787611" style="2" customWidth="1"/>
+    <col min="13" max="13" width="5.87610619469027" style="2" customWidth="1"/>
+    <col min="14" max="14" width="8.3716814159292" style="2" customWidth="1"/>
+    <col min="15" max="15" width="5.87610619469027" style="2" customWidth="1"/>
+    <col min="16" max="16" width="7.50442477876106" style="2" customWidth="1"/>
+    <col min="17" max="18" width="12.8761061946903" style="2" customWidth="1"/>
+    <col min="19" max="20" width="13.5044247787611" style="2" customWidth="1"/>
+    <col min="21" max="21" width="7.3716814159292" style="2" customWidth="1"/>
+    <col min="22" max="22" width="7.50442477876106" style="2" customWidth="1"/>
+    <col min="23" max="23" width="8.24778761061947" style="2" customWidth="1"/>
+    <col min="24" max="24" width="6.50442477876106" style="2" customWidth="1"/>
+    <col min="25" max="27" width="7.6283185840708" style="2" customWidth="1"/>
+    <col min="28" max="29" width="7.87610619469027" style="2" customWidth="1"/>
+    <col min="30" max="30" width="9.6283185840708" style="2" customWidth="1"/>
+    <col min="31" max="32" width="7.87610619469027" style="2" customWidth="1"/>
+    <col min="33" max="33" width="12.6283185840708" style="2" customWidth="1"/>
+    <col min="34" max="34" width="9.6283185840708" style="2" customWidth="1"/>
+    <col min="35" max="35" width="27.6283185840708" style="2" customWidth="1"/>
+    <col min="36" max="36" width="17.8761061946903" style="2" customWidth="1"/>
+    <col min="37" max="37" width="19.7522123893805" style="2" customWidth="1"/>
     <col min="38" max="38" width="9" style="2"/>
-    <col min="39" max="39" width="19.25" style="2" customWidth="1"/>
+    <col min="39" max="39" width="19.2477876106195" style="2" customWidth="1"/>
     <col min="40" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -2286,7 +2304,7 @@
         <v>60</v>
       </c>
       <c r="R6" s="1">
-        <f t="shared" ref="R6:R16" si="0">P6*5</f>
+        <f t="shared" ref="R6:R17" si="0">P6*5</f>
         <v>3000</v>
       </c>
       <c r="S6" s="1">
@@ -3411,129 +3429,129 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" spans="7:7">
-      <c r="G17" s="2"/>
+    <row r="17" s="1" customFormat="1" spans="3:37">
+      <c r="C17" s="1">
+        <v>1012</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1012</v>
+      </c>
+      <c r="E17" s="1">
+        <v>12</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>10</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="N17" s="1">
+        <v>2</v>
+      </c>
+      <c r="O17" s="1">
+        <v>1</v>
+      </c>
+      <c r="P17" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>1</v>
+      </c>
+      <c r="R17" s="1">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="S17" s="1">
+        <v>50</v>
+      </c>
+      <c r="T17" s="1">
+        <v>10</v>
+      </c>
+      <c r="U17" s="1">
+        <v>3</v>
+      </c>
+      <c r="V17" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="W17" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="X17" s="1">
+        <v>15</v>
+      </c>
+      <c r="Y17" s="1">
+        <v>5</v>
+      </c>
+      <c r="Z17" s="1">
+        <v>3</v>
+      </c>
+      <c r="AA17" s="1">
+        <v>3</v>
+      </c>
+      <c r="AB17" s="1">
+        <v>500</v>
+      </c>
+      <c r="AC17" s="1">
+        <v>100</v>
+      </c>
+      <c r="AD17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK17" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" s="1" customFormat="1" spans="3:37">
-      <c r="C18" s="1">
-        <v>2001</v>
-      </c>
-      <c r="D18" s="1">
-        <v>2001</v>
-      </c>
-      <c r="E18" s="1">
-        <v>1</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="H18" s="1">
-        <v>1</v>
-      </c>
-      <c r="I18" s="1">
-        <v>0</v>
-      </c>
-      <c r="J18" s="1">
-        <v>10</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L18" s="1">
-        <v>0</v>
-      </c>
-      <c r="M18" s="1">
-        <v>0</v>
-      </c>
-      <c r="N18" s="1">
-        <v>1</v>
-      </c>
-      <c r="O18" s="1">
-        <v>2</v>
-      </c>
-      <c r="P18" s="1">
-        <v>600</v>
-      </c>
-      <c r="Q18" s="1">
-        <v>60</v>
-      </c>
-      <c r="R18" s="1">
-        <f t="shared" ref="R18:R28" si="1">P18*5</f>
-        <v>3000</v>
-      </c>
-      <c r="S18" s="1">
-        <v>2</v>
-      </c>
-      <c r="T18" s="1">
-        <v>0</v>
-      </c>
-      <c r="U18" s="1">
-        <v>2</v>
-      </c>
-      <c r="V18" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="W18" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="X18" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="1">
-        <v>1</v>
-      </c>
-      <c r="Z18" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="1">
-        <v>120</v>
-      </c>
-      <c r="AC18" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD18" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE18" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF18" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG18" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH18" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ18" s="1">
-        <v>50</v>
-      </c>
-      <c r="AK18" s="1">
-        <v>4006</v>
-      </c>
+    <row r="18" s="1" customFormat="1" spans="7:7">
+      <c r="G18" s="2"/>
     </row>
     <row r="19" s="1" customFormat="1" spans="3:37">
       <c r="C19" s="1">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="D19" s="1">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="E19" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="H19" s="1">
         <v>1</v>
@@ -3545,7 +3563,7 @@
         <v>10</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L19" s="1">
         <v>0</v>
@@ -3566,17 +3584,17 @@
         <v>60</v>
       </c>
       <c r="R19" s="1">
-        <f>P19*2.5</f>
-        <v>1500</v>
+        <f t="shared" ref="R19:R30" si="1">P19*5</f>
+        <v>3000</v>
       </c>
       <c r="S19" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T19" s="1">
         <v>0</v>
       </c>
       <c r="U19" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V19" s="1" t="s">
         <v>83</v>
@@ -3597,13 +3615,13 @@
         <v>0</v>
       </c>
       <c r="AB19" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AC19" s="1">
         <v>0</v>
       </c>
       <c r="AD19" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AE19" s="1">
         <v>0</v>
@@ -3626,22 +3644,22 @@
     </row>
     <row r="20" s="1" customFormat="1" spans="3:37">
       <c r="C20" s="1">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="D20" s="1">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="E20" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F20" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="G20" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="H20" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I20" s="1">
         <v>0</v>
@@ -3650,16 +3668,16 @@
         <v>10</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L20" s="1">
         <v>0</v>
       </c>
       <c r="M20" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N20" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O20" s="1">
         <v>2</v>
@@ -3671,11 +3689,11 @@
         <v>60</v>
       </c>
       <c r="R20" s="1">
-        <f t="shared" si="1"/>
-        <v>3000</v>
+        <f>P20*2.5</f>
+        <v>1500</v>
       </c>
       <c r="S20" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T20" s="1">
         <v>0</v>
@@ -3687,28 +3705,28 @@
         <v>83</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="X20" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z20" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA20" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB20" s="1">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="AC20" s="1">
         <v>0</v>
       </c>
       <c r="AD20" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AE20" s="1">
         <v>0</v>
@@ -3731,22 +3749,22 @@
     </row>
     <row r="21" s="1" customFormat="1" spans="3:37">
       <c r="C21" s="1">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="D21" s="1">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="E21" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F21" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="G21" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="H21" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I21" s="1">
         <v>0</v>
@@ -3755,13 +3773,13 @@
         <v>10</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L21" s="1">
         <v>0</v>
       </c>
       <c r="M21" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N21" s="1">
         <v>2</v>
@@ -3786,19 +3804,19 @@
         <v>0</v>
       </c>
       <c r="U21" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V21" s="1" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="W21" s="1" t="s">
         <v>89</v>
       </c>
       <c r="X21" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y21" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z21" s="1">
         <v>2</v>
@@ -3807,7 +3825,7 @@
         <v>2</v>
       </c>
       <c r="AB21" s="1">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AC21" s="1">
         <v>0</v>
@@ -3826,9 +3844,6 @@
       </c>
       <c r="AH21" s="1">
         <v>0</v>
-      </c>
-      <c r="AI21" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="AJ21" s="1">
         <v>50</v>
@@ -3839,62 +3854,62 @@
     </row>
     <row r="22" s="1" customFormat="1" spans="3:37">
       <c r="C22" s="1">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="D22" s="1">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="E22" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F22" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1">
+        <v>0</v>
+      </c>
+      <c r="J22" s="1">
+        <v>10</v>
+      </c>
+      <c r="K22" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G22" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H22" s="1">
-        <v>5</v>
-      </c>
-      <c r="I22" s="1">
-        <v>5</v>
-      </c>
-      <c r="J22" s="1">
-        <v>50</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="L22" s="1">
         <v>0</v>
       </c>
       <c r="M22" s="1">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="N22" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O22" s="1">
         <v>2</v>
       </c>
       <c r="P22" s="1">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="Q22" s="1">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="R22" s="1">
         <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="S22" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T22" s="1">
         <v>0</v>
       </c>
       <c r="U22" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V22" s="1" t="s">
         <v>70</v>
@@ -3903,16 +3918,16 @@
         <v>89</v>
       </c>
       <c r="X22" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Y22" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z22" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA22" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB22" s="1">
         <v>100</v>
@@ -3935,8 +3950,8 @@
       <c r="AH22" s="1">
         <v>0</v>
       </c>
-      <c r="AI22" s="7" t="s">
-        <v>90</v>
+      <c r="AI22" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="AJ22" s="1">
         <v>50</v>
@@ -3947,37 +3962,37 @@
     </row>
     <row r="23" s="1" customFormat="1" spans="3:37">
       <c r="C23" s="1">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="D23" s="1">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="E23" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="G23" s="1" t="s">
-        <v>125</v>
+      <c r="G23" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="H23" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I23" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J23" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="L23" s="1">
         <v>0</v>
       </c>
       <c r="M23" s="1">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="N23" s="1">
         <v>1</v>
@@ -4008,10 +4023,10 @@
         <v>70</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="X23" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Y23" s="1">
         <v>0</v>
@@ -4023,7 +4038,7 @@
         <v>0</v>
       </c>
       <c r="AB23" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AC23" s="1">
         <v>0</v>
@@ -4042,6 +4057,9 @@
       </c>
       <c r="AH23" s="1">
         <v>0</v>
+      </c>
+      <c r="AI23" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="AJ23" s="1">
         <v>50</v>
@@ -4052,22 +4070,22 @@
     </row>
     <row r="24" s="1" customFormat="1" spans="3:37">
       <c r="C24" s="1">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D24" s="1">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="E24" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="G24" s="2" t="s">
-        <v>128</v>
+      <c r="G24" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="H24" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I24" s="1">
         <v>0</v>
@@ -4076,59 +4094,59 @@
         <v>10</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="L24" s="1">
         <v>0</v>
       </c>
-      <c r="M24" s="6">
-        <v>5</v>
+      <c r="M24" s="1">
+        <v>0</v>
       </c>
       <c r="N24" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O24" s="1">
         <v>2</v>
       </c>
       <c r="P24" s="1">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="Q24" s="1">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="R24" s="1">
         <f t="shared" si="1"/>
-        <v>3000</v>
-      </c>
-      <c r="S24" s="6">
-        <v>6</v>
+        <v>1000</v>
+      </c>
+      <c r="S24" s="1">
+        <v>1</v>
       </c>
       <c r="T24" s="1">
         <v>0</v>
       </c>
       <c r="U24" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V24" s="1" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="X24" s="1">
         <v>0</v>
       </c>
       <c r="Y24" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z24" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA24" s="1">
-        <v>3</v>
-      </c>
-      <c r="AB24" s="6">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="AB24" s="1">
+        <v>50</v>
       </c>
       <c r="AC24" s="1">
         <v>0</v>
@@ -4147,9 +4165,6 @@
       </c>
       <c r="AH24" s="1">
         <v>0</v>
-      </c>
-      <c r="AI24" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="AJ24" s="1">
         <v>50</v>
@@ -4160,83 +4175,83 @@
     </row>
     <row r="25" s="1" customFormat="1" spans="3:37">
       <c r="C25" s="1">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D25" s="1">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="E25" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="H25" s="1">
-        <v>2008</v>
+        <v>1</v>
       </c>
       <c r="I25" s="1">
         <v>0</v>
       </c>
       <c r="J25" s="1">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="L25" s="1">
         <v>0</v>
       </c>
-      <c r="M25" s="1">
-        <v>30</v>
+      <c r="M25" s="6">
+        <v>5</v>
       </c>
       <c r="N25" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O25" s="1">
         <v>2</v>
       </c>
       <c r="P25" s="1">
-        <v>30</v>
+        <v>600</v>
       </c>
       <c r="Q25" s="1">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="R25" s="1">
         <f t="shared" si="1"/>
-        <v>150</v>
-      </c>
-      <c r="S25" s="1">
-        <v>1</v>
+        <v>3000</v>
+      </c>
+      <c r="S25" s="6">
+        <v>6</v>
       </c>
       <c r="T25" s="1">
         <v>0</v>
       </c>
       <c r="U25" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V25" s="1" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="X25" s="1">
         <v>0</v>
       </c>
       <c r="Y25" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z25" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA25" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB25" s="1">
-        <v>50</v>
+        <v>3</v>
+      </c>
+      <c r="AB25" s="6">
+        <v>300</v>
       </c>
       <c r="AC25" s="1">
         <v>0</v>
@@ -4256,8 +4271,8 @@
       <c r="AH25" s="1">
         <v>0</v>
       </c>
-      <c r="AI25" s="1" t="s">
-        <v>133</v>
+      <c r="AI25" s="6" t="s">
+        <v>131</v>
       </c>
       <c r="AJ25" s="1">
         <v>50</v>
@@ -4268,83 +4283,83 @@
     </row>
     <row r="26" s="1" customFormat="1" spans="3:37">
       <c r="C26" s="1">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D26" s="1">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="E26" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F26" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H26" s="1">
+        <v>2008</v>
+      </c>
+      <c r="I26" s="1">
+        <v>0</v>
+      </c>
+      <c r="J26" s="1">
+        <v>200</v>
+      </c>
+      <c r="K26" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H26" s="1">
-        <v>3</v>
-      </c>
-      <c r="I26" s="1">
-        <v>0</v>
-      </c>
-      <c r="J26" s="1">
-        <v>10</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>136</v>
-      </c>
       <c r="L26" s="1">
         <v>0</v>
       </c>
       <c r="M26" s="1">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N26" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O26" s="1">
         <v>2</v>
       </c>
       <c r="P26" s="1">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="Q26" s="1">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="R26" s="1">
         <f t="shared" si="1"/>
-        <v>1500</v>
+        <v>150</v>
       </c>
       <c r="S26" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T26" s="1">
         <v>0</v>
       </c>
       <c r="U26" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V26" s="1" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="X26" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y26" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z26" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA26" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB26" s="1">
-        <v>400</v>
+        <v>50</v>
       </c>
       <c r="AC26" s="1">
         <v>0</v>
@@ -4365,7 +4380,7 @@
         <v>0</v>
       </c>
       <c r="AI26" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AJ26" s="1">
         <v>50</v>
@@ -4376,37 +4391,37 @@
     </row>
     <row r="27" s="1" customFormat="1" spans="3:37">
       <c r="C27" s="1">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D27" s="1">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="E27" s="1">
+        <v>9</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="H27" s="1">
+        <v>3</v>
+      </c>
+      <c r="I27" s="1">
+        <v>0</v>
+      </c>
+      <c r="J27" s="1">
         <v>10</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="K27" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="H27" s="1">
-        <v>2010</v>
-      </c>
-      <c r="I27" s="1">
-        <v>0</v>
-      </c>
-      <c r="J27" s="1">
-        <v>100</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="L27" s="1">
         <v>0</v>
       </c>
       <c r="M27" s="1">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N27" s="1">
         <v>2</v>
@@ -4415,17 +4430,17 @@
         <v>2</v>
       </c>
       <c r="P27" s="1">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="Q27" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="R27" s="1">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>1500</v>
       </c>
       <c r="S27" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T27" s="1">
         <v>0</v>
@@ -4440,7 +4455,7 @@
         <v>89</v>
       </c>
       <c r="X27" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y27" s="1">
         <v>5</v>
@@ -4452,7 +4467,7 @@
         <v>4</v>
       </c>
       <c r="AB27" s="1">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="AC27" s="1">
         <v>0</v>
@@ -4472,22 +4487,25 @@
       <c r="AH27" s="1">
         <v>0</v>
       </c>
+      <c r="AI27" s="1" t="s">
+        <v>139</v>
+      </c>
       <c r="AJ27" s="1">
         <v>50</v>
       </c>
       <c r="AK27" s="1">
-        <v>4102</v>
+        <v>4006</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" spans="3:37">
       <c r="C28" s="1">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D28" s="1">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="E28" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>140</v>
@@ -4496,13 +4514,13 @@
         <v>140</v>
       </c>
       <c r="H28" s="1">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="I28" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J28" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>141</v>
@@ -4530,10 +4548,10 @@
         <v>50</v>
       </c>
       <c r="S28" s="1">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T28" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U28" s="1">
         <v>3</v>
@@ -4557,117 +4575,220 @@
         <v>4</v>
       </c>
       <c r="AB28" s="1">
+        <v>150</v>
+      </c>
+      <c r="AC28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK28" s="1">
+        <v>4102</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="3:37">
+      <c r="C29" s="1">
+        <v>2011</v>
+      </c>
+      <c r="D29" s="1">
+        <v>2011</v>
+      </c>
+      <c r="E29" s="1">
+        <v>11</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H29" s="1">
+        <v>8</v>
+      </c>
+      <c r="I29" s="1">
+        <v>11</v>
+      </c>
+      <c r="J29" s="1">
+        <v>0</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="L29" s="1">
+        <v>0</v>
+      </c>
+      <c r="M29" s="1">
+        <v>30</v>
+      </c>
+      <c r="N29" s="1">
+        <v>2</v>
+      </c>
+      <c r="O29" s="1">
+        <v>2</v>
+      </c>
+      <c r="P29" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q29" s="1">
+        <v>1</v>
+      </c>
+      <c r="R29" s="1">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="S29" s="1">
+        <v>50</v>
+      </c>
+      <c r="T29" s="1">
+        <v>10</v>
+      </c>
+      <c r="U29" s="1">
+        <v>3</v>
+      </c>
+      <c r="V29" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="W29" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="X29" s="1">
+        <v>15</v>
+      </c>
+      <c r="Y29" s="1">
+        <v>5</v>
+      </c>
+      <c r="Z29" s="1">
+        <v>4</v>
+      </c>
+      <c r="AA29" s="1">
+        <v>4</v>
+      </c>
+      <c r="AB29" s="1">
         <v>500</v>
       </c>
-      <c r="AC28" s="1">
+      <c r="AC29" s="1">
         <v>100</v>
       </c>
-      <c r="AD28" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE28" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF28" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG28" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH28" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ28" s="1">
-        <v>50</v>
-      </c>
-      <c r="AK28" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="7:7">
-      <c r="G29" s="2"/>
+      <c r="AD29" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK29" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="3:37">
       <c r="C30" s="1">
-        <v>3001</v>
+        <v>2012</v>
       </c>
       <c r="D30" s="1">
-        <v>3001</v>
+        <v>2012</v>
       </c>
       <c r="E30" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="H30" s="1">
+        <v>8</v>
+      </c>
+      <c r="I30" s="1">
+        <v>0</v>
+      </c>
+      <c r="J30" s="1">
+        <v>10</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="L30" s="1">
+        <v>0</v>
+      </c>
+      <c r="M30" s="1">
+        <v>30</v>
+      </c>
+      <c r="N30" s="1">
+        <v>2</v>
+      </c>
+      <c r="O30" s="1">
+        <v>1</v>
+      </c>
+      <c r="P30" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>1</v>
+      </c>
+      <c r="R30" s="1">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="S30" s="1">
+        <v>50</v>
+      </c>
+      <c r="T30" s="1">
+        <v>10</v>
+      </c>
+      <c r="U30" s="1">
+        <v>3</v>
+      </c>
+      <c r="V30" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="W30" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="X30" s="1">
+        <v>15</v>
+      </c>
+      <c r="Y30" s="1">
+        <v>5</v>
+      </c>
+      <c r="Z30" s="1">
         <v>4</v>
       </c>
-      <c r="I30" s="1">
-        <v>0</v>
-      </c>
-      <c r="J30" s="1">
-        <v>20</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="L30" s="1">
-        <v>0</v>
-      </c>
-      <c r="M30" s="1">
+      <c r="AA30" s="1">
         <v>4</v>
       </c>
-      <c r="N30" s="1">
-        <v>1</v>
-      </c>
-      <c r="O30" s="1">
-        <v>3</v>
-      </c>
-      <c r="P30" s="1">
-        <v>600</v>
-      </c>
-      <c r="Q30" s="1">
-        <v>60</v>
-      </c>
-      <c r="R30" s="1">
-        <v>20</v>
-      </c>
-      <c r="S30" s="1">
-        <v>3</v>
-      </c>
-      <c r="T30" s="1">
-        <v>0</v>
-      </c>
-      <c r="U30" s="1">
-        <v>5</v>
-      </c>
-      <c r="V30" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="W30" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="X30" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y30" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z30" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA30" s="1">
-        <v>0</v>
-      </c>
       <c r="AB30" s="1">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AC30" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD30" s="1">
         <v>0</v>
@@ -4688,147 +4809,45 @@
         <v>50</v>
       </c>
       <c r="AK30" s="1">
-        <v>4006</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" spans="3:37">
-      <c r="C31" s="1">
-        <v>3002</v>
-      </c>
-      <c r="D31" s="1">
-        <v>3002</v>
-      </c>
-      <c r="E31" s="1">
-        <v>2</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="H31" s="1">
-        <v>1</v>
-      </c>
-      <c r="I31" s="1">
-        <v>0</v>
-      </c>
-      <c r="J31" s="1">
-        <v>10</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="L31" s="1">
-        <v>0</v>
-      </c>
-      <c r="M31" s="1">
-        <v>0</v>
-      </c>
-      <c r="N31" s="1">
-        <v>1</v>
-      </c>
-      <c r="O31" s="1">
-        <v>3</v>
-      </c>
-      <c r="P31" s="1">
-        <v>600</v>
-      </c>
-      <c r="Q31" s="1">
-        <v>60</v>
-      </c>
-      <c r="R31" s="1">
-        <f>P31*1.8</f>
-        <v>1080</v>
-      </c>
-      <c r="S31" s="1">
-        <v>2</v>
-      </c>
-      <c r="T31" s="1">
-        <v>0</v>
-      </c>
-      <c r="U31" s="1">
-        <v>3</v>
-      </c>
-      <c r="V31" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="W31" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="X31" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y31" s="1">
-        <v>1</v>
-      </c>
-      <c r="Z31" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA31" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB31" s="1">
-        <v>120</v>
-      </c>
-      <c r="AC31" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD31" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE31" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF31" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG31" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH31" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ31" s="1">
-        <v>50</v>
-      </c>
-      <c r="AK31" s="1">
-        <v>4006</v>
-      </c>
+    <row r="31" s="1" customFormat="1" spans="7:7">
+      <c r="G31" s="2"/>
     </row>
     <row r="32" s="1" customFormat="1" spans="3:37">
       <c r="C32" s="1">
-        <v>3003</v>
+        <v>3001</v>
       </c>
       <c r="D32" s="1">
-        <v>3003</v>
+        <v>3001</v>
       </c>
       <c r="E32" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F32" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H32" s="1">
+        <v>4</v>
+      </c>
+      <c r="I32" s="1">
+        <v>0</v>
+      </c>
+      <c r="J32" s="1">
+        <v>20</v>
+      </c>
+      <c r="K32" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="G32" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="H32" s="1">
-        <v>1</v>
-      </c>
-      <c r="I32" s="1">
-        <v>0</v>
-      </c>
-      <c r="J32" s="1">
-        <v>10</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="L32" s="1">
         <v>0</v>
       </c>
       <c r="M32" s="1">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N32" s="1">
         <v>1</v>
@@ -4843,20 +4862,19 @@
         <v>60</v>
       </c>
       <c r="R32" s="1">
-        <f t="shared" ref="R30:R40" si="2">P32*5</f>
-        <v>3000</v>
+        <v>20</v>
       </c>
       <c r="S32" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T32" s="1">
         <v>0</v>
       </c>
       <c r="U32" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V32" s="1" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="W32" s="1" t="s">
         <v>107</v>
@@ -4865,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="Y32" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z32" s="1">
         <v>0</v>
@@ -4874,13 +4892,13 @@
         <v>0</v>
       </c>
       <c r="AB32" s="1">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="AC32" s="1">
         <v>0</v>
       </c>
       <c r="AD32" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AE32" s="1">
         <v>0</v>
@@ -4893,9 +4911,6 @@
       </c>
       <c r="AH32" s="1">
         <v>0</v>
-      </c>
-      <c r="AI32" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="AJ32" s="1">
         <v>50</v>
@@ -4906,37 +4921,37 @@
     </row>
     <row r="33" s="1" customFormat="1" spans="3:37">
       <c r="C33" s="1">
-        <v>3004</v>
+        <v>3002</v>
       </c>
       <c r="D33" s="1">
-        <v>3004</v>
+        <v>3002</v>
       </c>
       <c r="E33" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="H33" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I33" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J33" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="L33" s="1">
         <v>0</v>
       </c>
       <c r="M33" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N33" s="1">
         <v>1</v>
@@ -4951,8 +4966,8 @@
         <v>60</v>
       </c>
       <c r="R33" s="1">
-        <f t="shared" si="2"/>
-        <v>3000</v>
+        <f>P33*1.8</f>
+        <v>1080</v>
       </c>
       <c r="S33" s="1">
         <v>2</v>
@@ -4961,13 +4976,13 @@
         <v>0</v>
       </c>
       <c r="U33" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V33" s="1" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="W33" s="1" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="X33" s="1">
         <v>0</v>
@@ -4982,7 +4997,7 @@
         <v>0</v>
       </c>
       <c r="AB33" s="1">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AC33" s="1">
         <v>0</v>
@@ -5011,37 +5026,37 @@
     </row>
     <row r="34" s="1" customFormat="1" spans="3:37">
       <c r="C34" s="1">
-        <v>3005</v>
+        <v>3003</v>
       </c>
       <c r="D34" s="1">
-        <v>3005</v>
+        <v>3003</v>
       </c>
       <c r="E34" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H34" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I34" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J34" s="1">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>88</v>
+        <v>154</v>
       </c>
       <c r="L34" s="1">
         <v>0</v>
       </c>
       <c r="M34" s="1">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="N34" s="1">
         <v>1</v>
@@ -5050,35 +5065,35 @@
         <v>3</v>
       </c>
       <c r="P34" s="1">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="Q34" s="1">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="R34" s="1">
-        <f t="shared" si="2"/>
-        <v>1000</v>
+        <f t="shared" ref="R32:R43" si="2">P34*5</f>
+        <v>3000</v>
       </c>
       <c r="S34" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T34" s="1">
         <v>0</v>
       </c>
       <c r="U34" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V34" s="1" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="X34" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Y34" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z34" s="1">
         <v>0</v>
@@ -5087,13 +5102,13 @@
         <v>0</v>
       </c>
       <c r="AB34" s="1">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="AC34" s="1">
         <v>0</v>
       </c>
       <c r="AD34" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AE34" s="1">
         <v>0</v>
@@ -5107,8 +5122,8 @@
       <c r="AH34" s="1">
         <v>0</v>
       </c>
-      <c r="AI34" s="7" t="s">
-        <v>90</v>
+      <c r="AI34" s="1" t="s">
+        <v>155</v>
       </c>
       <c r="AJ34" s="1">
         <v>50</v>
@@ -5119,37 +5134,37 @@
     </row>
     <row r="35" s="1" customFormat="1" spans="3:37">
       <c r="C35" s="1">
-        <v>3006</v>
+        <v>3004</v>
       </c>
       <c r="D35" s="1">
-        <v>3006</v>
+        <v>3004</v>
       </c>
       <c r="E35" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="G35" s="1" t="s">
-        <v>156</v>
+      <c r="G35" s="2" t="s">
+        <v>157</v>
       </c>
       <c r="H35" s="1">
+        <v>2</v>
+      </c>
+      <c r="I35" s="1">
         <v>6</v>
       </c>
-      <c r="I35" s="1">
-        <v>0</v>
-      </c>
       <c r="J35" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L35" s="1">
         <v>0</v>
       </c>
       <c r="M35" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N35" s="1">
         <v>1</v>
@@ -5158,23 +5173,23 @@
         <v>3</v>
       </c>
       <c r="P35" s="1">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="Q35" s="1">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="R35" s="1">
         <f t="shared" si="2"/>
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="S35" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T35" s="1">
         <v>0</v>
       </c>
       <c r="U35" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V35" s="1" t="s">
         <v>70</v>
@@ -5186,7 +5201,7 @@
         <v>0</v>
       </c>
       <c r="Y35" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z35" s="1">
         <v>0</v>
@@ -5195,7 +5210,7 @@
         <v>0</v>
       </c>
       <c r="AB35" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AC35" s="1">
         <v>0</v>
@@ -5224,37 +5239,37 @@
     </row>
     <row r="36" s="1" customFormat="1" spans="3:37">
       <c r="C36" s="1">
-        <v>3007</v>
+        <v>3005</v>
       </c>
       <c r="D36" s="1">
-        <v>3007</v>
+        <v>3005</v>
       </c>
       <c r="E36" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>159</v>
       </c>
       <c r="H36" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I36" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J36" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>160</v>
+        <v>88</v>
       </c>
       <c r="L36" s="1">
         <v>0</v>
       </c>
       <c r="M36" s="1">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="N36" s="1">
         <v>1</v>
@@ -5263,35 +5278,35 @@
         <v>3</v>
       </c>
       <c r="P36" s="1">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="Q36" s="1">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="R36" s="1">
         <f t="shared" si="2"/>
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="S36" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T36" s="1">
         <v>0</v>
       </c>
       <c r="U36" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V36" s="1" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="W36" s="1" t="s">
         <v>89</v>
       </c>
       <c r="X36" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Y36" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z36" s="1">
         <v>0</v>
@@ -5300,7 +5315,7 @@
         <v>0</v>
       </c>
       <c r="AB36" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AC36" s="1">
         <v>0</v>
@@ -5319,6 +5334,9 @@
       </c>
       <c r="AH36" s="1">
         <v>0</v>
+      </c>
+      <c r="AI36" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="AJ36" s="1">
         <v>50</v>
@@ -5329,37 +5347,37 @@
     </row>
     <row r="37" s="1" customFormat="1" spans="3:37">
       <c r="C37" s="1">
-        <v>3008</v>
+        <v>3006</v>
       </c>
       <c r="D37" s="1">
-        <v>3008</v>
+        <v>3006</v>
       </c>
       <c r="E37" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F37" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="H37" s="1">
+        <v>6</v>
+      </c>
+      <c r="I37" s="1">
+        <v>0</v>
+      </c>
+      <c r="J37" s="1">
+        <v>10</v>
+      </c>
+      <c r="K37" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="G37" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="H37" s="1">
-        <v>3008</v>
-      </c>
-      <c r="I37" s="1">
-        <v>0</v>
-      </c>
-      <c r="J37" s="1">
-        <v>200</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="L37" s="1">
         <v>0</v>
       </c>
       <c r="M37" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N37" s="1">
         <v>1</v>
@@ -5368,14 +5386,14 @@
         <v>3</v>
       </c>
       <c r="P37" s="1">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="Q37" s="1">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="R37" s="1">
         <f t="shared" si="2"/>
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="S37" s="1">
         <v>1</v>
@@ -5384,7 +5402,7 @@
         <v>0</v>
       </c>
       <c r="U37" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V37" s="1" t="s">
         <v>70</v>
@@ -5393,7 +5411,7 @@
         <v>93</v>
       </c>
       <c r="X37" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y37" s="1">
         <v>0</v>
@@ -5405,7 +5423,7 @@
         <v>0</v>
       </c>
       <c r="AB37" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AC37" s="1">
         <v>0</v>
@@ -5424,9 +5442,6 @@
       </c>
       <c r="AH37" s="1">
         <v>0</v>
-      </c>
-      <c r="AI37" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="AJ37" s="1">
         <v>50</v>
@@ -5437,19 +5452,19 @@
     </row>
     <row r="38" s="1" customFormat="1" spans="3:37">
       <c r="C38" s="1">
-        <v>3009</v>
+        <v>3007</v>
       </c>
       <c r="D38" s="1">
-        <v>3009</v>
+        <v>3007</v>
       </c>
       <c r="E38" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H38" s="1">
         <v>2</v>
@@ -5461,7 +5476,7 @@
         <v>100</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="L38" s="1">
         <v>0</v>
@@ -5476,16 +5491,17 @@
         <v>3</v>
       </c>
       <c r="P38" s="1">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="Q38" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="R38" s="1">
-        <v>200</v>
+        <f t="shared" si="2"/>
+        <v>3000</v>
       </c>
       <c r="S38" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T38" s="1">
         <v>0</v>
@@ -5503,7 +5519,7 @@
         <v>0</v>
       </c>
       <c r="Y38" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z38" s="1">
         <v>0</v>
@@ -5512,7 +5528,7 @@
         <v>0</v>
       </c>
       <c r="AB38" s="1">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="AC38" s="1">
         <v>0</v>
@@ -5541,37 +5557,37 @@
     </row>
     <row r="39" s="1" customFormat="1" spans="3:37">
       <c r="C39" s="1">
-        <v>3010</v>
+        <v>3008</v>
       </c>
       <c r="D39" s="1">
-        <v>3010</v>
+        <v>3008</v>
       </c>
       <c r="E39" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H39" s="1">
-        <v>8</v>
+        <v>3008</v>
       </c>
       <c r="I39" s="1">
         <v>0</v>
       </c>
       <c r="J39" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L39" s="1">
         <v>0</v>
       </c>
       <c r="M39" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N39" s="1">
         <v>1</v>
@@ -5580,13 +5596,14 @@
         <v>3</v>
       </c>
       <c r="P39" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="Q39" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R39" s="1">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="S39" s="1">
         <v>1</v>
@@ -5598,16 +5615,16 @@
         <v>0</v>
       </c>
       <c r="V39" s="1" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="W39" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="X39" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y39" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z39" s="1">
         <v>0</v>
@@ -5616,10 +5633,10 @@
         <v>0</v>
       </c>
       <c r="AB39" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AC39" s="1">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AD39" s="1">
         <v>0</v>
@@ -5636,39 +5653,42 @@
       <c r="AH39" s="1">
         <v>0</v>
       </c>
+      <c r="AI39" s="1" t="s">
+        <v>168</v>
+      </c>
       <c r="AJ39" s="1">
         <v>50</v>
       </c>
       <c r="AK39" s="1">
-        <v>4102</v>
+        <v>4006</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" spans="3:37">
       <c r="C40" s="1">
-        <v>3011</v>
+        <v>3009</v>
       </c>
       <c r="D40" s="1">
-        <v>3011</v>
+        <v>3009</v>
       </c>
       <c r="E40" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>170</v>
       </c>
       <c r="H40" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I40" s="1">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J40" s="1">
-        <v>0</v>
-      </c>
-      <c r="K40" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="K40" s="1" t="s">
         <v>171</v>
       </c>
       <c r="L40" s="1">
@@ -5678,29 +5698,28 @@
         <v>30</v>
       </c>
       <c r="N40" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O40" s="1">
         <v>3</v>
       </c>
       <c r="P40" s="1">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="Q40" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="R40" s="1">
-        <f t="shared" si="2"/>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="S40" s="1">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T40" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U40" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V40" s="1" t="s">
         <v>83</v>
@@ -5709,76 +5728,176 @@
         <v>89</v>
       </c>
       <c r="X40" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Y40" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z40" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA40" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB40" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="AC40" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE40" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF40" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG40" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH40" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ40" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK40" s="1">
+        <v>4006</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" spans="3:37">
+      <c r="C41" s="1">
+        <v>3010</v>
+      </c>
+      <c r="D41" s="1">
+        <v>3010</v>
+      </c>
+      <c r="E41" s="1">
+        <v>10</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H41" s="1">
+        <v>8</v>
+      </c>
+      <c r="I41" s="1">
+        <v>0</v>
+      </c>
+      <c r="J41" s="1">
         <v>100</v>
       </c>
-      <c r="AD40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ40" s="1">
-        <v>50</v>
-      </c>
-      <c r="AK40" s="1">
-        <v>0</v>
+      <c r="K41" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L41" s="1">
+        <v>0</v>
+      </c>
+      <c r="M41" s="1">
+        <v>0</v>
+      </c>
+      <c r="N41" s="1">
+        <v>1</v>
+      </c>
+      <c r="O41" s="1">
+        <v>3</v>
+      </c>
+      <c r="P41" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q41" s="1">
+        <v>1</v>
+      </c>
+      <c r="R41" s="1">
+        <v>1</v>
+      </c>
+      <c r="S41" s="1">
+        <v>1</v>
+      </c>
+      <c r="T41" s="1">
+        <v>0</v>
+      </c>
+      <c r="U41" s="1">
+        <v>0</v>
+      </c>
+      <c r="V41" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="W41" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="X41" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="1">
+        <v>3</v>
+      </c>
+      <c r="Z41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="1">
+        <v>20</v>
+      </c>
+      <c r="AC41" s="1">
+        <v>400</v>
+      </c>
+      <c r="AD41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ41" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK41" s="1">
+        <v>4102</v>
       </c>
     </row>
-    <row r="41" s="1" customFormat="1" spans="6:7">
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-    </row>
-    <row r="42" s="1" customFormat="1" spans="3:36">
+    <row r="42" s="1" customFormat="1" spans="3:37">
       <c r="C42" s="1">
-        <v>4001</v>
+        <v>3011</v>
       </c>
       <c r="D42" s="1">
-        <v>4001</v>
+        <v>3011</v>
       </c>
       <c r="E42" s="1">
-        <v>0</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>173</v>
+        <v>11</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>174</v>
       </c>
       <c r="H42" s="1">
-        <v>4001</v>
+        <v>8</v>
       </c>
       <c r="I42" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J42" s="1">
-        <v>-100</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>174</v>
+        <v>0</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>175</v>
       </c>
       <c r="L42" s="1">
         <v>0</v>
@@ -5787,157 +5906,159 @@
         <v>30</v>
       </c>
       <c r="N42" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O42" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P42" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q42" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" s="1">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>50</v>
       </c>
       <c r="S42" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="T42" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U42" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V42" s="1" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="W42" s="1" t="s">
         <v>89</v>
       </c>
       <c r="X42" s="1">
+        <v>15</v>
+      </c>
+      <c r="Y42" s="1">
+        <v>5</v>
+      </c>
+      <c r="Z42" s="1">
+        <v>4</v>
+      </c>
+      <c r="AA42" s="1">
+        <v>4</v>
+      </c>
+      <c r="AB42" s="1">
+        <v>500</v>
+      </c>
+      <c r="AC42" s="1">
+        <v>100</v>
+      </c>
+      <c r="AD42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK42" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" spans="3:37">
+      <c r="C43" s="1">
+        <v>3012</v>
+      </c>
+      <c r="D43" s="1">
+        <v>3012</v>
+      </c>
+      <c r="E43" s="1">
+        <v>12</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="H43" s="1">
+        <v>1</v>
+      </c>
+      <c r="I43" s="1">
+        <v>0</v>
+      </c>
+      <c r="J43" s="1">
+        <v>10</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="L43" s="1">
+        <v>0</v>
+      </c>
+      <c r="M43" s="1">
+        <v>30</v>
+      </c>
+      <c r="N43" s="1">
         <v>2</v>
       </c>
-      <c r="Y42" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z42" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA42" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB42" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC42" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD42" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE42" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF42" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG42" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH42" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI42" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="AJ42" s="1">
-        <v>99999</v>
-      </c>
-    </row>
-    <row r="43" s="1" customFormat="1" spans="3:36">
-      <c r="C43" s="1">
-        <v>4002</v>
-      </c>
-      <c r="D43" s="1">
-        <v>4002</v>
-      </c>
-      <c r="E43" s="1">
-        <v>0</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="H43" s="1">
-        <v>4002</v>
-      </c>
-      <c r="I43" s="1">
-        <v>0</v>
-      </c>
-      <c r="J43" s="1">
-        <v>200</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="L43" s="1">
-        <v>0</v>
-      </c>
-      <c r="M43" s="1">
-        <v>60</v>
-      </c>
-      <c r="N43" s="1">
-        <v>0</v>
-      </c>
       <c r="O43" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P43" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q43" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" s="1">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>50</v>
       </c>
       <c r="S43" s="1">
+        <v>50</v>
+      </c>
+      <c r="T43" s="1">
         <v>10</v>
       </c>
-      <c r="T43" s="1">
-        <v>0</v>
-      </c>
       <c r="U43" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V43" s="1" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="W43" s="1" t="s">
         <v>89</v>
       </c>
       <c r="X43" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y43" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z43" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA43" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB43" s="1">
+        <v>500</v>
+      </c>
+      <c r="AC43" s="1">
         <v>100</v>
       </c>
-      <c r="AC43" s="1">
-        <v>0</v>
-      </c>
       <c r="AD43" s="1">
         <v>0</v>
       </c>
@@ -5953,155 +6074,160 @@
       <c r="AH43" s="1">
         <v>0</v>
       </c>
-      <c r="AI43" s="7"/>
       <c r="AJ43" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK43" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" s="1" customFormat="1" spans="6:7">
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+    </row>
+    <row r="45" s="1" customFormat="1" spans="3:36">
+      <c r="C45" s="1">
+        <v>4001</v>
+      </c>
+      <c r="D45" s="1">
+        <v>4001</v>
+      </c>
+      <c r="E45" s="1">
+        <v>0</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="H45" s="1">
+        <v>4001</v>
+      </c>
+      <c r="I45" s="1">
+        <v>0</v>
+      </c>
+      <c r="J45" s="1">
+        <v>-100</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="L45" s="1">
+        <v>0</v>
+      </c>
+      <c r="M45" s="1">
+        <v>30</v>
+      </c>
+      <c r="N45" s="1">
+        <v>0</v>
+      </c>
+      <c r="O45" s="1">
+        <v>0</v>
+      </c>
+      <c r="P45" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="1">
+        <v>0</v>
+      </c>
+      <c r="R45" s="1">
+        <v>1</v>
+      </c>
+      <c r="S45" s="1">
+        <v>0</v>
+      </c>
+      <c r="T45" s="1">
+        <v>0</v>
+      </c>
+      <c r="U45" s="1">
+        <v>0</v>
+      </c>
+      <c r="V45" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="W45" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="X45" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y45" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI45" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="AJ45" s="1">
         <v>99999</v>
       </c>
     </row>
-    <row r="44" s="1" customFormat="1" spans="3:36">
-      <c r="C44" s="1">
-        <v>4003</v>
-      </c>
-      <c r="D44" s="1">
-        <v>4003</v>
-      </c>
-      <c r="E44" s="1">
-        <v>0</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="H44" s="1">
-        <v>4003</v>
-      </c>
-      <c r="I44" s="1">
-        <v>0</v>
-      </c>
-      <c r="J44" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="L44" s="1">
-        <v>0</v>
-      </c>
-      <c r="M44" s="1">
+    <row r="46" s="1" customFormat="1" spans="3:36">
+      <c r="C46" s="1">
+        <v>4002</v>
+      </c>
+      <c r="D46" s="1">
+        <v>4002</v>
+      </c>
+      <c r="E46" s="1">
+        <v>0</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="H46" s="1">
+        <v>4002</v>
+      </c>
+      <c r="I46" s="1">
+        <v>0</v>
+      </c>
+      <c r="J46" s="1">
+        <v>200</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L46" s="1">
+        <v>0</v>
+      </c>
+      <c r="M46" s="1">
         <v>60</v>
       </c>
-      <c r="N44" s="1">
-        <v>0</v>
-      </c>
-      <c r="O44" s="1">
-        <v>0</v>
-      </c>
-      <c r="P44" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="1">
-        <v>0</v>
-      </c>
-      <c r="R44" s="1">
-        <v>1</v>
-      </c>
-      <c r="S44" s="1">
-        <v>0</v>
-      </c>
-      <c r="T44" s="1">
-        <v>0</v>
-      </c>
-      <c r="U44" s="1">
-        <v>0</v>
-      </c>
-      <c r="V44" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="W44" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="X44" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y44" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z44" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA44" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB44" s="1">
-        <v>100</v>
-      </c>
-      <c r="AC44" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD44" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE44" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF44" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG44" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH44" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI44" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="AJ44" s="1">
-        <v>99999</v>
-      </c>
-    </row>
-    <row r="45" s="1" customFormat="1" spans="6:7">
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-    </row>
-    <row r="46" s="1" customFormat="1" spans="3:37">
-      <c r="C46" s="1">
-        <v>9001</v>
-      </c>
-      <c r="D46" s="1">
-        <v>9001</v>
-      </c>
-      <c r="E46" s="1">
-        <v>0</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="H46" s="1">
-        <v>9</v>
-      </c>
-      <c r="I46" s="1">
-        <v>0</v>
-      </c>
-      <c r="J46" s="1">
-        <v>0</v>
-      </c>
-      <c r="L46" s="1">
-        <v>0</v>
-      </c>
-      <c r="M46" s="1">
-        <v>0</v>
-      </c>
       <c r="N46" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P46" s="1">
         <v>0</v>
@@ -6113,22 +6239,25 @@
         <v>1</v>
       </c>
       <c r="S46" s="1">
+        <v>10</v>
+      </c>
+      <c r="T46" s="1">
         <v>0</v>
       </c>
       <c r="U46" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" s="1" t="s">
         <v>70</v>
       </c>
       <c r="W46" s="1" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="X46" s="1">
         <v>0</v>
       </c>
       <c r="Y46" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z46" s="1">
         <v>0</v>
@@ -6157,49 +6286,50 @@
       <c r="AH46" s="1">
         <v>0</v>
       </c>
+      <c r="AI46" s="7"/>
       <c r="AJ46" s="1">
-        <v>50</v>
-      </c>
-      <c r="AK46" s="1">
-        <v>50</v>
+        <v>99999</v>
       </c>
     </row>
-    <row r="47" s="1" customFormat="1" spans="3:37">
+    <row r="47" s="1" customFormat="1" spans="3:36">
       <c r="C47" s="1">
-        <v>9002</v>
+        <v>4003</v>
       </c>
       <c r="D47" s="1">
-        <v>9002</v>
+        <v>4003</v>
       </c>
       <c r="E47" s="1">
         <v>0</v>
       </c>
-      <c r="F47" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>184</v>
+      <c r="F47" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>186</v>
       </c>
       <c r="H47" s="1">
-        <v>9</v>
+        <v>4003</v>
       </c>
       <c r="I47" s="1">
         <v>0</v>
       </c>
       <c r="J47" s="1">
-        <v>0</v>
+        <v>-1</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>187</v>
       </c>
       <c r="L47" s="1">
         <v>0</v>
       </c>
       <c r="M47" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N47" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O47" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P47" s="1">
         <v>0</v>
@@ -6213,20 +6343,23 @@
       <c r="S47" s="1">
         <v>0</v>
       </c>
+      <c r="T47" s="1">
+        <v>0</v>
+      </c>
       <c r="U47" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V47" s="1" t="s">
         <v>70</v>
       </c>
       <c r="W47" s="1" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="X47" s="1">
         <v>0</v>
       </c>
       <c r="Y47" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z47" s="1">
         <v>0</v>
@@ -6255,41 +6388,41 @@
       <c r="AH47" s="1">
         <v>0</v>
       </c>
+      <c r="AI47" s="1" t="s">
+        <v>188</v>
+      </c>
       <c r="AJ47" s="1">
-        <v>50</v>
-      </c>
-      <c r="AK47" s="1">
-        <v>50</v>
+        <v>99999</v>
       </c>
     </row>
-    <row r="48" s="1" customFormat="1"/>
+    <row r="48" s="1" customFormat="1" spans="6:7">
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+    </row>
     <row r="49" s="1" customFormat="1" spans="3:37">
       <c r="C49" s="1">
-        <v>10001</v>
+        <v>9001</v>
       </c>
       <c r="D49" s="1">
-        <v>10001</v>
+        <v>9001</v>
       </c>
       <c r="E49" s="1">
         <v>0</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>189</v>
       </c>
       <c r="H49" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I49" s="1">
         <v>0</v>
       </c>
       <c r="J49" s="1">
-        <v>1</v>
-      </c>
-      <c r="K49" s="1" t="s">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="L49" s="1">
         <v>0</v>
@@ -6316,10 +6449,10 @@
         <v>0</v>
       </c>
       <c r="U49" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V49" s="1" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="W49" s="1" t="s">
         <v>107</v>
@@ -6337,7 +6470,7 @@
         <v>0</v>
       </c>
       <c r="AB49" s="1">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="AC49" s="1">
         <v>0</v>
@@ -6364,38 +6497,35 @@
         <v>50</v>
       </c>
     </row>
-    <row r="50" spans="3:37">
-      <c r="C50" s="2">
-        <v>10002</v>
-      </c>
-      <c r="D50" s="2">
-        <v>10002</v>
+    <row r="50" s="1" customFormat="1" spans="3:37">
+      <c r="C50" s="1">
+        <v>9002</v>
+      </c>
+      <c r="D50" s="1">
+        <v>9002</v>
       </c>
       <c r="E50" s="1">
         <v>0</v>
       </c>
-      <c r="F50" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="H50" s="2">
-        <v>4</v>
+      <c r="F50" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="H50" s="1">
+        <v>9</v>
       </c>
       <c r="I50" s="1">
         <v>0</v>
       </c>
-      <c r="J50" s="2">
-        <v>10</v>
-      </c>
-      <c r="K50" s="2" t="s">
-        <v>188</v>
+      <c r="J50" s="1">
+        <v>0</v>
       </c>
       <c r="L50" s="1">
         <v>0</v>
       </c>
-      <c r="M50" s="2">
+      <c r="M50" s="1">
         <v>0</v>
       </c>
       <c r="N50" s="1">
@@ -6416,9 +6546,8 @@
       <c r="S50" s="1">
         <v>0</v>
       </c>
-      <c r="T50" s="1"/>
-      <c r="U50" s="2">
-        <v>0</v>
+      <c r="U50" s="1">
+        <v>2</v>
       </c>
       <c r="V50" s="1" t="s">
         <v>70</v>
@@ -6426,10 +6555,10 @@
       <c r="W50" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="X50" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y50" s="2">
+      <c r="X50" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="1">
         <v>1</v>
       </c>
       <c r="Z50" s="1">
@@ -6438,7 +6567,7 @@
       <c r="AA50" s="1">
         <v>0</v>
       </c>
-      <c r="AB50" s="2">
+      <c r="AB50" s="1">
         <v>100</v>
       </c>
       <c r="AC50" s="1">
@@ -6459,7 +6588,6 @@
       <c r="AH50" s="1">
         <v>0</v>
       </c>
-      <c r="AI50" s="1"/>
       <c r="AJ50" s="1">
         <v>50</v>
       </c>
@@ -6467,243 +6595,140 @@
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="3:37">
-      <c r="C51" s="2">
-        <v>10003</v>
-      </c>
-      <c r="D51" s="2">
-        <v>10003</v>
-      </c>
-      <c r="E51" s="1">
-        <v>0</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="H51" s="2">
-        <v>1</v>
-      </c>
-      <c r="I51" s="1">
-        <v>0</v>
-      </c>
-      <c r="J51" s="2">
-        <v>1</v>
-      </c>
-      <c r="K51" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="L51" s="1">
-        <v>0</v>
-      </c>
-      <c r="M51" s="2">
-        <v>0</v>
-      </c>
-      <c r="N51" s="1">
-        <v>1</v>
-      </c>
-      <c r="O51" s="1">
-        <v>1</v>
-      </c>
-      <c r="P51" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="1">
-        <v>0</v>
-      </c>
-      <c r="R51" s="1">
-        <v>1</v>
-      </c>
-      <c r="S51" s="1">
-        <v>0</v>
-      </c>
-      <c r="T51" s="1"/>
-      <c r="U51" s="1">
-        <v>0</v>
-      </c>
-      <c r="V51" s="1" t="s">
+    <row r="51" s="1" customFormat="1"/>
+    <row r="52" s="1" customFormat="1" spans="3:37">
+      <c r="C52" s="1">
+        <v>10001</v>
+      </c>
+      <c r="D52" s="1">
+        <v>10001</v>
+      </c>
+      <c r="E52" s="1">
+        <v>0</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H52" s="1">
+        <v>1</v>
+      </c>
+      <c r="I52" s="1">
+        <v>0</v>
+      </c>
+      <c r="J52" s="1">
+        <v>1</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="L52" s="1">
+        <v>0</v>
+      </c>
+      <c r="M52" s="1">
+        <v>0</v>
+      </c>
+      <c r="N52" s="1">
+        <v>1</v>
+      </c>
+      <c r="O52" s="1">
+        <v>1</v>
+      </c>
+      <c r="P52" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="1">
+        <v>0</v>
+      </c>
+      <c r="R52" s="1">
+        <v>1</v>
+      </c>
+      <c r="S52" s="1">
+        <v>0</v>
+      </c>
+      <c r="U52" s="1">
+        <v>3</v>
+      </c>
+      <c r="V52" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="W51" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="X51" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y51" s="1">
+      <c r="W52" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="X52" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z52" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="1">
+        <v>150</v>
+      </c>
+      <c r="AC52" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ52" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK52" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="3:37">
+      <c r="C53" s="2">
+        <v>10002</v>
+      </c>
+      <c r="D53" s="2">
+        <v>10002</v>
+      </c>
+      <c r="E53" s="1">
+        <v>0</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H53" s="2">
+        <v>4</v>
+      </c>
+      <c r="I53" s="1">
+        <v>0</v>
+      </c>
+      <c r="J53" s="2">
         <v>10</v>
       </c>
-      <c r="Z51" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA51" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB51" s="1">
-        <v>100</v>
-      </c>
-      <c r="AC51" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD51" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE51" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF51" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG51" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI51" s="1"/>
-      <c r="AJ51" s="1">
-        <v>50</v>
-      </c>
-      <c r="AK51" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="52" spans="3:37">
-      <c r="C52" s="2">
-        <v>10004</v>
-      </c>
-      <c r="D52" s="2">
-        <v>10004</v>
-      </c>
-      <c r="E52" s="1">
-        <v>0</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="H52" s="2">
-        <v>4</v>
-      </c>
-      <c r="I52" s="1">
-        <v>0</v>
-      </c>
-      <c r="J52" s="2">
-        <v>10</v>
-      </c>
-      <c r="K52" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="L52" s="1">
-        <v>0</v>
-      </c>
-      <c r="M52" s="2">
-        <v>0</v>
-      </c>
-      <c r="N52" s="1">
-        <v>1</v>
-      </c>
-      <c r="O52" s="2">
-        <v>1</v>
-      </c>
-      <c r="P52" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="1">
-        <v>0</v>
-      </c>
-      <c r="R52" s="1">
-        <v>1</v>
-      </c>
-      <c r="S52" s="1">
-        <v>0</v>
-      </c>
-      <c r="T52" s="1"/>
-      <c r="U52" s="2">
-        <v>3</v>
-      </c>
-      <c r="V52" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="W52" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="X52" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y52" s="2">
-        <v>4</v>
-      </c>
-      <c r="Z52" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA52" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB52" s="2">
-        <v>50</v>
-      </c>
-      <c r="AC52" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD52" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE52" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF52" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG52" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH52" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ52" s="1">
-        <v>50</v>
-      </c>
-      <c r="AK52" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="53" s="1" customFormat="1" spans="3:37">
-      <c r="C53" s="1">
-        <v>10005</v>
-      </c>
-      <c r="D53" s="1">
-        <v>10005</v>
-      </c>
-      <c r="E53" s="1">
-        <v>0</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H53" s="1">
-        <v>1</v>
-      </c>
-      <c r="I53" s="1">
-        <v>0</v>
-      </c>
-      <c r="J53" s="1">
-        <v>10</v>
-      </c>
       <c r="K53" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L53" s="1">
         <v>0</v>
       </c>
-      <c r="M53" s="1">
+      <c r="M53" s="2">
         <v>0</v>
       </c>
       <c r="N53" s="1">
@@ -6712,7 +6737,7 @@
       <c r="O53" s="1">
         <v>1</v>
       </c>
-      <c r="P53" s="2">
+      <c r="P53" s="1">
         <v>0</v>
       </c>
       <c r="Q53" s="1">
@@ -6724,8 +6749,9 @@
       <c r="S53" s="1">
         <v>0</v>
       </c>
-      <c r="U53" s="1">
-        <v>2</v>
+      <c r="T53" s="1"/>
+      <c r="U53" s="2">
+        <v>0</v>
       </c>
       <c r="V53" s="1" t="s">
         <v>70</v>
@@ -6733,11 +6759,11 @@
       <c r="W53" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="X53" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y53" s="1">
-        <v>2</v>
+      <c r="X53" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="2">
+        <v>1</v>
       </c>
       <c r="Z53" s="1">
         <v>0</v>
@@ -6745,14 +6771,14 @@
       <c r="AA53" s="1">
         <v>0</v>
       </c>
-      <c r="AB53" s="1">
-        <v>150</v>
+      <c r="AB53" s="2">
+        <v>100</v>
       </c>
       <c r="AC53" s="1">
         <v>0</v>
       </c>
       <c r="AD53" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AE53" s="1">
         <v>0</v>
@@ -6766,6 +6792,7 @@
       <c r="AH53" s="1">
         <v>0</v>
       </c>
+      <c r="AI53" s="1"/>
       <c r="AJ53" s="1">
         <v>50</v>
       </c>
@@ -6773,45 +6800,151 @@
         <v>50</v>
       </c>
     </row>
-    <row r="55" s="1" customFormat="1" spans="3:37">
-      <c r="C55" s="1">
-        <v>11001</v>
-      </c>
-      <c r="D55" s="1">
-        <v>1001</v>
+    <row r="54" spans="3:37">
+      <c r="C54" s="2">
+        <v>10003</v>
+      </c>
+      <c r="D54" s="2">
+        <v>10003</v>
+      </c>
+      <c r="E54" s="1">
+        <v>0</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H54" s="2">
+        <v>1</v>
+      </c>
+      <c r="I54" s="1">
+        <v>0</v>
+      </c>
+      <c r="J54" s="2">
+        <v>1</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="L54" s="1">
+        <v>0</v>
+      </c>
+      <c r="M54" s="2">
+        <v>0</v>
+      </c>
+      <c r="N54" s="1">
+        <v>1</v>
+      </c>
+      <c r="O54" s="1">
+        <v>1</v>
+      </c>
+      <c r="P54" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="1">
+        <v>0</v>
+      </c>
+      <c r="R54" s="1">
+        <v>1</v>
+      </c>
+      <c r="S54" s="1">
+        <v>0</v>
+      </c>
+      <c r="T54" s="1"/>
+      <c r="U54" s="1">
+        <v>0</v>
+      </c>
+      <c r="V54" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="W54" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="X54" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="1">
+        <v>10</v>
+      </c>
+      <c r="Z54" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB54" s="1">
+        <v>100</v>
+      </c>
+      <c r="AC54" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD54" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE54" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF54" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG54" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH54" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI54" s="1"/>
+      <c r="AJ54" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK54" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" spans="3:37">
+      <c r="C55" s="2">
+        <v>10004</v>
+      </c>
+      <c r="D55" s="2">
+        <v>10004</v>
       </c>
       <c r="E55" s="1">
         <v>0</v>
       </c>
-      <c r="F55" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H55" s="1">
-        <v>1</v>
+      <c r="F55" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H55" s="2">
+        <v>4</v>
       </c>
       <c r="I55" s="1">
         <v>0</v>
       </c>
-      <c r="J55" s="1">
+      <c r="J55" s="2">
         <v>10</v>
       </c>
+      <c r="K55" s="2" t="s">
+        <v>196</v>
+      </c>
       <c r="L55" s="1">
         <v>0</v>
       </c>
-      <c r="M55" s="1">
+      <c r="M55" s="2">
         <v>0</v>
       </c>
       <c r="N55" s="1">
         <v>1</v>
       </c>
-      <c r="O55" s="1">
-        <v>1</v>
-      </c>
-      <c r="P55" s="1">
-        <v>9999</v>
+      <c r="O55" s="2">
+        <v>1</v>
+      </c>
+      <c r="P55" s="2">
+        <v>0</v>
       </c>
       <c r="Q55" s="1">
         <v>0</v>
@@ -6822,20 +6955,21 @@
       <c r="S55" s="1">
         <v>0</v>
       </c>
-      <c r="U55" s="1">
-        <v>1</v>
-      </c>
-      <c r="V55" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="W55" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="X55" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y55" s="1">
-        <v>1</v>
+      <c r="T55" s="1"/>
+      <c r="U55" s="2">
+        <v>3</v>
+      </c>
+      <c r="V55" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="W55" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="X55" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y55" s="2">
+        <v>4</v>
       </c>
       <c r="Z55" s="1">
         <v>0</v>
@@ -6843,22 +6977,22 @@
       <c r="AA55" s="1">
         <v>0</v>
       </c>
-      <c r="AB55" s="1">
-        <v>120</v>
-      </c>
-      <c r="AC55" s="1">
+      <c r="AB55" s="2">
+        <v>50</v>
+      </c>
+      <c r="AC55" s="2">
         <v>0</v>
       </c>
       <c r="AD55" s="1">
         <v>0</v>
       </c>
-      <c r="AE55" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF55" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG55" s="1">
+      <c r="AE55" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF55" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG55" s="2">
         <v>0</v>
       </c>
       <c r="AH55" s="1">
@@ -6873,16 +7007,16 @@
     </row>
     <row r="56" s="1" customFormat="1" spans="3:37">
       <c r="C56" s="1">
-        <v>11002</v>
+        <v>10005</v>
       </c>
       <c r="D56" s="1">
-        <v>1002</v>
+        <v>10005</v>
       </c>
       <c r="E56" s="1">
         <v>0</v>
       </c>
-      <c r="F56" s="1" t="s">
-        <v>72</v>
+      <c r="F56" s="2" t="s">
+        <v>198</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>73</v>
@@ -6896,6 +7030,9 @@
       <c r="J56" s="1">
         <v>10</v>
       </c>
+      <c r="K56" s="2" t="s">
+        <v>198</v>
+      </c>
       <c r="L56" s="1">
         <v>0</v>
       </c>
@@ -6903,13 +7040,13 @@
         <v>0</v>
       </c>
       <c r="N56" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O56" s="1">
         <v>1</v>
       </c>
-      <c r="P56" s="1">
-        <v>9999</v>
+      <c r="P56" s="2">
+        <v>0</v>
       </c>
       <c r="Q56" s="1">
         <v>0</v>
@@ -6966,125 +7103,27 @@
         <v>50</v>
       </c>
       <c r="AK56" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="57" s="1" customFormat="1" spans="3:37">
-      <c r="C57" s="1">
-        <v>11003</v>
-      </c>
-      <c r="D57" s="1">
-        <v>1003</v>
-      </c>
-      <c r="E57" s="1">
-        <v>0</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H57" s="1">
-        <v>1</v>
-      </c>
-      <c r="I57" s="1">
-        <v>0</v>
-      </c>
-      <c r="J57" s="1">
-        <v>10</v>
-      </c>
-      <c r="L57" s="1">
-        <v>0</v>
-      </c>
-      <c r="M57" s="1">
-        <v>0</v>
-      </c>
-      <c r="N57" s="1">
-        <v>2</v>
-      </c>
-      <c r="O57" s="1">
-        <v>1</v>
-      </c>
-      <c r="P57" s="1">
-        <v>9999</v>
-      </c>
-      <c r="Q57" s="1">
-        <v>0</v>
-      </c>
-      <c r="R57" s="1">
-        <v>1</v>
-      </c>
-      <c r="S57" s="1">
-        <v>0</v>
-      </c>
-      <c r="U57" s="1">
-        <v>1</v>
-      </c>
-      <c r="V57" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="W57" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="X57" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y57" s="1">
-        <v>5</v>
-      </c>
-      <c r="Z57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB57" s="1">
-        <v>100</v>
-      </c>
-      <c r="AC57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ57" s="1">
-        <v>50</v>
-      </c>
-      <c r="AK57" s="1">
         <v>50</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" spans="3:37">
       <c r="C58" s="1">
-        <v>11004</v>
+        <v>11001</v>
       </c>
       <c r="D58" s="1">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="E58" s="1">
         <v>0</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="H58" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I58" s="1">
         <v>0</v>
@@ -7096,7 +7135,7 @@
         <v>0</v>
       </c>
       <c r="M58" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N58" s="1">
         <v>1</v>
@@ -7117,16 +7156,16 @@
         <v>0</v>
       </c>
       <c r="U58" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V58" s="1" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="W58" s="1" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="X58" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y58" s="1">
         <v>1</v>
@@ -7138,7 +7177,7 @@
         <v>0</v>
       </c>
       <c r="AB58" s="1">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="AC58" s="1">
         <v>0</v>
@@ -7157,9 +7196,6 @@
       </c>
       <c r="AH58" s="1">
         <v>0</v>
-      </c>
-      <c r="AI58" s="1" t="s">
-        <v>193</v>
       </c>
       <c r="AJ58" s="1">
         <v>50</v>
@@ -7170,37 +7206,37 @@
     </row>
     <row r="59" s="1" customFormat="1" spans="3:37">
       <c r="C59" s="1">
-        <v>11005</v>
+        <v>11002</v>
       </c>
       <c r="D59" s="1">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="E59" s="1">
         <v>0</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="H59" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I59" s="1">
         <v>0</v>
       </c>
       <c r="J59" s="1">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="L59" s="1">
         <v>0</v>
       </c>
       <c r="M59" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N59" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O59" s="1">
         <v>1</v>
@@ -7218,19 +7254,19 @@
         <v>0</v>
       </c>
       <c r="U59" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V59" s="1" t="s">
         <v>70</v>
       </c>
       <c r="W59" s="1" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="X59" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Y59" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z59" s="1">
         <v>0</v>
@@ -7239,14 +7275,14 @@
         <v>0</v>
       </c>
       <c r="AB59" s="1">
+        <v>150</v>
+      </c>
+      <c r="AC59" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD59" s="1">
         <v>20</v>
       </c>
-      <c r="AC59" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD59" s="1">
-        <v>0</v>
-      </c>
       <c r="AE59" s="1">
         <v>0</v>
       </c>
@@ -7259,7 +7295,6 @@
       <c r="AH59" s="1">
         <v>0</v>
       </c>
-      <c r="AI59" s="7"/>
       <c r="AJ59" s="1">
         <v>50</v>
       </c>
@@ -7269,22 +7304,22 @@
     </row>
     <row r="60" s="1" customFormat="1" spans="3:37">
       <c r="C60" s="1">
-        <v>11006</v>
+        <v>11003</v>
       </c>
       <c r="D60" s="1">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="E60" s="1">
         <v>0</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H60" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I60" s="1">
         <v>0</v>
@@ -7299,7 +7334,7 @@
         <v>0</v>
       </c>
       <c r="N60" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O60" s="1">
         <v>1</v>
@@ -7317,19 +7352,19 @@
         <v>0</v>
       </c>
       <c r="U60" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V60" s="1" t="s">
         <v>70</v>
       </c>
       <c r="W60" s="1" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="X60" s="1">
         <v>0</v>
       </c>
       <c r="Y60" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z60" s="1">
         <v>0</v>
@@ -7338,7 +7373,7 @@
         <v>0</v>
       </c>
       <c r="AB60" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AC60" s="1">
         <v>0</v>
@@ -7367,22 +7402,22 @@
     </row>
     <row r="61" s="1" customFormat="1" spans="3:37">
       <c r="C61" s="1">
-        <v>11007</v>
+        <v>11004</v>
       </c>
       <c r="D61" s="1">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="E61" s="1">
         <v>0</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>95</v>
+        <v>80</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="H61" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I61" s="1">
         <v>0</v>
@@ -7394,7 +7429,7 @@
         <v>0</v>
       </c>
       <c r="M61" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N61" s="1">
         <v>1</v>
@@ -7415,16 +7450,16 @@
         <v>0</v>
       </c>
       <c r="U61" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V61" s="1" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="W61" s="1" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="X61" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y61" s="1">
         <v>1</v>
@@ -7436,7 +7471,7 @@
         <v>0</v>
       </c>
       <c r="AB61" s="1">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AC61" s="1">
         <v>0</v>
@@ -7455,6 +7490,9 @@
       </c>
       <c r="AH61" s="1">
         <v>0</v>
+      </c>
+      <c r="AI61" s="1" t="s">
+        <v>199</v>
       </c>
       <c r="AJ61" s="1">
         <v>50</v>
@@ -7465,40 +7503,40 @@
     </row>
     <row r="62" s="1" customFormat="1" spans="3:37">
       <c r="C62" s="1">
-        <v>12001</v>
+        <v>11005</v>
       </c>
       <c r="D62" s="1">
-        <v>2001</v>
+        <v>1005</v>
       </c>
       <c r="E62" s="1">
         <v>0</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>111</v>
+        <v>86</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="H62" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I62" s="1">
         <v>0</v>
       </c>
       <c r="J62" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="L62" s="1">
         <v>0</v>
       </c>
       <c r="M62" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N62" s="1">
         <v>1</v>
       </c>
       <c r="O62" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P62" s="1">
         <v>9999</v>
@@ -7513,19 +7551,19 @@
         <v>0</v>
       </c>
       <c r="U62" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V62" s="1" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="W62" s="1" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="X62" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Y62" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z62" s="1">
         <v>0</v>
@@ -7534,7 +7572,7 @@
         <v>0</v>
       </c>
       <c r="AB62" s="1">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="AC62" s="1">
         <v>0</v>
@@ -7554,6 +7592,7 @@
       <c r="AH62" s="1">
         <v>0</v>
       </c>
+      <c r="AI62" s="7"/>
       <c r="AJ62" s="1">
         <v>50</v>
       </c>
@@ -7563,22 +7602,22 @@
     </row>
     <row r="63" s="1" customFormat="1" spans="3:37">
       <c r="C63" s="1">
-        <v>12002</v>
+        <v>11006</v>
       </c>
       <c r="D63" s="1">
-        <v>2002</v>
+        <v>1006</v>
       </c>
       <c r="E63" s="1">
         <v>0</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="H63" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I63" s="1">
         <v>0</v>
@@ -7596,7 +7635,7 @@
         <v>1</v>
       </c>
       <c r="O63" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P63" s="1">
         <v>9999</v>
@@ -7611,19 +7650,19 @@
         <v>0</v>
       </c>
       <c r="U63" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V63" s="1" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="W63" s="1" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="X63" s="1">
         <v>0</v>
       </c>
       <c r="Y63" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z63" s="1">
         <v>0</v>
@@ -7632,7 +7671,7 @@
         <v>0</v>
       </c>
       <c r="AB63" s="1">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="AC63" s="1">
         <v>0</v>
@@ -7661,22 +7700,22 @@
     </row>
     <row r="64" s="1" customFormat="1" spans="3:37">
       <c r="C64" s="1">
-        <v>12003</v>
+        <v>11007</v>
       </c>
       <c r="D64" s="1">
-        <v>2003</v>
+        <v>1007</v>
       </c>
       <c r="E64" s="1">
         <v>0</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="H64" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I64" s="1">
         <v>0</v>
@@ -7688,13 +7727,13 @@
         <v>0</v>
       </c>
       <c r="M64" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N64" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O64" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P64" s="1">
         <v>9999</v>
@@ -7709,28 +7748,28 @@
         <v>0</v>
       </c>
       <c r="U64" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V64" s="1" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="W64" s="1" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="X64" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y64" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z64" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA64" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB64" s="1">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="AC64" s="1">
         <v>0</v>
@@ -7759,19 +7798,19 @@
     </row>
     <row r="65" s="1" customFormat="1" spans="3:37">
       <c r="C65" s="1">
-        <v>12004</v>
+        <v>12001</v>
       </c>
       <c r="D65" s="1">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="E65" s="1">
         <v>0</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>120</v>
+        <v>112</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="H65" s="1">
         <v>1</v>
@@ -7789,7 +7828,7 @@
         <v>0</v>
       </c>
       <c r="N65" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O65" s="1">
         <v>2</v>
@@ -7807,28 +7846,28 @@
         <v>0</v>
       </c>
       <c r="U65" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V65" s="1" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="W65" s="1" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="X65" s="1">
         <v>0</v>
       </c>
       <c r="Y65" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z65" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA65" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB65" s="1">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AC65" s="1">
         <v>0</v>
@@ -7857,34 +7896,34 @@
     </row>
     <row r="66" s="1" customFormat="1" spans="3:37">
       <c r="C66" s="1">
-        <v>12005</v>
+        <v>12002</v>
       </c>
       <c r="D66" s="1">
-        <v>2005</v>
+        <v>2002</v>
       </c>
       <c r="E66" s="1">
         <v>0</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="H66" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I66" s="1">
         <v>0</v>
       </c>
       <c r="J66" s="1">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="L66" s="1">
         <v>0</v>
       </c>
       <c r="M66" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N66" s="1">
         <v>1</v>
@@ -7905,19 +7944,19 @@
         <v>0</v>
       </c>
       <c r="U66" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V66" s="1" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="W66" s="1" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="X66" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Y66" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z66" s="1">
         <v>0</v>
@@ -7926,7 +7965,7 @@
         <v>0</v>
       </c>
       <c r="AB66" s="1">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="AC66" s="1">
         <v>0</v>
@@ -7946,7 +7985,6 @@
       <c r="AH66" s="1">
         <v>0</v>
       </c>
-      <c r="AI66" s="7"/>
       <c r="AJ66" s="1">
         <v>50</v>
       </c>
@@ -7956,22 +7994,22 @@
     </row>
     <row r="67" s="1" customFormat="1" spans="3:37">
       <c r="C67" s="1">
-        <v>12006</v>
+        <v>12003</v>
       </c>
       <c r="D67" s="1">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="E67" s="1">
         <v>0</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>125</v>
+        <v>118</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="H67" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I67" s="1">
         <v>0</v>
@@ -7983,10 +8021,10 @@
         <v>0</v>
       </c>
       <c r="M67" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N67" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O67" s="1">
         <v>2</v>
@@ -8004,28 +8042,28 @@
         <v>0</v>
       </c>
       <c r="U67" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V67" s="1" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="W67" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="X67" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y67" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z67" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA67" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB67" s="1">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="AC67" s="1">
         <v>0</v>
@@ -8054,19 +8092,19 @@
     </row>
     <row r="68" s="1" customFormat="1" spans="3:37">
       <c r="C68" s="1">
-        <v>12007</v>
+        <v>12004</v>
       </c>
       <c r="D68" s="1">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="E68" s="1">
         <v>0</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="H68" s="1">
         <v>1</v>
@@ -8102,10 +8140,10 @@
         <v>0</v>
       </c>
       <c r="U68" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V68" s="1" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="W68" s="1" t="s">
         <v>89</v>
@@ -8114,16 +8152,16 @@
         <v>0</v>
       </c>
       <c r="Y68" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z68" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA68" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB68" s="1">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="AC68" s="1">
         <v>0</v>
@@ -8152,40 +8190,40 @@
     </row>
     <row r="69" s="1" customFormat="1" spans="3:37">
       <c r="C69" s="1">
-        <v>13001</v>
+        <v>12005</v>
       </c>
       <c r="D69" s="1">
-        <v>3001</v>
+        <v>2005</v>
       </c>
       <c r="E69" s="1">
         <v>0</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="H69" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I69" s="1">
         <v>0</v>
       </c>
       <c r="J69" s="1">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="L69" s="1">
         <v>0</v>
       </c>
       <c r="M69" s="1">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="N69" s="1">
         <v>1</v>
       </c>
       <c r="O69" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P69" s="1">
         <v>9999</v>
@@ -8209,7 +8247,7 @@
         <v>89</v>
       </c>
       <c r="X69" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Y69" s="1">
         <v>0</v>
@@ -8221,7 +8259,7 @@
         <v>0</v>
       </c>
       <c r="AB69" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="AC69" s="1">
         <v>0</v>
@@ -8241,6 +8279,7 @@
       <c r="AH69" s="1">
         <v>0</v>
       </c>
+      <c r="AI69" s="7"/>
       <c r="AJ69" s="1">
         <v>50</v>
       </c>
@@ -8250,22 +8289,22 @@
     </row>
     <row r="70" s="1" customFormat="1" spans="3:37">
       <c r="C70" s="1">
-        <v>13002</v>
+        <v>12006</v>
       </c>
       <c r="D70" s="1">
-        <v>3002</v>
+        <v>2006</v>
       </c>
       <c r="E70" s="1">
         <v>0</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="H70" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I70" s="1">
         <v>0</v>
@@ -8283,7 +8322,7 @@
         <v>1</v>
       </c>
       <c r="O70" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P70" s="1">
         <v>9999</v>
@@ -8298,19 +8337,19 @@
         <v>0</v>
       </c>
       <c r="U70" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V70" s="1" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="W70" s="1" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="X70" s="1">
         <v>0</v>
       </c>
       <c r="Y70" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z70" s="1">
         <v>0</v>
@@ -8319,7 +8358,7 @@
         <v>0</v>
       </c>
       <c r="AB70" s="1">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="AC70" s="1">
         <v>0</v>
@@ -8348,19 +8387,19 @@
     </row>
     <row r="71" s="1" customFormat="1" spans="3:37">
       <c r="C71" s="1">
-        <v>13003</v>
+        <v>12007</v>
       </c>
       <c r="D71" s="1">
-        <v>3003</v>
+        <v>2007</v>
       </c>
       <c r="E71" s="1">
         <v>0</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="H71" s="1">
         <v>1</v>
@@ -8375,13 +8414,13 @@
         <v>0</v>
       </c>
       <c r="M71" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N71" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O71" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P71" s="1">
         <v>9999</v>
@@ -8396,13 +8435,13 @@
         <v>0</v>
       </c>
       <c r="U71" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V71" s="1" t="s">
         <v>83</v>
       </c>
       <c r="W71" s="1" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="X71" s="1">
         <v>0</v>
@@ -8411,19 +8450,19 @@
         <v>5</v>
       </c>
       <c r="Z71" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA71" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB71" s="1">
-        <v>35</v>
+        <v>150</v>
       </c>
       <c r="AC71" s="1">
         <v>0</v>
       </c>
       <c r="AD71" s="1">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AE71" s="1">
         <v>0</v>
@@ -8446,34 +8485,34 @@
     </row>
     <row r="72" s="1" customFormat="1" spans="3:37">
       <c r="C72" s="1">
-        <v>13004</v>
+        <v>13001</v>
       </c>
       <c r="D72" s="1">
-        <v>3004</v>
+        <v>3001</v>
       </c>
       <c r="E72" s="1">
         <v>0</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="H72" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I72" s="1">
         <v>0</v>
       </c>
       <c r="J72" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="L72" s="1">
         <v>0</v>
       </c>
       <c r="M72" s="1">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="N72" s="1">
         <v>1</v>
@@ -8500,13 +8539,13 @@
         <v>70</v>
       </c>
       <c r="W72" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="X72" s="1">
         <v>0</v>
       </c>
       <c r="Y72" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z72" s="1">
         <v>0</v>
@@ -8515,7 +8554,7 @@
         <v>0</v>
       </c>
       <c r="AB72" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AC72" s="1">
         <v>0</v>
@@ -8544,34 +8583,34 @@
     </row>
     <row r="73" s="1" customFormat="1" spans="3:37">
       <c r="C73" s="1">
-        <v>13005</v>
+        <v>13002</v>
       </c>
       <c r="D73" s="1">
-        <v>3005</v>
+        <v>3002</v>
       </c>
       <c r="E73" s="1">
         <v>0</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>155</v>
+        <v>149</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="H73" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I73" s="1">
         <v>0</v>
       </c>
       <c r="J73" s="1">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="L73" s="1">
         <v>0</v>
       </c>
       <c r="M73" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N73" s="1">
         <v>1</v>
@@ -8592,19 +8631,19 @@
         <v>0</v>
       </c>
       <c r="U73" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V73" s="1" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="W73" s="1" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="X73" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Y73" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z73" s="1">
         <v>0</v>
@@ -8613,7 +8652,7 @@
         <v>0</v>
       </c>
       <c r="AB73" s="1">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="AC73" s="1">
         <v>0</v>
@@ -8633,7 +8672,6 @@
       <c r="AH73" s="1">
         <v>0</v>
       </c>
-      <c r="AI73" s="7"/>
       <c r="AJ73" s="1">
         <v>50</v>
       </c>
@@ -8643,22 +8681,22 @@
     </row>
     <row r="74" s="1" customFormat="1" spans="3:37">
       <c r="C74" s="1">
-        <v>13006</v>
+        <v>13003</v>
       </c>
       <c r="D74" s="1">
-        <v>3006</v>
+        <v>3003</v>
       </c>
       <c r="E74" s="1">
         <v>0</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>153</v>
       </c>
       <c r="H74" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I74" s="1">
         <v>0</v>
@@ -8670,7 +8708,7 @@
         <v>0</v>
       </c>
       <c r="M74" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N74" s="1">
         <v>1</v>
@@ -8691,19 +8729,19 @@
         <v>0</v>
       </c>
       <c r="U74" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V74" s="1" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="W74" s="1" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="X74" s="1">
         <v>0</v>
       </c>
       <c r="Y74" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z74" s="1">
         <v>0</v>
@@ -8712,13 +8750,13 @@
         <v>0</v>
       </c>
       <c r="AB74" s="1">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="AC74" s="1">
         <v>0</v>
       </c>
       <c r="AD74" s="1">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AE74" s="1">
         <v>0</v>
@@ -8741,19 +8779,19 @@
     </row>
     <row r="75" s="1" customFormat="1" spans="3:37">
       <c r="C75" s="1">
-        <v>13007</v>
+        <v>13004</v>
       </c>
       <c r="D75" s="1">
-        <v>3007</v>
+        <v>3004</v>
       </c>
       <c r="E75" s="1">
         <v>0</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H75" s="1">
         <v>2</v>
@@ -8789,83 +8827,171 @@
         <v>0</v>
       </c>
       <c r="U75" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V75" s="1" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="W75" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="X75" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="1">
+        <v>100</v>
+      </c>
+      <c r="AC75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ75" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK75" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="76" s="1" customFormat="1" spans="3:37">
+      <c r="C76" s="1">
+        <v>13005</v>
+      </c>
+      <c r="D76" s="1">
+        <v>3005</v>
+      </c>
+      <c r="E76" s="1">
+        <v>0</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H76" s="1">
+        <v>5</v>
+      </c>
+      <c r="I76" s="1">
+        <v>0</v>
+      </c>
+      <c r="J76" s="1">
+        <v>50</v>
+      </c>
+      <c r="L76" s="1">
+        <v>0</v>
+      </c>
+      <c r="M76" s="1">
+        <v>30</v>
+      </c>
+      <c r="N76" s="1">
+        <v>1</v>
+      </c>
+      <c r="O76" s="1">
+        <v>3</v>
+      </c>
+      <c r="P76" s="1">
+        <v>9999</v>
+      </c>
+      <c r="Q76" s="1">
+        <v>0</v>
+      </c>
+      <c r="R76" s="1">
+        <v>1</v>
+      </c>
+      <c r="S76" s="1">
+        <v>0</v>
+      </c>
+      <c r="U76" s="1">
+        <v>0</v>
+      </c>
+      <c r="V76" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="W76" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="X75" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y75" s="1">
-        <v>2</v>
-      </c>
-      <c r="Z75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB75" s="1">
-        <v>120</v>
-      </c>
-      <c r="AC75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH75" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ75" s="1">
-        <v>50</v>
-      </c>
-      <c r="AK75" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="76" s="1" customFormat="1" spans="6:20">
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="K76" s="2"/>
-      <c r="L76" s="2"/>
-      <c r="P76" s="2"/>
-      <c r="Q76" s="2"/>
-      <c r="R76" s="2"/>
-      <c r="S76" s="2"/>
-      <c r="T76" s="2"/>
+      <c r="X76" s="1">
+        <v>30</v>
+      </c>
+      <c r="Y76" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB76" s="1">
+        <v>20</v>
+      </c>
+      <c r="AC76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI76" s="7"/>
+      <c r="AJ76" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK76" s="1">
+        <v>50</v>
+      </c>
     </row>
     <row r="77" s="1" customFormat="1" spans="3:37">
       <c r="C77" s="1">
-        <v>21002</v>
+        <v>13006</v>
       </c>
       <c r="D77" s="1">
-        <v>1002</v>
+        <v>3006</v>
       </c>
       <c r="E77" s="1">
         <v>0</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="G77" s="2" t="s">
-        <v>73</v>
+        <v>160</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="H77" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I77" s="1">
         <v>0</v>
@@ -8880,10 +9006,10 @@
         <v>0</v>
       </c>
       <c r="N77" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O77" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P77" s="1">
         <v>9999</v>
@@ -8898,60 +9024,267 @@
         <v>0</v>
       </c>
       <c r="U77" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V77" s="1" t="s">
         <v>70</v>
       </c>
       <c r="W77" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="X77" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="1">
+        <v>50</v>
+      </c>
+      <c r="AC77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ77" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK77" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="78" s="1" customFormat="1" spans="3:37">
+      <c r="C78" s="1">
+        <v>13007</v>
+      </c>
+      <c r="D78" s="1">
+        <v>3007</v>
+      </c>
+      <c r="E78" s="1">
+        <v>0</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="H78" s="1">
+        <v>2</v>
+      </c>
+      <c r="I78" s="1">
+        <v>0</v>
+      </c>
+      <c r="J78" s="1">
+        <v>100</v>
+      </c>
+      <c r="L78" s="1">
+        <v>0</v>
+      </c>
+      <c r="M78" s="1">
+        <v>15</v>
+      </c>
+      <c r="N78" s="1">
+        <v>1</v>
+      </c>
+      <c r="O78" s="1">
+        <v>3</v>
+      </c>
+      <c r="P78" s="1">
+        <v>9999</v>
+      </c>
+      <c r="Q78" s="1">
+        <v>0</v>
+      </c>
+      <c r="R78" s="1">
+        <v>1</v>
+      </c>
+      <c r="S78" s="1">
+        <v>0</v>
+      </c>
+      <c r="U78" s="1">
+        <v>2</v>
+      </c>
+      <c r="V78" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="W78" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="X78" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y78" s="1">
+        <v>2</v>
+      </c>
+      <c r="Z78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB78" s="1">
+        <v>120</v>
+      </c>
+      <c r="AC78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ78" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK78" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="79" s="1" customFormat="1" spans="6:20">
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="K79" s="2"/>
+      <c r="L79" s="2"/>
+      <c r="P79" s="2"/>
+      <c r="Q79" s="2"/>
+      <c r="R79" s="2"/>
+      <c r="S79" s="2"/>
+      <c r="T79" s="2"/>
+    </row>
+    <row r="80" s="1" customFormat="1" spans="3:37">
+      <c r="C80" s="1">
+        <v>21002</v>
+      </c>
+      <c r="D80" s="1">
+        <v>1002</v>
+      </c>
+      <c r="E80" s="1">
+        <v>0</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H80" s="1">
+        <v>1</v>
+      </c>
+      <c r="I80" s="1">
+        <v>0</v>
+      </c>
+      <c r="J80" s="1">
+        <v>10</v>
+      </c>
+      <c r="L80" s="1">
+        <v>0</v>
+      </c>
+      <c r="M80" s="1">
+        <v>0</v>
+      </c>
+      <c r="N80" s="1">
+        <v>2</v>
+      </c>
+      <c r="O80" s="1">
+        <v>1</v>
+      </c>
+      <c r="P80" s="1">
+        <v>9999</v>
+      </c>
+      <c r="Q80" s="1">
+        <v>0</v>
+      </c>
+      <c r="R80" s="1">
+        <v>1</v>
+      </c>
+      <c r="S80" s="1">
+        <v>0</v>
+      </c>
+      <c r="U80" s="1">
+        <v>2</v>
+      </c>
+      <c r="V80" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="W80" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="X77" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y77" s="1">
+      <c r="X80" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y80" s="1">
         <v>2</v>
       </c>
-      <c r="Z77" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA77" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB77" s="1">
+      <c r="Z80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB80" s="1">
         <v>150</v>
       </c>
-      <c r="AC77" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD77" s="1">
+      <c r="AC80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD80" s="1">
         <v>20</v>
       </c>
-      <c r="AE77" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF77" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG77" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH77" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI77" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="AJ77" s="1">
-        <v>50</v>
-      </c>
-      <c r="AK77" s="1">
+      <c r="AE80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI80" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="AJ80" s="1">
+        <v>50</v>
+      </c>
+      <c r="AK80" s="1">
         <v>50</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 C3:D5 F3:M5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:M5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -108,7 +108,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0">
+    <comment ref="K3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -130,7 +130,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N3" authorId="0">
+    <comment ref="O3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -154,7 +154,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O3" authorId="0">
+    <comment ref="P3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -176,7 +176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U3" authorId="0">
+    <comment ref="V3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -199,7 +199,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V3" authorId="0">
+    <comment ref="W3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -223,7 +223,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W3" authorId="0">
+    <comment ref="X3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -249,7 +249,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB3" authorId="0">
+    <comment ref="AC3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -271,7 +271,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AI3" authorId="0">
+    <comment ref="AJ3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -298,7 +298,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="203">
   <si>
     <t>_ID</t>
   </si>
@@ -321,6 +321,9 @@
     <t>互斥技能</t>
   </si>
   <si>
+    <t>来源技能</t>
+  </si>
+  <si>
     <t>优先度</t>
   </si>
   <si>
@@ -423,6 +426,9 @@
     <t>Repet</t>
   </si>
   <si>
+    <t>FromId</t>
+  </si>
+  <si>
     <t>Priority</t>
   </si>
   <si>
@@ -633,7 +639,7 @@
     <t>剑二十三</t>
   </si>
   <si>
-    <t>对3*3范围释放从天而降的流光剑气，造成流光剑法*10倍的伤害，并且附带20%的无视防御</t>
+    <t>对{0}个敌人，造成流光剑法*{1}%的伤害</t>
   </si>
   <si>
     <t>火球术</t>
@@ -735,7 +741,7 @@
     <t>魔法大炮</t>
   </si>
   <si>
-    <t>每释放一个技能，增加1%攻击倍率和2%生命倍率，最高叠加1000次</t>
+    <t>每次释放技能之后，增加{1}%攻击倍率和{5}%生命倍率，最高叠加{2}次</t>
   </si>
   <si>
     <t>疗伤术</t>
@@ -831,7 +837,7 @@
     <t>召唤白虎</t>
   </si>
   <si>
-    <t>召唤一个技能，继承人物所有属性，并且自身拥有100%无视防御，攻击，防御，血量为人物的1000%</t>
+    <t>召唤一个白虎，继承人物所有属性，并且自身拥有100%无视防御，攻击，防御，血量为人物的1000%</t>
   </si>
   <si>
     <t>定身指环</t>
@@ -1893,7 +1899,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:AM80"/>
+  <dimension ref="C3:AN80"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.35"/>
   <cols>
     <col min="1" max="1" width="5.6283185840708" style="2" customWidth="1"/>
@@ -1902,35 +1908,35 @@
     <col min="6" max="6" width="11.5044247787611" style="2" customWidth="1"/>
     <col min="7" max="7" width="9" style="2" customWidth="1"/>
     <col min="8" max="8" width="6.3716814159292" style="2" customWidth="1"/>
-    <col min="9" max="9" width="9.3716814159292" style="2" customWidth="1"/>
-    <col min="10" max="10" width="5.24778761061947" style="2" customWidth="1"/>
-    <col min="11" max="11" width="74.8761061946903" style="2" customWidth="1"/>
-    <col min="12" max="12" width="10.5044247787611" style="2" customWidth="1"/>
-    <col min="13" max="13" width="5.87610619469027" style="2" customWidth="1"/>
-    <col min="14" max="14" width="8.3716814159292" style="2" customWidth="1"/>
-    <col min="15" max="15" width="5.87610619469027" style="2" customWidth="1"/>
-    <col min="16" max="16" width="7.50442477876106" style="2" customWidth="1"/>
-    <col min="17" max="18" width="12.8761061946903" style="2" customWidth="1"/>
-    <col min="19" max="20" width="13.5044247787611" style="2" customWidth="1"/>
-    <col min="21" max="21" width="7.3716814159292" style="2" customWidth="1"/>
-    <col min="22" max="22" width="7.50442477876106" style="2" customWidth="1"/>
-    <col min="23" max="23" width="8.24778761061947" style="2" customWidth="1"/>
-    <col min="24" max="24" width="6.50442477876106" style="2" customWidth="1"/>
-    <col min="25" max="27" width="7.6283185840708" style="2" customWidth="1"/>
-    <col min="28" max="29" width="7.87610619469027" style="2" customWidth="1"/>
-    <col min="30" max="30" width="9.6283185840708" style="2" customWidth="1"/>
-    <col min="31" max="32" width="7.87610619469027" style="2" customWidth="1"/>
-    <col min="33" max="33" width="12.6283185840708" style="2" customWidth="1"/>
-    <col min="34" max="34" width="9.6283185840708" style="2" customWidth="1"/>
-    <col min="35" max="35" width="27.6283185840708" style="2" customWidth="1"/>
-    <col min="36" max="36" width="17.8761061946903" style="2" customWidth="1"/>
-    <col min="37" max="37" width="19.7522123893805" style="2" customWidth="1"/>
-    <col min="38" max="38" width="9" style="2"/>
-    <col min="39" max="39" width="19.2477876106195" style="2" customWidth="1"/>
-    <col min="40" max="16384" width="9" style="2"/>
+    <col min="9" max="10" width="9.3716814159292" style="2" customWidth="1"/>
+    <col min="11" max="11" width="5.24778761061947" style="2" customWidth="1"/>
+    <col min="12" max="12" width="74.8761061946903" style="2" customWidth="1"/>
+    <col min="13" max="13" width="10.5044247787611" style="2" customWidth="1"/>
+    <col min="14" max="14" width="5.87610619469027" style="2" customWidth="1"/>
+    <col min="15" max="15" width="8.3716814159292" style="2" customWidth="1"/>
+    <col min="16" max="16" width="5.87610619469027" style="2" customWidth="1"/>
+    <col min="17" max="17" width="7.50442477876106" style="2" customWidth="1"/>
+    <col min="18" max="19" width="12.8761061946903" style="2" customWidth="1"/>
+    <col min="20" max="21" width="13.5044247787611" style="2" customWidth="1"/>
+    <col min="22" max="22" width="7.3716814159292" style="2" customWidth="1"/>
+    <col min="23" max="23" width="7.50442477876106" style="2" customWidth="1"/>
+    <col min="24" max="24" width="8.24778761061947" style="2" customWidth="1"/>
+    <col min="25" max="25" width="6.50442477876106" style="2" customWidth="1"/>
+    <col min="26" max="28" width="7.6283185840708" style="2" customWidth="1"/>
+    <col min="29" max="30" width="7.87610619469027" style="2" customWidth="1"/>
+    <col min="31" max="31" width="9.6283185840708" style="2" customWidth="1"/>
+    <col min="32" max="33" width="7.87610619469027" style="2" customWidth="1"/>
+    <col min="34" max="34" width="12.6283185840708" style="2" customWidth="1"/>
+    <col min="35" max="35" width="9.6283185840708" style="2" customWidth="1"/>
+    <col min="36" max="36" width="27.6283185840708" style="2" customWidth="1"/>
+    <col min="37" max="37" width="17.8761061946903" style="2" customWidth="1"/>
+    <col min="38" max="38" width="19.7522123893805" style="2" customWidth="1"/>
+    <col min="39" max="39" width="9" style="2"/>
+    <col min="40" max="40" width="19.2477876106195" style="2" customWidth="1"/>
+    <col min="41" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:39">
+    <row r="3" spans="3:40">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1983,7 +1989,7 @@
         <v>16</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U3" s="3" t="s">
         <v>17</v>
@@ -2036,228 +2042,237 @@
       <c r="AK3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="AL3" s="2" t="s">
+      <c r="AL3" s="3" t="s">
         <v>34</v>
       </c>
       <c r="AM3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="4" spans="3:37">
+    <row r="4" spans="3:38">
       <c r="C4" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="R4" s="3" t="s">
         <v>15</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Y4" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z4" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AA4" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AB4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AC4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AD4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AE4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AF4" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AG4" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AH4" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AI4" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AJ4" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AK4" s="3" t="s">
-        <v>33</v>
+        <v>66</v>
+      </c>
+      <c r="AL4" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="5" spans="3:37">
+    <row r="5" spans="3:38">
       <c r="C5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="Y5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AA5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AB5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AC5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AD5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AE5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AF5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AG5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AH5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AI5" s="3" t="s">
         <v>67</v>
       </c>
       <c r="AJ5" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="AK5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="AL5" s="3" t="s">
+        <v>67</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="3:37">
+    <row r="6" s="1" customFormat="1" spans="3:38">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
@@ -2268,10 +2283,10 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
@@ -2280,66 +2295,66 @@
         <v>0</v>
       </c>
       <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
         <v>10</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="L6" s="1">
-        <v>0</v>
+      <c r="L6" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="M6" s="1">
         <v>0</v>
       </c>
       <c r="N6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" s="1">
         <v>1</v>
       </c>
       <c r="P6" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="1">
         <v>600</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="R6" s="1">
         <v>60</v>
       </c>
-      <c r="R6" s="1">
-        <f t="shared" ref="R6:R17" si="0">P6*5</f>
+      <c r="S6" s="1">
+        <f t="shared" ref="S6:S17" si="0">Q6*5</f>
         <v>3000</v>
       </c>
-      <c r="S6" s="1">
-        <v>1</v>
-      </c>
       <c r="T6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" s="1">
-        <v>1</v>
-      </c>
-      <c r="V6" s="1" t="s">
-        <v>70</v>
+        <v>0</v>
+      </c>
+      <c r="V6" s="1">
+        <v>1</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="X6" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="Y6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA6" s="1">
         <v>0</v>
       </c>
       <c r="AB6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="1">
         <v>120</v>
       </c>
-      <c r="AC6" s="1">
-        <v>0</v>
-      </c>
       <c r="AD6" s="1">
         <v>0</v>
       </c>
@@ -2355,14 +2370,17 @@
       <c r="AH6" s="1">
         <v>0</v>
       </c>
-      <c r="AJ6" s="1">
-        <v>50</v>
+      <c r="AI6" s="1">
+        <v>0</v>
       </c>
       <c r="AK6" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL6" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" spans="3:37">
+    <row r="7" s="1" customFormat="1" spans="3:38">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
@@ -2373,10 +2391,10 @@
         <v>2</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H7" s="1">
         <v>1</v>
@@ -2385,71 +2403,71 @@
         <v>0</v>
       </c>
       <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
         <v>10</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="L7" s="1">
-        <v>0</v>
+      <c r="L7" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="M7" s="1">
         <v>0</v>
       </c>
       <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1">
         <v>2</v>
       </c>
-      <c r="O7" s="1">
-        <v>1</v>
-      </c>
       <c r="P7" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="1">
         <v>600</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="R7" s="1">
         <v>60</v>
       </c>
-      <c r="R7" s="1">
+      <c r="S7" s="1">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="S7" s="1">
+      <c r="T7" s="1">
         <v>2</v>
       </c>
-      <c r="T7" s="1">
-        <v>0</v>
-      </c>
       <c r="U7" s="1">
+        <v>0</v>
+      </c>
+      <c r="V7" s="1">
         <v>2</v>
       </c>
-      <c r="V7" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="W7" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="X7" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="Y7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="1">
         <v>2</v>
       </c>
-      <c r="Z7" s="1">
-        <v>0</v>
-      </c>
       <c r="AA7" s="1">
         <v>0</v>
       </c>
       <c r="AB7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="1">
         <v>150</v>
       </c>
-      <c r="AC7" s="1">
-        <v>0</v>
-      </c>
       <c r="AD7" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF7" s="1">
         <v>0</v>
@@ -2460,14 +2478,17 @@
       <c r="AH7" s="1">
         <v>0</v>
       </c>
-      <c r="AJ7" s="1">
-        <v>50</v>
+      <c r="AI7" s="1">
+        <v>0</v>
       </c>
       <c r="AK7" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL7" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" spans="3:37">
+    <row r="8" s="1" customFormat="1" spans="3:38">
       <c r="C8" s="1">
         <v>1003</v>
       </c>
@@ -2478,10 +2499,10 @@
         <v>3</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H8" s="1">
         <v>1</v>
@@ -2490,66 +2511,66 @@
         <v>0</v>
       </c>
       <c r="J8" s="1">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
         <v>10</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="L8" s="1">
-        <v>0</v>
+      <c r="L8" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="M8" s="1">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1">
         <v>5</v>
       </c>
-      <c r="N8" s="1">
+      <c r="O8" s="1">
         <v>2</v>
       </c>
-      <c r="O8" s="1">
-        <v>1</v>
-      </c>
       <c r="P8" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="1">
         <v>600</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="R8" s="1">
         <v>60</v>
       </c>
-      <c r="R8" s="1">
+      <c r="S8" s="1">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="S8" s="1">
-        <v>1</v>
-      </c>
       <c r="T8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" s="1">
-        <v>1</v>
-      </c>
-      <c r="V8" s="1" t="s">
-        <v>70</v>
+        <v>0</v>
+      </c>
+      <c r="V8" s="1">
+        <v>1</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="X8" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="Y8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="1">
         <v>5</v>
       </c>
-      <c r="Z8" s="1">
-        <v>0</v>
-      </c>
       <c r="AA8" s="1">
         <v>0</v>
       </c>
       <c r="AB8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="1">
         <v>100</v>
       </c>
-      <c r="AC8" s="1">
-        <v>0</v>
-      </c>
       <c r="AD8" s="1">
         <v>0</v>
       </c>
@@ -2565,17 +2586,20 @@
       <c r="AH8" s="1">
         <v>0</v>
       </c>
-      <c r="AI8" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ8" s="1">
-        <v>50</v>
+      <c r="AI8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="AK8" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL8" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" spans="3:37">
+    <row r="9" s="1" customFormat="1" spans="3:38">
       <c r="C9" s="1">
         <v>1004</v>
       </c>
@@ -2586,10 +2610,10 @@
         <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H9" s="1">
         <v>7</v>
@@ -2598,66 +2622,66 @@
         <v>0</v>
       </c>
       <c r="J9" s="1">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
         <v>10</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="L9" s="1">
-        <v>0</v>
+      <c r="L9" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="M9" s="1">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
         <v>10</v>
       </c>
-      <c r="N9" s="1">
-        <v>1</v>
-      </c>
       <c r="O9" s="1">
         <v>1</v>
       </c>
       <c r="P9" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="1">
         <v>600</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="R9" s="1">
         <v>60</v>
       </c>
-      <c r="R9" s="1">
+      <c r="S9" s="1">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="S9" s="1">
+      <c r="T9" s="1">
         <v>4</v>
       </c>
-      <c r="T9" s="1">
-        <v>0</v>
-      </c>
       <c r="U9" s="1">
+        <v>0</v>
+      </c>
+      <c r="V9" s="1">
         <v>5</v>
       </c>
-      <c r="V9" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="W9" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="X9" s="1">
+        <v>85</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y9" s="1">
         <v>2</v>
       </c>
-      <c r="Y9" s="1">
-        <v>1</v>
-      </c>
       <c r="Z9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA9" s="1">
         <v>0</v>
       </c>
       <c r="AB9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="1">
         <v>200</v>
       </c>
-      <c r="AC9" s="1">
-        <v>0</v>
-      </c>
       <c r="AD9" s="1">
         <v>0</v>
       </c>
@@ -2673,17 +2697,20 @@
       <c r="AH9" s="1">
         <v>0</v>
       </c>
-      <c r="AI9" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AJ9" s="1">
-        <v>50</v>
+      <c r="AI9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="AK9" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL9" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" spans="3:37">
+    <row r="10" s="1" customFormat="1" spans="3:38">
       <c r="C10" s="1">
         <v>1005</v>
       </c>
@@ -2694,10 +2721,10 @@
         <v>5</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H10" s="1">
         <v>5</v>
@@ -2706,54 +2733,54 @@
         <v>5</v>
       </c>
       <c r="J10" s="1">
-        <v>50</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="L10" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
+        <v>50</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="M10" s="1">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1">
         <v>55</v>
       </c>
-      <c r="N10" s="1">
-        <v>1</v>
-      </c>
       <c r="O10" s="1">
         <v>1</v>
       </c>
       <c r="P10" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="1">
         <v>200</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="R10" s="1">
         <v>20</v>
       </c>
-      <c r="R10" s="1">
+      <c r="S10" s="1">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="S10" s="1">
-        <v>1</v>
-      </c>
       <c r="T10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10" s="1">
         <v>0</v>
       </c>
-      <c r="V10" s="1" t="s">
-        <v>70</v>
+      <c r="V10" s="1">
+        <v>0</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="X10" s="1">
+        <v>72</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y10" s="1">
         <v>30</v>
       </c>
-      <c r="Y10" s="1">
-        <v>0</v>
-      </c>
       <c r="Z10" s="1">
         <v>0</v>
       </c>
@@ -2761,11 +2788,11 @@
         <v>0</v>
       </c>
       <c r="AB10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="1">
         <v>100</v>
       </c>
-      <c r="AC10" s="1">
-        <v>0</v>
-      </c>
       <c r="AD10" s="1">
         <v>0</v>
       </c>
@@ -2781,17 +2808,20 @@
       <c r="AH10" s="1">
         <v>0</v>
       </c>
-      <c r="AI10" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="AJ10" s="1">
-        <v>50</v>
+      <c r="AI10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="AK10" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL10" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" spans="3:37">
+    <row r="11" s="1" customFormat="1" spans="3:38">
       <c r="C11" s="1">
         <v>1006</v>
       </c>
@@ -2802,10 +2832,10 @@
         <v>6</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H11" s="1">
         <v>6</v>
@@ -2814,50 +2844,50 @@
         <v>0</v>
       </c>
       <c r="J11" s="1">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1">
         <v>10</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="L11" s="1">
-        <v>0</v>
+      <c r="L11" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="M11" s="1">
         <v>0</v>
       </c>
       <c r="N11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" s="1">
         <v>1</v>
       </c>
       <c r="P11" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="1">
         <v>200</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="R11" s="1">
         <v>20</v>
       </c>
-      <c r="R11" s="1">
+      <c r="S11" s="1">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="S11" s="1">
-        <v>1</v>
-      </c>
       <c r="T11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11" s="1">
         <v>0</v>
       </c>
-      <c r="V11" s="1" t="s">
-        <v>70</v>
+      <c r="V11" s="1">
+        <v>0</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="X11" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="X11" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="Y11" s="1">
         <v>0</v>
@@ -2869,10 +2899,10 @@
         <v>0</v>
       </c>
       <c r="AB11" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AC11" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AD11" s="1">
         <v>0</v>
@@ -2889,14 +2919,17 @@
       <c r="AH11" s="1">
         <v>0</v>
       </c>
-      <c r="AJ11" s="1">
-        <v>50</v>
+      <c r="AI11" s="1">
+        <v>0</v>
       </c>
       <c r="AK11" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL11" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" spans="3:37">
+    <row r="12" s="1" customFormat="1" spans="3:38">
       <c r="C12" s="1">
         <v>1007</v>
       </c>
@@ -2907,10 +2940,10 @@
         <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H12" s="1">
         <v>1</v>
@@ -2919,71 +2952,71 @@
         <v>0</v>
       </c>
       <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
         <v>10</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="L12" s="1">
-        <v>0</v>
-      </c>
-      <c r="M12" s="6">
+      <c r="L12" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="N12" s="6">
         <v>5</v>
       </c>
-      <c r="N12" s="1">
-        <v>1</v>
-      </c>
       <c r="O12" s="1">
         <v>1</v>
       </c>
       <c r="P12" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="1">
         <v>600</v>
       </c>
-      <c r="Q12" s="1">
+      <c r="R12" s="1">
         <v>60</v>
       </c>
-      <c r="R12" s="1">
+      <c r="S12" s="1">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="S12" s="6">
+      <c r="T12" s="6">
         <v>10</v>
       </c>
-      <c r="T12" s="1">
-        <v>0</v>
-      </c>
       <c r="U12" s="1">
-        <v>1</v>
-      </c>
-      <c r="V12" s="1" t="s">
-        <v>70</v>
+        <v>0</v>
+      </c>
+      <c r="V12" s="1">
+        <v>1</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="X12" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="X12" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="Y12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA12" s="1">
         <v>0</v>
       </c>
-      <c r="AB12" s="6">
+      <c r="AB12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="6">
         <v>500</v>
       </c>
-      <c r="AC12" s="1">
-        <v>0</v>
-      </c>
       <c r="AD12" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AE12" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF12" s="1">
         <v>0</v>
@@ -2994,17 +3027,20 @@
       <c r="AH12" s="1">
         <v>0</v>
       </c>
-      <c r="AI12" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ12" s="1">
-        <v>50</v>
+      <c r="AI12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="6" t="s">
+        <v>99</v>
       </c>
       <c r="AK12" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL12" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" spans="3:37">
+    <row r="13" s="1" customFormat="1" spans="3:38">
       <c r="C13" s="1">
         <v>1008</v>
       </c>
@@ -3015,10 +3051,10 @@
         <v>8</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H13" s="1">
         <v>1008</v>
@@ -3027,54 +3063,54 @@
         <v>0</v>
       </c>
       <c r="J13" s="1">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
         <v>200</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="L13" s="1">
-        <v>0</v>
+      <c r="L13" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1">
         <v>30</v>
       </c>
-      <c r="N13" s="1">
-        <v>1</v>
-      </c>
       <c r="O13" s="1">
         <v>1</v>
       </c>
       <c r="P13" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="1">
         <v>30</v>
       </c>
-      <c r="Q13" s="1">
+      <c r="R13" s="1">
         <v>3</v>
       </c>
-      <c r="R13" s="1">
+      <c r="S13" s="1">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-      <c r="S13" s="1">
-        <v>1</v>
-      </c>
       <c r="T13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13" s="1">
         <v>0</v>
       </c>
-      <c r="V13" s="1" t="s">
-        <v>70</v>
+      <c r="V13" s="1">
+        <v>0</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="X13" s="1">
+        <v>72</v>
+      </c>
+      <c r="X13" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y13" s="1">
         <v>20</v>
       </c>
-      <c r="Y13" s="1">
-        <v>0</v>
-      </c>
       <c r="Z13" s="1">
         <v>0</v>
       </c>
@@ -3082,11 +3118,11 @@
         <v>0</v>
       </c>
       <c r="AB13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="1">
         <v>30</v>
       </c>
-      <c r="AC13" s="1">
-        <v>0</v>
-      </c>
       <c r="AD13" s="1">
         <v>0</v>
       </c>
@@ -3102,17 +3138,20 @@
       <c r="AH13" s="1">
         <v>0</v>
       </c>
-      <c r="AI13" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="AJ13" s="1">
-        <v>50</v>
+      <c r="AI13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="AK13" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL13" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" spans="3:37">
+    <row r="14" s="1" customFormat="1" spans="3:38">
       <c r="C14" s="1">
         <v>1009</v>
       </c>
@@ -3123,10 +3162,10 @@
         <v>9</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H14" s="1">
         <v>1</v>
@@ -3135,71 +3174,71 @@
         <v>0</v>
       </c>
       <c r="J14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
         <v>10</v>
       </c>
-      <c r="K14" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="L14" s="1">
-        <v>0</v>
+      <c r="L14" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1">
         <v>15</v>
       </c>
-      <c r="N14" s="1">
+      <c r="O14" s="1">
         <v>2</v>
       </c>
-      <c r="O14" s="1">
-        <v>1</v>
-      </c>
       <c r="P14" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="1">
         <v>300</v>
       </c>
-      <c r="Q14" s="1">
+      <c r="R14" s="1">
         <v>30</v>
       </c>
-      <c r="R14" s="1">
+      <c r="S14" s="1">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
-      <c r="S14" s="1">
+      <c r="T14" s="1">
         <v>12</v>
       </c>
-      <c r="T14" s="1">
-        <v>0</v>
-      </c>
       <c r="U14" s="1">
+        <v>0</v>
+      </c>
+      <c r="V14" s="1">
         <v>5</v>
       </c>
-      <c r="V14" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="W14" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="X14" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="X14" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="Y14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="1">
         <v>4</v>
       </c>
-      <c r="Z14" s="1">
-        <v>0</v>
-      </c>
       <c r="AA14" s="1">
         <v>0</v>
       </c>
       <c r="AB14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="1">
         <v>600</v>
       </c>
-      <c r="AC14" s="1">
-        <v>0</v>
-      </c>
       <c r="AD14" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AE14" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF14" s="1">
         <v>0</v>
@@ -3210,17 +3249,20 @@
       <c r="AH14" s="1">
         <v>0</v>
       </c>
-      <c r="AI14" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="AJ14" s="1">
-        <v>50</v>
+      <c r="AI14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="AK14" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL14" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" spans="3:37">
+    <row r="15" s="1" customFormat="1" spans="3:38">
       <c r="C15" s="1">
         <v>1010</v>
       </c>
@@ -3231,10 +3273,10 @@
         <v>10</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H15" s="1">
         <v>1</v>
@@ -3243,49 +3285,49 @@
         <v>0</v>
       </c>
       <c r="J15" s="1">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
         <v>10</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="L15" s="1">
+      <c r="L15" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="M15" s="1">
         <v>20</v>
       </c>
-      <c r="M15" s="1">
-        <v>0</v>
-      </c>
       <c r="N15" s="1">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1">
         <v>2</v>
       </c>
-      <c r="O15" s="1">
-        <v>1</v>
-      </c>
       <c r="P15" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="1">
         <v>10</v>
       </c>
-      <c r="Q15" s="1">
-        <v>1</v>
-      </c>
       <c r="R15" s="1">
+        <v>1</v>
+      </c>
+      <c r="S15" s="1">
         <v>250</v>
       </c>
-      <c r="S15" s="1">
+      <c r="T15" s="1">
         <v>10</v>
       </c>
-      <c r="T15" s="1">
-        <v>0</v>
-      </c>
       <c r="U15" s="1">
+        <v>0</v>
+      </c>
+      <c r="V15" s="1">
         <v>2</v>
       </c>
-      <c r="V15" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="W15" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="X15" s="1">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="X15" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="Y15" s="1">
         <v>0</v>
@@ -3297,11 +3339,11 @@
         <v>0</v>
       </c>
       <c r="AB15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="1">
         <v>200</v>
       </c>
-      <c r="AC15" s="1">
-        <v>0</v>
-      </c>
       <c r="AD15" s="1">
         <v>0</v>
       </c>
@@ -3317,14 +3359,17 @@
       <c r="AH15" s="1">
         <v>0</v>
       </c>
-      <c r="AJ15" s="1">
-        <v>50</v>
+      <c r="AI15" s="1">
+        <v>0</v>
       </c>
       <c r="AK15" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL15" s="1">
         <v>4102</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" spans="3:37">
+    <row r="16" s="1" customFormat="1" spans="3:38">
       <c r="C16" s="1">
         <v>1011</v>
       </c>
@@ -3335,10 +3380,10 @@
         <v>11</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H16" s="1">
         <v>8</v>
@@ -3349,67 +3394,67 @@
       <c r="J16" s="1">
         <v>0</v>
       </c>
-      <c r="K16" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="L16" s="1">
-        <v>0</v>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="N16" s="1">
         <v>30</v>
       </c>
-      <c r="N16" s="1">
+      <c r="O16" s="1">
         <v>2</v>
       </c>
-      <c r="O16" s="1">
-        <v>1</v>
-      </c>
       <c r="P16" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="1">
         <v>10</v>
       </c>
-      <c r="Q16" s="1">
-        <v>1</v>
-      </c>
       <c r="R16" s="1">
+        <v>1</v>
+      </c>
+      <c r="S16" s="1">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="S16" s="1">
-        <v>50</v>
-      </c>
       <c r="T16" s="1">
+        <v>50</v>
+      </c>
+      <c r="U16" s="1">
         <v>10</v>
       </c>
-      <c r="U16" s="1">
+      <c r="V16" s="1">
         <v>3</v>
       </c>
-      <c r="V16" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="W16" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="X16" s="1">
+        <v>85</v>
+      </c>
+      <c r="X16" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y16" s="1">
         <v>15</v>
       </c>
-      <c r="Y16" s="1">
+      <c r="Z16" s="1">
         <v>5</v>
-      </c>
-      <c r="Z16" s="1">
-        <v>4</v>
       </c>
       <c r="AA16" s="1">
         <v>4</v>
       </c>
       <c r="AB16" s="1">
+        <v>4</v>
+      </c>
+      <c r="AC16" s="1">
         <v>500</v>
       </c>
-      <c r="AC16" s="1">
+      <c r="AD16" s="1">
         <v>100</v>
       </c>
-      <c r="AD16" s="1">
-        <v>0</v>
-      </c>
       <c r="AE16" s="1">
         <v>0</v>
       </c>
@@ -3422,14 +3467,17 @@
       <c r="AH16" s="1">
         <v>0</v>
       </c>
-      <c r="AJ16" s="1">
-        <v>50</v>
+      <c r="AI16" s="1">
+        <v>0</v>
       </c>
       <c r="AK16" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL16" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" spans="3:37">
+    <row r="17" s="1" customFormat="1" spans="3:38">
       <c r="C17" s="1">
         <v>1012</v>
       </c>
@@ -3440,10 +3488,10 @@
         <v>12</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="H17" s="1">
         <v>1</v>
@@ -3452,53 +3500,53 @@
         <v>0</v>
       </c>
       <c r="J17" s="1">
+        <v>1002</v>
+      </c>
+      <c r="K17" s="1">
         <v>10</v>
       </c>
-      <c r="K17" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="L17" s="1">
-        <v>0</v>
+      <c r="L17" s="2" t="s">
+        <v>113</v>
       </c>
       <c r="M17" s="1">
         <v>0</v>
       </c>
       <c r="N17" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O17" s="1">
         <v>1</v>
       </c>
       <c r="P17" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="1">
         <v>10</v>
       </c>
-      <c r="Q17" s="1">
-        <v>1</v>
-      </c>
       <c r="R17" s="1">
+        <v>1</v>
+      </c>
+      <c r="S17" s="1">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="S17" s="1">
-        <v>50</v>
-      </c>
       <c r="T17" s="1">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="U17" s="1">
+        <v>0</v>
+      </c>
+      <c r="V17" s="1">
         <v>3</v>
       </c>
-      <c r="V17" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="W17" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="X17" s="1">
-        <v>15</v>
+        <v>85</v>
+      </c>
+      <c r="X17" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="Y17" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="1">
         <v>3</v>
@@ -3507,11 +3555,11 @@
         <v>3</v>
       </c>
       <c r="AB17" s="1">
+        <v>3</v>
+      </c>
+      <c r="AC17" s="1">
         <v>500</v>
       </c>
-      <c r="AC17" s="1">
-        <v>100</v>
-      </c>
       <c r="AD17" s="1">
         <v>0</v>
       </c>
@@ -3527,17 +3575,20 @@
       <c r="AH17" s="1">
         <v>0</v>
       </c>
-      <c r="AJ17" s="1">
-        <v>50</v>
+      <c r="AI17" s="1">
+        <v>0</v>
       </c>
       <c r="AK17" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL17" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="7:7">
       <c r="G18" s="2"/>
     </row>
-    <row r="19" s="1" customFormat="1" spans="3:37">
+    <row r="19" s="1" customFormat="1" spans="3:38">
       <c r="C19" s="1">
         <v>2001</v>
       </c>
@@ -3548,10 +3599,10 @@
         <v>1</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H19" s="1">
         <v>1</v>
@@ -3560,66 +3611,66 @@
         <v>0</v>
       </c>
       <c r="J19" s="1">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
         <v>10</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="L19" s="1">
-        <v>0</v>
+      <c r="L19" s="1" t="s">
+        <v>116</v>
       </c>
       <c r="M19" s="1">
         <v>0</v>
       </c>
       <c r="N19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" s="1">
+        <v>1</v>
+      </c>
+      <c r="P19" s="1">
         <v>2</v>
       </c>
-      <c r="P19" s="1">
+      <c r="Q19" s="1">
         <v>600</v>
       </c>
-      <c r="Q19" s="1">
+      <c r="R19" s="1">
         <v>60</v>
       </c>
-      <c r="R19" s="1">
-        <f t="shared" ref="R19:R30" si="1">P19*5</f>
+      <c r="S19" s="1">
+        <f t="shared" ref="S19:S30" si="1">Q19*5</f>
         <v>3000</v>
       </c>
-      <c r="S19" s="1">
+      <c r="T19" s="1">
         <v>2</v>
       </c>
-      <c r="T19" s="1">
-        <v>0</v>
-      </c>
       <c r="U19" s="1">
+        <v>0</v>
+      </c>
+      <c r="V19" s="1">
         <v>2</v>
       </c>
-      <c r="V19" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="W19" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="X19" s="1">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="X19" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="Y19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA19" s="1">
         <v>0</v>
       </c>
       <c r="AB19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="1">
         <v>120</v>
       </c>
-      <c r="AC19" s="1">
-        <v>0</v>
-      </c>
       <c r="AD19" s="1">
         <v>0</v>
       </c>
@@ -3635,14 +3686,17 @@
       <c r="AH19" s="1">
         <v>0</v>
       </c>
-      <c r="AJ19" s="1">
-        <v>50</v>
+      <c r="AI19" s="1">
+        <v>0</v>
       </c>
       <c r="AK19" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL19" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" spans="3:37">
+    <row r="20" s="1" customFormat="1" spans="3:38">
       <c r="C20" s="1">
         <v>2002</v>
       </c>
@@ -3653,10 +3707,10 @@
         <v>2</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H20" s="1">
         <v>1</v>
@@ -3665,71 +3719,71 @@
         <v>0</v>
       </c>
       <c r="J20" s="1">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
         <v>10</v>
       </c>
-      <c r="K20" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="L20" s="1">
-        <v>0</v>
+      <c r="L20" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="M20" s="1">
         <v>0</v>
       </c>
       <c r="N20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" s="1">
+        <v>1</v>
+      </c>
+      <c r="P20" s="1">
         <v>2</v>
       </c>
-      <c r="P20" s="1">
+      <c r="Q20" s="1">
         <v>600</v>
       </c>
-      <c r="Q20" s="1">
+      <c r="R20" s="1">
         <v>60</v>
       </c>
-      <c r="R20" s="1">
-        <f>P20*2.5</f>
+      <c r="S20" s="1">
+        <f>Q20*2.5</f>
         <v>1500</v>
       </c>
-      <c r="S20" s="1">
+      <c r="T20" s="1">
         <v>3</v>
       </c>
-      <c r="T20" s="1">
-        <v>0</v>
-      </c>
       <c r="U20" s="1">
+        <v>0</v>
+      </c>
+      <c r="V20" s="1">
         <v>3</v>
       </c>
-      <c r="V20" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="W20" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="X20" s="1">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="X20" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="Y20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA20" s="1">
         <v>0</v>
       </c>
       <c r="AB20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="1">
         <v>150</v>
       </c>
-      <c r="AC20" s="1">
-        <v>0</v>
-      </c>
       <c r="AD20" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AE20" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF20" s="1">
         <v>0</v>
@@ -3740,14 +3794,17 @@
       <c r="AH20" s="1">
         <v>0</v>
       </c>
-      <c r="AJ20" s="1">
-        <v>50</v>
+      <c r="AI20" s="1">
+        <v>0</v>
       </c>
       <c r="AK20" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL20" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" spans="3:37">
+    <row r="21" s="1" customFormat="1" spans="3:38">
       <c r="C21" s="1">
         <v>2003</v>
       </c>
@@ -3758,10 +3815,10 @@
         <v>3</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H21" s="1">
         <v>3</v>
@@ -3770,66 +3827,66 @@
         <v>0</v>
       </c>
       <c r="J21" s="1">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1">
         <v>10</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="L21" s="1">
-        <v>0</v>
+      <c r="L21" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="M21" s="1">
+        <v>0</v>
+      </c>
+      <c r="N21" s="1">
         <v>10</v>
-      </c>
-      <c r="N21" s="1">
-        <v>2</v>
       </c>
       <c r="O21" s="1">
         <v>2</v>
       </c>
       <c r="P21" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q21" s="1">
         <v>600</v>
       </c>
-      <c r="Q21" s="1">
+      <c r="R21" s="1">
         <v>60</v>
       </c>
-      <c r="R21" s="1">
+      <c r="S21" s="1">
         <f t="shared" si="1"/>
         <v>3000</v>
       </c>
-      <c r="S21" s="1">
+      <c r="T21" s="1">
         <v>2</v>
       </c>
-      <c r="T21" s="1">
-        <v>0</v>
-      </c>
       <c r="U21" s="1">
+        <v>0</v>
+      </c>
+      <c r="V21" s="1">
         <v>3</v>
       </c>
-      <c r="V21" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="W21" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="X21" s="1">
+        <v>85</v>
+      </c>
+      <c r="X21" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y21" s="1">
         <v>10</v>
       </c>
-      <c r="Y21" s="1">
+      <c r="Z21" s="1">
         <v>5</v>
-      </c>
-      <c r="Z21" s="1">
-        <v>2</v>
       </c>
       <c r="AA21" s="1">
         <v>2</v>
       </c>
       <c r="AB21" s="1">
+        <v>2</v>
+      </c>
+      <c r="AC21" s="1">
         <v>80</v>
       </c>
-      <c r="AC21" s="1">
-        <v>0</v>
-      </c>
       <c r="AD21" s="1">
         <v>0</v>
       </c>
@@ -3845,14 +3902,17 @@
       <c r="AH21" s="1">
         <v>0</v>
       </c>
-      <c r="AJ21" s="1">
-        <v>50</v>
+      <c r="AI21" s="1">
+        <v>0</v>
       </c>
       <c r="AK21" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL21" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" spans="3:37">
+    <row r="22" s="1" customFormat="1" spans="3:38">
       <c r="C22" s="1">
         <v>2004</v>
       </c>
@@ -3863,10 +3923,10 @@
         <v>4</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H22" s="1">
         <v>1</v>
@@ -3875,66 +3935,66 @@
         <v>0</v>
       </c>
       <c r="J22" s="1">
+        <v>0</v>
+      </c>
+      <c r="K22" s="1">
         <v>10</v>
       </c>
-      <c r="K22" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="L22" s="1">
-        <v>0</v>
+      <c r="L22" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="M22" s="1">
         <v>0</v>
       </c>
       <c r="N22" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O22" s="1">
         <v>2</v>
       </c>
       <c r="P22" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q22" s="1">
         <v>600</v>
       </c>
-      <c r="Q22" s="1">
+      <c r="R22" s="1">
         <v>60</v>
       </c>
-      <c r="R22" s="1">
+      <c r="S22" s="1">
         <f t="shared" si="1"/>
         <v>3000</v>
       </c>
-      <c r="S22" s="1">
+      <c r="T22" s="1">
         <v>2</v>
       </c>
-      <c r="T22" s="1">
-        <v>0</v>
-      </c>
       <c r="U22" s="1">
+        <v>0</v>
+      </c>
+      <c r="V22" s="1">
         <v>4</v>
       </c>
-      <c r="V22" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="W22" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="X22" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="X22" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="Y22" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="1">
         <v>4</v>
-      </c>
-      <c r="Z22" s="1">
-        <v>2</v>
       </c>
       <c r="AA22" s="1">
         <v>2</v>
       </c>
       <c r="AB22" s="1">
+        <v>2</v>
+      </c>
+      <c r="AC22" s="1">
         <v>100</v>
       </c>
-      <c r="AC22" s="1">
-        <v>0</v>
-      </c>
       <c r="AD22" s="1">
         <v>0</v>
       </c>
@@ -3950,17 +4010,20 @@
       <c r="AH22" s="1">
         <v>0</v>
       </c>
-      <c r="AI22" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="AJ22" s="1">
-        <v>50</v>
+      <c r="AI22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="AK22" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL22" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" spans="3:37">
+    <row r="23" s="1" customFormat="1" spans="3:38">
       <c r="C23" s="1">
         <v>2005</v>
       </c>
@@ -3971,10 +4034,10 @@
         <v>5</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H23" s="1">
         <v>5</v>
@@ -3983,54 +4046,54 @@
         <v>5</v>
       </c>
       <c r="J23" s="1">
-        <v>50</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="L23" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K23" s="1">
+        <v>50</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="M23" s="1">
+        <v>0</v>
+      </c>
+      <c r="N23" s="1">
         <v>55</v>
       </c>
-      <c r="N23" s="1">
-        <v>1</v>
-      </c>
       <c r="O23" s="1">
+        <v>1</v>
+      </c>
+      <c r="P23" s="1">
         <v>2</v>
       </c>
-      <c r="P23" s="1">
+      <c r="Q23" s="1">
         <v>200</v>
       </c>
-      <c r="Q23" s="1">
+      <c r="R23" s="1">
         <v>20</v>
       </c>
-      <c r="R23" s="1">
+      <c r="S23" s="1">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="S23" s="1">
-        <v>1</v>
-      </c>
       <c r="T23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U23" s="1">
         <v>0</v>
       </c>
-      <c r="V23" s="1" t="s">
-        <v>70</v>
+      <c r="V23" s="1">
+        <v>0</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="X23" s="1">
+        <v>72</v>
+      </c>
+      <c r="X23" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y23" s="1">
         <v>30</v>
       </c>
-      <c r="Y23" s="1">
-        <v>0</v>
-      </c>
       <c r="Z23" s="1">
         <v>0</v>
       </c>
@@ -4038,11 +4101,11 @@
         <v>0</v>
       </c>
       <c r="AB23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="1">
         <v>100</v>
       </c>
-      <c r="AC23" s="1">
-        <v>0</v>
-      </c>
       <c r="AD23" s="1">
         <v>0</v>
       </c>
@@ -4058,17 +4121,20 @@
       <c r="AH23" s="1">
         <v>0</v>
       </c>
-      <c r="AI23" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="AJ23" s="1">
-        <v>50</v>
+      <c r="AI23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="AK23" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL23" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" spans="3:37">
+    <row r="24" s="1" customFormat="1" spans="3:38">
       <c r="C24" s="1">
         <v>2006</v>
       </c>
@@ -4079,10 +4145,10 @@
         <v>6</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H24" s="1">
         <v>6</v>
@@ -4091,50 +4157,50 @@
         <v>0</v>
       </c>
       <c r="J24" s="1">
+        <v>0</v>
+      </c>
+      <c r="K24" s="1">
         <v>10</v>
       </c>
-      <c r="K24" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="L24" s="1">
-        <v>0</v>
+      <c r="L24" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="M24" s="1">
         <v>0</v>
       </c>
       <c r="N24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" s="1">
+        <v>1</v>
+      </c>
+      <c r="P24" s="1">
         <v>2</v>
       </c>
-      <c r="P24" s="1">
+      <c r="Q24" s="1">
         <v>200</v>
       </c>
-      <c r="Q24" s="1">
+      <c r="R24" s="1">
         <v>20</v>
       </c>
-      <c r="R24" s="1">
+      <c r="S24" s="1">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="S24" s="1">
-        <v>1</v>
-      </c>
       <c r="T24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U24" s="1">
         <v>0</v>
       </c>
-      <c r="V24" s="1" t="s">
-        <v>70</v>
+      <c r="V24" s="1">
+        <v>0</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="X24" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="X24" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="Y24" s="1">
         <v>0</v>
@@ -4146,10 +4212,10 @@
         <v>0</v>
       </c>
       <c r="AB24" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AC24" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AD24" s="1">
         <v>0</v>
@@ -4166,14 +4232,17 @@
       <c r="AH24" s="1">
         <v>0</v>
       </c>
-      <c r="AJ24" s="1">
-        <v>50</v>
+      <c r="AI24" s="1">
+        <v>0</v>
       </c>
       <c r="AK24" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL24" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" spans="3:37">
+    <row r="25" s="1" customFormat="1" spans="3:38">
       <c r="C25" s="1">
         <v>2007</v>
       </c>
@@ -4184,10 +4253,10 @@
         <v>7</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H25" s="1">
         <v>1</v>
@@ -4196,66 +4265,66 @@
         <v>0</v>
       </c>
       <c r="J25" s="1">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1">
         <v>10</v>
       </c>
-      <c r="K25" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="L25" s="1">
-        <v>0</v>
-      </c>
-      <c r="M25" s="6">
+      <c r="L25" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M25" s="1">
+        <v>0</v>
+      </c>
+      <c r="N25" s="6">
         <v>5</v>
-      </c>
-      <c r="N25" s="1">
-        <v>2</v>
       </c>
       <c r="O25" s="1">
         <v>2</v>
       </c>
       <c r="P25" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q25" s="1">
         <v>600</v>
       </c>
-      <c r="Q25" s="1">
+      <c r="R25" s="1">
         <v>60</v>
       </c>
-      <c r="R25" s="1">
+      <c r="S25" s="1">
         <f t="shared" si="1"/>
         <v>3000</v>
       </c>
-      <c r="S25" s="6">
+      <c r="T25" s="6">
         <v>6</v>
       </c>
-      <c r="T25" s="1">
-        <v>0</v>
-      </c>
       <c r="U25" s="1">
+        <v>0</v>
+      </c>
+      <c r="V25" s="1">
         <v>5</v>
       </c>
-      <c r="V25" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="W25" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="X25" s="1">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="X25" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="Y25" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="1">
         <v>5</v>
-      </c>
-      <c r="Z25" s="1">
-        <v>3</v>
       </c>
       <c r="AA25" s="1">
         <v>3</v>
       </c>
-      <c r="AB25" s="6">
+      <c r="AB25" s="1">
+        <v>3</v>
+      </c>
+      <c r="AC25" s="6">
         <v>300</v>
       </c>
-      <c r="AC25" s="1">
-        <v>0</v>
-      </c>
       <c r="AD25" s="1">
         <v>0</v>
       </c>
@@ -4271,17 +4340,20 @@
       <c r="AH25" s="1">
         <v>0</v>
       </c>
-      <c r="AI25" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="AJ25" s="1">
-        <v>50</v>
+      <c r="AI25" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="6" t="s">
+        <v>133</v>
       </c>
       <c r="AK25" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL25" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" spans="3:37">
+    <row r="26" s="1" customFormat="1" spans="3:38">
       <c r="C26" s="1">
         <v>2008</v>
       </c>
@@ -4292,10 +4364,10 @@
         <v>8</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H26" s="1">
         <v>2008</v>
@@ -4304,50 +4376,50 @@
         <v>0</v>
       </c>
       <c r="J26" s="1">
+        <v>0</v>
+      </c>
+      <c r="K26" s="1">
         <v>200</v>
       </c>
-      <c r="K26" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="L26" s="1">
-        <v>0</v>
+      <c r="L26" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="M26" s="1">
+        <v>0</v>
+      </c>
+      <c r="N26" s="1">
         <v>30</v>
       </c>
-      <c r="N26" s="1">
-        <v>1</v>
-      </c>
       <c r="O26" s="1">
+        <v>1</v>
+      </c>
+      <c r="P26" s="1">
         <v>2</v>
       </c>
-      <c r="P26" s="1">
+      <c r="Q26" s="1">
         <v>30</v>
       </c>
-      <c r="Q26" s="1">
+      <c r="R26" s="1">
         <v>3</v>
       </c>
-      <c r="R26" s="1">
+      <c r="S26" s="1">
         <f t="shared" si="1"/>
         <v>150</v>
       </c>
-      <c r="S26" s="1">
-        <v>1</v>
-      </c>
       <c r="T26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U26" s="1">
         <v>0</v>
       </c>
-      <c r="V26" s="1" t="s">
-        <v>70</v>
+      <c r="V26" s="1">
+        <v>0</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="X26" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="X26" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="Y26" s="1">
         <v>0</v>
@@ -4359,10 +4431,10 @@
         <v>0</v>
       </c>
       <c r="AB26" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AC26" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AD26" s="1">
         <v>0</v>
@@ -4379,17 +4451,20 @@
       <c r="AH26" s="1">
         <v>0</v>
       </c>
-      <c r="AI26" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="AJ26" s="1">
-        <v>50</v>
+      <c r="AI26" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="1" t="s">
+        <v>137</v>
       </c>
       <c r="AK26" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL26" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" spans="3:37">
+    <row r="27" s="1" customFormat="1" spans="3:38">
       <c r="C27" s="1">
         <v>2009</v>
       </c>
@@ -4400,10 +4475,10 @@
         <v>9</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H27" s="1">
         <v>3</v>
@@ -4412,66 +4487,66 @@
         <v>0</v>
       </c>
       <c r="J27" s="1">
+        <v>0</v>
+      </c>
+      <c r="K27" s="1">
         <v>10</v>
       </c>
-      <c r="K27" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="L27" s="1">
-        <v>0</v>
+      <c r="L27" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="M27" s="1">
+        <v>0</v>
+      </c>
+      <c r="N27" s="1">
         <v>15</v>
-      </c>
-      <c r="N27" s="1">
-        <v>2</v>
       </c>
       <c r="O27" s="1">
         <v>2</v>
       </c>
       <c r="P27" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q27" s="1">
         <v>300</v>
       </c>
-      <c r="Q27" s="1">
+      <c r="R27" s="1">
         <v>30</v>
       </c>
-      <c r="R27" s="1">
+      <c r="S27" s="1">
         <f t="shared" si="1"/>
         <v>1500</v>
       </c>
-      <c r="S27" s="1">
+      <c r="T27" s="1">
         <v>7</v>
       </c>
-      <c r="T27" s="1">
-        <v>0</v>
-      </c>
       <c r="U27" s="1">
+        <v>0</v>
+      </c>
+      <c r="V27" s="1">
         <v>3</v>
       </c>
-      <c r="V27" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="W27" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="X27" s="1">
+        <v>85</v>
+      </c>
+      <c r="X27" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y27" s="1">
         <v>10</v>
       </c>
-      <c r="Y27" s="1">
+      <c r="Z27" s="1">
         <v>5</v>
-      </c>
-      <c r="Z27" s="1">
-        <v>4</v>
       </c>
       <c r="AA27" s="1">
         <v>4</v>
       </c>
       <c r="AB27" s="1">
+        <v>4</v>
+      </c>
+      <c r="AC27" s="1">
         <v>400</v>
       </c>
-      <c r="AC27" s="1">
-        <v>0</v>
-      </c>
       <c r="AD27" s="1">
         <v>0</v>
       </c>
@@ -4487,17 +4562,20 @@
       <c r="AH27" s="1">
         <v>0</v>
       </c>
-      <c r="AI27" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="AJ27" s="1">
-        <v>50</v>
+      <c r="AI27" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="AK27" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL27" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" spans="3:37">
+    <row r="28" s="1" customFormat="1" spans="3:38">
       <c r="C28" s="1">
         <v>2010</v>
       </c>
@@ -4508,10 +4586,10 @@
         <v>10</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H28" s="1">
         <v>2010</v>
@@ -4520,66 +4598,66 @@
         <v>0</v>
       </c>
       <c r="J28" s="1">
+        <v>0</v>
+      </c>
+      <c r="K28" s="1">
         <v>100</v>
       </c>
-      <c r="K28" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="L28" s="1">
-        <v>0</v>
+      <c r="L28" s="2" t="s">
+        <v>143</v>
       </c>
       <c r="M28" s="1">
+        <v>0</v>
+      </c>
+      <c r="N28" s="1">
         <v>30</v>
-      </c>
-      <c r="N28" s="1">
-        <v>2</v>
       </c>
       <c r="O28" s="1">
         <v>2</v>
       </c>
       <c r="P28" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q28" s="1">
         <v>10</v>
       </c>
-      <c r="Q28" s="1">
-        <v>1</v>
-      </c>
       <c r="R28" s="1">
+        <v>1</v>
+      </c>
+      <c r="S28" s="1">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="S28" s="1">
+      <c r="T28" s="1">
         <v>5</v>
       </c>
-      <c r="T28" s="1">
-        <v>0</v>
-      </c>
       <c r="U28" s="1">
+        <v>0</v>
+      </c>
+      <c r="V28" s="1">
         <v>3</v>
       </c>
-      <c r="V28" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="W28" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="X28" s="1">
+        <v>85</v>
+      </c>
+      <c r="X28" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y28" s="1">
         <v>15</v>
       </c>
-      <c r="Y28" s="1">
+      <c r="Z28" s="1">
         <v>5</v>
-      </c>
-      <c r="Z28" s="1">
-        <v>4</v>
       </c>
       <c r="AA28" s="1">
         <v>4</v>
       </c>
       <c r="AB28" s="1">
+        <v>4</v>
+      </c>
+      <c r="AC28" s="1">
         <v>150</v>
       </c>
-      <c r="AC28" s="1">
-        <v>0</v>
-      </c>
       <c r="AD28" s="1">
         <v>0</v>
       </c>
@@ -4595,14 +4673,17 @@
       <c r="AH28" s="1">
         <v>0</v>
       </c>
-      <c r="AJ28" s="1">
-        <v>50</v>
+      <c r="AI28" s="1">
+        <v>0</v>
       </c>
       <c r="AK28" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL28" s="1">
         <v>4102</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" spans="3:37">
+    <row r="29" s="1" customFormat="1" spans="3:38">
       <c r="C29" s="1">
         <v>2011</v>
       </c>
@@ -4613,10 +4694,10 @@
         <v>11</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H29" s="1">
         <v>8</v>
@@ -4627,67 +4708,67 @@
       <c r="J29" s="1">
         <v>0</v>
       </c>
-      <c r="K29" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="L29" s="1">
-        <v>0</v>
+      <c r="K29" s="1">
+        <v>0</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>145</v>
       </c>
       <c r="M29" s="1">
+        <v>0</v>
+      </c>
+      <c r="N29" s="1">
         <v>30</v>
-      </c>
-      <c r="N29" s="1">
-        <v>2</v>
       </c>
       <c r="O29" s="1">
         <v>2</v>
       </c>
       <c r="P29" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q29" s="1">
         <v>10</v>
       </c>
-      <c r="Q29" s="1">
-        <v>1</v>
-      </c>
       <c r="R29" s="1">
+        <v>1</v>
+      </c>
+      <c r="S29" s="1">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="S29" s="1">
-        <v>50</v>
-      </c>
       <c r="T29" s="1">
+        <v>50</v>
+      </c>
+      <c r="U29" s="1">
         <v>10</v>
       </c>
-      <c r="U29" s="1">
+      <c r="V29" s="1">
         <v>3</v>
       </c>
-      <c r="V29" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="W29" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="X29" s="1">
+        <v>85</v>
+      </c>
+      <c r="X29" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y29" s="1">
         <v>15</v>
       </c>
-      <c r="Y29" s="1">
+      <c r="Z29" s="1">
         <v>5</v>
-      </c>
-      <c r="Z29" s="1">
-        <v>4</v>
       </c>
       <c r="AA29" s="1">
         <v>4</v>
       </c>
       <c r="AB29" s="1">
+        <v>4</v>
+      </c>
+      <c r="AC29" s="1">
         <v>500</v>
       </c>
-      <c r="AC29" s="1">
+      <c r="AD29" s="1">
         <v>100</v>
       </c>
-      <c r="AD29" s="1">
-        <v>0</v>
-      </c>
       <c r="AE29" s="1">
         <v>0</v>
       </c>
@@ -4700,14 +4781,17 @@
       <c r="AH29" s="1">
         <v>0</v>
       </c>
-      <c r="AJ29" s="1">
-        <v>50</v>
+      <c r="AI29" s="1">
+        <v>0</v>
       </c>
       <c r="AK29" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL29" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" spans="3:37">
+    <row r="30" s="1" customFormat="1" spans="3:38">
       <c r="C30" s="1">
         <v>2012</v>
       </c>
@@ -4718,10 +4802,10 @@
         <v>12</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H30" s="1">
         <v>8</v>
@@ -4730,68 +4814,68 @@
         <v>0</v>
       </c>
       <c r="J30" s="1">
+        <v>0</v>
+      </c>
+      <c r="K30" s="1">
         <v>10</v>
       </c>
-      <c r="K30" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="L30" s="1">
-        <v>0</v>
+      <c r="L30" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="M30" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N30" s="1">
+        <v>0</v>
+      </c>
+      <c r="O30" s="1">
         <v>2</v>
       </c>
-      <c r="O30" s="1">
-        <v>1</v>
-      </c>
       <c r="P30" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>1</v>
+      </c>
+      <c r="R30" s="1">
+        <v>1</v>
+      </c>
+      <c r="S30" s="1">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="T30" s="1">
+        <v>5</v>
+      </c>
+      <c r="U30" s="1">
         <v>10</v>
       </c>
-      <c r="Q30" s="1">
-        <v>1</v>
-      </c>
-      <c r="R30" s="1">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="S30" s="1">
-        <v>50</v>
-      </c>
-      <c r="T30" s="1">
-        <v>10</v>
-      </c>
-      <c r="U30" s="1">
+      <c r="V30" s="1">
         <v>3</v>
       </c>
-      <c r="V30" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="W30" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="X30" s="1">
-        <v>15</v>
+        <v>85</v>
+      </c>
+      <c r="X30" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="Y30" s="1">
+        <v>300</v>
+      </c>
+      <c r="Z30" s="1">
         <v>5</v>
-      </c>
-      <c r="Z30" s="1">
-        <v>4</v>
       </c>
       <c r="AA30" s="1">
         <v>4</v>
       </c>
       <c r="AB30" s="1">
-        <v>500</v>
+        <v>4</v>
       </c>
       <c r="AC30" s="1">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="AD30" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE30" s="1">
         <v>0</v>
@@ -4805,17 +4889,20 @@
       <c r="AH30" s="1">
         <v>0</v>
       </c>
-      <c r="AJ30" s="1">
-        <v>50</v>
+      <c r="AI30" s="1">
+        <v>0</v>
       </c>
       <c r="AK30" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL30" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="7:7">
       <c r="G31" s="2"/>
     </row>
-    <row r="32" s="1" customFormat="1" spans="3:37">
+    <row r="32" s="1" customFormat="1" spans="3:38">
       <c r="C32" s="1">
         <v>3001</v>
       </c>
@@ -4826,10 +4913,10 @@
         <v>1</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H32" s="1">
         <v>4</v>
@@ -4838,49 +4925,49 @@
         <v>0</v>
       </c>
       <c r="J32" s="1">
+        <v>0</v>
+      </c>
+      <c r="K32" s="1">
         <v>20</v>
       </c>
-      <c r="K32" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="L32" s="1">
-        <v>0</v>
+      <c r="L32" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="M32" s="1">
+        <v>0</v>
+      </c>
+      <c r="N32" s="1">
         <v>4</v>
       </c>
-      <c r="N32" s="1">
-        <v>1</v>
-      </c>
       <c r="O32" s="1">
+        <v>1</v>
+      </c>
+      <c r="P32" s="1">
         <v>3</v>
       </c>
-      <c r="P32" s="1">
+      <c r="Q32" s="1">
         <v>600</v>
       </c>
-      <c r="Q32" s="1">
+      <c r="R32" s="1">
         <v>60</v>
       </c>
-      <c r="R32" s="1">
+      <c r="S32" s="1">
         <v>20</v>
       </c>
-      <c r="S32" s="1">
+      <c r="T32" s="1">
         <v>3</v>
       </c>
-      <c r="T32" s="1">
-        <v>0</v>
-      </c>
       <c r="U32" s="1">
+        <v>0</v>
+      </c>
+      <c r="V32" s="1">
         <v>5</v>
       </c>
-      <c r="V32" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="W32" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="X32" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="X32" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="Y32" s="1">
         <v>0</v>
@@ -4892,10 +4979,10 @@
         <v>0</v>
       </c>
       <c r="AB32" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AC32" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AD32" s="1">
         <v>0</v>
@@ -4912,14 +4999,17 @@
       <c r="AH32" s="1">
         <v>0</v>
       </c>
-      <c r="AJ32" s="1">
-        <v>50</v>
+      <c r="AI32" s="1">
+        <v>0</v>
       </c>
       <c r="AK32" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL32" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" spans="3:37">
+    <row r="33" s="1" customFormat="1" spans="3:38">
       <c r="C33" s="1">
         <v>3002</v>
       </c>
@@ -4930,10 +5020,10 @@
         <v>2</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H33" s="1">
         <v>1</v>
@@ -4942,66 +5032,66 @@
         <v>0</v>
       </c>
       <c r="J33" s="1">
+        <v>0</v>
+      </c>
+      <c r="K33" s="1">
         <v>10</v>
       </c>
-      <c r="K33" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="L33" s="1">
-        <v>0</v>
+      <c r="L33" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="M33" s="1">
         <v>0</v>
       </c>
       <c r="N33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" s="1">
+        <v>1</v>
+      </c>
+      <c r="P33" s="1">
         <v>3</v>
       </c>
-      <c r="P33" s="1">
+      <c r="Q33" s="1">
         <v>600</v>
       </c>
-      <c r="Q33" s="1">
+      <c r="R33" s="1">
         <v>60</v>
       </c>
-      <c r="R33" s="1">
-        <f>P33*1.8</f>
+      <c r="S33" s="1">
+        <f>Q33*1.8</f>
         <v>1080</v>
       </c>
-      <c r="S33" s="1">
+      <c r="T33" s="1">
         <v>2</v>
       </c>
-      <c r="T33" s="1">
-        <v>0</v>
-      </c>
       <c r="U33" s="1">
+        <v>0</v>
+      </c>
+      <c r="V33" s="1">
         <v>3</v>
       </c>
-      <c r="V33" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="W33" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="X33" s="1">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="X33" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="Y33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z33" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA33" s="1">
         <v>0</v>
       </c>
       <c r="AB33" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="1">
         <v>120</v>
       </c>
-      <c r="AC33" s="1">
-        <v>0</v>
-      </c>
       <c r="AD33" s="1">
         <v>0</v>
       </c>
@@ -5017,14 +5107,17 @@
       <c r="AH33" s="1">
         <v>0</v>
       </c>
-      <c r="AJ33" s="1">
-        <v>50</v>
+      <c r="AI33" s="1">
+        <v>0</v>
       </c>
       <c r="AK33" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL33" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" spans="3:37">
+    <row r="34" s="1" customFormat="1" spans="3:38">
       <c r="C34" s="1">
         <v>3003</v>
       </c>
@@ -5035,10 +5128,10 @@
         <v>3</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H34" s="1">
         <v>1</v>
@@ -5047,72 +5140,72 @@
         <v>0</v>
       </c>
       <c r="J34" s="1">
+        <v>0</v>
+      </c>
+      <c r="K34" s="1">
         <v>10</v>
       </c>
-      <c r="K34" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="L34" s="1">
-        <v>0</v>
+      <c r="L34" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="M34" s="1">
+        <v>0</v>
+      </c>
+      <c r="N34" s="1">
         <v>10</v>
       </c>
-      <c r="N34" s="1">
-        <v>1</v>
-      </c>
       <c r="O34" s="1">
+        <v>1</v>
+      </c>
+      <c r="P34" s="1">
         <v>3</v>
       </c>
-      <c r="P34" s="1">
+      <c r="Q34" s="1">
         <v>600</v>
       </c>
-      <c r="Q34" s="1">
+      <c r="R34" s="1">
         <v>60</v>
       </c>
-      <c r="R34" s="1">
-        <f t="shared" ref="R32:R43" si="2">P34*5</f>
+      <c r="S34" s="1">
+        <f t="shared" ref="S32:S43" si="2">Q34*5</f>
         <v>3000</v>
       </c>
-      <c r="S34" s="1">
+      <c r="T34" s="1">
         <v>2</v>
       </c>
-      <c r="T34" s="1">
-        <v>0</v>
-      </c>
       <c r="U34" s="1">
+        <v>0</v>
+      </c>
+      <c r="V34" s="1">
         <v>2</v>
       </c>
-      <c r="V34" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="W34" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="X34" s="1">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="X34" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="Y34" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="1">
         <v>5</v>
       </c>
-      <c r="Z34" s="1">
-        <v>0</v>
-      </c>
       <c r="AA34" s="1">
         <v>0</v>
       </c>
       <c r="AB34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="1">
         <v>35</v>
       </c>
-      <c r="AC34" s="1">
-        <v>0</v>
-      </c>
       <c r="AD34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="1">
         <v>60</v>
       </c>
-      <c r="AE34" s="1">
-        <v>0</v>
-      </c>
       <c r="AF34" s="1">
         <v>0</v>
       </c>
@@ -5122,17 +5215,20 @@
       <c r="AH34" s="1">
         <v>0</v>
       </c>
-      <c r="AI34" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="AJ34" s="1">
-        <v>50</v>
+      <c r="AI34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="1" t="s">
+        <v>157</v>
       </c>
       <c r="AK34" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL34" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" spans="3:37">
+    <row r="35" s="1" customFormat="1" spans="3:38">
       <c r="C35" s="1">
         <v>3004</v>
       </c>
@@ -5143,10 +5239,10 @@
         <v>4</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H35" s="1">
         <v>2</v>
@@ -5155,66 +5251,66 @@
         <v>6</v>
       </c>
       <c r="J35" s="1">
+        <v>0</v>
+      </c>
+      <c r="K35" s="1">
         <v>100</v>
       </c>
-      <c r="K35" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="L35" s="1">
-        <v>0</v>
+      <c r="L35" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="M35" s="1">
+        <v>0</v>
+      </c>
+      <c r="N35" s="1">
         <v>15</v>
       </c>
-      <c r="N35" s="1">
-        <v>1</v>
-      </c>
       <c r="O35" s="1">
+        <v>1</v>
+      </c>
+      <c r="P35" s="1">
         <v>3</v>
       </c>
-      <c r="P35" s="1">
+      <c r="Q35" s="1">
         <v>600</v>
       </c>
-      <c r="Q35" s="1">
+      <c r="R35" s="1">
         <v>60</v>
       </c>
-      <c r="R35" s="1">
+      <c r="S35" s="1">
         <f t="shared" si="2"/>
         <v>3000</v>
       </c>
-      <c r="S35" s="1">
+      <c r="T35" s="1">
         <v>2</v>
       </c>
-      <c r="T35" s="1">
-        <v>0</v>
-      </c>
       <c r="U35" s="1">
         <v>0</v>
       </c>
-      <c r="V35" s="1" t="s">
-        <v>70</v>
+      <c r="V35" s="1">
+        <v>0</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="X35" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="X35" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="Y35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z35" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA35" s="1">
         <v>0</v>
       </c>
       <c r="AB35" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="1">
         <v>100</v>
       </c>
-      <c r="AC35" s="1">
-        <v>0</v>
-      </c>
       <c r="AD35" s="1">
         <v>0</v>
       </c>
@@ -5230,14 +5326,17 @@
       <c r="AH35" s="1">
         <v>0</v>
       </c>
-      <c r="AJ35" s="1">
-        <v>50</v>
+      <c r="AI35" s="1">
+        <v>0</v>
       </c>
       <c r="AK35" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL35" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" spans="3:37">
+    <row r="36" s="1" customFormat="1" spans="3:38">
       <c r="C36" s="1">
         <v>3005</v>
       </c>
@@ -5248,10 +5347,10 @@
         <v>5</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H36" s="1">
         <v>5</v>
@@ -5260,54 +5359,54 @@
         <v>5</v>
       </c>
       <c r="J36" s="1">
-        <v>50</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="L36" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K36" s="1">
+        <v>50</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="M36" s="1">
+        <v>0</v>
+      </c>
+      <c r="N36" s="1">
         <v>55</v>
       </c>
-      <c r="N36" s="1">
-        <v>1</v>
-      </c>
       <c r="O36" s="1">
+        <v>1</v>
+      </c>
+      <c r="P36" s="1">
         <v>3</v>
       </c>
-      <c r="P36" s="1">
+      <c r="Q36" s="1">
         <v>200</v>
       </c>
-      <c r="Q36" s="1">
+      <c r="R36" s="1">
         <v>20</v>
       </c>
-      <c r="R36" s="1">
+      <c r="S36" s="1">
         <f t="shared" si="2"/>
         <v>1000</v>
       </c>
-      <c r="S36" s="1">
-        <v>1</v>
-      </c>
       <c r="T36" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U36" s="1">
         <v>0</v>
       </c>
-      <c r="V36" s="1" t="s">
-        <v>70</v>
+      <c r="V36" s="1">
+        <v>0</v>
       </c>
       <c r="W36" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="X36" s="1">
+        <v>72</v>
+      </c>
+      <c r="X36" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y36" s="1">
         <v>30</v>
       </c>
-      <c r="Y36" s="1">
-        <v>0</v>
-      </c>
       <c r="Z36" s="1">
         <v>0</v>
       </c>
@@ -5315,11 +5414,11 @@
         <v>0</v>
       </c>
       <c r="AB36" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="1">
         <v>100</v>
       </c>
-      <c r="AC36" s="1">
-        <v>0</v>
-      </c>
       <c r="AD36" s="1">
         <v>0</v>
       </c>
@@ -5335,17 +5434,20 @@
       <c r="AH36" s="1">
         <v>0</v>
       </c>
-      <c r="AI36" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="AJ36" s="1">
-        <v>50</v>
+      <c r="AI36" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="AK36" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL36" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" spans="3:37">
+    <row r="37" s="1" customFormat="1" spans="3:38">
       <c r="C37" s="1">
         <v>3006</v>
       </c>
@@ -5356,10 +5458,10 @@
         <v>6</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H37" s="1">
         <v>6</v>
@@ -5368,50 +5470,50 @@
         <v>0</v>
       </c>
       <c r="J37" s="1">
+        <v>0</v>
+      </c>
+      <c r="K37" s="1">
         <v>10</v>
       </c>
-      <c r="K37" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="L37" s="1">
-        <v>0</v>
+      <c r="L37" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="M37" s="1">
         <v>0</v>
       </c>
       <c r="N37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37" s="1">
+        <v>1</v>
+      </c>
+      <c r="P37" s="1">
         <v>3</v>
       </c>
-      <c r="P37" s="1">
+      <c r="Q37" s="1">
         <v>200</v>
       </c>
-      <c r="Q37" s="1">
+      <c r="R37" s="1">
         <v>20</v>
       </c>
-      <c r="R37" s="1">
+      <c r="S37" s="1">
         <f t="shared" si="2"/>
         <v>1000</v>
       </c>
-      <c r="S37" s="1">
-        <v>1</v>
-      </c>
       <c r="T37" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U37" s="1">
+        <v>0</v>
+      </c>
+      <c r="V37" s="1">
         <v>3</v>
       </c>
-      <c r="V37" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="W37" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="X37" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="X37" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="Y37" s="1">
         <v>0</v>
@@ -5423,10 +5525,10 @@
         <v>0</v>
       </c>
       <c r="AB37" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AC37" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AD37" s="1">
         <v>0</v>
@@ -5443,14 +5545,17 @@
       <c r="AH37" s="1">
         <v>0</v>
       </c>
-      <c r="AJ37" s="1">
-        <v>50</v>
+      <c r="AI37" s="1">
+        <v>0</v>
       </c>
       <c r="AK37" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL37" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" spans="3:37">
+    <row r="38" s="1" customFormat="1" spans="3:38">
       <c r="C38" s="1">
         <v>3007</v>
       </c>
@@ -5461,10 +5566,10 @@
         <v>7</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H38" s="1">
         <v>2</v>
@@ -5473,66 +5578,66 @@
         <v>6</v>
       </c>
       <c r="J38" s="1">
+        <v>0</v>
+      </c>
+      <c r="K38" s="1">
         <v>100</v>
       </c>
-      <c r="K38" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="L38" s="1">
-        <v>0</v>
+      <c r="L38" s="1" t="s">
+        <v>166</v>
       </c>
       <c r="M38" s="1">
+        <v>0</v>
+      </c>
+      <c r="N38" s="1">
         <v>30</v>
       </c>
-      <c r="N38" s="1">
-        <v>1</v>
-      </c>
       <c r="O38" s="1">
+        <v>1</v>
+      </c>
+      <c r="P38" s="1">
         <v>3</v>
       </c>
-      <c r="P38" s="1">
+      <c r="Q38" s="1">
         <v>600</v>
       </c>
-      <c r="Q38" s="1">
+      <c r="R38" s="1">
         <v>60</v>
       </c>
-      <c r="R38" s="1">
+      <c r="S38" s="1">
         <f t="shared" si="2"/>
         <v>3000</v>
       </c>
-      <c r="S38" s="1">
+      <c r="T38" s="1">
         <v>3</v>
       </c>
-      <c r="T38" s="1">
-        <v>0</v>
-      </c>
       <c r="U38" s="1">
+        <v>0</v>
+      </c>
+      <c r="V38" s="1">
         <v>2</v>
       </c>
-      <c r="V38" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="W38" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="X38" s="1">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="X38" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="Y38" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="1">
         <v>2</v>
       </c>
-      <c r="Z38" s="1">
-        <v>0</v>
-      </c>
       <c r="AA38" s="1">
         <v>0</v>
       </c>
       <c r="AB38" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="1">
         <v>120</v>
       </c>
-      <c r="AC38" s="1">
-        <v>0</v>
-      </c>
       <c r="AD38" s="1">
         <v>0</v>
       </c>
@@ -5548,14 +5653,17 @@
       <c r="AH38" s="1">
         <v>0</v>
       </c>
-      <c r="AJ38" s="1">
-        <v>50</v>
+      <c r="AI38" s="1">
+        <v>0</v>
       </c>
       <c r="AK38" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL38" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" spans="3:37">
+    <row r="39" s="1" customFormat="1" spans="3:38">
       <c r="C39" s="1">
         <v>3008</v>
       </c>
@@ -5566,10 +5674,10 @@
         <v>8</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H39" s="1">
         <v>3008</v>
@@ -5578,54 +5686,54 @@
         <v>0</v>
       </c>
       <c r="J39" s="1">
+        <v>0</v>
+      </c>
+      <c r="K39" s="1">
         <v>200</v>
       </c>
-      <c r="K39" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="L39" s="1">
-        <v>0</v>
+      <c r="L39" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="M39" s="1">
+        <v>0</v>
+      </c>
+      <c r="N39" s="1">
         <v>30</v>
       </c>
-      <c r="N39" s="1">
-        <v>1</v>
-      </c>
       <c r="O39" s="1">
+        <v>1</v>
+      </c>
+      <c r="P39" s="1">
         <v>3</v>
       </c>
-      <c r="P39" s="1">
+      <c r="Q39" s="1">
         <v>30</v>
       </c>
-      <c r="Q39" s="1">
+      <c r="R39" s="1">
         <v>3</v>
       </c>
-      <c r="R39" s="1">
+      <c r="S39" s="1">
         <f t="shared" si="2"/>
         <v>150</v>
       </c>
-      <c r="S39" s="1">
-        <v>1</v>
-      </c>
       <c r="T39" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U39" s="1">
         <v>0</v>
       </c>
-      <c r="V39" s="1" t="s">
-        <v>70</v>
+      <c r="V39" s="1">
+        <v>0</v>
       </c>
       <c r="W39" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="X39" s="1">
+        <v>72</v>
+      </c>
+      <c r="X39" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y39" s="1">
         <v>5</v>
       </c>
-      <c r="Y39" s="1">
-        <v>0</v>
-      </c>
       <c r="Z39" s="1">
         <v>0</v>
       </c>
@@ -5633,11 +5741,11 @@
         <v>0</v>
       </c>
       <c r="AB39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="1">
         <v>30</v>
       </c>
-      <c r="AC39" s="1">
-        <v>0</v>
-      </c>
       <c r="AD39" s="1">
         <v>0</v>
       </c>
@@ -5653,17 +5761,20 @@
       <c r="AH39" s="1">
         <v>0</v>
       </c>
-      <c r="AI39" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="AJ39" s="1">
-        <v>50</v>
+      <c r="AI39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ39" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="AK39" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL39" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="40" s="1" customFormat="1" spans="3:37">
+    <row r="40" s="1" customFormat="1" spans="3:38">
       <c r="C40" s="1">
         <v>3009</v>
       </c>
@@ -5674,10 +5785,10 @@
         <v>9</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H40" s="1">
         <v>2</v>
@@ -5686,65 +5797,65 @@
         <v>6</v>
       </c>
       <c r="J40" s="1">
+        <v>0</v>
+      </c>
+      <c r="K40" s="1">
         <v>100</v>
       </c>
-      <c r="K40" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="L40" s="1">
-        <v>0</v>
+      <c r="L40" s="1" t="s">
+        <v>173</v>
       </c>
       <c r="M40" s="1">
+        <v>0</v>
+      </c>
+      <c r="N40" s="1">
         <v>30</v>
       </c>
-      <c r="N40" s="1">
-        <v>1</v>
-      </c>
       <c r="O40" s="1">
+        <v>1</v>
+      </c>
+      <c r="P40" s="1">
         <v>3</v>
       </c>
-      <c r="P40" s="1">
+      <c r="Q40" s="1">
         <v>300</v>
       </c>
-      <c r="Q40" s="1">
+      <c r="R40" s="1">
         <v>30</v>
       </c>
-      <c r="R40" s="1">
+      <c r="S40" s="1">
         <v>200</v>
       </c>
-      <c r="S40" s="1">
+      <c r="T40" s="1">
         <v>4</v>
       </c>
-      <c r="T40" s="1">
-        <v>0</v>
-      </c>
       <c r="U40" s="1">
+        <v>0</v>
+      </c>
+      <c r="V40" s="1">
         <v>2</v>
       </c>
-      <c r="V40" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="W40" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="X40" s="1">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="X40" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="Y40" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z40" s="1">
         <v>3</v>
       </c>
-      <c r="Z40" s="1">
-        <v>0</v>
-      </c>
       <c r="AA40" s="1">
         <v>0</v>
       </c>
       <c r="AB40" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="1">
         <v>300</v>
       </c>
-      <c r="AC40" s="1">
-        <v>0</v>
-      </c>
       <c r="AD40" s="1">
         <v>0</v>
       </c>
@@ -5760,14 +5871,17 @@
       <c r="AH40" s="1">
         <v>0</v>
       </c>
-      <c r="AJ40" s="1">
-        <v>50</v>
+      <c r="AI40" s="1">
+        <v>0</v>
       </c>
       <c r="AK40" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL40" s="1">
         <v>4006</v>
       </c>
     </row>
-    <row r="41" s="1" customFormat="1" spans="3:37">
+    <row r="41" s="1" customFormat="1" spans="3:38">
       <c r="C41" s="1">
         <v>3010</v>
       </c>
@@ -5778,10 +5892,10 @@
         <v>10</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H41" s="1">
         <v>8</v>
@@ -5790,29 +5904,29 @@
         <v>0</v>
       </c>
       <c r="J41" s="1">
+        <v>0</v>
+      </c>
+      <c r="K41" s="1">
         <v>100</v>
       </c>
-      <c r="K41" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="L41" s="1">
-        <v>0</v>
+      <c r="L41" s="1" t="s">
+        <v>175</v>
       </c>
       <c r="M41" s="1">
         <v>0</v>
       </c>
       <c r="N41" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" s="1">
+        <v>1</v>
+      </c>
+      <c r="P41" s="1">
         <v>3</v>
       </c>
-      <c r="P41" s="1">
+      <c r="Q41" s="1">
         <v>10</v>
       </c>
-      <c r="Q41" s="1">
-        <v>1</v>
-      </c>
       <c r="R41" s="1">
         <v>1</v>
       </c>
@@ -5820,38 +5934,38 @@
         <v>1</v>
       </c>
       <c r="T41" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U41" s="1">
         <v>0</v>
       </c>
-      <c r="V41" s="1" t="s">
-        <v>83</v>
+      <c r="V41" s="1">
+        <v>0</v>
       </c>
       <c r="W41" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="X41" s="1">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="X41" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="Y41" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="1">
         <v>3</v>
       </c>
-      <c r="Z41" s="1">
-        <v>0</v>
-      </c>
       <c r="AA41" s="1">
         <v>0</v>
       </c>
       <c r="AB41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="1">
         <v>20</v>
       </c>
-      <c r="AC41" s="1">
+      <c r="AD41" s="1">
         <v>400</v>
       </c>
-      <c r="AD41" s="1">
-        <v>0</v>
-      </c>
       <c r="AE41" s="1">
         <v>0</v>
       </c>
@@ -5864,14 +5978,17 @@
       <c r="AH41" s="1">
         <v>0</v>
       </c>
-      <c r="AJ41" s="1">
-        <v>50</v>
+      <c r="AI41" s="1">
+        <v>0</v>
       </c>
       <c r="AK41" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL41" s="1">
         <v>4102</v>
       </c>
     </row>
-    <row r="42" s="1" customFormat="1" spans="3:37">
+    <row r="42" s="1" customFormat="1" spans="3:38">
       <c r="C42" s="1">
         <v>3011</v>
       </c>
@@ -5882,10 +5999,10 @@
         <v>11</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H42" s="1">
         <v>8</v>
@@ -5896,67 +6013,67 @@
       <c r="J42" s="1">
         <v>0</v>
       </c>
-      <c r="K42" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="L42" s="1">
-        <v>0</v>
+      <c r="K42" s="1">
+        <v>0</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>177</v>
       </c>
       <c r="M42" s="1">
+        <v>0</v>
+      </c>
+      <c r="N42" s="1">
         <v>30</v>
       </c>
-      <c r="N42" s="1">
+      <c r="O42" s="1">
         <v>2</v>
       </c>
-      <c r="O42" s="1">
+      <c r="P42" s="1">
         <v>3</v>
       </c>
-      <c r="P42" s="1">
+      <c r="Q42" s="1">
         <v>10</v>
       </c>
-      <c r="Q42" s="1">
-        <v>1</v>
-      </c>
       <c r="R42" s="1">
+        <v>1</v>
+      </c>
+      <c r="S42" s="1">
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
-      <c r="S42" s="1">
-        <v>50</v>
-      </c>
       <c r="T42" s="1">
+        <v>50</v>
+      </c>
+      <c r="U42" s="1">
         <v>10</v>
       </c>
-      <c r="U42" s="1">
+      <c r="V42" s="1">
         <v>3</v>
       </c>
-      <c r="V42" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="W42" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="X42" s="1">
+        <v>85</v>
+      </c>
+      <c r="X42" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y42" s="1">
         <v>15</v>
       </c>
-      <c r="Y42" s="1">
+      <c r="Z42" s="1">
         <v>5</v>
-      </c>
-      <c r="Z42" s="1">
-        <v>4</v>
       </c>
       <c r="AA42" s="1">
         <v>4</v>
       </c>
       <c r="AB42" s="1">
+        <v>4</v>
+      </c>
+      <c r="AC42" s="1">
         <v>500</v>
       </c>
-      <c r="AC42" s="1">
+      <c r="AD42" s="1">
         <v>100</v>
       </c>
-      <c r="AD42" s="1">
-        <v>0</v>
-      </c>
       <c r="AE42" s="1">
         <v>0</v>
       </c>
@@ -5969,14 +6086,17 @@
       <c r="AH42" s="1">
         <v>0</v>
       </c>
-      <c r="AJ42" s="1">
-        <v>50</v>
+      <c r="AI42" s="1">
+        <v>0</v>
       </c>
       <c r="AK42" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL42" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="43" s="1" customFormat="1" spans="3:37">
+    <row r="43" s="1" customFormat="1" spans="3:38">
       <c r="C43" s="1">
         <v>3012</v>
       </c>
@@ -5987,81 +6107,81 @@
         <v>12</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="H43" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I43" s="1">
         <v>0</v>
       </c>
       <c r="J43" s="1">
+        <v>0</v>
+      </c>
+      <c r="K43" s="1">
         <v>10</v>
       </c>
-      <c r="K43" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="L43" s="1">
-        <v>0</v>
+      <c r="L43" s="2" t="s">
+        <v>179</v>
       </c>
       <c r="M43" s="1">
+        <v>0</v>
+      </c>
+      <c r="N43" s="1">
         <v>30</v>
       </c>
-      <c r="N43" s="1">
+      <c r="O43" s="1">
         <v>2</v>
       </c>
-      <c r="O43" s="1">
-        <v>1</v>
-      </c>
       <c r="P43" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="1">
         <v>10</v>
       </c>
-      <c r="Q43" s="1">
-        <v>1</v>
-      </c>
       <c r="R43" s="1">
+        <v>1</v>
+      </c>
+      <c r="S43" s="1">
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
-      <c r="S43" s="1">
-        <v>50</v>
-      </c>
       <c r="T43" s="1">
+        <v>50</v>
+      </c>
+      <c r="U43" s="1">
         <v>10</v>
       </c>
-      <c r="U43" s="1">
+      <c r="V43" s="1">
         <v>3</v>
       </c>
-      <c r="V43" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="W43" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="X43" s="1">
+        <v>85</v>
+      </c>
+      <c r="X43" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y43" s="1">
         <v>15</v>
       </c>
-      <c r="Y43" s="1">
+      <c r="Z43" s="1">
         <v>5</v>
-      </c>
-      <c r="Z43" s="1">
-        <v>4</v>
       </c>
       <c r="AA43" s="1">
         <v>4</v>
       </c>
       <c r="AB43" s="1">
+        <v>4</v>
+      </c>
+      <c r="AC43" s="1">
         <v>500</v>
       </c>
-      <c r="AC43" s="1">
+      <c r="AD43" s="1">
         <v>100</v>
       </c>
-      <c r="AD43" s="1">
-        <v>0</v>
-      </c>
       <c r="AE43" s="1">
         <v>0</v>
       </c>
@@ -6074,10 +6194,13 @@
       <c r="AH43" s="1">
         <v>0</v>
       </c>
-      <c r="AJ43" s="1">
-        <v>50</v>
+      <c r="AI43" s="1">
+        <v>0</v>
       </c>
       <c r="AK43" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL43" s="1">
         <v>0</v>
       </c>
     </row>
@@ -6085,7 +6208,7 @@
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
     </row>
-    <row r="45" s="1" customFormat="1" spans="3:36">
+    <row r="45" s="1" customFormat="1" spans="3:37">
       <c r="C45" s="1">
         <v>4001</v>
       </c>
@@ -6096,10 +6219,10 @@
         <v>0</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H45" s="1">
         <v>4001</v>
@@ -6108,20 +6231,20 @@
         <v>0</v>
       </c>
       <c r="J45" s="1">
+        <v>0</v>
+      </c>
+      <c r="K45" s="1">
         <v>-100</v>
       </c>
-      <c r="K45" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="L45" s="1">
-        <v>0</v>
+      <c r="L45" s="1" t="s">
+        <v>182</v>
       </c>
       <c r="M45" s="1">
+        <v>0</v>
+      </c>
+      <c r="N45" s="1">
         <v>30</v>
       </c>
-      <c r="N45" s="1">
-        <v>0</v>
-      </c>
       <c r="O45" s="1">
         <v>0</v>
       </c>
@@ -6132,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="R45" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T45" s="1">
         <v>0</v>
@@ -6143,18 +6266,18 @@
       <c r="U45" s="1">
         <v>0</v>
       </c>
-      <c r="V45" s="1" t="s">
-        <v>70</v>
+      <c r="V45" s="1">
+        <v>0</v>
       </c>
       <c r="W45" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="X45" s="1">
+        <v>72</v>
+      </c>
+      <c r="X45" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y45" s="1">
         <v>2</v>
       </c>
-      <c r="Y45" s="1">
-        <v>0</v>
-      </c>
       <c r="Z45" s="1">
         <v>0</v>
       </c>
@@ -6182,14 +6305,17 @@
       <c r="AH45" s="1">
         <v>0</v>
       </c>
-      <c r="AI45" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="AJ45" s="1">
+      <c r="AI45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ45" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="AK45" s="1">
         <v>99999</v>
       </c>
     </row>
-    <row r="46" s="1" customFormat="1" spans="3:36">
+    <row r="46" s="1" customFormat="1" spans="3:37">
       <c r="C46" s="1">
         <v>4002</v>
       </c>
@@ -6200,10 +6326,10 @@
         <v>0</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H46" s="1">
         <v>4002</v>
@@ -6212,20 +6338,20 @@
         <v>0</v>
       </c>
       <c r="J46" s="1">
+        <v>0</v>
+      </c>
+      <c r="K46" s="1">
         <v>200</v>
       </c>
-      <c r="K46" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="L46" s="1">
-        <v>0</v>
+      <c r="L46" s="1" t="s">
+        <v>186</v>
       </c>
       <c r="M46" s="1">
+        <v>0</v>
+      </c>
+      <c r="N46" s="1">
         <v>60</v>
       </c>
-      <c r="N46" s="1">
-        <v>0</v>
-      </c>
       <c r="O46" s="1">
         <v>0</v>
       </c>
@@ -6236,25 +6362,25 @@
         <v>0</v>
       </c>
       <c r="R46" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S46" s="1">
+        <v>1</v>
+      </c>
+      <c r="T46" s="1">
         <v>10</v>
       </c>
-      <c r="T46" s="1">
-        <v>0</v>
-      </c>
       <c r="U46" s="1">
         <v>0</v>
       </c>
-      <c r="V46" s="1" t="s">
-        <v>70</v>
+      <c r="V46" s="1">
+        <v>0</v>
       </c>
       <c r="W46" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="X46" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="X46" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="Y46" s="1">
         <v>0</v>
@@ -6266,11 +6392,11 @@
         <v>0</v>
       </c>
       <c r="AB46" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="1">
         <v>100</v>
       </c>
-      <c r="AC46" s="1">
-        <v>0</v>
-      </c>
       <c r="AD46" s="1">
         <v>0</v>
       </c>
@@ -6286,12 +6412,15 @@
       <c r="AH46" s="1">
         <v>0</v>
       </c>
-      <c r="AI46" s="7"/>
-      <c r="AJ46" s="1">
+      <c r="AI46" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ46" s="7"/>
+      <c r="AK46" s="1">
         <v>99999</v>
       </c>
     </row>
-    <row r="47" s="1" customFormat="1" spans="3:36">
+    <row r="47" s="1" customFormat="1" spans="3:37">
       <c r="C47" s="1">
         <v>4003</v>
       </c>
@@ -6302,10 +6431,10 @@
         <v>0</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H47" s="1">
         <v>4003</v>
@@ -6314,20 +6443,20 @@
         <v>0</v>
       </c>
       <c r="J47" s="1">
+        <v>0</v>
+      </c>
+      <c r="K47" s="1">
         <v>-1</v>
       </c>
-      <c r="K47" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="L47" s="1">
-        <v>0</v>
+      <c r="L47" s="1" t="s">
+        <v>189</v>
       </c>
       <c r="M47" s="1">
+        <v>0</v>
+      </c>
+      <c r="N47" s="1">
         <v>60</v>
       </c>
-      <c r="N47" s="1">
-        <v>0</v>
-      </c>
       <c r="O47" s="1">
         <v>0</v>
       </c>
@@ -6338,10 +6467,10 @@
         <v>0</v>
       </c>
       <c r="R47" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T47" s="1">
         <v>0</v>
@@ -6349,14 +6478,14 @@
       <c r="U47" s="1">
         <v>0</v>
       </c>
-      <c r="V47" s="1" t="s">
-        <v>70</v>
+      <c r="V47" s="1">
+        <v>0</v>
       </c>
       <c r="W47" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="X47" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="X47" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="Y47" s="1">
         <v>0</v>
@@ -6368,11 +6497,11 @@
         <v>0</v>
       </c>
       <c r="AB47" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="1">
         <v>100</v>
       </c>
-      <c r="AC47" s="1">
-        <v>0</v>
-      </c>
       <c r="AD47" s="1">
         <v>0</v>
       </c>
@@ -6388,10 +6517,13 @@
       <c r="AH47" s="1">
         <v>0</v>
       </c>
-      <c r="AI47" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="AJ47" s="1">
+      <c r="AI47" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ47" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="AK47" s="1">
         <v>99999</v>
       </c>
     </row>
@@ -6399,7 +6531,7 @@
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
     </row>
-    <row r="49" s="1" customFormat="1" spans="3:37">
+    <row r="49" s="1" customFormat="1" spans="3:38">
       <c r="C49" s="1">
         <v>9001</v>
       </c>
@@ -6410,10 +6542,10 @@
         <v>0</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H49" s="1">
         <v>9</v>
@@ -6424,57 +6556,57 @@
       <c r="J49" s="1">
         <v>0</v>
       </c>
-      <c r="L49" s="1">
+      <c r="K49" s="1">
         <v>0</v>
       </c>
       <c r="M49" s="1">
         <v>0</v>
       </c>
       <c r="N49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O49" s="1">
         <v>1</v>
       </c>
       <c r="P49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q49" s="1">
         <v>0</v>
       </c>
       <c r="R49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S49" s="1">
-        <v>0</v>
-      </c>
-      <c r="U49" s="1">
-        <v>1</v>
-      </c>
-      <c r="V49" s="1" t="s">
-        <v>70</v>
+        <v>1</v>
+      </c>
+      <c r="T49" s="1">
+        <v>0</v>
+      </c>
+      <c r="V49" s="1">
+        <v>1</v>
       </c>
       <c r="W49" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="X49" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="X49" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="Y49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA49" s="1">
         <v>0</v>
       </c>
       <c r="AB49" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="1">
         <v>100</v>
       </c>
-      <c r="AC49" s="1">
-        <v>0</v>
-      </c>
       <c r="AD49" s="1">
         <v>0</v>
       </c>
@@ -6490,14 +6622,17 @@
       <c r="AH49" s="1">
         <v>0</v>
       </c>
-      <c r="AJ49" s="1">
-        <v>50</v>
+      <c r="AI49" s="1">
+        <v>0</v>
       </c>
       <c r="AK49" s="1">
         <v>50</v>
       </c>
+      <c r="AL49" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="50" s="1" customFormat="1" spans="3:37">
+    <row r="50" s="1" customFormat="1" spans="3:38">
       <c r="C50" s="1">
         <v>9002</v>
       </c>
@@ -6508,10 +6643,10 @@
         <v>0</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H50" s="1">
         <v>9</v>
@@ -6522,57 +6657,57 @@
       <c r="J50" s="1">
         <v>0</v>
       </c>
-      <c r="L50" s="1">
+      <c r="K50" s="1">
         <v>0</v>
       </c>
       <c r="M50" s="1">
         <v>0</v>
       </c>
       <c r="N50" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O50" s="1">
         <v>1</v>
       </c>
       <c r="P50" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q50" s="1">
         <v>0</v>
       </c>
       <c r="R50" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50" s="1">
-        <v>0</v>
-      </c>
-      <c r="U50" s="1">
+        <v>1</v>
+      </c>
+      <c r="T50" s="1">
+        <v>0</v>
+      </c>
+      <c r="V50" s="1">
         <v>2</v>
       </c>
-      <c r="V50" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="W50" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="X50" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="X50" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="Y50" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z50" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA50" s="1">
         <v>0</v>
       </c>
       <c r="AB50" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="1">
         <v>100</v>
       </c>
-      <c r="AC50" s="1">
-        <v>0</v>
-      </c>
       <c r="AD50" s="1">
         <v>0</v>
       </c>
@@ -6588,15 +6723,18 @@
       <c r="AH50" s="1">
         <v>0</v>
       </c>
-      <c r="AJ50" s="1">
-        <v>50</v>
+      <c r="AI50" s="1">
+        <v>0</v>
       </c>
       <c r="AK50" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL50" s="1">
         <v>50</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1"/>
-    <row r="52" s="1" customFormat="1" spans="3:37">
+    <row r="52" s="1" customFormat="1" spans="3:38">
       <c r="C52" s="1">
         <v>10001</v>
       </c>
@@ -6607,10 +6745,10 @@
         <v>0</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H52" s="1">
         <v>1</v>
@@ -6619,62 +6757,62 @@
         <v>0</v>
       </c>
       <c r="J52" s="1">
-        <v>1</v>
-      </c>
-      <c r="K52" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="L52" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K52" s="1">
+        <v>1</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>193</v>
       </c>
       <c r="M52" s="1">
         <v>0</v>
       </c>
       <c r="N52" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O52" s="1">
         <v>1</v>
       </c>
       <c r="P52" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q52" s="1">
         <v>0</v>
       </c>
       <c r="R52" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S52" s="1">
-        <v>0</v>
-      </c>
-      <c r="U52" s="1">
+        <v>1</v>
+      </c>
+      <c r="T52" s="1">
+        <v>0</v>
+      </c>
+      <c r="V52" s="1">
         <v>3</v>
       </c>
-      <c r="V52" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="W52" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="X52" s="1">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="X52" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="Y52" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z52" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA52" s="1">
         <v>0</v>
       </c>
       <c r="AB52" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="1">
         <v>150</v>
       </c>
-      <c r="AC52" s="1">
-        <v>0</v>
-      </c>
       <c r="AD52" s="1">
         <v>0</v>
       </c>
@@ -6690,14 +6828,17 @@
       <c r="AH52" s="1">
         <v>0</v>
       </c>
-      <c r="AJ52" s="1">
-        <v>50</v>
+      <c r="AI52" s="1">
+        <v>0</v>
       </c>
       <c r="AK52" s="1">
         <v>50</v>
       </c>
+      <c r="AL52" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="53" spans="3:37">
+    <row r="53" spans="3:38">
       <c r="C53" s="2">
         <v>10002</v>
       </c>
@@ -6708,10 +6849,10 @@
         <v>0</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H53" s="2">
         <v>4</v>
@@ -6719,64 +6860,64 @@
       <c r="I53" s="1">
         <v>0</v>
       </c>
-      <c r="J53" s="2">
+      <c r="J53" s="1">
+        <v>0</v>
+      </c>
+      <c r="K53" s="2">
         <v>10</v>
       </c>
-      <c r="K53" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="L53" s="1">
-        <v>0</v>
-      </c>
-      <c r="M53" s="2">
-        <v>0</v>
-      </c>
-      <c r="N53" s="1">
-        <v>1</v>
+      <c r="L53" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="M53" s="1">
+        <v>0</v>
+      </c>
+      <c r="N53" s="2">
+        <v>0</v>
       </c>
       <c r="O53" s="1">
         <v>1</v>
       </c>
       <c r="P53" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q53" s="1">
         <v>0</v>
       </c>
       <c r="R53" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S53" s="1">
-        <v>0</v>
-      </c>
-      <c r="T53" s="1"/>
-      <c r="U53" s="2">
-        <v>0</v>
-      </c>
-      <c r="V53" s="1" t="s">
-        <v>70</v>
+        <v>1</v>
+      </c>
+      <c r="T53" s="1">
+        <v>0</v>
+      </c>
+      <c r="U53" s="1"/>
+      <c r="V53" s="2">
+        <v>0</v>
       </c>
       <c r="W53" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="X53" s="2">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="X53" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="Y53" s="2">
-        <v>1</v>
-      </c>
-      <c r="Z53" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Z53" s="2">
+        <v>1</v>
       </c>
       <c r="AA53" s="1">
         <v>0</v>
       </c>
-      <c r="AB53" s="2">
+      <c r="AB53" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="2">
         <v>100</v>
       </c>
-      <c r="AC53" s="1">
-        <v>0</v>
-      </c>
       <c r="AD53" s="1">
         <v>0</v>
       </c>
@@ -6792,15 +6933,18 @@
       <c r="AH53" s="1">
         <v>0</v>
       </c>
-      <c r="AI53" s="1"/>
-      <c r="AJ53" s="1">
-        <v>50</v>
-      </c>
+      <c r="AI53" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="1"/>
       <c r="AK53" s="1">
         <v>50</v>
       </c>
+      <c r="AL53" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="54" spans="3:37">
+    <row r="54" spans="3:38">
       <c r="C54" s="2">
         <v>10003</v>
       </c>
@@ -6811,10 +6955,10 @@
         <v>0</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H54" s="2">
         <v>1</v>
@@ -6822,64 +6966,64 @@
       <c r="I54" s="1">
         <v>0</v>
       </c>
-      <c r="J54" s="2">
-        <v>1</v>
-      </c>
-      <c r="K54" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="L54" s="1">
-        <v>0</v>
-      </c>
-      <c r="M54" s="2">
-        <v>0</v>
-      </c>
-      <c r="N54" s="1">
-        <v>1</v>
+      <c r="J54" s="1">
+        <v>0</v>
+      </c>
+      <c r="K54" s="2">
+        <v>1</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="M54" s="1">
+        <v>0</v>
+      </c>
+      <c r="N54" s="2">
+        <v>0</v>
       </c>
       <c r="O54" s="1">
         <v>1</v>
       </c>
       <c r="P54" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q54" s="1">
         <v>0</v>
       </c>
       <c r="R54" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S54" s="1">
-        <v>0</v>
-      </c>
-      <c r="T54" s="1"/>
-      <c r="U54" s="1">
-        <v>0</v>
-      </c>
-      <c r="V54" s="1" t="s">
-        <v>83</v>
+        <v>1</v>
+      </c>
+      <c r="T54" s="1">
+        <v>0</v>
+      </c>
+      <c r="U54" s="1"/>
+      <c r="V54" s="1">
+        <v>0</v>
       </c>
       <c r="W54" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="X54" s="1">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="X54" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="Y54" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="1">
         <v>10</v>
       </c>
-      <c r="Z54" s="1">
-        <v>0</v>
-      </c>
       <c r="AA54" s="1">
         <v>0</v>
       </c>
       <c r="AB54" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC54" s="1">
         <v>100</v>
       </c>
-      <c r="AC54" s="1">
-        <v>0</v>
-      </c>
       <c r="AD54" s="1">
         <v>0</v>
       </c>
@@ -6895,15 +7039,18 @@
       <c r="AH54" s="1">
         <v>0</v>
       </c>
-      <c r="AI54" s="1"/>
-      <c r="AJ54" s="1">
-        <v>50</v>
-      </c>
+      <c r="AI54" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ54" s="1"/>
       <c r="AK54" s="1">
         <v>50</v>
       </c>
+      <c r="AL54" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="55" spans="3:37">
+    <row r="55" spans="3:38">
       <c r="C55" s="2">
         <v>10004</v>
       </c>
@@ -6914,10 +7061,10 @@
         <v>0</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H55" s="2">
         <v>4</v>
@@ -6925,68 +7072,68 @@
       <c r="I55" s="1">
         <v>0</v>
       </c>
-      <c r="J55" s="2">
+      <c r="J55" s="1">
+        <v>0</v>
+      </c>
+      <c r="K55" s="2">
         <v>10</v>
       </c>
-      <c r="K55" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="L55" s="1">
-        <v>0</v>
-      </c>
-      <c r="M55" s="2">
-        <v>0</v>
-      </c>
-      <c r="N55" s="1">
-        <v>1</v>
-      </c>
-      <c r="O55" s="2">
+      <c r="L55" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="M55" s="1">
+        <v>0</v>
+      </c>
+      <c r="N55" s="2">
+        <v>0</v>
+      </c>
+      <c r="O55" s="1">
         <v>1</v>
       </c>
       <c r="P55" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q55" s="2">
         <v>0</v>
       </c>
       <c r="R55" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S55" s="1">
-        <v>0</v>
-      </c>
-      <c r="T55" s="1"/>
-      <c r="U55" s="2">
+        <v>1</v>
+      </c>
+      <c r="T55" s="1">
+        <v>0</v>
+      </c>
+      <c r="U55" s="1"/>
+      <c r="V55" s="2">
         <v>3</v>
       </c>
-      <c r="V55" s="2" t="s">
-        <v>197</v>
-      </c>
       <c r="W55" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="X55" s="2">
-        <v>0</v>
+        <v>199</v>
+      </c>
+      <c r="X55" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="Y55" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="2">
         <v>4</v>
       </c>
-      <c r="Z55" s="1">
-        <v>0</v>
-      </c>
       <c r="AA55" s="1">
         <v>0</v>
       </c>
-      <c r="AB55" s="2">
-        <v>50</v>
+      <c r="AB55" s="1">
+        <v>0</v>
       </c>
       <c r="AC55" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD55" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE55" s="2">
+        <v>50</v>
+      </c>
+      <c r="AD55" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE55" s="1">
         <v>0</v>
       </c>
       <c r="AF55" s="2">
@@ -6995,17 +7142,20 @@
       <c r="AG55" s="2">
         <v>0</v>
       </c>
-      <c r="AH55" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ55" s="1">
-        <v>50</v>
+      <c r="AH55" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI55" s="1">
+        <v>0</v>
       </c>
       <c r="AK55" s="1">
         <v>50</v>
       </c>
+      <c r="AL55" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="56" s="1" customFormat="1" spans="3:37">
+    <row r="56" s="1" customFormat="1" spans="3:38">
       <c r="C56" s="1">
         <v>10005</v>
       </c>
@@ -7016,80 +7166,80 @@
         <v>0</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G56" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H56" s="1">
+        <v>1</v>
+      </c>
+      <c r="I56" s="1">
+        <v>0</v>
+      </c>
+      <c r="J56" s="1">
+        <v>0</v>
+      </c>
+      <c r="K56" s="1">
+        <v>10</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="M56" s="1">
+        <v>0</v>
+      </c>
+      <c r="N56" s="1">
+        <v>0</v>
+      </c>
+      <c r="O56" s="1">
+        <v>1</v>
+      </c>
+      <c r="P56" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q56" s="2">
+        <v>0</v>
+      </c>
+      <c r="R56" s="1">
+        <v>0</v>
+      </c>
+      <c r="S56" s="1">
+        <v>1</v>
+      </c>
+      <c r="T56" s="1">
+        <v>0</v>
+      </c>
+      <c r="V56" s="1">
+        <v>2</v>
+      </c>
+      <c r="W56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="X56" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="H56" s="1">
-        <v>1</v>
-      </c>
-      <c r="I56" s="1">
-        <v>0</v>
-      </c>
-      <c r="J56" s="1">
-        <v>10</v>
-      </c>
-      <c r="K56" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="L56" s="1">
-        <v>0</v>
-      </c>
-      <c r="M56" s="1">
-        <v>0</v>
-      </c>
-      <c r="N56" s="1">
-        <v>1</v>
-      </c>
-      <c r="O56" s="1">
-        <v>1</v>
-      </c>
-      <c r="P56" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="1">
-        <v>0</v>
-      </c>
-      <c r="R56" s="1">
-        <v>1</v>
-      </c>
-      <c r="S56" s="1">
-        <v>0</v>
-      </c>
-      <c r="U56" s="1">
+      <c r="Y56" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z56" s="1">
         <v>2</v>
       </c>
-      <c r="V56" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="W56" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="X56" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y56" s="1">
-        <v>2</v>
-      </c>
-      <c r="Z56" s="1">
-        <v>0</v>
-      </c>
       <c r="AA56" s="1">
         <v>0</v>
       </c>
       <c r="AB56" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC56" s="1">
         <v>150</v>
       </c>
-      <c r="AC56" s="1">
-        <v>0</v>
-      </c>
       <c r="AD56" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE56" s="1">
         <v>20</v>
       </c>
-      <c r="AE56" s="1">
-        <v>0</v>
-      </c>
       <c r="AF56" s="1">
         <v>0</v>
       </c>
@@ -7099,14 +7249,17 @@
       <c r="AH56" s="1">
         <v>0</v>
       </c>
-      <c r="AJ56" s="1">
-        <v>50</v>
+      <c r="AI56" s="1">
+        <v>0</v>
       </c>
       <c r="AK56" s="1">
         <v>50</v>
       </c>
+      <c r="AL56" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="58" s="1" customFormat="1" spans="3:37">
+    <row r="58" s="1" customFormat="1" spans="3:38">
       <c r="C58" s="1">
         <v>11001</v>
       </c>
@@ -7117,10 +7270,10 @@
         <v>0</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H58" s="1">
         <v>1</v>
@@ -7129,59 +7282,59 @@
         <v>0</v>
       </c>
       <c r="J58" s="1">
+        <v>0</v>
+      </c>
+      <c r="K58" s="1">
         <v>10</v>
       </c>
-      <c r="L58" s="1">
-        <v>0</v>
-      </c>
       <c r="M58" s="1">
         <v>0</v>
       </c>
       <c r="N58" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O58" s="1">
         <v>1</v>
       </c>
       <c r="P58" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q58" s="1">
         <v>9999</v>
       </c>
-      <c r="Q58" s="1">
-        <v>0</v>
-      </c>
       <c r="R58" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S58" s="1">
-        <v>0</v>
-      </c>
-      <c r="U58" s="1">
-        <v>1</v>
-      </c>
-      <c r="V58" s="1" t="s">
-        <v>70</v>
+        <v>1</v>
+      </c>
+      <c r="T58" s="1">
+        <v>0</v>
+      </c>
+      <c r="V58" s="1">
+        <v>1</v>
       </c>
       <c r="W58" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="X58" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="X58" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="Y58" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z58" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA58" s="1">
         <v>0</v>
       </c>
       <c r="AB58" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="1">
         <v>120</v>
       </c>
-      <c r="AC58" s="1">
-        <v>0</v>
-      </c>
       <c r="AD58" s="1">
         <v>0</v>
       </c>
@@ -7197,14 +7350,17 @@
       <c r="AH58" s="1">
         <v>0</v>
       </c>
-      <c r="AJ58" s="1">
-        <v>50</v>
+      <c r="AI58" s="1">
+        <v>0</v>
       </c>
       <c r="AK58" s="1">
         <v>50</v>
       </c>
+      <c r="AL58" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="59" s="1" customFormat="1" spans="3:37">
+    <row r="59" s="1" customFormat="1" spans="3:38">
       <c r="C59" s="1">
         <v>11002</v>
       </c>
@@ -7215,77 +7371,77 @@
         <v>0</v>
       </c>
       <c r="F59" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H59" s="1">
+        <v>1</v>
+      </c>
+      <c r="I59" s="1">
+        <v>0</v>
+      </c>
+      <c r="J59" s="1">
+        <v>0</v>
+      </c>
+      <c r="K59" s="1">
+        <v>10</v>
+      </c>
+      <c r="M59" s="1">
+        <v>0</v>
+      </c>
+      <c r="N59" s="1">
+        <v>0</v>
+      </c>
+      <c r="O59" s="1">
+        <v>2</v>
+      </c>
+      <c r="P59" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q59" s="1">
+        <v>9999</v>
+      </c>
+      <c r="R59" s="1">
+        <v>0</v>
+      </c>
+      <c r="S59" s="1">
+        <v>1</v>
+      </c>
+      <c r="T59" s="1">
+        <v>0</v>
+      </c>
+      <c r="V59" s="1">
+        <v>2</v>
+      </c>
+      <c r="W59" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G59" s="2" t="s">
+      <c r="X59" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="H59" s="1">
-        <v>1</v>
-      </c>
-      <c r="I59" s="1">
-        <v>0</v>
-      </c>
-      <c r="J59" s="1">
-        <v>10</v>
-      </c>
-      <c r="L59" s="1">
-        <v>0</v>
-      </c>
-      <c r="M59" s="1">
-        <v>0</v>
-      </c>
-      <c r="N59" s="1">
+      <c r="Y59" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="1">
         <v>2</v>
       </c>
-      <c r="O59" s="1">
-        <v>1</v>
-      </c>
-      <c r="P59" s="1">
-        <v>9999</v>
-      </c>
-      <c r="Q59" s="1">
-        <v>0</v>
-      </c>
-      <c r="R59" s="1">
-        <v>1</v>
-      </c>
-      <c r="S59" s="1">
-        <v>0</v>
-      </c>
-      <c r="U59" s="1">
-        <v>2</v>
-      </c>
-      <c r="V59" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="W59" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="X59" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y59" s="1">
-        <v>2</v>
-      </c>
-      <c r="Z59" s="1">
-        <v>0</v>
-      </c>
       <c r="AA59" s="1">
         <v>0</v>
       </c>
       <c r="AB59" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="1">
         <v>150</v>
       </c>
-      <c r="AC59" s="1">
-        <v>0</v>
-      </c>
       <c r="AD59" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="1">
         <v>20</v>
       </c>
-      <c r="AE59" s="1">
-        <v>0</v>
-      </c>
       <c r="AF59" s="1">
         <v>0</v>
       </c>
@@ -7295,14 +7451,17 @@
       <c r="AH59" s="1">
         <v>0</v>
       </c>
-      <c r="AJ59" s="1">
-        <v>50</v>
+      <c r="AI59" s="1">
+        <v>0</v>
       </c>
       <c r="AK59" s="1">
         <v>50</v>
       </c>
+      <c r="AL59" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="60" s="1" customFormat="1" spans="3:37">
+    <row r="60" s="1" customFormat="1" spans="3:38">
       <c r="C60" s="1">
         <v>11003</v>
       </c>
@@ -7313,10 +7472,10 @@
         <v>0</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H60" s="1">
         <v>1</v>
@@ -7325,59 +7484,59 @@
         <v>0</v>
       </c>
       <c r="J60" s="1">
+        <v>0</v>
+      </c>
+      <c r="K60" s="1">
         <v>10</v>
       </c>
-      <c r="L60" s="1">
-        <v>0</v>
-      </c>
       <c r="M60" s="1">
         <v>0</v>
       </c>
       <c r="N60" s="1">
+        <v>0</v>
+      </c>
+      <c r="O60" s="1">
         <v>2</v>
       </c>
-      <c r="O60" s="1">
-        <v>1</v>
-      </c>
       <c r="P60" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q60" s="1">
         <v>9999</v>
       </c>
-      <c r="Q60" s="1">
-        <v>0</v>
-      </c>
       <c r="R60" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S60" s="1">
-        <v>0</v>
-      </c>
-      <c r="U60" s="1">
-        <v>1</v>
-      </c>
-      <c r="V60" s="1" t="s">
-        <v>70</v>
+        <v>1</v>
+      </c>
+      <c r="T60" s="1">
+        <v>0</v>
+      </c>
+      <c r="V60" s="1">
+        <v>1</v>
       </c>
       <c r="W60" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="X60" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="X60" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="Y60" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="1">
         <v>5</v>
       </c>
-      <c r="Z60" s="1">
-        <v>0</v>
-      </c>
       <c r="AA60" s="1">
         <v>0</v>
       </c>
       <c r="AB60" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="1">
         <v>100</v>
       </c>
-      <c r="AC60" s="1">
-        <v>0</v>
-      </c>
       <c r="AD60" s="1">
         <v>0</v>
       </c>
@@ -7393,14 +7552,17 @@
       <c r="AH60" s="1">
         <v>0</v>
       </c>
-      <c r="AJ60" s="1">
-        <v>50</v>
+      <c r="AI60" s="1">
+        <v>0</v>
       </c>
       <c r="AK60" s="1">
         <v>50</v>
       </c>
+      <c r="AL60" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="61" s="1" customFormat="1" spans="3:37">
+    <row r="61" s="1" customFormat="1" spans="3:38">
       <c r="C61" s="1">
         <v>11004</v>
       </c>
@@ -7411,10 +7573,10 @@
         <v>0</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H61" s="1">
         <v>7</v>
@@ -7423,59 +7585,59 @@
         <v>0</v>
       </c>
       <c r="J61" s="1">
+        <v>0</v>
+      </c>
+      <c r="K61" s="1">
         <v>10</v>
       </c>
-      <c r="L61" s="1">
-        <v>0</v>
-      </c>
       <c r="M61" s="1">
+        <v>0</v>
+      </c>
+      <c r="N61" s="1">
         <v>5</v>
       </c>
-      <c r="N61" s="1">
-        <v>1</v>
-      </c>
       <c r="O61" s="1">
         <v>1</v>
       </c>
       <c r="P61" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q61" s="1">
         <v>9999</v>
       </c>
-      <c r="Q61" s="1">
-        <v>0</v>
-      </c>
       <c r="R61" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S61" s="1">
-        <v>0</v>
-      </c>
-      <c r="U61" s="1">
+        <v>1</v>
+      </c>
+      <c r="T61" s="1">
+        <v>0</v>
+      </c>
+      <c r="V61" s="1">
         <v>4</v>
       </c>
-      <c r="V61" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="W61" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="X61" s="1">
+        <v>85</v>
+      </c>
+      <c r="X61" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y61" s="1">
         <v>2</v>
       </c>
-      <c r="Y61" s="1">
-        <v>1</v>
-      </c>
       <c r="Z61" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA61" s="1">
         <v>0</v>
       </c>
       <c r="AB61" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="1">
         <v>200</v>
       </c>
-      <c r="AC61" s="1">
-        <v>0</v>
-      </c>
       <c r="AD61" s="1">
         <v>0</v>
       </c>
@@ -7491,17 +7653,20 @@
       <c r="AH61" s="1">
         <v>0</v>
       </c>
-      <c r="AI61" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="AJ61" s="1">
-        <v>50</v>
+      <c r="AI61" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="1" t="s">
+        <v>201</v>
       </c>
       <c r="AK61" s="1">
         <v>50</v>
       </c>
+      <c r="AL61" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="62" s="1" customFormat="1" spans="3:37">
+    <row r="62" s="1" customFormat="1" spans="3:38">
       <c r="C62" s="1">
         <v>11005</v>
       </c>
@@ -7512,10 +7677,10 @@
         <v>0</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H62" s="1">
         <v>5</v>
@@ -7524,47 +7689,47 @@
         <v>0</v>
       </c>
       <c r="J62" s="1">
-        <v>50</v>
-      </c>
-      <c r="L62" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K62" s="1">
+        <v>50</v>
       </c>
       <c r="M62" s="1">
+        <v>0</v>
+      </c>
+      <c r="N62" s="1">
         <v>30</v>
       </c>
-      <c r="N62" s="1">
-        <v>1</v>
-      </c>
       <c r="O62" s="1">
         <v>1</v>
       </c>
       <c r="P62" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q62" s="1">
         <v>9999</v>
       </c>
-      <c r="Q62" s="1">
-        <v>0</v>
-      </c>
       <c r="R62" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S62" s="1">
-        <v>0</v>
-      </c>
-      <c r="U62" s="1">
-        <v>0</v>
-      </c>
-      <c r="V62" s="1" t="s">
-        <v>70</v>
+        <v>1</v>
+      </c>
+      <c r="T62" s="1">
+        <v>0</v>
+      </c>
+      <c r="V62" s="1">
+        <v>0</v>
       </c>
       <c r="W62" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="X62" s="1">
+        <v>72</v>
+      </c>
+      <c r="X62" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y62" s="1">
         <v>30</v>
       </c>
-      <c r="Y62" s="1">
-        <v>0</v>
-      </c>
       <c r="Z62" s="1">
         <v>0</v>
       </c>
@@ -7572,11 +7737,11 @@
         <v>0</v>
       </c>
       <c r="AB62" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="1">
         <v>20</v>
       </c>
-      <c r="AC62" s="1">
-        <v>0</v>
-      </c>
       <c r="AD62" s="1">
         <v>0</v>
       </c>
@@ -7592,15 +7757,18 @@
       <c r="AH62" s="1">
         <v>0</v>
       </c>
-      <c r="AI62" s="7"/>
-      <c r="AJ62" s="1">
-        <v>50</v>
-      </c>
+      <c r="AI62" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ62" s="7"/>
       <c r="AK62" s="1">
         <v>50</v>
       </c>
+      <c r="AL62" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="63" s="1" customFormat="1" spans="3:37">
+    <row r="63" s="1" customFormat="1" spans="3:38">
       <c r="C63" s="1">
         <v>11006</v>
       </c>
@@ -7611,10 +7779,10 @@
         <v>0</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H63" s="1">
         <v>6</v>
@@ -7623,43 +7791,43 @@
         <v>0</v>
       </c>
       <c r="J63" s="1">
+        <v>0</v>
+      </c>
+      <c r="K63" s="1">
         <v>10</v>
       </c>
-      <c r="L63" s="1">
-        <v>0</v>
-      </c>
       <c r="M63" s="1">
         <v>0</v>
       </c>
       <c r="N63" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O63" s="1">
         <v>1</v>
       </c>
       <c r="P63" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q63" s="1">
         <v>9999</v>
       </c>
-      <c r="Q63" s="1">
-        <v>0</v>
-      </c>
       <c r="R63" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S63" s="1">
-        <v>0</v>
-      </c>
-      <c r="U63" s="1">
-        <v>0</v>
-      </c>
-      <c r="V63" s="1" t="s">
-        <v>70</v>
+        <v>1</v>
+      </c>
+      <c r="T63" s="1">
+        <v>0</v>
+      </c>
+      <c r="V63" s="1">
+        <v>0</v>
       </c>
       <c r="W63" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="X63" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="X63" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="Y63" s="1">
         <v>0</v>
@@ -7671,10 +7839,10 @@
         <v>0</v>
       </c>
       <c r="AB63" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AC63" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AD63" s="1">
         <v>0</v>
@@ -7691,14 +7859,17 @@
       <c r="AH63" s="1">
         <v>0</v>
       </c>
-      <c r="AJ63" s="1">
-        <v>50</v>
+      <c r="AI63" s="1">
+        <v>0</v>
       </c>
       <c r="AK63" s="1">
         <v>50</v>
       </c>
+      <c r="AL63" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="64" s="1" customFormat="1" spans="3:37">
+    <row r="64" s="1" customFormat="1" spans="3:38">
       <c r="C64" s="1">
         <v>11007</v>
       </c>
@@ -7709,10 +7880,10 @@
         <v>0</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H64" s="1">
         <v>1</v>
@@ -7721,59 +7892,59 @@
         <v>0</v>
       </c>
       <c r="J64" s="1">
+        <v>0</v>
+      </c>
+      <c r="K64" s="1">
         <v>10</v>
       </c>
-      <c r="L64" s="1">
-        <v>0</v>
-      </c>
       <c r="M64" s="1">
         <v>0</v>
       </c>
       <c r="N64" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O64" s="1">
         <v>1</v>
       </c>
       <c r="P64" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q64" s="1">
         <v>9999</v>
       </c>
-      <c r="Q64" s="1">
-        <v>0</v>
-      </c>
       <c r="R64" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S64" s="1">
-        <v>0</v>
-      </c>
-      <c r="U64" s="1">
-        <v>1</v>
-      </c>
-      <c r="V64" s="1" t="s">
-        <v>70</v>
+        <v>1</v>
+      </c>
+      <c r="T64" s="1">
+        <v>0</v>
+      </c>
+      <c r="V64" s="1">
+        <v>1</v>
       </c>
       <c r="W64" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="X64" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="X64" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="Y64" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z64" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA64" s="1">
         <v>0</v>
       </c>
       <c r="AB64" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="1">
         <v>300</v>
       </c>
-      <c r="AC64" s="1">
-        <v>0</v>
-      </c>
       <c r="AD64" s="1">
         <v>0</v>
       </c>
@@ -7789,14 +7960,17 @@
       <c r="AH64" s="1">
         <v>0</v>
       </c>
-      <c r="AJ64" s="1">
-        <v>50</v>
+      <c r="AI64" s="1">
+        <v>0</v>
       </c>
       <c r="AK64" s="1">
         <v>50</v>
       </c>
+      <c r="AL64" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="65" s="1" customFormat="1" spans="3:37">
+    <row r="65" s="1" customFormat="1" spans="3:38">
       <c r="C65" s="1">
         <v>12001</v>
       </c>
@@ -7807,10 +7981,10 @@
         <v>0</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H65" s="1">
         <v>1</v>
@@ -7819,59 +7993,59 @@
         <v>0</v>
       </c>
       <c r="J65" s="1">
+        <v>0</v>
+      </c>
+      <c r="K65" s="1">
         <v>10</v>
       </c>
-      <c r="L65" s="1">
-        <v>0</v>
-      </c>
       <c r="M65" s="1">
         <v>0</v>
       </c>
       <c r="N65" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O65" s="1">
+        <v>1</v>
+      </c>
+      <c r="P65" s="1">
         <v>2</v>
       </c>
-      <c r="P65" s="1">
+      <c r="Q65" s="1">
         <v>9999</v>
       </c>
-      <c r="Q65" s="1">
-        <v>0</v>
-      </c>
       <c r="R65" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S65" s="1">
-        <v>0</v>
-      </c>
-      <c r="U65" s="1">
+        <v>1</v>
+      </c>
+      <c r="T65" s="1">
+        <v>0</v>
+      </c>
+      <c r="V65" s="1">
         <v>2</v>
       </c>
-      <c r="V65" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="W65" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="X65" s="1">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="X65" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="Y65" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z65" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA65" s="1">
         <v>0</v>
       </c>
       <c r="AB65" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="1">
         <v>120</v>
       </c>
-      <c r="AC65" s="1">
-        <v>0</v>
-      </c>
       <c r="AD65" s="1">
         <v>0</v>
       </c>
@@ -7887,14 +8061,17 @@
       <c r="AH65" s="1">
         <v>0</v>
       </c>
-      <c r="AJ65" s="1">
-        <v>50</v>
+      <c r="AI65" s="1">
+        <v>0</v>
       </c>
       <c r="AK65" s="1">
         <v>50</v>
       </c>
+      <c r="AL65" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="66" s="1" customFormat="1" spans="3:37">
+    <row r="66" s="1" customFormat="1" spans="3:38">
       <c r="C66" s="1">
         <v>12002</v>
       </c>
@@ -7905,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H66" s="1">
         <v>1</v>
@@ -7917,59 +8094,59 @@
         <v>0</v>
       </c>
       <c r="J66" s="1">
+        <v>0</v>
+      </c>
+      <c r="K66" s="1">
         <v>10</v>
       </c>
-      <c r="L66" s="1">
-        <v>0</v>
-      </c>
       <c r="M66" s="1">
         <v>0</v>
       </c>
       <c r="N66" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O66" s="1">
+        <v>1</v>
+      </c>
+      <c r="P66" s="1">
         <v>2</v>
       </c>
-      <c r="P66" s="1">
+      <c r="Q66" s="1">
         <v>9999</v>
       </c>
-      <c r="Q66" s="1">
-        <v>0</v>
-      </c>
       <c r="R66" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S66" s="1">
-        <v>0</v>
-      </c>
-      <c r="U66" s="1">
+        <v>1</v>
+      </c>
+      <c r="T66" s="1">
+        <v>0</v>
+      </c>
+      <c r="V66" s="1">
         <v>3</v>
       </c>
-      <c r="V66" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="W66" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="X66" s="1">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="X66" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="Y66" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z66" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA66" s="1">
         <v>0</v>
       </c>
       <c r="AB66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC66" s="1">
         <v>150</v>
       </c>
-      <c r="AC66" s="1">
-        <v>0</v>
-      </c>
       <c r="AD66" s="1">
         <v>0</v>
       </c>
@@ -7985,14 +8162,17 @@
       <c r="AH66" s="1">
         <v>0</v>
       </c>
-      <c r="AJ66" s="1">
-        <v>50</v>
+      <c r="AI66" s="1">
+        <v>0</v>
       </c>
       <c r="AK66" s="1">
         <v>50</v>
       </c>
+      <c r="AL66" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="67" s="1" customFormat="1" spans="3:37">
+    <row r="67" s="1" customFormat="1" spans="3:38">
       <c r="C67" s="1">
         <v>12003</v>
       </c>
@@ -8003,10 +8183,10 @@
         <v>0</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H67" s="1">
         <v>3</v>
@@ -8015,59 +8195,59 @@
         <v>0</v>
       </c>
       <c r="J67" s="1">
+        <v>0</v>
+      </c>
+      <c r="K67" s="1">
         <v>10</v>
       </c>
-      <c r="L67" s="1">
-        <v>0</v>
-      </c>
       <c r="M67" s="1">
+        <v>0</v>
+      </c>
+      <c r="N67" s="1">
         <v>5</v>
-      </c>
-      <c r="N67" s="1">
-        <v>2</v>
       </c>
       <c r="O67" s="1">
         <v>2</v>
       </c>
       <c r="P67" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q67" s="1">
         <v>9999</v>
       </c>
-      <c r="Q67" s="1">
-        <v>0</v>
-      </c>
       <c r="R67" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S67" s="1">
-        <v>0</v>
-      </c>
-      <c r="U67" s="1">
+        <v>1</v>
+      </c>
+      <c r="T67" s="1">
+        <v>0</v>
+      </c>
+      <c r="V67" s="1">
         <v>3</v>
       </c>
-      <c r="V67" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="W67" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="X67" s="1">
-        <v>5</v>
+        <v>85</v>
+      </c>
+      <c r="X67" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="Y67" s="1">
         <v>5</v>
       </c>
       <c r="Z67" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AA67" s="1">
         <v>2</v>
       </c>
       <c r="AB67" s="1">
+        <v>2</v>
+      </c>
+      <c r="AC67" s="1">
         <v>80</v>
       </c>
-      <c r="AC67" s="1">
-        <v>0</v>
-      </c>
       <c r="AD67" s="1">
         <v>0</v>
       </c>
@@ -8083,14 +8263,17 @@
       <c r="AH67" s="1">
         <v>0</v>
       </c>
-      <c r="AJ67" s="1">
-        <v>50</v>
+      <c r="AI67" s="1">
+        <v>0</v>
       </c>
       <c r="AK67" s="1">
         <v>50</v>
       </c>
+      <c r="AL67" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="68" s="1" customFormat="1" spans="3:37">
+    <row r="68" s="1" customFormat="1" spans="3:38">
       <c r="C68" s="1">
         <v>12004</v>
       </c>
@@ -8101,10 +8284,10 @@
         <v>0</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H68" s="1">
         <v>1</v>
@@ -8113,59 +8296,59 @@
         <v>0</v>
       </c>
       <c r="J68" s="1">
+        <v>0</v>
+      </c>
+      <c r="K68" s="1">
         <v>10</v>
       </c>
-      <c r="L68" s="1">
-        <v>0</v>
-      </c>
       <c r="M68" s="1">
         <v>0</v>
       </c>
       <c r="N68" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O68" s="1">
         <v>2</v>
       </c>
       <c r="P68" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q68" s="1">
         <v>9999</v>
       </c>
-      <c r="Q68" s="1">
-        <v>0</v>
-      </c>
       <c r="R68" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S68" s="1">
-        <v>0</v>
-      </c>
-      <c r="U68" s="1">
+        <v>1</v>
+      </c>
+      <c r="T68" s="1">
+        <v>0</v>
+      </c>
+      <c r="V68" s="1">
         <v>4</v>
       </c>
-      <c r="V68" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="W68" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="X68" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="X68" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="Y68" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="1">
         <v>4</v>
-      </c>
-      <c r="Z68" s="1">
-        <v>2</v>
       </c>
       <c r="AA68" s="1">
         <v>2</v>
       </c>
       <c r="AB68" s="1">
+        <v>2</v>
+      </c>
+      <c r="AC68" s="1">
         <v>100</v>
       </c>
-      <c r="AC68" s="1">
-        <v>0</v>
-      </c>
       <c r="AD68" s="1">
         <v>0</v>
       </c>
@@ -8181,14 +8364,17 @@
       <c r="AH68" s="1">
         <v>0</v>
       </c>
-      <c r="AJ68" s="1">
-        <v>50</v>
+      <c r="AI68" s="1">
+        <v>0</v>
       </c>
       <c r="AK68" s="1">
         <v>50</v>
       </c>
+      <c r="AL68" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="69" s="1" customFormat="1" spans="3:37">
+    <row r="69" s="1" customFormat="1" spans="3:38">
       <c r="C69" s="1">
         <v>12005</v>
       </c>
@@ -8199,10 +8385,10 @@
         <v>0</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H69" s="1">
         <v>5</v>
@@ -8211,47 +8397,47 @@
         <v>0</v>
       </c>
       <c r="J69" s="1">
-        <v>50</v>
-      </c>
-      <c r="L69" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K69" s="1">
+        <v>50</v>
       </c>
       <c r="M69" s="1">
+        <v>0</v>
+      </c>
+      <c r="N69" s="1">
         <v>30</v>
       </c>
-      <c r="N69" s="1">
-        <v>1</v>
-      </c>
       <c r="O69" s="1">
+        <v>1</v>
+      </c>
+      <c r="P69" s="1">
         <v>2</v>
       </c>
-      <c r="P69" s="1">
+      <c r="Q69" s="1">
         <v>9999</v>
       </c>
-      <c r="Q69" s="1">
-        <v>0</v>
-      </c>
       <c r="R69" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S69" s="1">
-        <v>0</v>
-      </c>
-      <c r="U69" s="1">
-        <v>0</v>
-      </c>
-      <c r="V69" s="1" t="s">
-        <v>70</v>
+        <v>1</v>
+      </c>
+      <c r="T69" s="1">
+        <v>0</v>
+      </c>
+      <c r="V69" s="1">
+        <v>0</v>
       </c>
       <c r="W69" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="X69" s="1">
+        <v>72</v>
+      </c>
+      <c r="X69" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y69" s="1">
         <v>30</v>
       </c>
-      <c r="Y69" s="1">
-        <v>0</v>
-      </c>
       <c r="Z69" s="1">
         <v>0</v>
       </c>
@@ -8259,11 +8445,11 @@
         <v>0</v>
       </c>
       <c r="AB69" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="1">
         <v>20</v>
       </c>
-      <c r="AC69" s="1">
-        <v>0</v>
-      </c>
       <c r="AD69" s="1">
         <v>0</v>
       </c>
@@ -8279,15 +8465,18 @@
       <c r="AH69" s="1">
         <v>0</v>
       </c>
-      <c r="AI69" s="7"/>
-      <c r="AJ69" s="1">
-        <v>50</v>
-      </c>
+      <c r="AI69" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ69" s="7"/>
       <c r="AK69" s="1">
         <v>50</v>
       </c>
+      <c r="AL69" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="70" s="1" customFormat="1" spans="3:37">
+    <row r="70" s="1" customFormat="1" spans="3:38">
       <c r="C70" s="1">
         <v>12006</v>
       </c>
@@ -8298,10 +8487,10 @@
         <v>0</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H70" s="1">
         <v>6</v>
@@ -8310,43 +8499,43 @@
         <v>0</v>
       </c>
       <c r="J70" s="1">
+        <v>0</v>
+      </c>
+      <c r="K70" s="1">
         <v>10</v>
       </c>
-      <c r="L70" s="1">
-        <v>0</v>
-      </c>
       <c r="M70" s="1">
         <v>0</v>
       </c>
       <c r="N70" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O70" s="1">
+        <v>1</v>
+      </c>
+      <c r="P70" s="1">
         <v>2</v>
       </c>
-      <c r="P70" s="1">
+      <c r="Q70" s="1">
         <v>9999</v>
       </c>
-      <c r="Q70" s="1">
-        <v>0</v>
-      </c>
       <c r="R70" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S70" s="1">
-        <v>0</v>
-      </c>
-      <c r="U70" s="1">
-        <v>0</v>
-      </c>
-      <c r="V70" s="1" t="s">
-        <v>70</v>
+        <v>1</v>
+      </c>
+      <c r="T70" s="1">
+        <v>0</v>
+      </c>
+      <c r="V70" s="1">
+        <v>0</v>
       </c>
       <c r="W70" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="X70" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="X70" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="Y70" s="1">
         <v>0</v>
@@ -8358,10 +8547,10 @@
         <v>0</v>
       </c>
       <c r="AB70" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AC70" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AD70" s="1">
         <v>0</v>
@@ -8378,14 +8567,17 @@
       <c r="AH70" s="1">
         <v>0</v>
       </c>
-      <c r="AJ70" s="1">
-        <v>50</v>
+      <c r="AI70" s="1">
+        <v>0</v>
       </c>
       <c r="AK70" s="1">
         <v>50</v>
       </c>
+      <c r="AL70" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="71" s="1" customFormat="1" spans="3:37">
+    <row r="71" s="1" customFormat="1" spans="3:38">
       <c r="C71" s="1">
         <v>12007</v>
       </c>
@@ -8396,10 +8588,10 @@
         <v>0</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H71" s="1">
         <v>1</v>
@@ -8408,59 +8600,59 @@
         <v>0</v>
       </c>
       <c r="J71" s="1">
+        <v>0</v>
+      </c>
+      <c r="K71" s="1">
         <v>10</v>
       </c>
-      <c r="L71" s="1">
-        <v>0</v>
-      </c>
       <c r="M71" s="1">
         <v>0</v>
       </c>
       <c r="N71" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O71" s="1">
         <v>2</v>
       </c>
       <c r="P71" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q71" s="1">
         <v>9999</v>
       </c>
-      <c r="Q71" s="1">
-        <v>0</v>
-      </c>
       <c r="R71" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S71" s="1">
-        <v>0</v>
-      </c>
-      <c r="U71" s="1">
+        <v>1</v>
+      </c>
+      <c r="T71" s="1">
+        <v>0</v>
+      </c>
+      <c r="V71" s="1">
         <v>5</v>
       </c>
-      <c r="V71" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="W71" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="X71" s="1">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="X71" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="Y71" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="1">
         <v>5</v>
-      </c>
-      <c r="Z71" s="1">
-        <v>3</v>
       </c>
       <c r="AA71" s="1">
         <v>3</v>
       </c>
       <c r="AB71" s="1">
+        <v>3</v>
+      </c>
+      <c r="AC71" s="1">
         <v>150</v>
       </c>
-      <c r="AC71" s="1">
-        <v>0</v>
-      </c>
       <c r="AD71" s="1">
         <v>0</v>
       </c>
@@ -8476,14 +8668,17 @@
       <c r="AH71" s="1">
         <v>0</v>
       </c>
-      <c r="AJ71" s="1">
-        <v>50</v>
+      <c r="AI71" s="1">
+        <v>0</v>
       </c>
       <c r="AK71" s="1">
         <v>50</v>
       </c>
+      <c r="AL71" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="72" s="1" customFormat="1" spans="3:37">
+    <row r="72" s="1" customFormat="1" spans="3:38">
       <c r="C72" s="1">
         <v>13001</v>
       </c>
@@ -8494,10 +8689,10 @@
         <v>0</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H72" s="1">
         <v>4</v>
@@ -8506,43 +8701,43 @@
         <v>0</v>
       </c>
       <c r="J72" s="1">
+        <v>0</v>
+      </c>
+      <c r="K72" s="1">
         <v>20</v>
       </c>
-      <c r="L72" s="1">
-        <v>0</v>
-      </c>
       <c r="M72" s="1">
+        <v>0</v>
+      </c>
+      <c r="N72" s="1">
         <v>4</v>
       </c>
-      <c r="N72" s="1">
-        <v>1</v>
-      </c>
       <c r="O72" s="1">
+        <v>1</v>
+      </c>
+      <c r="P72" s="1">
         <v>3</v>
       </c>
-      <c r="P72" s="1">
+      <c r="Q72" s="1">
         <v>9999</v>
       </c>
-      <c r="Q72" s="1">
-        <v>0</v>
-      </c>
       <c r="R72" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S72" s="1">
-        <v>0</v>
-      </c>
-      <c r="U72" s="1">
-        <v>0</v>
-      </c>
-      <c r="V72" s="1" t="s">
-        <v>70</v>
+        <v>1</v>
+      </c>
+      <c r="T72" s="1">
+        <v>0</v>
+      </c>
+      <c r="V72" s="1">
+        <v>0</v>
       </c>
       <c r="W72" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="X72" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="X72" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="Y72" s="1">
         <v>0</v>
@@ -8554,10 +8749,10 @@
         <v>0</v>
       </c>
       <c r="AB72" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AC72" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AD72" s="1">
         <v>0</v>
@@ -8574,14 +8769,17 @@
       <c r="AH72" s="1">
         <v>0</v>
       </c>
-      <c r="AJ72" s="1">
-        <v>50</v>
+      <c r="AI72" s="1">
+        <v>0</v>
       </c>
       <c r="AK72" s="1">
         <v>50</v>
       </c>
+      <c r="AL72" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="73" s="1" customFormat="1" spans="3:37">
+    <row r="73" s="1" customFormat="1" spans="3:38">
       <c r="C73" s="1">
         <v>13002</v>
       </c>
@@ -8592,10 +8790,10 @@
         <v>0</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H73" s="1">
         <v>1</v>
@@ -8604,59 +8802,59 @@
         <v>0</v>
       </c>
       <c r="J73" s="1">
+        <v>0</v>
+      </c>
+      <c r="K73" s="1">
         <v>10</v>
       </c>
-      <c r="L73" s="1">
-        <v>0</v>
-      </c>
       <c r="M73" s="1">
         <v>0</v>
       </c>
       <c r="N73" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O73" s="1">
+        <v>1</v>
+      </c>
+      <c r="P73" s="1">
         <v>3</v>
       </c>
-      <c r="P73" s="1">
+      <c r="Q73" s="1">
         <v>9999</v>
       </c>
-      <c r="Q73" s="1">
-        <v>0</v>
-      </c>
       <c r="R73" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S73" s="1">
-        <v>0</v>
-      </c>
-      <c r="U73" s="1">
+        <v>1</v>
+      </c>
+      <c r="T73" s="1">
+        <v>0</v>
+      </c>
+      <c r="V73" s="1">
         <v>3</v>
       </c>
-      <c r="V73" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="W73" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="X73" s="1">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="X73" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="Y73" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z73" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA73" s="1">
         <v>0</v>
       </c>
       <c r="AB73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="1">
         <v>120</v>
       </c>
-      <c r="AC73" s="1">
-        <v>0</v>
-      </c>
       <c r="AD73" s="1">
         <v>0</v>
       </c>
@@ -8672,14 +8870,17 @@
       <c r="AH73" s="1">
         <v>0</v>
       </c>
-      <c r="AJ73" s="1">
-        <v>50</v>
+      <c r="AI73" s="1">
+        <v>0</v>
       </c>
       <c r="AK73" s="1">
         <v>50</v>
       </c>
+      <c r="AL73" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="74" s="1" customFormat="1" spans="3:37">
+    <row r="74" s="1" customFormat="1" spans="3:38">
       <c r="C74" s="1">
         <v>13003</v>
       </c>
@@ -8690,10 +8891,10 @@
         <v>0</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H74" s="1">
         <v>1</v>
@@ -8702,65 +8903,65 @@
         <v>0</v>
       </c>
       <c r="J74" s="1">
+        <v>0</v>
+      </c>
+      <c r="K74" s="1">
         <v>10</v>
       </c>
-      <c r="L74" s="1">
-        <v>0</v>
-      </c>
       <c r="M74" s="1">
+        <v>0</v>
+      </c>
+      <c r="N74" s="1">
         <v>5</v>
       </c>
-      <c r="N74" s="1">
-        <v>1</v>
-      </c>
       <c r="O74" s="1">
+        <v>1</v>
+      </c>
+      <c r="P74" s="1">
         <v>3</v>
       </c>
-      <c r="P74" s="1">
+      <c r="Q74" s="1">
         <v>9999</v>
       </c>
-      <c r="Q74" s="1">
-        <v>0</v>
-      </c>
       <c r="R74" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S74" s="1">
-        <v>0</v>
-      </c>
-      <c r="U74" s="1">
+        <v>1</v>
+      </c>
+      <c r="T74" s="1">
+        <v>0</v>
+      </c>
+      <c r="V74" s="1">
         <v>2</v>
       </c>
-      <c r="V74" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="W74" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="X74" s="1">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="X74" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="Y74" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="1">
         <v>5</v>
       </c>
-      <c r="Z74" s="1">
-        <v>0</v>
-      </c>
       <c r="AA74" s="1">
         <v>0</v>
       </c>
       <c r="AB74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="1">
         <v>35</v>
       </c>
-      <c r="AC74" s="1">
-        <v>0</v>
-      </c>
       <c r="AD74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="1">
         <v>65</v>
       </c>
-      <c r="AE74" s="1">
-        <v>0</v>
-      </c>
       <c r="AF74" s="1">
         <v>0</v>
       </c>
@@ -8770,14 +8971,17 @@
       <c r="AH74" s="1">
         <v>0</v>
       </c>
-      <c r="AJ74" s="1">
-        <v>50</v>
+      <c r="AI74" s="1">
+        <v>0</v>
       </c>
       <c r="AK74" s="1">
         <v>50</v>
       </c>
+      <c r="AL74" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="75" s="1" customFormat="1" spans="3:37">
+    <row r="75" s="1" customFormat="1" spans="3:38">
       <c r="C75" s="1">
         <v>13004</v>
       </c>
@@ -8788,10 +8992,10 @@
         <v>0</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H75" s="1">
         <v>2</v>
@@ -8800,59 +9004,59 @@
         <v>0</v>
       </c>
       <c r="J75" s="1">
+        <v>0</v>
+      </c>
+      <c r="K75" s="1">
         <v>100</v>
       </c>
-      <c r="L75" s="1">
-        <v>0</v>
-      </c>
       <c r="M75" s="1">
+        <v>0</v>
+      </c>
+      <c r="N75" s="1">
         <v>15</v>
       </c>
-      <c r="N75" s="1">
-        <v>1</v>
-      </c>
       <c r="O75" s="1">
+        <v>1</v>
+      </c>
+      <c r="P75" s="1">
         <v>3</v>
       </c>
-      <c r="P75" s="1">
+      <c r="Q75" s="1">
         <v>9999</v>
       </c>
-      <c r="Q75" s="1">
-        <v>0</v>
-      </c>
       <c r="R75" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S75" s="1">
-        <v>0</v>
-      </c>
-      <c r="U75" s="1">
-        <v>0</v>
-      </c>
-      <c r="V75" s="1" t="s">
-        <v>70</v>
+        <v>1</v>
+      </c>
+      <c r="T75" s="1">
+        <v>0</v>
+      </c>
+      <c r="V75" s="1">
+        <v>0</v>
       </c>
       <c r="W75" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="X75" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="X75" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="Y75" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z75" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA75" s="1">
         <v>0</v>
       </c>
       <c r="AB75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="1">
         <v>100</v>
       </c>
-      <c r="AC75" s="1">
-        <v>0</v>
-      </c>
       <c r="AD75" s="1">
         <v>0</v>
       </c>
@@ -8868,14 +9072,17 @@
       <c r="AH75" s="1">
         <v>0</v>
       </c>
-      <c r="AJ75" s="1">
-        <v>50</v>
+      <c r="AI75" s="1">
+        <v>0</v>
       </c>
       <c r="AK75" s="1">
         <v>50</v>
       </c>
+      <c r="AL75" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="76" s="1" customFormat="1" spans="3:37">
+    <row r="76" s="1" customFormat="1" spans="3:38">
       <c r="C76" s="1">
         <v>13005</v>
       </c>
@@ -8886,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H76" s="1">
         <v>5</v>
@@ -8898,47 +9105,47 @@
         <v>0</v>
       </c>
       <c r="J76" s="1">
-        <v>50</v>
-      </c>
-      <c r="L76" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="K76" s="1">
+        <v>50</v>
       </c>
       <c r="M76" s="1">
+        <v>0</v>
+      </c>
+      <c r="N76" s="1">
         <v>30</v>
       </c>
-      <c r="N76" s="1">
-        <v>1</v>
-      </c>
       <c r="O76" s="1">
+        <v>1</v>
+      </c>
+      <c r="P76" s="1">
         <v>3</v>
       </c>
-      <c r="P76" s="1">
+      <c r="Q76" s="1">
         <v>9999</v>
       </c>
-      <c r="Q76" s="1">
-        <v>0</v>
-      </c>
       <c r="R76" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S76" s="1">
-        <v>0</v>
-      </c>
-      <c r="U76" s="1">
-        <v>0</v>
-      </c>
-      <c r="V76" s="1" t="s">
-        <v>70</v>
+        <v>1</v>
+      </c>
+      <c r="T76" s="1">
+        <v>0</v>
+      </c>
+      <c r="V76" s="1">
+        <v>0</v>
       </c>
       <c r="W76" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="X76" s="1">
+        <v>72</v>
+      </c>
+      <c r="X76" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y76" s="1">
         <v>30</v>
       </c>
-      <c r="Y76" s="1">
-        <v>0</v>
-      </c>
       <c r="Z76" s="1">
         <v>0</v>
       </c>
@@ -8946,11 +9153,11 @@
         <v>0</v>
       </c>
       <c r="AB76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC76" s="1">
         <v>20</v>
       </c>
-      <c r="AC76" s="1">
-        <v>0</v>
-      </c>
       <c r="AD76" s="1">
         <v>0</v>
       </c>
@@ -8966,15 +9173,18 @@
       <c r="AH76" s="1">
         <v>0</v>
       </c>
-      <c r="AI76" s="7"/>
-      <c r="AJ76" s="1">
-        <v>50</v>
-      </c>
+      <c r="AI76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ76" s="7"/>
       <c r="AK76" s="1">
         <v>50</v>
       </c>
+      <c r="AL76" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="77" s="1" customFormat="1" spans="3:37">
+    <row r="77" s="1" customFormat="1" spans="3:38">
       <c r="C77" s="1">
         <v>13006</v>
       </c>
@@ -8985,10 +9195,10 @@
         <v>0</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H77" s="1">
         <v>6</v>
@@ -8997,43 +9207,43 @@
         <v>0</v>
       </c>
       <c r="J77" s="1">
+        <v>0</v>
+      </c>
+      <c r="K77" s="1">
         <v>10</v>
       </c>
-      <c r="L77" s="1">
-        <v>0</v>
-      </c>
       <c r="M77" s="1">
         <v>0</v>
       </c>
       <c r="N77" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O77" s="1">
+        <v>1</v>
+      </c>
+      <c r="P77" s="1">
         <v>3</v>
       </c>
-      <c r="P77" s="1">
+      <c r="Q77" s="1">
         <v>9999</v>
       </c>
-      <c r="Q77" s="1">
-        <v>0</v>
-      </c>
       <c r="R77" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S77" s="1">
-        <v>0</v>
-      </c>
-      <c r="U77" s="1">
+        <v>1</v>
+      </c>
+      <c r="T77" s="1">
+        <v>0</v>
+      </c>
+      <c r="V77" s="1">
         <v>3</v>
       </c>
-      <c r="V77" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="W77" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="X77" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="X77" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="Y77" s="1">
         <v>0</v>
@@ -9045,10 +9255,10 @@
         <v>0</v>
       </c>
       <c r="AB77" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AC77" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AD77" s="1">
         <v>0</v>
@@ -9065,14 +9275,17 @@
       <c r="AH77" s="1">
         <v>0</v>
       </c>
-      <c r="AJ77" s="1">
-        <v>50</v>
+      <c r="AI77" s="1">
+        <v>0</v>
       </c>
       <c r="AK77" s="1">
         <v>50</v>
       </c>
+      <c r="AL77" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="78" s="1" customFormat="1" spans="3:37">
+    <row r="78" s="1" customFormat="1" spans="3:38">
       <c r="C78" s="1">
         <v>13007</v>
       </c>
@@ -9083,10 +9296,10 @@
         <v>0</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H78" s="1">
         <v>2</v>
@@ -9095,59 +9308,59 @@
         <v>0</v>
       </c>
       <c r="J78" s="1">
+        <v>0</v>
+      </c>
+      <c r="K78" s="1">
         <v>100</v>
       </c>
-      <c r="L78" s="1">
-        <v>0</v>
-      </c>
       <c r="M78" s="1">
+        <v>0</v>
+      </c>
+      <c r="N78" s="1">
         <v>15</v>
       </c>
-      <c r="N78" s="1">
-        <v>1</v>
-      </c>
       <c r="O78" s="1">
+        <v>1</v>
+      </c>
+      <c r="P78" s="1">
         <v>3</v>
       </c>
-      <c r="P78" s="1">
+      <c r="Q78" s="1">
         <v>9999</v>
       </c>
-      <c r="Q78" s="1">
-        <v>0</v>
-      </c>
       <c r="R78" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S78" s="1">
-        <v>0</v>
-      </c>
-      <c r="U78" s="1">
+        <v>1</v>
+      </c>
+      <c r="T78" s="1">
+        <v>0</v>
+      </c>
+      <c r="V78" s="1">
         <v>2</v>
       </c>
-      <c r="V78" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="W78" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="X78" s="1">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="X78" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="Y78" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z78" s="1">
         <v>2</v>
       </c>
-      <c r="Z78" s="1">
-        <v>0</v>
-      </c>
       <c r="AA78" s="1">
         <v>0</v>
       </c>
       <c r="AB78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC78" s="1">
         <v>120</v>
       </c>
-      <c r="AC78" s="1">
-        <v>0</v>
-      </c>
       <c r="AD78" s="1">
         <v>0</v>
       </c>
@@ -9163,25 +9376,28 @@
       <c r="AH78" s="1">
         <v>0</v>
       </c>
-      <c r="AJ78" s="1">
-        <v>50</v>
+      <c r="AI78" s="1">
+        <v>0</v>
       </c>
       <c r="AK78" s="1">
         <v>50</v>
       </c>
+      <c r="AL78" s="1">
+        <v>50</v>
+      </c>
     </row>
-    <row r="79" s="1" customFormat="1" spans="6:20">
+    <row r="79" s="1" customFormat="1" spans="6:21">
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
-      <c r="K79" s="2"/>
       <c r="L79" s="2"/>
-      <c r="P79" s="2"/>
+      <c r="M79" s="2"/>
       <c r="Q79" s="2"/>
       <c r="R79" s="2"/>
       <c r="S79" s="2"/>
       <c r="T79" s="2"/>
+      <c r="U79" s="2"/>
     </row>
-    <row r="80" s="1" customFormat="1" spans="3:37">
+    <row r="80" s="1" customFormat="1" spans="3:38">
       <c r="C80" s="1">
         <v>21002</v>
       </c>
@@ -9192,77 +9408,77 @@
         <v>0</v>
       </c>
       <c r="F80" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H80" s="1">
+        <v>1</v>
+      </c>
+      <c r="I80" s="1">
+        <v>0</v>
+      </c>
+      <c r="J80" s="1">
+        <v>0</v>
+      </c>
+      <c r="K80" s="1">
+        <v>10</v>
+      </c>
+      <c r="M80" s="1">
+        <v>0</v>
+      </c>
+      <c r="N80" s="1">
+        <v>0</v>
+      </c>
+      <c r="O80" s="1">
+        <v>2</v>
+      </c>
+      <c r="P80" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q80" s="1">
+        <v>9999</v>
+      </c>
+      <c r="R80" s="1">
+        <v>0</v>
+      </c>
+      <c r="S80" s="1">
+        <v>1</v>
+      </c>
+      <c r="T80" s="1">
+        <v>0</v>
+      </c>
+      <c r="V80" s="1">
+        <v>2</v>
+      </c>
+      <c r="W80" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G80" s="2" t="s">
+      <c r="X80" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="H80" s="1">
-        <v>1</v>
-      </c>
-      <c r="I80" s="1">
-        <v>0</v>
-      </c>
-      <c r="J80" s="1">
-        <v>10</v>
-      </c>
-      <c r="L80" s="1">
-        <v>0</v>
-      </c>
-      <c r="M80" s="1">
-        <v>0</v>
-      </c>
-      <c r="N80" s="1">
+      <c r="Y80" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z80" s="1">
         <v>2</v>
       </c>
-      <c r="O80" s="1">
-        <v>1</v>
-      </c>
-      <c r="P80" s="1">
-        <v>9999</v>
-      </c>
-      <c r="Q80" s="1">
-        <v>0</v>
-      </c>
-      <c r="R80" s="1">
-        <v>1</v>
-      </c>
-      <c r="S80" s="1">
-        <v>0</v>
-      </c>
-      <c r="U80" s="1">
-        <v>2</v>
-      </c>
-      <c r="V80" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="W80" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="X80" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y80" s="1">
-        <v>2</v>
-      </c>
-      <c r="Z80" s="1">
-        <v>0</v>
-      </c>
       <c r="AA80" s="1">
         <v>0</v>
       </c>
       <c r="AB80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC80" s="1">
         <v>150</v>
       </c>
-      <c r="AC80" s="1">
-        <v>0</v>
-      </c>
       <c r="AD80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE80" s="1">
         <v>20</v>
       </c>
-      <c r="AE80" s="1">
-        <v>0</v>
-      </c>
       <c r="AF80" s="1">
         <v>0</v>
       </c>
@@ -9272,19 +9488,22 @@
       <c r="AH80" s="1">
         <v>0</v>
       </c>
-      <c r="AI80" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="AJ80" s="1">
-        <v>50</v>
+      <c r="AI80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ80" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="AK80" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL80" s="1">
         <v>50</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:M5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:N5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -298,7 +298,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="202">
   <si>
     <t>_ID</t>
   </si>
@@ -835,9 +835,6 @@
   </si>
   <si>
     <t>召唤白虎</t>
-  </si>
-  <si>
-    <t>召唤一个白虎，继承人物所有属性，并且自身拥有100%无视防御，攻击，防御，血量为人物的1000%</t>
   </si>
   <si>
     <t>定身指环</t>
@@ -6104,28 +6101,28 @@
         <v>3012</v>
       </c>
       <c r="E43" s="1">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="G43" s="2" t="s">
-        <v>172</v>
+      <c r="G43" s="1" t="s">
+        <v>178</v>
       </c>
       <c r="H43" s="1">
         <v>2</v>
       </c>
       <c r="I43" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J43" s="1">
         <v>0</v>
       </c>
       <c r="K43" s="1">
-        <v>10</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>179</v>
+        <v>100</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>173</v>
       </c>
       <c r="M43" s="1">
         <v>0</v>
@@ -6134,29 +6131,28 @@
         <v>30</v>
       </c>
       <c r="O43" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P43" s="1">
         <v>3</v>
       </c>
       <c r="Q43" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R43" s="1">
         <v>1</v>
       </c>
       <c r="S43" s="1">
-        <f t="shared" si="2"/>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="T43" s="1">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="U43" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V43" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W43" s="1" t="s">
         <v>85</v>
@@ -6165,22 +6161,22 @@
         <v>91</v>
       </c>
       <c r="Y43" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z43" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AA43" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB43" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC43" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="AD43" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE43" s="1">
         <v>0</v>
@@ -6201,7 +6197,7 @@
         <v>50</v>
       </c>
       <c r="AL43" s="1">
-        <v>0</v>
+        <v>4006</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" spans="6:7">
@@ -6219,10 +6215,10 @@
         <v>0</v>
       </c>
       <c r="F45" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="G45" s="5" t="s">
         <v>180</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>181</v>
       </c>
       <c r="H45" s="1">
         <v>4001</v>
@@ -6237,7 +6233,7 @@
         <v>-100</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M45" s="1">
         <v>0</v>
@@ -6309,7 +6305,7 @@
         <v>0</v>
       </c>
       <c r="AJ45" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AK45" s="1">
         <v>99999</v>
@@ -6326,10 +6322,10 @@
         <v>0</v>
       </c>
       <c r="F46" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="G46" s="5" t="s">
         <v>184</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>185</v>
       </c>
       <c r="H46" s="1">
         <v>4002</v>
@@ -6344,7 +6340,7 @@
         <v>200</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M46" s="1">
         <v>0</v>
@@ -6431,10 +6427,10 @@
         <v>0</v>
       </c>
       <c r="F47" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="G47" s="5" t="s">
         <v>187</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>188</v>
       </c>
       <c r="H47" s="1">
         <v>4003</v>
@@ -6449,7 +6445,7 @@
         <v>-1</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M47" s="1">
         <v>0</v>
@@ -6521,7 +6517,7 @@
         <v>0</v>
       </c>
       <c r="AJ47" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AK47" s="1">
         <v>99999</v>
@@ -6542,10 +6538,10 @@
         <v>0</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H49" s="1">
         <v>9</v>
@@ -6643,10 +6639,10 @@
         <v>0</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H50" s="1">
         <v>9</v>
@@ -6745,11 +6741,11 @@
         <v>0</v>
       </c>
       <c r="F52" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G52" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="G52" s="2" t="s">
-        <v>194</v>
-      </c>
       <c r="H52" s="1">
         <v>1</v>
       </c>
@@ -6763,7 +6759,7 @@
         <v>1</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M52" s="1">
         <v>0</v>
@@ -6849,10 +6845,10 @@
         <v>0</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H53" s="2">
         <v>4</v>
@@ -6867,7 +6863,7 @@
         <v>10</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M53" s="1">
         <v>0</v>
@@ -6955,10 +6951,10 @@
         <v>0</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H54" s="2">
         <v>1</v>
@@ -6973,7 +6969,7 @@
         <v>1</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M54" s="1">
         <v>0</v>
@@ -7061,10 +7057,10 @@
         <v>0</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H55" s="2">
         <v>4</v>
@@ -7079,7 +7075,7 @@
         <v>10</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="M55" s="1">
         <v>0</v>
@@ -7110,7 +7106,7 @@
         <v>3</v>
       </c>
       <c r="W55" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="X55" s="2" t="s">
         <v>91</v>
@@ -7166,7 +7162,7 @@
         <v>0</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>75</v>
@@ -7184,7 +7180,7 @@
         <v>10</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M56" s="1">
         <v>0</v>
@@ -7657,7 +7653,7 @@
         <v>0</v>
       </c>
       <c r="AJ61" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AK61" s="1">
         <v>50</v>
@@ -9492,7 +9488,7 @@
         <v>0</v>
       </c>
       <c r="AJ80" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AK80" s="1">
         <v>50</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -298,7 +298,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="204">
   <si>
     <t>_ID</t>
   </si>
@@ -507,6 +507,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>double</t>
+  </si>
+  <si>
     <t>string[]</t>
   </si>
   <si>
@@ -639,7 +642,7 @@
     <t>剑二十三</t>
   </si>
   <si>
-    <t>对{0}个敌人，造成流光剑法*{1}%的伤害</t>
+    <t>对{0}个敌人，造成流光剑法*{1}%的伤害，并且计算流光剑法的最远距离伤害</t>
   </si>
   <si>
     <t>火球术</t>
@@ -835,6 +838,9 @@
   </si>
   <si>
     <t>召唤白虎</t>
+  </si>
+  <si>
+    <t>召唤{0}只白虎战斗，攻击和生命为人物的{1}%,其他所有属性为100%</t>
   </si>
   <si>
     <t>定身指环</t>
@@ -2206,7 +2212,7 @@
         <v>67</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="S5" s="3" t="s">
         <v>67</v>
@@ -2260,7 +2266,7 @@
         <v>67</v>
       </c>
       <c r="AJ5" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AK5" s="3" t="s">
         <v>67</v>
@@ -2280,10 +2286,10 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
@@ -2298,7 +2304,7 @@
         <v>10</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M6" s="1">
         <v>0</v>
@@ -2332,10 +2338,10 @@
         <v>1</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y6" s="1">
         <v>0</v>
@@ -2388,10 +2394,10 @@
         <v>2</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H7" s="1">
         <v>1</v>
@@ -2406,7 +2412,7 @@
         <v>10</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M7" s="1">
         <v>0</v>
@@ -2440,10 +2446,10 @@
         <v>2</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y7" s="1">
         <v>0</v>
@@ -2496,10 +2502,10 @@
         <v>3</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H8" s="1">
         <v>1</v>
@@ -2514,7 +2520,7 @@
         <v>10</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M8" s="1">
         <v>0</v>
@@ -2548,10 +2554,10 @@
         <v>1</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X8" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Y8" s="1">
         <v>0</v>
@@ -2587,7 +2593,7 @@
         <v>0</v>
       </c>
       <c r="AJ8" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AK8" s="1">
         <v>50</v>
@@ -2607,10 +2613,10 @@
         <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H9" s="1">
         <v>7</v>
@@ -2625,7 +2631,7 @@
         <v>10</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M9" s="1">
         <v>0</v>
@@ -2659,10 +2665,10 @@
         <v>5</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X9" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Y9" s="1">
         <v>2</v>
@@ -2698,7 +2704,7 @@
         <v>0</v>
       </c>
       <c r="AJ9" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AK9" s="1">
         <v>50</v>
@@ -2718,10 +2724,10 @@
         <v>5</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H10" s="1">
         <v>5</v>
@@ -2736,7 +2742,7 @@
         <v>50</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M10" s="1">
         <v>0</v>
@@ -2770,10 +2776,10 @@
         <v>0</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y10" s="1">
         <v>30</v>
@@ -2809,7 +2815,7 @@
         <v>0</v>
       </c>
       <c r="AJ10" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AK10" s="1">
         <v>50</v>
@@ -2829,10 +2835,10 @@
         <v>6</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H11" s="1">
         <v>6</v>
@@ -2847,7 +2853,7 @@
         <v>10</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M11" s="1">
         <v>0</v>
@@ -2881,10 +2887,10 @@
         <v>0</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X11" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Y11" s="1">
         <v>0</v>
@@ -2937,10 +2943,10 @@
         <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H12" s="1">
         <v>1</v>
@@ -2955,7 +2961,7 @@
         <v>10</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M12" s="1">
         <v>0</v>
@@ -2989,10 +2995,10 @@
         <v>1</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X12" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y12" s="1">
         <v>0</v>
@@ -3028,7 +3034,7 @@
         <v>0</v>
       </c>
       <c r="AJ12" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK12" s="1">
         <v>50</v>
@@ -3048,10 +3054,10 @@
         <v>8</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H13" s="1">
         <v>1008</v>
@@ -3066,7 +3072,7 @@
         <v>200</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M13" s="1">
         <v>0</v>
@@ -3100,10 +3106,10 @@
         <v>0</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X13" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Y13" s="1">
         <v>20</v>
@@ -3139,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="AJ13" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK13" s="1">
         <v>50</v>
@@ -3159,10 +3165,10 @@
         <v>9</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H14" s="1">
         <v>1</v>
@@ -3177,7 +3183,7 @@
         <v>10</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M14" s="1">
         <v>0</v>
@@ -3211,10 +3217,10 @@
         <v>5</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y14" s="1">
         <v>0</v>
@@ -3250,7 +3256,7 @@
         <v>0</v>
       </c>
       <c r="AJ14" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK14" s="1">
         <v>50</v>
@@ -3270,10 +3276,10 @@
         <v>10</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H15" s="1">
         <v>1</v>
@@ -3288,7 +3294,7 @@
         <v>10</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M15" s="1">
         <v>20</v>
@@ -3321,10 +3327,10 @@
         <v>2</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X15" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y15" s="1">
         <v>0</v>
@@ -3377,10 +3383,10 @@
         <v>11</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H16" s="1">
         <v>8</v>
@@ -3395,7 +3401,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M16" s="1">
         <v>0</v>
@@ -3429,10 +3435,10 @@
         <v>3</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X16" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y16" s="1">
         <v>15</v>
@@ -3485,10 +3491,10 @@
         <v>12</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H17" s="1">
         <v>1</v>
@@ -3503,7 +3509,7 @@
         <v>10</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M17" s="1">
         <v>0</v>
@@ -3521,11 +3527,10 @@
         <v>10</v>
       </c>
       <c r="R17" s="1">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="S17" s="1">
-        <f t="shared" si="0"/>
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="T17" s="1">
         <v>500</v>
@@ -3537,10 +3542,10 @@
         <v>3</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X17" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y17" s="1">
         <v>0</v>
@@ -3596,10 +3601,10 @@
         <v>1</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H19" s="1">
         <v>1</v>
@@ -3614,7 +3619,7 @@
         <v>10</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M19" s="1">
         <v>0</v>
@@ -3648,10 +3653,10 @@
         <v>2</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X19" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y19" s="1">
         <v>0</v>
@@ -3704,10 +3709,10 @@
         <v>2</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H20" s="1">
         <v>1</v>
@@ -3722,7 +3727,7 @@
         <v>10</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M20" s="1">
         <v>0</v>
@@ -3756,10 +3761,10 @@
         <v>3</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X20" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y20" s="1">
         <v>0</v>
@@ -3812,10 +3817,10 @@
         <v>3</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H21" s="1">
         <v>3</v>
@@ -3830,7 +3835,7 @@
         <v>10</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M21" s="1">
         <v>0</v>
@@ -3864,10 +3869,10 @@
         <v>3</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X21" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y21" s="1">
         <v>10</v>
@@ -3920,10 +3925,10 @@
         <v>4</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H22" s="1">
         <v>1</v>
@@ -3938,7 +3943,7 @@
         <v>10</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M22" s="1">
         <v>0</v>
@@ -3972,10 +3977,10 @@
         <v>4</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X22" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y22" s="1">
         <v>0</v>
@@ -4011,7 +4016,7 @@
         <v>0</v>
       </c>
       <c r="AJ22" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AK22" s="1">
         <v>50</v>
@@ -4031,10 +4036,10 @@
         <v>5</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H23" s="1">
         <v>5</v>
@@ -4049,7 +4054,7 @@
         <v>50</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M23" s="1">
         <v>0</v>
@@ -4083,10 +4088,10 @@
         <v>0</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X23" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y23" s="1">
         <v>30</v>
@@ -4122,7 +4127,7 @@
         <v>0</v>
       </c>
       <c r="AJ23" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AK23" s="1">
         <v>50</v>
@@ -4142,10 +4147,10 @@
         <v>6</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H24" s="1">
         <v>6</v>
@@ -4160,7 +4165,7 @@
         <v>10</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M24" s="1">
         <v>0</v>
@@ -4194,10 +4199,10 @@
         <v>0</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X24" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Y24" s="1">
         <v>0</v>
@@ -4250,10 +4255,10 @@
         <v>7</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H25" s="1">
         <v>1</v>
@@ -4268,7 +4273,7 @@
         <v>10</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M25" s="1">
         <v>0</v>
@@ -4302,10 +4307,10 @@
         <v>5</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X25" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y25" s="1">
         <v>0</v>
@@ -4341,7 +4346,7 @@
         <v>0</v>
       </c>
       <c r="AJ25" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AK25" s="1">
         <v>50</v>
@@ -4361,10 +4366,10 @@
         <v>8</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H26" s="1">
         <v>2008</v>
@@ -4379,7 +4384,7 @@
         <v>200</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M26" s="1">
         <v>0</v>
@@ -4413,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X26" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Y26" s="1">
         <v>0</v>
@@ -4452,7 +4457,7 @@
         <v>0</v>
       </c>
       <c r="AJ26" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK26" s="1">
         <v>50</v>
@@ -4472,10 +4477,10 @@
         <v>9</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H27" s="1">
         <v>3</v>
@@ -4490,7 +4495,7 @@
         <v>10</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M27" s="1">
         <v>0</v>
@@ -4524,10 +4529,10 @@
         <v>3</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X27" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y27" s="1">
         <v>10</v>
@@ -4563,7 +4568,7 @@
         <v>0</v>
       </c>
       <c r="AJ27" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK27" s="1">
         <v>50</v>
@@ -4583,10 +4588,10 @@
         <v>10</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H28" s="1">
         <v>2010</v>
@@ -4601,7 +4606,7 @@
         <v>100</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M28" s="1">
         <v>0</v>
@@ -4635,10 +4640,10 @@
         <v>3</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X28" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y28" s="1">
         <v>15</v>
@@ -4691,10 +4696,10 @@
         <v>11</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H29" s="1">
         <v>8</v>
@@ -4709,7 +4714,7 @@
         <v>0</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M29" s="1">
         <v>0</v>
@@ -4743,10 +4748,10 @@
         <v>3</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X29" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y29" s="1">
         <v>15</v>
@@ -4799,10 +4804,10 @@
         <v>12</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H30" s="1">
         <v>8</v>
@@ -4817,7 +4822,7 @@
         <v>10</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M30" s="1">
         <v>0</v>
@@ -4835,11 +4840,10 @@
         <v>1</v>
       </c>
       <c r="R30" s="1">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="S30" s="1">
-        <f t="shared" si="1"/>
-        <v>5</v>
+        <v>500</v>
       </c>
       <c r="T30" s="1">
         <v>5</v>
@@ -4851,10 +4855,10 @@
         <v>3</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X30" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y30" s="1">
         <v>300</v>
@@ -4910,10 +4914,10 @@
         <v>1</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H32" s="1">
         <v>4</v>
@@ -4928,7 +4932,7 @@
         <v>20</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M32" s="1">
         <v>0</v>
@@ -4961,10 +4965,10 @@
         <v>5</v>
       </c>
       <c r="W32" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X32" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y32" s="1">
         <v>0</v>
@@ -5017,10 +5021,10 @@
         <v>2</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H33" s="1">
         <v>1</v>
@@ -5035,7 +5039,7 @@
         <v>10</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M33" s="1">
         <v>0</v>
@@ -5069,10 +5073,10 @@
         <v>3</v>
       </c>
       <c r="W33" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X33" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y33" s="1">
         <v>0</v>
@@ -5125,10 +5129,10 @@
         <v>3</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H34" s="1">
         <v>1</v>
@@ -5143,7 +5147,7 @@
         <v>10</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M34" s="1">
         <v>0</v>
@@ -5177,10 +5181,10 @@
         <v>2</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X34" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y34" s="1">
         <v>0</v>
@@ -5216,7 +5220,7 @@
         <v>0</v>
       </c>
       <c r="AJ34" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AK34" s="1">
         <v>50</v>
@@ -5236,10 +5240,10 @@
         <v>4</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H35" s="1">
         <v>2</v>
@@ -5254,7 +5258,7 @@
         <v>100</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M35" s="1">
         <v>0</v>
@@ -5288,10 +5292,10 @@
         <v>0</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X35" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Y35" s="1">
         <v>0</v>
@@ -5344,10 +5348,10 @@
         <v>5</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H36" s="1">
         <v>5</v>
@@ -5362,7 +5366,7 @@
         <v>50</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M36" s="1">
         <v>0</v>
@@ -5396,10 +5400,10 @@
         <v>0</v>
       </c>
       <c r="W36" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X36" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y36" s="1">
         <v>30</v>
@@ -5435,7 +5439,7 @@
         <v>0</v>
       </c>
       <c r="AJ36" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AK36" s="1">
         <v>50</v>
@@ -5455,10 +5459,10 @@
         <v>6</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H37" s="1">
         <v>6</v>
@@ -5473,7 +5477,7 @@
         <v>10</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M37" s="1">
         <v>0</v>
@@ -5507,10 +5511,10 @@
         <v>3</v>
       </c>
       <c r="W37" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X37" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Y37" s="1">
         <v>0</v>
@@ -5563,10 +5567,10 @@
         <v>7</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H38" s="1">
         <v>2</v>
@@ -5581,7 +5585,7 @@
         <v>100</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M38" s="1">
         <v>0</v>
@@ -5615,10 +5619,10 @@
         <v>2</v>
       </c>
       <c r="W38" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X38" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y38" s="1">
         <v>0</v>
@@ -5671,10 +5675,10 @@
         <v>8</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H39" s="1">
         <v>3008</v>
@@ -5689,7 +5693,7 @@
         <v>200</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M39" s="1">
         <v>0</v>
@@ -5723,10 +5727,10 @@
         <v>0</v>
       </c>
       <c r="W39" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X39" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Y39" s="1">
         <v>5</v>
@@ -5762,7 +5766,7 @@
         <v>0</v>
       </c>
       <c r="AJ39" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AK39" s="1">
         <v>50</v>
@@ -5782,10 +5786,10 @@
         <v>9</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H40" s="1">
         <v>2</v>
@@ -5800,7 +5804,7 @@
         <v>100</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M40" s="1">
         <v>0</v>
@@ -5833,10 +5837,10 @@
         <v>2</v>
       </c>
       <c r="W40" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X40" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y40" s="1">
         <v>0</v>
@@ -5889,10 +5893,10 @@
         <v>10</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H41" s="1">
         <v>8</v>
@@ -5907,7 +5911,7 @@
         <v>100</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M41" s="1">
         <v>0</v>
@@ -5940,10 +5944,10 @@
         <v>0</v>
       </c>
       <c r="W41" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X41" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y41" s="1">
         <v>0</v>
@@ -5996,10 +6000,10 @@
         <v>11</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H42" s="1">
         <v>8</v>
@@ -6014,7 +6018,7 @@
         <v>0</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M42" s="1">
         <v>0</v>
@@ -6048,10 +6052,10 @@
         <v>3</v>
       </c>
       <c r="W42" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X42" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y42" s="1">
         <v>15</v>
@@ -6104,10 +6108,10 @@
         <v>9</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H43" s="1">
         <v>2</v>
@@ -6122,7 +6126,7 @@
         <v>100</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="M43" s="1">
         <v>0</v>
@@ -6140,7 +6144,7 @@
         <v>1</v>
       </c>
       <c r="R43" s="1">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="S43" s="1">
         <v>200</v>
@@ -6155,10 +6159,10 @@
         <v>2</v>
       </c>
       <c r="W43" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X43" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y43" s="1">
         <v>0</v>
@@ -6215,10 +6219,10 @@
         <v>0</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H45" s="1">
         <v>4001</v>
@@ -6233,7 +6237,7 @@
         <v>-100</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="M45" s="1">
         <v>0</v>
@@ -6266,10 +6270,10 @@
         <v>0</v>
       </c>
       <c r="W45" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X45" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y45" s="1">
         <v>2</v>
@@ -6305,7 +6309,7 @@
         <v>0</v>
       </c>
       <c r="AJ45" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AK45" s="1">
         <v>99999</v>
@@ -6322,10 +6326,10 @@
         <v>0</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H46" s="1">
         <v>4002</v>
@@ -6340,7 +6344,7 @@
         <v>200</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M46" s="1">
         <v>0</v>
@@ -6373,10 +6377,10 @@
         <v>0</v>
       </c>
       <c r="W46" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X46" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y46" s="1">
         <v>0</v>
@@ -6427,10 +6431,10 @@
         <v>0</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H47" s="1">
         <v>4003</v>
@@ -6445,7 +6449,7 @@
         <v>-1</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="M47" s="1">
         <v>0</v>
@@ -6478,10 +6482,10 @@
         <v>0</v>
       </c>
       <c r="W47" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X47" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y47" s="1">
         <v>0</v>
@@ -6517,7 +6521,7 @@
         <v>0</v>
       </c>
       <c r="AJ47" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AK47" s="1">
         <v>99999</v>
@@ -6538,10 +6542,10 @@
         <v>0</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H49" s="1">
         <v>9</v>
@@ -6583,10 +6587,10 @@
         <v>1</v>
       </c>
       <c r="W49" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X49" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y49" s="1">
         <v>0</v>
@@ -6639,10 +6643,10 @@
         <v>0</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H50" s="1">
         <v>9</v>
@@ -6684,10 +6688,10 @@
         <v>2</v>
       </c>
       <c r="W50" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X50" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y50" s="1">
         <v>0</v>
@@ -6741,10 +6745,10 @@
         <v>0</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H52" s="1">
         <v>1</v>
@@ -6759,7 +6763,7 @@
         <v>1</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M52" s="1">
         <v>0</v>
@@ -6789,10 +6793,10 @@
         <v>3</v>
       </c>
       <c r="W52" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X52" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y52" s="1">
         <v>0</v>
@@ -6845,10 +6849,10 @@
         <v>0</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H53" s="2">
         <v>4</v>
@@ -6863,7 +6867,7 @@
         <v>10</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="M53" s="1">
         <v>0</v>
@@ -6894,10 +6898,10 @@
         <v>0</v>
       </c>
       <c r="W53" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X53" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y53" s="2">
         <v>0</v>
@@ -6951,10 +6955,10 @@
         <v>0</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H54" s="2">
         <v>1</v>
@@ -6969,7 +6973,7 @@
         <v>1</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M54" s="1">
         <v>0</v>
@@ -7000,10 +7004,10 @@
         <v>0</v>
       </c>
       <c r="W54" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X54" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Y54" s="1">
         <v>0</v>
@@ -7057,10 +7061,10 @@
         <v>0</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H55" s="2">
         <v>4</v>
@@ -7075,7 +7079,7 @@
         <v>10</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="M55" s="1">
         <v>0</v>
@@ -7106,10 +7110,10 @@
         <v>3</v>
       </c>
       <c r="W55" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="X55" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y55" s="2">
         <v>0</v>
@@ -7162,10 +7166,10 @@
         <v>0</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H56" s="1">
         <v>1</v>
@@ -7180,7 +7184,7 @@
         <v>10</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M56" s="1">
         <v>0</v>
@@ -7210,10 +7214,10 @@
         <v>2</v>
       </c>
       <c r="W56" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X56" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y56" s="1">
         <v>0</v>
@@ -7266,10 +7270,10 @@
         <v>0</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H58" s="1">
         <v>1</v>
@@ -7311,10 +7315,10 @@
         <v>1</v>
       </c>
       <c r="W58" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X58" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y58" s="1">
         <v>0</v>
@@ -7367,10 +7371,10 @@
         <v>0</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H59" s="1">
         <v>1</v>
@@ -7412,10 +7416,10 @@
         <v>2</v>
       </c>
       <c r="W59" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X59" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y59" s="1">
         <v>0</v>
@@ -7468,10 +7472,10 @@
         <v>0</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H60" s="1">
         <v>1</v>
@@ -7513,10 +7517,10 @@
         <v>1</v>
       </c>
       <c r="W60" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X60" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Y60" s="1">
         <v>0</v>
@@ -7569,10 +7573,10 @@
         <v>0</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H61" s="1">
         <v>7</v>
@@ -7614,10 +7618,10 @@
         <v>4</v>
       </c>
       <c r="W61" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X61" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Y61" s="1">
         <v>2</v>
@@ -7653,7 +7657,7 @@
         <v>0</v>
       </c>
       <c r="AJ61" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AK61" s="1">
         <v>50</v>
@@ -7673,10 +7677,10 @@
         <v>0</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H62" s="1">
         <v>5</v>
@@ -7718,10 +7722,10 @@
         <v>0</v>
       </c>
       <c r="W62" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X62" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y62" s="1">
         <v>30</v>
@@ -7775,10 +7779,10 @@
         <v>0</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H63" s="1">
         <v>6</v>
@@ -7820,10 +7824,10 @@
         <v>0</v>
       </c>
       <c r="W63" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X63" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Y63" s="1">
         <v>0</v>
@@ -7876,10 +7880,10 @@
         <v>0</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H64" s="1">
         <v>1</v>
@@ -7921,10 +7925,10 @@
         <v>1</v>
       </c>
       <c r="W64" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X64" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y64" s="1">
         <v>0</v>
@@ -7977,10 +7981,10 @@
         <v>0</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H65" s="1">
         <v>1</v>
@@ -8022,10 +8026,10 @@
         <v>2</v>
       </c>
       <c r="W65" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X65" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y65" s="1">
         <v>0</v>
@@ -8078,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H66" s="1">
         <v>1</v>
@@ -8123,10 +8127,10 @@
         <v>3</v>
       </c>
       <c r="W66" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X66" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y66" s="1">
         <v>0</v>
@@ -8179,10 +8183,10 @@
         <v>0</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H67" s="1">
         <v>3</v>
@@ -8224,10 +8228,10 @@
         <v>3</v>
       </c>
       <c r="W67" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X67" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y67" s="1">
         <v>5</v>
@@ -8280,10 +8284,10 @@
         <v>0</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H68" s="1">
         <v>1</v>
@@ -8325,10 +8329,10 @@
         <v>4</v>
       </c>
       <c r="W68" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X68" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y68" s="1">
         <v>0</v>
@@ -8381,10 +8385,10 @@
         <v>0</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H69" s="1">
         <v>5</v>
@@ -8426,10 +8430,10 @@
         <v>0</v>
       </c>
       <c r="W69" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X69" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y69" s="1">
         <v>30</v>
@@ -8483,10 +8487,10 @@
         <v>0</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H70" s="1">
         <v>6</v>
@@ -8528,10 +8532,10 @@
         <v>0</v>
       </c>
       <c r="W70" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X70" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Y70" s="1">
         <v>0</v>
@@ -8584,10 +8588,10 @@
         <v>0</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H71" s="1">
         <v>1</v>
@@ -8629,10 +8633,10 @@
         <v>5</v>
       </c>
       <c r="W71" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X71" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y71" s="1">
         <v>0</v>
@@ -8685,10 +8689,10 @@
         <v>0</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H72" s="1">
         <v>4</v>
@@ -8730,10 +8734,10 @@
         <v>0</v>
       </c>
       <c r="W72" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X72" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y72" s="1">
         <v>0</v>
@@ -8786,10 +8790,10 @@
         <v>0</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H73" s="1">
         <v>1</v>
@@ -8831,10 +8835,10 @@
         <v>3</v>
       </c>
       <c r="W73" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X73" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y73" s="1">
         <v>0</v>
@@ -8887,10 +8891,10 @@
         <v>0</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H74" s="1">
         <v>1</v>
@@ -8932,10 +8936,10 @@
         <v>2</v>
       </c>
       <c r="W74" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X74" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y74" s="1">
         <v>0</v>
@@ -8988,10 +8992,10 @@
         <v>0</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H75" s="1">
         <v>2</v>
@@ -9033,10 +9037,10 @@
         <v>0</v>
       </c>
       <c r="W75" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X75" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Y75" s="1">
         <v>0</v>
@@ -9089,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H76" s="1">
         <v>5</v>
@@ -9134,10 +9138,10 @@
         <v>0</v>
       </c>
       <c r="W76" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X76" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y76" s="1">
         <v>30</v>
@@ -9191,10 +9195,10 @@
         <v>0</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H77" s="1">
         <v>6</v>
@@ -9236,10 +9240,10 @@
         <v>3</v>
       </c>
       <c r="W77" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X77" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Y77" s="1">
         <v>0</v>
@@ -9292,10 +9296,10 @@
         <v>0</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H78" s="1">
         <v>2</v>
@@ -9337,10 +9341,10 @@
         <v>2</v>
       </c>
       <c r="W78" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X78" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y78" s="1">
         <v>0</v>
@@ -9404,10 +9408,10 @@
         <v>0</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H80" s="1">
         <v>1</v>
@@ -9449,10 +9453,10 @@
         <v>2</v>
       </c>
       <c r="W80" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X80" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y80" s="1">
         <v>0</v>
@@ -9488,7 +9492,7 @@
         <v>0</v>
       </c>
       <c r="AJ80" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AK80" s="1">
         <v>50</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -298,7 +298,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="206">
   <si>
     <t>_ID</t>
   </si>
@@ -874,6 +874,12 @@
   </si>
   <si>
     <t>"18,3,0,100"</t>
+  </si>
+  <si>
+    <t>飓风破</t>
+  </si>
+  <si>
+    <t>对{3}*{4}范围内的敌人造成{1}%道术伤害</t>
   </si>
   <si>
     <t>普攻</t>
@@ -1902,7 +1908,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:AN80"/>
+  <dimension ref="C3:AN81"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.35"/>
   <cols>
     <col min="1" max="1" width="5.6283185840708" style="2" customWidth="1"/>
@@ -6527,126 +6533,133 @@
         <v>99999</v>
       </c>
     </row>
-    <row r="48" s="1" customFormat="1" spans="6:7">
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
+    <row r="48" s="1" customFormat="1" spans="3:38">
+      <c r="C48" s="1">
+        <v>4004</v>
+      </c>
+      <c r="D48" s="1">
+        <v>4004</v>
+      </c>
+      <c r="E48" s="1">
+        <v>7</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H48" s="1">
+        <v>1</v>
+      </c>
+      <c r="I48" s="1">
+        <v>0</v>
+      </c>
+      <c r="J48" s="1">
+        <v>0</v>
+      </c>
+      <c r="K48" s="1">
+        <v>10</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="M48" s="1">
+        <v>0</v>
+      </c>
+      <c r="N48" s="1">
+        <v>0</v>
+      </c>
+      <c r="O48" s="1">
+        <v>2</v>
+      </c>
+      <c r="P48" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="1">
+        <v>1</v>
+      </c>
+      <c r="R48" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="S48" s="1">
+        <v>500</v>
+      </c>
+      <c r="T48" s="1">
+        <v>500</v>
+      </c>
+      <c r="U48" s="1">
+        <v>0</v>
+      </c>
+      <c r="V48" s="1">
+        <v>5</v>
+      </c>
+      <c r="W48" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="X48" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y48" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z48" s="1">
+        <v>5</v>
+      </c>
+      <c r="AA48" s="1">
+        <v>3</v>
+      </c>
+      <c r="AB48" s="1">
+        <v>3</v>
+      </c>
+      <c r="AC48" s="1">
+        <v>500</v>
+      </c>
+      <c r="AD48" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE48" s="1">
+        <v>70</v>
+      </c>
+      <c r="AF48" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG48" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH48" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI48" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ48" s="6"/>
+      <c r="AK48" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL48" s="1">
+        <v>4006</v>
+      </c>
     </row>
-    <row r="49" s="1" customFormat="1" spans="3:38">
-      <c r="C49" s="1">
-        <v>9001</v>
-      </c>
-      <c r="D49" s="1">
-        <v>9001</v>
-      </c>
-      <c r="E49" s="1">
-        <v>0</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="H49" s="1">
-        <v>9</v>
-      </c>
-      <c r="I49" s="1">
-        <v>0</v>
-      </c>
-      <c r="J49" s="1">
-        <v>0</v>
-      </c>
-      <c r="K49" s="1">
-        <v>0</v>
-      </c>
-      <c r="M49" s="1">
-        <v>0</v>
-      </c>
-      <c r="N49" s="1">
-        <v>0</v>
-      </c>
-      <c r="O49" s="1">
-        <v>1</v>
-      </c>
-      <c r="P49" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q49" s="1">
-        <v>0</v>
-      </c>
-      <c r="R49" s="1">
-        <v>0</v>
-      </c>
-      <c r="S49" s="1">
-        <v>1</v>
-      </c>
-      <c r="T49" s="1">
-        <v>0</v>
-      </c>
-      <c r="V49" s="1">
-        <v>1</v>
-      </c>
-      <c r="W49" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="X49" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="Y49" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z49" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA49" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB49" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC49" s="1">
-        <v>100</v>
-      </c>
-      <c r="AD49" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE49" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF49" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG49" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH49" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI49" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK49" s="1">
-        <v>50</v>
-      </c>
-      <c r="AL49" s="1">
-        <v>50</v>
-      </c>
+    <row r="49" s="1" customFormat="1" spans="6:7">
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
     </row>
     <row r="50" s="1" customFormat="1" spans="3:38">
       <c r="C50" s="1">
-        <v>9002</v>
+        <v>9001</v>
       </c>
       <c r="D50" s="1">
-        <v>9002</v>
+        <v>9001</v>
       </c>
       <c r="E50" s="1">
         <v>0</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H50" s="1">
         <v>9</v>
@@ -6685,13 +6698,13 @@
         <v>0</v>
       </c>
       <c r="V50" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W50" s="1" t="s">
         <v>73</v>
       </c>
       <c r="X50" s="1" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="Y50" s="1">
         <v>0</v>
@@ -6733,191 +6746,187 @@
         <v>50</v>
       </c>
     </row>
-    <row r="51" s="1" customFormat="1"/>
-    <row r="52" s="1" customFormat="1" spans="3:38">
-      <c r="C52" s="1">
+    <row r="51" s="1" customFormat="1" spans="3:38">
+      <c r="C51" s="1">
+        <v>9002</v>
+      </c>
+      <c r="D51" s="1">
+        <v>9002</v>
+      </c>
+      <c r="E51" s="1">
+        <v>0</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="H51" s="1">
+        <v>9</v>
+      </c>
+      <c r="I51" s="1">
+        <v>0</v>
+      </c>
+      <c r="J51" s="1">
+        <v>0</v>
+      </c>
+      <c r="K51" s="1">
+        <v>0</v>
+      </c>
+      <c r="M51" s="1">
+        <v>0</v>
+      </c>
+      <c r="N51" s="1">
+        <v>0</v>
+      </c>
+      <c r="O51" s="1">
+        <v>1</v>
+      </c>
+      <c r="P51" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q51" s="1">
+        <v>0</v>
+      </c>
+      <c r="R51" s="1">
+        <v>0</v>
+      </c>
+      <c r="S51" s="1">
+        <v>1</v>
+      </c>
+      <c r="T51" s="1">
+        <v>0</v>
+      </c>
+      <c r="V51" s="1">
+        <v>2</v>
+      </c>
+      <c r="W51" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X51" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y51" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="1">
+        <v>100</v>
+      </c>
+      <c r="AD51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL51" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" s="1" customFormat="1"/>
+    <row r="53" s="1" customFormat="1" spans="3:38">
+      <c r="C53" s="1">
         <v>10001</v>
       </c>
-      <c r="D52" s="1">
+      <c r="D53" s="1">
         <v>10001</v>
       </c>
-      <c r="E52" s="1">
-        <v>0</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="H52" s="1">
-        <v>1</v>
-      </c>
-      <c r="I52" s="1">
-        <v>0</v>
-      </c>
-      <c r="J52" s="1">
-        <v>0</v>
-      </c>
-      <c r="K52" s="1">
-        <v>1</v>
-      </c>
-      <c r="L52" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="M52" s="1">
-        <v>0</v>
-      </c>
-      <c r="N52" s="1">
-        <v>0</v>
-      </c>
-      <c r="O52" s="1">
-        <v>1</v>
-      </c>
-      <c r="P52" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q52" s="1">
-        <v>0</v>
-      </c>
-      <c r="R52" s="1">
-        <v>0</v>
-      </c>
-      <c r="S52" s="1">
-        <v>1</v>
-      </c>
-      <c r="T52" s="1">
-        <v>0</v>
-      </c>
-      <c r="V52" s="1">
+      <c r="E53" s="1">
+        <v>0</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="H53" s="1">
+        <v>1</v>
+      </c>
+      <c r="I53" s="1">
+        <v>0</v>
+      </c>
+      <c r="J53" s="1">
+        <v>0</v>
+      </c>
+      <c r="K53" s="1">
+        <v>1</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="M53" s="1">
+        <v>0</v>
+      </c>
+      <c r="N53" s="1">
+        <v>0</v>
+      </c>
+      <c r="O53" s="1">
+        <v>1</v>
+      </c>
+      <c r="P53" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q53" s="1">
+        <v>0</v>
+      </c>
+      <c r="R53" s="1">
+        <v>0</v>
+      </c>
+      <c r="S53" s="1">
+        <v>1</v>
+      </c>
+      <c r="T53" s="1">
+        <v>0</v>
+      </c>
+      <c r="V53" s="1">
         <v>3</v>
       </c>
-      <c r="W52" s="1" t="s">
+      <c r="W53" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="X52" s="1" t="s">
+      <c r="X53" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="Y52" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z52" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA52" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB52" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC52" s="1">
+      <c r="Y53" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA53" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="1">
         <v>150</v>
       </c>
-      <c r="AD52" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE52" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF52" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG52" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH52" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI52" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK52" s="1">
-        <v>50</v>
-      </c>
-      <c r="AL52" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="53" spans="3:38">
-      <c r="C53" s="2">
-        <v>10002</v>
-      </c>
-      <c r="D53" s="2">
-        <v>10002</v>
-      </c>
-      <c r="E53" s="1">
-        <v>0</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="H53" s="2">
-        <v>4</v>
-      </c>
-      <c r="I53" s="1">
-        <v>0</v>
-      </c>
-      <c r="J53" s="1">
-        <v>0</v>
-      </c>
-      <c r="K53" s="2">
-        <v>10</v>
-      </c>
-      <c r="L53" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="M53" s="1">
-        <v>0</v>
-      </c>
-      <c r="N53" s="2">
-        <v>0</v>
-      </c>
-      <c r="O53" s="1">
-        <v>1</v>
-      </c>
-      <c r="P53" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q53" s="1">
-        <v>0</v>
-      </c>
-      <c r="R53" s="1">
-        <v>0</v>
-      </c>
-      <c r="S53" s="1">
-        <v>1</v>
-      </c>
-      <c r="T53" s="1">
-        <v>0</v>
-      </c>
-      <c r="U53" s="1"/>
-      <c r="V53" s="2">
-        <v>0</v>
-      </c>
-      <c r="W53" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="X53" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y53" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z53" s="2">
-        <v>1</v>
-      </c>
-      <c r="AA53" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB53" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC53" s="2">
-        <v>100</v>
-      </c>
       <c r="AD53" s="1">
         <v>0</v>
       </c>
@@ -6936,7 +6945,6 @@
       <c r="AI53" s="1">
         <v>0</v>
       </c>
-      <c r="AJ53" s="1"/>
       <c r="AK53" s="1">
         <v>50</v>
       </c>
@@ -6946,10 +6954,10 @@
     </row>
     <row r="54" spans="3:38">
       <c r="C54" s="2">
-        <v>10003</v>
+        <v>10002</v>
       </c>
       <c r="D54" s="2">
-        <v>10003</v>
+        <v>10002</v>
       </c>
       <c r="E54" s="1">
         <v>0</v>
@@ -6958,10 +6966,10 @@
         <v>198</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H54" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I54" s="1">
         <v>0</v>
@@ -6970,10 +6978,10 @@
         <v>0</v>
       </c>
       <c r="K54" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M54" s="1">
         <v>0</v>
@@ -7000,20 +7008,20 @@
         <v>0</v>
       </c>
       <c r="U54" s="1"/>
-      <c r="V54" s="1">
+      <c r="V54" s="2">
         <v>0</v>
       </c>
       <c r="W54" s="1" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="X54" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="Y54" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z54" s="1">
-        <v>10</v>
+        <v>74</v>
+      </c>
+      <c r="Y54" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="2">
+        <v>1</v>
       </c>
       <c r="AA54" s="1">
         <v>0</v>
@@ -7021,7 +7029,7 @@
       <c r="AB54" s="1">
         <v>0</v>
       </c>
-      <c r="AC54" s="1">
+      <c r="AC54" s="2">
         <v>100</v>
       </c>
       <c r="AD54" s="1">
@@ -7052,115 +7060,116 @@
     </row>
     <row r="55" spans="3:38">
       <c r="C55" s="2">
+        <v>10003</v>
+      </c>
+      <c r="D55" s="2">
+        <v>10003</v>
+      </c>
+      <c r="E55" s="1">
+        <v>0</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="H55" s="2">
+        <v>1</v>
+      </c>
+      <c r="I55" s="1">
+        <v>0</v>
+      </c>
+      <c r="J55" s="1">
+        <v>0</v>
+      </c>
+      <c r="K55" s="2">
+        <v>1</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="M55" s="1">
+        <v>0</v>
+      </c>
+      <c r="N55" s="2">
+        <v>0</v>
+      </c>
+      <c r="O55" s="1">
+        <v>1</v>
+      </c>
+      <c r="P55" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q55" s="1">
+        <v>0</v>
+      </c>
+      <c r="R55" s="1">
+        <v>0</v>
+      </c>
+      <c r="S55" s="1">
+        <v>1</v>
+      </c>
+      <c r="T55" s="1">
+        <v>0</v>
+      </c>
+      <c r="U55" s="1"/>
+      <c r="V55" s="1">
+        <v>0</v>
+      </c>
+      <c r="W55" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="X55" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y55" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="1">
+        <v>10</v>
+      </c>
+      <c r="AA55" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB55" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC55" s="1">
+        <v>100</v>
+      </c>
+      <c r="AD55" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE55" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF55" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG55" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH55" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI55" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ55" s="1"/>
+      <c r="AK55" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL55" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="56" spans="3:38">
+      <c r="C56" s="2">
         <v>10004</v>
       </c>
-      <c r="D55" s="2">
+      <c r="D56" s="2">
         <v>10004</v>
-      </c>
-      <c r="E55" s="1">
-        <v>0</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="H55" s="2">
-        <v>4</v>
-      </c>
-      <c r="I55" s="1">
-        <v>0</v>
-      </c>
-      <c r="J55" s="1">
-        <v>0</v>
-      </c>
-      <c r="K55" s="2">
-        <v>10</v>
-      </c>
-      <c r="L55" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="M55" s="1">
-        <v>0</v>
-      </c>
-      <c r="N55" s="2">
-        <v>0</v>
-      </c>
-      <c r="O55" s="1">
-        <v>1</v>
-      </c>
-      <c r="P55" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q55" s="2">
-        <v>0</v>
-      </c>
-      <c r="R55" s="1">
-        <v>0</v>
-      </c>
-      <c r="S55" s="1">
-        <v>1</v>
-      </c>
-      <c r="T55" s="1">
-        <v>0</v>
-      </c>
-      <c r="U55" s="1"/>
-      <c r="V55" s="2">
-        <v>3</v>
-      </c>
-      <c r="W55" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="X55" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="Y55" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z55" s="2">
-        <v>4</v>
-      </c>
-      <c r="AA55" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB55" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC55" s="2">
-        <v>50</v>
-      </c>
-      <c r="AD55" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE55" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF55" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG55" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH55" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI55" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK55" s="1">
-        <v>50</v>
-      </c>
-      <c r="AL55" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="56" s="1" customFormat="1" spans="3:38">
-      <c r="C56" s="1">
-        <v>10005</v>
-      </c>
-      <c r="D56" s="1">
-        <v>10005</v>
       </c>
       <c r="E56" s="1">
         <v>0</v>
@@ -7169,10 +7178,10 @@
         <v>201</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H56" s="1">
-        <v>1</v>
+        <v>197</v>
+      </c>
+      <c r="H56" s="2">
+        <v>4</v>
       </c>
       <c r="I56" s="1">
         <v>0</v>
@@ -7180,7 +7189,7 @@
       <c r="J56" s="1">
         <v>0</v>
       </c>
-      <c r="K56" s="1">
+      <c r="K56" s="2">
         <v>10</v>
       </c>
       <c r="L56" s="2" t="s">
@@ -7189,13 +7198,13 @@
       <c r="M56" s="1">
         <v>0</v>
       </c>
-      <c r="N56" s="1">
+      <c r="N56" s="2">
         <v>0</v>
       </c>
       <c r="O56" s="1">
         <v>1</v>
       </c>
-      <c r="P56" s="1">
+      <c r="P56" s="2">
         <v>1</v>
       </c>
       <c r="Q56" s="2">
@@ -7210,171 +7219,175 @@
       <c r="T56" s="1">
         <v>0</v>
       </c>
-      <c r="V56" s="1">
+      <c r="U56" s="1"/>
+      <c r="V56" s="2">
+        <v>3</v>
+      </c>
+      <c r="W56" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="X56" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y56" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z56" s="2">
+        <v>4</v>
+      </c>
+      <c r="AA56" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB56" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC56" s="2">
+        <v>50</v>
+      </c>
+      <c r="AD56" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE56" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF56" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG56" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH56" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI56" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK56" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL56" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57" s="1" customFormat="1" spans="3:38">
+      <c r="C57" s="1">
+        <v>10005</v>
+      </c>
+      <c r="D57" s="1">
+        <v>10005</v>
+      </c>
+      <c r="E57" s="1">
+        <v>0</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H57" s="1">
+        <v>1</v>
+      </c>
+      <c r="I57" s="1">
+        <v>0</v>
+      </c>
+      <c r="J57" s="1">
+        <v>0</v>
+      </c>
+      <c r="K57" s="1">
+        <v>10</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="M57" s="1">
+        <v>0</v>
+      </c>
+      <c r="N57" s="1">
+        <v>0</v>
+      </c>
+      <c r="O57" s="1">
+        <v>1</v>
+      </c>
+      <c r="P57" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q57" s="2">
+        <v>0</v>
+      </c>
+      <c r="R57" s="1">
+        <v>0</v>
+      </c>
+      <c r="S57" s="1">
+        <v>1</v>
+      </c>
+      <c r="T57" s="1">
+        <v>0</v>
+      </c>
+      <c r="V57" s="1">
         <v>2</v>
       </c>
-      <c r="W56" s="1" t="s">
+      <c r="W57" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="X56" s="1" t="s">
+      <c r="X57" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="Y56" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z56" s="1">
+      <c r="Y57" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="1">
         <v>2</v>
       </c>
-      <c r="AA56" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB56" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC56" s="1">
+      <c r="AA57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC57" s="1">
         <v>150</v>
       </c>
-      <c r="AD56" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE56" s="1">
+      <c r="AD57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="1">
         <v>20</v>
       </c>
-      <c r="AF56" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG56" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH56" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI56" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK56" s="1">
-        <v>50</v>
-      </c>
-      <c r="AL56" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="58" s="1" customFormat="1" spans="3:38">
-      <c r="C58" s="1">
-        <v>11001</v>
-      </c>
-      <c r="D58" s="1">
-        <v>1001</v>
-      </c>
-      <c r="E58" s="1">
-        <v>0</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="H58" s="1">
-        <v>1</v>
-      </c>
-      <c r="I58" s="1">
-        <v>0</v>
-      </c>
-      <c r="J58" s="1">
-        <v>0</v>
-      </c>
-      <c r="K58" s="1">
-        <v>10</v>
-      </c>
-      <c r="M58" s="1">
-        <v>0</v>
-      </c>
-      <c r="N58" s="1">
-        <v>0</v>
-      </c>
-      <c r="O58" s="1">
-        <v>1</v>
-      </c>
-      <c r="P58" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q58" s="1">
-        <v>9999</v>
-      </c>
-      <c r="R58" s="1">
-        <v>0</v>
-      </c>
-      <c r="S58" s="1">
-        <v>1</v>
-      </c>
-      <c r="T58" s="1">
-        <v>0</v>
-      </c>
-      <c r="V58" s="1">
-        <v>1</v>
-      </c>
-      <c r="W58" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="X58" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y58" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z58" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA58" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB58" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC58" s="1">
-        <v>120</v>
-      </c>
-      <c r="AD58" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE58" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF58" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG58" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH58" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI58" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK58" s="1">
-        <v>50</v>
-      </c>
-      <c r="AL58" s="1">
+      <c r="AF57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK57" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL57" s="1">
         <v>50</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" spans="3:38">
       <c r="C59" s="1">
-        <v>11002</v>
+        <v>11001</v>
       </c>
       <c r="D59" s="1">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E59" s="1">
         <v>0</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="H59" s="1">
         <v>1</v>
@@ -7395,7 +7408,7 @@
         <v>0</v>
       </c>
       <c r="O59" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P59" s="1">
         <v>1</v>
@@ -7413,7 +7426,7 @@
         <v>0</v>
       </c>
       <c r="V59" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W59" s="1" t="s">
         <v>73</v>
@@ -7425,7 +7438,7 @@
         <v>0</v>
       </c>
       <c r="Z59" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA59" s="1">
         <v>0</v>
@@ -7434,13 +7447,13 @@
         <v>0</v>
       </c>
       <c r="AC59" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AD59" s="1">
         <v>0</v>
       </c>
       <c r="AE59" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AF59" s="1">
         <v>0</v>
@@ -7463,19 +7476,19 @@
     </row>
     <row r="60" s="1" customFormat="1" spans="3:38">
       <c r="C60" s="1">
-        <v>11003</v>
+        <v>11002</v>
       </c>
       <c r="D60" s="1">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E60" s="1">
         <v>0</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H60" s="1">
         <v>1</v>
@@ -7514,19 +7527,19 @@
         <v>0</v>
       </c>
       <c r="V60" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W60" s="1" t="s">
         <v>73</v>
       </c>
       <c r="X60" s="1" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="Y60" s="1">
         <v>0</v>
       </c>
       <c r="Z60" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AA60" s="1">
         <v>0</v>
@@ -7535,13 +7548,13 @@
         <v>0</v>
       </c>
       <c r="AC60" s="1">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="AD60" s="1">
         <v>0</v>
       </c>
       <c r="AE60" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AF60" s="1">
         <v>0</v>
@@ -7564,22 +7577,22 @@
     </row>
     <row r="61" s="1" customFormat="1" spans="3:38">
       <c r="C61" s="1">
-        <v>11004</v>
+        <v>11003</v>
       </c>
       <c r="D61" s="1">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="E61" s="1">
         <v>0</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="H61" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I61" s="1">
         <v>0</v>
@@ -7594,10 +7607,10 @@
         <v>0</v>
       </c>
       <c r="N61" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O61" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P61" s="1">
         <v>1</v>
@@ -7615,19 +7628,19 @@
         <v>0</v>
       </c>
       <c r="V61" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W61" s="1" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="X61" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="Y61" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z61" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA61" s="1">
         <v>0</v>
@@ -7636,7 +7649,7 @@
         <v>0</v>
       </c>
       <c r="AC61" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AD61" s="1">
         <v>0</v>
@@ -7655,9 +7668,6 @@
       </c>
       <c r="AI61" s="1">
         <v>0</v>
-      </c>
-      <c r="AJ61" s="1" t="s">
-        <v>202</v>
       </c>
       <c r="AK61" s="1">
         <v>50</v>
@@ -7668,37 +7678,37 @@
     </row>
     <row r="62" s="1" customFormat="1" spans="3:38">
       <c r="C62" s="1">
-        <v>11005</v>
+        <v>11004</v>
       </c>
       <c r="D62" s="1">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E62" s="1">
         <v>0</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="H62" s="1">
+        <v>7</v>
+      </c>
+      <c r="I62" s="1">
+        <v>0</v>
+      </c>
+      <c r="J62" s="1">
+        <v>0</v>
+      </c>
+      <c r="K62" s="1">
+        <v>10</v>
+      </c>
+      <c r="M62" s="1">
+        <v>0</v>
+      </c>
+      <c r="N62" s="1">
         <v>5</v>
-      </c>
-      <c r="I62" s="1">
-        <v>0</v>
-      </c>
-      <c r="J62" s="1">
-        <v>0</v>
-      </c>
-      <c r="K62" s="1">
-        <v>50</v>
-      </c>
-      <c r="M62" s="1">
-        <v>0</v>
-      </c>
-      <c r="N62" s="1">
-        <v>30</v>
       </c>
       <c r="O62" s="1">
         <v>1</v>
@@ -7719,19 +7729,19 @@
         <v>0</v>
       </c>
       <c r="V62" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W62" s="1" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="X62" s="1" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="Y62" s="1">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="Z62" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA62" s="1">
         <v>0</v>
@@ -7740,7 +7750,7 @@
         <v>0</v>
       </c>
       <c r="AC62" s="1">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="AD62" s="1">
         <v>0</v>
@@ -7760,7 +7770,9 @@
       <c r="AI62" s="1">
         <v>0</v>
       </c>
-      <c r="AJ62" s="7"/>
+      <c r="AJ62" s="1" t="s">
+        <v>204</v>
+      </c>
       <c r="AK62" s="1">
         <v>50</v>
       </c>
@@ -7770,22 +7782,22 @@
     </row>
     <row r="63" s="1" customFormat="1" spans="3:38">
       <c r="C63" s="1">
-        <v>11006</v>
+        <v>11005</v>
       </c>
       <c r="D63" s="1">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="E63" s="1">
         <v>0</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H63" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I63" s="1">
         <v>0</v>
@@ -7794,13 +7806,13 @@
         <v>0</v>
       </c>
       <c r="K63" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="M63" s="1">
         <v>0</v>
       </c>
       <c r="N63" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O63" s="1">
         <v>1</v>
@@ -7827,10 +7839,10 @@
         <v>73</v>
       </c>
       <c r="X63" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="Y63" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Z63" s="1">
         <v>0</v>
@@ -7842,7 +7854,7 @@
         <v>0</v>
       </c>
       <c r="AC63" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="AD63" s="1">
         <v>0</v>
@@ -7862,6 +7874,7 @@
       <c r="AI63" s="1">
         <v>0</v>
       </c>
+      <c r="AJ63" s="7"/>
       <c r="AK63" s="1">
         <v>50</v>
       </c>
@@ -7871,22 +7884,22 @@
     </row>
     <row r="64" s="1" customFormat="1" spans="3:38">
       <c r="C64" s="1">
-        <v>11007</v>
+        <v>11006</v>
       </c>
       <c r="D64" s="1">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="E64" s="1">
         <v>0</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="H64" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I64" s="1">
         <v>0</v>
@@ -7922,19 +7935,19 @@
         <v>0</v>
       </c>
       <c r="V64" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W64" s="1" t="s">
         <v>73</v>
       </c>
       <c r="X64" s="1" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="Y64" s="1">
         <v>0</v>
       </c>
       <c r="Z64" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA64" s="1">
         <v>0</v>
@@ -7943,7 +7956,7 @@
         <v>0</v>
       </c>
       <c r="AC64" s="1">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="AD64" s="1">
         <v>0</v>
@@ -7972,19 +7985,19 @@
     </row>
     <row r="65" s="1" customFormat="1" spans="3:38">
       <c r="C65" s="1">
-        <v>12001</v>
+        <v>11007</v>
       </c>
       <c r="D65" s="1">
-        <v>2001</v>
+        <v>1007</v>
       </c>
       <c r="E65" s="1">
         <v>0</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>116</v>
+        <v>97</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="H65" s="1">
         <v>1</v>
@@ -8008,7 +8021,7 @@
         <v>1</v>
       </c>
       <c r="P65" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q65" s="1">
         <v>9999</v>
@@ -8023,13 +8036,13 @@
         <v>0</v>
       </c>
       <c r="V65" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W65" s="1" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="X65" s="1" t="s">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="Y65" s="1">
         <v>0</v>
@@ -8044,7 +8057,7 @@
         <v>0</v>
       </c>
       <c r="AC65" s="1">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="AD65" s="1">
         <v>0</v>
@@ -8073,19 +8086,19 @@
     </row>
     <row r="66" s="1" customFormat="1" spans="3:38">
       <c r="C66" s="1">
-        <v>12002</v>
+        <v>12001</v>
       </c>
       <c r="D66" s="1">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="E66" s="1">
         <v>0</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>116</v>
       </c>
       <c r="H66" s="1">
         <v>1</v>
@@ -8124,7 +8137,7 @@
         <v>0</v>
       </c>
       <c r="V66" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W66" s="1" t="s">
         <v>86</v>
@@ -8145,7 +8158,7 @@
         <v>0</v>
       </c>
       <c r="AC66" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AD66" s="1">
         <v>0</v>
@@ -8174,22 +8187,22 @@
     </row>
     <row r="67" s="1" customFormat="1" spans="3:38">
       <c r="C67" s="1">
-        <v>12003</v>
+        <v>12002</v>
       </c>
       <c r="D67" s="1">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="E67" s="1">
         <v>0</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H67" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I67" s="1">
         <v>0</v>
@@ -8204,10 +8217,10 @@
         <v>0</v>
       </c>
       <c r="N67" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O67" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P67" s="1">
         <v>2</v>
@@ -8231,22 +8244,22 @@
         <v>86</v>
       </c>
       <c r="X67" s="1" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="Y67" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z67" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA67" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB67" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC67" s="1">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="AD67" s="1">
         <v>0</v>
@@ -8275,22 +8288,22 @@
     </row>
     <row r="68" s="1" customFormat="1" spans="3:38">
       <c r="C68" s="1">
-        <v>12004</v>
+        <v>12003</v>
       </c>
       <c r="D68" s="1">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="E68" s="1">
         <v>0</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H68" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I68" s="1">
         <v>0</v>
@@ -8305,7 +8318,7 @@
         <v>0</v>
       </c>
       <c r="N68" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O68" s="1">
         <v>2</v>
@@ -8326,19 +8339,19 @@
         <v>0</v>
       </c>
       <c r="V68" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W68" s="1" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="X68" s="1" t="s">
         <v>92</v>
       </c>
       <c r="Y68" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z68" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA68" s="1">
         <v>2</v>
@@ -8347,7 +8360,7 @@
         <v>2</v>
       </c>
       <c r="AC68" s="1">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AD68" s="1">
         <v>0</v>
@@ -8376,22 +8389,22 @@
     </row>
     <row r="69" s="1" customFormat="1" spans="3:38">
       <c r="C69" s="1">
-        <v>12005</v>
+        <v>12004</v>
       </c>
       <c r="D69" s="1">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="E69" s="1">
         <v>0</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="H69" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I69" s="1">
         <v>0</v>
@@ -8400,16 +8413,16 @@
         <v>0</v>
       </c>
       <c r="K69" s="1">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="M69" s="1">
         <v>0</v>
       </c>
       <c r="N69" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O69" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P69" s="1">
         <v>2</v>
@@ -8427,7 +8440,7 @@
         <v>0</v>
       </c>
       <c r="V69" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W69" s="1" t="s">
         <v>73</v>
@@ -8436,19 +8449,19 @@
         <v>92</v>
       </c>
       <c r="Y69" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Z69" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA69" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB69" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC69" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AD69" s="1">
         <v>0</v>
@@ -8468,7 +8481,6 @@
       <c r="AI69" s="1">
         <v>0</v>
       </c>
-      <c r="AJ69" s="7"/>
       <c r="AK69" s="1">
         <v>50</v>
       </c>
@@ -8478,22 +8490,22 @@
     </row>
     <row r="70" s="1" customFormat="1" spans="3:38">
       <c r="C70" s="1">
-        <v>12006</v>
+        <v>12005</v>
       </c>
       <c r="D70" s="1">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="E70" s="1">
         <v>0</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="H70" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I70" s="1">
         <v>0</v>
@@ -8502,13 +8514,13 @@
         <v>0</v>
       </c>
       <c r="K70" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="M70" s="1">
         <v>0</v>
       </c>
       <c r="N70" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O70" s="1">
         <v>1</v>
@@ -8535,10 +8547,10 @@
         <v>73</v>
       </c>
       <c r="X70" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="Y70" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Z70" s="1">
         <v>0</v>
@@ -8550,7 +8562,7 @@
         <v>0</v>
       </c>
       <c r="AC70" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="AD70" s="1">
         <v>0</v>
@@ -8570,6 +8582,7 @@
       <c r="AI70" s="1">
         <v>0</v>
       </c>
+      <c r="AJ70" s="7"/>
       <c r="AK70" s="1">
         <v>50</v>
       </c>
@@ -8579,22 +8592,22 @@
     </row>
     <row r="71" s="1" customFormat="1" spans="3:38">
       <c r="C71" s="1">
-        <v>12007</v>
+        <v>12006</v>
       </c>
       <c r="D71" s="1">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="E71" s="1">
         <v>0</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="G71" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="H71" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I71" s="1">
         <v>0</v>
@@ -8612,7 +8625,7 @@
         <v>0</v>
       </c>
       <c r="O71" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P71" s="1">
         <v>2</v>
@@ -8630,28 +8643,28 @@
         <v>0</v>
       </c>
       <c r="V71" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W71" s="1" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="X71" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="Y71" s="1">
         <v>0</v>
       </c>
       <c r="Z71" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA71" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB71" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC71" s="1">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="AD71" s="1">
         <v>0</v>
@@ -8680,22 +8693,22 @@
     </row>
     <row r="72" s="1" customFormat="1" spans="3:38">
       <c r="C72" s="1">
-        <v>13001</v>
+        <v>12007</v>
       </c>
       <c r="D72" s="1">
-        <v>3001</v>
+        <v>2007</v>
       </c>
       <c r="E72" s="1">
         <v>0</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="H72" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I72" s="1">
         <v>0</v>
@@ -8704,19 +8717,19 @@
         <v>0</v>
       </c>
       <c r="K72" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M72" s="1">
         <v>0</v>
       </c>
       <c r="N72" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O72" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P72" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q72" s="1">
         <v>9999</v>
@@ -8731,10 +8744,10 @@
         <v>0</v>
       </c>
       <c r="V72" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W72" s="1" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="X72" s="1" t="s">
         <v>92</v>
@@ -8743,16 +8756,16 @@
         <v>0</v>
       </c>
       <c r="Z72" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA72" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB72" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC72" s="1">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="AD72" s="1">
         <v>0</v>
@@ -8781,22 +8794,22 @@
     </row>
     <row r="73" s="1" customFormat="1" spans="3:38">
       <c r="C73" s="1">
-        <v>13002</v>
+        <v>13001</v>
       </c>
       <c r="D73" s="1">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="E73" s="1">
         <v>0</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>150</v>
       </c>
       <c r="H73" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I73" s="1">
         <v>0</v>
@@ -8805,13 +8818,13 @@
         <v>0</v>
       </c>
       <c r="K73" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M73" s="1">
         <v>0</v>
       </c>
       <c r="N73" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O73" s="1">
         <v>1</v>
@@ -8832,19 +8845,19 @@
         <v>0</v>
       </c>
       <c r="V73" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W73" s="1" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="X73" s="1" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="Y73" s="1">
         <v>0</v>
       </c>
       <c r="Z73" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA73" s="1">
         <v>0</v>
@@ -8853,7 +8866,7 @@
         <v>0</v>
       </c>
       <c r="AC73" s="1">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="AD73" s="1">
         <v>0</v>
@@ -8882,19 +8895,19 @@
     </row>
     <row r="74" s="1" customFormat="1" spans="3:38">
       <c r="C74" s="1">
-        <v>13003</v>
+        <v>13002</v>
       </c>
       <c r="D74" s="1">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="E74" s="1">
         <v>0</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="H74" s="1">
         <v>1</v>
@@ -8912,7 +8925,7 @@
         <v>0</v>
       </c>
       <c r="N74" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O74" s="1">
         <v>1</v>
@@ -8933,7 +8946,7 @@
         <v>0</v>
       </c>
       <c r="V74" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W74" s="1" t="s">
         <v>86</v>
@@ -8945,7 +8958,7 @@
         <v>0</v>
       </c>
       <c r="Z74" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA74" s="1">
         <v>0</v>
@@ -8954,13 +8967,13 @@
         <v>0</v>
       </c>
       <c r="AC74" s="1">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="AD74" s="1">
         <v>0</v>
       </c>
       <c r="AE74" s="1">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AF74" s="1">
         <v>0</v>
@@ -8983,22 +8996,22 @@
     </row>
     <row r="75" s="1" customFormat="1" spans="3:38">
       <c r="C75" s="1">
-        <v>13004</v>
+        <v>13003</v>
       </c>
       <c r="D75" s="1">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="E75" s="1">
         <v>0</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="H75" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I75" s="1">
         <v>0</v>
@@ -9007,13 +9020,13 @@
         <v>0</v>
       </c>
       <c r="K75" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="M75" s="1">
         <v>0</v>
       </c>
       <c r="N75" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O75" s="1">
         <v>1</v>
@@ -9034,19 +9047,19 @@
         <v>0</v>
       </c>
       <c r="V75" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W75" s="1" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="X75" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="Y75" s="1">
         <v>0</v>
       </c>
       <c r="Z75" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA75" s="1">
         <v>0</v>
@@ -9055,13 +9068,13 @@
         <v>0</v>
       </c>
       <c r="AC75" s="1">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="AD75" s="1">
         <v>0</v>
       </c>
       <c r="AE75" s="1">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF75" s="1">
         <v>0</v>
@@ -9084,22 +9097,22 @@
     </row>
     <row r="76" s="1" customFormat="1" spans="3:38">
       <c r="C76" s="1">
-        <v>13005</v>
+        <v>13004</v>
       </c>
       <c r="D76" s="1">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="E76" s="1">
         <v>0</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H76" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I76" s="1">
         <v>0</v>
@@ -9108,13 +9121,13 @@
         <v>0</v>
       </c>
       <c r="K76" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M76" s="1">
         <v>0</v>
       </c>
       <c r="N76" s="1">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="O76" s="1">
         <v>1</v>
@@ -9141,13 +9154,13 @@
         <v>73</v>
       </c>
       <c r="X76" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="Y76" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Z76" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA76" s="1">
         <v>0</v>
@@ -9156,7 +9169,7 @@
         <v>0</v>
       </c>
       <c r="AC76" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AD76" s="1">
         <v>0</v>
@@ -9176,7 +9189,6 @@
       <c r="AI76" s="1">
         <v>0</v>
       </c>
-      <c r="AJ76" s="7"/>
       <c r="AK76" s="1">
         <v>50</v>
       </c>
@@ -9186,22 +9198,22 @@
     </row>
     <row r="77" s="1" customFormat="1" spans="3:38">
       <c r="C77" s="1">
-        <v>13006</v>
+        <v>13005</v>
       </c>
       <c r="D77" s="1">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="E77" s="1">
         <v>0</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>162</v>
       </c>
       <c r="H77" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I77" s="1">
         <v>0</v>
@@ -9210,13 +9222,13 @@
         <v>0</v>
       </c>
       <c r="K77" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="M77" s="1">
         <v>0</v>
       </c>
       <c r="N77" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O77" s="1">
         <v>1</v>
@@ -9237,16 +9249,16 @@
         <v>0</v>
       </c>
       <c r="V77" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W77" s="1" t="s">
         <v>73</v>
       </c>
       <c r="X77" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="Y77" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Z77" s="1">
         <v>0</v>
@@ -9258,7 +9270,7 @@
         <v>0</v>
       </c>
       <c r="AC77" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="AD77" s="1">
         <v>0</v>
@@ -9278,6 +9290,7 @@
       <c r="AI77" s="1">
         <v>0</v>
       </c>
+      <c r="AJ77" s="7"/>
       <c r="AK77" s="1">
         <v>50</v>
       </c>
@@ -9287,22 +9300,22 @@
     </row>
     <row r="78" s="1" customFormat="1" spans="3:38">
       <c r="C78" s="1">
-        <v>13007</v>
+        <v>13006</v>
       </c>
       <c r="D78" s="1">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="E78" s="1">
         <v>0</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="H78" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I78" s="1">
         <v>0</v>
@@ -9311,13 +9324,13 @@
         <v>0</v>
       </c>
       <c r="K78" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="M78" s="1">
         <v>0</v>
       </c>
       <c r="N78" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O78" s="1">
         <v>1</v>
@@ -9338,166 +9351,267 @@
         <v>0</v>
       </c>
       <c r="V78" s="1">
+        <v>3</v>
+      </c>
+      <c r="W78" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X78" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y78" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC78" s="1">
+        <v>50</v>
+      </c>
+      <c r="AD78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK78" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL78" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="79" s="1" customFormat="1" spans="3:38">
+      <c r="C79" s="1">
+        <v>13007</v>
+      </c>
+      <c r="D79" s="1">
+        <v>3007</v>
+      </c>
+      <c r="E79" s="1">
+        <v>0</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="H79" s="1">
         <v>2</v>
       </c>
-      <c r="W78" s="1" t="s">
+      <c r="I79" s="1">
+        <v>0</v>
+      </c>
+      <c r="J79" s="1">
+        <v>0</v>
+      </c>
+      <c r="K79" s="1">
+        <v>100</v>
+      </c>
+      <c r="M79" s="1">
+        <v>0</v>
+      </c>
+      <c r="N79" s="1">
+        <v>15</v>
+      </c>
+      <c r="O79" s="1">
+        <v>1</v>
+      </c>
+      <c r="P79" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q79" s="1">
+        <v>9999</v>
+      </c>
+      <c r="R79" s="1">
+        <v>0</v>
+      </c>
+      <c r="S79" s="1">
+        <v>1</v>
+      </c>
+      <c r="T79" s="1">
+        <v>0</v>
+      </c>
+      <c r="V79" s="1">
+        <v>2</v>
+      </c>
+      <c r="W79" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="X78" s="1" t="s">
+      <c r="X79" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="Y78" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z78" s="1">
+      <c r="Y79" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z79" s="1">
         <v>2</v>
       </c>
-      <c r="AA78" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB78" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC78" s="1">
+      <c r="AA79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC79" s="1">
         <v>120</v>
       </c>
-      <c r="AD78" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE78" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF78" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG78" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH78" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI78" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK78" s="1">
-        <v>50</v>
-      </c>
-      <c r="AL78" s="1">
+      <c r="AD79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK79" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL79" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="79" s="1" customFormat="1" spans="6:21">
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="L79" s="2"/>
-      <c r="M79" s="2"/>
-      <c r="Q79" s="2"/>
-      <c r="R79" s="2"/>
-      <c r="S79" s="2"/>
-      <c r="T79" s="2"/>
-      <c r="U79" s="2"/>
+    <row r="80" s="1" customFormat="1" spans="6:21">
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
+      <c r="L80" s="2"/>
+      <c r="M80" s="2"/>
+      <c r="Q80" s="2"/>
+      <c r="R80" s="2"/>
+      <c r="S80" s="2"/>
+      <c r="T80" s="2"/>
+      <c r="U80" s="2"/>
     </row>
-    <row r="80" s="1" customFormat="1" spans="3:38">
-      <c r="C80" s="1">
+    <row r="81" s="1" customFormat="1" spans="3:38">
+      <c r="C81" s="1">
         <v>21002</v>
       </c>
-      <c r="D80" s="1">
+      <c r="D81" s="1">
         <v>1002</v>
       </c>
-      <c r="E80" s="1">
-        <v>0</v>
-      </c>
-      <c r="F80" s="1" t="s">
+      <c r="E81" s="1">
+        <v>0</v>
+      </c>
+      <c r="F81" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="G80" s="2" t="s">
+      <c r="G81" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="H80" s="1">
-        <v>1</v>
-      </c>
-      <c r="I80" s="1">
-        <v>0</v>
-      </c>
-      <c r="J80" s="1">
-        <v>0</v>
-      </c>
-      <c r="K80" s="1">
+      <c r="H81" s="1">
+        <v>1</v>
+      </c>
+      <c r="I81" s="1">
+        <v>0</v>
+      </c>
+      <c r="J81" s="1">
+        <v>0</v>
+      </c>
+      <c r="K81" s="1">
         <v>10</v>
       </c>
-      <c r="M80" s="1">
-        <v>0</v>
-      </c>
-      <c r="N80" s="1">
-        <v>0</v>
-      </c>
-      <c r="O80" s="1">
+      <c r="M81" s="1">
+        <v>0</v>
+      </c>
+      <c r="N81" s="1">
+        <v>0</v>
+      </c>
+      <c r="O81" s="1">
         <v>2</v>
       </c>
-      <c r="P80" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q80" s="1">
+      <c r="P81" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q81" s="1">
         <v>9999</v>
       </c>
-      <c r="R80" s="1">
-        <v>0</v>
-      </c>
-      <c r="S80" s="1">
-        <v>1</v>
-      </c>
-      <c r="T80" s="1">
-        <v>0</v>
-      </c>
-      <c r="V80" s="1">
+      <c r="R81" s="1">
+        <v>0</v>
+      </c>
+      <c r="S81" s="1">
+        <v>1</v>
+      </c>
+      <c r="T81" s="1">
+        <v>0</v>
+      </c>
+      <c r="V81" s="1">
         <v>2</v>
       </c>
-      <c r="W80" s="1" t="s">
+      <c r="W81" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="X80" s="1" t="s">
+      <c r="X81" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="Y80" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z80" s="1">
+      <c r="Y81" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="1">
         <v>2</v>
       </c>
-      <c r="AA80" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB80" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC80" s="1">
+      <c r="AA81" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB81" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC81" s="1">
         <v>150</v>
       </c>
-      <c r="AD80" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE80" s="1">
+      <c r="AD81" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE81" s="1">
         <v>20</v>
       </c>
-      <c r="AF80" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG80" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH80" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI80" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ80" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="AK80" s="1">
-        <v>50</v>
-      </c>
-      <c r="AL80" s="1">
+      <c r="AF81" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG81" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH81" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI81" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ81" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="AK81" s="1">
+        <v>50</v>
+      </c>
+      <c r="AL81" s="1">
         <v>50</v>
       </c>
     </row>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -642,7 +642,7 @@
     <t>剑二十三</t>
   </si>
   <si>
-    <t>对{0}个敌人，造成流光剑法*{1}%的伤害，并且计算流光剑法的最远距离伤害</t>
+    <t>对{0}个敌人，释放流光剑法，视为最远距离，额外附加20%无视防御，提高*{1}%的伤害</t>
   </si>
   <si>
     <t>火球术</t>
@@ -879,7 +879,7 @@
     <t>飓风破</t>
   </si>
   <si>
-    <t>对{3}*{4}范围内的敌人造成{1}%道术伤害</t>
+    <t>对{3}*{4}范围内的敌人造成驱魔符伤害*火符弹射次数*{1}%，额外附带70%无视伤害</t>
   </si>
   <si>
     <t>普攻</t>
@@ -3572,7 +3572,7 @@
         <v>0</v>
       </c>
       <c r="AE17" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AF17" s="1">
         <v>0</v>
@@ -6111,7 +6111,7 @@
         <v>3012</v>
       </c>
       <c r="E43" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>179</v>
@@ -6556,7 +6556,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="1">
-        <v>0</v>
+        <v>3002</v>
       </c>
       <c r="K48" s="1">
         <v>10</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -6174,7 +6174,7 @@
         <v>0</v>
       </c>
       <c r="Z43" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA43" s="1">
         <v>0</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -840,7 +840,7 @@
     <t>召唤白虎</t>
   </si>
   <si>
-    <t>召唤{0}只白虎战斗，攻击和生命为人物的{1}%,其他所有属性为100%</t>
+    <t>召唤{0}只白虎战斗，100%继承人物一切属性、天赋、神器特效，攻击和生命额外提高{1}%</t>
   </si>
   <si>
     <t>定身指环</t>
@@ -5938,7 +5938,7 @@
         <v>1</v>
       </c>
       <c r="S41" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T41" s="1">
         <v>1</v>
@@ -6153,7 +6153,7 @@
         <v>0.1</v>
       </c>
       <c r="S43" s="1">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="T43" s="1">
         <v>4</v>
@@ -6207,14 +6207,14 @@
         <v>50</v>
       </c>
       <c r="AL43" s="1">
-        <v>4006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" spans="6:7">
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
     </row>
-    <row r="45" s="1" customFormat="1" spans="3:37">
+    <row r="45" s="1" customFormat="1" spans="3:38">
       <c r="C45" s="1">
         <v>4001</v>
       </c>
@@ -6320,8 +6320,11 @@
       <c r="AK45" s="1">
         <v>99999</v>
       </c>
+      <c r="AL45" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" s="1" customFormat="1" spans="3:37">
+    <row r="46" s="1" customFormat="1" spans="3:38">
       <c r="C46" s="1">
         <v>4002</v>
       </c>
@@ -6425,8 +6428,11 @@
       <c r="AK46" s="1">
         <v>99999</v>
       </c>
+      <c r="AL46" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" s="1" customFormat="1" spans="3:37">
+    <row r="47" s="1" customFormat="1" spans="3:38">
       <c r="C47" s="1">
         <v>4003</v>
       </c>
@@ -6531,6 +6537,9 @@
       </c>
       <c r="AK47" s="1">
         <v>99999</v>
+      </c>
+      <c r="AL47" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" spans="3:38">
@@ -6592,7 +6601,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W48" s="1" t="s">
         <v>86</v>
@@ -6604,13 +6613,13 @@
         <v>0</v>
       </c>
       <c r="Z48" s="1">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AA48" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB48" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC48" s="1">
         <v>500</v>
@@ -6638,7 +6647,7 @@
         <v>50</v>
       </c>
       <c r="AL48" s="1">
-        <v>4006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" spans="6:7">

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -642,7 +642,7 @@
     <t>剑二十三</t>
   </si>
   <si>
-    <t>对{0}个敌人，释放流光剑法，视为最远距离，额外附加20%无视防御，提高*{1}%的伤害</t>
+    <t>对{0}个敌人造成伤害，技能伤害来源流光剑法，额外附加20%无视防御，提高*{1}%的伤害</t>
   </si>
   <si>
     <t>火球术</t>
@@ -744,7 +744,7 @@
     <t>魔法大炮</t>
   </si>
   <si>
-    <t>每次释放技能之后，增加{1}%攻击倍率和{5}%生命倍率，最高叠加{2}次</t>
+    <t>每次释放技能之后，增加{1}%魔法倍率和{5}%生命倍率，最高叠加{2}次</t>
   </si>
   <si>
     <t>疗伤术</t>
@@ -840,7 +840,7 @@
     <t>召唤白虎</t>
   </si>
   <si>
-    <t>召唤{0}只白虎战斗，100%继承人物一切属性、天赋、神器特效，攻击和生命额外提高{1}%</t>
+    <t>召唤{0}只白虎战斗，技能伤害来源驱魔符，100%继承人物一切属性、天赋、神器特效，攻击和生命额外提高{1}%</t>
   </si>
   <si>
     <t>定身指环</t>
@@ -1107,12 +1107,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3530,13 +3530,13 @@
         <v>1</v>
       </c>
       <c r="Q17" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R17" s="1">
         <v>0.1</v>
       </c>
       <c r="S17" s="1">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="T17" s="1">
         <v>500</v>
@@ -3566,7 +3566,7 @@
         <v>3</v>
       </c>
       <c r="AC17" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AD17" s="1">
         <v>0</v>
@@ -4879,10 +4879,10 @@
         <v>4</v>
       </c>
       <c r="AC30" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AD30" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AE30" s="1">
         <v>0</v>
@@ -6183,7 +6183,7 @@
         <v>0</v>
       </c>
       <c r="AC43" s="1">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AD43" s="1">
         <v>0</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -741,7 +741,7 @@
     <t>上阵后，提高人物{1}%的生命倍率和{5}%的魔攻倍率（分身和宠物享受）</t>
   </si>
   <si>
-    <t>魔法大炮</t>
+    <t>魔尊附体</t>
   </si>
   <si>
     <t>每次释放技能之后，增加{1}%魔法倍率和{5}%生命倍率，最高叠加{2}次</t>
@@ -1909,43 +1909,43 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C3:AN81"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="5.6283185840708" style="2" customWidth="1"/>
-    <col min="2" max="2" width="3.50442477876106" style="2" customWidth="1"/>
+    <col min="1" max="1" width="5.625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="3.50833333333333" style="2" customWidth="1"/>
     <col min="3" max="5" width="9" style="2"/>
-    <col min="6" max="6" width="11.5044247787611" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.5083333333333" style="2" customWidth="1"/>
     <col min="7" max="7" width="9" style="2" customWidth="1"/>
-    <col min="8" max="8" width="6.3716814159292" style="2" customWidth="1"/>
-    <col min="9" max="10" width="9.3716814159292" style="2" customWidth="1"/>
-    <col min="11" max="11" width="5.24778761061947" style="2" customWidth="1"/>
-    <col min="12" max="12" width="74.8761061946903" style="2" customWidth="1"/>
-    <col min="13" max="13" width="10.5044247787611" style="2" customWidth="1"/>
-    <col min="14" max="14" width="5.87610619469027" style="2" customWidth="1"/>
-    <col min="15" max="15" width="8.3716814159292" style="2" customWidth="1"/>
-    <col min="16" max="16" width="5.87610619469027" style="2" customWidth="1"/>
-    <col min="17" max="17" width="7.50442477876106" style="2" customWidth="1"/>
-    <col min="18" max="19" width="12.8761061946903" style="2" customWidth="1"/>
-    <col min="20" max="21" width="13.5044247787611" style="2" customWidth="1"/>
-    <col min="22" max="22" width="7.3716814159292" style="2" customWidth="1"/>
-    <col min="23" max="23" width="7.50442477876106" style="2" customWidth="1"/>
-    <col min="24" max="24" width="8.24778761061947" style="2" customWidth="1"/>
-    <col min="25" max="25" width="6.50442477876106" style="2" customWidth="1"/>
-    <col min="26" max="28" width="7.6283185840708" style="2" customWidth="1"/>
-    <col min="29" max="30" width="7.87610619469027" style="2" customWidth="1"/>
-    <col min="31" max="31" width="9.6283185840708" style="2" customWidth="1"/>
-    <col min="32" max="33" width="7.87610619469027" style="2" customWidth="1"/>
-    <col min="34" max="34" width="12.6283185840708" style="2" customWidth="1"/>
-    <col min="35" max="35" width="9.6283185840708" style="2" customWidth="1"/>
-    <col min="36" max="36" width="27.6283185840708" style="2" customWidth="1"/>
-    <col min="37" max="37" width="17.8761061946903" style="2" customWidth="1"/>
-    <col min="38" max="38" width="19.7522123893805" style="2" customWidth="1"/>
+    <col min="8" max="8" width="6.375" style="2" customWidth="1"/>
+    <col min="9" max="10" width="9.375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="5.25" style="2" customWidth="1"/>
+    <col min="12" max="12" width="74.875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="10.5083333333333" style="2" customWidth="1"/>
+    <col min="14" max="14" width="5.875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="8.375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="5.875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="7.50833333333333" style="2" customWidth="1"/>
+    <col min="18" max="19" width="12.875" style="2" customWidth="1"/>
+    <col min="20" max="21" width="13.5083333333333" style="2" customWidth="1"/>
+    <col min="22" max="22" width="7.375" style="2" customWidth="1"/>
+    <col min="23" max="23" width="7.50833333333333" style="2" customWidth="1"/>
+    <col min="24" max="24" width="8.25" style="2" customWidth="1"/>
+    <col min="25" max="25" width="6.50833333333333" style="2" customWidth="1"/>
+    <col min="26" max="28" width="7.625" style="2" customWidth="1"/>
+    <col min="29" max="30" width="7.875" style="2" customWidth="1"/>
+    <col min="31" max="31" width="9.625" style="2" customWidth="1"/>
+    <col min="32" max="33" width="7.875" style="2" customWidth="1"/>
+    <col min="34" max="34" width="12.625" style="2" customWidth="1"/>
+    <col min="35" max="35" width="9.625" style="2" customWidth="1"/>
+    <col min="36" max="36" width="27.625" style="2" customWidth="1"/>
+    <col min="37" max="37" width="17.875" style="2" customWidth="1"/>
+    <col min="38" max="38" width="19.75" style="2" customWidth="1"/>
     <col min="39" max="39" width="9" style="2"/>
-    <col min="40" max="40" width="19.2477876106195" style="2" customWidth="1"/>
+    <col min="40" max="40" width="19.25" style="2" customWidth="1"/>
     <col min="41" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:40">
+    <row r="3" ht="13.5" spans="3:40">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="3:38">
+    <row r="4" ht="13.5" spans="3:38">
       <c r="C4" s="3" t="s">
         <v>36</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="3:38">
+    <row r="5" ht="13.5" spans="3:38">
       <c r="C5" s="3" t="s">
         <v>67</v>
       </c>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -840,7 +840,7 @@
     <t>召唤白虎</t>
   </si>
   <si>
-    <t>召唤{0}只白虎战斗，技能伤害来源驱魔符，100%继承人物一切属性、天赋、神器特效，攻击和生命额外提高{1}%</t>
+    <t>召唤{0}只白虎战斗，技能伤害来源驱魔符，额外附带70%无视防御，100%继承人物一切属性、天赋、神器特效，攻击和生命额外提高{1}%</t>
   </si>
   <si>
     <t>定身指环</t>
@@ -1107,12 +1107,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -3545,7 +3545,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W17" s="1" t="s">
         <v>86</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -4870,7 +4870,7 @@
         <v>300</v>
       </c>
       <c r="Z30" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA30" s="1">
         <v>4</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -6174,7 +6174,7 @@
         <v>0</v>
       </c>
       <c r="Z43" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA43" s="1">
         <v>0</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -6162,7 +6162,7 @@
         <v>0</v>
       </c>
       <c r="V43" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W43" s="1" t="s">
         <v>86</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -840,7 +840,7 @@
     <t>召唤白虎</t>
   </si>
   <si>
-    <t>召唤{0}只白虎战斗，技能伤害来源驱魔符，额外附带70%无视防御，100%继承人物一切属性、天赋、神器特效，攻击和生命额外提高{1}%</t>
+    <t>召唤{0}只白虎战斗，技能伤害来源驱魔符，额外附带70%无视防御，100%继承人物一切属性、天赋、神器特效。攻击和生命额外提高{1}%</t>
   </si>
   <si>
     <t>定身指环</t>
@@ -6156,7 +6156,7 @@
         <v>500</v>
       </c>
       <c r="T43" s="1">
-        <v>4</v>
+        <v>500</v>
       </c>
       <c r="U43" s="1">
         <v>0</v>
@@ -6183,7 +6183,7 @@
         <v>0</v>
       </c>
       <c r="AC43" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD43" s="1">
         <v>0</v>
@@ -6595,7 +6595,7 @@
         <v>500</v>
       </c>
       <c r="T48" s="1">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="U48" s="1">
         <v>0</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -6183,7 +6183,7 @@
         <v>0</v>
       </c>
       <c r="AC43" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AD43" s="1">
         <v>0</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -3453,10 +3453,10 @@
         <v>5</v>
       </c>
       <c r="AA16" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB16" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC16" s="1">
         <v>500</v>
@@ -3560,10 +3560,10 @@
         <v>3</v>
       </c>
       <c r="AA17" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB17" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC17" s="1">
         <v>1000</v>
@@ -4658,10 +4658,10 @@
         <v>5</v>
       </c>
       <c r="AA28" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB28" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC28" s="1">
         <v>150</v>
@@ -4766,10 +4766,10 @@
         <v>5</v>
       </c>
       <c r="AA29" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB29" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC29" s="1">
         <v>500</v>
@@ -4873,10 +4873,10 @@
         <v>1</v>
       </c>
       <c r="AA30" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB30" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC30" s="1">
         <v>10</v>
@@ -6070,10 +6070,10 @@
         <v>5</v>
       </c>
       <c r="AA42" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB42" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC42" s="1">
         <v>500</v>
@@ -6580,7 +6580,7 @@
         <v>0</v>
       </c>
       <c r="O48" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P48" s="1">
         <v>3</v>
@@ -6601,25 +6601,25 @@
         <v>0</v>
       </c>
       <c r="V48" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W48" s="1" t="s">
         <v>86</v>
       </c>
       <c r="X48" s="1" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="Y48" s="1">
         <v>0</v>
       </c>
       <c r="Z48" s="1">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AA48" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB48" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC48" s="1">
         <v>500</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -6556,7 +6556,7 @@
         <v>192</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>192</v>
+        <v>156</v>
       </c>
       <c r="H48" s="1">
         <v>1</v>
@@ -6601,7 +6601,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W48" s="1" t="s">
         <v>86</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -762,7 +762,7 @@
     <t>火符术</t>
   </si>
   <si>
-    <t>对{0}个敌人造成{1}%道术伤害</t>
+    <t>对{0}个敌人造成{1}%道术伤害，无视70%防御</t>
   </si>
   <si>
     <t>毒咒术</t>
@@ -1107,12 +1107,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1585,10 +1585,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2061,7 +2061,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" ht="13.5" spans="3:38">
+    <row r="4" ht="13.5" spans="3:40">
       <c r="C4" s="3" t="s">
         <v>36</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" ht="13.5" spans="3:38">
+    <row r="5" ht="13.5" spans="3:40">
       <c r="C5" s="3" t="s">
         <v>67</v>
       </c>
@@ -2281,7 +2281,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="3:38">
+    <row r="6" s="1" customFormat="1" spans="3:40">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
@@ -2389,7 +2389,7 @@
         <v>4006</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" spans="3:38">
+    <row r="7" s="1" customFormat="1" spans="3:40">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
@@ -2497,7 +2497,7 @@
         <v>4006</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" spans="3:38">
+    <row r="8" s="1" customFormat="1" spans="3:40">
       <c r="C8" s="1">
         <v>1003</v>
       </c>
@@ -2608,7 +2608,7 @@
         <v>4006</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" spans="3:38">
+    <row r="9" s="1" customFormat="1" spans="3:40">
       <c r="C9" s="1">
         <v>1004</v>
       </c>
@@ -2719,7 +2719,7 @@
         <v>4006</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" spans="3:38">
+    <row r="10" s="1" customFormat="1" spans="3:40">
       <c r="C10" s="1">
         <v>1005</v>
       </c>
@@ -2820,7 +2820,7 @@
       <c r="AI10" s="1">
         <v>0</v>
       </c>
-      <c r="AJ10" s="7" t="s">
+      <c r="AJ10" s="4" t="s">
         <v>93</v>
       </c>
       <c r="AK10" s="1">
@@ -2830,7 +2830,7 @@
         <v>4006</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" spans="3:38">
+    <row r="11" s="1" customFormat="1" spans="3:40">
       <c r="C11" s="1">
         <v>1006</v>
       </c>
@@ -2938,7 +2938,7 @@
         <v>4006</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" spans="3:38">
+    <row r="12" s="1" customFormat="1" spans="3:40">
       <c r="C12" s="1">
         <v>1007</v>
       </c>
@@ -2972,7 +2972,7 @@
       <c r="M12" s="1">
         <v>0</v>
       </c>
-      <c r="N12" s="6">
+      <c r="N12" s="5">
         <v>5</v>
       </c>
       <c r="O12" s="1">
@@ -2991,7 +2991,7 @@
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="T12" s="6">
+      <c r="T12" s="5">
         <v>10</v>
       </c>
       <c r="U12" s="1">
@@ -3018,7 +3018,7 @@
       <c r="AB12" s="1">
         <v>0</v>
       </c>
-      <c r="AC12" s="6">
+      <c r="AC12" s="5">
         <v>500</v>
       </c>
       <c r="AD12" s="1">
@@ -3039,7 +3039,7 @@
       <c r="AI12" s="1">
         <v>0</v>
       </c>
-      <c r="AJ12" s="6" t="s">
+      <c r="AJ12" s="5" t="s">
         <v>100</v>
       </c>
       <c r="AK12" s="1">
@@ -3049,7 +3049,7 @@
         <v>4006</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" spans="3:38">
+    <row r="13" s="1" customFormat="1" spans="3:40">
       <c r="C13" s="1">
         <v>1008</v>
       </c>
@@ -3160,7 +3160,7 @@
         <v>4006</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" spans="3:38">
+    <row r="14" s="1" customFormat="1" spans="3:40">
       <c r="C14" s="1">
         <v>1009</v>
       </c>
@@ -3271,7 +3271,7 @@
         <v>4006</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" spans="3:38">
+    <row r="15" s="1" customFormat="1" spans="3:40">
       <c r="C15" s="1">
         <v>1010</v>
       </c>
@@ -3378,7 +3378,7 @@
         <v>4102</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" spans="3:38">
+    <row r="16" s="1" customFormat="1" spans="3:40">
       <c r="C16" s="1">
         <v>1011</v>
       </c>
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" spans="7:7">
+    <row r="18" s="1" customFormat="1" spans="3:38">
       <c r="G18" s="2"/>
     </row>
     <row r="19" s="1" customFormat="1" spans="3:38">
@@ -4132,7 +4132,7 @@
       <c r="AI23" s="1">
         <v>0</v>
       </c>
-      <c r="AJ23" s="7" t="s">
+      <c r="AJ23" s="4" t="s">
         <v>93</v>
       </c>
       <c r="AK23" s="1">
@@ -4284,7 +4284,7 @@
       <c r="M25" s="1">
         <v>0</v>
       </c>
-      <c r="N25" s="6">
+      <c r="N25" s="5">
         <v>5</v>
       </c>
       <c r="O25" s="1">
@@ -4303,7 +4303,7 @@
         <f t="shared" si="1"/>
         <v>3000</v>
       </c>
-      <c r="T25" s="6">
+      <c r="T25" s="5">
         <v>6</v>
       </c>
       <c r="U25" s="1">
@@ -4330,7 +4330,7 @@
       <c r="AB25" s="1">
         <v>3</v>
       </c>
-      <c r="AC25" s="6">
+      <c r="AC25" s="5">
         <v>300</v>
       </c>
       <c r="AD25" s="1">
@@ -4351,7 +4351,7 @@
       <c r="AI25" s="1">
         <v>0</v>
       </c>
-      <c r="AJ25" s="6" t="s">
+      <c r="AJ25" s="5" t="s">
         <v>134</v>
       </c>
       <c r="AK25" s="1">
@@ -4906,7 +4906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" spans="7:7">
+    <row r="31" s="1" customFormat="1" spans="3:38">
       <c r="G31" s="2"/>
     </row>
     <row r="32" s="1" customFormat="1" spans="3:38">
@@ -5103,7 +5103,7 @@
         <v>0</v>
       </c>
       <c r="AE33" s="1">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF33" s="1">
         <v>0</v>
@@ -5444,7 +5444,7 @@
       <c r="AI36" s="1">
         <v>0</v>
       </c>
-      <c r="AJ36" s="7" t="s">
+      <c r="AJ36" s="4" t="s">
         <v>93</v>
       </c>
       <c r="AK36" s="1">
@@ -6210,7 +6210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" s="1" customFormat="1" spans="6:7">
+    <row r="44" s="1" customFormat="1" spans="3:38">
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
     </row>
@@ -6224,10 +6224,10 @@
       <c r="E45" s="1">
         <v>0</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="F45" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="G45" s="5" t="s">
+      <c r="G45" s="7" t="s">
         <v>182</v>
       </c>
       <c r="H45" s="1">
@@ -6334,10 +6334,10 @@
       <c r="E46" s="1">
         <v>0</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="F46" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="G46" s="5" t="s">
+      <c r="G46" s="7" t="s">
         <v>186</v>
       </c>
       <c r="H46" s="1">
@@ -6424,7 +6424,7 @@
       <c r="AI46" s="1">
         <v>0</v>
       </c>
-      <c r="AJ46" s="7"/>
+      <c r="AJ46" s="4"/>
       <c r="AK46" s="1">
         <v>99999</v>
       </c>
@@ -6442,10 +6442,10 @@
       <c r="E47" s="1">
         <v>0</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="F47" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="G47" s="5" t="s">
+      <c r="G47" s="7" t="s">
         <v>189</v>
       </c>
       <c r="H47" s="1">
@@ -6642,7 +6642,7 @@
       <c r="AI48" s="1">
         <v>0</v>
       </c>
-      <c r="AJ48" s="6"/>
+      <c r="AJ48" s="5"/>
       <c r="AK48" s="1">
         <v>50</v>
       </c>
@@ -6650,7 +6650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" s="1" customFormat="1" spans="6:7">
+    <row r="49" s="1" customFormat="1" spans="3:38">
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
     </row>
@@ -7883,7 +7883,7 @@
       <c r="AI63" s="1">
         <v>0</v>
       </c>
-      <c r="AJ63" s="7"/>
+      <c r="AJ63" s="4"/>
       <c r="AK63" s="1">
         <v>50</v>
       </c>
@@ -8591,7 +8591,7 @@
       <c r="AI70" s="1">
         <v>0</v>
       </c>
-      <c r="AJ70" s="7"/>
+      <c r="AJ70" s="4"/>
       <c r="AK70" s="1">
         <v>50</v>
       </c>
@@ -9299,7 +9299,7 @@
       <c r="AI77" s="1">
         <v>0</v>
       </c>
-      <c r="AJ77" s="7"/>
+      <c r="AJ77" s="4"/>
       <c r="AK77" s="1">
         <v>50</v>
       </c>
@@ -9509,7 +9509,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="80" s="1" customFormat="1" spans="6:21">
+    <row r="80" s="1" customFormat="1" spans="3:38">
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
       <c r="L80" s="2"/>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -298,7 +298,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="207">
+  <si>
+    <t>#</t>
+  </si>
   <si>
     <t>_ID</t>
   </si>
@@ -405,9 +408,6 @@
     <t>UpItemId</t>
   </si>
   <si>
-    <t>#</t>
-  </si>
-  <si>
     <t>Id</t>
   </si>
   <si>
@@ -880,6 +880,9 @@
   </si>
   <si>
     <t>对{3}*{4}范围内的敌人造成驱魔符伤害*火符弹射次数*{1}%，额外附带70%无视伤害</t>
+  </si>
+  <si>
+    <t>"101,0,0,10"</t>
   </si>
   <si>
     <t>普攻</t>
@@ -1107,12 +1110,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1908,7 +1911,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:AN81"/>
+  <dimension ref="C1:AN81"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="5.625" style="2" customWidth="1"/>
@@ -1945,120 +1948,130 @@
     <col min="41" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
+    <row r="1" spans="3:40">
+      <c r="AM1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="3:40">
+      <c r="AM2" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
     <row r="3" ht="13.5" spans="3:40">
       <c r="C3" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA3" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB3" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AC3" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AD3" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE3" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF3" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG3" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AH3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AI3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AJ3" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AK3" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AL3" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AM3" s="2" t="s">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="AN3" s="2" t="s">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" ht="13.5" spans="3:40">
@@ -2069,7 +2082,7 @@
         <v>37</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>38</v>
@@ -2093,7 +2106,7 @@
         <v>44</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>45</v>
@@ -2108,10 +2121,10 @@
         <v>48</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T4" s="3" t="s">
         <v>49</v>
@@ -2168,7 +2181,7 @@
         <v>66</v>
       </c>
       <c r="AL4" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" ht="13.5" spans="3:40">
@@ -5016,7 +5029,7 @@
         <v>4006</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" spans="3:38">
+    <row r="33" s="1" customFormat="1" spans="3:39">
       <c r="C33" s="1">
         <v>3002</v>
       </c>
@@ -5124,7 +5137,7 @@
         <v>4006</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" spans="3:38">
+    <row r="34" s="1" customFormat="1" spans="3:39">
       <c r="C34" s="1">
         <v>3003</v>
       </c>
@@ -5235,7 +5248,7 @@
         <v>4006</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" spans="3:38">
+    <row r="35" s="1" customFormat="1" spans="3:39">
       <c r="C35" s="1">
         <v>3004</v>
       </c>
@@ -5343,7 +5356,7 @@
         <v>4006</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" spans="3:38">
+    <row r="36" s="1" customFormat="1" spans="3:39">
       <c r="C36" s="1">
         <v>3005</v>
       </c>
@@ -5454,7 +5467,7 @@
         <v>4006</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" spans="3:38">
+    <row r="37" s="1" customFormat="1" spans="3:39">
       <c r="C37" s="1">
         <v>3006</v>
       </c>
@@ -5562,7 +5575,7 @@
         <v>4006</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" spans="3:38">
+    <row r="38" s="1" customFormat="1" spans="3:39">
       <c r="C38" s="1">
         <v>3007</v>
       </c>
@@ -5670,7 +5683,7 @@
         <v>4006</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" spans="3:38">
+    <row r="39" s="1" customFormat="1" spans="3:39">
       <c r="C39" s="1">
         <v>3008</v>
       </c>
@@ -5781,7 +5794,7 @@
         <v>4006</v>
       </c>
     </row>
-    <row r="40" s="1" customFormat="1" spans="3:38">
+    <row r="40" s="1" customFormat="1" spans="3:39">
       <c r="C40" s="1">
         <v>3009</v>
       </c>
@@ -5888,7 +5901,7 @@
         <v>4006</v>
       </c>
     </row>
-    <row r="41" s="1" customFormat="1" spans="3:38">
+    <row r="41" s="1" customFormat="1" spans="3:39">
       <c r="C41" s="1">
         <v>3010</v>
       </c>
@@ -5995,7 +6008,7 @@
         <v>4102</v>
       </c>
     </row>
-    <row r="42" s="1" customFormat="1" spans="3:38">
+    <row r="42" s="1" customFormat="1" spans="3:39">
       <c r="C42" s="1">
         <v>3011</v>
       </c>
@@ -6103,7 +6116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" s="1" customFormat="1" spans="3:38">
+    <row r="43" s="1" customFormat="1" spans="3:39">
       <c r="C43" s="1">
         <v>3012</v>
       </c>
@@ -6210,11 +6223,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" s="1" customFormat="1" spans="3:38">
+    <row r="44" s="1" customFormat="1" spans="3:39">
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
     </row>
-    <row r="45" s="1" customFormat="1" spans="3:38">
+    <row r="45" s="1" customFormat="1" spans="3:39">
       <c r="C45" s="1">
         <v>4001</v>
       </c>
@@ -6324,7 +6337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" s="1" customFormat="1" spans="3:38">
+    <row r="46" s="1" customFormat="1" spans="3:39">
       <c r="C46" s="1">
         <v>4002</v>
       </c>
@@ -6432,7 +6445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" s="1" customFormat="1" spans="3:38">
+    <row r="47" s="1" customFormat="1" spans="3:39">
       <c r="C47" s="1">
         <v>4003</v>
       </c>
@@ -6542,7 +6555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" s="1" customFormat="1" spans="3:38">
+    <row r="48" s="1" customFormat="1" spans="3:39">
       <c r="C48" s="1">
         <v>4004</v>
       </c>
@@ -6642,12 +6655,14 @@
       <c r="AI48" s="1">
         <v>0</v>
       </c>
-      <c r="AJ48" s="5"/>
       <c r="AK48" s="1">
         <v>50</v>
       </c>
       <c r="AL48" s="1">
         <v>0</v>
+      </c>
+      <c r="AM48" s="1" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" spans="3:38">
@@ -6665,10 +6680,10 @@
         <v>0</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H50" s="1">
         <v>9</v>
@@ -6766,10 +6781,10 @@
         <v>0</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H51" s="1">
         <v>9</v>
@@ -6868,25 +6883,25 @@
         <v>0</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G53" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H53" s="1">
+        <v>1</v>
+      </c>
+      <c r="I53" s="1">
+        <v>0</v>
+      </c>
+      <c r="J53" s="1">
+        <v>0</v>
+      </c>
+      <c r="K53" s="1">
+        <v>1</v>
+      </c>
+      <c r="L53" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="H53" s="1">
-        <v>1</v>
-      </c>
-      <c r="I53" s="1">
-        <v>0</v>
-      </c>
-      <c r="J53" s="1">
-        <v>0</v>
-      </c>
-      <c r="K53" s="1">
-        <v>1</v>
-      </c>
-      <c r="L53" s="1" t="s">
-        <v>196</v>
       </c>
       <c r="M53" s="1">
         <v>0</v>
@@ -6972,10 +6987,10 @@
         <v>0</v>
       </c>
       <c r="F54" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="G54" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>197</v>
       </c>
       <c r="H54" s="2">
         <v>4</v>
@@ -6990,7 +7005,7 @@
         <v>10</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M54" s="1">
         <v>0</v>
@@ -7078,10 +7093,10 @@
         <v>0</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H55" s="2">
         <v>1</v>
@@ -7096,7 +7111,7 @@
         <v>1</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M55" s="1">
         <v>0</v>
@@ -7184,10 +7199,10 @@
         <v>0</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H56" s="2">
         <v>4</v>
@@ -7202,7 +7217,7 @@
         <v>10</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M56" s="1">
         <v>0</v>
@@ -7233,7 +7248,7 @@
         <v>3</v>
       </c>
       <c r="W56" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="X56" s="2" t="s">
         <v>92</v>
@@ -7289,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>76</v>
@@ -7307,7 +7322,7 @@
         <v>10</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M57" s="1">
         <v>0</v>
@@ -7780,7 +7795,7 @@
         <v>0</v>
       </c>
       <c r="AJ62" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AK62" s="1">
         <v>50</v>
@@ -9615,7 +9630,7 @@
         <v>0</v>
       </c>
       <c r="AJ81" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AK81" s="1">
         <v>50</v>
